--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -734,13 +734,13 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>318.96</v>
+        <v>316.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>361.43</v>
+        <v>330.05</v>
       </c>
       <c r="Z2" t="n">
-        <v>361.43</v>
+        <v>291.87</v>
       </c>
       <c r="AA2" t="n">
         <v>313.17</v>
@@ -781,10 +781,10 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>334.78</v>
+        <v>335.64</v>
       </c>
       <c r="AN2" t="n">
-        <v>313.45</v>
+        <v>312.05</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>361.43</v>
+        <v>291.87</v>
       </c>
     </row>
     <row r="3">
@@ -883,31 +883,31 @@
         <v>12.29</v>
       </c>
       <c r="R3" t="n">
-        <v>47.3</v>
+        <v>47.5</v>
       </c>
       <c r="S3" t="n">
         <v>0.21</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.51</v>
+        <v>-1.5</v>
       </c>
       <c r="U3" t="n">
         <v>60.7</v>
       </c>
       <c r="V3" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>483.68</v>
+        <v>479.56</v>
       </c>
       <c r="Y3" t="n">
-        <v>512.71</v>
+        <v>500.48</v>
       </c>
       <c r="Z3" t="n">
-        <v>512.71</v>
+        <v>471.66</v>
       </c>
       <c r="AA3" t="n">
         <v>470.96</v>
@@ -948,10 +948,10 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>504.45</v>
+        <v>504.34</v>
       </c>
       <c r="AN3" t="n">
-        <v>475.24</v>
+        <v>474.93</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>512.71</v>
+        <v>471.66</v>
       </c>
     </row>
     <row r="4">
@@ -1050,13 +1050,13 @@
         <v>12.29</v>
       </c>
       <c r="R4" t="n">
-        <v>46.4</v>
+        <v>45.9</v>
       </c>
       <c r="S4" t="n">
         <v>0.18</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.9</v>
+        <v>-1.93</v>
       </c>
       <c r="U4" t="n">
         <v>52.5</v>
@@ -1068,13 +1068,13 @@
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>3254.88</v>
+        <v>3227.15</v>
       </c>
       <c r="Y4" t="n">
-        <v>3293.11</v>
+        <v>4081.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>2650.75</v>
+        <v>4081.14</v>
       </c>
       <c r="AA4" t="n">
         <v>3127.14</v>
@@ -1103,7 +1103,7 @@
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>54.6</v>
+        <v>54.1</v>
       </c>
       <c r="AJ4" t="n">
         <v>85.3</v>
@@ -1115,14 +1115,14 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>3406.85</v>
+        <v>3414.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>3164.87</v>
+        <v>3154.92</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 54.65, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1137,21 +1137,21 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[3276.0, 3296.03, 3316.06, 3336.1, 3356.13, 3376.16]</t>
+          <t>[3276.0, 3296.0, 3316.0, 3336.0, 3356.0, 3376.01]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[3276.0, 3335.73, 3372.2, 3404.85, 3435.52, 3464.92]</t>
+          <t>[3276.0, 3335.7, 3372.14, 3404.76, 3435.4, 3464.77]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[3276.0, 3266.26, 3273.96, 3284.53, 3296.58, 3309.58]</t>
+          <t>[3276.0, 3266.23, 3273.9, 3284.43, 3296.46, 3309.43]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2650.75</v>
+        <v>4081.14</v>
       </c>
     </row>
     <row r="5">
@@ -1217,13 +1217,13 @@
         <v>12.29</v>
       </c>
       <c r="R5" t="n">
-        <v>45.9</v>
+        <v>45.4</v>
       </c>
       <c r="S5" t="n">
         <v>0.19</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.71</v>
+        <v>-1.74</v>
       </c>
       <c r="U5" t="n">
         <v>52.5</v>
@@ -1235,13 +1235,13 @@
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>1009.53</v>
+        <v>1000.89</v>
       </c>
       <c r="Y5" t="n">
-        <v>1021.74</v>
+        <v>1109.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>957.6</v>
+        <v>1109.16</v>
       </c>
       <c r="AA5" t="n">
         <v>984.23</v>
@@ -1282,10 +1282,10 @@
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1067.86</v>
+        <v>1066.02</v>
       </c>
       <c r="AN5" t="n">
-        <v>990.61</v>
+        <v>989.28</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>957.6</v>
+        <v>1109.16</v>
       </c>
     </row>
     <row r="6">
@@ -1402,13 +1402,13 @@
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2137.15</v>
+        <v>2118.92</v>
       </c>
       <c r="Y6" t="n">
-        <v>2162.34</v>
+        <v>2210.94</v>
       </c>
       <c r="Z6" t="n">
-        <v>2159.29</v>
+        <v>2164.91</v>
       </c>
       <c r="AA6" t="n">
         <v>2065.4</v>
@@ -1449,10 +1449,10 @@
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>2210.36</v>
+        <v>2214.74</v>
       </c>
       <c r="AN6" t="n">
-        <v>2094.98</v>
+        <v>2098.63</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[2153.5, 2164.21, 2174.92, 2185.64, 2196.35, 2207.06]</t>
+          <t>[2153.5, 2164.16, 2174.82, 2185.48, 2196.14, 2206.8]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2153.5, 2187.71, 2208.15, 2226.33, 2243.34, 2259.59]</t>
+          <t>[2153.5, 2187.65, 2208.05, 2226.17, 2243.13, 2259.34]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2153.5, 2146.59, 2150.01, 2155.12, 2161.11, 2167.66]</t>
+          <t>[2153.5, 2146.54, 2149.9, 2154.96, 2160.9, 2167.41]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>2159.29</v>
+        <v>2164.91</v>
       </c>
     </row>
     <row r="7">
@@ -1551,13 +1551,13 @@
         <v>12.29</v>
       </c>
       <c r="R7" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="S7" t="n">
         <v>0.21</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.79</v>
+        <v>-1.81</v>
       </c>
       <c r="U7" t="n">
         <v>47.5</v>
@@ -1569,13 +1569,13 @@
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>429.28</v>
+        <v>425.63</v>
       </c>
       <c r="Y7" t="n">
-        <v>434.29</v>
+        <v>444.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>432.25</v>
+        <v>433.44</v>
       </c>
       <c r="AA7" t="n">
         <v>413.41</v>
@@ -1616,10 +1616,10 @@
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>447.86</v>
+        <v>447.57</v>
       </c>
       <c r="AN7" t="n">
-        <v>415.88</v>
+        <v>416.69</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>432.25</v>
+        <v>433.44</v>
       </c>
     </row>
     <row r="8">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>134180.11</v>
+        <v>416806.78</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1680,146 +1680,146 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>116.75</v>
+        <v>419</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹116.33 - ₹117.37</t>
+          <t>₹417.59 - ₹421.11</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>118.42</v>
+        <v>424.62</v>
       </c>
       <c r="I8" t="n">
-        <v>115.78</v>
+        <v>405.16</v>
       </c>
       <c r="J8" t="n">
-        <v>112.52</v>
+        <v>396.17</v>
       </c>
       <c r="K8" t="n">
-        <v>112.43</v>
+        <v>400</v>
       </c>
       <c r="L8" t="n">
-        <v>3.93</v>
+        <v>4.14</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8</v>
+        <v>7.02</v>
       </c>
       <c r="N8" t="n">
-        <v>1.06</v>
+        <v>7.53</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.26</v>
+        <v>-0.52</v>
       </c>
       <c r="P8" t="n">
-        <v>2.08</v>
+        <v>7.03</v>
       </c>
       <c r="Q8" t="n">
         <v>12.29</v>
       </c>
       <c r="R8" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.13</v>
+        <v>-0.95</v>
       </c>
       <c r="U8" t="n">
-        <v>52.5</v>
+        <v>50.8</v>
       </c>
       <c r="V8" t="n">
-        <v>2.49</v>
+        <v>3.96</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>115.96</v>
+        <v>410.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>118.63</v>
+        <v>428.17</v>
       </c>
       <c r="Z8" t="n">
-        <v>118.63</v>
+        <v>413.48</v>
       </c>
       <c r="AA8" t="n">
-        <v>113.63</v>
+        <v>408.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>116.35</v>
+        <v>416.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>118.18</v>
+        <v>422.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>119.62</v>
+        <v>426.83</v>
       </c>
       <c r="AE8" t="n">
-        <v>51.3</v>
+        <v>62.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.1</v>
+        <v>20.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15.2</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
-        <v>38.1</v>
+        <v>28.5</v>
       </c>
       <c r="AL8" t="n">
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>120.03</v>
+        <v>427.8</v>
       </c>
       <c r="AN8" t="n">
-        <v>113.79</v>
+        <v>409.47</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,180.11 Cr., a P/E ratio of 6.07, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹416,806.78 Cr., a P/E ratio of 20.53, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.30 (Consolidation Zone), while MACD Line (0.80) trades below Signal (1.06) with an expanding histogram (-0.26). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.93% above the 200-day DMA (₹112.43). Daily volatility envelope is bounded by ATR(14) of ₹2.08.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (7.02) trades below Signal (7.53) with an expanding histogram (-0.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹400.00). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.75) is positioned above the 30-day DMA (₹115.78), 50-day DMA (₹112.52), and 200-day DMA (₹112.43). The price distance from 200 DMA is +3.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹419.00) is positioned above the 30-day DMA (₹405.16), 50-day DMA (₹396.17), and 200-day DMA (₹400.00). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[116.75, 117.43, 118.11, 118.79, 119.47, 120.15]</t>
+          <t>[419.0, 420.26, 421.51, 422.77, 424.03, 425.28]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[116.75, 118.26, 119.29, 120.23, 121.13, 122.01]</t>
+          <t>[419.0, 423.07, 425.49, 427.64, 429.65, 431.57]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[116.75, 116.81, 117.23, 117.71, 118.22, 118.75]</t>
+          <t>[419.0, 418.15, 418.53, 419.12, 419.81, 420.57]</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>118.63</v>
+        <v>413.48</v>
       </c>
     </row>
     <row r="9">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>416806.78</v>
+        <v>30963.05</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1847,146 +1847,146 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>419</v>
+        <v>562.9</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹417.59 - ₹421.11</t>
+          <t>₹559.68 - ₹567.73</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>424.62</v>
+        <v>575.79</v>
       </c>
       <c r="I9" t="n">
-        <v>405.16</v>
+        <v>515.35</v>
       </c>
       <c r="J9" t="n">
-        <v>396.17</v>
+        <v>523.51</v>
       </c>
       <c r="K9" t="n">
-        <v>400</v>
+        <v>523.36</v>
       </c>
       <c r="L9" t="n">
-        <v>4.14</v>
+        <v>5.53</v>
       </c>
       <c r="M9" t="n">
-        <v>7.02</v>
+        <v>12.09</v>
       </c>
       <c r="N9" t="n">
-        <v>7.53</v>
+        <v>6.96</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.52</v>
+        <v>5.13</v>
       </c>
       <c r="P9" t="n">
-        <v>7.03</v>
+        <v>16.11</v>
       </c>
       <c r="Q9" t="n">
         <v>12.29</v>
       </c>
       <c r="R9" t="n">
-        <v>47</v>
+        <v>46.3</v>
       </c>
       <c r="S9" t="n">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.96</v>
+        <v>-2.06</v>
       </c>
       <c r="U9" t="n">
-        <v>50.8</v>
+        <v>45</v>
       </c>
       <c r="V9" t="n">
-        <v>3.96</v>
+        <v>4.79</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>413.81</v>
+        <v>542.86</v>
       </c>
       <c r="Y9" t="n">
-        <v>427.99</v>
+        <v>572.1900000000001</v>
       </c>
       <c r="Z9" t="n">
-        <v>427.99</v>
+        <v>572.1900000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>408.46</v>
+        <v>538.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>416.08</v>
+        <v>560.42</v>
       </c>
       <c r="AC9" t="n">
-        <v>422.91</v>
+        <v>574.84</v>
       </c>
       <c r="AD9" t="n">
-        <v>426.83</v>
+        <v>586.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>62.6</v>
+        <v>78</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>20.5</v>
+        <v>5.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>28.5</v>
+        <v>65.2</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>428.98</v>
+        <v>577.48</v>
       </c>
       <c r="AN9" t="n">
-        <v>409.32</v>
+        <v>548.35</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹416,806.78 Cr., a P/E ratio of 20.53, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,963.05 Cr., a P/E ratio of 5.40, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (7.02) trades below Signal (7.53) with an expanding histogram (-0.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹400.00). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.98 (Bullish Momentum Zone), while MACD Line (12.09) trades above Signal (6.96) with an expanding histogram (+5.13). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.53% above the 200-day DMA (₹523.36). Daily volatility envelope is bounded by ATR(14) of ₹16.11.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹419.00) is positioned above the 30-day DMA (₹405.16), 50-day DMA (₹396.17), and 200-day DMA (₹400.00). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹562.90) is positioned above the 30-day DMA (₹515.35), 50-day DMA (₹523.51), and 200-day DMA (₹523.36). The price distance from 200 DMA is +5.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[419.0, 420.26, 421.51, 422.77, 424.03, 425.28]</t>
+          <t>[562.9, 564.59, 566.28, 567.97, 569.65, 571.34]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[419.0, 423.07, 425.49, 427.64, 429.65, 431.57]</t>
+          <t>[562.9, 571.03, 575.39, 579.13, 582.54, 585.75]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[419.0, 418.15, 418.53, 419.12, 419.81, 420.57]</t>
+          <t>[562.9, 559.76, 559.44, 559.6, 559.99, 560.54]</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>427.99</v>
+        <v>572.1900000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2052,7 +2052,7 @@
         <v>12.29</v>
       </c>
       <c r="R10" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
       <c r="S10" t="n">
         <v>0.26</v>
@@ -2070,13 +2070,13 @@
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>282.97</v>
+        <v>280.58</v>
       </c>
       <c r="Y10" t="n">
-        <v>286.38</v>
+        <v>296.54</v>
       </c>
       <c r="Z10" t="n">
-        <v>280.38</v>
+        <v>296.54</v>
       </c>
       <c r="AA10" t="n">
         <v>278.48</v>
@@ -2117,10 +2117,10 @@
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>295.71</v>
+        <v>295.73</v>
       </c>
       <c r="AN10" t="n">
-        <v>278.99</v>
+        <v>278.59</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>280.38</v>
+        <v>296.54</v>
       </c>
     </row>
     <row r="11">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>83053.21000000001</v>
+        <v>134180.11</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2181,146 +2181,146 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1797.3</v>
+        <v>116.75</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹1787.84 - ₹1811.5</t>
+          <t>₹116.33 - ₹117.37</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1835.16</v>
+        <v>118.42</v>
       </c>
       <c r="I11" t="n">
-        <v>1748.18</v>
+        <v>115.78</v>
       </c>
       <c r="J11" t="n">
-        <v>1680.74</v>
+        <v>112.52</v>
       </c>
       <c r="K11" t="n">
-        <v>1651.86</v>
+        <v>112.43</v>
       </c>
       <c r="L11" t="n">
-        <v>8.970000000000001</v>
+        <v>3.93</v>
       </c>
       <c r="M11" t="n">
-        <v>42.02</v>
+        <v>0.8</v>
       </c>
       <c r="N11" t="n">
-        <v>50.65</v>
+        <v>1.06</v>
       </c>
       <c r="O11" t="n">
-        <v>-8.630000000000001</v>
+        <v>-0.26</v>
       </c>
       <c r="P11" t="n">
-        <v>47.32</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
         <v>12.29</v>
       </c>
       <c r="R11" t="n">
-        <v>45.7</v>
+        <v>44.6</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.9</v>
+        <v>-1.12</v>
       </c>
       <c r="U11" t="n">
-        <v>55</v>
+        <v>52.5</v>
       </c>
       <c r="V11" t="n">
-        <v>5.59</v>
+        <v>2.49</v>
       </c>
       <c r="W11" t="n">
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>1783.33</v>
+        <v>114.98</v>
       </c>
       <c r="Y11" t="n">
-        <v>1820.18</v>
+        <v>119.96</v>
       </c>
       <c r="Z11" t="n">
-        <v>1820.18</v>
+        <v>115.81</v>
       </c>
       <c r="AA11" t="n">
-        <v>1726.32</v>
+        <v>113.63</v>
       </c>
       <c r="AB11" t="n">
-        <v>1789.3</v>
+        <v>116.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>1821.3</v>
+        <v>118.18</v>
       </c>
       <c r="AD11" t="n">
-        <v>1845.3</v>
+        <v>119.62</v>
       </c>
       <c r="AE11" t="n">
-        <v>53.1</v>
+        <v>51.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.19</v>
+        <v>-0.09</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH11" t="n">
         <v>0.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>111.1</v>
+        <v>6.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>40.1</v>
+        <v>15.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>10.2</v>
+        <v>38.1</v>
       </c>
       <c r="AL11" t="n">
         <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>1857.46</v>
+        <v>120.03</v>
       </c>
       <c r="AN11" t="n">
-        <v>1738.02</v>
+        <v>113.35</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹83,053.21 Cr., a P/E ratio of 111.08, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,180.11 Cr., a P/E ratio of 6.07, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.10 (Consolidation Zone), while MACD Line (42.02) trades below Signal (50.65) with an expanding histogram (-8.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.97% above the 200-day DMA (₹1651.86). Daily volatility envelope is bounded by ATR(14) of ₹47.32.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.30 (Consolidation Zone), while MACD Line (0.80) trades below Signal (1.06) with an expanding histogram (-0.26). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.93% above the 200-day DMA (₹112.43). Daily volatility envelope is bounded by ATR(14) of ₹2.08.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,797.30) is positioned above the 30-day DMA (₹1,748.18), 50-day DMA (₹1,680.74), and 200-day DMA (₹1,651.86). The price distance from 200 DMA is +8.97%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.75) is positioned above the 30-day DMA (₹115.78), 50-day DMA (₹112.52), and 200-day DMA (₹112.43). The price distance from 200 DMA is +3.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[1797.3, 1805.91, 1814.52, 1823.13, 1831.75, 1840.36]</t>
+          <t>[116.75, 117.43, 118.11, 118.79, 119.47, 120.15]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[1797.3, 1824.84, 1841.29, 1855.92, 1869.6, 1882.68]</t>
+          <t>[116.75, 118.26, 119.29, 120.23, 121.13, 122.01]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[1797.3, 1791.71, 1794.45, 1798.55, 1803.35, 1808.61]</t>
+          <t>[116.75, 116.8, 117.23, 117.71, 118.22, 118.75]</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>1820.18</v>
+        <v>115.81</v>
       </c>
     </row>
     <row r="12">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>30963.05</v>
+        <v>83053.21000000001</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2348,87 +2348,87 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>562.9</v>
+        <v>1797.3</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹559.68 - ₹567.73</t>
+          <t>₹1787.84 - ₹1811.5</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>575.79</v>
+        <v>1835.16</v>
       </c>
       <c r="I12" t="n">
-        <v>515.35</v>
+        <v>1748.18</v>
       </c>
       <c r="J12" t="n">
-        <v>523.51</v>
+        <v>1680.74</v>
       </c>
       <c r="K12" t="n">
-        <v>523.36</v>
+        <v>1651.86</v>
       </c>
       <c r="L12" t="n">
-        <v>5.53</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>12.09</v>
+        <v>42.02</v>
       </c>
       <c r="N12" t="n">
-        <v>6.96</v>
+        <v>50.65</v>
       </c>
       <c r="O12" t="n">
-        <v>5.13</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="P12" t="n">
-        <v>16.11</v>
+        <v>47.32</v>
       </c>
       <c r="Q12" t="n">
         <v>12.29</v>
       </c>
       <c r="R12" t="n">
-        <v>43.6</v>
+        <v>43.2</v>
       </c>
       <c r="S12" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.07</v>
+        <v>-1.9</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>4.79</v>
+        <v>5.59</v>
       </c>
       <c r="W12" t="n">
         <v>-0.77</v>
       </c>
       <c r="X12" t="n">
-        <v>547.52</v>
+        <v>1768.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>558.1900000000001</v>
+        <v>1844.95</v>
       </c>
       <c r="Z12" t="n">
-        <v>558.1900000000001</v>
+        <v>1788.91</v>
       </c>
       <c r="AA12" t="n">
-        <v>538.74</v>
+        <v>1726.32</v>
       </c>
       <c r="AB12" t="n">
-        <v>560.42</v>
+        <v>1789.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>574.84</v>
+        <v>1821.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>586.77</v>
+        <v>1845.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>78</v>
+        <v>53.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.26</v>
+        <v>0.19</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2439,55 +2439,55 @@
         <v>0.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.3</v>
+        <v>111.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>14.5</v>
+        <v>40.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>65.2</v>
+        <v>10.2</v>
       </c>
       <c r="AL12" t="n">
         <v>15</v>
       </c>
       <c r="AM12" t="n">
-        <v>577.58</v>
+        <v>1856.16</v>
       </c>
       <c r="AN12" t="n">
-        <v>549.21</v>
+        <v>1740.66</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,963.05 Cr., a P/E ratio of 5.29, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹83,053.21 Cr., a P/E ratio of 111.08, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.98 (Bullish Momentum Zone), while MACD Line (12.09) trades above Signal (6.96) with an expanding histogram (+5.13). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.53% above the 200-day DMA (₹523.36). Daily volatility envelope is bounded by ATR(14) of ₹16.11.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.10 (Consolidation Zone), while MACD Line (42.02) trades below Signal (50.65) with an expanding histogram (-8.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.97% above the 200-day DMA (₹1651.86). Daily volatility envelope is bounded by ATR(14) of ₹47.32.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹562.90) is positioned above the 30-day DMA (₹515.35), 50-day DMA (₹523.51), and 200-day DMA (₹523.36). The price distance from 200 DMA is +5.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,797.30) is positioned above the 30-day DMA (₹1,748.18), 50-day DMA (₹1,680.74), and 200-day DMA (₹1,651.86). The price distance from 200 DMA is +8.97%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>[562.9, 564.59, 566.28, 567.97, 569.65, 571.34]</t>
+          <t>[1797.3, 1805.91, 1814.52, 1823.13, 1831.75, 1840.36]</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[562.9, 571.03, 575.39, 579.13, 582.54, 585.75]</t>
+          <t>[1797.3, 1824.84, 1841.29, 1855.92, 1869.6, 1882.68]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[562.9, 559.76, 559.44, 559.6, 559.99, 560.54]</t>
+          <t>[1797.3, 1791.71, 1794.45, 1798.55, 1803.35, 1808.61]</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>558.1900000000001</v>
+        <v>1788.91</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -716,28 +716,28 @@
         <v>12.29</v>
       </c>
       <c r="R2" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
       <c r="S2" t="n">
         <v>0.25</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.15</v>
+        <v>-1.12</v>
       </c>
       <c r="U2" t="n">
         <v>50</v>
       </c>
       <c r="V2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>316.25</v>
+        <v>313.87</v>
       </c>
       <c r="Y2" t="n">
-        <v>330.05</v>
+        <v>327.66</v>
       </c>
       <c r="Z2" t="n">
         <v>291.87</v>
@@ -781,10 +781,10 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>335.64</v>
+        <v>334.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>312.05</v>
+        <v>312.38</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -883,28 +883,28 @@
         <v>12.29</v>
       </c>
       <c r="R3" t="n">
-        <v>47.5</v>
+        <v>48.4</v>
       </c>
       <c r="S3" t="n">
         <v>0.21</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5</v>
+        <v>-1.46</v>
       </c>
       <c r="U3" t="n">
-        <v>60.7</v>
+        <v>61.7</v>
       </c>
       <c r="V3" t="n">
-        <v>3.81</v>
+        <v>3.7</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>479.56</v>
+        <v>480.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>500.48</v>
+        <v>501.32</v>
       </c>
       <c r="Z3" t="n">
         <v>471.66</v>
@@ -948,10 +948,10 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>504.34</v>
+        <v>505.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>474.93</v>
+        <v>475</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1059,16 +1059,16 @@
         <v>-1.93</v>
       </c>
       <c r="U4" t="n">
-        <v>52.5</v>
+        <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>3.37</v>
+        <v>3.51</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>3227.15</v>
+        <v>3222.34</v>
       </c>
       <c r="Y4" t="n">
         <v>4081.14</v>
@@ -1115,10 +1115,10 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>3414.28</v>
+        <v>3413.16</v>
       </c>
       <c r="AN4" t="n">
-        <v>3154.92</v>
+        <v>3152.87</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[3276.0, 3296.0, 3316.0, 3336.0, 3356.0, 3376.01]</t>
+          <t>[3276.0, 3291.16, 3306.33, 3321.49, 3336.65, 3351.81]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[3276.0, 3335.7, 3372.14, 3404.76, 3435.4, 3464.77]</t>
+          <t>[3276.0, 3330.86, 3362.47, 3390.25, 3416.05, 3440.58]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[3276.0, 3266.23, 3273.9, 3284.43, 3296.46, 3309.43]</t>
+          <t>[3276.0, 3261.39, 3264.22, 3269.92, 3277.11, 3285.24]</t>
         </is>
       </c>
       <c r="AU4" t="n">
@@ -1217,25 +1217,25 @@
         <v>12.29</v>
       </c>
       <c r="R5" t="n">
-        <v>45.4</v>
+        <v>45.1</v>
       </c>
       <c r="S5" t="n">
         <v>0.19</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.74</v>
+        <v>-1.75</v>
       </c>
       <c r="U5" t="n">
-        <v>52.5</v>
+        <v>51.7</v>
       </c>
       <c r="V5" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>1000.89</v>
+        <v>1002.1</v>
       </c>
       <c r="Y5" t="n">
         <v>1109.16</v>
@@ -1282,10 +1282,10 @@
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1066.02</v>
+        <v>1065.18</v>
       </c>
       <c r="AN5" t="n">
-        <v>989.28</v>
+        <v>986.3099999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -1329,16 +1329,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59793.74</v>
+        <v>150076.93</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,146 +1346,146 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2153.5</v>
+        <v>431</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹2141.75 - ₹2171.12</t>
+          <t>₹428.65 - ₹434.52</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2200.49</v>
+        <v>440.38</v>
       </c>
       <c r="I6" t="n">
-        <v>2094.62</v>
+        <v>420.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1982.91</v>
+        <v>413.87</v>
       </c>
       <c r="K6" t="n">
-        <v>1948.54</v>
+        <v>337.32</v>
       </c>
       <c r="L6" t="n">
-        <v>12.64</v>
+        <v>27.33</v>
       </c>
       <c r="M6" t="n">
-        <v>60.53</v>
+        <v>4.4</v>
       </c>
       <c r="N6" t="n">
-        <v>71.01000000000001</v>
+        <v>4.67</v>
       </c>
       <c r="O6" t="n">
-        <v>-10.48</v>
+        <v>-0.27</v>
       </c>
       <c r="P6" t="n">
-        <v>58.73</v>
+        <v>11.73</v>
       </c>
       <c r="Q6" t="n">
         <v>12.29</v>
       </c>
       <c r="R6" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="S6" t="n">
         <v>0.2</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.78</v>
+        <v>-1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>50.8</v>
+        <v>46.7</v>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>3.66</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2118.92</v>
+        <v>424.93</v>
       </c>
       <c r="Y6" t="n">
-        <v>2210.94</v>
+        <v>443.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2164.91</v>
+        <v>433.19</v>
       </c>
       <c r="AA6" t="n">
-        <v>2065.4</v>
+        <v>413.41</v>
       </c>
       <c r="AB6" t="n">
-        <v>2146.5</v>
+        <v>427.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>2183.2</v>
+        <v>436.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>2212.9</v>
+        <v>442.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>57</v>
+        <v>59.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>48.5</v>
+        <v>61.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>8.5</v>
+        <v>40.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>2214.74</v>
+        <v>447.67</v>
       </c>
       <c r="AN6" t="n">
-        <v>2098.63</v>
+        <v>416.08</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹59,793.74 Cr., a P/E ratio of 48.55, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>BHEL operates in the Industrials sector. With an estimated Market Cap of ₹150,076.93 Cr., a P/E ratio of 61.75, and YoY Revenue Growth of +40.3%, the company demonstrates strong institutional backing, solid operating profit margins (6.76%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.04 (Bullish Momentum Zone), while MACD Line (60.53) trades below Signal (71.01) with an expanding histogram (-10.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.64% above the 200-day DMA (₹1948.54). Daily volatility envelope is bounded by ATR(14) of ₹58.73.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.15 (Bullish Momentum Zone), while MACD Line (4.40) trades below Signal (4.67) with an expanding histogram (-0.27). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.33% above the 200-day DMA (₹337.32). Daily volatility envelope is bounded by ATR(14) of ₹11.73.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,153.50) is positioned above the 30-day DMA (₹2,094.62), 50-day DMA (₹1,982.91), and 200-day DMA (₹1,948.54). The price distance from 200 DMA is +12.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHEL. Current Market Price (₹431.00) is positioned above the 30-day DMA (₹420.40), 50-day DMA (₹413.87), and 200-day DMA (₹337.32). The price distance from 200 DMA is +27.33%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[2153.5, 2164.16, 2174.82, 2185.48, 2196.14, 2206.8]</t>
+          <t>[431.0, 434.0, 437.0, 439.99, 442.99, 445.99]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2153.5, 2187.65, 2208.05, 2226.17, 2243.13, 2259.34]</t>
+          <t>[431.0, 438.69, 443.63, 448.12, 452.37, 456.48]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2153.5, 2146.54, 2149.9, 2154.96, 2160.9, 2167.41]</t>
+          <t>[431.0, 430.48, 432.02, 433.9, 435.96, 438.12]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>2164.91</v>
+        <v>433.19</v>
       </c>
     </row>
     <row r="7">
@@ -1496,16 +1496,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>150076.93</v>
+        <v>59793.74</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,146 +1513,146 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>431</v>
+        <v>2153.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹428.65 - ₹434.52</t>
+          <t>₹2141.75 - ₹2171.12</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>440.38</v>
+        <v>2200.49</v>
       </c>
       <c r="I7" t="n">
-        <v>420.4</v>
+        <v>2094.62</v>
       </c>
       <c r="J7" t="n">
-        <v>413.87</v>
+        <v>1982.91</v>
       </c>
       <c r="K7" t="n">
-        <v>337.32</v>
+        <v>1948.54</v>
       </c>
       <c r="L7" t="n">
-        <v>27.33</v>
+        <v>12.64</v>
       </c>
       <c r="M7" t="n">
-        <v>4.4</v>
+        <v>60.53</v>
       </c>
       <c r="N7" t="n">
-        <v>4.67</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.27</v>
+        <v>-10.48</v>
       </c>
       <c r="P7" t="n">
-        <v>11.73</v>
+        <v>58.73</v>
       </c>
       <c r="Q7" t="n">
         <v>12.29</v>
       </c>
       <c r="R7" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.81</v>
+        <v>-1.85</v>
       </c>
       <c r="U7" t="n">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="V7" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>425.63</v>
+        <v>2117.38</v>
       </c>
       <c r="Y7" t="n">
-        <v>444.06</v>
+        <v>2209.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>433.44</v>
+        <v>2164.91</v>
       </c>
       <c r="AA7" t="n">
-        <v>413.41</v>
+        <v>2065.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>427.4</v>
+        <v>2146.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>436.6</v>
+        <v>2183.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>442.2</v>
+        <v>2212.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>59.1</v>
+        <v>57</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>61.7</v>
+        <v>48.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>40.3</v>
+        <v>8.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>447.57</v>
+        <v>2214.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>416.69</v>
+        <v>2097.08</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>BHEL operates in the Industrials sector. With an estimated Market Cap of ₹150,076.93 Cr., a P/E ratio of 61.75, and YoY Revenue Growth of +40.3%, the company demonstrates strong institutional backing, solid operating profit margins (6.76%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹59,793.74 Cr., a P/E ratio of 48.55, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.15 (Bullish Momentum Zone), while MACD Line (4.40) trades below Signal (4.67) with an expanding histogram (-0.27). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.33% above the 200-day DMA (₹337.32). Daily volatility envelope is bounded by ATR(14) of ₹11.73.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.04 (Bullish Momentum Zone), while MACD Line (60.53) trades below Signal (71.01) with an expanding histogram (-10.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.64% above the 200-day DMA (₹1948.54). Daily volatility envelope is bounded by ATR(14) of ₹58.73.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHEL. Current Market Price (₹431.00) is positioned above the 30-day DMA (₹420.40), 50-day DMA (₹413.87), and 200-day DMA (₹337.32). The price distance from 200 DMA is +27.33%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,153.50) is positioned above the 30-day DMA (₹2,094.62), 50-day DMA (₹1,982.91), and 200-day DMA (₹1,948.54). The price distance from 200 DMA is +12.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[431.0, 434.7, 438.39, 442.09, 445.79, 449.48]</t>
+          <t>[2153.5, 2162.61, 2171.73, 2180.84, 2189.95, 2199.07]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[431.0, 439.39, 445.03, 450.21, 455.17, 459.97]</t>
+          <t>[2153.5, 2186.11, 2204.95, 2221.53, 2236.94, 2251.6]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[431.0, 431.18, 433.42, 436.0, 438.75, 441.62]</t>
+          <t>[2153.5, 2144.99, 2146.81, 2150.32, 2154.71, 2159.67]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>433.44</v>
+        <v>2164.91</v>
       </c>
     </row>
     <row r="8">
@@ -1718,7 +1718,7 @@
         <v>12.29</v>
       </c>
       <c r="R8" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="S8" t="n">
         <v>0.32</v>
@@ -1727,19 +1727,19 @@
         <v>-0.95</v>
       </c>
       <c r="U8" t="n">
-        <v>50.8</v>
+        <v>51.7</v>
       </c>
       <c r="V8" t="n">
-        <v>3.96</v>
+        <v>3.57</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>410.28</v>
+        <v>409.94</v>
       </c>
       <c r="Y8" t="n">
-        <v>428.17</v>
+        <v>427.83</v>
       </c>
       <c r="Z8" t="n">
         <v>413.48</v>
@@ -1783,10 +1783,10 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>427.8</v>
+        <v>428.68</v>
       </c>
       <c r="AN8" t="n">
-        <v>409.47</v>
+        <v>409.96</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -1885,25 +1885,25 @@
         <v>12.29</v>
       </c>
       <c r="R9" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
       <c r="S9" t="n">
         <v>0.19</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.06</v>
+        <v>-2.04</v>
       </c>
       <c r="U9" t="n">
         <v>45</v>
       </c>
       <c r="V9" t="n">
-        <v>4.79</v>
+        <v>5.71</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>542.86</v>
+        <v>542.64</v>
       </c>
       <c r="Y9" t="n">
         <v>572.1900000000001</v>
@@ -1950,10 +1950,10 @@
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>577.48</v>
+        <v>577.17</v>
       </c>
       <c r="AN9" t="n">
-        <v>548.35</v>
+        <v>548.83</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -2052,25 +2052,25 @@
         <v>12.29</v>
       </c>
       <c r="R10" t="n">
-        <v>45.9</v>
+        <v>46.3</v>
       </c>
       <c r="S10" t="n">
         <v>0.26</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.28</v>
+        <v>-1.26</v>
       </c>
       <c r="U10" t="n">
         <v>50</v>
       </c>
       <c r="V10" t="n">
-        <v>4.81</v>
+        <v>5.01</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>280.58</v>
+        <v>280.57</v>
       </c>
       <c r="Y10" t="n">
         <v>296.54</v>
@@ -2117,10 +2117,10 @@
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>295.73</v>
+        <v>295.54</v>
       </c>
       <c r="AN10" t="n">
-        <v>278.59</v>
+        <v>278.93</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -2228,19 +2228,19 @@
         <v>-1.12</v>
       </c>
       <c r="U11" t="n">
-        <v>52.5</v>
+        <v>53.3</v>
       </c>
       <c r="V11" t="n">
-        <v>2.49</v>
+        <v>2.87</v>
       </c>
       <c r="W11" t="n">
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>114.98</v>
+        <v>115.23</v>
       </c>
       <c r="Y11" t="n">
-        <v>119.96</v>
+        <v>120.07</v>
       </c>
       <c r="Z11" t="n">
         <v>115.81</v>
@@ -2284,10 +2284,10 @@
         <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>120.03</v>
+        <v>119.87</v>
       </c>
       <c r="AN11" t="n">
-        <v>113.35</v>
+        <v>113.66</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -2306,17 +2306,17 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[116.75, 117.43, 118.11, 118.79, 119.47, 120.15]</t>
+          <t>[116.75, 117.68, 118.6, 119.53, 120.46, 121.38]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[116.75, 118.26, 119.29, 120.23, 121.13, 122.01]</t>
+          <t>[116.75, 118.51, 119.78, 120.97, 122.12, 123.24]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[116.75, 116.8, 117.23, 117.71, 118.22, 118.75]</t>
+          <t>[116.75, 117.05, 117.72, 118.45, 119.21, 119.98]</t>
         </is>
       </c>
       <c r="AU11" t="n">
@@ -2398,16 +2398,16 @@
         <v>55</v>
       </c>
       <c r="V12" t="n">
-        <v>5.59</v>
+        <v>5.58</v>
       </c>
       <c r="W12" t="n">
         <v>-0.77</v>
       </c>
       <c r="X12" t="n">
-        <v>1768.15</v>
+        <v>1768.66</v>
       </c>
       <c r="Y12" t="n">
-        <v>1844.95</v>
+        <v>1845.46</v>
       </c>
       <c r="Z12" t="n">
         <v>1788.91</v>
@@ -2451,10 +2451,10 @@
         <v>15</v>
       </c>
       <c r="AM12" t="n">
-        <v>1856.16</v>
+        <v>1859.01</v>
       </c>
       <c r="AN12" t="n">
-        <v>1740.66</v>
+        <v>1740.38</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -2473,17 +2473,17 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>[1797.3, 1805.91, 1814.52, 1823.13, 1831.75, 1840.36]</t>
+          <t>[1797.3, 1806.42, 1815.54, 1824.65, 1833.77, 1842.89]</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[1797.3, 1824.84, 1841.29, 1855.92, 1869.6, 1882.68]</t>
+          <t>[1797.3, 1825.35, 1842.31, 1857.44, 1871.63, 1885.22]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[1797.3, 1791.71, 1794.45, 1798.55, 1803.35, 1808.61]</t>
+          <t>[1797.3, 1792.22, 1795.46, 1800.07, 1805.38, 1811.15]</t>
         </is>
       </c>
       <c r="AU12" t="n">

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>297794.48</v>
+        <v>79671.24000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>323.5</v>
+        <v>489.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹322.12 - ₹325.57</t>
+          <t>₹487.29 - ₹493.57</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>329.01</v>
+        <v>499.85</v>
       </c>
       <c r="I2" t="n">
-        <v>320.1</v>
+        <v>473.15</v>
       </c>
       <c r="J2" t="n">
-        <v>307.72</v>
+        <v>459</v>
       </c>
       <c r="K2" t="n">
-        <v>273.9</v>
+        <v>453.98</v>
       </c>
       <c r="L2" t="n">
-        <v>17.6</v>
+        <v>10.2</v>
       </c>
       <c r="M2" t="n">
-        <v>4.55</v>
+        <v>10.64</v>
       </c>
       <c r="N2" t="n">
-        <v>6.65</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>6.89</v>
+        <v>12.56</v>
       </c>
       <c r="Q2" t="n">
         <v>12.29</v>
       </c>
       <c r="R2" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="S2" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.12</v>
+        <v>-1.44</v>
       </c>
       <c r="U2" t="n">
-        <v>50</v>
+        <v>61.7</v>
       </c>
       <c r="V2" t="n">
-        <v>2.44</v>
+        <v>3.71</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>313.87</v>
+        <v>480.38</v>
       </c>
       <c r="Y2" t="n">
-        <v>327.66</v>
+        <v>501.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>291.87</v>
+        <v>471.66</v>
       </c>
       <c r="AA2" t="n">
-        <v>313.17</v>
+        <v>470.96</v>
       </c>
       <c r="AB2" t="n">
-        <v>321.45</v>
+        <v>495.72</v>
       </c>
       <c r="AC2" t="n">
-        <v>326.85</v>
+        <v>506.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>330.2</v>
+        <v>522.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>35.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.24</v>
+        <v>-0.14</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Vol Spike 1.9x | Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>718.9</v>
+        <v>9.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>182</v>
+        <v>57.7</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.6</v>
+        <v>21.7</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>334.75</v>
+        <v>505.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>312.38</v>
+        <v>475.79</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹297,794.48 Cr., a P/E ratio of 718.89, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹79,671.24 Cr., a P/E ratio of 9.53, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 35.26 (Consolidation Zone), while MACD Line (4.55) trades below Signal (6.65) with an expanding histogram (-2.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.60% above the 200-day DMA (₹273.90). Daily volatility envelope is bounded by ATR(14) of ₹6.89.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.05 (Bullish Momentum Zone), while MACD Line (10.64) trades above Signal (9.70) with an expanding histogram (+0.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.20% above the 200-day DMA (₹453.98). Daily volatility envelope is bounded by ATR(14) of ₹12.56.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹323.50) is positioned above the 30-day DMA (₹320.10), 50-day DMA (₹307.72), and 200-day DMA (₹273.90). The price distance from 200 DMA is +17.60%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹489.80) is positioned above the 30-day DMA (₹473.15), 50-day DMA (₹459.00), and 200-day DMA (₹453.98). The price distance from 200 DMA is +10.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[323.5, 324.47, 325.44, 326.41, 327.38, 328.35]</t>
+          <t>[489.8, 491.27, 492.74, 494.21, 495.68, 497.15]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[323.5, 327.22, 329.34, 331.18, 332.89, 334.51]</t>
+          <t>[489.8, 496.29, 499.84, 502.91, 505.73, 508.38]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[323.5, 322.4, 322.52, 322.83, 323.25, 323.73]</t>
+          <t>[489.8, 487.5, 487.41, 487.68, 488.14, 488.72]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>291.87</v>
+        <v>471.66</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79671.24000000001</v>
+        <v>297794.48</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>489.8</v>
+        <v>323.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹487.29 - ₹493.57</t>
+          <t>₹322.12 - ₹325.57</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>499.85</v>
+        <v>329.01</v>
       </c>
       <c r="I3" t="n">
-        <v>473.15</v>
+        <v>320.1</v>
       </c>
       <c r="J3" t="n">
-        <v>459</v>
+        <v>307.72</v>
       </c>
       <c r="K3" t="n">
-        <v>453.98</v>
+        <v>273.9</v>
       </c>
       <c r="L3" t="n">
-        <v>10.2</v>
+        <v>17.6</v>
       </c>
       <c r="M3" t="n">
-        <v>10.64</v>
+        <v>4.55</v>
       </c>
       <c r="N3" t="n">
-        <v>9.699999999999999</v>
+        <v>6.65</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9399999999999999</v>
+        <v>-2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>12.56</v>
+        <v>6.89</v>
       </c>
       <c r="Q3" t="n">
         <v>12.29</v>
       </c>
       <c r="R3" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.46</v>
+        <v>-1.14</v>
       </c>
       <c r="U3" t="n">
-        <v>61.7</v>
+        <v>50</v>
       </c>
       <c r="V3" t="n">
-        <v>3.7</v>
+        <v>2.44</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>480.4</v>
+        <v>313.87</v>
       </c>
       <c r="Y3" t="n">
-        <v>501.32</v>
+        <v>327.66</v>
       </c>
       <c r="Z3" t="n">
-        <v>471.66</v>
+        <v>291.87</v>
       </c>
       <c r="AA3" t="n">
-        <v>470.96</v>
+        <v>313.17</v>
       </c>
       <c r="AB3" t="n">
-        <v>495.72</v>
+        <v>321.45</v>
       </c>
       <c r="AC3" t="n">
-        <v>506.04</v>
+        <v>326.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>522.27</v>
+        <v>330.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>70.09999999999999</v>
+        <v>35.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.14</v>
+        <v>0.24</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Vol Spike 1.9x | Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>9.5</v>
+        <v>718.9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>57.7</v>
+        <v>182</v>
       </c>
       <c r="AK3" t="n">
-        <v>21.7</v>
+        <v>0.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>505.18</v>
+        <v>334.61</v>
       </c>
       <c r="AN3" t="n">
-        <v>475</v>
+        <v>312.64</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹79,671.24 Cr., a P/E ratio of 9.53, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹297,794.48 Cr., a P/E ratio of 718.89, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.05 (Bullish Momentum Zone), while MACD Line (10.64) trades above Signal (9.70) with an expanding histogram (+0.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.20% above the 200-day DMA (₹453.98). Daily volatility envelope is bounded by ATR(14) of ₹12.56.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 35.26 (Consolidation Zone), while MACD Line (4.55) trades below Signal (6.65) with an expanding histogram (-2.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.60% above the 200-day DMA (₹273.90). Daily volatility envelope is bounded by ATR(14) of ₹6.89.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹489.80) is positioned above the 30-day DMA (₹473.15), 50-day DMA (₹459.00), and 200-day DMA (₹453.98). The price distance from 200 DMA is +10.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹323.50) is positioned above the 30-day DMA (₹320.10), 50-day DMA (₹307.72), and 200-day DMA (₹273.90). The price distance from 200 DMA is +17.60%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[489.8, 491.27, 492.74, 494.21, 495.68, 497.15]</t>
+          <t>[323.5, 324.47, 325.44, 326.41, 327.38, 328.35]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[489.8, 496.29, 499.84, 502.91, 505.73, 508.38]</t>
+          <t>[323.5, 327.22, 329.34, 331.18, 332.89, 334.51]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[489.8, 487.5, 487.41, 487.68, 488.14, 488.72]</t>
+          <t>[323.5, 322.4, 322.52, 322.83, 323.25, 323.73]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>471.66</v>
+        <v>291.87</v>
       </c>
     </row>
     <row r="4">
@@ -1050,25 +1050,25 @@
         <v>12.29</v>
       </c>
       <c r="R4" t="n">
-        <v>45.9</v>
+        <v>46.3</v>
       </c>
       <c r="S4" t="n">
         <v>0.18</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.93</v>
+        <v>-1.91</v>
       </c>
       <c r="U4" t="n">
         <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>3222.34</v>
+        <v>3222.36</v>
       </c>
       <c r="Y4" t="n">
         <v>4081.14</v>
@@ -1115,10 +1115,10 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>3413.16</v>
+        <v>3407.31</v>
       </c>
       <c r="AN4" t="n">
-        <v>3152.87</v>
+        <v>3160.6</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[3276.0, 3291.16, 3306.33, 3321.49, 3336.65, 3351.81]</t>
+          <t>[3276.0, 3291.18, 3306.36, 3321.54, 3336.72, 3351.9]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[3276.0, 3330.86, 3362.47, 3390.25, 3416.05, 3440.58]</t>
+          <t>[3276.0, 3330.88, 3362.5, 3390.3, 3416.12, 3440.67]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[3276.0, 3261.39, 3264.22, 3269.92, 3277.11, 3285.24]</t>
+          <t>[3276.0, 3261.41, 3264.26, 3269.97, 3277.18, 3285.33]</t>
         </is>
       </c>
       <c r="AU4" t="n">
@@ -1162,163 +1162,163 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61810.36</v>
+        <v>150076.93</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1026.5</v>
+        <v>431</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹1020.86 - ₹1034.95</t>
+          <t>₹428.65 - ₹434.52</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1049.04</v>
+        <v>440.38</v>
       </c>
       <c r="I5" t="n">
-        <v>962.21</v>
+        <v>420.4</v>
       </c>
       <c r="J5" t="n">
-        <v>950.4</v>
+        <v>413.87</v>
       </c>
       <c r="K5" t="n">
-        <v>849.74</v>
+        <v>337.32</v>
       </c>
       <c r="L5" t="n">
-        <v>19.45</v>
+        <v>27.33</v>
       </c>
       <c r="M5" t="n">
-        <v>29.14</v>
+        <v>4.4</v>
       </c>
       <c r="N5" t="n">
-        <v>30.5</v>
+        <v>4.67</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.36</v>
+        <v>-0.27</v>
       </c>
       <c r="P5" t="n">
-        <v>28.18</v>
+        <v>11.73</v>
       </c>
       <c r="Q5" t="n">
         <v>12.29</v>
       </c>
       <c r="R5" t="n">
-        <v>45.1</v>
+        <v>49.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.75</v>
+        <v>-1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>51.7</v>
+        <v>46.7</v>
       </c>
       <c r="V5" t="n">
-        <v>3.69</v>
+        <v>3.66</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>1002.1</v>
+        <v>424.93</v>
       </c>
       <c r="Y5" t="n">
-        <v>1109.16</v>
+        <v>443.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>1109.16</v>
+        <v>433.19</v>
       </c>
       <c r="AA5" t="n">
-        <v>984.23</v>
+        <v>413.41</v>
       </c>
       <c r="AB5" t="n">
-        <v>1015.07</v>
+        <v>427.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>1042.14</v>
+        <v>436.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>1057.77</v>
+        <v>442.2</v>
       </c>
       <c r="AE5" t="n">
-        <v>57.3</v>
+        <v>59.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>31.8</v>
+        <v>61.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23.9</v>
+        <v>40.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>6.8</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1065.18</v>
+        <v>447.84</v>
       </c>
       <c r="AN5" t="n">
-        <v>986.3099999999999</v>
+        <v>415.84</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹61,810.36 Cr., a P/E ratio of 31.85, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>BHEL operates in the Industrials sector. With an estimated Market Cap of ₹150,076.93 Cr., a P/E ratio of 61.75, and YoY Revenue Growth of +40.3%, the company demonstrates strong institutional backing, solid operating profit margins (6.76%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.26 (Bullish Momentum Zone), while MACD Line (29.14) trades below Signal (30.50) with an expanding histogram (-1.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.45% above the 200-day DMA (₹849.74). Daily volatility envelope is bounded by ATR(14) of ₹28.18.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.15 (Bullish Momentum Zone), while MACD Line (4.40) trades below Signal (4.67) with an expanding histogram (-0.27). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.33% above the 200-day DMA (₹337.32). Daily volatility envelope is bounded by ATR(14) of ₹11.73.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,026.50) is positioned above the 30-day DMA (₹962.21), 50-day DMA (₹950.40), and 200-day DMA (₹849.74). The price distance from 200 DMA is +19.45%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHEL. Current Market Price (₹431.00) is positioned above the 30-day DMA (₹420.40), 50-day DMA (₹413.87), and 200-day DMA (₹337.32). The price distance from 200 DMA is +27.33%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[1026.5, 1029.58, 1032.66, 1035.74, 1038.82, 1041.9]</t>
+          <t>[431.0, 434.0, 437.0, 439.99, 442.99, 445.99]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[1026.5, 1040.85, 1048.6, 1055.26, 1061.36, 1067.1]</t>
+          <t>[431.0, 438.69, 443.63, 448.12, 452.37, 456.48]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[1026.5, 1021.13, 1020.7, 1021.1, 1021.91, 1022.99]</t>
+          <t>[431.0, 430.48, 432.02, 433.9, 435.96, 438.12]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1109.16</v>
+        <v>433.19</v>
       </c>
     </row>
     <row r="6">
@@ -1329,16 +1329,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>150076.93</v>
+        <v>59793.74</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,146 +1346,146 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>431</v>
+        <v>2153.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹428.65 - ₹434.52</t>
+          <t>₹2141.75 - ₹2171.12</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>440.38</v>
+        <v>2200.49</v>
       </c>
       <c r="I6" t="n">
-        <v>420.4</v>
+        <v>2094.62</v>
       </c>
       <c r="J6" t="n">
-        <v>413.87</v>
+        <v>1982.91</v>
       </c>
       <c r="K6" t="n">
-        <v>337.32</v>
+        <v>1948.54</v>
       </c>
       <c r="L6" t="n">
-        <v>27.33</v>
+        <v>12.64</v>
       </c>
       <c r="M6" t="n">
-        <v>4.4</v>
+        <v>60.53</v>
       </c>
       <c r="N6" t="n">
-        <v>4.67</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.27</v>
+        <v>-10.48</v>
       </c>
       <c r="P6" t="n">
-        <v>11.73</v>
+        <v>58.73</v>
       </c>
       <c r="Q6" t="n">
         <v>12.29</v>
       </c>
       <c r="R6" t="n">
-        <v>49.5</v>
+        <v>48.3</v>
       </c>
       <c r="S6" t="n">
         <v>0.2</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.79</v>
+        <v>-1.85</v>
       </c>
       <c r="U6" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="V6" t="n">
-        <v>3.66</v>
+        <v>2.78</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>424.93</v>
+        <v>2117.49</v>
       </c>
       <c r="Y6" t="n">
-        <v>443.36</v>
+        <v>2209.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>433.19</v>
+        <v>2164.91</v>
       </c>
       <c r="AA6" t="n">
-        <v>413.41</v>
+        <v>2065.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>427.4</v>
+        <v>2146.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>436.6</v>
+        <v>2183.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>442.2</v>
+        <v>2212.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>59.1</v>
+        <v>57</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>61.7</v>
+        <v>48.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>40.3</v>
+        <v>8.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>6.8</v>
+        <v>5.2</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>447.67</v>
+        <v>2212.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>416.08</v>
+        <v>2093.93</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>BHEL operates in the Industrials sector. With an estimated Market Cap of ₹150,076.93 Cr., a P/E ratio of 61.75, and YoY Revenue Growth of +40.3%, the company demonstrates strong institutional backing, solid operating profit margins (6.76%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹59,793.74 Cr., a P/E ratio of 48.55, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.15 (Bullish Momentum Zone), while MACD Line (4.40) trades below Signal (4.67) with an expanding histogram (-0.27). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.33% above the 200-day DMA (₹337.32). Daily volatility envelope is bounded by ATR(14) of ₹11.73.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.04 (Bullish Momentum Zone), while MACD Line (60.53) trades below Signal (71.01) with an expanding histogram (-10.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.64% above the 200-day DMA (₹1948.54). Daily volatility envelope is bounded by ATR(14) of ₹58.73.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHEL. Current Market Price (₹431.00) is positioned above the 30-day DMA (₹420.40), 50-day DMA (₹413.87), and 200-day DMA (₹337.32). The price distance from 200 DMA is +27.33%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,153.50) is positioned above the 30-day DMA (₹2,094.62), 50-day DMA (₹1,982.91), and 200-day DMA (₹1,948.54). The price distance from 200 DMA is +12.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[431.0, 434.0, 437.0, 439.99, 442.99, 445.99]</t>
+          <t>[2153.5, 2162.72, 2171.94, 2181.16, 2190.38, 2199.6]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[431.0, 438.69, 443.63, 448.12, 452.37, 456.48]</t>
+          <t>[2153.5, 2186.21, 2205.17, 2221.85, 2237.37, 2252.13]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[431.0, 430.48, 432.02, 433.9, 435.96, 438.12]</t>
+          <t>[2153.5, 2145.1, 2147.02, 2150.64, 2155.14, 2160.2]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>433.19</v>
+        <v>2164.91</v>
       </c>
     </row>
     <row r="7">
@@ -1496,16 +1496,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>59793.74</v>
+        <v>416806.78</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,146 +1513,146 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2153.5</v>
+        <v>419</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹2141.75 - ₹2171.12</t>
+          <t>₹417.59 - ₹421.11</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2200.49</v>
+        <v>424.62</v>
       </c>
       <c r="I7" t="n">
-        <v>2094.62</v>
+        <v>405.16</v>
       </c>
       <c r="J7" t="n">
-        <v>1982.91</v>
+        <v>396.17</v>
       </c>
       <c r="K7" t="n">
-        <v>1948.54</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>12.64</v>
+        <v>4.14</v>
       </c>
       <c r="M7" t="n">
-        <v>60.53</v>
+        <v>7.02</v>
       </c>
       <c r="N7" t="n">
-        <v>71.01000000000001</v>
+        <v>7.53</v>
       </c>
       <c r="O7" t="n">
-        <v>-10.48</v>
+        <v>-0.52</v>
       </c>
       <c r="P7" t="n">
-        <v>58.73</v>
+        <v>7.03</v>
       </c>
       <c r="Q7" t="n">
         <v>12.29</v>
       </c>
       <c r="R7" t="n">
-        <v>48.4</v>
+        <v>47.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.85</v>
+        <v>-0.95</v>
       </c>
       <c r="U7" t="n">
-        <v>50</v>
+        <v>51.7</v>
       </c>
       <c r="V7" t="n">
-        <v>2.78</v>
+        <v>3.57</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>2117.38</v>
+        <v>409.96</v>
       </c>
       <c r="Y7" t="n">
-        <v>2209.39</v>
+        <v>427.84</v>
       </c>
       <c r="Z7" t="n">
-        <v>2164.91</v>
+        <v>413.48</v>
       </c>
       <c r="AA7" t="n">
-        <v>2065.4</v>
+        <v>408.46</v>
       </c>
       <c r="AB7" t="n">
-        <v>2146.5</v>
+        <v>416.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>2183.2</v>
+        <v>422.91</v>
       </c>
       <c r="AD7" t="n">
-        <v>2212.9</v>
+        <v>426.83</v>
       </c>
       <c r="AE7" t="n">
-        <v>57</v>
+        <v>62.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>48.5</v>
+        <v>20.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>8.5</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
-        <v>5.2</v>
+        <v>28.5</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>2214.26</v>
+        <v>428.35</v>
       </c>
       <c r="AN7" t="n">
-        <v>2097.08</v>
+        <v>409.48</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹59,793.74 Cr., a P/E ratio of 48.55, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹416,806.78 Cr., a P/E ratio of 20.53, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.04 (Bullish Momentum Zone), while MACD Line (60.53) trades below Signal (71.01) with an expanding histogram (-10.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.64% above the 200-day DMA (₹1948.54). Daily volatility envelope is bounded by ATR(14) of ₹58.73.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (7.02) trades below Signal (7.53) with an expanding histogram (-0.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹400.00). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,153.50) is positioned above the 30-day DMA (₹2,094.62), 50-day DMA (₹1,982.91), and 200-day DMA (₹1,948.54). The price distance from 200 DMA is +12.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹419.00) is positioned above the 30-day DMA (₹405.16), 50-day DMA (₹396.17), and 200-day DMA (₹400.00). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[2153.5, 2162.61, 2171.73, 2180.84, 2189.95, 2199.07]</t>
+          <t>[419.0, 420.26, 421.51, 422.77, 424.03, 425.28]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[2153.5, 2186.11, 2204.95, 2221.53, 2236.94, 2251.6]</t>
+          <t>[419.0, 423.07, 425.49, 427.64, 429.65, 431.57]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[2153.5, 2144.99, 2146.81, 2150.32, 2154.71, 2159.67]</t>
+          <t>[419.0, 418.15, 418.53, 419.12, 419.81, 420.57]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>2164.91</v>
+        <v>413.48</v>
       </c>
     </row>
     <row r="8">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>416806.78</v>
+        <v>30963.05</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1680,146 +1680,146 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>419</v>
+        <v>562.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹417.59 - ₹421.11</t>
+          <t>₹559.68 - ₹567.73</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>424.62</v>
+        <v>575.79</v>
       </c>
       <c r="I8" t="n">
-        <v>405.16</v>
+        <v>515.35</v>
       </c>
       <c r="J8" t="n">
-        <v>396.17</v>
+        <v>523.51</v>
       </c>
       <c r="K8" t="n">
-        <v>400</v>
+        <v>523.36</v>
       </c>
       <c r="L8" t="n">
-        <v>4.14</v>
+        <v>5.53</v>
       </c>
       <c r="M8" t="n">
-        <v>7.02</v>
+        <v>12.09</v>
       </c>
       <c r="N8" t="n">
-        <v>7.53</v>
+        <v>6.96</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.52</v>
+        <v>5.13</v>
       </c>
       <c r="P8" t="n">
-        <v>7.03</v>
+        <v>16.11</v>
       </c>
       <c r="Q8" t="n">
         <v>12.29</v>
       </c>
       <c r="R8" t="n">
-        <v>47.3</v>
+        <v>46.6</v>
       </c>
       <c r="S8" t="n">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.95</v>
+        <v>-2.05</v>
       </c>
       <c r="U8" t="n">
-        <v>51.7</v>
+        <v>45</v>
       </c>
       <c r="V8" t="n">
-        <v>3.57</v>
+        <v>5.71</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>409.94</v>
+        <v>542.64</v>
       </c>
       <c r="Y8" t="n">
-        <v>427.83</v>
+        <v>572.1900000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>413.48</v>
+        <v>572.1900000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>408.46</v>
+        <v>538.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>416.08</v>
+        <v>560.42</v>
       </c>
       <c r="AC8" t="n">
-        <v>422.91</v>
+        <v>574.84</v>
       </c>
       <c r="AD8" t="n">
-        <v>426.83</v>
+        <v>586.77</v>
       </c>
       <c r="AE8" t="n">
-        <v>62.6</v>
+        <v>78</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>20.5</v>
+        <v>5.4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>28.5</v>
+        <v>65.2</v>
       </c>
       <c r="AL8" t="n">
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>428.68</v>
+        <v>576.83</v>
       </c>
       <c r="AN8" t="n">
-        <v>409.96</v>
+        <v>548.13</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹416,806.78 Cr., a P/E ratio of 20.53, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,963.05 Cr., a P/E ratio of 5.40, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (7.02) trades below Signal (7.53) with an expanding histogram (-0.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹400.00). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.98 (Bullish Momentum Zone), while MACD Line (12.09) trades above Signal (6.96) with an expanding histogram (+5.13). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.53% above the 200-day DMA (₹523.36). Daily volatility envelope is bounded by ATR(14) of ₹16.11.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹419.00) is positioned above the 30-day DMA (₹405.16), 50-day DMA (₹396.17), and 200-day DMA (₹400.00). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹562.90) is positioned above the 30-day DMA (₹515.35), 50-day DMA (₹523.51), and 200-day DMA (₹523.36). The price distance from 200 DMA is +5.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[419.0, 420.26, 421.51, 422.77, 424.03, 425.28]</t>
+          <t>[562.9, 564.59, 566.28, 567.97, 569.65, 571.34]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[419.0, 423.07, 425.49, 427.64, 429.65, 431.57]</t>
+          <t>[562.9, 571.03, 575.39, 579.13, 582.54, 585.75]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[419.0, 418.15, 418.53, 419.12, 419.81, 420.57]</t>
+          <t>[562.9, 559.76, 559.44, 559.6, 559.99, 560.54]</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>413.48</v>
+        <v>572.1900000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1830,16 +1830,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>30963.05</v>
+        <v>43080</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1847,146 +1847,146 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>562.9</v>
+        <v>287.2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹559.68 - ₹567.73</t>
+          <t>₹286.04 - ₹288.94</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>575.79</v>
+        <v>291.85</v>
       </c>
       <c r="I9" t="n">
-        <v>515.35</v>
+        <v>286.26</v>
       </c>
       <c r="J9" t="n">
-        <v>523.51</v>
+        <v>282.16</v>
       </c>
       <c r="K9" t="n">
-        <v>523.36</v>
+        <v>278.2</v>
       </c>
       <c r="L9" t="n">
-        <v>5.53</v>
+        <v>3.77</v>
       </c>
       <c r="M9" t="n">
-        <v>12.09</v>
+        <v>1.76</v>
       </c>
       <c r="N9" t="n">
-        <v>6.96</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>5.13</v>
+        <v>-0.95</v>
       </c>
       <c r="P9" t="n">
-        <v>16.11</v>
+        <v>5.81</v>
       </c>
       <c r="Q9" t="n">
         <v>12.29</v>
       </c>
       <c r="R9" t="n">
-        <v>46.7</v>
+        <v>46.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.04</v>
+        <v>-1.25</v>
       </c>
       <c r="U9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="V9" t="n">
-        <v>5.71</v>
+        <v>5.01</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>542.64</v>
+        <v>280.56</v>
       </c>
       <c r="Y9" t="n">
-        <v>572.1900000000001</v>
+        <v>296.54</v>
       </c>
       <c r="Z9" t="n">
-        <v>572.1900000000001</v>
+        <v>296.54</v>
       </c>
       <c r="AA9" t="n">
-        <v>538.74</v>
+        <v>278.48</v>
       </c>
       <c r="AB9" t="n">
-        <v>560.42</v>
+        <v>286.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>574.84</v>
+        <v>288.31</v>
       </c>
       <c r="AD9" t="n">
-        <v>586.77</v>
+        <v>289.43</v>
       </c>
       <c r="AE9" t="n">
-        <v>78</v>
+        <v>46.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.4</v>
+        <v>10.2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14.5</v>
+        <v>-53.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>65.2</v>
+        <v>11.3</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>577.17</v>
+        <v>295.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>548.83</v>
+        <v>278.56</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,963.05 Cr., a P/E ratio of 5.40, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,080.00 Cr., a P/E ratio of 10.24, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.98 (Bullish Momentum Zone), while MACD Line (12.09) trades above Signal (6.96) with an expanding histogram (+5.13). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.53% above the 200-day DMA (₹523.36). Daily volatility envelope is bounded by ATR(14) of ₹16.11.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.74 (Consolidation Zone), while MACD Line (1.76) trades below Signal (2.70) with an expanding histogram (-0.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.77% above the 200-day DMA (₹278.20). Daily volatility envelope is bounded by ATR(14) of ₹5.81.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹562.90) is positioned above the 30-day DMA (₹515.35), 50-day DMA (₹523.51), and 200-day DMA (₹523.36). The price distance from 200 DMA is +5.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹287.20) is positioned above the 30-day DMA (₹286.26), 50-day DMA (₹282.16), and 200-day DMA (₹278.20). The price distance from 200 DMA is +3.77%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[562.9, 564.59, 566.28, 567.97, 569.65, 571.34]</t>
+          <t>[287.2, 288.06, 288.92, 289.78, 290.65, 291.51]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[562.9, 571.03, 575.39, 579.13, 582.54, 585.75]</t>
+          <t>[287.2, 290.39, 292.21, 293.81, 295.3, 296.71]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[562.9, 559.76, 559.44, 559.6, 559.99, 560.54]</t>
+          <t>[287.2, 286.32, 286.46, 286.76, 287.16, 287.61]</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>572.1900000000001</v>
+        <v>296.54</v>
       </c>
     </row>
     <row r="10">
@@ -1997,16 +1997,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>43080</v>
+        <v>134180.11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2014,146 +2014,146 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>287.2</v>
+        <v>116.75</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹286.04 - ₹288.94</t>
+          <t>₹116.33 - ₹117.37</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>291.85</v>
+        <v>118.42</v>
       </c>
       <c r="I10" t="n">
-        <v>286.26</v>
+        <v>115.78</v>
       </c>
       <c r="J10" t="n">
-        <v>282.16</v>
+        <v>112.52</v>
       </c>
       <c r="K10" t="n">
-        <v>278.2</v>
+        <v>112.43</v>
       </c>
       <c r="L10" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="M10" t="n">
-        <v>1.76</v>
+        <v>0.8</v>
       </c>
       <c r="N10" t="n">
-        <v>2.7</v>
+        <v>1.06</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.95</v>
+        <v>-0.26</v>
       </c>
       <c r="P10" t="n">
-        <v>5.81</v>
+        <v>2.08</v>
       </c>
       <c r="Q10" t="n">
         <v>12.29</v>
       </c>
       <c r="R10" t="n">
-        <v>46.3</v>
+        <v>45</v>
       </c>
       <c r="S10" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.26</v>
+        <v>-1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="V10" t="n">
-        <v>5.01</v>
+        <v>2.87</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>280.57</v>
+        <v>115.23</v>
       </c>
       <c r="Y10" t="n">
-        <v>296.54</v>
+        <v>120.07</v>
       </c>
       <c r="Z10" t="n">
-        <v>296.54</v>
+        <v>115.81</v>
       </c>
       <c r="AA10" t="n">
-        <v>278.48</v>
+        <v>113.63</v>
       </c>
       <c r="AB10" t="n">
-        <v>286.08</v>
+        <v>116.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>288.31</v>
+        <v>118.18</v>
       </c>
       <c r="AD10" t="n">
-        <v>289.43</v>
+        <v>119.62</v>
       </c>
       <c r="AE10" t="n">
-        <v>46.7</v>
+        <v>51.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Low VIX (12.29) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>10.2</v>
+        <v>6.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-53.2</v>
+        <v>15.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>11.3</v>
+        <v>38.1</v>
       </c>
       <c r="AL10" t="n">
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>295.54</v>
+        <v>120.06</v>
       </c>
       <c r="AN10" t="n">
-        <v>278.93</v>
+        <v>113.5</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,080.00 Cr., a P/E ratio of 10.24, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,180.11 Cr., a P/E ratio of 6.07, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.74 (Consolidation Zone), while MACD Line (1.76) trades below Signal (2.70) with an expanding histogram (-0.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.77% above the 200-day DMA (₹278.20). Daily volatility envelope is bounded by ATR(14) of ₹5.81.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.30 (Consolidation Zone), while MACD Line (0.80) trades below Signal (1.06) with an expanding histogram (-0.26). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.93% above the 200-day DMA (₹112.43). Daily volatility envelope is bounded by ATR(14) of ₹2.08.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹287.20) is positioned above the 30-day DMA (₹286.26), 50-day DMA (₹282.16), and 200-day DMA (₹278.20). The price distance from 200 DMA is +3.77%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.75) is positioned above the 30-day DMA (₹115.78), 50-day DMA (₹112.52), and 200-day DMA (₹112.43). The price distance from 200 DMA is +3.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[287.2, 288.06, 288.92, 289.78, 290.65, 291.51]</t>
+          <t>[116.75, 117.68, 118.6, 119.53, 120.46, 121.38]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[287.2, 290.39, 292.21, 293.81, 295.3, 296.71]</t>
+          <t>[116.75, 118.51, 119.78, 120.97, 122.12, 123.24]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[287.2, 286.32, 286.46, 286.76, 287.16, 287.61]</t>
+          <t>[116.75, 117.05, 117.72, 118.45, 119.21, 119.98]</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>296.54</v>
+        <v>115.81</v>
       </c>
     </row>
     <row r="11">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>134180.11</v>
+        <v>61810.36</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2181,146 +2181,146 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>116.75</v>
+        <v>1026.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹116.33 - ₹117.37</t>
+          <t>₹1020.86 - ₹1034.95</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>118.42</v>
+        <v>1049.04</v>
       </c>
       <c r="I11" t="n">
-        <v>115.78</v>
+        <v>962.21</v>
       </c>
       <c r="J11" t="n">
-        <v>112.52</v>
+        <v>950.4</v>
       </c>
       <c r="K11" t="n">
-        <v>112.43</v>
+        <v>849.74</v>
       </c>
       <c r="L11" t="n">
-        <v>3.93</v>
+        <v>19.45</v>
       </c>
       <c r="M11" t="n">
-        <v>0.8</v>
+        <v>29.14</v>
       </c>
       <c r="N11" t="n">
-        <v>1.06</v>
+        <v>30.5</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.26</v>
+        <v>-1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>28.18</v>
       </c>
       <c r="Q11" t="n">
         <v>12.29</v>
       </c>
       <c r="R11" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3</v>
+        <v>0.19</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.12</v>
+        <v>-1.77</v>
       </c>
       <c r="U11" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="V11" t="n">
-        <v>2.87</v>
+        <v>3.69</v>
       </c>
       <c r="W11" t="n">
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>115.23</v>
+        <v>1002.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>120.07</v>
+        <v>1109.16</v>
       </c>
       <c r="Z11" t="n">
-        <v>115.81</v>
+        <v>1109.16</v>
       </c>
       <c r="AA11" t="n">
-        <v>113.63</v>
+        <v>984.23</v>
       </c>
       <c r="AB11" t="n">
-        <v>116.35</v>
+        <v>1015.07</v>
       </c>
       <c r="AC11" t="n">
-        <v>118.18</v>
+        <v>1042.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>119.62</v>
+        <v>1057.77</v>
       </c>
       <c r="AE11" t="n">
-        <v>51.3</v>
+        <v>57.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.09</v>
+        <v>0.33</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH11" t="n">
         <v>0.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.1</v>
+        <v>31.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>15.2</v>
+        <v>23.9</v>
       </c>
       <c r="AK11" t="n">
-        <v>38.1</v>
+        <v>23</v>
       </c>
       <c r="AL11" t="n">
         <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>119.87</v>
+        <v>1065.37</v>
       </c>
       <c r="AN11" t="n">
-        <v>113.66</v>
+        <v>984.45</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,180.11 Cr., a P/E ratio of 6.07, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹61,810.36 Cr., a P/E ratio of 31.85, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.30 (Consolidation Zone), while MACD Line (0.80) trades below Signal (1.06) with an expanding histogram (-0.26). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.93% above the 200-day DMA (₹112.43). Daily volatility envelope is bounded by ATR(14) of ₹2.08.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.26 (Bullish Momentum Zone), while MACD Line (29.14) trades below Signal (30.50) with an expanding histogram (-1.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.45% above the 200-day DMA (₹849.74). Daily volatility envelope is bounded by ATR(14) of ₹28.18.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.75) is positioned above the 30-day DMA (₹115.78), 50-day DMA (₹112.52), and 200-day DMA (₹112.43). The price distance from 200 DMA is +3.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,026.50) is positioned above the 30-day DMA (₹962.21), 50-day DMA (₹950.40), and 200-day DMA (₹849.74). The price distance from 200 DMA is +19.45%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[116.75, 117.68, 118.6, 119.53, 120.46, 121.38]</t>
+          <t>[1026.5, 1029.58, 1032.66, 1035.74, 1038.82, 1041.9]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[116.75, 118.51, 119.78, 120.97, 122.12, 123.24]</t>
+          <t>[1026.5, 1040.85, 1048.6, 1055.26, 1061.36, 1067.1]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[116.75, 117.05, 117.72, 118.45, 119.21, 119.98]</t>
+          <t>[1026.5, 1021.13, 1020.7, 1021.1, 1021.91, 1022.99]</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>115.81</v>
+        <v>1109.16</v>
       </c>
     </row>
     <row r="12">
@@ -2386,13 +2386,13 @@
         <v>12.29</v>
       </c>
       <c r="R12" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="S12" t="n">
         <v>0.2</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.9</v>
+        <v>-1.91</v>
       </c>
       <c r="U12" t="n">
         <v>55</v>
@@ -2451,10 +2451,10 @@
         <v>15</v>
       </c>
       <c r="AM12" t="n">
-        <v>1859.01</v>
+        <v>1858.98</v>
       </c>
       <c r="AN12" t="n">
-        <v>1740.38</v>
+        <v>1742.5</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79671.24000000001</v>
+        <v>297794.48</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,39 +678,39 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>489.8</v>
+        <v>323.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹487.29 - ₹493.57</t>
+          <t>₹322.12 - ₹325.57</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>499.85</v>
+        <v>329.01</v>
       </c>
       <c r="I2" t="n">
-        <v>473.15</v>
+        <v>320.1</v>
       </c>
       <c r="J2" t="n">
-        <v>459</v>
+        <v>307.72</v>
       </c>
       <c r="K2" t="n">
-        <v>453.98</v>
+        <v>273.9</v>
       </c>
       <c r="L2" t="n">
-        <v>10.2</v>
+        <v>17.6</v>
       </c>
       <c r="M2" t="n">
-        <v>10.64</v>
+        <v>4.55</v>
       </c>
       <c r="N2" t="n">
-        <v>9.699999999999999</v>
+        <v>6.65</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9399999999999999</v>
+        <v>-2.1</v>
       </c>
       <c r="P2" t="n">
-        <v>12.56</v>
+        <v>6.89</v>
       </c>
       <c r="Q2" t="n">
         <v>12.29</v>
@@ -719,105 +719,105 @@
         <v>48.9</v>
       </c>
       <c r="S2" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.44</v>
+        <v>-1.12</v>
       </c>
       <c r="U2" t="n">
-        <v>61.7</v>
+        <v>50</v>
       </c>
       <c r="V2" t="n">
-        <v>3.71</v>
+        <v>2.44</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>480.38</v>
+        <v>317.41</v>
       </c>
       <c r="Y2" t="n">
-        <v>501.29</v>
+        <v>361.43</v>
       </c>
       <c r="Z2" t="n">
-        <v>471.66</v>
+        <v>361.43</v>
       </c>
       <c r="AA2" t="n">
-        <v>470.96</v>
+        <v>313.17</v>
       </c>
       <c r="AB2" t="n">
-        <v>495.72</v>
+        <v>321.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>506.04</v>
+        <v>326.85</v>
       </c>
       <c r="AD2" t="n">
-        <v>522.27</v>
+        <v>330.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>70.09999999999999</v>
+        <v>35.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.14</v>
+        <v>0.24</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Vol Spike 1.9x | Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.5</v>
+        <v>718.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>57.7</v>
+        <v>182</v>
       </c>
       <c r="AK2" t="n">
-        <v>21.7</v>
+        <v>0.6</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>505.75</v>
+        <v>336.6</v>
       </c>
       <c r="AN2" t="n">
-        <v>475.79</v>
+        <v>312.39</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹79,671.24 Cr., a P/E ratio of 9.53, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹297,794.48 Cr., a P/E ratio of 718.89, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.05 (Bullish Momentum Zone), while MACD Line (10.64) trades above Signal (9.70) with an expanding histogram (+0.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.20% above the 200-day DMA (₹453.98). Daily volatility envelope is bounded by ATR(14) of ₹12.56.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 35.26 (Consolidation Zone), while MACD Line (4.55) trades below Signal (6.65) with an expanding histogram (-2.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.60% above the 200-day DMA (₹273.90). Daily volatility envelope is bounded by ATR(14) of ₹6.89.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹489.80) is positioned above the 30-day DMA (₹473.15), 50-day DMA (₹459.00), and 200-day DMA (₹453.98). The price distance from 200 DMA is +10.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹323.50) is positioned above the 30-day DMA (₹320.10), 50-day DMA (₹307.72), and 200-day DMA (₹273.90). The price distance from 200 DMA is +17.60%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[489.8, 491.27, 492.74, 494.21, 495.68, 497.15]</t>
+          <t>[323.5, 324.47, 325.44, 326.41, 327.38, 328.35]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[489.8, 496.29, 499.84, 502.91, 505.73, 508.38]</t>
+          <t>[323.5, 327.22, 329.34, 331.18, 332.89, 334.51]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[489.8, 487.5, 487.41, 487.68, 488.14, 488.72]</t>
+          <t>[323.5, 322.4, 322.52, 322.83, 323.25, 323.73]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>471.66</v>
+        <v>361.43</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>297794.48</v>
+        <v>79671.24000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>323.5</v>
+        <v>489.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹322.12 - ₹325.57</t>
+          <t>₹487.29 - ₹493.57</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>329.01</v>
+        <v>499.85</v>
       </c>
       <c r="I3" t="n">
-        <v>320.1</v>
+        <v>473.15</v>
       </c>
       <c r="J3" t="n">
-        <v>307.72</v>
+        <v>459</v>
       </c>
       <c r="K3" t="n">
-        <v>273.9</v>
+        <v>453.98</v>
       </c>
       <c r="L3" t="n">
-        <v>17.6</v>
+        <v>10.2</v>
       </c>
       <c r="M3" t="n">
-        <v>4.55</v>
+        <v>10.64</v>
       </c>
       <c r="N3" t="n">
-        <v>6.65</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>6.89</v>
+        <v>12.56</v>
       </c>
       <c r="Q3" t="n">
         <v>12.29</v>
       </c>
       <c r="R3" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.14</v>
+        <v>-1.46</v>
       </c>
       <c r="U3" t="n">
-        <v>50</v>
+        <v>61.7</v>
       </c>
       <c r="V3" t="n">
-        <v>2.44</v>
+        <v>3.71</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>313.87</v>
+        <v>485.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>327.66</v>
+        <v>512.71</v>
       </c>
       <c r="Z3" t="n">
-        <v>291.87</v>
+        <v>512.71</v>
       </c>
       <c r="AA3" t="n">
-        <v>313.17</v>
+        <v>470.96</v>
       </c>
       <c r="AB3" t="n">
-        <v>321.45</v>
+        <v>495.72</v>
       </c>
       <c r="AC3" t="n">
-        <v>326.85</v>
+        <v>506.04</v>
       </c>
       <c r="AD3" t="n">
-        <v>330.2</v>
+        <v>522.27</v>
       </c>
       <c r="AE3" t="n">
-        <v>35.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.24</v>
+        <v>-0.14</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Vol Spike 1.9x | Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>718.9</v>
+        <v>9.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>182</v>
+        <v>57.7</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.6</v>
+        <v>21.7</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>334.61</v>
+        <v>505.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>312.64</v>
+        <v>475.2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹297,794.48 Cr., a P/E ratio of 718.89, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹79,671.24 Cr., a P/E ratio of 9.53, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 35.26 (Consolidation Zone), while MACD Line (4.55) trades below Signal (6.65) with an expanding histogram (-2.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.60% above the 200-day DMA (₹273.90). Daily volatility envelope is bounded by ATR(14) of ₹6.89.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.05 (Bullish Momentum Zone), while MACD Line (10.64) trades above Signal (9.70) with an expanding histogram (+0.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.20% above the 200-day DMA (₹453.98). Daily volatility envelope is bounded by ATR(14) of ₹12.56.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹323.50) is positioned above the 30-day DMA (₹320.10), 50-day DMA (₹307.72), and 200-day DMA (₹273.90). The price distance from 200 DMA is +17.60%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹489.80) is positioned above the 30-day DMA (₹473.15), 50-day DMA (₹459.00), and 200-day DMA (₹453.98). The price distance from 200 DMA is +10.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[323.5, 324.47, 325.44, 326.41, 327.38, 328.35]</t>
+          <t>[489.8, 491.27, 492.74, 494.21, 495.68, 497.15]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[323.5, 327.22, 329.34, 331.18, 332.89, 334.51]</t>
+          <t>[489.8, 496.29, 499.84, 502.91, 505.73, 508.38]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[323.5, 322.4, 322.52, 322.83, 323.25, 323.73]</t>
+          <t>[489.8, 487.5, 487.41, 487.68, 488.14, 488.72]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>291.87</v>
+        <v>512.71</v>
       </c>
     </row>
     <row r="4">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25000</v>
+        <v>83378.82000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1050,13 +1050,13 @@
         <v>12.29</v>
       </c>
       <c r="R4" t="n">
-        <v>46.3</v>
+        <v>45.9</v>
       </c>
       <c r="S4" t="n">
         <v>0.18</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.91</v>
+        <v>-1.93</v>
       </c>
       <c r="U4" t="n">
         <v>53.3</v>
@@ -1068,13 +1068,13 @@
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>3222.36</v>
+        <v>3258.71</v>
       </c>
       <c r="Y4" t="n">
-        <v>4081.14</v>
+        <v>3275.68</v>
       </c>
       <c r="Z4" t="n">
-        <v>4081.14</v>
+        <v>2650.75</v>
       </c>
       <c r="AA4" t="n">
         <v>3127.14</v>
@@ -1115,14 +1115,14 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>3407.31</v>
+        <v>3420.97</v>
       </c>
       <c r="AN4" t="n">
-        <v>3160.6</v>
+        <v>3170.13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹83,378.82 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1137,21 +1137,21 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[3276.0, 3291.18, 3306.36, 3321.54, 3336.72, 3351.9]</t>
+          <t>[3276.0, 3291.19, 3306.37, 3321.56, 3336.74, 3351.93]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[3276.0, 3330.88, 3362.5, 3390.3, 3416.12, 3440.67]</t>
+          <t>[3276.0, 3330.88, 3362.51, 3390.32, 3416.14, 3440.69]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[3276.0, 3261.41, 3264.26, 3269.97, 3277.18, 3285.33]</t>
+          <t>[3276.0, 3261.41, 3264.27, 3269.99, 3277.2, 3285.35]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>4081.14</v>
+        <v>2650.75</v>
       </c>
     </row>
     <row r="5">
@@ -1217,31 +1217,31 @@
         <v>12.29</v>
       </c>
       <c r="R5" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="S5" t="n">
         <v>0.2</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.79</v>
+        <v>-1.8</v>
       </c>
       <c r="U5" t="n">
         <v>46.7</v>
       </c>
       <c r="V5" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>424.93</v>
+        <v>429.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>443.36</v>
+        <v>432.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>433.19</v>
+        <v>432.25</v>
       </c>
       <c r="AA5" t="n">
         <v>413.41</v>
@@ -1282,10 +1282,10 @@
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>447.84</v>
+        <v>448.37</v>
       </c>
       <c r="AN5" t="n">
-        <v>415.84</v>
+        <v>416.05</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>433.19</v>
+        <v>432.25</v>
       </c>
     </row>
     <row r="6">
@@ -1402,13 +1402,13 @@
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2117.49</v>
+        <v>2141.31</v>
       </c>
       <c r="Y6" t="n">
-        <v>2209.5</v>
+        <v>2159.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>2164.91</v>
+        <v>2159.29</v>
       </c>
       <c r="AA6" t="n">
         <v>2065.4</v>
@@ -1449,10 +1449,10 @@
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>2212.22</v>
+        <v>2214.48</v>
       </c>
       <c r="AN6" t="n">
-        <v>2093.93</v>
+        <v>2093.51</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[2153.5, 2162.72, 2171.94, 2181.16, 2190.38, 2199.6]</t>
+          <t>[2153.5, 2162.66, 2171.83, 2180.99, 2190.15, 2199.32]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2153.5, 2186.21, 2205.17, 2221.85, 2237.37, 2252.13]</t>
+          <t>[2153.5, 2186.16, 2205.05, 2221.68, 2237.14, 2251.85]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2153.5, 2145.1, 2147.02, 2150.64, 2155.14, 2160.2]</t>
+          <t>[2153.5, 2145.04, 2146.91, 2150.47, 2154.91, 2159.92]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>2164.91</v>
+        <v>2159.29</v>
       </c>
     </row>
     <row r="7">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>416806.78</v>
+        <v>134180.11</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,146 +1513,146 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>419</v>
+        <v>116.75</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹417.59 - ₹421.11</t>
+          <t>₹116.33 - ₹117.37</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>424.62</v>
+        <v>118.42</v>
       </c>
       <c r="I7" t="n">
-        <v>405.16</v>
+        <v>115.78</v>
       </c>
       <c r="J7" t="n">
-        <v>396.17</v>
+        <v>112.52</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>112.43</v>
       </c>
       <c r="L7" t="n">
-        <v>4.14</v>
+        <v>3.93</v>
       </c>
       <c r="M7" t="n">
-        <v>7.02</v>
+        <v>0.8</v>
       </c>
       <c r="N7" t="n">
-        <v>7.53</v>
+        <v>1.06</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.52</v>
+        <v>-0.26</v>
       </c>
       <c r="P7" t="n">
-        <v>7.03</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
         <v>12.29</v>
       </c>
       <c r="R7" t="n">
-        <v>47.3</v>
+        <v>47.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.95</v>
+        <v>-1.12</v>
       </c>
       <c r="U7" t="n">
-        <v>51.7</v>
+        <v>53.3</v>
       </c>
       <c r="V7" t="n">
-        <v>3.57</v>
+        <v>2.87</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>409.96</v>
+        <v>116.53</v>
       </c>
       <c r="Y7" t="n">
-        <v>427.84</v>
+        <v>118.64</v>
       </c>
       <c r="Z7" t="n">
-        <v>413.48</v>
+        <v>118.64</v>
       </c>
       <c r="AA7" t="n">
-        <v>408.46</v>
+        <v>113.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>416.08</v>
+        <v>116.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>422.91</v>
+        <v>118.18</v>
       </c>
       <c r="AD7" t="n">
-        <v>426.83</v>
+        <v>119.62</v>
       </c>
       <c r="AE7" t="n">
-        <v>62.6</v>
+        <v>51.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>20.5</v>
+        <v>6.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>21</v>
+        <v>15.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>28.5</v>
+        <v>38.1</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>428.35</v>
+        <v>120.02</v>
       </c>
       <c r="AN7" t="n">
-        <v>409.48</v>
+        <v>113.6</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹416,806.78 Cr., a P/E ratio of 20.53, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,180.11 Cr., a P/E ratio of 6.07, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (7.02) trades below Signal (7.53) with an expanding histogram (-0.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹400.00). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.30 (Consolidation Zone), while MACD Line (0.80) trades below Signal (1.06) with an expanding histogram (-0.26). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.93% above the 200-day DMA (₹112.43). Daily volatility envelope is bounded by ATR(14) of ₹2.08.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹419.00) is positioned above the 30-day DMA (₹405.16), 50-day DMA (₹396.17), and 200-day DMA (₹400.00). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.75) is positioned above the 30-day DMA (₹115.78), 50-day DMA (₹112.52), and 200-day DMA (₹112.43). The price distance from 200 DMA is +3.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[419.0, 420.26, 421.51, 422.77, 424.03, 425.28]</t>
+          <t>[116.75, 117.68, 118.6, 119.53, 120.46, 121.38]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[419.0, 423.07, 425.49, 427.64, 429.65, 431.57]</t>
+          <t>[116.75, 118.51, 119.78, 120.97, 122.12, 123.24]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[419.0, 418.15, 418.53, 419.12, 419.81, 420.57]</t>
+          <t>[116.75, 117.05, 117.72, 118.45, 119.21, 119.98]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>413.48</v>
+        <v>118.64</v>
       </c>
     </row>
     <row r="8">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30963.05</v>
+        <v>416806.78</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1680,146 +1680,146 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>562.9</v>
+        <v>419</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹559.68 - ₹567.73</t>
+          <t>₹417.59 - ₹421.11</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>575.79</v>
+        <v>424.62</v>
       </c>
       <c r="I8" t="n">
-        <v>515.35</v>
+        <v>405.16</v>
       </c>
       <c r="J8" t="n">
-        <v>523.51</v>
+        <v>396.17</v>
       </c>
       <c r="K8" t="n">
-        <v>523.36</v>
+        <v>400</v>
       </c>
       <c r="L8" t="n">
-        <v>5.53</v>
+        <v>4.14</v>
       </c>
       <c r="M8" t="n">
-        <v>12.09</v>
+        <v>7.02</v>
       </c>
       <c r="N8" t="n">
-        <v>6.96</v>
+        <v>7.53</v>
       </c>
       <c r="O8" t="n">
-        <v>5.13</v>
+        <v>-0.52</v>
       </c>
       <c r="P8" t="n">
-        <v>16.11</v>
+        <v>7.03</v>
       </c>
       <c r="Q8" t="n">
         <v>12.29</v>
       </c>
       <c r="R8" t="n">
-        <v>46.6</v>
+        <v>46.9</v>
       </c>
       <c r="S8" t="n">
-        <v>0.19</v>
+        <v>0.32</v>
       </c>
       <c r="T8" t="n">
-        <v>-2.05</v>
+        <v>-0.96</v>
       </c>
       <c r="U8" t="n">
-        <v>45</v>
+        <v>51.7</v>
       </c>
       <c r="V8" t="n">
-        <v>5.71</v>
+        <v>3.57</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>542.64</v>
+        <v>414.58</v>
       </c>
       <c r="Y8" t="n">
-        <v>572.1900000000001</v>
+        <v>427.99</v>
       </c>
       <c r="Z8" t="n">
-        <v>572.1900000000001</v>
+        <v>427.99</v>
       </c>
       <c r="AA8" t="n">
-        <v>538.74</v>
+        <v>408.46</v>
       </c>
       <c r="AB8" t="n">
-        <v>560.42</v>
+        <v>416.08</v>
       </c>
       <c r="AC8" t="n">
-        <v>574.84</v>
+        <v>422.91</v>
       </c>
       <c r="AD8" t="n">
-        <v>586.77</v>
+        <v>426.83</v>
       </c>
       <c r="AE8" t="n">
-        <v>78</v>
+        <v>62.6</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.26</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.4</v>
+        <v>20.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AK8" t="n">
-        <v>65.2</v>
+        <v>28.5</v>
       </c>
       <c r="AL8" t="n">
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>576.83</v>
+        <v>428.01</v>
       </c>
       <c r="AN8" t="n">
-        <v>548.13</v>
+        <v>410.24</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,963.05 Cr., a P/E ratio of 5.40, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹416,806.78 Cr., a P/E ratio of 20.53, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.98 (Bullish Momentum Zone), while MACD Line (12.09) trades above Signal (6.96) with an expanding histogram (+5.13). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.53% above the 200-day DMA (₹523.36). Daily volatility envelope is bounded by ATR(14) of ₹16.11.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (7.02) trades below Signal (7.53) with an expanding histogram (-0.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹400.00). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹562.90) is positioned above the 30-day DMA (₹515.35), 50-day DMA (₹523.51), and 200-day DMA (₹523.36). The price distance from 200 DMA is +5.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹419.00) is positioned above the 30-day DMA (₹405.16), 50-day DMA (₹396.17), and 200-day DMA (₹400.00). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[562.9, 564.59, 566.28, 567.97, 569.65, 571.34]</t>
+          <t>[419.0, 420.26, 421.51, 422.77, 424.03, 425.28]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[562.9, 571.03, 575.39, 579.13, 582.54, 585.75]</t>
+          <t>[419.0, 423.07, 425.49, 427.64, 429.65, 431.57]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[562.9, 559.76, 559.44, 559.6, 559.99, 560.54]</t>
+          <t>[419.0, 418.15, 418.53, 419.12, 419.81, 420.57]</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>572.1900000000001</v>
+        <v>427.99</v>
       </c>
     </row>
     <row r="9">
@@ -1885,13 +1885,13 @@
         <v>12.29</v>
       </c>
       <c r="R9" t="n">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="S9" t="n">
         <v>0.26</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.25</v>
+        <v>-1.26</v>
       </c>
       <c r="U9" t="n">
         <v>50</v>
@@ -1903,13 +1903,13 @@
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>280.56</v>
+        <v>283.72</v>
       </c>
       <c r="Y9" t="n">
-        <v>296.54</v>
+        <v>285.26</v>
       </c>
       <c r="Z9" t="n">
-        <v>296.54</v>
+        <v>280.38</v>
       </c>
       <c r="AA9" t="n">
         <v>278.48</v>
@@ -1950,10 +1950,10 @@
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>295.38</v>
+        <v>295.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>278.56</v>
+        <v>278.83</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>296.54</v>
+        <v>280.38</v>
       </c>
     </row>
     <row r="10">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>134180.11</v>
+        <v>83053.21000000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2014,146 +2014,146 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>116.75</v>
+        <v>1797.3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹116.33 - ₹117.37</t>
+          <t>₹1787.84 - ₹1811.5</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>118.42</v>
+        <v>1835.16</v>
       </c>
       <c r="I10" t="n">
-        <v>115.78</v>
+        <v>1748.18</v>
       </c>
       <c r="J10" t="n">
-        <v>112.52</v>
+        <v>1680.74</v>
       </c>
       <c r="K10" t="n">
-        <v>112.43</v>
+        <v>1651.86</v>
       </c>
       <c r="L10" t="n">
-        <v>3.93</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8</v>
+        <v>42.02</v>
       </c>
       <c r="N10" t="n">
-        <v>1.06</v>
+        <v>50.65</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.26</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>47.32</v>
       </c>
       <c r="Q10" t="n">
         <v>12.29</v>
       </c>
       <c r="R10" t="n">
-        <v>45</v>
+        <v>45.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.11</v>
+        <v>-1.91</v>
       </c>
       <c r="U10" t="n">
-        <v>53.3</v>
+        <v>55</v>
       </c>
       <c r="V10" t="n">
-        <v>2.87</v>
+        <v>5.58</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>115.23</v>
+        <v>1788.61</v>
       </c>
       <c r="Y10" t="n">
-        <v>120.07</v>
+        <v>1820.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>115.81</v>
+        <v>1820.18</v>
       </c>
       <c r="AA10" t="n">
-        <v>113.63</v>
+        <v>1726.32</v>
       </c>
       <c r="AB10" t="n">
-        <v>116.35</v>
+        <v>1789.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>118.18</v>
+        <v>1821.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>119.62</v>
+        <v>1845.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>51.3</v>
+        <v>53.1</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.09</v>
+        <v>0.19</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.1</v>
+        <v>111.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>15.2</v>
+        <v>40.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>38.1</v>
+        <v>10.2</v>
       </c>
       <c r="AL10" t="n">
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>120.06</v>
+        <v>1858.09</v>
       </c>
       <c r="AN10" t="n">
-        <v>113.5</v>
+        <v>1737.68</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,180.11 Cr., a P/E ratio of 6.07, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹83,053.21 Cr., a P/E ratio of 111.08, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.30 (Consolidation Zone), while MACD Line (0.80) trades below Signal (1.06) with an expanding histogram (-0.26). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.93% above the 200-day DMA (₹112.43). Daily volatility envelope is bounded by ATR(14) of ₹2.08.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.10 (Consolidation Zone), while MACD Line (42.02) trades below Signal (50.65) with an expanding histogram (-8.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.97% above the 200-day DMA (₹1651.86). Daily volatility envelope is bounded by ATR(14) of ₹47.32.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.75) is positioned above the 30-day DMA (₹115.78), 50-day DMA (₹112.52), and 200-day DMA (₹112.43). The price distance from 200 DMA is +3.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,797.30) is positioned above the 30-day DMA (₹1,748.18), 50-day DMA (₹1,680.74), and 200-day DMA (₹1,651.86). The price distance from 200 DMA is +8.97%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[116.75, 117.68, 118.6, 119.53, 120.46, 121.38]</t>
+          <t>[1797.3, 1806.42, 1815.54, 1824.65, 1833.77, 1842.89]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[116.75, 118.51, 119.78, 120.97, 122.12, 123.24]</t>
+          <t>[1797.3, 1825.35, 1842.31, 1857.44, 1871.63, 1885.22]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[116.75, 117.05, 117.72, 118.45, 119.21, 119.98]</t>
+          <t>[1797.3, 1792.22, 1795.46, 1800.07, 1805.38, 1811.15]</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>115.81</v>
+        <v>1820.18</v>
       </c>
     </row>
     <row r="11">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>61810.36</v>
+        <v>61828.48</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2219,13 +2219,13 @@
         <v>12.29</v>
       </c>
       <c r="R11" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="S11" t="n">
         <v>0.19</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.77</v>
+        <v>-1.76</v>
       </c>
       <c r="U11" t="n">
         <v>51.7</v>
@@ -2237,13 +2237,13 @@
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>1002.1</v>
+        <v>1013.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>1109.16</v>
+        <v>1018.94</v>
       </c>
       <c r="Z11" t="n">
-        <v>1109.16</v>
+        <v>957.6</v>
       </c>
       <c r="AA11" t="n">
         <v>984.23</v>
@@ -2284,14 +2284,14 @@
         <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>1065.37</v>
+        <v>1068.2</v>
       </c>
       <c r="AN11" t="n">
-        <v>984.45</v>
+        <v>986.89</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹61,810.36 Cr., a P/E ratio of 31.85, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹61,828.48 Cr., a P/E ratio of 31.85, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>1109.16</v>
+        <v>957.6</v>
       </c>
     </row>
     <row r="12">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>83053.21000000001</v>
+        <v>30963.05</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2348,87 +2348,87 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1797.3</v>
+        <v>562.9</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹1787.84 - ₹1811.5</t>
+          <t>₹559.68 - ₹567.73</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1835.16</v>
+        <v>575.79</v>
       </c>
       <c r="I12" t="n">
-        <v>1748.18</v>
+        <v>515.35</v>
       </c>
       <c r="J12" t="n">
-        <v>1680.74</v>
+        <v>523.51</v>
       </c>
       <c r="K12" t="n">
-        <v>1651.86</v>
+        <v>523.36</v>
       </c>
       <c r="L12" t="n">
-        <v>8.970000000000001</v>
+        <v>5.53</v>
       </c>
       <c r="M12" t="n">
-        <v>42.02</v>
+        <v>12.09</v>
       </c>
       <c r="N12" t="n">
-        <v>50.65</v>
+        <v>6.96</v>
       </c>
       <c r="O12" t="n">
-        <v>-8.630000000000001</v>
+        <v>5.13</v>
       </c>
       <c r="P12" t="n">
-        <v>47.32</v>
+        <v>16.11</v>
       </c>
       <c r="Q12" t="n">
         <v>12.29</v>
       </c>
       <c r="R12" t="n">
-        <v>43</v>
+        <v>44.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.91</v>
+        <v>-2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="V12" t="n">
-        <v>5.58</v>
+        <v>5.71</v>
       </c>
       <c r="W12" t="n">
         <v>-0.77</v>
       </c>
       <c r="X12" t="n">
-        <v>1768.66</v>
+        <v>548.76</v>
       </c>
       <c r="Y12" t="n">
-        <v>1845.46</v>
+        <v>558.1900000000001</v>
       </c>
       <c r="Z12" t="n">
-        <v>1788.91</v>
+        <v>558.1900000000001</v>
       </c>
       <c r="AA12" t="n">
-        <v>1726.32</v>
+        <v>538.74</v>
       </c>
       <c r="AB12" t="n">
-        <v>1789.3</v>
+        <v>560.42</v>
       </c>
       <c r="AC12" t="n">
-        <v>1821.3</v>
+        <v>574.84</v>
       </c>
       <c r="AD12" t="n">
-        <v>1845.3</v>
+        <v>586.77</v>
       </c>
       <c r="AE12" t="n">
-        <v>53.1</v>
+        <v>78</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
@@ -2439,55 +2439,55 @@
         <v>0.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>111.1</v>
+        <v>5.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>40.1</v>
+        <v>14.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>10.2</v>
+        <v>65.2</v>
       </c>
       <c r="AL12" t="n">
         <v>15</v>
       </c>
       <c r="AM12" t="n">
-        <v>1858.98</v>
+        <v>577.64</v>
       </c>
       <c r="AN12" t="n">
-        <v>1742.5</v>
+        <v>548.73</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹83,053.21 Cr., a P/E ratio of 111.08, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,963.05 Cr., a P/E ratio of 5.40, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.10 (Consolidation Zone), while MACD Line (42.02) trades below Signal (50.65) with an expanding histogram (-8.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.97% above the 200-day DMA (₹1651.86). Daily volatility envelope is bounded by ATR(14) of ₹47.32.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.98 (Bullish Momentum Zone), while MACD Line (12.09) trades above Signal (6.96) with an expanding histogram (+5.13). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.53% above the 200-day DMA (₹523.36). Daily volatility envelope is bounded by ATR(14) of ₹16.11.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,797.30) is positioned above the 30-day DMA (₹1,748.18), 50-day DMA (₹1,680.74), and 200-day DMA (₹1,651.86). The price distance from 200 DMA is +8.97%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹562.90) is positioned above the 30-day DMA (₹515.35), 50-day DMA (₹523.51), and 200-day DMA (₹523.36). The price distance from 200 DMA is +5.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>[1797.3, 1806.42, 1815.54, 1824.65, 1833.77, 1842.89]</t>
+          <t>[562.9, 564.59, 566.28, 567.97, 569.65, 571.34]</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[1797.3, 1825.35, 1842.31, 1857.44, 1871.63, 1885.22]</t>
+          <t>[562.9, 571.03, 575.39, 579.13, 582.54, 585.75]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[1797.3, 1792.22, 1795.46, 1800.07, 1805.38, 1811.15]</t>
+          <t>[562.9, 559.76, 559.44, 559.6, 559.99, 560.54]</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>1788.91</v>
+        <v>558.1900000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -656,21 +656,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>297794.48</v>
+        <v>88067.42999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,152 +678,152 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>323.5</v>
+        <v>5637</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹322.12 - ₹325.57</t>
+          <t>₹5604.57 - ₹5685.64</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>329.01</v>
+        <v>5766.71</v>
       </c>
       <c r="I2" t="n">
-        <v>320.1</v>
+        <v>5579.23</v>
       </c>
       <c r="J2" t="n">
-        <v>307.72</v>
+        <v>5399.24</v>
       </c>
       <c r="K2" t="n">
-        <v>273.9</v>
+        <v>5400.46</v>
       </c>
       <c r="L2" t="n">
-        <v>17.6</v>
+        <v>2.14</v>
       </c>
       <c r="M2" t="n">
-        <v>4.55</v>
+        <v>29</v>
       </c>
       <c r="N2" t="n">
-        <v>6.65</v>
+        <v>69.16</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.1</v>
+        <v>-40.16</v>
       </c>
       <c r="P2" t="n">
-        <v>6.89</v>
+        <v>162.14</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.29</v>
+        <v>12.89</v>
       </c>
       <c r="R2" t="n">
-        <v>48.9</v>
+        <v>54.6</v>
       </c>
       <c r="S2" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.12</v>
+        <v>-1.52</v>
       </c>
       <c r="U2" t="n">
-        <v>50</v>
+        <v>58.3</v>
       </c>
       <c r="V2" t="n">
-        <v>2.44</v>
+        <v>6.14</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>317.41</v>
+        <v>5504.89</v>
       </c>
       <c r="Y2" t="n">
-        <v>361.43</v>
+        <v>5544.71</v>
       </c>
       <c r="Z2" t="n">
-        <v>361.43</v>
+        <v>5544.71</v>
       </c>
       <c r="AA2" t="n">
-        <v>313.17</v>
+        <v>5393.79</v>
       </c>
       <c r="AB2" t="n">
-        <v>321.45</v>
+        <v>5671</v>
       </c>
       <c r="AC2" t="n">
-        <v>326.85</v>
+        <v>5725</v>
       </c>
       <c r="AD2" t="n">
-        <v>330.2</v>
+        <v>5813</v>
       </c>
       <c r="AE2" t="n">
-        <v>35.3</v>
+        <v>43.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.24</v>
+        <v>0.03</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>718.9</v>
+        <v>46.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>182</v>
+        <v>29.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.6</v>
+        <v>12.2</v>
       </c>
       <c r="AL2" t="n">
-        <v>15</v>
+        <v>25.2</v>
       </c>
       <c r="AM2" t="n">
-        <v>336.6</v>
+        <v>5835.17</v>
       </c>
       <c r="AN2" t="n">
-        <v>312.39</v>
+        <v>5443.03</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹297,794.48 Cr., a P/E ratio of 718.89, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>PERSISTENT operates in the Technology sector. With an estimated Market Cap of ₹88,067.43 Cr., a P/E ratio of 46.24, and YoY Revenue Growth of +29.1%, the company demonstrates strong institutional backing, solid operating profit margins (12.24%), and healthy Return on Equity (25.20%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 35.26 (Consolidation Zone), while MACD Line (4.55) trades below Signal (6.65) with an expanding histogram (-2.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.60% above the 200-day DMA (₹273.90). Daily volatility envelope is bounded by ATR(14) of ₹6.89.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.61 (Consolidation Zone), while MACD Line (29.00) trades below Signal (69.16) with an expanding histogram (-40.16). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.14% above the 200-day DMA (₹5400.46). Daily volatility envelope is bounded by ATR(14) of ₹162.14.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹323.50) is positioned above the 30-day DMA (₹320.10), 50-day DMA (₹307.72), and 200-day DMA (₹273.90). The price distance from 200 DMA is +17.60%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PERSISTENT. Current Market Price (₹5,637.00) is positioned above the 30-day DMA (₹5,579.23), 50-day DMA (₹5,399.24), and 200-day DMA (₹5,400.46). The price distance from 200 DMA is +2.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[323.5, 324.47, 325.44, 326.41, 327.38, 328.35]</t>
+          <t>[5637.0, 5653.91, 5670.82, 5687.73, 5704.64, 5721.55]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[323.5, 327.22, 329.34, 331.18, 332.89, 334.51]</t>
+          <t>[5637.0, 5718.77, 5762.54, 5800.07, 5834.36, 5866.58]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[323.5, 322.4, 322.52, 322.83, 323.25, 323.73]</t>
+          <t>[5637.0, 5605.27, 5602.03, 5603.48, 5607.36, 5612.79]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>361.43</v>
+        <v>5544.71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79671.24000000001</v>
+        <v>79427.25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,91 +845,91 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>489.8</v>
+        <v>488.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹487.29 - ₹493.57</t>
+          <t>₹485.51 - ₹492.48</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>499.85</v>
+        <v>499.45</v>
       </c>
       <c r="I3" t="n">
-        <v>473.15</v>
+        <v>474.22</v>
       </c>
       <c r="J3" t="n">
-        <v>459</v>
+        <v>460.37</v>
       </c>
       <c r="K3" t="n">
-        <v>453.98</v>
+        <v>454.35</v>
       </c>
       <c r="L3" t="n">
-        <v>10.2</v>
+        <v>7.8</v>
       </c>
       <c r="M3" t="n">
-        <v>10.64</v>
+        <v>9.94</v>
       </c>
       <c r="N3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="P3" t="n">
-        <v>12.56</v>
+        <v>13.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.29</v>
+        <v>12.89</v>
       </c>
       <c r="R3" t="n">
-        <v>48.4</v>
+        <v>49.3</v>
       </c>
       <c r="S3" t="n">
         <v>0.21</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.46</v>
+        <v>-1.57</v>
       </c>
       <c r="U3" t="n">
-        <v>61.7</v>
+        <v>60</v>
       </c>
       <c r="V3" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>485.8</v>
+        <v>487.88</v>
       </c>
       <c r="Y3" t="n">
-        <v>512.71</v>
+        <v>511.66</v>
       </c>
       <c r="Z3" t="n">
-        <v>512.71</v>
+        <v>511.66</v>
       </c>
       <c r="AA3" t="n">
-        <v>470.96</v>
+        <v>467.39</v>
       </c>
       <c r="AB3" t="n">
-        <v>495.72</v>
+        <v>489.57</v>
       </c>
       <c r="AC3" t="n">
-        <v>506.04</v>
+        <v>493.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>522.27</v>
+        <v>497.97</v>
       </c>
       <c r="AE3" t="n">
-        <v>70.09999999999999</v>
+        <v>59.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Vol Spike 1.9x | Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Vol Spike 2.1x | Low VIX (12.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
@@ -948,54 +948,54 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>505.22</v>
+        <v>504.34</v>
       </c>
       <c r="AN3" t="n">
-        <v>475.2</v>
+        <v>473.28</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹79,671.24 Cr., a P/E ratio of 9.53, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
+          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹79,427.25 Cr., a P/E ratio of 9.50, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.05 (Bullish Momentum Zone), while MACD Line (10.64) trades above Signal (9.70) with an expanding histogram (+0.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.20% above the 200-day DMA (₹453.98). Daily volatility envelope is bounded by ATR(14) of ₹12.56.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.31 (Bullish Momentum Zone), while MACD Line (9.94) trades above Signal (9.75) with an expanding histogram (+0.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.80% above the 200-day DMA (₹454.35). Daily volatility envelope is bounded by ATR(14) of ₹13.94.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹489.80) is positioned above the 30-day DMA (₹473.15), 50-day DMA (₹459.00), and 200-day DMA (₹453.98). The price distance from 200 DMA is +10.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹488.30) is positioned above the 30-day DMA (₹474.22), 50-day DMA (₹460.37), and 200-day DMA (₹454.35). The price distance from 200 DMA is +7.80%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[489.8, 491.27, 492.74, 494.21, 495.68, 497.15]</t>
+          <t>[488.3, 492.71, 497.12, 501.54, 505.95, 510.36]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[489.8, 496.29, 499.84, 502.91, 505.73, 508.38]</t>
+          <t>[488.3, 498.29, 505.01, 511.19, 517.1, 522.83]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[489.8, 487.5, 487.41, 487.68, 488.14, 488.72]</t>
+          <t>[488.3, 488.53, 491.21, 494.29, 497.58, 501.01]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>512.71</v>
+        <v>511.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1004,160 +1004,160 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>83378.82000000001</v>
+        <v>133433.07</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3276</v>
+        <v>116.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹3256.15 - ₹3305.77</t>
+          <t>₹115.67 - ₹116.75</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3355.39</v>
+        <v>117.84</v>
       </c>
       <c r="I4" t="n">
-        <v>3059</v>
+        <v>115.92</v>
       </c>
       <c r="J4" t="n">
-        <v>2940.21</v>
+        <v>112.74</v>
       </c>
       <c r="K4" t="n">
-        <v>2665.63</v>
+        <v>112.41</v>
       </c>
       <c r="L4" t="n">
-        <v>23.8</v>
+        <v>3.86</v>
       </c>
       <c r="M4" t="n">
-        <v>116.44</v>
+        <v>0.79</v>
       </c>
       <c r="N4" t="n">
-        <v>122.73</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.29</v>
+        <v>-0.21</v>
       </c>
       <c r="P4" t="n">
-        <v>99.23999999999999</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.29</v>
+        <v>12.89</v>
       </c>
       <c r="R4" t="n">
-        <v>45.9</v>
+        <v>48</v>
       </c>
       <c r="S4" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.93</v>
+        <v>-1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="V4" t="n">
-        <v>3.5</v>
+        <v>2.87</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>3258.71</v>
+        <v>116.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>3275.68</v>
+        <v>118.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>2650.75</v>
+        <v>118.12</v>
       </c>
       <c r="AA4" t="n">
-        <v>3127.14</v>
+        <v>112.84</v>
       </c>
       <c r="AB4" t="n">
-        <v>3304.07</v>
+        <v>116.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>3360.94</v>
+        <v>117.07</v>
       </c>
       <c r="AD4" t="n">
-        <v>3445.87</v>
+        <v>118.05</v>
       </c>
       <c r="AE4" t="n">
-        <v>57.3</v>
+        <v>54.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.16</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>54.1</v>
+        <v>6</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85.3</v>
+        <v>15.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>55.6</v>
+        <v>38.1</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>3420.97</v>
+        <v>119.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>3170.13</v>
+        <v>113.14</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹83,378.82 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹133,433.07 Cr., a P/E ratio of 6.04, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.34 (Bullish Momentum Zone), while MACD Line (116.44) trades below Signal (122.73) with an expanding histogram (-6.29). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +23.80% above the 200-day DMA (₹2665.63). Daily volatility envelope is bounded by ATR(14) of ₹99.24.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.06 (Consolidation Zone), while MACD Line (0.79) trades below Signal (1.00) with an expanding histogram (-0.21). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.86% above the 200-day DMA (₹112.41). Daily volatility envelope is bounded by ATR(14) of ₹2.17.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,276.00) is positioned above the 30-day DMA (₹3,059.00), 50-day DMA (₹2,940.21), and 200-day DMA (₹2,665.63). The price distance from 200 DMA is +23.80%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.10) is positioned above the 30-day DMA (₹115.92), 50-day DMA (₹112.74), and 200-day DMA (₹112.41). The price distance from 200 DMA is +3.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[3276.0, 3291.19, 3306.37, 3321.56, 3336.74, 3351.93]</t>
+          <t>[116.1, 117.17, 118.23, 119.3, 120.37, 121.43]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[3276.0, 3330.88, 3362.51, 3390.32, 3416.14, 3440.69]</t>
+          <t>[116.1, 118.03, 119.46, 120.8, 122.1, 123.38]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[3276.0, 3261.41, 3264.27, 3269.99, 3277.2, 3285.35]</t>
+          <t>[116.1, 116.52, 117.31, 118.17, 119.07, 119.98]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2650.75</v>
+        <v>118.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>150076.93</v>
+        <v>147064.95</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,98 +1179,98 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>431</v>
+        <v>422.35</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹428.65 - ₹434.52</t>
+          <t>₹419.86 - ₹426.09</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>440.38</v>
+        <v>432.31</v>
       </c>
       <c r="I5" t="n">
-        <v>420.4</v>
+        <v>421.2</v>
       </c>
       <c r="J5" t="n">
-        <v>413.87</v>
+        <v>414.85</v>
       </c>
       <c r="K5" t="n">
-        <v>337.32</v>
+        <v>338.03</v>
       </c>
       <c r="L5" t="n">
-        <v>27.33</v>
+        <v>27.5</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4</v>
+        <v>4.39</v>
       </c>
       <c r="N5" t="n">
-        <v>4.67</v>
+        <v>4.61</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.27</v>
+        <v>-0.23</v>
       </c>
       <c r="P5" t="n">
-        <v>11.73</v>
+        <v>12.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.29</v>
+        <v>12.89</v>
       </c>
       <c r="R5" t="n">
-        <v>49.2</v>
+        <v>47.7</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.8</v>
+        <v>-2.06</v>
       </c>
       <c r="U5" t="n">
         <v>46.7</v>
       </c>
       <c r="V5" t="n">
-        <v>3.67</v>
+        <v>3.41</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>429.73</v>
+        <v>419.27</v>
       </c>
       <c r="Y5" t="n">
-        <v>432.25</v>
+        <v>423.58</v>
       </c>
       <c r="Z5" t="n">
-        <v>432.25</v>
+        <v>423.58</v>
       </c>
       <c r="AA5" t="n">
-        <v>413.41</v>
+        <v>403.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>427.4</v>
+        <v>425.23</v>
       </c>
       <c r="AC5" t="n">
-        <v>436.6</v>
+        <v>429.11</v>
       </c>
       <c r="AD5" t="n">
-        <v>442.2</v>
+        <v>435.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>59.1</v>
+        <v>60.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (12.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>61.7</v>
+        <v>60.5</v>
       </c>
       <c r="AJ5" t="n">
         <v>40.3</v>
@@ -1282,49 +1282,49 @@
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>448.37</v>
+        <v>437.87</v>
       </c>
       <c r="AN5" t="n">
-        <v>416.05</v>
+        <v>407.39</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>BHEL operates in the Industrials sector. With an estimated Market Cap of ₹150,076.93 Cr., a P/E ratio of 61.75, and YoY Revenue Growth of +40.3%, the company demonstrates strong institutional backing, solid operating profit margins (6.76%), and healthy Return on Equity (15.00%).</t>
+          <t>BHEL operates in the Industrials sector. With an estimated Market Cap of ₹147,064.95 Cr., a P/E ratio of 60.51, and YoY Revenue Growth of +40.3%, the company demonstrates strong institutional backing, solid operating profit margins (6.76%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.15 (Bullish Momentum Zone), while MACD Line (4.40) trades below Signal (4.67) with an expanding histogram (-0.27). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.33% above the 200-day DMA (₹337.32). Daily volatility envelope is bounded by ATR(14) of ₹11.73.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.88 (Bullish Momentum Zone), while MACD Line (4.39) trades below Signal (4.61) with an expanding histogram (-0.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.50% above the 200-day DMA (₹338.03). Daily volatility envelope is bounded by ATR(14) of ₹12.45.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHEL. Current Market Price (₹431.00) is positioned above the 30-day DMA (₹420.40), 50-day DMA (₹413.87), and 200-day DMA (₹337.32). The price distance from 200 DMA is +27.33%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHEL. Current Market Price (₹422.35) is positioned above the 30-day DMA (₹421.20), 50-day DMA (₹414.85), and 200-day DMA (₹338.03). The price distance from 200 DMA is +27.50%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[431.0, 434.0, 437.0, 439.99, 442.99, 445.99]</t>
+          <t>[422.35, 423.62, 424.88, 426.15, 427.42, 428.69]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[431.0, 438.69, 443.63, 448.12, 452.37, 456.48]</t>
+          <t>[422.35, 428.6, 431.93, 434.78, 437.38, 439.82]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[431.0, 430.48, 432.02, 433.9, 435.96, 438.12]</t>
+          <t>[422.35, 419.88, 419.6, 419.68, 419.95, 420.33]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>432.25</v>
+        <v>423.58</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59793.74</v>
+        <v>58894.12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,98 +1346,98 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2153.5</v>
+        <v>2121.1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹2141.75 - ₹2171.12</t>
+          <t>₹2108.72 - ₹2139.67</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2200.49</v>
+        <v>2170.61</v>
       </c>
       <c r="I6" t="n">
-        <v>2094.62</v>
+        <v>2105.99</v>
       </c>
       <c r="J6" t="n">
-        <v>1982.91</v>
+        <v>1990.35</v>
       </c>
       <c r="K6" t="n">
-        <v>1948.54</v>
+        <v>1950.67</v>
       </c>
       <c r="L6" t="n">
-        <v>12.64</v>
+        <v>10.4</v>
       </c>
       <c r="M6" t="n">
-        <v>60.53</v>
+        <v>53.98</v>
       </c>
       <c r="N6" t="n">
-        <v>71.01000000000001</v>
+        <v>67.61</v>
       </c>
       <c r="O6" t="n">
-        <v>-10.48</v>
+        <v>-13.62</v>
       </c>
       <c r="P6" t="n">
-        <v>58.73</v>
+        <v>61.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.29</v>
+        <v>12.89</v>
       </c>
       <c r="R6" t="n">
-        <v>48.3</v>
+        <v>47.2</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.85</v>
+        <v>-2.06</v>
       </c>
       <c r="U6" t="n">
         <v>50</v>
       </c>
       <c r="V6" t="n">
-        <v>2.78</v>
+        <v>2.95</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2141.31</v>
+        <v>2073.44</v>
       </c>
       <c r="Y6" t="n">
-        <v>2159.29</v>
+        <v>2126.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>2159.29</v>
+        <v>2126.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>2065.4</v>
+        <v>2028.27</v>
       </c>
       <c r="AB6" t="n">
-        <v>2146.5</v>
+        <v>2129.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>2183.2</v>
+        <v>2151.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>2212.9</v>
+        <v>2181.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>57</v>
+        <v>51.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Low VIX (12.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>48.5</v>
+        <v>47.8</v>
       </c>
       <c r="AJ6" t="n">
         <v>8.5</v>
@@ -1449,54 +1449,54 @@
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>2214.48</v>
+        <v>2180.15</v>
       </c>
       <c r="AN6" t="n">
-        <v>2093.51</v>
+        <v>2061.81</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹59,793.74 Cr., a P/E ratio of 48.55, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹58,894.12 Cr., a P/E ratio of 47.82, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.04 (Bullish Momentum Zone), while MACD Line (60.53) trades below Signal (71.01) with an expanding histogram (-10.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.64% above the 200-day DMA (₹1948.54). Daily volatility envelope is bounded by ATR(14) of ₹58.73.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.71 (Consolidation Zone), while MACD Line (53.98) trades below Signal (67.61) with an expanding histogram (-13.62). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.40% above the 200-day DMA (₹1950.67). Daily volatility envelope is bounded by ATR(14) of ₹61.89.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,153.50) is positioned above the 30-day DMA (₹2,094.62), 50-day DMA (₹1,982.91), and 200-day DMA (₹1,948.54). The price distance from 200 DMA is +12.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,121.10) is positioned above the 30-day DMA (₹2,105.99), 50-day DMA (₹1,990.35), and 200-day DMA (₹1,950.67). The price distance from 200 DMA is +10.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[2153.5, 2162.66, 2171.83, 2180.99, 2190.15, 2199.32]</t>
+          <t>[2121.1, 2127.46, 2133.83, 2140.19, 2146.55, 2152.92]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2153.5, 2186.16, 2205.05, 2221.68, 2237.14, 2251.85]</t>
+          <t>[2121.1, 2152.22, 2168.83, 2183.07, 2196.06, 2208.27]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2153.5, 2145.04, 2146.91, 2150.47, 2154.91, 2159.92]</t>
+          <t>[2121.1, 2108.9, 2107.57, 2108.03, 2109.42, 2111.4]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>2159.29</v>
+        <v>2126.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>134180.11</v>
+        <v>82410.89</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,166 +1513,166 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>116.75</v>
+        <v>1783.4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹116.33 - ₹117.37</t>
+          <t>₹1773.74 - ₹1797.9</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>118.42</v>
+        <v>1822.06</v>
       </c>
       <c r="I7" t="n">
-        <v>115.78</v>
+        <v>1754.97</v>
       </c>
       <c r="J7" t="n">
-        <v>112.52</v>
+        <v>1683.04</v>
       </c>
       <c r="K7" t="n">
-        <v>112.43</v>
+        <v>1651.94</v>
       </c>
       <c r="L7" t="n">
-        <v>3.93</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8</v>
+        <v>37.52</v>
       </c>
       <c r="N7" t="n">
-        <v>1.06</v>
+        <v>48.03</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.26</v>
+        <v>-10.51</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>48.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.29</v>
+        <v>12.89</v>
       </c>
       <c r="R7" t="n">
-        <v>47.1</v>
+        <v>45.2</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.12</v>
+        <v>-1.96</v>
       </c>
       <c r="U7" t="n">
         <v>53.3</v>
       </c>
       <c r="V7" t="n">
-        <v>2.87</v>
+        <v>4.84</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>116.53</v>
+        <v>1781.19</v>
       </c>
       <c r="Y7" t="n">
-        <v>118.64</v>
+        <v>1807.27</v>
       </c>
       <c r="Z7" t="n">
-        <v>118.64</v>
+        <v>1807.27</v>
       </c>
       <c r="AA7" t="n">
-        <v>113.63</v>
+        <v>1710.92</v>
       </c>
       <c r="AB7" t="n">
-        <v>116.35</v>
+        <v>1788.87</v>
       </c>
       <c r="AC7" t="n">
-        <v>118.18</v>
+        <v>1798.84</v>
       </c>
       <c r="AD7" t="n">
-        <v>119.62</v>
+        <v>1814.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>51.3</v>
+        <v>50.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.1</v>
+        <v>110.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15.2</v>
+        <v>40.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>38.1</v>
+        <v>10.2</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>120.02</v>
+        <v>1838.48</v>
       </c>
       <c r="AN7" t="n">
-        <v>113.6</v>
+        <v>1725.05</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,180.11 Cr., a P/E ratio of 6.07, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹82,410.89 Cr., a P/E ratio of 110.22, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.30 (Consolidation Zone), while MACD Line (0.80) trades below Signal (1.06) with an expanding histogram (-0.26). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.93% above the 200-day DMA (₹112.43). Daily volatility envelope is bounded by ATR(14) of ₹2.08.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.33 (Consolidation Zone), while MACD Line (37.52) trades below Signal (48.03) with an expanding histogram (-10.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.80% above the 200-day DMA (₹1651.94). Daily volatility envelope is bounded by ATR(14) of ₹48.32.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.75) is positioned above the 30-day DMA (₹115.78), 50-day DMA (₹112.52), and 200-day DMA (₹112.43). The price distance from 200 DMA is +3.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,783.40) is positioned above the 30-day DMA (₹1,754.97), 50-day DMA (₹1,683.04), and 200-day DMA (₹1,651.94). The price distance from 200 DMA is +8.80%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[116.75, 117.68, 118.6, 119.53, 120.46, 121.38]</t>
+          <t>[1783.4, 1798.83, 1814.26, 1829.69, 1845.12, 1860.56]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[116.75, 118.51, 119.78, 120.97, 122.12, 123.24]</t>
+          <t>[1783.4, 1818.16, 1841.6, 1863.17, 1883.78, 1903.78]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[116.75, 117.05, 117.72, 118.45, 119.21, 119.98]</t>
+          <t>[1783.4, 1784.33, 1793.76, 1804.58, 1816.13, 1828.14]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>118.64</v>
+        <v>1807.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>416806.78</v>
+        <v>142939.67</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1680,166 +1680,166 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>419</v>
+        <v>1613.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹417.59 - ₹421.11</t>
+          <t>₹1605.36 - ₹1625.72</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>424.62</v>
+        <v>1646.08</v>
       </c>
       <c r="I8" t="n">
-        <v>405.16</v>
+        <v>1604.16</v>
       </c>
       <c r="J8" t="n">
-        <v>396.17</v>
+        <v>1577.26</v>
       </c>
       <c r="K8" t="n">
-        <v>400</v>
+        <v>1489.53</v>
       </c>
       <c r="L8" t="n">
-        <v>4.14</v>
+        <v>3.46</v>
       </c>
       <c r="M8" t="n">
-        <v>7.02</v>
+        <v>-11.97</v>
       </c>
       <c r="N8" t="n">
-        <v>7.53</v>
+        <v>-0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.52</v>
+        <v>-11.94</v>
       </c>
       <c r="P8" t="n">
-        <v>7.03</v>
+        <v>40.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.29</v>
+        <v>12.89</v>
       </c>
       <c r="R8" t="n">
-        <v>46.9</v>
+        <v>44.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.96</v>
+        <v>-1.55</v>
       </c>
       <c r="U8" t="n">
-        <v>51.7</v>
+        <v>46.7</v>
       </c>
       <c r="V8" t="n">
-        <v>3.57</v>
+        <v>4.31</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>414.58</v>
+        <v>1613.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>427.99</v>
+        <v>1625.89</v>
       </c>
       <c r="Z8" t="n">
-        <v>427.99</v>
+        <v>1594.33</v>
       </c>
       <c r="AA8" t="n">
-        <v>408.46</v>
+        <v>1552.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>416.08</v>
+        <v>1611.23</v>
       </c>
       <c r="AC8" t="n">
-        <v>422.91</v>
+        <v>1635.46</v>
       </c>
       <c r="AD8" t="n">
-        <v>426.83</v>
+        <v>1657.43</v>
       </c>
       <c r="AE8" t="n">
-        <v>62.6</v>
+        <v>42.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Low VIX (12.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>20.5</v>
+        <v>27.9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>21</v>
+        <v>17.7</v>
       </c>
       <c r="AK8" t="n">
-        <v>28.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AL8" t="n">
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>428.01</v>
+        <v>1658.98</v>
       </c>
       <c r="AN8" t="n">
-        <v>410.24</v>
+        <v>1570.05</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹416,806.78 Cr., a P/E ratio of 20.53, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹142,939.67 Cr., a P/E ratio of 27.92, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.56 (Bullish Momentum Zone), while MACD Line (7.02) trades below Signal (7.53) with an expanding histogram (-0.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.14% above the 200-day DMA (₹400.00). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.85 (Consolidation Zone), while MACD Line (-11.97) trades below Signal (-0.03) with an expanding histogram (-11.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.46% above the 200-day DMA (₹1489.53). Daily volatility envelope is bounded by ATR(14) of ₹40.72.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹419.00) is positioned above the 30-day DMA (₹405.16), 50-day DMA (₹396.17), and 200-day DMA (₹400.00). The price distance from 200 DMA is +4.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,613.50) is positioned above the 30-day DMA (₹1,604.16), 50-day DMA (₹1,577.26), and 200-day DMA (₹1,489.53). The price distance from 200 DMA is +3.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[419.0, 420.26, 421.51, 422.77, 424.03, 425.28]</t>
+          <t>[1613.5, 1633.84, 1654.17, 1674.51, 1694.84, 1715.18]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[419.0, 423.07, 425.49, 427.64, 429.65, 431.57]</t>
+          <t>[1613.5, 1650.12, 1677.21, 1702.72, 1727.42, 1751.6]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[419.0, 418.15, 418.53, 419.12, 419.81, 420.57]</t>
+          <t>[1613.5, 1621.62, 1636.89, 1653.35, 1670.41, 1687.86]</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>427.99</v>
+        <v>1594.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>43080</v>
+        <v>410887.94</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1847,157 +1847,157 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>287.2</v>
+        <v>413.05</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹286.04 - ₹288.94</t>
+          <t>₹411.6 - ₹415.23</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>291.85</v>
+        <v>418.86</v>
       </c>
       <c r="I9" t="n">
-        <v>286.26</v>
+        <v>406.12</v>
       </c>
       <c r="J9" t="n">
-        <v>282.16</v>
+        <v>396.63</v>
       </c>
       <c r="K9" t="n">
-        <v>278.2</v>
+        <v>400</v>
       </c>
       <c r="L9" t="n">
-        <v>3.77</v>
+        <v>4.75</v>
       </c>
       <c r="M9" t="n">
-        <v>1.76</v>
+        <v>6.69</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>7.36</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.95</v>
+        <v>-0.67</v>
       </c>
       <c r="P9" t="n">
-        <v>5.81</v>
+        <v>7.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.29</v>
+        <v>12.89</v>
       </c>
       <c r="R9" t="n">
-        <v>46.3</v>
+        <v>44.2</v>
       </c>
       <c r="S9" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.26</v>
+        <v>-1.12</v>
       </c>
       <c r="U9" t="n">
         <v>50</v>
       </c>
       <c r="V9" t="n">
-        <v>5.01</v>
+        <v>3.61</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>283.72</v>
+        <v>407.16</v>
       </c>
       <c r="Y9" t="n">
-        <v>285.26</v>
+        <v>421.91</v>
       </c>
       <c r="Z9" t="n">
-        <v>280.38</v>
+        <v>421.91</v>
       </c>
       <c r="AA9" t="n">
-        <v>278.48</v>
+        <v>402.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>286.08</v>
+        <v>414.9</v>
       </c>
       <c r="AC9" t="n">
-        <v>288.31</v>
+        <v>418.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>289.43</v>
+        <v>424.25</v>
       </c>
       <c r="AE9" t="n">
-        <v>46.7</v>
+        <v>65.7</v>
       </c>
       <c r="AF9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>10.2</v>
+        <v>20.2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-53.2</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
-        <v>11.3</v>
+        <v>28.5</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>295.25</v>
+        <v>421.69</v>
       </c>
       <c r="AN9" t="n">
-        <v>278.83</v>
+        <v>403.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,080.00 Cr., a P/E ratio of 10.24, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹410,887.94 Cr., a P/E ratio of 20.24, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.74 (Consolidation Zone), while MACD Line (1.76) trades below Signal (2.70) with an expanding histogram (-0.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.77% above the 200-day DMA (₹278.20). Daily volatility envelope is bounded by ATR(14) of ₹5.81.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.71 (Bullish Momentum Zone), while MACD Line (6.69) trades below Signal (7.36) with an expanding histogram (-0.67). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.75% above the 200-day DMA (₹400.00). Daily volatility envelope is bounded by ATR(14) of ₹7.26.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹287.20) is positioned above the 30-day DMA (₹286.26), 50-day DMA (₹282.16), and 200-day DMA (₹278.20). The price distance from 200 DMA is +3.77%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹413.05) is positioned above the 30-day DMA (₹406.12), 50-day DMA (₹396.63), and 200-day DMA (₹400.00). The price distance from 200 DMA is +4.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[287.2, 288.06, 288.92, 289.78, 290.65, 291.51]</t>
+          <t>[413.05, 414.29, 415.53, 416.77, 418.01, 419.25]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[287.2, 290.39, 292.21, 293.81, 295.3, 296.71]</t>
+          <t>[413.05, 417.19, 419.64, 421.8, 423.82, 425.74]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[287.2, 286.32, 286.46, 286.76, 287.16, 287.61]</t>
+          <t>[413.05, 412.11, 412.45, 412.99, 413.65, 414.37]</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>280.38</v>
+        <v>421.91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>83053.21000000001</v>
+        <v>81495.41</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2014,152 +2014,152 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1797.3</v>
+        <v>3202</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹1787.84 - ₹1811.5</t>
+          <t>₹3181.69 - ₹3232.47</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1835.16</v>
+        <v>3283.25</v>
       </c>
       <c r="I10" t="n">
-        <v>1748.18</v>
+        <v>3078.68</v>
       </c>
       <c r="J10" t="n">
-        <v>1680.74</v>
+        <v>2949.59</v>
       </c>
       <c r="K10" t="n">
-        <v>1651.86</v>
+        <v>2671.75</v>
       </c>
       <c r="L10" t="n">
-        <v>8.970000000000001</v>
+        <v>22.62</v>
       </c>
       <c r="M10" t="n">
-        <v>42.02</v>
+        <v>108.05</v>
       </c>
       <c r="N10" t="n">
-        <v>50.65</v>
+        <v>119.79</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.630000000000001</v>
+        <v>-11.74</v>
       </c>
       <c r="P10" t="n">
-        <v>47.32</v>
+        <v>101.56</v>
       </c>
       <c r="Q10" t="n">
-        <v>12.29</v>
+        <v>12.89</v>
       </c>
       <c r="R10" t="n">
-        <v>45.4</v>
+        <v>43.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.91</v>
+        <v>-2.17</v>
       </c>
       <c r="U10" t="n">
-        <v>55</v>
+        <v>51.7</v>
       </c>
       <c r="V10" t="n">
-        <v>5.58</v>
+        <v>3.37</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>1788.61</v>
+        <v>3186.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>1820.18</v>
+        <v>3203.43</v>
       </c>
       <c r="Z10" t="n">
-        <v>1820.18</v>
+        <v>2590.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>1726.32</v>
+        <v>3049.66</v>
       </c>
       <c r="AB10" t="n">
-        <v>1789.3</v>
+        <v>3208.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>1821.3</v>
+        <v>3260.94</v>
       </c>
       <c r="AD10" t="n">
-        <v>1845.3</v>
+        <v>3319.87</v>
       </c>
       <c r="AE10" t="n">
-        <v>53.1</v>
+        <v>51</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>111.1</v>
+        <v>52.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>40.1</v>
+        <v>85.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>10.2</v>
+        <v>55.6</v>
       </c>
       <c r="AL10" t="n">
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>1858.09</v>
+        <v>3332.62</v>
       </c>
       <c r="AN10" t="n">
-        <v>1737.68</v>
+        <v>3087.57</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹83,053.21 Cr., a P/E ratio of 111.08, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹81,495.41 Cr., a P/E ratio of 52.83, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.10 (Consolidation Zone), while MACD Line (42.02) trades below Signal (50.65) with an expanding histogram (-8.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.97% above the 200-day DMA (₹1651.86). Daily volatility envelope is bounded by ATR(14) of ₹47.32.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.03 (Consolidation Zone), while MACD Line (108.05) trades below Signal (119.79) with an expanding histogram (-11.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +22.62% above the 200-day DMA (₹2671.75). Daily volatility envelope is bounded by ATR(14) of ₹101.56.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,797.30) is positioned above the 30-day DMA (₹1,748.18), 50-day DMA (₹1,680.74), and 200-day DMA (₹1,651.86). The price distance from 200 DMA is +8.97%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,202.00) is positioned above the 30-day DMA (₹3,078.68), 50-day DMA (₹2,949.59), and 200-day DMA (₹2,671.75). The price distance from 200 DMA is +22.62%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[1797.3, 1806.42, 1815.54, 1824.65, 1833.77, 1842.89]</t>
+          <t>[3202.0, 3218.63, 3235.26, 3251.89, 3268.52, 3285.15]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[1797.3, 1825.35, 1842.31, 1857.44, 1871.63, 1885.22]</t>
+          <t>[3202.0, 3259.25, 3292.71, 3322.25, 3349.77, 3375.99]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[1797.3, 1792.22, 1795.46, 1800.07, 1805.38, 1811.15]</t>
+          <t>[3202.0, 3188.16, 3192.17, 3199.12, 3207.58, 3217.02]</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1820.18</v>
+        <v>2590.88</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>61828.48</v>
+        <v>60087.77</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2181,98 +2181,98 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1026.5</v>
+        <v>997.6</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹1020.86 - ₹1034.95</t>
+          <t>₹991.74 - ₹1006.4</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1049.04</v>
+        <v>1021.06</v>
       </c>
       <c r="I11" t="n">
-        <v>962.21</v>
+        <v>968.03</v>
       </c>
       <c r="J11" t="n">
-        <v>950.4</v>
+        <v>951.5700000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>849.74</v>
+        <v>850.11</v>
       </c>
       <c r="L11" t="n">
-        <v>19.45</v>
+        <v>20.75</v>
       </c>
       <c r="M11" t="n">
-        <v>29.14</v>
+        <v>27.47</v>
       </c>
       <c r="N11" t="n">
-        <v>30.5</v>
+        <v>29.9</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.36</v>
+        <v>-2.43</v>
       </c>
       <c r="P11" t="n">
-        <v>28.18</v>
+        <v>29.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>12.29</v>
+        <v>12.89</v>
       </c>
       <c r="R11" t="n">
-        <v>44.9</v>
+        <v>43</v>
       </c>
       <c r="S11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.76</v>
+        <v>-2.01</v>
       </c>
       <c r="U11" t="n">
         <v>51.7</v>
       </c>
       <c r="V11" t="n">
-        <v>3.69</v>
+        <v>3.94</v>
       </c>
       <c r="W11" t="n">
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>1013.4</v>
+        <v>978.17</v>
       </c>
       <c r="Y11" t="n">
-        <v>1018.94</v>
+        <v>983.74</v>
       </c>
       <c r="Z11" t="n">
-        <v>957.6</v>
+        <v>930.64</v>
       </c>
       <c r="AA11" t="n">
-        <v>984.23</v>
+        <v>953.62</v>
       </c>
       <c r="AB11" t="n">
-        <v>1015.07</v>
+        <v>1006.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1042.14</v>
+        <v>1021.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1057.77</v>
+        <v>1045.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>57.3</v>
+        <v>59.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH11" t="n">
         <v>0.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>31.8</v>
+        <v>31</v>
       </c>
       <c r="AJ11" t="n">
         <v>23.9</v>
@@ -2284,49 +2284,49 @@
         <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>1068.2</v>
+        <v>1039.61</v>
       </c>
       <c r="AN11" t="n">
-        <v>986.89</v>
+        <v>959.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹61,828.48 Cr., a P/E ratio of 31.85, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹60,087.77 Cr., a P/E ratio of 30.95, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.26 (Bullish Momentum Zone), while MACD Line (29.14) trades below Signal (30.50) with an expanding histogram (-1.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.45% above the 200-day DMA (₹849.74). Daily volatility envelope is bounded by ATR(14) of ₹28.18.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.93 (Bullish Momentum Zone), while MACD Line (27.47) trades below Signal (29.90) with an expanding histogram (-2.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.75% above the 200-day DMA (₹850.11). Daily volatility envelope is bounded by ATR(14) of ₹29.32.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,026.50) is positioned above the 30-day DMA (₹962.21), 50-day DMA (₹950.40), and 200-day DMA (₹849.74). The price distance from 200 DMA is +19.45%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹997.60) is positioned above the 30-day DMA (₹968.03), 50-day DMA (₹951.57), and 200-day DMA (₹850.11). The price distance from 200 DMA is +20.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[1026.5, 1029.58, 1032.66, 1035.74, 1038.82, 1041.9]</t>
+          <t>[997.6, 1000.59, 1003.59, 1006.58, 1009.57, 1012.56]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[1026.5, 1040.85, 1048.6, 1055.26, 1061.36, 1067.1]</t>
+          <t>[997.6, 1012.32, 1020.17, 1026.89, 1033.03, 1038.79]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[1026.5, 1021.13, 1020.7, 1021.1, 1021.91, 1022.99]</t>
+          <t>[997.6, 991.8, 991.15, 991.34, 991.98, 992.89]</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>957.6</v>
+        <v>930.64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>30963.05</v>
+        <v>30393.73</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2348,98 +2348,98 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>562.9</v>
+        <v>552.55</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>₹559.68 - ₹567.73</t>
+          <t>₹549.09 - ₹557.74</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>575.79</v>
+        <v>566.38</v>
       </c>
       <c r="I12" t="n">
-        <v>515.35</v>
+        <v>516.4400000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>523.51</v>
+        <v>523.9299999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>523.36</v>
+        <v>523.49</v>
       </c>
       <c r="L12" t="n">
-        <v>5.53</v>
+        <v>7.53</v>
       </c>
       <c r="M12" t="n">
-        <v>12.09</v>
+        <v>12.89</v>
       </c>
       <c r="N12" t="n">
-        <v>6.96</v>
+        <v>8.15</v>
       </c>
       <c r="O12" t="n">
-        <v>5.13</v>
+        <v>4.75</v>
       </c>
       <c r="P12" t="n">
-        <v>16.11</v>
+        <v>17.29</v>
       </c>
       <c r="Q12" t="n">
-        <v>12.29</v>
+        <v>12.89</v>
       </c>
       <c r="R12" t="n">
-        <v>44.3</v>
+        <v>40.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.04</v>
+        <v>-2.48</v>
       </c>
       <c r="U12" t="n">
         <v>45</v>
       </c>
       <c r="V12" t="n">
-        <v>5.71</v>
+        <v>5.03</v>
       </c>
       <c r="W12" t="n">
         <v>-0.77</v>
       </c>
       <c r="X12" t="n">
-        <v>548.76</v>
+        <v>541.22</v>
       </c>
       <c r="Y12" t="n">
-        <v>558.1900000000001</v>
+        <v>547.92</v>
       </c>
       <c r="Z12" t="n">
-        <v>558.1900000000001</v>
+        <v>547.92</v>
       </c>
       <c r="AA12" t="n">
-        <v>538.74</v>
+        <v>526.62</v>
       </c>
       <c r="AB12" t="n">
-        <v>560.42</v>
+        <v>555.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>574.84</v>
+        <v>562.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>586.77</v>
+        <v>571.85</v>
       </c>
       <c r="AE12" t="n">
-        <v>78</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Vol Spike 2.9x | Inst. Buying (CMF+) | Low VIX (12.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH12" t="n">
         <v>0.15</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AJ12" t="n">
         <v>14.5</v>
@@ -2451,43 +2451,43 @@
         <v>15</v>
       </c>
       <c r="AM12" t="n">
-        <v>577.64</v>
+        <v>565.78</v>
       </c>
       <c r="AN12" t="n">
-        <v>548.73</v>
+        <v>537.85</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,963.05 Cr., a P/E ratio of 5.40, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,393.73 Cr., a P/E ratio of 5.30, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 77.98 (Bullish Momentum Zone), while MACD Line (12.09) trades above Signal (6.96) with an expanding histogram (+5.13). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.53% above the 200-day DMA (₹523.36). Daily volatility envelope is bounded by ATR(14) of ₹16.11.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 80.94 (Bullish Momentum Zone), while MACD Line (12.89) trades above Signal (8.15) with an expanding histogram (+4.75). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.53% above the 200-day DMA (₹523.49). Daily volatility envelope is bounded by ATR(14) of ₹17.29.</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹562.90) is positioned above the 30-day DMA (₹515.35), 50-day DMA (₹523.51), and 200-day DMA (₹523.36). The price distance from 200 DMA is +5.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹552.55) is positioned above the 30-day DMA (₹516.44), 50-day DMA (₹523.93), and 200-day DMA (₹523.49). The price distance from 200 DMA is +7.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>[562.9, 564.59, 566.28, 567.97, 569.65, 571.34]</t>
+          <t>[552.55, 554.21, 555.87, 557.52, 559.18, 560.84]</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>[562.9, 571.03, 575.39, 579.13, 582.54, 585.75]</t>
+          <t>[552.55, 561.12, 565.65, 569.5, 573.01, 576.3]</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>[562.9, 559.76, 559.44, 559.6, 559.99, 560.54]</t>
+          <t>[552.55, 549.02, 548.53, 548.54, 548.81, 549.24]</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>558.1900000000001</v>
+        <v>547.92</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU12"/>
+  <dimension ref="A1:AU7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>88067.42999999999</v>
+        <v>78988.07000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5637</v>
+        <v>485.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹5604.57 - ₹5685.64</t>
+          <t>₹482.81 - ₹489.78</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5766.71</v>
+        <v>496.75</v>
       </c>
       <c r="I2" t="n">
-        <v>5579.23</v>
+        <v>474.22</v>
       </c>
       <c r="J2" t="n">
-        <v>5399.24</v>
+        <v>460.37</v>
       </c>
       <c r="K2" t="n">
-        <v>5400.46</v>
+        <v>454.35</v>
       </c>
       <c r="L2" t="n">
-        <v>2.14</v>
+        <v>7.8</v>
       </c>
       <c r="M2" t="n">
-        <v>29</v>
+        <v>9.94</v>
       </c>
       <c r="N2" t="n">
-        <v>69.16</v>
+        <v>9.75</v>
       </c>
       <c r="O2" t="n">
-        <v>-40.16</v>
+        <v>0.2</v>
       </c>
       <c r="P2" t="n">
-        <v>162.14</v>
+        <v>13.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.89</v>
+        <v>13.43</v>
       </c>
       <c r="R2" t="n">
-        <v>54.6</v>
+        <v>48.7</v>
       </c>
       <c r="S2" t="n">
         <v>0.19</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.52</v>
+        <v>-1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>58.3</v>
+        <v>60</v>
       </c>
       <c r="V2" t="n">
-        <v>6.14</v>
+        <v>3.71</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>5504.89</v>
+        <v>484.69</v>
       </c>
       <c r="Y2" t="n">
-        <v>5544.71</v>
+        <v>508.32</v>
       </c>
       <c r="Z2" t="n">
-        <v>5544.71</v>
+        <v>508.32</v>
       </c>
       <c r="AA2" t="n">
-        <v>5393.79</v>
+        <v>464.69</v>
       </c>
       <c r="AB2" t="n">
-        <v>5671</v>
+        <v>487.67</v>
       </c>
       <c r="AC2" t="n">
-        <v>5725</v>
+        <v>492.34</v>
       </c>
       <c r="AD2" t="n">
-        <v>5813</v>
+        <v>499.07</v>
       </c>
       <c r="AE2" t="n">
-        <v>43.6</v>
+        <v>59.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.03</v>
+        <v>-0.18</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.89) | LSTM Deep Net</t>
+          <t>Vol Spike 2.1x | Low VIX (13.43) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>46.2</v>
+        <v>9.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>29.1</v>
+        <v>57.7</v>
       </c>
       <c r="AK2" t="n">
-        <v>12.2</v>
+        <v>21.7</v>
       </c>
       <c r="AL2" t="n">
-        <v>25.2</v>
+        <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>5835.17</v>
+        <v>500.42</v>
       </c>
       <c r="AN2" t="n">
-        <v>5443.03</v>
+        <v>470.84</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PERSISTENT operates in the Technology sector. With an estimated Market Cap of ₹88,067.43 Cr., a P/E ratio of 46.24, and YoY Revenue Growth of +29.1%, the company demonstrates strong institutional backing, solid operating profit margins (12.24%), and healthy Return on Equity (25.20%).</t>
+          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹78,988.07 Cr., a P/E ratio of 9.45, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.61 (Consolidation Zone), while MACD Line (29.00) trades below Signal (69.16) with an expanding histogram (-40.16). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.14% above the 200-day DMA (₹5400.46). Daily volatility envelope is bounded by ATR(14) of ₹162.14.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.31 (Bullish Momentum Zone), while MACD Line (9.94) trades above Signal (9.75) with an expanding histogram (+0.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.80% above the 200-day DMA (₹454.35). Daily volatility envelope is bounded by ATR(14) of ₹13.94.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PERSISTENT. Current Market Price (₹5,637.00) is positioned above the 30-day DMA (₹5,579.23), 50-day DMA (₹5,399.24), and 200-day DMA (₹5,400.46). The price distance from 200 DMA is +2.14%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹485.60) is positioned above the 30-day DMA (₹474.22), 50-day DMA (₹460.37), and 200-day DMA (₹454.35). The price distance from 200 DMA is +7.80%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[5637.0, 5653.91, 5670.82, 5687.73, 5704.64, 5721.55]</t>
+          <t>[485.6, 489.49, 493.38, 497.27, 501.16, 505.05]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[5637.0, 5718.77, 5762.54, 5800.07, 5834.36, 5866.58]</t>
+          <t>[485.6, 495.07, 501.27, 506.93, 512.32, 517.52]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[5637.0, 5605.27, 5602.03, 5603.48, 5607.36, 5612.79]</t>
+          <t>[485.6, 485.31, 487.47, 490.03, 492.8, 495.7]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>5544.71</v>
+        <v>508.32</v>
       </c>
     </row>
     <row r="3">
@@ -828,163 +828,163 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79427.25</v>
+        <v>58844.15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>488.3</v>
+        <v>2119.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹485.51 - ₹492.48</t>
+          <t>₹2106.92 - ₹2137.87</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>499.45</v>
+        <v>2168.81</v>
       </c>
       <c r="I3" t="n">
-        <v>474.22</v>
+        <v>2105.99</v>
       </c>
       <c r="J3" t="n">
-        <v>460.37</v>
+        <v>1990.35</v>
       </c>
       <c r="K3" t="n">
-        <v>454.35</v>
+        <v>1950.67</v>
       </c>
       <c r="L3" t="n">
-        <v>7.8</v>
+        <v>10.4</v>
       </c>
       <c r="M3" t="n">
-        <v>9.94</v>
+        <v>53.98</v>
       </c>
       <c r="N3" t="n">
-        <v>9.75</v>
+        <v>67.61</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2</v>
+        <v>-13.62</v>
       </c>
       <c r="P3" t="n">
-        <v>13.94</v>
+        <v>61.89</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.89</v>
+        <v>13.43</v>
       </c>
       <c r="R3" t="n">
-        <v>49.3</v>
+        <v>47.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.57</v>
+        <v>-2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="V3" t="n">
-        <v>3.72</v>
+        <v>2.95</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>487.88</v>
+        <v>2071.16</v>
       </c>
       <c r="Y3" t="n">
-        <v>511.66</v>
+        <v>2124.99</v>
       </c>
       <c r="Z3" t="n">
-        <v>511.66</v>
+        <v>2124.99</v>
       </c>
       <c r="AA3" t="n">
-        <v>467.39</v>
+        <v>2026.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>489.57</v>
+        <v>2129</v>
       </c>
       <c r="AC3" t="n">
-        <v>493.14</v>
+        <v>2150.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>497.97</v>
+        <v>2181.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>59.3</v>
+        <v>51.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.18</v>
+        <v>0.06</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Vol Spike 2.1x | Low VIX (12.89) | LSTM Deep Net</t>
+          <t>Low VIX (13.43) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>9.5</v>
+        <v>47.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>57.7</v>
+        <v>8.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>21.7</v>
+        <v>5.2</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>504.34</v>
+        <v>2178.15</v>
       </c>
       <c r="AN3" t="n">
-        <v>473.28</v>
+        <v>2065.79</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹79,427.25 Cr., a P/E ratio of 9.50, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹58,844.15 Cr., a P/E ratio of 47.78, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.31 (Bullish Momentum Zone), while MACD Line (9.94) trades above Signal (9.75) with an expanding histogram (+0.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.80% above the 200-day DMA (₹454.35). Daily volatility envelope is bounded by ATR(14) of ₹13.94.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.71 (Consolidation Zone), while MACD Line (53.98) trades below Signal (67.61) with an expanding histogram (-13.62). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.40% above the 200-day DMA (₹1950.67). Daily volatility envelope is bounded by ATR(14) of ₹61.89.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹488.30) is positioned above the 30-day DMA (₹474.22), 50-day DMA (₹460.37), and 200-day DMA (₹454.35). The price distance from 200 DMA is +7.80%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,119.30) is positioned above the 30-day DMA (₹2,105.99), 50-day DMA (₹1,990.35), and 200-day DMA (₹1,950.67). The price distance from 200 DMA is +10.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[488.3, 492.71, 497.12, 501.54, 505.95, 510.36]</t>
+          <t>[2119.3, 2125.66, 2132.02, 2138.37, 2144.73, 2151.09]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[488.3, 498.29, 505.01, 511.19, 517.1, 522.83]</t>
+          <t>[2119.3, 2150.41, 2167.02, 2181.25, 2194.24, 2206.44]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[488.3, 488.53, 491.21, 494.29, 497.58, 501.01]</t>
+          <t>[2119.3, 2107.09, 2105.76, 2106.22, 2107.6, 2109.58]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>511.66</v>
+        <v>2124.99</v>
       </c>
     </row>
     <row r="4">
@@ -995,7 +995,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>133433.07</v>
+        <v>407654.94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,146 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>116.1</v>
+        <v>409.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹115.67 - ₹116.75</t>
+          <t>₹408.35 - ₹411.98</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>117.84</v>
+        <v>415.61</v>
       </c>
       <c r="I4" t="n">
-        <v>115.92</v>
+        <v>406.12</v>
       </c>
       <c r="J4" t="n">
-        <v>112.74</v>
+        <v>396.63</v>
       </c>
       <c r="K4" t="n">
-        <v>112.41</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>3.86</v>
+        <v>4.75</v>
       </c>
       <c r="M4" t="n">
-        <v>0.79</v>
+        <v>6.69</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>7.36</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.21</v>
+        <v>-0.67</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>7.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.89</v>
+        <v>13.43</v>
       </c>
       <c r="R4" t="n">
-        <v>48</v>
+        <v>44.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.11</v>
+        <v>-1.13</v>
       </c>
       <c r="U4" t="n">
-        <v>51.7</v>
+        <v>50</v>
       </c>
       <c r="V4" t="n">
-        <v>2.87</v>
+        <v>3.61</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>116.02</v>
+        <v>403.32</v>
       </c>
       <c r="Y4" t="n">
-        <v>118.12</v>
+        <v>418.59</v>
       </c>
       <c r="Z4" t="n">
-        <v>118.12</v>
+        <v>418.59</v>
       </c>
       <c r="AA4" t="n">
-        <v>112.84</v>
+        <v>398.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>116.25</v>
+        <v>413.37</v>
       </c>
       <c r="AC4" t="n">
-        <v>117.07</v>
+        <v>416.94</v>
       </c>
       <c r="AD4" t="n">
-        <v>118.05</v>
+        <v>424.07</v>
       </c>
       <c r="AE4" t="n">
-        <v>54.1</v>
+        <v>65.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.89) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (13.43) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>6</v>
+        <v>20.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>15.2</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
-        <v>38.1</v>
+        <v>28.5</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>119.38</v>
+        <v>419.64</v>
       </c>
       <c r="AN4" t="n">
-        <v>113.14</v>
+        <v>401.2</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹133,433.07 Cr., a P/E ratio of 6.04, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹407,654.94 Cr., a P/E ratio of 20.08, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.06 (Consolidation Zone), while MACD Line (0.79) trades below Signal (1.00) with an expanding histogram (-0.21). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.86% above the 200-day DMA (₹112.41). Daily volatility envelope is bounded by ATR(14) of ₹2.17.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.71 (Bullish Momentum Zone), while MACD Line (6.69) trades below Signal (7.36) with an expanding histogram (-0.67). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.75% above the 200-day DMA (₹400.00). Daily volatility envelope is bounded by ATR(14) of ₹7.26.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.10) is positioned above the 30-day DMA (₹115.92), 50-day DMA (₹112.74), and 200-day DMA (₹112.41). The price distance from 200 DMA is +3.86%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹409.80) is positioned above the 30-day DMA (₹406.12), 50-day DMA (₹396.63), and 200-day DMA (₹400.00). The price distance from 200 DMA is +4.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[116.1, 117.17, 118.23, 119.3, 120.37, 121.43]</t>
+          <t>[409.8, 411.03, 412.26, 413.49, 414.72, 415.95]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[116.1, 118.03, 119.46, 120.8, 122.1, 123.38]</t>
+          <t>[409.8, 413.94, 416.37, 418.52, 420.53, 422.44]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[116.1, 116.52, 117.31, 118.17, 119.07, 119.98]</t>
+          <t>[409.8, 408.85, 409.18, 409.71, 410.36, 411.07]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>118.12</v>
+        <v>418.59</v>
       </c>
     </row>
     <row r="5">
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>147064.95</v>
+        <v>25000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,146 +1179,146 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>422.35</v>
+        <v>3173.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹419.86 - ₹426.09</t>
+          <t>₹3153.19 - ₹3203.97</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>432.31</v>
+        <v>3254.75</v>
       </c>
       <c r="I5" t="n">
-        <v>421.2</v>
+        <v>3078.68</v>
       </c>
       <c r="J5" t="n">
-        <v>414.85</v>
+        <v>2949.59</v>
       </c>
       <c r="K5" t="n">
-        <v>338.03</v>
+        <v>2671.75</v>
       </c>
       <c r="L5" t="n">
-        <v>27.5</v>
+        <v>22.62</v>
       </c>
       <c r="M5" t="n">
-        <v>4.39</v>
+        <v>108.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4.61</v>
+        <v>119.79</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.23</v>
+        <v>-11.74</v>
       </c>
       <c r="P5" t="n">
-        <v>12.45</v>
+        <v>101.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.89</v>
+        <v>13.43</v>
       </c>
       <c r="R5" t="n">
-        <v>47.7</v>
+        <v>43.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.06</v>
+        <v>-2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>46.7</v>
+        <v>51.7</v>
       </c>
       <c r="V5" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>419.27</v>
+        <v>3153.81</v>
       </c>
       <c r="Y5" t="n">
-        <v>423.58</v>
+        <v>3170.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>423.58</v>
+        <v>2567.81</v>
       </c>
       <c r="AA5" t="n">
-        <v>403.67</v>
+        <v>3021.16</v>
       </c>
       <c r="AB5" t="n">
-        <v>425.23</v>
+        <v>3199.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>429.11</v>
+        <v>3241.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>435.88</v>
+        <v>3310.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>60.9</v>
+        <v>51</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.26</v>
+        <v>0.17</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (12.89) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (13.43) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>60.5</v>
+        <v>52.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>40.3</v>
+        <v>85.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>6.8</v>
+        <v>55.6</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>437.87</v>
+        <v>3308.2</v>
       </c>
       <c r="AN5" t="n">
-        <v>407.39</v>
+        <v>3057.3</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>BHEL operates in the Industrials sector. With an estimated Market Cap of ₹147,064.95 Cr., a P/E ratio of 60.51, and YoY Revenue Growth of +40.3%, the company demonstrates strong institutional backing, solid operating profit margins (6.76%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 52.36, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.88 (Bullish Momentum Zone), while MACD Line (4.39) trades below Signal (4.61) with an expanding histogram (-0.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +27.50% above the 200-day DMA (₹338.03). Daily volatility envelope is bounded by ATR(14) of ₹12.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.03 (Consolidation Zone), while MACD Line (108.05) trades below Signal (119.79) with an expanding histogram (-11.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +22.62% above the 200-day DMA (₹2671.75). Daily volatility envelope is bounded by ATR(14) of ₹101.56.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BHEL. Current Market Price (₹422.35) is positioned above the 30-day DMA (₹421.20), 50-day DMA (₹414.85), and 200-day DMA (₹338.03). The price distance from 200 DMA is +27.50%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,173.50) is positioned above the 30-day DMA (₹3,078.68), 50-day DMA (₹2,949.59), and 200-day DMA (₹2,671.75). The price distance from 200 DMA is +22.62%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[422.35, 423.62, 424.88, 426.15, 427.42, 428.69]</t>
+          <t>[3173.5, 3185.28, 3197.07, 3208.85, 3220.64, 3232.42]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[422.35, 428.6, 431.93, 434.78, 437.38, 439.82]</t>
+          <t>[3173.5, 3225.91, 3254.52, 3279.22, 3301.89, 3323.26]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[422.35, 419.88, 419.6, 419.68, 419.95, 420.33]</t>
+          <t>[3173.5, 3154.82, 3153.98, 3156.08, 3159.7, 3164.29]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>423.58</v>
+        <v>2567.81</v>
       </c>
     </row>
     <row r="6">
@@ -1329,16 +1329,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>58894.12</v>
+        <v>59660.69</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,45 +1346,45 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2121.1</v>
+        <v>990.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹2108.72 - ₹2139.67</t>
+          <t>₹984.94 - ₹999.6</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2170.61</v>
+        <v>1014.26</v>
       </c>
       <c r="I6" t="n">
-        <v>2105.99</v>
+        <v>968.03</v>
       </c>
       <c r="J6" t="n">
-        <v>1990.35</v>
+        <v>951.5700000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>1950.67</v>
+        <v>850.11</v>
       </c>
       <c r="L6" t="n">
-        <v>10.4</v>
+        <v>20.75</v>
       </c>
       <c r="M6" t="n">
-        <v>53.98</v>
+        <v>27.47</v>
       </c>
       <c r="N6" t="n">
-        <v>67.61</v>
+        <v>29.9</v>
       </c>
       <c r="O6" t="n">
-        <v>-13.62</v>
+        <v>-2.43</v>
       </c>
       <c r="P6" t="n">
-        <v>61.89</v>
+        <v>29.32</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.89</v>
+        <v>13.43</v>
       </c>
       <c r="R6" t="n">
-        <v>47.2</v>
+        <v>42.5</v>
       </c>
       <c r="S6" t="n">
         <v>0.18</v>
@@ -1393,99 +1393,99 @@
         <v>-2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>50</v>
+        <v>51.7</v>
       </c>
       <c r="V6" t="n">
-        <v>2.95</v>
+        <v>3.94</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2073.44</v>
+        <v>969.96</v>
       </c>
       <c r="Y6" t="n">
-        <v>2126.8</v>
+        <v>975.54</v>
       </c>
       <c r="Z6" t="n">
-        <v>2126.8</v>
+        <v>924.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2028.27</v>
+        <v>946.8200000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>2129.6</v>
+        <v>1001.97</v>
       </c>
       <c r="AC6" t="n">
-        <v>2151.5</v>
+        <v>1018.84</v>
       </c>
       <c r="AD6" t="n">
-        <v>2181.9</v>
+        <v>1046.87</v>
       </c>
       <c r="AE6" t="n">
-        <v>51.7</v>
+        <v>59.9</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.06</v>
+        <v>0.34</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Low VIX (12.89) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (13.43) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>47.8</v>
+        <v>30.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>8.5</v>
+        <v>23.9</v>
       </c>
       <c r="AK6" t="n">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>2180.15</v>
+        <v>1029.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>2061.81</v>
+        <v>953.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹58,894.12 Cr., a P/E ratio of 47.82, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹59,660.69 Cr., a P/E ratio of 30.74, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.71 (Consolidation Zone), while MACD Line (53.98) trades below Signal (67.61) with an expanding histogram (-13.62). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.40% above the 200-day DMA (₹1950.67). Daily volatility envelope is bounded by ATR(14) of ₹61.89.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.93 (Bullish Momentum Zone), while MACD Line (27.47) trades below Signal (29.90) with an expanding histogram (-2.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.75% above the 200-day DMA (₹850.11). Daily volatility envelope is bounded by ATR(14) of ₹29.32.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,121.10) is positioned above the 30-day DMA (₹2,105.99), 50-day DMA (₹1,990.35), and 200-day DMA (₹1,950.67). The price distance from 200 DMA is +10.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹990.80) is positioned above the 30-day DMA (₹968.03), 50-day DMA (₹951.57), and 200-day DMA (₹850.11). The price distance from 200 DMA is +20.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[2121.1, 2127.46, 2133.83, 2140.19, 2146.55, 2152.92]</t>
+          <t>[990.8, 993.77, 996.74, 999.72, 1002.69, 1005.66]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2121.1, 2152.22, 2168.83, 2183.07, 2196.06, 2208.27]</t>
+          <t>[990.8, 1005.5, 1013.33, 1020.03, 1026.15, 1031.89]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2121.1, 2108.9, 2107.57, 2108.03, 2109.42, 2111.4]</t>
+          <t>[990.8, 984.98, 984.3, 984.48, 985.1, 985.99]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>2126.8</v>
+        <v>924.3</v>
       </c>
     </row>
     <row r="7">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>82410.89</v>
+        <v>29813.41</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,981 +1513,146 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1783.4</v>
+        <v>542</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹1773.74 - ₹1797.9</t>
+          <t>₹538.54 - ₹547.19</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1822.06</v>
+        <v>555.83</v>
       </c>
       <c r="I7" t="n">
-        <v>1754.97</v>
+        <v>516.4400000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>1683.04</v>
+        <v>523.9299999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>1651.94</v>
+        <v>523.49</v>
       </c>
       <c r="L7" t="n">
-        <v>8.800000000000001</v>
+        <v>7.53</v>
       </c>
       <c r="M7" t="n">
-        <v>37.52</v>
+        <v>12.89</v>
       </c>
       <c r="N7" t="n">
-        <v>48.03</v>
+        <v>8.15</v>
       </c>
       <c r="O7" t="n">
-        <v>-10.51</v>
+        <v>4.75</v>
       </c>
       <c r="P7" t="n">
-        <v>48.32</v>
+        <v>17.29</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.89</v>
+        <v>13.43</v>
       </c>
       <c r="R7" t="n">
-        <v>45.2</v>
+        <v>40.7</v>
       </c>
       <c r="S7" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.96</v>
+        <v>-2.51</v>
       </c>
       <c r="U7" t="n">
-        <v>53.3</v>
+        <v>45</v>
       </c>
       <c r="V7" t="n">
-        <v>4.84</v>
+        <v>5.03</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>1781.19</v>
+        <v>526.5599999999999</v>
       </c>
       <c r="Y7" t="n">
-        <v>1807.27</v>
+        <v>537.47</v>
       </c>
       <c r="Z7" t="n">
-        <v>1807.27</v>
+        <v>537.47</v>
       </c>
       <c r="AA7" t="n">
-        <v>1710.92</v>
+        <v>516.0700000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>1788.87</v>
+        <v>548.58</v>
       </c>
       <c r="AC7" t="n">
-        <v>1798.84</v>
+        <v>558.66</v>
       </c>
       <c r="AD7" t="n">
-        <v>1814.27</v>
+        <v>575.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>50.3</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.89) | LSTM Deep Net</t>
+          <t>Vol Spike 2.9x | Inst. Buying (CMF+) | Low VIX (13.43) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>110.2</v>
+        <v>5.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>40.1</v>
+        <v>14.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>10.2</v>
+        <v>65.2</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>1838.48</v>
+        <v>556.21</v>
       </c>
       <c r="AN7" t="n">
-        <v>1725.05</v>
+        <v>527.97</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹82,410.89 Cr., a P/E ratio of 110.22, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹29,813.41 Cr., a P/E ratio of 5.20, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.33 (Consolidation Zone), while MACD Line (37.52) trades below Signal (48.03) with an expanding histogram (-10.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.80% above the 200-day DMA (₹1651.94). Daily volatility envelope is bounded by ATR(14) of ₹48.32.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 80.94 (Bullish Momentum Zone), while MACD Line (12.89) trades above Signal (8.15) with an expanding histogram (+4.75). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.53% above the 200-day DMA (₹523.49). Daily volatility envelope is bounded by ATR(14) of ₹17.29.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,783.40) is positioned above the 30-day DMA (₹1,754.97), 50-day DMA (₹1,683.04), and 200-day DMA (₹1,651.94). The price distance from 200 DMA is +8.80%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹542.00) is positioned above the 30-day DMA (₹516.44), 50-day DMA (₹523.93), and 200-day DMA (₹523.49). The price distance from 200 DMA is +7.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[1783.4, 1798.83, 1814.26, 1829.69, 1845.12, 1860.56]</t>
+          <t>[542.0, 543.63, 545.25, 546.88, 548.5, 550.13]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[1783.4, 1818.16, 1841.6, 1863.17, 1883.78, 1903.78]</t>
+          <t>[542.0, 550.54, 555.03, 558.86, 562.34, 565.59]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[1783.4, 1784.33, 1793.76, 1804.58, 1816.13, 1828.14]</t>
+          <t>[542.0, 538.44, 537.92, 537.89, 538.13, 538.53]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1807.27</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>142939.67</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1613.5</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>₹1605.36 - ₹1625.72</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1646.08</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1604.16</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1577.26</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1489.53</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="M8" t="n">
-        <v>-11.97</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-11.94</v>
-      </c>
-      <c r="P8" t="n">
-        <v>40.72</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="R8" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="U8" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1613.5</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1625.89</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1594.33</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1552.42</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1611.23</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1635.46</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1657.43</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>42.8</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>Low VIX (12.89) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>27.9</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1658.98</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1570.05</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>TECHM operates in the Technology sector. With an estimated Market Cap of ₹142,939.67 Cr., a P/E ratio of 27.92, and YoY Revenue Growth of +17.7%, the company demonstrates strong institutional backing, solid operating profit margins (8.68%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.85 (Consolidation Zone), while MACD Line (-11.97) trades below Signal (-0.03) with an expanding histogram (-11.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.46% above the 200-day DMA (₹1489.53). Daily volatility envelope is bounded by ATR(14) of ₹40.72.</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for TECHM. Current Market Price (₹1,613.50) is positioned above the 30-day DMA (₹1,604.16), 50-day DMA (₹1,577.26), and 200-day DMA (₹1,489.53). The price distance from 200 DMA is +3.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>[1613.5, 1633.84, 1654.17, 1674.51, 1694.84, 1715.18]</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>[1613.5, 1650.12, 1677.21, 1702.72, 1727.42, 1751.6]</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>[1613.5, 1621.62, 1636.89, 1653.35, 1670.41, 1687.86]</t>
-        </is>
-      </c>
-      <c r="AU8" t="n">
-        <v>1594.33</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>410887.94</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>413.05</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>₹411.6 - ₹415.23</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>418.86</v>
-      </c>
-      <c r="I9" t="n">
-        <v>406.12</v>
-      </c>
-      <c r="J9" t="n">
-        <v>396.63</v>
-      </c>
-      <c r="K9" t="n">
-        <v>400</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="M9" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="N9" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="P9" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="R9" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="U9" t="n">
-        <v>50</v>
-      </c>
-      <c r="V9" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X9" t="n">
-        <v>407.16</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>421.91</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>421.91</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>402.15</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>414.9</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>418.65</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>424.25</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>Strong RSI | Low VIX (12.89) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>421.69</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>403.48</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹410,887.94 Cr., a P/E ratio of 20.24, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.71 (Bullish Momentum Zone), while MACD Line (6.69) trades below Signal (7.36) with an expanding histogram (-0.67). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.75% above the 200-day DMA (₹400.00). Daily volatility envelope is bounded by ATR(14) of ₹7.26.</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹413.05) is positioned above the 30-day DMA (₹406.12), 50-day DMA (₹396.63), and 200-day DMA (₹400.00). The price distance from 200 DMA is +4.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>[413.05, 414.29, 415.53, 416.77, 418.01, 419.25]</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>[413.05, 417.19, 419.64, 421.8, 423.82, 425.74]</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>[413.05, 412.11, 412.45, 412.99, 413.65, 414.37]</t>
-        </is>
-      </c>
-      <c r="AU9" t="n">
-        <v>421.91</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>81495.41</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>3202</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>₹3181.69 - ₹3232.47</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>3283.25</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3078.68</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2949.59</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2671.75</v>
-      </c>
-      <c r="L10" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="M10" t="n">
-        <v>108.05</v>
-      </c>
-      <c r="N10" t="n">
-        <v>119.79</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-11.74</v>
-      </c>
-      <c r="P10" t="n">
-        <v>101.56</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="R10" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-2.17</v>
-      </c>
-      <c r="U10" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V10" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3186.9</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>3203.43</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2590.88</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3049.66</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>3208.67</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3260.94</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>3319.87</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>51</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.89) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>3332.62</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>3087.57</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹81,495.41 Cr., a P/E ratio of 52.83, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.03 (Consolidation Zone), while MACD Line (108.05) trades below Signal (119.79) with an expanding histogram (-11.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +22.62% above the 200-day DMA (₹2671.75). Daily volatility envelope is bounded by ATR(14) of ₹101.56.</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,202.00) is positioned above the 30-day DMA (₹3,078.68), 50-day DMA (₹2,949.59), and 200-day DMA (₹2,671.75). The price distance from 200 DMA is +22.62%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>[3202.0, 3218.63, 3235.26, 3251.89, 3268.52, 3285.15]</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>[3202.0, 3259.25, 3292.71, 3322.25, 3349.77, 3375.99]</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>[3202.0, 3188.16, 3192.17, 3199.12, 3207.58, 3217.02]</t>
-        </is>
-      </c>
-      <c r="AU10" t="n">
-        <v>2590.88</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>60087.77</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>997.6</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>₹991.74 - ₹1006.4</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1021.06</v>
-      </c>
-      <c r="I11" t="n">
-        <v>968.03</v>
-      </c>
-      <c r="J11" t="n">
-        <v>951.5700000000001</v>
-      </c>
-      <c r="K11" t="n">
-        <v>850.11</v>
-      </c>
-      <c r="L11" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="M11" t="n">
-        <v>27.47</v>
-      </c>
-      <c r="N11" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="P11" t="n">
-        <v>29.32</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="R11" t="n">
-        <v>43</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-2.01</v>
-      </c>
-      <c r="U11" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X11" t="n">
-        <v>978.17</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>983.74</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>930.64</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>953.62</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1006.1</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1021.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1045.4</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.89) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>31</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1039.61</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>959.1</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹60,087.77 Cr., a P/E ratio of 30.95, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.93 (Bullish Momentum Zone), while MACD Line (27.47) trades below Signal (29.90) with an expanding histogram (-2.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.75% above the 200-day DMA (₹850.11). Daily volatility envelope is bounded by ATR(14) of ₹29.32.</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹997.60) is positioned above the 30-day DMA (₹968.03), 50-day DMA (₹951.57), and 200-day DMA (₹850.11). The price distance from 200 DMA is +20.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>[997.6, 1000.59, 1003.59, 1006.58, 1009.57, 1012.56]</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>[997.6, 1012.32, 1020.17, 1026.89, 1033.03, 1038.79]</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>[997.6, 991.8, 991.15, 991.34, 991.98, 992.89]</t>
-        </is>
-      </c>
-      <c r="AU11" t="n">
-        <v>930.64</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>30393.73</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>552.55</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>₹549.09 - ₹557.74</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>566.38</v>
-      </c>
-      <c r="I12" t="n">
-        <v>516.4400000000001</v>
-      </c>
-      <c r="J12" t="n">
-        <v>523.9299999999999</v>
-      </c>
-      <c r="K12" t="n">
-        <v>523.49</v>
-      </c>
-      <c r="L12" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="M12" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="N12" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P12" t="n">
-        <v>17.29</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="R12" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-2.48</v>
-      </c>
-      <c r="U12" t="n">
-        <v>45</v>
-      </c>
-      <c r="V12" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X12" t="n">
-        <v>541.22</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>547.92</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>547.92</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>526.62</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>555.6</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>562.2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>571.85</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>Vol Spike 2.9x | Inst. Buying (CMF+) | Low VIX (12.89) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>565.78</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>537.85</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,393.73 Cr., a P/E ratio of 5.30, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 80.94 (Bullish Momentum Zone), while MACD Line (12.89) trades above Signal (8.15) with an expanding histogram (+4.75). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.53% above the 200-day DMA (₹523.49). Daily volatility envelope is bounded by ATR(14) of ₹17.29.</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹552.55) is positioned above the 30-day DMA (₹516.44), 50-day DMA (₹523.93), and 200-day DMA (₹523.49). The price distance from 200 DMA is +7.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>[552.55, 554.21, 555.87, 557.52, 559.18, 560.84]</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>[552.55, 561.12, 565.65, 569.5, 573.01, 576.3]</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>[552.55, 549.02, 548.53, 548.54, 548.81, 549.24]</t>
-        </is>
-      </c>
-      <c r="AU12" t="n">
-        <v>547.92</v>
+        <v>537.47</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU7"/>
+  <dimension ref="A1:AU4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,68 +682,68 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹482.81 - ₹489.78</t>
+          <t>₹483.0 - ₹489.51</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>496.75</v>
+        <v>496.01</v>
       </c>
       <c r="I2" t="n">
-        <v>474.22</v>
+        <v>475.51</v>
       </c>
       <c r="J2" t="n">
-        <v>460.37</v>
+        <v>461.67</v>
       </c>
       <c r="K2" t="n">
-        <v>454.35</v>
+        <v>454.75</v>
       </c>
       <c r="L2" t="n">
-        <v>7.8</v>
+        <v>7.71</v>
       </c>
       <c r="M2" t="n">
-        <v>9.94</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>9.75</v>
+        <v>9.65</v>
       </c>
       <c r="O2" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="P2" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="R2" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="S2" t="n">
         <v>0.2</v>
       </c>
-      <c r="P2" t="n">
-        <v>13.94</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="R2" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.19</v>
-      </c>
       <c r="T2" t="n">
-        <v>-1.67</v>
+        <v>-1.58</v>
       </c>
       <c r="U2" t="n">
         <v>60</v>
       </c>
       <c r="V2" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>484.69</v>
+        <v>481.82</v>
       </c>
       <c r="Y2" t="n">
-        <v>508.32</v>
+        <v>502.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>508.32</v>
+        <v>471.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>464.69</v>
+        <v>466.07</v>
       </c>
       <c r="AB2" t="n">
         <v>487.67</v>
@@ -755,14 +755,14 @@
         <v>499.07</v>
       </c>
       <c r="AE2" t="n">
-        <v>59.3</v>
+        <v>68</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Vol Spike 2.1x | Low VIX (13.43) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
@@ -781,43 +781,43 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>500.42</v>
+        <v>500.97</v>
       </c>
       <c r="AN2" t="n">
-        <v>470.84</v>
+        <v>470.7</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹78,988.07 Cr., a P/E ratio of 9.45, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
+          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹78,988.07 Cr., a P/E ratio of 9.53, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.31 (Bullish Momentum Zone), while MACD Line (9.94) trades above Signal (9.75) with an expanding histogram (+0.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.80% above the 200-day DMA (₹454.35). Daily volatility envelope is bounded by ATR(14) of ₹13.94.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 68.02 (Bullish Momentum Zone), while MACD Line (9.28) trades below Signal (9.65) with an expanding histogram (-0.37). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.71% above the 200-day DMA (₹454.75). Daily volatility envelope is bounded by ATR(14) of ₹13.02.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹485.60) is positioned above the 30-day DMA (₹474.22), 50-day DMA (₹460.37), and 200-day DMA (₹454.35). The price distance from 200 DMA is +7.80%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹485.60) is positioned above the 30-day DMA (₹475.51), 50-day DMA (₹461.67), and 200-day DMA (₹454.75). The price distance from 200 DMA is +7.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[485.6, 489.49, 493.38, 497.27, 501.16, 505.05]</t>
+          <t>[485.6, 487.06, 488.51, 489.97, 491.43, 492.88]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[485.6, 495.07, 501.27, 506.93, 512.32, 517.52]</t>
+          <t>[485.6, 492.26, 495.88, 498.99, 501.84, 504.53]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[485.6, 485.31, 487.47, 490.03, 492.8, 495.7]</t>
+          <t>[485.6, 483.15, 482.99, 483.21, 483.62, 484.15]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>508.32</v>
+        <v>471.65</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>58844.15</v>
+        <v>407654.94</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2119.3</v>
+        <v>409.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹2106.92 - ₹2137.87</t>
+          <t>₹408.4 - ₹411.9</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2168.81</v>
+        <v>415.39</v>
       </c>
       <c r="I3" t="n">
-        <v>2105.99</v>
+        <v>406.84</v>
       </c>
       <c r="J3" t="n">
-        <v>1990.35</v>
+        <v>397.4</v>
       </c>
       <c r="K3" t="n">
-        <v>1950.67</v>
+        <v>399.98</v>
       </c>
       <c r="L3" t="n">
-        <v>10.4</v>
+        <v>4.75</v>
       </c>
       <c r="M3" t="n">
-        <v>53.98</v>
+        <v>6.36</v>
       </c>
       <c r="N3" t="n">
-        <v>67.61</v>
+        <v>7.16</v>
       </c>
       <c r="O3" t="n">
-        <v>-13.62</v>
+        <v>-0.8</v>
       </c>
       <c r="P3" t="n">
-        <v>61.89</v>
+        <v>6.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.43</v>
+        <v>12.29</v>
       </c>
       <c r="R3" t="n">
-        <v>47.3</v>
+        <v>46</v>
       </c>
       <c r="S3" t="n">
-        <v>0.18</v>
+        <v>0.31</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.06</v>
+        <v>-1.1</v>
       </c>
       <c r="U3" t="n">
         <v>50</v>
       </c>
       <c r="V3" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>2071.16</v>
+        <v>408.49</v>
       </c>
       <c r="Y3" t="n">
-        <v>2124.99</v>
+        <v>416.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>2124.99</v>
+        <v>413.48</v>
       </c>
       <c r="AA3" t="n">
-        <v>2026.47</v>
+        <v>399.32</v>
       </c>
       <c r="AB3" t="n">
-        <v>2129</v>
+        <v>413.37</v>
       </c>
       <c r="AC3" t="n">
-        <v>2150.3</v>
+        <v>416.94</v>
       </c>
       <c r="AD3" t="n">
-        <v>2181.3</v>
+        <v>424.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>51.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Low VIX (13.43) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>47.8</v>
+        <v>20.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8.5</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
-        <v>5.2</v>
+        <v>28.5</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>2178.15</v>
+        <v>419.28</v>
       </c>
       <c r="AN3" t="n">
-        <v>2065.79</v>
+        <v>400.77</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹58,844.15 Cr., a P/E ratio of 47.78, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹407,654.94 Cr., a P/E ratio of 20.53, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.71 (Consolidation Zone), while MACD Line (53.98) trades below Signal (67.61) with an expanding histogram (-13.62). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.40% above the 200-day DMA (₹1950.67). Daily volatility envelope is bounded by ATR(14) of ₹61.89.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.62 (Bullish Momentum Zone), while MACD Line (6.36) trades below Signal (7.16) with an expanding histogram (-0.80). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.75% above the 200-day DMA (₹399.98). Daily volatility envelope is bounded by ATR(14) of ₹6.99.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,119.30) is positioned above the 30-day DMA (₹2,105.99), 50-day DMA (₹1,990.35), and 200-day DMA (₹1,950.67). The price distance from 200 DMA is +10.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹409.80) is positioned above the 30-day DMA (₹406.84), 50-day DMA (₹397.40), and 200-day DMA (₹399.98). The price distance from 200 DMA is +4.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[2119.3, 2125.66, 2132.02, 2138.37, 2144.73, 2151.09]</t>
+          <t>[409.8, 411.03, 412.26, 413.49, 414.72, 415.95]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[2119.3, 2150.41, 2167.02, 2181.25, 2194.24, 2206.44]</t>
+          <t>[409.8, 413.82, 416.21, 418.33, 420.31, 422.2]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[2119.3, 2107.09, 2105.76, 2106.22, 2107.6, 2109.58]</t>
+          <t>[409.8, 408.93, 409.29, 409.86, 410.53, 411.26]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2124.99</v>
+        <v>413.48</v>
       </c>
     </row>
     <row r="4">
@@ -995,7 +995,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>407654.94</v>
+        <v>80770.05</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,647 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>409.8</v>
+        <v>3173.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹408.35 - ₹411.98</t>
+          <t>₹3153.96 - ₹3202.81</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>415.61</v>
+        <v>3251.65</v>
       </c>
       <c r="I4" t="n">
-        <v>406.12</v>
+        <v>3100.02</v>
       </c>
       <c r="J4" t="n">
-        <v>396.63</v>
+        <v>2960.78</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>2677.73</v>
       </c>
       <c r="L4" t="n">
-        <v>4.75</v>
+        <v>22.34</v>
       </c>
       <c r="M4" t="n">
-        <v>6.69</v>
+        <v>100.25</v>
       </c>
       <c r="N4" t="n">
-        <v>7.36</v>
+        <v>115.88</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.67</v>
+        <v>-15.63</v>
       </c>
       <c r="P4" t="n">
-        <v>7.26</v>
+        <v>97.69</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.43</v>
+        <v>12.29</v>
       </c>
       <c r="R4" t="n">
-        <v>44.3</v>
+        <v>41.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.13</v>
+        <v>-2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>50</v>
+        <v>51.7</v>
       </c>
       <c r="V4" t="n">
-        <v>3.61</v>
+        <v>3.4</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>403.32</v>
+        <v>3153.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>418.59</v>
+        <v>4081.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>418.59</v>
+        <v>4081.14</v>
       </c>
       <c r="AA4" t="n">
-        <v>398.9</v>
+        <v>3026.97</v>
       </c>
       <c r="AB4" t="n">
-        <v>413.37</v>
+        <v>3199.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>416.94</v>
+        <v>3241.94</v>
       </c>
       <c r="AD4" t="n">
-        <v>424.07</v>
+        <v>3310.37</v>
       </c>
       <c r="AE4" t="n">
-        <v>65.7</v>
+        <v>50.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (13.43) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>20.1</v>
+        <v>54.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>85.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>28.5</v>
+        <v>55.6</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>419.64</v>
+        <v>3303.35</v>
       </c>
       <c r="AN4" t="n">
-        <v>401.2</v>
+        <v>3058.32</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹407,654.94 Cr., a P/E ratio of 20.08, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹80,770.05 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.71 (Bullish Momentum Zone), while MACD Line (6.69) trades below Signal (7.36) with an expanding histogram (-0.67). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.75% above the 200-day DMA (₹400.00). Daily volatility envelope is bounded by ATR(14) of ₹7.26.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.26 (Consolidation Zone), while MACD Line (100.25) trades below Signal (115.88) with an expanding histogram (-15.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +22.34% above the 200-day DMA (₹2677.73). Daily volatility envelope is bounded by ATR(14) of ₹97.69.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹409.80) is positioned above the 30-day DMA (₹406.12), 50-day DMA (₹396.63), and 200-day DMA (₹400.00). The price distance from 200 DMA is +4.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,173.50) is positioned above the 30-day DMA (₹3,100.02), 50-day DMA (₹2,960.78), and 200-day DMA (₹2,677.73). The price distance from 200 DMA is +22.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[409.8, 411.03, 412.26, 413.49, 414.72, 415.95]</t>
+          <t>[3173.5, 3183.02, 3192.54, 3202.06, 3211.58, 3221.1]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[409.8, 413.94, 416.37, 418.52, 420.53, 422.44]</t>
+          <t>[3173.5, 3222.09, 3247.8, 3269.74, 3289.73, 3308.48]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[409.8, 408.85, 409.18, 409.71, 410.36, 411.07]</t>
+          <t>[3173.5, 3153.71, 3151.1, 3151.3, 3152.97, 3155.57]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>418.59</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>3173.5</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>₹3153.19 - ₹3203.97</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3254.75</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3078.68</v>
-      </c>
-      <c r="J5" t="n">
-        <v>2949.59</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2671.75</v>
-      </c>
-      <c r="L5" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="M5" t="n">
-        <v>108.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>119.79</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-11.74</v>
-      </c>
-      <c r="P5" t="n">
-        <v>101.56</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="R5" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-2.2</v>
-      </c>
-      <c r="U5" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V5" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3153.81</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3170.33</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2567.81</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3021.16</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3199.17</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3241.94</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3310.37</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>51</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (13.43) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>85.3</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>3308.2</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>3057.3</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 52.36, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.03 (Consolidation Zone), while MACD Line (108.05) trades below Signal (119.79) with an expanding histogram (-11.74). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +22.62% above the 200-day DMA (₹2671.75). Daily volatility envelope is bounded by ATR(14) of ₹101.56.</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,173.50) is positioned above the 30-day DMA (₹3,078.68), 50-day DMA (₹2,949.59), and 200-day DMA (₹2,671.75). The price distance from 200 DMA is +22.62%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>[3173.5, 3185.28, 3197.07, 3208.85, 3220.64, 3232.42]</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>[3173.5, 3225.91, 3254.52, 3279.22, 3301.89, 3323.26]</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>[3173.5, 3154.82, 3153.98, 3156.08, 3159.7, 3164.29]</t>
-        </is>
-      </c>
-      <c r="AU5" t="n">
-        <v>2567.81</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>59660.69</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>990.8</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>₹984.94 - ₹999.6</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1014.26</v>
-      </c>
-      <c r="I6" t="n">
-        <v>968.03</v>
-      </c>
-      <c r="J6" t="n">
-        <v>951.5700000000001</v>
-      </c>
-      <c r="K6" t="n">
-        <v>850.11</v>
-      </c>
-      <c r="L6" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="M6" t="n">
-        <v>27.47</v>
-      </c>
-      <c r="N6" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="P6" t="n">
-        <v>29.32</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="R6" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="U6" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V6" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X6" t="n">
-        <v>969.96</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>975.54</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>924.3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>946.8200000000001</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1001.97</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1018.84</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1046.87</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (13.43) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1029.22</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>953.79</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹59,660.69 Cr., a P/E ratio of 30.74, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.93 (Bullish Momentum Zone), while MACD Line (27.47) trades below Signal (29.90) with an expanding histogram (-2.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.75% above the 200-day DMA (₹850.11). Daily volatility envelope is bounded by ATR(14) of ₹29.32.</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹990.80) is positioned above the 30-day DMA (₹968.03), 50-day DMA (₹951.57), and 200-day DMA (₹850.11). The price distance from 200 DMA is +20.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>[990.8, 993.77, 996.74, 999.72, 1002.69, 1005.66]</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>[990.8, 1005.5, 1013.33, 1020.03, 1026.15, 1031.89]</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>[990.8, 984.98, 984.3, 984.48, 985.1, 985.99]</t>
-        </is>
-      </c>
-      <c r="AU6" t="n">
-        <v>924.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>29813.41</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>542</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>₹538.54 - ₹547.19</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>555.83</v>
-      </c>
-      <c r="I7" t="n">
-        <v>516.4400000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>523.9299999999999</v>
-      </c>
-      <c r="K7" t="n">
-        <v>523.49</v>
-      </c>
-      <c r="L7" t="n">
-        <v>7.53</v>
-      </c>
-      <c r="M7" t="n">
-        <v>12.89</v>
-      </c>
-      <c r="N7" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="O7" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="P7" t="n">
-        <v>17.29</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="R7" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-2.51</v>
-      </c>
-      <c r="U7" t="n">
-        <v>45</v>
-      </c>
-      <c r="V7" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X7" t="n">
-        <v>526.5599999999999</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>537.47</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>537.47</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>516.0700000000001</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>548.58</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>558.66</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>575.33</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>80.90000000000001</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>Vol Spike 2.9x | Inst. Buying (CMF+) | Low VIX (13.43) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>556.21</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>527.97</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹29,813.41 Cr., a P/E ratio of 5.20, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 80.94 (Bullish Momentum Zone), while MACD Line (12.89) trades above Signal (8.15) with an expanding histogram (+4.75). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.53% above the 200-day DMA (₹523.49). Daily volatility envelope is bounded by ATR(14) of ₹17.29.</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹542.00) is positioned above the 30-day DMA (₹516.44), 50-day DMA (₹523.93), and 200-day DMA (₹523.49). The price distance from 200 DMA is +7.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>[542.0, 543.63, 545.25, 546.88, 548.5, 550.13]</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>[542.0, 550.54, 555.03, 558.86, 562.34, 565.59]</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>[542.0, 538.44, 537.92, 537.89, 538.13, 538.53]</t>
-        </is>
-      </c>
-      <c r="AU7" t="n">
-        <v>537.47</v>
+        <v>4081.14</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU4"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,21 +656,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>78988.07000000001</v>
+        <v>410738.73</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,157 +678,157 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>485.6</v>
+        <v>412.9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹483.0 - ₹489.51</t>
+          <t>₹411.58 - ₹414.87</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>496.01</v>
+        <v>418.16</v>
       </c>
       <c r="I2" t="n">
-        <v>475.51</v>
+        <v>407.23</v>
       </c>
       <c r="J2" t="n">
-        <v>461.67</v>
+        <v>397.97</v>
       </c>
       <c r="K2" t="n">
-        <v>454.75</v>
+        <v>399.91</v>
       </c>
       <c r="L2" t="n">
-        <v>7.71</v>
+        <v>2.47</v>
       </c>
       <c r="M2" t="n">
-        <v>9.279999999999999</v>
+        <v>5.29</v>
       </c>
       <c r="N2" t="n">
-        <v>9.65</v>
+        <v>6.79</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.37</v>
+        <v>-1.5</v>
       </c>
       <c r="P2" t="n">
-        <v>13.02</v>
+        <v>6.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.29</v>
+        <v>13.28</v>
       </c>
       <c r="R2" t="n">
-        <v>47.7</v>
+        <v>52.7</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.58</v>
+        <v>-0.79</v>
       </c>
       <c r="U2" t="n">
-        <v>60</v>
+        <v>50.8</v>
       </c>
       <c r="V2" t="n">
-        <v>3.73</v>
+        <v>3.62</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>481.82</v>
+        <v>412.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>502.11</v>
+        <v>432.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>471.65</v>
+        <v>416.61</v>
       </c>
       <c r="AA2" t="n">
-        <v>466.07</v>
+        <v>403.04</v>
       </c>
       <c r="AB2" t="n">
-        <v>487.67</v>
+        <v>412.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>492.34</v>
+        <v>414.95</v>
       </c>
       <c r="AD2" t="n">
-        <v>499.07</v>
+        <v>417</v>
       </c>
       <c r="AE2" t="n">
-        <v>68</v>
+        <v>43.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.19</v>
+        <v>0.03</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Low VIX (13.28) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.5</v>
+        <v>20.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>57.7</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>21.7</v>
+        <v>28.5</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>500.97</v>
+        <v>421.63</v>
       </c>
       <c r="AN2" t="n">
-        <v>470.7</v>
+        <v>404.29</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹78,988.07 Cr., a P/E ratio of 9.53, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹410,738.73 Cr., a P/E ratio of 20.69, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 68.02 (Bullish Momentum Zone), while MACD Line (9.28) trades below Signal (9.65) with an expanding histogram (-0.37). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.71% above the 200-day DMA (₹454.75). Daily volatility envelope is bounded by ATR(14) of ₹13.02.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.07 (Consolidation Zone), while MACD Line (5.29) trades below Signal (6.79) with an expanding histogram (-1.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.47% above the 200-day DMA (₹399.91). Daily volatility envelope is bounded by ATR(14) of ₹6.58.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹485.60) is positioned above the 30-day DMA (₹475.51), 50-day DMA (₹461.67), and 200-day DMA (₹454.75). The price distance from 200 DMA is +7.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹412.90) is positioned above the 30-day DMA (₹407.23), 50-day DMA (₹397.97), and 200-day DMA (₹399.91). The price distance from 200 DMA is +2.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[485.6, 487.06, 488.51, 489.97, 491.43, 492.88]</t>
+          <t>[412.9, 414.14, 415.38, 416.62, 417.85, 419.09]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[485.6, 492.26, 495.88, 498.99, 501.84, 504.53]</t>
+          <t>[412.9, 416.77, 419.1, 421.17, 423.11, 424.97]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[485.6, 483.15, 482.99, 483.21, 483.62, 484.15]</t>
+          <t>[412.9, 412.17, 412.59, 413.2, 413.91, 414.68]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>471.65</v>
+        <v>416.61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -837,321 +837,655 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>407654.94</v>
+        <v>134409.96</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>409.8</v>
+        <v>116.95</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹408.4 - ₹411.9</t>
+          <t>₹116.54 - ₹117.57</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>415.39</v>
+        <v>118.59</v>
       </c>
       <c r="I3" t="n">
-        <v>406.84</v>
+        <v>116.06</v>
       </c>
       <c r="J3" t="n">
-        <v>397.4</v>
+        <v>113.21</v>
       </c>
       <c r="K3" t="n">
-        <v>399.98</v>
+        <v>112.35</v>
       </c>
       <c r="L3" t="n">
-        <v>4.75</v>
+        <v>2.09</v>
       </c>
       <c r="M3" t="n">
-        <v>6.36</v>
+        <v>0.6</v>
       </c>
       <c r="N3" t="n">
-        <v>7.16</v>
+        <v>0.89</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8</v>
+        <v>-0.29</v>
       </c>
       <c r="P3" t="n">
-        <v>6.99</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.29</v>
+        <v>13.28</v>
       </c>
       <c r="R3" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="S3" t="n">
-        <v>0.31</v>
+        <v>0.4</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1</v>
+        <v>-0.76</v>
       </c>
       <c r="U3" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="V3" t="n">
-        <v>3.65</v>
+        <v>2.56</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>408.49</v>
+        <v>116.95</v>
       </c>
       <c r="Y3" t="n">
-        <v>416.8</v>
+        <v>122.88</v>
       </c>
       <c r="Z3" t="n">
-        <v>413.48</v>
+        <v>122.14</v>
       </c>
       <c r="AA3" t="n">
-        <v>399.32</v>
+        <v>113.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>413.37</v>
+        <v>116.29</v>
       </c>
       <c r="AC3" t="n">
-        <v>416.94</v>
+        <v>117.95</v>
       </c>
       <c r="AD3" t="n">
-        <v>424.07</v>
+        <v>118.95</v>
       </c>
       <c r="AE3" t="n">
-        <v>65.59999999999999</v>
+        <v>41.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (13.28) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>20.5</v>
+        <v>6.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>21</v>
+        <v>15.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>28.5</v>
+        <v>38.1</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>419.28</v>
+        <v>120.01</v>
       </c>
       <c r="AN3" t="n">
-        <v>400.77</v>
+        <v>113.82</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹407,654.94 Cr., a P/E ratio of 20.53, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,409.96 Cr., a P/E ratio of 6.19, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.62 (Bullish Momentum Zone), while MACD Line (6.36) trades below Signal (7.16) with an expanding histogram (-0.80). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.75% above the 200-day DMA (₹399.98). Daily volatility envelope is bounded by ATR(14) of ₹6.99.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 41.79 (Consolidation Zone), while MACD Line (0.60) trades below Signal (0.89) with an expanding histogram (-0.29). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.09% above the 200-day DMA (₹112.35). Daily volatility envelope is bounded by ATR(14) of ₹2.05.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹409.80) is positioned above the 30-day DMA (₹406.84), 50-day DMA (₹397.40), and 200-day DMA (₹399.98). The price distance from 200 DMA is +4.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.95) is positioned above the 30-day DMA (₹116.06), 50-day DMA (₹113.21), and 200-day DMA (₹112.35). The price distance from 200 DMA is +2.09%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[409.8, 411.03, 412.26, 413.49, 414.72, 415.95]</t>
+          <t>[116.95, 118.17, 119.39, 120.61, 121.83, 123.05]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[409.8, 413.82, 416.21, 418.33, 420.31, 422.2]</t>
+          <t>[116.95, 118.99, 120.55, 122.03, 123.47, 124.88]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[409.8, 408.93, 409.29, 409.86, 410.53, 411.26]</t>
+          <t>[116.95, 117.55, 118.52, 119.54, 120.59, 121.67]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>413.48</v>
+        <v>122.14</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>80770.05</v>
+        <v>78581.42</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3173.5</v>
+        <v>483.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹3153.96 - ₹3202.81</t>
+          <t>₹480.52 - ₹486.97</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3251.65</v>
+        <v>493.43</v>
       </c>
       <c r="I4" t="n">
-        <v>3100.02</v>
+        <v>476.73</v>
       </c>
       <c r="J4" t="n">
-        <v>2960.78</v>
+        <v>462.94</v>
       </c>
       <c r="K4" t="n">
-        <v>2677.73</v>
+        <v>455.15</v>
       </c>
       <c r="L4" t="n">
-        <v>22.34</v>
+        <v>6.69</v>
       </c>
       <c r="M4" t="n">
-        <v>100.25</v>
+        <v>8.32</v>
       </c>
       <c r="N4" t="n">
-        <v>115.88</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-15.63</v>
+        <v>-1.07</v>
       </c>
       <c r="P4" t="n">
-        <v>97.69</v>
+        <v>12.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.29</v>
+        <v>13.28</v>
       </c>
       <c r="R4" t="n">
-        <v>41.6</v>
+        <v>48.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.2</v>
+        <v>-1.53</v>
       </c>
       <c r="U4" t="n">
-        <v>51.7</v>
+        <v>59</v>
       </c>
       <c r="V4" t="n">
-        <v>3.4</v>
+        <v>3.73</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>3153.5</v>
+        <v>482.27</v>
       </c>
       <c r="Y4" t="n">
-        <v>4081.14</v>
+        <v>502.47</v>
       </c>
       <c r="Z4" t="n">
-        <v>4081.14</v>
+        <v>469.22</v>
       </c>
       <c r="AA4" t="n">
-        <v>3026.97</v>
+        <v>463.73</v>
       </c>
       <c r="AB4" t="n">
-        <v>3199.17</v>
+        <v>484.22</v>
       </c>
       <c r="AC4" t="n">
-        <v>3241.94</v>
+        <v>487.04</v>
       </c>
       <c r="AD4" t="n">
-        <v>3310.37</v>
+        <v>490.97</v>
       </c>
       <c r="AE4" t="n">
-        <v>50.3</v>
+        <v>63</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (13.28) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>54.1</v>
+        <v>9.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85.3</v>
+        <v>57.7</v>
       </c>
       <c r="AK4" t="n">
-        <v>55.6</v>
+        <v>21.7</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>3303.35</v>
+        <v>497.13</v>
       </c>
       <c r="AN4" t="n">
-        <v>3058.32</v>
+        <v>468.41</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹80,770.05 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹78,581.42 Cr., a P/E ratio of 9.48, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.26 (Consolidation Zone), while MACD Line (100.25) trades below Signal (115.88) with an expanding histogram (-15.63). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +22.34% above the 200-day DMA (₹2677.73). Daily volatility envelope is bounded by ATR(14) of ₹97.69.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.98 (Bullish Momentum Zone), while MACD Line (8.32) trades below Signal (9.39) with an expanding histogram (-1.07). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.69% above the 200-day DMA (₹455.15). Daily volatility envelope is bounded by ATR(14) of ₹12.91.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,173.50) is positioned above the 30-day DMA (₹3,100.02), 50-day DMA (₹2,960.78), and 200-day DMA (₹2,677.73). The price distance from 200 DMA is +22.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹483.10) is positioned above the 30-day DMA (₹476.73), 50-day DMA (₹462.94), and 200-day DMA (₹455.15). The price distance from 200 DMA is +6.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[3173.5, 3183.02, 3192.54, 3202.06, 3211.58, 3221.1]</t>
+          <t>[483.1, 484.55, 486.0, 487.45, 488.9, 490.35]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[3173.5, 3222.09, 3247.8, 3269.74, 3289.73, 3308.48]</t>
+          <t>[483.1, 489.71, 493.3, 496.39, 499.23, 501.9]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[3173.5, 3153.71, 3151.1, 3151.3, 3152.97, 3155.57]</t>
+          <t>[483.1, 480.68, 480.52, 480.74, 481.15, 481.68]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>4081.14</v>
+        <v>469.22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>59124.78</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>981.9</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>₹976.04 - ₹990.7</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1005.36</v>
+      </c>
+      <c r="I5" t="n">
+        <v>968.03</v>
+      </c>
+      <c r="J5" t="n">
+        <v>951.5700000000001</v>
+      </c>
+      <c r="K5" t="n">
+        <v>850.11</v>
+      </c>
+      <c r="L5" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="M5" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="N5" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-2.43</v>
+      </c>
+      <c r="P5" t="n">
+        <v>29.32</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="R5" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-2.06</v>
+      </c>
+      <c r="U5" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X5" t="n">
+        <v>970.23</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1099.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1099.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>937.92</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>978.53</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>993.26</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1004.63</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Low VIX (13.28) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1020.84</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>944.36</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹59,124.78 Cr., a P/E ratio of 30.47, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.93 (Bullish Momentum Zone), while MACD Line (27.47) trades below Signal (29.90) with an expanding histogram (-2.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.75% above the 200-day DMA (₹850.11). Daily volatility envelope is bounded by ATR(14) of ₹29.32.</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹981.90) is positioned above the 30-day DMA (₹968.03), 50-day DMA (₹951.57), and 200-day DMA (₹850.11). The price distance from 200 DMA is +20.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>[981.9, 984.85, 987.79, 990.74, 993.68, 996.63]</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>[981.9, 996.57, 1004.38, 1011.05, 1017.14, 1022.85]</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>[981.9, 976.05, 975.35, 975.5, 976.09, 976.96]</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>1099.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>29785.91</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>541.5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>₹538.04 - ₹546.69</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>555.33</v>
+      </c>
+      <c r="I6" t="n">
+        <v>516.4400000000001</v>
+      </c>
+      <c r="J6" t="n">
+        <v>523.9299999999999</v>
+      </c>
+      <c r="K6" t="n">
+        <v>523.49</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="N6" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="P6" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>13.28</v>
+      </c>
+      <c r="R6" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="U6" t="n">
+        <v>45</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X6" t="n">
+        <v>532.4</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>571.65</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>571.65</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>515.5700000000001</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>540.35</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>551.1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>560.7</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Vol Spike 2.9x | Inst. Buying (CMF+) | Low VIX (13.28) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>554.91</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>528.27</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹29,785.91 Cr., a P/E ratio of 5.19, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 80.94 (Bullish Momentum Zone), while MACD Line (12.89) trades above Signal (8.15) with an expanding histogram (+4.75). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.53% above the 200-day DMA (₹523.49). Daily volatility envelope is bounded by ATR(14) of ₹17.29.</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹541.50) is positioned above the 30-day DMA (₹516.44), 50-day DMA (₹523.93), and 200-day DMA (₹523.49). The price distance from 200 DMA is +7.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>[541.5, 543.12, 544.75, 546.37, 548.0, 549.62]</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>[541.5, 550.04, 554.53, 558.35, 561.83, 565.09]</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>[541.5, 537.94, 537.41, 537.39, 537.62, 538.02]</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>571.65</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU6"/>
+  <dimension ref="A1:AU8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>410738.73</v>
+        <v>79313.39999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>412.9</v>
+        <v>487.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹411.58 - ₹414.87</t>
+          <t>₹485.02 - ₹491.47</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>418.16</v>
+        <v>497.93</v>
       </c>
       <c r="I2" t="n">
-        <v>407.23</v>
+        <v>476.73</v>
       </c>
       <c r="J2" t="n">
-        <v>397.97</v>
+        <v>462.94</v>
       </c>
       <c r="K2" t="n">
-        <v>399.91</v>
+        <v>455.15</v>
       </c>
       <c r="L2" t="n">
-        <v>2.47</v>
+        <v>6.69</v>
       </c>
       <c r="M2" t="n">
-        <v>5.29</v>
+        <v>8.32</v>
       </c>
       <c r="N2" t="n">
-        <v>6.79</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.5</v>
+        <v>-1.07</v>
       </c>
       <c r="P2" t="n">
-        <v>6.58</v>
+        <v>12.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.28</v>
+        <v>13.17</v>
       </c>
       <c r="R2" t="n">
-        <v>52.7</v>
+        <v>53.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.33</v>
+        <v>0.2</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.79</v>
+        <v>-1.28</v>
       </c>
       <c r="U2" t="n">
-        <v>50.8</v>
+        <v>60.7</v>
       </c>
       <c r="V2" t="n">
-        <v>3.62</v>
+        <v>3.74</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>412.9</v>
+        <v>487.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>432.22</v>
+        <v>507.49</v>
       </c>
       <c r="Z2" t="n">
-        <v>416.61</v>
+        <v>473.59</v>
       </c>
       <c r="AA2" t="n">
-        <v>403.04</v>
+        <v>468.23</v>
       </c>
       <c r="AB2" t="n">
-        <v>412.15</v>
+        <v>486.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>414.95</v>
+        <v>490.94</v>
       </c>
       <c r="AD2" t="n">
-        <v>417</v>
+        <v>494.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>43.1</v>
+        <v>63</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.03</v>
+        <v>-0.16</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Low VIX (13.28) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (13.17) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>20.7</v>
+        <v>9.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>57.7</v>
       </c>
       <c r="AK2" t="n">
-        <v>28.5</v>
+        <v>21.7</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>421.63</v>
+        <v>502.32</v>
       </c>
       <c r="AN2" t="n">
-        <v>404.29</v>
+        <v>471.85</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹410,738.73 Cr., a P/E ratio of 20.69, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹79,313.40 Cr., a P/E ratio of 9.49, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.07 (Consolidation Zone), while MACD Line (5.29) trades below Signal (6.79) with an expanding histogram (-1.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.47% above the 200-day DMA (₹399.91). Daily volatility envelope is bounded by ATR(14) of ₹6.58.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.98 (Bullish Momentum Zone), while MACD Line (8.32) trades below Signal (9.39) with an expanding histogram (-1.07). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.69% above the 200-day DMA (₹455.15). Daily volatility envelope is bounded by ATR(14) of ₹12.91.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹412.90) is positioned above the 30-day DMA (₹407.23), 50-day DMA (₹397.97), and 200-day DMA (₹399.91). The price distance from 200 DMA is +2.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹487.60) is positioned above the 30-day DMA (₹476.73), 50-day DMA (₹462.94), and 200-day DMA (₹455.15). The price distance from 200 DMA is +6.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[412.9, 414.14, 415.38, 416.62, 417.85, 419.09]</t>
+          <t>[487.6, 489.06, 490.53, 491.99, 493.45, 494.91]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[412.9, 416.77, 419.1, 421.17, 423.11, 424.97]</t>
+          <t>[487.6, 494.23, 497.83, 500.93, 503.78, 506.46]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[412.9, 412.17, 412.59, 413.2, 413.91, 414.68]</t>
+          <t>[487.6, 485.19, 485.05, 485.28, 485.7, 486.25]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>416.61</v>
+        <v>473.59</v>
       </c>
     </row>
     <row r="3">
@@ -828,7 +828,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>134409.96</v>
+        <v>412827.73</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>116.95</v>
+        <v>415</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹116.54 - ₹117.57</t>
+          <t>₹413.68 - ₹416.97</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>118.59</v>
+        <v>420.26</v>
       </c>
       <c r="I3" t="n">
-        <v>116.06</v>
+        <v>407.23</v>
       </c>
       <c r="J3" t="n">
-        <v>113.21</v>
+        <v>397.97</v>
       </c>
       <c r="K3" t="n">
-        <v>112.35</v>
+        <v>399.91</v>
       </c>
       <c r="L3" t="n">
-        <v>2.09</v>
+        <v>2.47</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6</v>
+        <v>5.29</v>
       </c>
       <c r="N3" t="n">
-        <v>0.89</v>
+        <v>6.79</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.29</v>
+        <v>-1.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>6.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.28</v>
+        <v>13.17</v>
       </c>
       <c r="R3" t="n">
-        <v>51</v>
+        <v>52.7</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.76</v>
+        <v>-0.78</v>
       </c>
       <c r="U3" t="n">
-        <v>52.5</v>
+        <v>50.8</v>
       </c>
       <c r="V3" t="n">
-        <v>2.56</v>
+        <v>3.62</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>116.95</v>
+        <v>415</v>
       </c>
       <c r="Y3" t="n">
-        <v>122.88</v>
+        <v>434.81</v>
       </c>
       <c r="Z3" t="n">
-        <v>122.14</v>
+        <v>418.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>113.87</v>
+        <v>405.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>116.29</v>
+        <v>413.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>117.95</v>
+        <v>418.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>118.95</v>
+        <v>421.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>41.8</v>
+        <v>43.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.11</v>
+        <v>0.03</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (13.28) | LSTM Deep Net</t>
+          <t>Low VIX (13.17) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.2</v>
+        <v>20.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15.2</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
-        <v>38.1</v>
+        <v>28.5</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>120.01</v>
+        <v>424.58</v>
       </c>
       <c r="AN3" t="n">
-        <v>113.82</v>
+        <v>405.66</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,409.96 Cr., a P/E ratio of 6.19, and YoY Revenue Growth of +15.2%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹412,827.73 Cr., a P/E ratio of 20.33, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 41.79 (Consolidation Zone), while MACD Line (0.60) trades below Signal (0.89) with an expanding histogram (-0.29). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.09% above the 200-day DMA (₹112.35). Daily volatility envelope is bounded by ATR(14) of ₹2.05.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.07 (Consolidation Zone), while MACD Line (5.29) trades below Signal (6.79) with an expanding histogram (-1.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.47% above the 200-day DMA (₹399.91). Daily volatility envelope is bounded by ATR(14) of ₹6.58.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.95) is positioned above the 30-day DMA (₹116.06), 50-day DMA (₹113.21), and 200-day DMA (₹112.35). The price distance from 200 DMA is +2.09%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹415.00) is positioned above the 30-day DMA (₹407.23), 50-day DMA (₹397.97), and 200-day DMA (₹399.91). The price distance from 200 DMA is +2.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[116.95, 118.17, 119.39, 120.61, 121.83, 123.05]</t>
+          <t>[415.0, 416.44, 417.88, 419.32, 420.76, 422.2]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[116.95, 118.99, 120.55, 122.03, 123.47, 124.88]</t>
+          <t>[415.0, 419.07, 421.6, 423.88, 426.02, 428.08]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[116.95, 117.55, 118.52, 119.54, 120.59, 121.67]</t>
+          <t>[415.0, 414.47, 415.09, 415.9, 416.82, 417.79]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>122.14</v>
+        <v>418.73</v>
       </c>
     </row>
     <row r="4">
@@ -995,16 +995,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>78581.42</v>
+        <v>84430.25999999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,146 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>483.1</v>
+        <v>1827.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹480.52 - ₹486.97</t>
+          <t>₹1817.01 - ₹1842.24</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>493.43</v>
+        <v>1867.47</v>
       </c>
       <c r="I4" t="n">
-        <v>476.73</v>
+        <v>1759.45</v>
       </c>
       <c r="J4" t="n">
-        <v>462.94</v>
+        <v>1685.94</v>
       </c>
       <c r="K4" t="n">
-        <v>455.15</v>
+        <v>1651.79</v>
       </c>
       <c r="L4" t="n">
-        <v>6.69</v>
+        <v>5.1</v>
       </c>
       <c r="M4" t="n">
-        <v>8.32</v>
+        <v>28.67</v>
       </c>
       <c r="N4" t="n">
-        <v>9.390000000000001</v>
+        <v>44.16</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.07</v>
+        <v>-15.48</v>
       </c>
       <c r="P4" t="n">
-        <v>12.91</v>
+        <v>50.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.28</v>
+        <v>13.17</v>
       </c>
       <c r="R4" t="n">
-        <v>48.6</v>
+        <v>51.7</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.53</v>
+        <v>-0.8</v>
       </c>
       <c r="U4" t="n">
-        <v>59</v>
+        <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>3.73</v>
+        <v>4.57</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>482.27</v>
+        <v>1827.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>502.47</v>
+        <v>1947.92</v>
       </c>
       <c r="Z4" t="n">
-        <v>469.22</v>
+        <v>1932.24</v>
       </c>
       <c r="AA4" t="n">
-        <v>463.73</v>
+        <v>1751.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>484.22</v>
+        <v>1794.73</v>
       </c>
       <c r="AC4" t="n">
-        <v>487.04</v>
+        <v>1879.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>490.97</v>
+        <v>1931.63</v>
       </c>
       <c r="AE4" t="n">
-        <v>63</v>
+        <v>43.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.16</v>
+        <v>0.14</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (13.28) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (13.17) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>9.5</v>
+        <v>113.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>57.7</v>
+        <v>40.1</v>
       </c>
       <c r="AK4" t="n">
-        <v>21.7</v>
+        <v>10.2</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>497.13</v>
+        <v>1886.68</v>
       </c>
       <c r="AN4" t="n">
-        <v>468.41</v>
+        <v>1768.6</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹78,581.42 Cr., a P/E ratio of 9.48, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
+          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹84,430.26 Cr., a P/E ratio of 113.20, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.98 (Bullish Momentum Zone), while MACD Line (8.32) trades below Signal (9.39) with an expanding histogram (-1.07). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.69% above the 200-day DMA (₹455.15). Daily volatility envelope is bounded by ATR(14) of ₹12.91.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.34 (Consolidation Zone), while MACD Line (28.67) trades below Signal (44.16) with an expanding histogram (-15.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.10% above the 200-day DMA (₹1651.79). Daily volatility envelope is bounded by ATR(14) of ₹50.46.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹483.10) is positioned above the 30-day DMA (₹476.73), 50-day DMA (₹462.94), and 200-day DMA (₹455.15). The price distance from 200 DMA is +6.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,827.10) is positioned above the 30-day DMA (₹1,759.45), 50-day DMA (₹1,685.94), and 200-day DMA (₹1,651.79). The price distance from 200 DMA is +5.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[483.1, 484.55, 486.0, 487.45, 488.9, 490.35]</t>
+          <t>[1827.1, 1869.43, 1911.75, 1954.08, 1996.4, 2038.73]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[483.1, 489.71, 493.3, 496.39, 499.23, 501.9]</t>
+          <t>[1827.1, 1889.61, 1940.3, 1989.04, 2036.78, 2083.87]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[483.1, 480.68, 480.52, 480.74, 481.15, 481.68]</t>
+          <t>[1827.1, 1854.29, 1890.34, 1927.86, 1966.13, 2004.88]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>469.22</v>
+        <v>1932.24</v>
       </c>
     </row>
     <row r="5">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,154 +1171,154 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>59124.78</v>
+        <v>134237.57</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>981.9</v>
+        <v>116.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹976.04 - ₹990.7</t>
+          <t>₹116.39 - ₹117.42</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1005.36</v>
+        <v>118.44</v>
       </c>
       <c r="I5" t="n">
-        <v>968.03</v>
+        <v>116.06</v>
       </c>
       <c r="J5" t="n">
-        <v>951.5700000000001</v>
+        <v>113.21</v>
       </c>
       <c r="K5" t="n">
-        <v>850.11</v>
+        <v>112.35</v>
       </c>
       <c r="L5" t="n">
-        <v>20.75</v>
+        <v>2.09</v>
       </c>
       <c r="M5" t="n">
-        <v>27.47</v>
+        <v>0.6</v>
       </c>
       <c r="N5" t="n">
-        <v>29.9</v>
+        <v>0.89</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.43</v>
+        <v>-0.29</v>
       </c>
       <c r="P5" t="n">
-        <v>29.32</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.28</v>
+        <v>13.17</v>
       </c>
       <c r="R5" t="n">
-        <v>42.8</v>
+        <v>50.8</v>
       </c>
       <c r="S5" t="n">
-        <v>0.18</v>
+        <v>0.39</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.06</v>
+        <v>-0.78</v>
       </c>
       <c r="U5" t="n">
-        <v>51.7</v>
+        <v>52.5</v>
       </c>
       <c r="V5" t="n">
-        <v>3.95</v>
+        <v>2.56</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>970.23</v>
+        <v>116.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>1099.2</v>
+        <v>122.72</v>
       </c>
       <c r="Z5" t="n">
-        <v>1099.2</v>
+        <v>121.96</v>
       </c>
       <c r="AA5" t="n">
-        <v>937.92</v>
+        <v>113.72</v>
       </c>
       <c r="AB5" t="n">
-        <v>978.53</v>
+        <v>116.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>993.26</v>
+        <v>117.97</v>
       </c>
       <c r="AD5" t="n">
-        <v>1004.63</v>
+        <v>119.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>59.9</v>
+        <v>41.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.34</v>
+        <v>-0.11</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (13.28) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (13.17) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>30.5</v>
+        <v>6.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23.9</v>
+        <v>-6.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>38.1</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1020.84</v>
+        <v>119.95</v>
       </c>
       <c r="AN5" t="n">
-        <v>944.36</v>
+        <v>113.58</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹59,124.78 Cr., a P/E ratio of 30.47, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,237.57 Cr., a P/E ratio of 6.08, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.93 (Bullish Momentum Zone), while MACD Line (27.47) trades below Signal (29.90) with an expanding histogram (-2.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.75% above the 200-day DMA (₹850.11). Daily volatility envelope is bounded by ATR(14) of ₹29.32.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 41.79 (Consolidation Zone), while MACD Line (0.60) trades below Signal (0.89) with an expanding histogram (-0.29). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.09% above the 200-day DMA (₹112.35). Daily volatility envelope is bounded by ATR(14) of ₹2.05.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹981.90) is positioned above the 30-day DMA (₹968.03), 50-day DMA (₹951.57), and 200-day DMA (₹850.11). The price distance from 200 DMA is +20.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.80) is positioned above the 30-day DMA (₹116.06), 50-day DMA (₹113.21), and 200-day DMA (₹112.35). The price distance from 200 DMA is +2.09%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[981.9, 984.85, 987.79, 990.74, 993.68, 996.63]</t>
+          <t>[116.8, 118.0, 119.19, 120.39, 121.59, 122.79]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[981.9, 996.57, 1004.38, 1011.05, 1017.14, 1022.85]</t>
+          <t>[116.8, 118.82, 120.36, 121.81, 123.23, 124.62]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[981.9, 976.05, 975.35, 975.5, 976.09, 976.96]</t>
+          <t>[116.8, 117.38, 118.32, 119.32, 120.36, 121.41]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1099.2</v>
+        <v>121.96</v>
       </c>
     </row>
     <row r="6">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,154 +1338,488 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29785.91</v>
+        <v>81729.57000000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>541.5</v>
+        <v>3211.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹538.04 - ₹546.69</t>
+          <t>₹3191.55 - ₹3240.68</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>555.33</v>
+        <v>3289.82</v>
       </c>
       <c r="I6" t="n">
-        <v>516.4400000000001</v>
+        <v>3116.69</v>
       </c>
       <c r="J6" t="n">
-        <v>523.9299999999999</v>
+        <v>2971.52</v>
       </c>
       <c r="K6" t="n">
-        <v>523.49</v>
+        <v>2683.55</v>
       </c>
       <c r="L6" t="n">
-        <v>7.53</v>
+        <v>18.26</v>
       </c>
       <c r="M6" t="n">
-        <v>12.89</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>8.15</v>
+        <v>109.67</v>
       </c>
       <c r="O6" t="n">
-        <v>4.75</v>
+        <v>-24.85</v>
       </c>
       <c r="P6" t="n">
-        <v>17.29</v>
+        <v>98.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.28</v>
+        <v>13.17</v>
       </c>
       <c r="R6" t="n">
-        <v>37.4</v>
+        <v>46.1</v>
       </c>
       <c r="S6" t="n">
         <v>0.17</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.53</v>
+        <v>-1.94</v>
       </c>
       <c r="U6" t="n">
-        <v>45</v>
+        <v>52.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5.03</v>
+        <v>3.38</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>532.4</v>
+        <v>3181.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>571.65</v>
+        <v>4129.62</v>
       </c>
       <c r="Z6" t="n">
-        <v>571.65</v>
+        <v>4129.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>515.5700000000001</v>
+        <v>3063.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>540.35</v>
+        <v>3164.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>551.1</v>
+        <v>3271.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>560.7</v>
+        <v>3332</v>
       </c>
       <c r="AE6" t="n">
-        <v>80.90000000000001</v>
+        <v>39.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Vol Spike 2.9x | Inst. Buying (CMF+) | Low VIX (13.28) | LSTM Deep Net</t>
+          <t>Low VIX (13.17) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.2</v>
+        <v>53</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14.5</v>
+        <v>85.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>65.2</v>
+        <v>55.6</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>554.91</v>
+        <v>3338.72</v>
       </c>
       <c r="AN6" t="n">
-        <v>528.27</v>
+        <v>3099.62</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹29,785.91 Cr., a P/E ratio of 5.19, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹81,729.57 Cr., a P/E ratio of 52.98, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 80.94 (Bullish Momentum Zone), while MACD Line (12.89) trades above Signal (8.15) with an expanding histogram (+4.75). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.53% above the 200-day DMA (₹523.49). Daily volatility envelope is bounded by ATR(14) of ₹17.29.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.45 (Consolidation Zone), while MACD Line (84.82) trades below Signal (109.67) with an expanding histogram (-24.85). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.26% above the 200-day DMA (₹2683.55). Daily volatility envelope is bounded by ATR(14) of ₹98.27.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹541.50) is positioned above the 30-day DMA (₹516.44), 50-day DMA (₹523.93), and 200-day DMA (₹523.49). The price distance from 200 DMA is +7.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,211.20) is positioned above the 30-day DMA (₹3,116.69), 50-day DMA (₹2,971.52), and 200-day DMA (₹2,683.55). The price distance from 200 DMA is +18.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[541.5, 543.12, 544.75, 546.37, 548.0, 549.62]</t>
+          <t>[3211.2, 3220.83, 3230.47, 3240.1, 3249.73, 3259.37]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[541.5, 550.04, 554.53, 558.35, 561.83, 565.09]</t>
+          <t>[3211.2, 3260.14, 3286.06, 3308.18, 3328.35, 3347.26]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[541.5, 537.94, 537.41, 537.39, 537.62, 538.02]</t>
+          <t>[3211.2, 3191.35, 3188.77, 3189.04, 3190.77, 3193.45]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>571.65</v>
+        <v>4129.62</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>29868.42</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>543</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>₹539.37 - ₹548.45</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>557.53</v>
+      </c>
+      <c r="I7" t="n">
+        <v>517.41</v>
+      </c>
+      <c r="J7" t="n">
+        <v>523.91</v>
+      </c>
+      <c r="K7" t="n">
+        <v>523.47</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="M7" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="P7" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="R7" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-2.22</v>
+      </c>
+      <c r="U7" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="V7" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X7" t="n">
+        <v>542.7</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>573.23</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>573.23</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>515.75</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>541.35</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>553.1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>563.2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.17) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>556.15</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>529.65</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹29,868.42 Cr., a P/E ratio of 5.21, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.77 (Bullish Momentum Zone), while MACD Line (11.70) trades above Signal (8.86) with an expanding histogram (+2.85). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.54% above the 200-day DMA (₹523.47). Daily volatility envelope is bounded by ATR(14) of ₹18.16.</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹543.00) is positioned above the 30-day DMA (₹517.41), 50-day DMA (₹523.91), and 200-day DMA (₹523.47). The price distance from 200 DMA is +3.54%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>[543.0, 544.63, 546.26, 547.89, 549.52, 551.14]</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>[543.0, 551.89, 556.53, 560.47, 564.05, 567.39]</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>[543.0, 539.18, 538.55, 538.45, 538.62, 538.96]</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>573.23</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>58816.87</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>976.5</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>₹970.42 - ₹985.62</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1000.81</v>
+      </c>
+      <c r="I8" t="n">
+        <v>972.12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>952.3200000000001</v>
+      </c>
+      <c r="K8" t="n">
+        <v>850.47</v>
+      </c>
+      <c r="L8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="N8" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-5.52</v>
+      </c>
+      <c r="P8" t="n">
+        <v>30.39</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="R8" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="U8" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X8" t="n">
+        <v>974.96</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1093.15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1093.15</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>930.91</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>976.73</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>989.66</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1002.83</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Low VIX (13.17) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1014.54</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>940.58</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹58,816.87 Cr., a P/E ratio of 30.33, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.77 (Consolidation Zone), while MACD Line (22.99) trades below Signal (28.52) with an expanding histogram (-5.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.50% above the 200-day DMA (₹850.47). Daily volatility envelope is bounded by ATR(14) of ₹30.39.</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹976.50) is positioned above the 30-day DMA (₹972.12), 50-day DMA (₹952.32), and 200-day DMA (₹850.47). The price distance from 200 DMA is +16.50%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>[976.5, 979.43, 982.36, 985.29, 988.22, 991.15]</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>[976.5, 991.59, 999.55, 1006.35, 1012.53, 1018.33]</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>[976.5, 970.31, 969.46, 969.5, 969.98, 970.76]</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>1093.15</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU8"/>
+  <dimension ref="A1:AU7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,16 +713,16 @@
         <v>12.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.17</v>
+        <v>13.43</v>
       </c>
       <c r="R2" t="n">
-        <v>53.5</v>
+        <v>56.9</v>
       </c>
       <c r="S2" t="n">
         <v>0.2</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.28</v>
+        <v>-1.26</v>
       </c>
       <c r="U2" t="n">
         <v>60.7</v>
@@ -734,13 +734,13 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>487.1</v>
+        <v>472.19</v>
       </c>
       <c r="Y2" t="n">
-        <v>507.49</v>
+        <v>503.96</v>
       </c>
       <c r="Z2" t="n">
-        <v>473.59</v>
+        <v>503.96</v>
       </c>
       <c r="AA2" t="n">
         <v>468.23</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (13.17) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (13.43) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
@@ -781,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>502.32</v>
+        <v>502.12</v>
       </c>
       <c r="AN2" t="n">
-        <v>471.85</v>
+        <v>471.8</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹79,313.40 Cr., a P/E ratio of 9.49, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
+          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹79,313.40 Cr., a P/E ratio of 9.45, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>473.59</v>
+        <v>503.96</v>
       </c>
     </row>
     <row r="3">
@@ -880,16 +880,16 @@
         <v>6.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.17</v>
+        <v>13.43</v>
       </c>
       <c r="R3" t="n">
-        <v>52.7</v>
+        <v>50.1</v>
       </c>
       <c r="S3" t="n">
         <v>0.34</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.78</v>
+        <v>-0.79</v>
       </c>
       <c r="U3" t="n">
         <v>50.8</v>
@@ -901,13 +901,13 @@
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>415</v>
+        <v>404.66</v>
       </c>
       <c r="Y3" t="n">
-        <v>434.81</v>
+        <v>409.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>418.73</v>
+        <v>409.4</v>
       </c>
       <c r="AA3" t="n">
         <v>405.14</v>
@@ -929,14 +929,14 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Low VIX (13.17) | LSTM Deep Net</t>
+          <t>Low VIX (13.43) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AJ3" t="n">
         <v>21</v>
@@ -948,14 +948,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>424.58</v>
+        <v>423.9</v>
       </c>
       <c r="AN3" t="n">
-        <v>405.66</v>
+        <v>405.18</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹412,827.73 Cr., a P/E ratio of 20.33, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹412,827.73 Cr., a P/E ratio of 20.08, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>418.73</v>
+        <v>409.4</v>
       </c>
     </row>
     <row r="4">
@@ -1016,68 +1016,68 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹1817.01 - ₹1842.24</t>
+          <t>₹1817.58 - ₹1841.38</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1867.47</v>
+        <v>1865.19</v>
       </c>
       <c r="I4" t="n">
-        <v>1759.45</v>
+        <v>1764.36</v>
       </c>
       <c r="J4" t="n">
-        <v>1685.94</v>
+        <v>1690.27</v>
       </c>
       <c r="K4" t="n">
-        <v>1651.79</v>
+        <v>1651.84</v>
       </c>
       <c r="L4" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="M4" t="n">
-        <v>28.67</v>
+        <v>25.19</v>
       </c>
       <c r="N4" t="n">
-        <v>44.16</v>
+        <v>41.15</v>
       </c>
       <c r="O4" t="n">
-        <v>-15.48</v>
+        <v>-15.95</v>
       </c>
       <c r="P4" t="n">
-        <v>50.46</v>
+        <v>47.61</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.17</v>
+        <v>13.43</v>
       </c>
       <c r="R4" t="n">
-        <v>51.7</v>
+        <v>48.1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U4" t="n">
         <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>4.57</v>
+        <v>3.9</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>1827.1</v>
+        <v>1818.35</v>
       </c>
       <c r="Y4" t="n">
-        <v>1947.92</v>
+        <v>1807.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>1932.24</v>
+        <v>1680.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>1751.4</v>
+        <v>1755.69</v>
       </c>
       <c r="AB4" t="n">
         <v>1794.73</v>
@@ -1089,21 +1089,21 @@
         <v>1931.63</v>
       </c>
       <c r="AE4" t="n">
-        <v>43.3</v>
+        <v>41.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (13.17) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (13.43) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>113.2</v>
+        <v>107.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>40.1</v>
@@ -1115,43 +1115,43 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>1886.68</v>
+        <v>1888.65</v>
       </c>
       <c r="AN4" t="n">
-        <v>1768.6</v>
+        <v>1763.23</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹84,430.26 Cr., a P/E ratio of 113.20, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
+          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹84,430.26 Cr., a P/E ratio of 107.54, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.34 (Consolidation Zone), while MACD Line (28.67) trades below Signal (44.16) with an expanding histogram (-15.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.10% above the 200-day DMA (₹1651.79). Daily volatility envelope is bounded by ATR(14) of ₹50.46.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 41.21 (Consolidation Zone), while MACD Line (25.19) trades below Signal (41.15) with an expanding histogram (-15.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.09% above the 200-day DMA (₹1651.84). Daily volatility envelope is bounded by ATR(14) of ₹47.61.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,827.10) is positioned above the 30-day DMA (₹1,759.45), 50-day DMA (₹1,685.94), and 200-day DMA (₹1,651.79). The price distance from 200 DMA is +5.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,827.10) is positioned above the 30-day DMA (₹1,764.36), 50-day DMA (₹1,690.27), and 200-day DMA (₹1,651.84). The price distance from 200 DMA is +5.09%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[1827.1, 1869.43, 1911.75, 1954.08, 1996.4, 2038.73]</t>
+          <t>[1827.1, 1870.74, 1914.37, 1958.01, 2001.64, 2045.28]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[1827.1, 1889.61, 1940.3, 1989.04, 2036.78, 2083.87]</t>
+          <t>[1827.1, 1889.78, 1941.3, 1990.99, 2039.73, 2087.86]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[1827.1, 1854.29, 1890.34, 1927.86, 1966.13, 2004.88]</t>
+          <t>[1827.1, 1856.45, 1894.17, 1933.27, 1973.08, 2013.34]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1932.24</v>
+        <v>1680.75</v>
       </c>
     </row>
     <row r="5">
@@ -1214,16 +1214,16 @@
         <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.17</v>
+        <v>13.43</v>
       </c>
       <c r="R5" t="n">
-        <v>50.8</v>
+        <v>47.9</v>
       </c>
       <c r="S5" t="n">
         <v>0.39</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.78</v>
+        <v>-0.77</v>
       </c>
       <c r="U5" t="n">
         <v>52.5</v>
@@ -1235,13 +1235,13 @@
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>116.8</v>
+        <v>114.66</v>
       </c>
       <c r="Y5" t="n">
-        <v>122.72</v>
+        <v>114.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>121.96</v>
+        <v>110.98</v>
       </c>
       <c r="AA5" t="n">
         <v>113.72</v>
@@ -1263,14 +1263,14 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (13.17) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (13.43) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AJ5" t="n">
         <v>-6.4</v>
@@ -1282,14 +1282,14 @@
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>119.95</v>
+        <v>119.94</v>
       </c>
       <c r="AN5" t="n">
-        <v>113.58</v>
+        <v>113.86</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,237.57 Cr., a P/E ratio of 6.08, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,237.57 Cr., a P/E ratio of 5.97, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1304,21 +1304,21 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[116.8, 118.0, 119.19, 120.39, 121.59, 122.79]</t>
+          <t>[116.8, 118.0, 119.19, 120.39, 121.58, 122.78]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[116.8, 118.82, 120.36, 121.81, 123.23, 124.62]</t>
+          <t>[116.8, 118.82, 120.35, 121.81, 123.23, 124.62]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[116.8, 117.38, 118.32, 119.32, 120.36, 121.41]</t>
+          <t>[116.8, 117.38, 118.32, 119.32, 120.35, 121.4]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>121.96</v>
+        <v>110.98</v>
       </c>
     </row>
     <row r="6">
@@ -1381,16 +1381,16 @@
         <v>98.27</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.17</v>
+        <v>13.43</v>
       </c>
       <c r="R6" t="n">
-        <v>46.1</v>
+        <v>45.7</v>
       </c>
       <c r="S6" t="n">
         <v>0.17</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.94</v>
+        <v>-1.97</v>
       </c>
       <c r="U6" t="n">
         <v>52.5</v>
@@ -1402,13 +1402,13 @@
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>3181.06</v>
+        <v>3083.65</v>
       </c>
       <c r="Y6" t="n">
-        <v>4129.62</v>
+        <v>3082.89</v>
       </c>
       <c r="Z6" t="n">
-        <v>4129.62</v>
+        <v>2487.45</v>
       </c>
       <c r="AA6" t="n">
         <v>3063.8</v>
@@ -1430,14 +1430,14 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Low VIX (13.17) | LSTM Deep Net</t>
+          <t>Low VIX (13.43) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>53</v>
+        <v>52.4</v>
       </c>
       <c r="AJ6" t="n">
         <v>85.3</v>
@@ -1449,14 +1449,14 @@
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>3338.72</v>
+        <v>3338.82</v>
       </c>
       <c r="AN6" t="n">
-        <v>3099.62</v>
+        <v>3092.96</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹81,729.57 Cr., a P/E ratio of 52.98, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹81,729.57 Cr., a P/E ratio of 52.36, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>4129.62</v>
+        <v>2487.45</v>
       </c>
     </row>
     <row r="7">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1517,68 +1517,68 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹539.37 - ₹548.45</t>
+          <t>₹539.61 - ₹548.08</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>557.53</v>
+        <v>556.55</v>
       </c>
       <c r="I7" t="n">
-        <v>517.41</v>
+        <v>519.22</v>
       </c>
       <c r="J7" t="n">
-        <v>523.91</v>
+        <v>524.41</v>
       </c>
       <c r="K7" t="n">
-        <v>523.47</v>
+        <v>523.59</v>
       </c>
       <c r="L7" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="M7" t="n">
-        <v>11.7</v>
+        <v>11.93</v>
       </c>
       <c r="N7" t="n">
-        <v>8.859999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="O7" t="n">
-        <v>2.85</v>
+        <v>2.19</v>
       </c>
       <c r="P7" t="n">
-        <v>18.16</v>
+        <v>16.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.17</v>
+        <v>13.43</v>
       </c>
       <c r="R7" t="n">
-        <v>45.1</v>
+        <v>43.9</v>
       </c>
       <c r="S7" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.22</v>
+        <v>-2.11</v>
       </c>
       <c r="U7" t="n">
         <v>46.7</v>
       </c>
       <c r="V7" t="n">
-        <v>4.96</v>
+        <v>5.14</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>542.7</v>
+        <v>525.41</v>
       </c>
       <c r="Y7" t="n">
-        <v>573.23</v>
+        <v>525.15</v>
       </c>
       <c r="Z7" t="n">
-        <v>573.23</v>
+        <v>517.52</v>
       </c>
       <c r="AA7" t="n">
-        <v>515.75</v>
+        <v>517.6</v>
       </c>
       <c r="AB7" t="n">
         <v>541.35</v>
@@ -1590,14 +1590,14 @@
         <v>563.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>70.8</v>
+        <v>66.8</v>
       </c>
       <c r="AF7" t="n">
         <v>0.23</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.17) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.43) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
@@ -1616,24 +1616,24 @@
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>556.15</v>
+        <v>555.48</v>
       </c>
       <c r="AN7" t="n">
-        <v>529.65</v>
+        <v>529.97</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹29,868.42 Cr., a P/E ratio of 5.21, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹29,868.42 Cr., a P/E ratio of 5.19, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.77 (Bullish Momentum Zone), while MACD Line (11.70) trades above Signal (8.86) with an expanding histogram (+2.85). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.54% above the 200-day DMA (₹523.47). Daily volatility envelope is bounded by ATR(14) of ₹18.16.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 66.79 (Bullish Momentum Zone), while MACD Line (11.93) trades above Signal (9.74) with an expanding histogram (+2.19). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.52% above the 200-day DMA (₹523.59). Daily volatility envelope is bounded by ATR(14) of ₹16.93.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹543.00) is positioned above the 30-day DMA (₹517.41), 50-day DMA (₹523.91), and 200-day DMA (₹523.47). The price distance from 200 DMA is +3.54%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹543.00) is positioned above the 30-day DMA (₹519.22), 50-day DMA (₹524.41), and 200-day DMA (₹523.59). The price distance from 200 DMA is +3.52%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -1643,183 +1643,16 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[543.0, 551.89, 556.53, 560.47, 564.05, 567.39]</t>
+          <t>[543.0, 551.4, 555.84, 559.62, 563.06, 566.29]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[543.0, 539.18, 538.55, 538.45, 538.62, 538.96]</t>
+          <t>[543.0, 539.55, 539.07, 539.09, 539.36, 539.79]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>573.23</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>58816.87</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>976.5</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>₹970.42 - ₹985.62</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1000.81</v>
-      </c>
-      <c r="I8" t="n">
-        <v>972.12</v>
-      </c>
-      <c r="J8" t="n">
-        <v>952.3200000000001</v>
-      </c>
-      <c r="K8" t="n">
-        <v>850.47</v>
-      </c>
-      <c r="L8" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="N8" t="n">
-        <v>28.52</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-5.52</v>
-      </c>
-      <c r="P8" t="n">
-        <v>30.39</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="R8" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="U8" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X8" t="n">
-        <v>974.96</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1093.15</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1093.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>930.91</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>976.73</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>989.66</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1002.83</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (13.17) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1014.54</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>940.58</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹58,816.87 Cr., a P/E ratio of 30.33, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.77 (Consolidation Zone), while MACD Line (22.99) trades below Signal (28.52) with an expanding histogram (-5.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.50% above the 200-day DMA (₹850.47). Daily volatility envelope is bounded by ATR(14) of ₹30.39.</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹976.50) is positioned above the 30-day DMA (₹972.12), 50-day DMA (₹952.32), and 200-day DMA (₹850.47). The price distance from 200 DMA is +16.50%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>[976.5, 979.43, 982.36, 985.29, 988.22, 991.15]</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>[976.5, 991.59, 999.55, 1006.35, 1012.53, 1018.33]</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>[976.5, 970.31, 969.46, 969.5, 969.98, 970.76]</t>
-        </is>
-      </c>
-      <c r="AU8" t="n">
-        <v>1093.15</v>
+        <v>517.52</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU7"/>
+  <dimension ref="A1:AU8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,21 +656,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79313.39999999999</v>
+        <v>25000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,166 +678,166 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>487.6</v>
+        <v>3281.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹485.02 - ₹491.47</t>
+          <t>₹3261.05 - ₹3312.93</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>497.93</v>
+        <v>3364.81</v>
       </c>
       <c r="I2" t="n">
-        <v>476.73</v>
+        <v>3137.32</v>
       </c>
       <c r="J2" t="n">
-        <v>462.94</v>
+        <v>2981.04</v>
       </c>
       <c r="K2" t="n">
-        <v>455.15</v>
+        <v>2689.42</v>
       </c>
       <c r="L2" t="n">
-        <v>6.69</v>
+        <v>19.4</v>
       </c>
       <c r="M2" t="n">
-        <v>8.32</v>
+        <v>74.77</v>
       </c>
       <c r="N2" t="n">
-        <v>9.390000000000001</v>
+        <v>102.69</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.07</v>
+        <v>-27.92</v>
       </c>
       <c r="P2" t="n">
-        <v>12.91</v>
+        <v>103.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.43</v>
+        <v>12.59</v>
       </c>
       <c r="R2" t="n">
-        <v>56.9</v>
+        <v>47.9</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.26</v>
+        <v>-1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>60.7</v>
+        <v>52.5</v>
       </c>
       <c r="V2" t="n">
-        <v>3.74</v>
+        <v>3.39</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>472.19</v>
+        <v>3235.82</v>
       </c>
       <c r="Y2" t="n">
-        <v>503.96</v>
+        <v>3232.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>503.96</v>
+        <v>2558.62</v>
       </c>
       <c r="AA2" t="n">
-        <v>468.23</v>
+        <v>3126.15</v>
       </c>
       <c r="AB2" t="n">
-        <v>486.17</v>
+        <v>3255.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>490.94</v>
+        <v>3330.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>494.27</v>
+        <v>3379.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>63</v>
+        <v>46.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.16</v>
+        <v>0.2</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (13.43) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.59) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>9.5</v>
+        <v>53.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>57.7</v>
+        <v>85.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>21.7</v>
+        <v>55.6</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>502.12</v>
+        <v>3409.65</v>
       </c>
       <c r="AN2" t="n">
-        <v>471.8</v>
+        <v>3172.37</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>OIL operates in the Energy sector. With an estimated Market Cap of ₹79,313.40 Cr., a P/E ratio of 9.45, and YoY Revenue Growth of +57.7%, the company demonstrates strong institutional backing, solid operating profit margins (21.68%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.51, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.98 (Bullish Momentum Zone), while MACD Line (8.32) trades below Signal (9.39) with an expanding histogram (-1.07). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.69% above the 200-day DMA (₹455.15). Daily volatility envelope is bounded by ATR(14) of ₹12.91.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.45 (Consolidation Zone), while MACD Line (74.77) trades below Signal (102.69) with an expanding histogram (-27.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.40% above the 200-day DMA (₹2689.42). Daily volatility envelope is bounded by ATR(14) of ₹103.76.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for OIL. Current Market Price (₹487.60) is positioned above the 30-day DMA (₹476.73), 50-day DMA (₹462.94), and 200-day DMA (₹455.15). The price distance from 200 DMA is +6.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,281.80) is positioned above the 30-day DMA (₹3,137.32), 50-day DMA (₹2,981.04), and 200-day DMA (₹2,689.42). The price distance from 200 DMA is +19.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[487.6, 489.06, 490.53, 491.99, 493.45, 494.91]</t>
+          <t>[3281.8, 3329.5, 3377.19, 3424.89, 3472.58, 3520.28]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[487.6, 494.23, 497.83, 500.93, 503.78, 506.46]</t>
+          <t>[3281.8, 3371.0, 3435.89, 3496.78, 3555.6, 3613.09]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[487.6, 485.19, 485.05, 485.28, 485.7, 486.25]</t>
+          <t>[3281.8, 3298.37, 3333.17, 3370.97, 3410.33, 3450.67]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>503.96</v>
+        <v>2558.62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>412827.73</v>
+        <v>298715.03</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,166 +845,166 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>415</v>
+        <v>324.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹413.68 - ₹416.97</t>
+          <t>₹323.08 - ₹326.63</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>420.26</v>
+        <v>330.18</v>
       </c>
       <c r="I3" t="n">
-        <v>407.23</v>
+        <v>321.54</v>
       </c>
       <c r="J3" t="n">
-        <v>397.97</v>
+        <v>310.62</v>
       </c>
       <c r="K3" t="n">
-        <v>399.91</v>
+        <v>274.23</v>
       </c>
       <c r="L3" t="n">
-        <v>2.47</v>
+        <v>15.6</v>
       </c>
       <c r="M3" t="n">
-        <v>5.29</v>
+        <v>2.3</v>
       </c>
       <c r="N3" t="n">
-        <v>6.79</v>
+        <v>4.59</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.5</v>
+        <v>-2.28</v>
       </c>
       <c r="P3" t="n">
-        <v>6.58</v>
+        <v>7.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.43</v>
+        <v>12.59</v>
       </c>
       <c r="R3" t="n">
-        <v>50.1</v>
+        <v>47.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0.34</v>
+        <v>0.24</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.79</v>
+        <v>-1.23</v>
       </c>
       <c r="U3" t="n">
-        <v>50.8</v>
+        <v>51.7</v>
       </c>
       <c r="V3" t="n">
-        <v>3.62</v>
+        <v>2.52</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>404.66</v>
+        <v>316.21</v>
       </c>
       <c r="Y3" t="n">
-        <v>409.4</v>
+        <v>315.97</v>
       </c>
       <c r="Z3" t="n">
-        <v>409.4</v>
+        <v>302.74</v>
       </c>
       <c r="AA3" t="n">
-        <v>405.14</v>
+        <v>313.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>413.8</v>
+        <v>323.52</v>
       </c>
       <c r="AC3" t="n">
-        <v>418.25</v>
+        <v>328.79</v>
       </c>
       <c r="AD3" t="n">
-        <v>421.5</v>
+        <v>333.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>43.1</v>
+        <v>27.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.03</v>
+        <v>0.31</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Low VIX (13.43) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.59) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>20.1</v>
+        <v>676</v>
       </c>
       <c r="AJ3" t="n">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="AK3" t="n">
-        <v>28.5</v>
+        <v>0.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>423.9</v>
+        <v>335.89</v>
       </c>
       <c r="AN3" t="n">
-        <v>405.18</v>
+        <v>313.65</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹412,827.73 Cr., a P/E ratio of 20.08, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹298,715.03 Cr., a P/E ratio of 676.04, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.07 (Consolidation Zone), while MACD Line (5.29) trades below Signal (6.79) with an expanding histogram (-1.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.47% above the 200-day DMA (₹399.91). Daily volatility envelope is bounded by ATR(14) of ₹6.58.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 27.78 (Consolidation Zone), while MACD Line (2.30) trades below Signal (4.59) with an expanding histogram (-2.28). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.60% above the 200-day DMA (₹274.23). Daily volatility envelope is bounded by ATR(14) of ₹7.10.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹415.00) is positioned above the 30-day DMA (₹407.23), 50-day DMA (₹397.97), and 200-day DMA (₹399.91). The price distance from 200 DMA is +2.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹324.50) is positioned above the 30-day DMA (₹321.54), 50-day DMA (₹310.62), and 200-day DMA (₹274.23). The price distance from 200 DMA is +15.60%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[415.0, 416.44, 417.88, 419.32, 420.76, 422.2]</t>
+          <t>[324.5, 325.47, 326.45, 327.42, 328.39, 329.37]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[415.0, 419.07, 421.6, 423.88, 426.02, 428.08]</t>
+          <t>[324.5, 328.31, 330.46, 332.34, 334.07, 335.72]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[415.0, 414.47, 415.09, 415.9, 416.82, 417.79]</t>
+          <t>[324.5, 323.34, 323.43, 323.73, 324.13, 324.6]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>409.4</v>
+        <v>302.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>84430.25999999999</v>
+        <v>59357.82</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,157 +1012,157 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1827.1</v>
+        <v>2137.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹1817.58 - ₹1841.38</t>
+          <t>₹2125.63 - ₹2156.05</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1865.19</v>
+        <v>2186.48</v>
       </c>
       <c r="I4" t="n">
-        <v>1764.36</v>
+        <v>2120.19</v>
       </c>
       <c r="J4" t="n">
-        <v>1690.27</v>
+        <v>2003.6</v>
       </c>
       <c r="K4" t="n">
-        <v>1651.84</v>
+        <v>1954.83</v>
       </c>
       <c r="L4" t="n">
-        <v>5.09</v>
+        <v>8.41</v>
       </c>
       <c r="M4" t="n">
-        <v>25.19</v>
+        <v>40.46</v>
       </c>
       <c r="N4" t="n">
-        <v>41.15</v>
+        <v>59.08</v>
       </c>
       <c r="O4" t="n">
-        <v>-15.95</v>
+        <v>-18.62</v>
       </c>
       <c r="P4" t="n">
-        <v>47.61</v>
+        <v>60.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.43</v>
+        <v>12.59</v>
       </c>
       <c r="R4" t="n">
-        <v>48.1</v>
+        <v>46.1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.61</v>
+        <v>0.2</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="V4" t="n">
-        <v>3.9</v>
+        <v>2.83</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>1818.35</v>
+        <v>2095.17</v>
       </c>
       <c r="Y4" t="n">
-        <v>1807.34</v>
+        <v>2093.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>1680.75</v>
+        <v>1995.45</v>
       </c>
       <c r="AA4" t="n">
-        <v>1755.69</v>
+        <v>2046.53</v>
       </c>
       <c r="AB4" t="n">
-        <v>1794.73</v>
+        <v>2132.1</v>
       </c>
       <c r="AC4" t="n">
-        <v>1879.36</v>
+        <v>2154.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1931.63</v>
+        <v>2170.6</v>
       </c>
       <c r="AE4" t="n">
-        <v>41.2</v>
+        <v>46.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.18</v>
+        <v>0.04</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (13.43) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.59) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>107.5</v>
+        <v>48.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>40.1</v>
+        <v>8.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>10.2</v>
+        <v>5.2</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>1888.65</v>
+        <v>2201.91</v>
       </c>
       <c r="AN4" t="n">
-        <v>1763.23</v>
+        <v>2082.77</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹84,430.26 Cr., a P/E ratio of 107.54, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹59,357.82 Cr., a P/E ratio of 48.27, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 41.21 (Consolidation Zone), while MACD Line (25.19) trades below Signal (41.15) with an expanding histogram (-15.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.09% above the 200-day DMA (₹1651.84). Daily volatility envelope is bounded by ATR(14) of ₹47.61.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.85 (Consolidation Zone), while MACD Line (40.46) trades below Signal (59.08) with an expanding histogram (-18.62). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.41% above the 200-day DMA (₹1954.83). Daily volatility envelope is bounded by ATR(14) of ₹60.85.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,827.10) is positioned above the 30-day DMA (₹1,764.36), 50-day DMA (₹1,690.27), and 200-day DMA (₹1,651.84). The price distance from 200 DMA is +5.09%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,137.80) is positioned above the 30-day DMA (₹2,120.19), 50-day DMA (₹2,003.60), and 200-day DMA (₹1,954.83). The price distance from 200 DMA is +8.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[1827.1, 1870.74, 1914.37, 1958.01, 2001.64, 2045.28]</t>
+          <t>[2137.8, 2156.01, 2174.23, 2192.44, 2210.66, 2228.87]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[1827.1, 1889.78, 1941.3, 1990.99, 2039.73, 2087.86]</t>
+          <t>[2137.8, 2180.35, 2208.65, 2234.6, 2259.34, 2283.3]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[1827.1, 1856.45, 1894.17, 1933.27, 1973.08, 2013.34]</t>
+          <t>[2137.8, 2137.76, 2148.41, 2160.83, 2174.15, 2188.06]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1680.75</v>
+        <v>1995.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>134237.57</v>
+        <v>29994.93</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,157 +1179,157 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>116.8</v>
+        <v>545.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹116.39 - ₹117.42</t>
+          <t>₹541.9 - ₹550.4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>118.44</v>
+        <v>558.9</v>
       </c>
       <c r="I5" t="n">
-        <v>116.06</v>
+        <v>520.59</v>
       </c>
       <c r="J5" t="n">
-        <v>113.21</v>
+        <v>524.61</v>
       </c>
       <c r="K5" t="n">
-        <v>112.35</v>
+        <v>523.61</v>
       </c>
       <c r="L5" t="n">
-        <v>2.09</v>
+        <v>3.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6</v>
+        <v>10.74</v>
       </c>
       <c r="N5" t="n">
-        <v>0.89</v>
+        <v>9.94</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.29</v>
+        <v>0.8</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>17</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.43</v>
+        <v>12.59</v>
       </c>
       <c r="R5" t="n">
-        <v>47.9</v>
+        <v>46</v>
       </c>
       <c r="S5" t="n">
-        <v>0.39</v>
+        <v>0.17</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.77</v>
+        <v>-1.99</v>
       </c>
       <c r="U5" t="n">
-        <v>52.5</v>
+        <v>46.7</v>
       </c>
       <c r="V5" t="n">
-        <v>2.56</v>
+        <v>4.87</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>114.66</v>
+        <v>525.5599999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>114.12</v>
+        <v>525.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>110.98</v>
+        <v>519.71</v>
       </c>
       <c r="AA5" t="n">
-        <v>113.72</v>
+        <v>519.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>116.3</v>
+        <v>545.42</v>
       </c>
       <c r="AC5" t="n">
-        <v>117.97</v>
+        <v>549.79</v>
       </c>
       <c r="AD5" t="n">
-        <v>119.15</v>
+        <v>554.27</v>
       </c>
       <c r="AE5" t="n">
-        <v>41.8</v>
+        <v>60.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.11</v>
+        <v>0.24</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (13.43) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.59) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>38.1</v>
+        <v>65.2</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>119.94</v>
+        <v>559.0599999999999</v>
       </c>
       <c r="AN5" t="n">
-        <v>113.86</v>
+        <v>531.45</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,237.57 Cr., a P/E ratio of 5.97, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹29,994.93 Cr., a P/E ratio of 5.22, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 41.79 (Consolidation Zone), while MACD Line (0.60) trades below Signal (0.89) with an expanding histogram (-0.29). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.09% above the 200-day DMA (₹112.35). Daily volatility envelope is bounded by ATR(14) of ₹2.05.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.36 (Bullish Momentum Zone), while MACD Line (10.74) trades above Signal (9.94) with an expanding histogram (+0.80). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.70% above the 200-day DMA (₹523.61). Daily volatility envelope is bounded by ATR(14) of ₹17.00.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.80) is positioned above the 30-day DMA (₹116.06), 50-day DMA (₹113.21), and 200-day DMA (₹112.35). The price distance from 200 DMA is +2.09%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹545.30) is positioned above the 30-day DMA (₹520.59), 50-day DMA (₹524.61), and 200-day DMA (₹523.61). The price distance from 200 DMA is +3.70%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[116.8, 118.0, 119.19, 120.39, 121.58, 122.78]</t>
+          <t>[545.3, 546.94, 548.57, 550.21, 551.84, 553.48]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[116.8, 118.82, 120.35, 121.81, 123.23, 124.62]</t>
+          <t>[545.3, 553.74, 558.19, 561.99, 565.44, 568.68]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[116.8, 117.38, 118.32, 119.32, 120.35, 121.4]</t>
+          <t>[545.3, 541.84, 541.36, 541.37, 541.64, 542.08]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>110.98</v>
+        <v>519.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>81729.57000000001</v>
+        <v>59905.79</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,157 +1346,157 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3211.2</v>
+        <v>993.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹3191.55 - ₹3240.68</t>
+          <t>₹987.9 - ₹1001.9</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3289.82</v>
+        <v>1015.89</v>
       </c>
       <c r="I6" t="n">
-        <v>3116.69</v>
+        <v>980.86</v>
       </c>
       <c r="J6" t="n">
-        <v>2971.52</v>
+        <v>955.17</v>
       </c>
       <c r="K6" t="n">
-        <v>2683.55</v>
+        <v>850.98</v>
       </c>
       <c r="L6" t="n">
-        <v>18.26</v>
+        <v>14.75</v>
       </c>
       <c r="M6" t="n">
-        <v>84.81999999999999</v>
+        <v>16.58</v>
       </c>
       <c r="N6" t="n">
-        <v>109.67</v>
+        <v>25.36</v>
       </c>
       <c r="O6" t="n">
-        <v>-24.85</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>98.27</v>
+        <v>27.99</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.43</v>
+        <v>12.59</v>
       </c>
       <c r="R6" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.97</v>
+        <v>-1.71</v>
       </c>
       <c r="U6" t="n">
         <v>52.5</v>
       </c>
       <c r="V6" t="n">
-        <v>3.38</v>
+        <v>3.51</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>3083.65</v>
+        <v>974.27</v>
       </c>
       <c r="Y6" t="n">
-        <v>3082.89</v>
+        <v>973.3200000000001</v>
       </c>
       <c r="Z6" t="n">
-        <v>2487.45</v>
+        <v>908.6799999999999</v>
       </c>
       <c r="AA6" t="n">
-        <v>3063.8</v>
+        <v>951.51</v>
       </c>
       <c r="AB6" t="n">
-        <v>3164.1</v>
+        <v>991.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>3271.6</v>
+        <v>1006.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>3332</v>
+        <v>1019.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>39.5</v>
+        <v>33.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.1</v>
+        <v>0.22</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Low VIX (13.43) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.59) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>52.4</v>
+        <v>31.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85.3</v>
+        <v>23.9</v>
       </c>
       <c r="AK6" t="n">
-        <v>55.6</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>3338.82</v>
+        <v>1032.83</v>
       </c>
       <c r="AN6" t="n">
-        <v>3092.96</v>
+        <v>956.79</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹81,729.57 Cr., a P/E ratio of 52.36, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹59,905.79 Cr., a P/E ratio of 31.30, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.45 (Consolidation Zone), while MACD Line (84.82) trades below Signal (109.67) with an expanding histogram (-24.85). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.26% above the 200-day DMA (₹2683.55). Daily volatility envelope is bounded by ATR(14) of ₹98.27.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.06 (Consolidation Zone), while MACD Line (16.58) trades below Signal (25.36) with an expanding histogram (-8.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.75% above the 200-day DMA (₹850.98). Daily volatility envelope is bounded by ATR(14) of ₹27.99.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,211.20) is positioned above the 30-day DMA (₹3,116.69), 50-day DMA (₹2,971.52), and 200-day DMA (₹2,683.55). The price distance from 200 DMA is +18.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹993.50) is positioned above the 30-day DMA (₹980.86), 50-day DMA (₹955.17), and 200-day DMA (₹850.98). The price distance from 200 DMA is +14.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[3211.2, 3220.83, 3230.47, 3240.1, 3249.73, 3259.37]</t>
+          <t>[993.5, 1002.55, 1011.6, 1020.65, 1029.69, 1038.74]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[3211.2, 3260.14, 3286.06, 3308.18, 3328.35, 3347.26]</t>
+          <t>[993.5, 1013.75, 1027.43, 1040.04, 1052.09, 1063.78]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[3211.2, 3191.35, 3188.77, 3189.04, 3190.77, 3193.45]</t>
+          <t>[993.5, 994.15, 999.72, 1006.1, 1012.9, 1019.97]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>2487.45</v>
+        <v>908.6799999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29868.42</v>
+        <v>134858.19</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,146 +1513,313 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>543</v>
+        <v>117.34</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹539.61 - ₹548.08</t>
+          <t>₹116.92 - ₹117.97</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>556.55</v>
+        <v>119.02</v>
       </c>
       <c r="I7" t="n">
-        <v>519.22</v>
+        <v>116.17</v>
       </c>
       <c r="J7" t="n">
-        <v>524.41</v>
+        <v>113.53</v>
       </c>
       <c r="K7" t="n">
-        <v>523.59</v>
+        <v>112.33</v>
       </c>
       <c r="L7" t="n">
-        <v>3.52</v>
+        <v>3.98</v>
       </c>
       <c r="M7" t="n">
-        <v>11.93</v>
+        <v>0.61</v>
       </c>
       <c r="N7" t="n">
-        <v>9.74</v>
+        <v>0.83</v>
       </c>
       <c r="O7" t="n">
-        <v>2.19</v>
+        <v>-0.22</v>
       </c>
       <c r="P7" t="n">
-        <v>16.93</v>
+        <v>2.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.43</v>
+        <v>12.59</v>
       </c>
       <c r="R7" t="n">
-        <v>43.9</v>
+        <v>44.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.11</v>
+        <v>-1.04</v>
       </c>
       <c r="U7" t="n">
-        <v>46.7</v>
+        <v>52.5</v>
       </c>
       <c r="V7" t="n">
-        <v>5.14</v>
+        <v>2.65</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>525.41</v>
+        <v>113.41</v>
       </c>
       <c r="Y7" t="n">
-        <v>525.15</v>
+        <v>113.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>517.52</v>
+        <v>111.24</v>
       </c>
       <c r="AA7" t="n">
-        <v>517.6</v>
+        <v>114.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>541.35</v>
+        <v>117.74</v>
       </c>
       <c r="AC7" t="n">
-        <v>553.1</v>
+        <v>118.99</v>
       </c>
       <c r="AD7" t="n">
-        <v>563.2</v>
+        <v>120.65</v>
       </c>
       <c r="AE7" t="n">
-        <v>66.8</v>
+        <v>55.4</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.23</v>
+        <v>-0.1</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.43) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.59) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>65.2</v>
+        <v>38.1</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>555.48</v>
+        <v>120.41</v>
       </c>
       <c r="AN7" t="n">
-        <v>529.97</v>
+        <v>114.02</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹29,868.42 Cr., a P/E ratio of 5.19, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,858.19 Cr., a P/E ratio of 5.99, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 66.79 (Bullish Momentum Zone), while MACD Line (11.93) trades above Signal (9.74) with an expanding histogram (+2.19). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.52% above the 200-day DMA (₹523.59). Daily volatility envelope is bounded by ATR(14) of ₹16.93.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.39 (Bullish Momentum Zone), while MACD Line (0.61) trades below Signal (0.83) with an expanding histogram (-0.22). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.98% above the 200-day DMA (₹112.33). Daily volatility envelope is bounded by ATR(14) of ₹2.11.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹543.00) is positioned above the 30-day DMA (₹519.22), 50-day DMA (₹524.41), and 200-day DMA (₹523.59). The price distance from 200 DMA is +3.52%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.34) is positioned above the 30-day DMA (₹116.17), 50-day DMA (₹113.53), and 200-day DMA (₹112.33). The price distance from 200 DMA is +3.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[543.0, 544.63, 546.26, 547.89, 549.52, 551.14]</t>
+          <t>[117.34, 117.69, 118.04, 118.4, 118.75, 119.1]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[543.0, 551.4, 555.84, 559.62, 563.06, 566.29]</t>
+          <t>[117.34, 118.53, 119.23, 119.85, 120.43, 120.98]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[543.0, 539.55, 539.07, 539.09, 539.36, 539.79]</t>
+          <t>[117.34, 117.06, 117.15, 117.3, 117.49, 117.69]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>517.52</v>
+        <v>111.24</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>411285.85</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>413.45</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>₹412.21 - ₹415.32</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>418.42</v>
+      </c>
+      <c r="I8" t="n">
+        <v>407.73</v>
+      </c>
+      <c r="J8" t="n">
+        <v>398.88</v>
+      </c>
+      <c r="K8" t="n">
+        <v>399.84</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="N8" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>12.59</v>
+      </c>
+      <c r="R8" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="U8" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X8" t="n">
+        <v>403.86</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>407.87</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>407.87</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>404.12</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>414.52</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>416.54</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>419.62</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Low VIX (12.59) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>422.4</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>404.73</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹411,285.85 Cr., a P/E ratio of 20.00, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 40.32 (Consolidation Zone), while MACD Line (4.81) trades below Signal (6.39) with an expanding histogram (-1.58). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.79% above the 200-day DMA (₹399.84). Daily volatility envelope is bounded by ATR(14) of ₹6.22.</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹413.45) is positioned above the 30-day DMA (₹407.73), 50-day DMA (₹398.88), and 200-day DMA (₹399.84). The price distance from 200 DMA is +3.79%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>[413.45, 415.61, 417.78, 419.94, 422.1, 424.27]</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>[413.45, 418.1, 421.29, 424.25, 427.08, 429.83]</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>[413.45, 413.75, 415.14, 416.71, 418.37, 420.1]</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>407.87</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25000</v>
+        <v>83103.94</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,15 +678,15 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3281.8</v>
+        <v>3265.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹3261.05 - ₹3312.93</t>
+          <t>₹3244.45 - ₹3296.33</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3364.81</v>
+        <v>3348.21</v>
       </c>
       <c r="I2" t="n">
         <v>3137.32</v>
@@ -713,16 +713,16 @@
         <v>103.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.59</v>
+        <v>12.29</v>
       </c>
       <c r="R2" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="S2" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.59</v>
+        <v>-1.67</v>
       </c>
       <c r="U2" t="n">
         <v>52.5</v>
@@ -734,25 +734,25 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>3235.82</v>
+        <v>3215.78</v>
       </c>
       <c r="Y2" t="n">
-        <v>3232.1</v>
+        <v>3212.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>2558.62</v>
+        <v>2542.81</v>
       </c>
       <c r="AA2" t="n">
-        <v>3126.15</v>
+        <v>3109.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>3255.3</v>
+        <v>3249.77</v>
       </c>
       <c r="AC2" t="n">
-        <v>3330.5</v>
+        <v>3319.44</v>
       </c>
       <c r="AD2" t="n">
-        <v>3379.2</v>
+        <v>3373.67</v>
       </c>
       <c r="AE2" t="n">
         <v>46.5</v>
@@ -762,14 +762,14 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.59) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>53.5</v>
+        <v>53.2</v>
       </c>
       <c r="AJ2" t="n">
         <v>85.3</v>
@@ -781,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>3409.65</v>
+        <v>3400.92</v>
       </c>
       <c r="AN2" t="n">
-        <v>3172.37</v>
+        <v>3142.07</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.51, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹83,103.94 Cr., a P/E ratio of 53.24, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -798,26 +798,26 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,281.80) is positioned above the 30-day DMA (₹3,137.32), 50-day DMA (₹2,981.04), and 200-day DMA (₹2,689.42). The price distance from 200 DMA is +19.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,265.20) is positioned above the 30-day DMA (₹3,137.32), 50-day DMA (₹2,981.04), and 200-day DMA (₹2,689.42). The price distance from 200 DMA is +19.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[3281.8, 3329.5, 3377.19, 3424.89, 3472.58, 3520.28]</t>
+          <t>[3265.2, 3308.92, 3352.65, 3396.37, 3440.1, 3483.82]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[3281.8, 3371.0, 3435.89, 3496.78, 3555.6, 3613.09]</t>
+          <t>[3265.2, 3350.43, 3411.35, 3468.26, 3523.11, 3576.63]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[3281.8, 3298.37, 3333.17, 3370.97, 3410.33, 3450.67]</t>
+          <t>[3265.2, 3277.79, 3308.62, 3342.45, 3377.84, 3414.21]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2558.62</v>
+        <v>2542.81</v>
       </c>
     </row>
     <row r="3">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>298715.03</v>
+        <v>296735.87</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,15 +845,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>324.5</v>
+        <v>322.35</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹323.08 - ₹326.63</t>
+          <t>₹320.93 - ₹324.48</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>330.18</v>
+        <v>328.03</v>
       </c>
       <c r="I3" t="n">
         <v>321.54</v>
@@ -880,46 +880,46 @@
         <v>7.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.59</v>
+        <v>12.29</v>
       </c>
       <c r="R3" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="S3" t="n">
         <v>0.24</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.23</v>
+        <v>-1.24</v>
       </c>
       <c r="U3" t="n">
         <v>51.7</v>
       </c>
       <c r="V3" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>316.21</v>
+        <v>313.71</v>
       </c>
       <c r="Y3" t="n">
-        <v>315.97</v>
+        <v>313.49</v>
       </c>
       <c r="Z3" t="n">
-        <v>302.74</v>
+        <v>300.73</v>
       </c>
       <c r="AA3" t="n">
-        <v>313.85</v>
+        <v>311.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>323.52</v>
+        <v>322.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>328.79</v>
+        <v>327.35</v>
       </c>
       <c r="AD3" t="n">
-        <v>333.07</v>
+        <v>332.35</v>
       </c>
       <c r="AE3" t="n">
         <v>27.8</v>
@@ -929,14 +929,14 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.59) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>676</v>
+        <v>671.6</v>
       </c>
       <c r="AJ3" t="n">
         <v>182</v>
@@ -948,14 +948,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>335.89</v>
+        <v>333.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>313.65</v>
+        <v>311.87</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹298,715.03 Cr., a P/E ratio of 676.04, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹296,735.87 Cr., a P/E ratio of 671.56, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -965,26 +965,26 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹324.50) is positioned above the 30-day DMA (₹321.54), 50-day DMA (₹310.62), and 200-day DMA (₹274.23). The price distance from 200 DMA is +15.60%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹322.35) is positioned above the 30-day DMA (₹321.54), 50-day DMA (₹310.62), and 200-day DMA (₹274.23). The price distance from 200 DMA is +15.60%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[324.5, 325.47, 326.45, 327.42, 328.39, 329.37]</t>
+          <t>[322.35, 323.32, 324.28, 325.25, 326.22, 327.19]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[324.5, 328.31, 330.46, 332.34, 334.07, 335.72]</t>
+          <t>[322.35, 326.16, 328.3, 330.17, 331.9, 333.54]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[324.5, 323.34, 323.43, 323.73, 324.13, 324.6]</t>
+          <t>[322.35, 321.19, 321.27, 321.56, 321.96, 322.42]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>302.74</v>
+        <v>300.73</v>
       </c>
     </row>
     <row r="4">
@@ -995,16 +995,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>59357.82</v>
+        <v>30027.94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,146 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2137.8</v>
+        <v>545.9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹2125.63 - ₹2156.05</t>
+          <t>₹542.5 - ₹551.0</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2186.48</v>
+        <v>559.5</v>
       </c>
       <c r="I4" t="n">
-        <v>2120.19</v>
+        <v>520.59</v>
       </c>
       <c r="J4" t="n">
-        <v>2003.6</v>
+        <v>524.61</v>
       </c>
       <c r="K4" t="n">
-        <v>1954.83</v>
+        <v>523.61</v>
       </c>
       <c r="L4" t="n">
-        <v>8.41</v>
+        <v>3.7</v>
       </c>
       <c r="M4" t="n">
-        <v>40.46</v>
+        <v>10.74</v>
       </c>
       <c r="N4" t="n">
-        <v>59.08</v>
+        <v>9.94</v>
       </c>
       <c r="O4" t="n">
-        <v>-18.62</v>
+        <v>0.8</v>
       </c>
       <c r="P4" t="n">
-        <v>60.85</v>
+        <v>17</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.59</v>
+        <v>12.29</v>
       </c>
       <c r="R4" t="n">
-        <v>46.1</v>
+        <v>46.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.75</v>
+        <v>-1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>51.7</v>
+        <v>46.7</v>
       </c>
       <c r="V4" t="n">
-        <v>2.83</v>
+        <v>4.87</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2095.17</v>
+        <v>526.17</v>
       </c>
       <c r="Y4" t="n">
-        <v>2093.19</v>
+        <v>525.98</v>
       </c>
       <c r="Z4" t="n">
-        <v>1995.45</v>
+        <v>520.29</v>
       </c>
       <c r="AA4" t="n">
-        <v>2046.53</v>
+        <v>520.4</v>
       </c>
       <c r="AB4" t="n">
-        <v>2132.1</v>
+        <v>547.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>2154.2</v>
+        <v>553.29</v>
       </c>
       <c r="AD4" t="n">
-        <v>2170.6</v>
+        <v>560.67</v>
       </c>
       <c r="AE4" t="n">
-        <v>46.9</v>
+        <v>60.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.59) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>48.3</v>
+        <v>5.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>5.2</v>
+        <v>65.2</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>2201.91</v>
+        <v>559.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>2082.77</v>
+        <v>531.79</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹59,357.82 Cr., a P/E ratio of 48.27, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,027.94 Cr., a P/E ratio of 5.23, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.85 (Consolidation Zone), while MACD Line (40.46) trades below Signal (59.08) with an expanding histogram (-18.62). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.41% above the 200-day DMA (₹1954.83). Daily volatility envelope is bounded by ATR(14) of ₹60.85.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.36 (Bullish Momentum Zone), while MACD Line (10.74) trades above Signal (9.94) with an expanding histogram (+0.80). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.70% above the 200-day DMA (₹523.61). Daily volatility envelope is bounded by ATR(14) of ₹17.00.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,137.80) is positioned above the 30-day DMA (₹2,120.19), 50-day DMA (₹2,003.60), and 200-day DMA (₹1,954.83). The price distance from 200 DMA is +8.41%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹545.90) is positioned above the 30-day DMA (₹520.59), 50-day DMA (₹524.61), and 200-day DMA (₹523.61). The price distance from 200 DMA is +3.70%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[2137.8, 2156.01, 2174.23, 2192.44, 2210.66, 2228.87]</t>
+          <t>[545.9, 547.54, 549.18, 550.81, 552.45, 554.09]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[2137.8, 2180.35, 2208.65, 2234.6, 2259.34, 2283.3]</t>
+          <t>[545.9, 554.34, 558.79, 562.59, 566.05, 569.29]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[2137.8, 2137.76, 2148.41, 2160.83, 2174.15, 2188.06]</t>
+          <t>[545.9, 542.44, 541.96, 541.98, 542.25, 542.68]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1995.45</v>
+        <v>520.29</v>
       </c>
     </row>
     <row r="5">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29994.93</v>
+        <v>59616.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,146 +1179,146 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>545.3</v>
+        <v>988.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹541.9 - ₹550.4</t>
+          <t>₹983.1 - ₹997.1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>558.9</v>
+        <v>1011.09</v>
       </c>
       <c r="I5" t="n">
-        <v>520.59</v>
+        <v>980.86</v>
       </c>
       <c r="J5" t="n">
-        <v>524.61</v>
+        <v>955.17</v>
       </c>
       <c r="K5" t="n">
-        <v>523.61</v>
+        <v>850.98</v>
       </c>
       <c r="L5" t="n">
-        <v>3.7</v>
+        <v>14.75</v>
       </c>
       <c r="M5" t="n">
-        <v>10.74</v>
+        <v>16.58</v>
       </c>
       <c r="N5" t="n">
-        <v>9.94</v>
+        <v>25.36</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>17</v>
+        <v>27.99</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.59</v>
+        <v>12.29</v>
       </c>
       <c r="R5" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.99</v>
+        <v>-1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>46.7</v>
+        <v>52.5</v>
       </c>
       <c r="V5" t="n">
-        <v>4.87</v>
+        <v>3.51</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>525.5599999999999</v>
+        <v>968.92</v>
       </c>
       <c r="Y5" t="n">
-        <v>525.37</v>
+        <v>968</v>
       </c>
       <c r="Z5" t="n">
-        <v>519.71</v>
+        <v>903.71</v>
       </c>
       <c r="AA5" t="n">
-        <v>519.8</v>
+        <v>946.71</v>
       </c>
       <c r="AB5" t="n">
-        <v>545.42</v>
+        <v>990</v>
       </c>
       <c r="AC5" t="n">
-        <v>549.79</v>
+        <v>1003.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>554.27</v>
+        <v>1018.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>60.4</v>
+        <v>33.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.59) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.2</v>
+        <v>30.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14.5</v>
+        <v>23.9</v>
       </c>
       <c r="AK5" t="n">
-        <v>65.2</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>559.0599999999999</v>
+        <v>1028.68</v>
       </c>
       <c r="AN5" t="n">
-        <v>531.45</v>
+        <v>950.78</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹29,994.93 Cr., a P/E ratio of 5.22, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹59,616.36 Cr., a P/E ratio of 30.69, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.36 (Bullish Momentum Zone), while MACD Line (10.74) trades above Signal (9.94) with an expanding histogram (+0.80). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.70% above the 200-day DMA (₹523.61). Daily volatility envelope is bounded by ATR(14) of ₹17.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.06 (Consolidation Zone), while MACD Line (16.58) trades below Signal (25.36) with an expanding histogram (-8.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.75% above the 200-day DMA (₹850.98). Daily volatility envelope is bounded by ATR(14) of ₹27.99.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹545.30) is positioned above the 30-day DMA (₹520.59), 50-day DMA (₹524.61), and 200-day DMA (₹523.61). The price distance from 200 DMA is +3.70%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹988.70) is positioned above the 30-day DMA (₹980.86), 50-day DMA (₹955.17), and 200-day DMA (₹850.98). The price distance from 200 DMA is +14.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[545.3, 546.94, 548.57, 550.21, 551.84, 553.48]</t>
+          <t>[988.7, 997.06, 1005.42, 1013.78, 1022.14, 1030.5]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[545.3, 553.74, 558.19, 561.99, 565.44, 568.68]</t>
+          <t>[988.7, 1008.26, 1021.25, 1033.17, 1044.53, 1055.53]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[545.3, 541.84, 541.36, 541.37, 541.64, 542.08]</t>
+          <t>[988.7, 988.66, 993.54, 999.23, 1005.34, 1011.72]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>519.71</v>
+        <v>903.71</v>
       </c>
     </row>
     <row r="6">
@@ -1329,16 +1329,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>59905.79</v>
+        <v>59654.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,146 +1346,146 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>993.5</v>
+        <v>2148.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹987.9 - ₹1001.9</t>
+          <t>₹2136.16 - ₹2167.0</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1015.89</v>
+        <v>2197.84</v>
       </c>
       <c r="I6" t="n">
-        <v>980.86</v>
+        <v>2126.16</v>
       </c>
       <c r="J6" t="n">
-        <v>955.17</v>
+        <v>2009.95</v>
       </c>
       <c r="K6" t="n">
-        <v>850.98</v>
+        <v>1956.8</v>
       </c>
       <c r="L6" t="n">
-        <v>14.75</v>
+        <v>8.34</v>
       </c>
       <c r="M6" t="n">
-        <v>16.58</v>
+        <v>33.95</v>
       </c>
       <c r="N6" t="n">
-        <v>25.36</v>
+        <v>54.05</v>
       </c>
       <c r="O6" t="n">
-        <v>-8.779999999999999</v>
+        <v>-20.1</v>
       </c>
       <c r="P6" t="n">
-        <v>27.99</v>
+        <v>61.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.59</v>
+        <v>12.29</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.71</v>
+        <v>-1.8</v>
       </c>
       <c r="U6" t="n">
         <v>52.5</v>
       </c>
       <c r="V6" t="n">
-        <v>3.51</v>
+        <v>2.82</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>974.27</v>
+        <v>2068.96</v>
       </c>
       <c r="Y6" t="n">
-        <v>973.3200000000001</v>
+        <v>2068.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>908.6799999999999</v>
+        <v>2004.41</v>
       </c>
       <c r="AA6" t="n">
-        <v>951.51</v>
+        <v>2055.99</v>
       </c>
       <c r="AB6" t="n">
-        <v>991.6</v>
+        <v>2142.83</v>
       </c>
       <c r="AC6" t="n">
-        <v>1006.7</v>
+        <v>2175.66</v>
       </c>
       <c r="AD6" t="n">
-        <v>1019.9</v>
+        <v>2202.83</v>
       </c>
       <c r="AE6" t="n">
-        <v>33.1</v>
+        <v>43.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.59) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>31.3</v>
+        <v>48.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23.9</v>
+        <v>8.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>5.2</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>1032.83</v>
+        <v>2211.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>956.79</v>
+        <v>2090.01</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹59,905.79 Cr., a P/E ratio of 31.30, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹59,654.90 Cr., a P/E ratio of 48.49, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.06 (Consolidation Zone), while MACD Line (16.58) trades below Signal (25.36) with an expanding histogram (-8.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.75% above the 200-day DMA (₹850.98). Daily volatility envelope is bounded by ATR(14) of ₹27.99.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.67 (Consolidation Zone), while MACD Line (33.95) trades below Signal (54.05) with an expanding histogram (-20.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.34% above the 200-day DMA (₹1956.80). Daily volatility envelope is bounded by ATR(14) of ₹61.68.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹993.50) is positioned above the 30-day DMA (₹980.86), 50-day DMA (₹955.17), and 200-day DMA (₹850.98). The price distance from 200 DMA is +14.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,148.50) is positioned above the 30-day DMA (₹2,126.16), 50-day DMA (₹2,009.95), and 200-day DMA (₹1,956.80). The price distance from 200 DMA is +8.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[993.5, 1002.55, 1011.6, 1020.65, 1029.69, 1038.74]</t>
+          <t>[2148.5, 2154.95, 2161.39, 2167.84, 2174.28, 2180.73]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[993.5, 1013.75, 1027.43, 1040.04, 1052.09, 1063.78]</t>
+          <t>[2148.5, 2179.62, 2196.28, 2210.57, 2223.62, 2235.89]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[993.5, 994.15, 999.72, 1006.1, 1012.9, 1019.97]</t>
+          <t>[2148.5, 2136.44, 2135.22, 2135.79, 2137.28, 2139.35]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>908.6799999999999</v>
+        <v>2004.41</v>
       </c>
     </row>
     <row r="7">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>134858.19</v>
+        <v>414319.88</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,146 +1513,146 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>117.34</v>
+        <v>416.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹116.92 - ₹117.97</t>
+          <t>₹415.26 - ₹418.37</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>119.02</v>
+        <v>421.47</v>
       </c>
       <c r="I7" t="n">
-        <v>116.17</v>
+        <v>407.73</v>
       </c>
       <c r="J7" t="n">
-        <v>113.53</v>
+        <v>398.88</v>
       </c>
       <c r="K7" t="n">
-        <v>112.33</v>
+        <v>399.84</v>
       </c>
       <c r="L7" t="n">
-        <v>3.98</v>
+        <v>3.79</v>
       </c>
       <c r="M7" t="n">
-        <v>0.61</v>
+        <v>4.81</v>
       </c>
       <c r="N7" t="n">
-        <v>0.83</v>
+        <v>6.39</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.22</v>
+        <v>-1.58</v>
       </c>
       <c r="P7" t="n">
-        <v>2.11</v>
+        <v>6.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.59</v>
+        <v>12.29</v>
       </c>
       <c r="R7" t="n">
-        <v>44.3</v>
+        <v>47.7</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.04</v>
+        <v>-0.79</v>
       </c>
       <c r="U7" t="n">
-        <v>52.5</v>
+        <v>50.8</v>
       </c>
       <c r="V7" t="n">
-        <v>2.65</v>
+        <v>3.63</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>113.41</v>
+        <v>407.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>113.35</v>
+        <v>410.88</v>
       </c>
       <c r="Z7" t="n">
-        <v>111.24</v>
+        <v>410.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>114.18</v>
+        <v>407.17</v>
       </c>
       <c r="AB7" t="n">
-        <v>117.74</v>
+        <v>415.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>118.99</v>
+        <v>418.56</v>
       </c>
       <c r="AD7" t="n">
-        <v>120.65</v>
+        <v>420.63</v>
       </c>
       <c r="AE7" t="n">
-        <v>55.4</v>
+        <v>40.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.59) | LSTM Deep Net</t>
+          <t>Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>6</v>
+        <v>20.4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-6.4</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
-        <v>38.1</v>
+        <v>28.5</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>120.41</v>
+        <v>425.62</v>
       </c>
       <c r="AN7" t="n">
-        <v>114.02</v>
+        <v>407.32</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,858.19 Cr., a P/E ratio of 5.99, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹414,319.88 Cr., a P/E ratio of 20.40, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.39 (Bullish Momentum Zone), while MACD Line (0.61) trades below Signal (0.83) with an expanding histogram (-0.22). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.98% above the 200-day DMA (₹112.33). Daily volatility envelope is bounded by ATR(14) of ₹2.11.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 40.32 (Consolidation Zone), while MACD Line (4.81) trades below Signal (6.39) with an expanding histogram (-1.58). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.79% above the 200-day DMA (₹399.84). Daily volatility envelope is bounded by ATR(14) of ₹6.22.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.34) is positioned above the 30-day DMA (₹116.17), 50-day DMA (₹113.53), and 200-day DMA (₹112.33). The price distance from 200 DMA is +3.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹416.50) is positioned above the 30-day DMA (₹407.73), 50-day DMA (₹398.88), and 200-day DMA (₹399.84). The price distance from 200 DMA is +3.79%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[117.34, 117.69, 118.04, 118.4, 118.75, 119.1]</t>
+          <t>[416.5, 419.03, 421.57, 424.1, 426.63, 429.17]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[117.34, 118.53, 119.23, 119.85, 120.43, 120.98]</t>
+          <t>[416.5, 421.52, 425.08, 428.41, 431.61, 434.73]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[117.34, 117.06, 117.15, 117.3, 117.49, 117.69]</t>
+          <t>[416.5, 417.17, 418.93, 420.87, 422.9, 425.0]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>111.24</v>
+        <v>410.88</v>
       </c>
     </row>
     <row r="8">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>411285.85</v>
+        <v>133858.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1680,146 +1680,146 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>413.45</v>
+        <v>116.47</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹412.21 - ₹415.32</t>
+          <t>₹116.05 - ₹117.1</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>418.42</v>
+        <v>118.15</v>
       </c>
       <c r="I8" t="n">
-        <v>407.73</v>
+        <v>116.17</v>
       </c>
       <c r="J8" t="n">
-        <v>398.88</v>
+        <v>113.53</v>
       </c>
       <c r="K8" t="n">
-        <v>399.84</v>
+        <v>112.33</v>
       </c>
       <c r="L8" t="n">
-        <v>3.79</v>
+        <v>3.98</v>
       </c>
       <c r="M8" t="n">
-        <v>4.81</v>
+        <v>0.61</v>
       </c>
       <c r="N8" t="n">
-        <v>6.39</v>
+        <v>0.83</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.58</v>
+        <v>-0.22</v>
       </c>
       <c r="P8" t="n">
-        <v>6.22</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.59</v>
+        <v>12.29</v>
       </c>
       <c r="R8" t="n">
-        <v>42.7</v>
+        <v>38.7</v>
       </c>
       <c r="S8" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.95</v>
+        <v>-1.25</v>
       </c>
       <c r="U8" t="n">
-        <v>49.2</v>
+        <v>50.8</v>
       </c>
       <c r="V8" t="n">
-        <v>3.63</v>
+        <v>2.65</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>403.86</v>
+        <v>112.46</v>
       </c>
       <c r="Y8" t="n">
-        <v>407.87</v>
+        <v>112.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>407.87</v>
+        <v>110.41</v>
       </c>
       <c r="AA8" t="n">
-        <v>404.12</v>
+        <v>113.31</v>
       </c>
       <c r="AB8" t="n">
-        <v>414.52</v>
+        <v>117.41</v>
       </c>
       <c r="AC8" t="n">
-        <v>416.54</v>
+        <v>118.46</v>
       </c>
       <c r="AD8" t="n">
-        <v>419.62</v>
+        <v>120.45</v>
       </c>
       <c r="AE8" t="n">
-        <v>40.3</v>
+        <v>55.4</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Low VIX (12.59) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>20</v>
+        <v>5.9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>21</v>
+        <v>-6.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>28.5</v>
+        <v>38.1</v>
       </c>
       <c r="AL8" t="n">
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>422.4</v>
+        <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>404.73</v>
+        <v>113.21</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹411,285.85 Cr., a P/E ratio of 20.00, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹133,858.30 Cr., a P/E ratio of 5.95, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 40.32 (Consolidation Zone), while MACD Line (4.81) trades below Signal (6.39) with an expanding histogram (-1.58). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.79% above the 200-day DMA (₹399.84). Daily volatility envelope is bounded by ATR(14) of ₹6.22.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.39 (Bullish Momentum Zone), while MACD Line (0.61) trades below Signal (0.83) with an expanding histogram (-0.22). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.98% above the 200-day DMA (₹112.33). Daily volatility envelope is bounded by ATR(14) of ₹2.11.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹413.45) is positioned above the 30-day DMA (₹407.73), 50-day DMA (₹398.88), and 200-day DMA (₹399.84). The price distance from 200 DMA is +3.79%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.47) is positioned above the 30-day DMA (₹116.17), 50-day DMA (₹113.53), and 200-day DMA (₹112.33). The price distance from 200 DMA is +3.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[413.45, 415.61, 417.78, 419.94, 422.1, 424.27]</t>
+          <t>[116.47, 116.82, 117.17, 117.52, 117.87, 118.22]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[413.45, 418.1, 421.29, 424.25, 427.08, 429.83]</t>
+          <t>[116.47, 117.66, 118.36, 118.98, 119.55, 120.1]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[413.45, 413.75, 415.14, 416.71, 418.37, 420.1]</t>
+          <t>[116.47, 116.19, 116.28, 116.42, 116.6, 116.8]</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>407.87</v>
+        <v>110.41</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU8"/>
+  <dimension ref="A1:AU4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>83103.94</v>
+        <v>296735.87</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3265.2</v>
+        <v>322.35</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹3244.45 - ₹3296.33</t>
+          <t>₹320.93 - ₹324.48</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3348.21</v>
+        <v>328.03</v>
       </c>
       <c r="I2" t="n">
-        <v>3137.32</v>
+        <v>321.54</v>
       </c>
       <c r="J2" t="n">
-        <v>2981.04</v>
+        <v>310.62</v>
       </c>
       <c r="K2" t="n">
-        <v>2689.42</v>
+        <v>274.23</v>
       </c>
       <c r="L2" t="n">
-        <v>19.4</v>
+        <v>15.6</v>
       </c>
       <c r="M2" t="n">
-        <v>74.77</v>
+        <v>2.3</v>
       </c>
       <c r="N2" t="n">
-        <v>102.69</v>
+        <v>4.59</v>
       </c>
       <c r="O2" t="n">
-        <v>-27.92</v>
+        <v>-2.28</v>
       </c>
       <c r="P2" t="n">
-        <v>103.76</v>
+        <v>7.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.29</v>
+        <v>13.17</v>
       </c>
       <c r="R2" t="n">
-        <v>47.7</v>
+        <v>47.3</v>
       </c>
       <c r="S2" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.67</v>
+        <v>-1.24</v>
       </c>
       <c r="U2" t="n">
-        <v>52.5</v>
+        <v>51.7</v>
       </c>
       <c r="V2" t="n">
-        <v>3.39</v>
+        <v>2.51</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>3215.78</v>
+        <v>319.22</v>
       </c>
       <c r="Y2" t="n">
-        <v>3212.2</v>
+        <v>342.51</v>
       </c>
       <c r="Z2" t="n">
-        <v>2542.81</v>
+        <v>342.51</v>
       </c>
       <c r="AA2" t="n">
-        <v>3109.55</v>
+        <v>311.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>3249.77</v>
+        <v>322.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3319.44</v>
+        <v>327.35</v>
       </c>
       <c r="AD2" t="n">
-        <v>3373.67</v>
+        <v>332.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>46.5</v>
+        <v>27.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.17) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>53.2</v>
+        <v>671.6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>85.3</v>
+        <v>182</v>
       </c>
       <c r="AK2" t="n">
-        <v>55.6</v>
+        <v>0.6</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>3400.92</v>
+        <v>333.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>3142.07</v>
+        <v>312.03</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹83,103.94 Cr., a P/E ratio of 53.24, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹296,735.87 Cr., a P/E ratio of 671.56, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.45 (Consolidation Zone), while MACD Line (74.77) trades below Signal (102.69) with an expanding histogram (-27.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.40% above the 200-day DMA (₹2689.42). Daily volatility envelope is bounded by ATR(14) of ₹103.76.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 27.78 (Consolidation Zone), while MACD Line (2.30) trades below Signal (4.59) with an expanding histogram (-2.28). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.60% above the 200-day DMA (₹274.23). Daily volatility envelope is bounded by ATR(14) of ₹7.10.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,265.20) is positioned above the 30-day DMA (₹3,137.32), 50-day DMA (₹2,981.04), and 200-day DMA (₹2,689.42). The price distance from 200 DMA is +19.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹322.35) is positioned above the 30-day DMA (₹321.54), 50-day DMA (₹310.62), and 200-day DMA (₹274.23). The price distance from 200 DMA is +15.60%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[3265.2, 3308.92, 3352.65, 3396.37, 3440.1, 3483.82]</t>
+          <t>[322.35, 323.32, 324.28, 325.25, 326.22, 327.19]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[3265.2, 3350.43, 3411.35, 3468.26, 3523.11, 3576.63]</t>
+          <t>[322.35, 326.16, 328.3, 330.17, 331.9, 333.54]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[3265.2, 3277.79, 3308.62, 3342.45, 3377.84, 3414.21]</t>
+          <t>[322.35, 321.19, 321.27, 321.56, 321.96, 322.42]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2542.81</v>
+        <v>342.51</v>
       </c>
     </row>
     <row r="3">
@@ -828,163 +828,163 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>296735.87</v>
+        <v>414319.88</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>322.35</v>
+        <v>416.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹320.93 - ₹324.48</t>
+          <t>₹415.26 - ₹418.37</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>328.03</v>
+        <v>421.47</v>
       </c>
       <c r="I3" t="n">
-        <v>321.54</v>
+        <v>407.73</v>
       </c>
       <c r="J3" t="n">
-        <v>310.62</v>
+        <v>398.88</v>
       </c>
       <c r="K3" t="n">
-        <v>274.23</v>
+        <v>399.84</v>
       </c>
       <c r="L3" t="n">
-        <v>15.6</v>
+        <v>3.79</v>
       </c>
       <c r="M3" t="n">
-        <v>2.3</v>
+        <v>4.81</v>
       </c>
       <c r="N3" t="n">
-        <v>4.59</v>
+        <v>6.39</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.28</v>
+        <v>-1.58</v>
       </c>
       <c r="P3" t="n">
-        <v>7.1</v>
+        <v>6.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.29</v>
+        <v>13.17</v>
       </c>
       <c r="R3" t="n">
         <v>47.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.24</v>
+        <v>-0.8</v>
       </c>
       <c r="U3" t="n">
-        <v>51.7</v>
+        <v>50.8</v>
       </c>
       <c r="V3" t="n">
-        <v>2.51</v>
+        <v>3.63</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>313.71</v>
+        <v>414.35</v>
       </c>
       <c r="Y3" t="n">
-        <v>313.49</v>
+        <v>433.69</v>
       </c>
       <c r="Z3" t="n">
-        <v>300.73</v>
+        <v>424.04</v>
       </c>
       <c r="AA3" t="n">
-        <v>311.7</v>
+        <v>407.17</v>
       </c>
       <c r="AB3" t="n">
-        <v>322.8</v>
+        <v>415.53</v>
       </c>
       <c r="AC3" t="n">
-        <v>327.35</v>
+        <v>418.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>332.35</v>
+        <v>420.63</v>
       </c>
       <c r="AE3" t="n">
-        <v>27.8</v>
+        <v>40.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.31</v>
+        <v>0.05</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Low VIX (13.17) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>671.6</v>
+        <v>20.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.6</v>
+        <v>28.5</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>333.22</v>
+        <v>425.94</v>
       </c>
       <c r="AN3" t="n">
-        <v>311.87</v>
+        <v>407.59</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹296,735.87 Cr., a P/E ratio of 671.56, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹414,319.88 Cr., a P/E ratio of 20.33, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 27.78 (Consolidation Zone), while MACD Line (2.30) trades below Signal (4.59) with an expanding histogram (-2.28). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.60% above the 200-day DMA (₹274.23). Daily volatility envelope is bounded by ATR(14) of ₹7.10.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 40.32 (Consolidation Zone), while MACD Line (4.81) trades below Signal (6.39) with an expanding histogram (-1.58). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.79% above the 200-day DMA (₹399.84). Daily volatility envelope is bounded by ATR(14) of ₹6.22.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹322.35) is positioned above the 30-day DMA (₹321.54), 50-day DMA (₹310.62), and 200-day DMA (₹274.23). The price distance from 200 DMA is +15.60%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹416.50) is positioned above the 30-day DMA (₹407.73), 50-day DMA (₹398.88), and 200-day DMA (₹399.84). The price distance from 200 DMA is +3.79%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[322.35, 323.32, 324.28, 325.25, 326.22, 327.19]</t>
+          <t>[416.5, 419.03, 421.57, 424.1, 426.63, 429.17]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[322.35, 326.16, 328.3, 330.17, 331.9, 333.54]</t>
+          <t>[416.5, 421.52, 425.08, 428.41, 431.61, 434.73]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[322.35, 321.19, 321.27, 321.56, 321.96, 322.42]</t>
+          <t>[416.5, 417.17, 418.93, 420.87, 422.9, 425.0]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>300.73</v>
+        <v>424.04</v>
       </c>
     </row>
     <row r="4">
@@ -995,7 +995,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1004,822 +1004,154 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30027.94</v>
+        <v>133858.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>545.9</v>
+        <v>116.47</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹542.5 - ₹551.0</t>
+          <t>₹116.05 - ₹117.1</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>559.5</v>
+        <v>118.15</v>
       </c>
       <c r="I4" t="n">
-        <v>520.59</v>
+        <v>116.17</v>
       </c>
       <c r="J4" t="n">
-        <v>524.61</v>
+        <v>113.53</v>
       </c>
       <c r="K4" t="n">
-        <v>523.61</v>
+        <v>112.33</v>
       </c>
       <c r="L4" t="n">
-        <v>3.7</v>
+        <v>3.98</v>
       </c>
       <c r="M4" t="n">
-        <v>10.74</v>
+        <v>0.61</v>
       </c>
       <c r="N4" t="n">
-        <v>9.94</v>
+        <v>0.83</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8</v>
+        <v>-0.22</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>2.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.29</v>
+        <v>13.17</v>
       </c>
       <c r="R4" t="n">
-        <v>46.4</v>
+        <v>38.5</v>
       </c>
       <c r="S4" t="n">
-        <v>0.17</v>
+        <v>0.3</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.97</v>
+        <v>-1.25</v>
       </c>
       <c r="U4" t="n">
-        <v>46.7</v>
+        <v>50.8</v>
       </c>
       <c r="V4" t="n">
-        <v>4.87</v>
+        <v>2.65</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>526.17</v>
+        <v>114.43</v>
       </c>
       <c r="Y4" t="n">
-        <v>525.98</v>
+        <v>124.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>520.29</v>
+        <v>124.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>520.4</v>
+        <v>113.31</v>
       </c>
       <c r="AB4" t="n">
-        <v>547.17</v>
+        <v>117.41</v>
       </c>
       <c r="AC4" t="n">
-        <v>553.29</v>
+        <v>118.46</v>
       </c>
       <c r="AD4" t="n">
-        <v>560.67</v>
+        <v>120.45</v>
       </c>
       <c r="AE4" t="n">
-        <v>60.4</v>
+        <v>55.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.24</v>
+        <v>-0.1</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (13.17) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>14.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AK4" t="n">
-        <v>65.2</v>
+        <v>38.1</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>559.26</v>
+        <v>119.69</v>
       </c>
       <c r="AN4" t="n">
-        <v>531.79</v>
+        <v>113.42</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,027.94 Cr., a P/E ratio of 5.23, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹133,858.30 Cr., a P/E ratio of 6.08, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.36 (Bullish Momentum Zone), while MACD Line (10.74) trades above Signal (9.94) with an expanding histogram (+0.80). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.70% above the 200-day DMA (₹523.61). Daily volatility envelope is bounded by ATR(14) of ₹17.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.39 (Bullish Momentum Zone), while MACD Line (0.61) trades below Signal (0.83) with an expanding histogram (-0.22). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.98% above the 200-day DMA (₹112.33). Daily volatility envelope is bounded by ATR(14) of ₹2.11.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹545.90) is positioned above the 30-day DMA (₹520.59), 50-day DMA (₹524.61), and 200-day DMA (₹523.61). The price distance from 200 DMA is +3.70%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.47) is positioned above the 30-day DMA (₹116.17), 50-day DMA (₹113.53), and 200-day DMA (₹112.33). The price distance from 200 DMA is +3.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[545.9, 547.54, 549.18, 550.81, 552.45, 554.09]</t>
+          <t>[116.47, 116.82, 117.17, 117.52, 117.87, 118.22]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[545.9, 554.34, 558.79, 562.59, 566.05, 569.29]</t>
+          <t>[116.47, 117.66, 118.36, 118.98, 119.55, 120.1]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[545.9, 542.44, 541.96, 541.98, 542.25, 542.68]</t>
+          <t>[116.47, 116.19, 116.28, 116.42, 116.6, 116.8]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>520.29</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>59616.36</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>988.7</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>₹983.1 - ₹997.1</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1011.09</v>
-      </c>
-      <c r="I5" t="n">
-        <v>980.86</v>
-      </c>
-      <c r="J5" t="n">
-        <v>955.17</v>
-      </c>
-      <c r="K5" t="n">
-        <v>850.98</v>
-      </c>
-      <c r="L5" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="M5" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="N5" t="n">
-        <v>25.36</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-8.779999999999999</v>
-      </c>
-      <c r="P5" t="n">
-        <v>27.99</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="R5" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-1.74</v>
-      </c>
-      <c r="U5" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X5" t="n">
-        <v>968.92</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>968</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>903.71</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>946.71</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>990</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1003.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1018.3</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1028.68</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>950.78</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹59,616.36 Cr., a P/E ratio of 30.69, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.06 (Consolidation Zone), while MACD Line (16.58) trades below Signal (25.36) with an expanding histogram (-8.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.75% above the 200-day DMA (₹850.98). Daily volatility envelope is bounded by ATR(14) of ₹27.99.</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹988.70) is positioned above the 30-day DMA (₹980.86), 50-day DMA (₹955.17), and 200-day DMA (₹850.98). The price distance from 200 DMA is +14.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>[988.7, 997.06, 1005.42, 1013.78, 1022.14, 1030.5]</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>[988.7, 1008.26, 1021.25, 1033.17, 1044.53, 1055.53]</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>[988.7, 988.66, 993.54, 999.23, 1005.34, 1011.72]</t>
-        </is>
-      </c>
-      <c r="AU5" t="n">
-        <v>903.71</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>59654.9</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2148.5</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>₹2136.16 - ₹2167.0</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>2197.84</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2126.16</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2009.95</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1956.8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8.34</v>
-      </c>
-      <c r="M6" t="n">
-        <v>33.95</v>
-      </c>
-      <c r="N6" t="n">
-        <v>54.05</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-20.1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>61.68</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="R6" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="U6" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2068.96</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2068.25</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2004.41</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2055.99</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2142.83</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2175.66</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2202.83</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>2211.92</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2090.01</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹59,654.90 Cr., a P/E ratio of 48.49, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.67 (Consolidation Zone), while MACD Line (33.95) trades below Signal (54.05) with an expanding histogram (-20.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.34% above the 200-day DMA (₹1956.80). Daily volatility envelope is bounded by ATR(14) of ₹61.68.</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,148.50) is positioned above the 30-day DMA (₹2,126.16), 50-day DMA (₹2,009.95), and 200-day DMA (₹1,956.80). The price distance from 200 DMA is +8.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>[2148.5, 2154.95, 2161.39, 2167.84, 2174.28, 2180.73]</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>[2148.5, 2179.62, 2196.28, 2210.57, 2223.62, 2235.89]</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>[2148.5, 2136.44, 2135.22, 2135.79, 2137.28, 2139.35]</t>
-        </is>
-      </c>
-      <c r="AU6" t="n">
-        <v>2004.41</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>414319.88</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>416.5</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>₹415.26 - ₹418.37</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>421.47</v>
-      </c>
-      <c r="I7" t="n">
-        <v>407.73</v>
-      </c>
-      <c r="J7" t="n">
-        <v>398.88</v>
-      </c>
-      <c r="K7" t="n">
-        <v>399.84</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="N7" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-1.58</v>
-      </c>
-      <c r="P7" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="R7" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="U7" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X7" t="n">
-        <v>407.2</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>410.88</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>410.88</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>407.17</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>415.53</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>418.56</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>420.63</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>Low VIX (12.29) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>425.62</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>407.32</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹414,319.88 Cr., a P/E ratio of 20.40, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 40.32 (Consolidation Zone), while MACD Line (4.81) trades below Signal (6.39) with an expanding histogram (-1.58). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.79% above the 200-day DMA (₹399.84). Daily volatility envelope is bounded by ATR(14) of ₹6.22.</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹416.50) is positioned above the 30-day DMA (₹407.73), 50-day DMA (₹398.88), and 200-day DMA (₹399.84). The price distance from 200 DMA is +3.79%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>[416.5, 419.03, 421.57, 424.1, 426.63, 429.17]</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>[416.5, 421.52, 425.08, 428.41, 431.61, 434.73]</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>[416.5, 417.17, 418.93, 420.87, 422.9, 425.0]</t>
-        </is>
-      </c>
-      <c r="AU7" t="n">
-        <v>410.88</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>133858.3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>116.47</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>₹116.05 - ₹117.1</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>118.15</v>
-      </c>
-      <c r="I8" t="n">
-        <v>116.17</v>
-      </c>
-      <c r="J8" t="n">
-        <v>113.53</v>
-      </c>
-      <c r="K8" t="n">
-        <v>112.33</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.22</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="R8" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="U8" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X8" t="n">
-        <v>112.46</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>112.41</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>110.41</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>113.31</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>117.41</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>118.46</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>120.45</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>113.21</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹133,858.30 Cr., a P/E ratio of 5.95, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.39 (Bullish Momentum Zone), while MACD Line (0.61) trades below Signal (0.83) with an expanding histogram (-0.22). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.98% above the 200-day DMA (₹112.33). Daily volatility envelope is bounded by ATR(14) of ₹2.11.</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.47) is positioned above the 30-day DMA (₹116.17), 50-day DMA (₹113.53), and 200-day DMA (₹112.33). The price distance from 200 DMA is +3.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>[116.47, 116.82, 117.17, 117.52, 117.87, 118.22]</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>[116.47, 117.66, 118.36, 118.98, 119.55, 120.1]</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>[116.47, 116.19, 116.28, 116.42, 116.6, 116.8]</t>
-        </is>
-      </c>
-      <c r="AU8" t="n">
-        <v>110.41</v>
+        <v>124.2</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU4"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,21 +656,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>296735.87</v>
+        <v>414867</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,324 +678,324 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>322.35</v>
+        <v>417.05</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹320.93 - ₹324.48</t>
+          <t>₹415.81 - ₹418.91</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>328.03</v>
+        <v>422.02</v>
       </c>
       <c r="I2" t="n">
-        <v>321.54</v>
+        <v>408.48</v>
       </c>
       <c r="J2" t="n">
-        <v>310.62</v>
+        <v>399.68</v>
       </c>
       <c r="K2" t="n">
-        <v>274.23</v>
+        <v>399.79</v>
       </c>
       <c r="L2" t="n">
-        <v>15.6</v>
+        <v>4.18</v>
       </c>
       <c r="M2" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="N2" t="n">
-        <v>4.59</v>
+        <v>6.01</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.28</v>
+        <v>-1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>7.1</v>
+        <v>6.21</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.17</v>
+        <v>11.89</v>
       </c>
       <c r="R2" t="n">
-        <v>47.3</v>
+        <v>49.3</v>
       </c>
       <c r="S2" t="n">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.24</v>
+        <v>-0.74</v>
       </c>
       <c r="U2" t="n">
-        <v>51.7</v>
+        <v>50.8</v>
       </c>
       <c r="V2" t="n">
-        <v>2.51</v>
+        <v>3.61</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>319.22</v>
+        <v>414.92</v>
       </c>
       <c r="Y2" t="n">
-        <v>342.51</v>
+        <v>434.24</v>
       </c>
       <c r="Z2" t="n">
-        <v>342.51</v>
+        <v>424.61</v>
       </c>
       <c r="AA2" t="n">
-        <v>311.7</v>
+        <v>407.73</v>
       </c>
       <c r="AB2" t="n">
-        <v>322.8</v>
+        <v>416.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>327.35</v>
+        <v>418.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>332.35</v>
+        <v>419.15</v>
       </c>
       <c r="AE2" t="n">
-        <v>27.8</v>
+        <v>42.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.31</v>
+        <v>0.06</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.17) | LSTM Deep Net</t>
+          <t>Low VIX (11.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>671.6</v>
+        <v>20.4</v>
       </c>
       <c r="AJ2" t="n">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.6</v>
+        <v>28.5</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>333.22</v>
+        <v>426.41</v>
       </c>
       <c r="AN2" t="n">
-        <v>312.03</v>
+        <v>408.12</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹296,735.87 Cr., a P/E ratio of 671.56, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹414,867.00 Cr., a P/E ratio of 20.35, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 27.78 (Consolidation Zone), while MACD Line (2.30) trades below Signal (4.59) with an expanding histogram (-2.28). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.60% above the 200-day DMA (₹274.23). Daily volatility envelope is bounded by ATR(14) of ₹7.10.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.58 (Consolidation Zone), while MACD Line (4.50) trades below Signal (6.01) with an expanding histogram (-1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹399.79). Daily volatility envelope is bounded by ATR(14) of ₹6.21.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹322.35) is positioned above the 30-day DMA (₹321.54), 50-day DMA (₹310.62), and 200-day DMA (₹274.23). The price distance from 200 DMA is +15.60%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹417.05) is positioned above the 30-day DMA (₹408.48), 50-day DMA (₹399.68), and 200-day DMA (₹399.79). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[322.35, 323.32, 324.28, 325.25, 326.22, 327.19]</t>
+          <t>[417.05, 419.62, 422.18, 424.75, 427.31, 429.88]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[322.35, 326.16, 328.3, 330.17, 331.9, 333.54]</t>
+          <t>[417.05, 422.1, 425.7, 429.05, 432.28, 435.44]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[322.35, 321.19, 321.27, 321.56, 321.96, 322.42]</t>
+          <t>[417.05, 417.75, 419.55, 421.52, 423.59, 425.71]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>342.51</v>
+        <v>424.61</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>414319.88</v>
+        <v>302351.15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>416.5</v>
+        <v>328.45</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹415.26 - ₹418.37</t>
+          <t>₹326.96 - ₹330.69</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>421.47</v>
+        <v>334.43</v>
       </c>
       <c r="I3" t="n">
-        <v>407.73</v>
+        <v>321.94</v>
       </c>
       <c r="J3" t="n">
-        <v>398.88</v>
+        <v>311.34</v>
       </c>
       <c r="K3" t="n">
-        <v>399.84</v>
+        <v>274.34</v>
       </c>
       <c r="L3" t="n">
-        <v>3.79</v>
+        <v>17.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4.81</v>
+        <v>2.21</v>
       </c>
       <c r="N3" t="n">
-        <v>6.39</v>
+        <v>4.11</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.58</v>
+        <v>-1.9</v>
       </c>
       <c r="P3" t="n">
-        <v>6.22</v>
+        <v>7.47</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.17</v>
+        <v>11.89</v>
       </c>
       <c r="R3" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0.36</v>
+        <v>0.23</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8</v>
+        <v>-1.27</v>
       </c>
       <c r="U3" t="n">
-        <v>50.8</v>
+        <v>53.3</v>
       </c>
       <c r="V3" t="n">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>414.35</v>
+        <v>324.26</v>
       </c>
       <c r="Y3" t="n">
-        <v>433.69</v>
+        <v>348.99</v>
       </c>
       <c r="Z3" t="n">
-        <v>424.04</v>
+        <v>348.99</v>
       </c>
       <c r="AA3" t="n">
-        <v>407.17</v>
+        <v>317.24</v>
       </c>
       <c r="AB3" t="n">
-        <v>415.53</v>
+        <v>327.97</v>
       </c>
       <c r="AC3" t="n">
-        <v>418.56</v>
+        <v>330.24</v>
       </c>
       <c r="AD3" t="n">
-        <v>420.63</v>
+        <v>332.02</v>
       </c>
       <c r="AE3" t="n">
-        <v>40.3</v>
+        <v>38.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Low VIX (13.17) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>20.3</v>
+        <v>684.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="AK3" t="n">
-        <v>28.5</v>
+        <v>0.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>425.94</v>
+        <v>340.46</v>
       </c>
       <c r="AN3" t="n">
-        <v>407.59</v>
+        <v>317.27</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹414,319.88 Cr., a P/E ratio of 20.33, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹302,351.15 Cr., a P/E ratio of 684.27, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 40.32 (Consolidation Zone), while MACD Line (4.81) trades below Signal (6.39) with an expanding histogram (-1.58). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.79% above the 200-day DMA (₹399.84). Daily volatility envelope is bounded by ATR(14) of ₹6.22.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 38.33 (Consolidation Zone), while MACD Line (2.21) trades below Signal (4.11) with an expanding histogram (-1.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.50% above the 200-day DMA (₹274.34). Daily volatility envelope is bounded by ATR(14) of ₹7.47.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹416.50) is positioned above the 30-day DMA (₹407.73), 50-day DMA (₹398.88), and 200-day DMA (₹399.84). The price distance from 200 DMA is +3.79%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹328.45) is positioned above the 30-day DMA (₹321.94), 50-day DMA (₹311.34), and 200-day DMA (₹274.34). The price distance from 200 DMA is +17.50%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[416.5, 419.03, 421.57, 424.1, 426.63, 429.17]</t>
+          <t>[328.45, 329.44, 330.42, 331.41, 332.39, 333.38]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[416.5, 421.52, 425.08, 428.41, 431.61, 434.73]</t>
+          <t>[328.45, 332.42, 334.65, 336.58, 338.37, 340.06]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[416.5, 417.17, 418.93, 420.87, 422.9, 425.0]</t>
+          <t>[328.45, 327.19, 327.25, 327.52, 327.91, 328.36]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>424.04</v>
+        <v>348.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1004,154 +1004,989 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>133858.3</v>
+        <v>83193.02</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>116.47</v>
+        <v>3268.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹116.05 - ₹117.1</t>
+          <t>₹3247.95 - ₹3299.83</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>118.15</v>
+        <v>3351.71</v>
       </c>
       <c r="I4" t="n">
-        <v>116.17</v>
+        <v>3137.32</v>
       </c>
       <c r="J4" t="n">
-        <v>113.53</v>
+        <v>2981.04</v>
       </c>
       <c r="K4" t="n">
-        <v>112.33</v>
+        <v>2689.42</v>
       </c>
       <c r="L4" t="n">
-        <v>3.98</v>
+        <v>19.4</v>
       </c>
       <c r="M4" t="n">
-        <v>0.61</v>
+        <v>74.77</v>
       </c>
       <c r="N4" t="n">
-        <v>0.83</v>
+        <v>102.69</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.22</v>
+        <v>-27.92</v>
       </c>
       <c r="P4" t="n">
-        <v>2.11</v>
+        <v>103.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.17</v>
+        <v>11.89</v>
       </c>
       <c r="R4" t="n">
-        <v>38.5</v>
+        <v>47.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.25</v>
+        <v>-1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>50.8</v>
+        <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>114.43</v>
+        <v>3268.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>124.2</v>
+        <v>4185.32</v>
       </c>
       <c r="Z4" t="n">
-        <v>124.2</v>
+        <v>4185.32</v>
       </c>
       <c r="AA4" t="n">
-        <v>113.31</v>
+        <v>3113.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>117.41</v>
+        <v>3271.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>118.46</v>
+        <v>3312.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>120.45</v>
+        <v>3356.03</v>
       </c>
       <c r="AE4" t="n">
-        <v>55.4</v>
+        <v>46.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (13.17) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.1</v>
+        <v>54.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-6.4</v>
+        <v>85.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>38.1</v>
+        <v>55.6</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>119.69</v>
+        <v>3392.34</v>
       </c>
       <c r="AN4" t="n">
-        <v>113.42</v>
+        <v>3142.13</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹133,858.30 Cr., a P/E ratio of 6.08, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹83,193.02 Cr., a P/E ratio of 54.14, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.39 (Bullish Momentum Zone), while MACD Line (0.61) trades below Signal (0.83) with an expanding histogram (-0.22). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.98% above the 200-day DMA (₹112.33). Daily volatility envelope is bounded by ATR(14) of ₹2.11.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.45 (Consolidation Zone), while MACD Line (74.77) trades below Signal (102.69) with an expanding histogram (-27.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.40% above the 200-day DMA (₹2689.42). Daily volatility envelope is bounded by ATR(14) of ₹103.76.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.47) is positioned above the 30-day DMA (₹116.17), 50-day DMA (₹113.53), and 200-day DMA (₹112.33). The price distance from 200 DMA is +3.98%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,268.70) is positioned above the 30-day DMA (₹3,137.32), 50-day DMA (₹2,981.04), and 200-day DMA (₹2,689.42). The price distance from 200 DMA is +19.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[116.47, 116.82, 117.17, 117.52, 117.87, 118.22]</t>
+          <t>[3268.7, 3314.19, 3359.69, 3405.18, 3450.68, 3496.17]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[116.47, 117.66, 118.36, 118.98, 119.55, 120.1]</t>
+          <t>[3268.7, 3355.7, 3418.39, 3477.07, 3533.69, 3588.98]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[116.47, 116.19, 116.28, 116.42, 116.6, 116.8]</t>
+          <t>[3268.7, 3283.06, 3315.66, 3351.26, 3388.42, 3426.56]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>124.2</v>
+        <v>4185.32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>60632.26</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2183.7</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>₹2171.36 - ₹2202.2</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2233.04</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2126.16</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2009.95</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1956.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.34</v>
+      </c>
+      <c r="M5" t="n">
+        <v>33.95</v>
+      </c>
+      <c r="N5" t="n">
+        <v>54.05</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-20.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>61.68</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="R5" t="n">
+        <v>47</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="U5" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>3</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2151.27</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2328.11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2328.11</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2091.19</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2176.33</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2206.36</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2229.03</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>TTM Squeeze | Low VIX (11.89) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2245.15</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2123.32</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,632.26 Cr., a P/E ratio of 49.28, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.67 (Consolidation Zone), while MACD Line (33.95) trades below Signal (54.05) with an expanding histogram (-20.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.34% above the 200-day DMA (₹1956.80). Daily volatility envelope is bounded by ATR(14) of ₹61.68.</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,183.70) is positioned above the 30-day DMA (₹2,126.16), 50-day DMA (₹2,009.95), and 200-day DMA (₹1,956.80). The price distance from 200 DMA is +8.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>[2183.7, 2190.25, 2196.8, 2203.35, 2209.9, 2216.46]</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>[2183.7, 2214.92, 2231.69, 2246.08, 2259.25, 2271.62]</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>[2183.7, 2171.75, 2170.64, 2171.31, 2172.9, 2175.08]</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>2328.11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>30115.95</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>547.5</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>₹544.1 - ₹552.6</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>561.1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>520.59</v>
+      </c>
+      <c r="J6" t="n">
+        <v>524.61</v>
+      </c>
+      <c r="K6" t="n">
+        <v>523.61</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9.94</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="R6" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="U6" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="V6" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X6" t="n">
+        <v>537.5700000000001</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>575.97</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>575.97</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>522</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>547.7</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>551.8</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>556.1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.89) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>561.59</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>533.38</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,115.95 Cr., a P/E ratio of 5.25, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.36 (Bullish Momentum Zone), while MACD Line (10.74) trades above Signal (9.94) with an expanding histogram (+0.80). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.70% above the 200-day DMA (₹523.61). Daily volatility envelope is bounded by ATR(14) of ₹17.00.</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹547.50) is positioned above the 30-day DMA (₹520.59), 50-day DMA (₹524.61), and 200-day DMA (₹523.61). The price distance from 200 DMA is +3.70%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>[547.5, 549.14, 550.78, 552.43, 554.07, 555.71]</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>[547.5, 555.94, 560.4, 564.21, 567.67, 570.92]</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>[547.5, 544.04, 543.57, 543.59, 543.87, 544.31]</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>575.97</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>134524.9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>117.05</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>₹116.6 - ₹117.72</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>118.83</v>
+      </c>
+      <c r="I7" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="J7" t="n">
+        <v>113.79</v>
+      </c>
+      <c r="K7" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="R7" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="U7" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X7" t="n">
+        <v>116.52</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>124.82</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>124.82</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>113.71</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>117.04</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>117.44</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>117.84</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>54</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>TTM Squeeze | Low VIX (11.89) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>120.21</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>113.89</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,524.90 Cr., a P/E ratio of 6.11, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.02 (Consolidation Zone), while MACD Line (0.59) trades below Signal (0.78) with an expanding histogram (-0.19). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.71% above the 200-day DMA (₹112.30). Daily volatility envelope is bounded by ATR(14) of ₹2.23.</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.05) is positioned above the 30-day DMA (₹116.25), 50-day DMA (₹113.79), and 200-day DMA (₹112.30). The price distance from 200 DMA is +3.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>[117.05, 117.83, 118.62, 119.4, 120.18, 120.97]</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>[117.05, 118.72, 119.88, 120.94, 121.97, 122.96]</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>[117.05, 117.17, 117.67, 118.24, 118.85, 119.47]</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>124.82</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>60327.87</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1000.5</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>₹994.9 - ₹1008.9</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1022.89</v>
+      </c>
+      <c r="I8" t="n">
+        <v>980.86</v>
+      </c>
+      <c r="J8" t="n">
+        <v>955.17</v>
+      </c>
+      <c r="K8" t="n">
+        <v>850.98</v>
+      </c>
+      <c r="L8" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="M8" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="N8" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="P8" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="R8" t="n">
+        <v>45</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="U8" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X8" t="n">
+        <v>999.84</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1092.53</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1092.53</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>958.51</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>998.83</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1008.96</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1017.43</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Low VIX (11.89) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1039.68</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>963</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹60,327.87 Cr., a P/E ratio of 31.05, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.06 (Consolidation Zone), while MACD Line (16.58) trades below Signal (25.36) with an expanding histogram (-8.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.75% above the 200-day DMA (₹850.98). Daily volatility envelope is bounded by ATR(14) of ₹27.99.</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,000.50) is positioned above the 30-day DMA (₹980.86), 50-day DMA (₹955.17), and 200-day DMA (₹850.98). The price distance from 200 DMA is +14.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>[1000.5, 1011.09, 1021.68, 1032.27, 1042.86, 1053.44]</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>[1000.5, 1022.29, 1037.51, 1051.66, 1065.25, 1078.48]</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>[1000.5, 1002.69, 1009.8, 1017.72, 1026.06, 1034.67]</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>1092.53</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>106614.84</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>737</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>₹733.8 - ₹741.8</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>749.8099999999999</v>
+      </c>
+      <c r="I9" t="n">
+        <v>722.83</v>
+      </c>
+      <c r="J9" t="n">
+        <v>728.36</v>
+      </c>
+      <c r="K9" t="n">
+        <v>686</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="R9" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="U9" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X9" t="n">
+        <v>720.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>783.74</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>783.74</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>712.99</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>734.2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>745.8</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>754.6</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.89) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>754.67</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>719.05</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,614.84 Cr., a P/E ratio of 48.08, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.74 (Bullish Momentum Zone), while MACD Line (-2.09) trades below Signal (-2.08) with an expanding histogram (-0.00). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.93% above the 200-day DMA (₹686.00). Daily volatility envelope is bounded by ATR(14) of ₹16.01.</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹737.00) is positioned above the 30-day DMA (₹722.83), 50-day DMA (₹728.36), and 200-day DMA (₹686.00). The price distance from 200 DMA is +5.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>[737.0, 739.21, 741.42, 743.63, 745.84, 748.05]</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>[737.0, 745.61, 750.48, 754.72, 758.65, 762.37]</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>[737.0, 734.41, 734.63, 735.32, 736.24, 737.32]</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>783.74</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU9"/>
+  <dimension ref="A1:AU12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>414867</v>
+        <v>179474.08</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>417.05</v>
+        <v>2208.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹415.81 - ₹418.91</t>
+          <t>₹2197.33 - ₹2226.01</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>422.02</v>
+        <v>2254.68</v>
       </c>
       <c r="I2" t="n">
-        <v>408.48</v>
+        <v>2200.73</v>
       </c>
       <c r="J2" t="n">
-        <v>399.68</v>
+        <v>2129.15</v>
       </c>
       <c r="K2" t="n">
-        <v>399.79</v>
+        <v>2052.76</v>
       </c>
       <c r="L2" t="n">
-        <v>4.18</v>
+        <v>5.22</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>6.01</v>
+        <v>15.47</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.51</v>
+        <v>-11.86</v>
       </c>
       <c r="P2" t="n">
-        <v>6.21</v>
+        <v>57.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.89</v>
+        <v>11.39</v>
       </c>
       <c r="R2" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="S2" t="n">
-        <v>0.36</v>
+        <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.74</v>
+        <v>-1.43</v>
       </c>
       <c r="U2" t="n">
-        <v>50.8</v>
+        <v>51.8</v>
       </c>
       <c r="V2" t="n">
-        <v>3.61</v>
+        <v>4.4</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>414.92</v>
+        <v>2187.28</v>
       </c>
       <c r="Y2" t="n">
-        <v>434.24</v>
+        <v>2348.86</v>
       </c>
       <c r="Z2" t="n">
-        <v>424.61</v>
+        <v>2348.86</v>
       </c>
       <c r="AA2" t="n">
-        <v>407.73</v>
+        <v>2122.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>416.7</v>
+        <v>2191.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>418.1</v>
+        <v>2226.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>419.15</v>
+        <v>2244.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>42.6</v>
+        <v>33.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.06</v>
+        <v>-0.17</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Low VIX (11.89) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>20.4</v>
+        <v>36.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>-0.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>28.5</v>
+        <v>7</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>426.41</v>
+        <v>2270.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>408.12</v>
+        <v>2140.02</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹414,867.00 Cr., a P/E ratio of 20.35, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>HYUNDAI operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹179,474.08 Cr., a P/E ratio of 36.26, and YoY Revenue Growth of -0.5%, the company demonstrates strong institutional backing, solid operating profit margins (7.00%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.58 (Consolidation Zone), while MACD Line (4.50) trades below Signal (6.01) with an expanding histogram (-1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹399.79). Daily volatility envelope is bounded by ATR(14) of ₹6.21.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.70 (Consolidation Zone), while MACD Line (3.60) trades below Signal (15.47) with an expanding histogram (-11.86). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.22% above the 200-day DMA (₹2052.76). Daily volatility envelope is bounded by ATR(14) of ₹57.35.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹417.05) is positioned above the 30-day DMA (₹408.48), 50-day DMA (₹399.68), and 200-day DMA (₹399.79). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HYUNDAI. Current Market Price (₹2,208.80) is positioned above the 30-day DMA (₹2,200.73), 50-day DMA (₹2,129.15), and 200-day DMA (₹2,052.76). The price distance from 200 DMA is +5.22%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[417.05, 419.62, 422.18, 424.75, 427.31, 429.88]</t>
+          <t>[2208.8, 2215.43, 2222.05, 2228.68, 2235.31, 2241.93]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[417.05, 422.1, 425.7, 429.05, 432.28, 435.44]</t>
+          <t>[2208.8, 2238.37, 2254.49, 2268.41, 2281.19, 2293.23]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[417.05, 417.75, 419.55, 421.52, 423.59, 425.71]</t>
+          <t>[2208.8, 2198.22, 2197.72, 2198.88, 2200.9, 2203.46]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>424.61</v>
+        <v>2348.86</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>302351.15</v>
+        <v>25000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>328.45</v>
+        <v>3260</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹326.96 - ₹330.69</t>
+          <t>₹3239.25 - ₹3291.13</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>334.43</v>
+        <v>3343.01</v>
       </c>
       <c r="I3" t="n">
-        <v>321.94</v>
+        <v>3137.32</v>
       </c>
       <c r="J3" t="n">
-        <v>311.34</v>
+        <v>2981.04</v>
       </c>
       <c r="K3" t="n">
-        <v>274.34</v>
+        <v>2689.42</v>
       </c>
       <c r="L3" t="n">
-        <v>17.5</v>
+        <v>19.4</v>
       </c>
       <c r="M3" t="n">
-        <v>2.21</v>
+        <v>74.77</v>
       </c>
       <c r="N3" t="n">
-        <v>4.11</v>
+        <v>102.69</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9</v>
+        <v>-27.92</v>
       </c>
       <c r="P3" t="n">
-        <v>7.47</v>
+        <v>103.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.89</v>
+        <v>11.39</v>
       </c>
       <c r="R3" t="n">
-        <v>47.8</v>
+        <v>48.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.27</v>
+        <v>-1.63</v>
       </c>
       <c r="U3" t="n">
         <v>53.3</v>
       </c>
       <c r="V3" t="n">
-        <v>2.55</v>
+        <v>3.39</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>324.26</v>
+        <v>3260</v>
       </c>
       <c r="Y3" t="n">
-        <v>348.99</v>
+        <v>4172</v>
       </c>
       <c r="Z3" t="n">
-        <v>348.99</v>
+        <v>4172</v>
       </c>
       <c r="AA3" t="n">
-        <v>317.24</v>
+        <v>3104.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>327.97</v>
+        <v>3268.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>330.24</v>
+        <v>3306.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>332.02</v>
+        <v>3353.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>38.3</v>
+        <v>46.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.89) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>684.3</v>
+        <v>54</v>
       </c>
       <c r="AJ3" t="n">
-        <v>182</v>
+        <v>85.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.6</v>
+        <v>55.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>340.46</v>
+        <v>3393.55</v>
       </c>
       <c r="AN3" t="n">
-        <v>317.27</v>
+        <v>3137.57</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹302,351.15 Cr., a P/E ratio of 684.27, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.96, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 38.33 (Consolidation Zone), while MACD Line (2.21) trades below Signal (4.11) with an expanding histogram (-1.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.50% above the 200-day DMA (₹274.34). Daily volatility envelope is bounded by ATR(14) of ₹7.47.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.45 (Consolidation Zone), while MACD Line (74.77) trades below Signal (102.69) with an expanding histogram (-27.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.40% above the 200-day DMA (₹2689.42). Daily volatility envelope is bounded by ATR(14) of ₹103.76.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹328.45) is positioned above the 30-day DMA (₹321.94), 50-day DMA (₹311.34), and 200-day DMA (₹274.34). The price distance from 200 DMA is +17.50%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,260.00) is positioned above the 30-day DMA (₹3,137.32), 50-day DMA (₹2,981.04), and 200-day DMA (₹2,689.42). The price distance from 200 DMA is +19.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[328.45, 329.44, 330.42, 331.41, 332.39, 333.38]</t>
+          <t>[3260.0, 3303.64, 3347.27, 3390.91, 3434.55, 3478.18]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[328.45, 332.42, 334.65, 336.58, 338.37, 340.06]</t>
+          <t>[3260.0, 3345.14, 3405.97, 3462.8, 3517.56, 3570.99]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[328.45, 327.19, 327.25, 327.52, 327.91, 328.36]</t>
+          <t>[3260.0, 3272.51, 3303.25, 3336.99, 3372.29, 3408.58]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>348.99</v>
+        <v>4172</v>
       </c>
     </row>
     <row r="4">
@@ -995,16 +995,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>83193.02</v>
+        <v>300878.29</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,146 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3268.7</v>
+        <v>326.85</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹3247.95 - ₹3299.83</t>
+          <t>₹325.35 - ₹329.1</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3351.71</v>
+        <v>332.85</v>
       </c>
       <c r="I4" t="n">
-        <v>3137.32</v>
+        <v>322.09</v>
       </c>
       <c r="J4" t="n">
-        <v>2981.04</v>
+        <v>311.9</v>
       </c>
       <c r="K4" t="n">
-        <v>2689.42</v>
+        <v>274.44</v>
       </c>
       <c r="L4" t="n">
-        <v>19.4</v>
+        <v>17.46</v>
       </c>
       <c r="M4" t="n">
-        <v>74.77</v>
+        <v>1.94</v>
       </c>
       <c r="N4" t="n">
-        <v>102.69</v>
+        <v>3.71</v>
       </c>
       <c r="O4" t="n">
-        <v>-27.92</v>
+        <v>-1.77</v>
       </c>
       <c r="P4" t="n">
-        <v>103.76</v>
+        <v>7.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.89</v>
+        <v>11.39</v>
       </c>
       <c r="R4" t="n">
         <v>47.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.65</v>
+        <v>-1.29</v>
       </c>
       <c r="U4" t="n">
-        <v>53.3</v>
+        <v>54.1</v>
       </c>
       <c r="V4" t="n">
-        <v>3.4</v>
+        <v>2.51</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>3268.7</v>
+        <v>323.67</v>
       </c>
       <c r="Y4" t="n">
-        <v>4185.32</v>
+        <v>347.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>4185.32</v>
+        <v>347.28</v>
       </c>
       <c r="AA4" t="n">
-        <v>3113.05</v>
+        <v>315.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>3271.23</v>
+        <v>327.43</v>
       </c>
       <c r="AC4" t="n">
-        <v>3312.36</v>
+        <v>329.16</v>
       </c>
       <c r="AD4" t="n">
-        <v>3356.03</v>
+        <v>331.48</v>
       </c>
       <c r="AE4" t="n">
-        <v>46.5</v>
+        <v>39.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.89) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>54.1</v>
+        <v>726.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85.3</v>
+        <v>182</v>
       </c>
       <c r="AK4" t="n">
-        <v>55.6</v>
+        <v>0.6</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>3392.34</v>
+        <v>338.61</v>
       </c>
       <c r="AN4" t="n">
-        <v>3142.13</v>
+        <v>315.76</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹83,193.02 Cr., a P/E ratio of 54.14, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹300,878.29 Cr., a P/E ratio of 726.33, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.45 (Consolidation Zone), while MACD Line (74.77) trades below Signal (102.69) with an expanding histogram (-27.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.40% above the 200-day DMA (₹2689.42). Daily volatility envelope is bounded by ATR(14) of ₹103.76.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.71 (Consolidation Zone), while MACD Line (1.94) trades below Signal (3.71) with an expanding histogram (-1.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.46% above the 200-day DMA (₹274.44). Daily volatility envelope is bounded by ATR(14) of ₹7.50.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,268.70) is positioned above the 30-day DMA (₹3,137.32), 50-day DMA (₹2,981.04), and 200-day DMA (₹2,689.42). The price distance from 200 DMA is +19.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹326.85) is positioned above the 30-day DMA (₹322.09), 50-day DMA (₹311.90), and 200-day DMA (₹274.44). The price distance from 200 DMA is +17.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[3268.7, 3314.19, 3359.69, 3405.18, 3450.68, 3496.17]</t>
+          <t>[326.85, 327.83, 328.81, 329.79, 330.77, 331.75]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[3268.7, 3355.7, 3418.39, 3477.07, 3533.69, 3588.98]</t>
+          <t>[326.85, 330.83, 333.05, 334.99, 336.77, 338.46]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[3268.7, 3283.06, 3315.66, 3351.26, 3388.42, 3426.56]</t>
+          <t>[326.85, 325.58, 325.63, 325.9, 326.27, 326.72]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>4185.32</v>
+        <v>347.28</v>
       </c>
     </row>
     <row r="5">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60632.26</v>
+        <v>63031.23</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,15 +1179,15 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2183.7</v>
+        <v>2270.1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹2171.36 - ₹2202.2</t>
+          <t>₹2257.76 - ₹2288.6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2233.04</v>
+        <v>2319.44</v>
       </c>
       <c r="I5" t="n">
         <v>2126.16</v>
@@ -1214,46 +1214,46 @@
         <v>61.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.89</v>
+        <v>11.39</v>
       </c>
       <c r="R5" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="S5" t="n">
-        <v>0.19</v>
+        <v>0.41</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.72</v>
+        <v>-1.21</v>
       </c>
       <c r="U5" t="n">
         <v>53.3</v>
       </c>
       <c r="V5" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>2151.27</v>
+        <v>2270.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>2328.11</v>
+        <v>2440.89</v>
       </c>
       <c r="Z5" t="n">
-        <v>2328.11</v>
+        <v>2440.89</v>
       </c>
       <c r="AA5" t="n">
-        <v>2091.19</v>
+        <v>2177.59</v>
       </c>
       <c r="AB5" t="n">
-        <v>2176.33</v>
+        <v>2228.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>2206.36</v>
+        <v>2311.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>2229.03</v>
+        <v>2352.63</v>
       </c>
       <c r="AE5" t="n">
         <v>43.7</v>
@@ -1263,14 +1263,14 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.89) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>49.3</v>
+        <v>51.3</v>
       </c>
       <c r="AJ5" t="n">
         <v>8.5</v>
@@ -1282,14 +1282,14 @@
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>2245.15</v>
+        <v>2333.88</v>
       </c>
       <c r="AN5" t="n">
-        <v>2123.32</v>
+        <v>2205.6</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,632.26 Cr., a P/E ratio of 49.28, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹63,031.23 Cr., a P/E ratio of 51.29, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1299,26 +1299,26 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,183.70) is positioned above the 30-day DMA (₹2,126.16), 50-day DMA (₹2,009.95), and 200-day DMA (₹1,956.80). The price distance from 200 DMA is +8.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,270.10) is positioned above the 30-day DMA (₹2,126.16), 50-day DMA (₹2,009.95), and 200-day DMA (₹1,956.80). The price distance from 200 DMA is +8.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[2183.7, 2190.25, 2196.8, 2203.35, 2209.9, 2216.46]</t>
+          <t>[2270.1, 2307.8, 2345.49, 2383.19, 2420.88, 2458.58]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[2183.7, 2214.92, 2231.69, 2246.08, 2259.25, 2271.62]</t>
+          <t>[2270.1, 2332.47, 2380.38, 2425.92, 2470.22, 2513.74]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[2183.7, 2171.75, 2170.64, 2171.31, 2172.9, 2175.08]</t>
+          <t>[2270.1, 2289.29, 2319.32, 2351.14, 2383.88, 2417.2]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>2328.11</v>
+        <v>2440.89</v>
       </c>
     </row>
     <row r="6">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30115.95</v>
+        <v>134777.73</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,146 +1346,146 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>547.5</v>
+        <v>117.27</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹544.1 - ₹552.6</t>
+          <t>₹116.82 - ₹117.94</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>561.1</v>
+        <v>119.05</v>
       </c>
       <c r="I6" t="n">
-        <v>520.59</v>
+        <v>116.25</v>
       </c>
       <c r="J6" t="n">
-        <v>524.61</v>
+        <v>113.79</v>
       </c>
       <c r="K6" t="n">
-        <v>523.61</v>
+        <v>112.3</v>
       </c>
       <c r="L6" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="M6" t="n">
-        <v>10.74</v>
+        <v>0.59</v>
       </c>
       <c r="N6" t="n">
-        <v>9.94</v>
+        <v>0.78</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8</v>
+        <v>-0.19</v>
       </c>
       <c r="P6" t="n">
-        <v>17</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.89</v>
+        <v>11.39</v>
       </c>
       <c r="R6" t="n">
-        <v>46.8</v>
+        <v>46</v>
       </c>
       <c r="S6" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.94</v>
+        <v>-1.06</v>
       </c>
       <c r="U6" t="n">
-        <v>46.7</v>
+        <v>50.8</v>
       </c>
       <c r="V6" t="n">
-        <v>5.05</v>
+        <v>2.38</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>537.5700000000001</v>
+        <v>116.78</v>
       </c>
       <c r="Y6" t="n">
-        <v>575.97</v>
+        <v>125.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>575.97</v>
+        <v>125.05</v>
       </c>
       <c r="AA6" t="n">
-        <v>522</v>
+        <v>113.93</v>
       </c>
       <c r="AB6" t="n">
-        <v>547.7</v>
+        <v>117.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>551.8</v>
+        <v>117.68</v>
       </c>
       <c r="AD6" t="n">
-        <v>556.1</v>
+        <v>118.09</v>
       </c>
       <c r="AE6" t="n">
-        <v>60.4</v>
+        <v>54</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.24</v>
+        <v>-0.14</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.89) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>65.2</v>
+        <v>38.1</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>561.59</v>
+        <v>120.34</v>
       </c>
       <c r="AN6" t="n">
-        <v>533.38</v>
+        <v>114.12</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,115.95 Cr., a P/E ratio of 5.25, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,777.73 Cr., a P/E ratio of 6.10, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.36 (Bullish Momentum Zone), while MACD Line (10.74) trades above Signal (9.94) with an expanding histogram (+0.80). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.70% above the 200-day DMA (₹523.61). Daily volatility envelope is bounded by ATR(14) of ₹17.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.02 (Consolidation Zone), while MACD Line (0.59) trades below Signal (0.78) with an expanding histogram (-0.19). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.71% above the 200-day DMA (₹112.30). Daily volatility envelope is bounded by ATR(14) of ₹2.23.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹547.50) is positioned above the 30-day DMA (₹520.59), 50-day DMA (₹524.61), and 200-day DMA (₹523.61). The price distance from 200 DMA is +3.70%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.27) is positioned above the 30-day DMA (₹116.25), 50-day DMA (₹113.79), and 200-day DMA (₹112.30). The price distance from 200 DMA is +3.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[547.5, 549.14, 550.78, 552.43, 554.07, 555.71]</t>
+          <t>[117.27, 118.09, 118.92, 119.74, 120.57, 121.39]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[547.5, 555.94, 560.4, 564.21, 567.67, 570.92]</t>
+          <t>[117.27, 118.98, 120.18, 121.29, 122.35, 123.38]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[547.5, 544.04, 543.57, 543.59, 543.87, 544.31]</t>
+          <t>[117.27, 117.43, 117.97, 118.58, 119.23, 119.9]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>575.97</v>
+        <v>125.05</v>
       </c>
     </row>
     <row r="7">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>134524.9</v>
+        <v>30151.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,146 +1513,146 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>117.05</v>
+        <v>548.15</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹116.6 - ₹117.72</t>
+          <t>₹544.76 - ₹553.24</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>118.83</v>
+        <v>561.73</v>
       </c>
       <c r="I7" t="n">
-        <v>116.25</v>
+        <v>522.25</v>
       </c>
       <c r="J7" t="n">
-        <v>113.79</v>
+        <v>525.25</v>
       </c>
       <c r="K7" t="n">
-        <v>112.3</v>
+        <v>523.6799999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="M7" t="n">
-        <v>0.59</v>
+        <v>10.41</v>
       </c>
       <c r="N7" t="n">
-        <v>0.78</v>
+        <v>10.21</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.19</v>
+        <v>0.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>16.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.89</v>
+        <v>11.39</v>
       </c>
       <c r="R7" t="n">
-        <v>46.5</v>
+        <v>45.9</v>
       </c>
       <c r="S7" t="n">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.05</v>
+        <v>-1.98</v>
       </c>
       <c r="U7" t="n">
-        <v>50.8</v>
+        <v>46.7</v>
       </c>
       <c r="V7" t="n">
-        <v>2.38</v>
+        <v>4.8</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>116.52</v>
+        <v>541.51</v>
       </c>
       <c r="Y7" t="n">
-        <v>124.82</v>
+        <v>576.66</v>
       </c>
       <c r="Z7" t="n">
-        <v>124.82</v>
+        <v>576.66</v>
       </c>
       <c r="AA7" t="n">
-        <v>113.71</v>
+        <v>522.6900000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>117.04</v>
+        <v>547.92</v>
       </c>
       <c r="AC7" t="n">
-        <v>117.44</v>
+        <v>552.24</v>
       </c>
       <c r="AD7" t="n">
-        <v>117.84</v>
+        <v>556.3200000000001</v>
       </c>
       <c r="AE7" t="n">
-        <v>54</v>
+        <v>53.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.14</v>
+        <v>0.23</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.89) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>38.1</v>
+        <v>65.2</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>120.21</v>
+        <v>561.49</v>
       </c>
       <c r="AN7" t="n">
-        <v>113.89</v>
+        <v>534.35</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,524.90 Cr., a P/E ratio of 6.11, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,151.70 Cr., a P/E ratio of 5.26, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.02 (Consolidation Zone), while MACD Line (0.59) trades below Signal (0.78) with an expanding histogram (-0.19). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.71% above the 200-day DMA (₹112.30). Daily volatility envelope is bounded by ATR(14) of ₹2.23.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.80 (Consolidation Zone), while MACD Line (10.41) trades above Signal (10.21) with an expanding histogram (+0.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.69% above the 200-day DMA (₹523.68). Daily volatility envelope is bounded by ATR(14) of ₹16.97.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.05) is positioned above the 30-day DMA (₹116.25), 50-day DMA (₹113.79), and 200-day DMA (₹112.30). The price distance from 200 DMA is +3.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹548.15) is positioned above the 30-day DMA (₹522.25), 50-day DMA (₹525.25), and 200-day DMA (₹523.68). The price distance from 200 DMA is +3.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[117.05, 117.83, 118.62, 119.4, 120.18, 120.97]</t>
+          <t>[548.15, 549.79, 551.44, 553.08, 554.73, 556.37]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[117.05, 118.72, 119.88, 120.94, 121.97, 122.96]</t>
+          <t>[548.15, 556.58, 561.04, 564.84, 568.3, 571.55]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[117.05, 117.17, 117.67, 118.24, 118.85, 119.47]</t>
+          <t>[548.15, 544.7, 544.24, 544.26, 544.54, 544.99]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>124.82</v>
+        <v>576.66</v>
       </c>
     </row>
     <row r="8">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>60327.87</v>
+        <v>125561.34</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1680,146 +1680,146 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1000.5</v>
+        <v>11282</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹994.9 - ₹1008.9</t>
+          <t>₹11240.61 - ₹11344.08</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1022.89</v>
+        <v>11447.54</v>
       </c>
       <c r="I8" t="n">
-        <v>980.86</v>
+        <v>11278.87</v>
       </c>
       <c r="J8" t="n">
-        <v>955.17</v>
+        <v>11082.86</v>
       </c>
       <c r="K8" t="n">
-        <v>850.98</v>
+        <v>10584.38</v>
       </c>
       <c r="L8" t="n">
-        <v>14.75</v>
+        <v>3.27</v>
       </c>
       <c r="M8" t="n">
-        <v>16.58</v>
+        <v>-41.34</v>
       </c>
       <c r="N8" t="n">
-        <v>25.36</v>
+        <v>-2.16</v>
       </c>
       <c r="O8" t="n">
-        <v>-8.779999999999999</v>
+        <v>-39.18</v>
       </c>
       <c r="P8" t="n">
-        <v>27.99</v>
+        <v>206.93</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.89</v>
+        <v>11.39</v>
       </c>
       <c r="R8" t="n">
-        <v>45</v>
+        <v>45.6</v>
       </c>
       <c r="S8" t="n">
-        <v>0.25</v>
+        <v>0.53</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.67</v>
+        <v>-0.7</v>
       </c>
       <c r="U8" t="n">
-        <v>51.7</v>
+        <v>50</v>
       </c>
       <c r="V8" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>999.84</v>
+        <v>11282</v>
       </c>
       <c r="Y8" t="n">
-        <v>1092.53</v>
+        <v>12076.13</v>
       </c>
       <c r="Z8" t="n">
-        <v>1092.53</v>
+        <v>12076.13</v>
       </c>
       <c r="AA8" t="n">
-        <v>958.51</v>
+        <v>10971.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>998.83</v>
+        <v>11238.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>1008.96</v>
+        <v>11406.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>1017.43</v>
+        <v>11531.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>33.1</v>
+        <v>36.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.22</v>
+        <v>-0.02</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.89) | LSTM Deep Net</t>
+          <t>Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>31.1</v>
+        <v>14.2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>23</v>
+        <v>734.6</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="AM8" t="n">
-        <v>1039.68</v>
+        <v>11590.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>963</v>
+        <v>10960.91</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹60,327.87 Cr., a P/E ratio of 31.05, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹125,561.34 Cr., a P/E ratio of 14.17, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.06 (Consolidation Zone), while MACD Line (16.58) trades below Signal (25.36) with an expanding histogram (-8.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.75% above the 200-day DMA (₹850.98). Daily volatility envelope is bounded by ATR(14) of ₹27.99.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 36.48 (Consolidation Zone), while MACD Line (-41.34) trades below Signal (-2.16) with an expanding histogram (-39.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.27% above the 200-day DMA (₹10584.38). Daily volatility envelope is bounded by ATR(14) of ₹206.93.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,000.50) is positioned above the 30-day DMA (₹980.86), 50-day DMA (₹955.17), and 200-day DMA (₹850.98). The price distance from 200 DMA is +14.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,282.00) is positioned above the 30-day DMA (₹11,278.87), 50-day DMA (₹11,082.86), and 200-day DMA (₹10,584.38). The price distance from 200 DMA is +3.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[1000.5, 1011.09, 1021.68, 1032.27, 1042.86, 1053.44]</t>
+          <t>[11282.0, 11446.89, 11611.77, 11776.66, 11941.55, 12106.44]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[1000.5, 1022.29, 1037.51, 1051.66, 1065.25, 1078.48]</t>
+          <t>[11282.0, 11529.66, 11728.83, 11920.03, 12107.09, 12291.52]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[1000.5, 1002.69, 1009.8, 1017.72, 1026.06, 1034.67]</t>
+          <t>[11282.0, 11384.81, 11523.98, 11669.14, 11817.39, 11967.63]</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>1092.53</v>
+        <v>12076.13</v>
       </c>
     </row>
     <row r="9">
@@ -1830,163 +1830,664 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>106614.84</v>
+        <v>43890</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>737</v>
+        <v>292.6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹733.8 - ₹741.8</t>
+          <t>₹291.43 - ₹294.36</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>749.8099999999999</v>
+        <v>297.3</v>
       </c>
       <c r="I9" t="n">
-        <v>722.83</v>
+        <v>287.18</v>
       </c>
       <c r="J9" t="n">
-        <v>728.36</v>
+        <v>283.36</v>
       </c>
       <c r="K9" t="n">
-        <v>686</v>
+        <v>278.69</v>
       </c>
       <c r="L9" t="n">
-        <v>5.93</v>
+        <v>1.71</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.09</v>
+        <v>-0.1</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.08</v>
+        <v>1.17</v>
       </c>
       <c r="O9" t="n">
-        <v>-0</v>
+        <v>-1.27</v>
       </c>
       <c r="P9" t="n">
-        <v>16.01</v>
+        <v>5.88</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.89</v>
+        <v>11.39</v>
       </c>
       <c r="R9" t="n">
-        <v>40.9</v>
+        <v>45</v>
       </c>
       <c r="S9" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.48</v>
+        <v>-1.18</v>
       </c>
       <c r="U9" t="n">
-        <v>44.3</v>
+        <v>50.8</v>
       </c>
       <c r="V9" t="n">
-        <v>11.47</v>
+        <v>5</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>720.5</v>
+        <v>286.71</v>
       </c>
       <c r="Y9" t="n">
-        <v>783.74</v>
+        <v>311.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>783.74</v>
+        <v>311.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>712.99</v>
+        <v>283.79</v>
       </c>
       <c r="AB9" t="n">
-        <v>734.2</v>
+        <v>289.77</v>
       </c>
       <c r="AC9" t="n">
-        <v>745.8</v>
+        <v>295.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>754.6</v>
+        <v>298.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>58.7</v>
+        <v>39.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2</v>
+        <v>-0.03</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.89) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>48.1</v>
+        <v>10.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15.1</v>
+        <v>-53.2</v>
       </c>
       <c r="AK9" t="n">
-        <v>20.9</v>
+        <v>11.3</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>754.67</v>
+        <v>301.19</v>
       </c>
       <c r="AN9" t="n">
-        <v>719.05</v>
+        <v>284.12</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,614.84 Cr., a P/E ratio of 48.08, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,890.00 Cr., a P/E ratio of 10.39, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.46 (Consolidation Zone), while MACD Line (-0.10) trades below Signal (1.17) with an expanding histogram (-1.27). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +1.71% above the 200-day DMA (₹278.69). Daily volatility envelope is bounded by ATR(14) of ₹5.88.</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹292.60) is positioned above the 30-day DMA (₹287.18), 50-day DMA (₹283.36), and 200-day DMA (₹278.69). The price distance from 200 DMA is +1.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>[292.6, 293.48, 294.36, 295.23, 296.11, 296.99]</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>[292.6, 295.83, 297.68, 299.3, 300.81, 302.24]</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>[292.6, 291.72, 291.86, 292.18, 292.59, 293.05]</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>311.15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>60900.7</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1010</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>₹1004.4 - ₹1018.4</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1032.39</v>
+      </c>
+      <c r="I10" t="n">
+        <v>980.86</v>
+      </c>
+      <c r="J10" t="n">
+        <v>955.17</v>
+      </c>
+      <c r="K10" t="n">
+        <v>850.98</v>
+      </c>
+      <c r="L10" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="M10" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="N10" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="P10" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="R10" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="U10" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1010</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1105.23</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1105.23</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>968.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1002.9</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1017.1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1024.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Low VIX (11.39) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1047.16</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>969.87</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹60,900.70 Cr., a P/E ratio of 31.34, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.06 (Consolidation Zone), while MACD Line (16.58) trades below Signal (25.36) with an expanding histogram (-8.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.75% above the 200-day DMA (₹850.98). Daily volatility envelope is bounded by ATR(14) of ₹27.99.</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,010.00) is positioned above the 30-day DMA (₹980.86), 50-day DMA (₹955.17), and 200-day DMA (₹850.98). The price distance from 200 DMA is +14.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>[1010.0, 1022.84, 1035.67, 1048.51, 1061.34, 1074.18]</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>[1010.0, 1034.03, 1051.51, 1067.9, 1083.74, 1099.22]</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>[1010.0, 1014.44, 1023.79, 1033.96, 1044.55, 1055.4]</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>1105.23</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>410340.82</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>₹411.26 - ₹414.36</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>417.47</v>
+      </c>
+      <c r="I11" t="n">
+        <v>408.48</v>
+      </c>
+      <c r="J11" t="n">
+        <v>399.68</v>
+      </c>
+      <c r="K11" t="n">
+        <v>399.79</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="P11" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="R11" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X11" t="n">
+        <v>410.12</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>429.6</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>419.97</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>403.18</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>414.73</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>416.96</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>421.43</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Low VIX (11.39) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>421.16</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>402.58</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹410,340.82 Cr., a P/E ratio of 20.21, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.58 (Consolidation Zone), while MACD Line (4.50) trades below Signal (6.01) with an expanding histogram (-1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹399.79). Daily volatility envelope is bounded by ATR(14) of ₹6.21.</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹412.50) is positioned above the 30-day DMA (₹408.48), 50-day DMA (₹399.68), and 200-day DMA (₹399.79). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>[412.5, 414.76, 417.03, 419.29, 421.56, 423.82]</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>[412.5, 417.25, 420.54, 423.6, 426.53, 429.38]</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>[412.5, 412.9, 414.39, 416.07, 417.83, 419.66]</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>419.97</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>106000.03</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>732.75</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>₹729.55 - ₹737.55</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>745.5599999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>722.83</v>
+      </c>
+      <c r="J12" t="n">
+        <v>728.36</v>
+      </c>
+      <c r="K12" t="n">
+        <v>686</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="R12" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1.47</v>
+      </c>
+      <c r="U12" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X12" t="n">
+        <v>716.23</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>779.21</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>779.21</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>708.74</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>732.78</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>742.96</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>753.1799999999999</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>751.39</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>715.78</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,000.03 Cr., a P/E ratio of 48.72, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
           <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.74 (Bullish Momentum Zone), while MACD Line (-2.09) trades below Signal (-2.08) with an expanding histogram (-0.00). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.93% above the 200-day DMA (₹686.00). Daily volatility envelope is bounded by ATR(14) of ₹16.01.</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹737.00) is positioned above the 30-day DMA (₹722.83), 50-day DMA (₹728.36), and 200-day DMA (₹686.00). The price distance from 200 DMA is +5.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>[737.0, 739.21, 741.42, 743.63, 745.84, 748.05]</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>[737.0, 745.61, 750.48, 754.72, 758.65, 762.37]</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>[737.0, 734.41, 734.63, 735.32, 736.24, 737.32]</t>
-        </is>
-      </c>
-      <c r="AU9" t="n">
-        <v>783.74</v>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹732.75) is positioned above the 30-day DMA (₹722.83), 50-day DMA (₹728.36), and 200-day DMA (₹686.00). The price distance from 200 DMA is +5.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>[732.75, 734.95, 737.15, 739.34, 741.54, 743.74]</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>[732.75, 741.35, 746.2, 750.43, 754.35, 758.06]</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>[732.75, 730.15, 730.36, 731.03, 731.94, 733.0]</t>
+        </is>
+      </c>
+      <c r="AU12" t="n">
+        <v>779.21</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU12"/>
+  <dimension ref="A1:AU8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>179474.08</v>
+        <v>25000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2208.8</v>
+        <v>3260</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹2197.33 - ₹2226.01</t>
+          <t>₹3239.25 - ₹3291.13</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2254.68</v>
+        <v>3343.01</v>
       </c>
       <c r="I2" t="n">
-        <v>2200.73</v>
+        <v>3137.32</v>
       </c>
       <c r="J2" t="n">
-        <v>2129.15</v>
+        <v>2981.04</v>
       </c>
       <c r="K2" t="n">
-        <v>2052.76</v>
+        <v>2689.42</v>
       </c>
       <c r="L2" t="n">
-        <v>5.22</v>
+        <v>19.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.6</v>
+        <v>74.77</v>
       </c>
       <c r="N2" t="n">
-        <v>15.47</v>
+        <v>102.69</v>
       </c>
       <c r="O2" t="n">
-        <v>-11.86</v>
+        <v>-27.92</v>
       </c>
       <c r="P2" t="n">
-        <v>57.35</v>
+        <v>103.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.39</v>
+        <v>12.29</v>
       </c>
       <c r="R2" t="n">
-        <v>49.6</v>
+        <v>48.1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.43</v>
+        <v>-1.65</v>
       </c>
       <c r="U2" t="n">
-        <v>51.8</v>
+        <v>53.3</v>
       </c>
       <c r="V2" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2187.28</v>
+        <v>3191.82</v>
       </c>
       <c r="Y2" t="n">
-        <v>2348.86</v>
+        <v>3184.06</v>
       </c>
       <c r="Z2" t="n">
-        <v>2348.86</v>
+        <v>2542.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>2122.78</v>
+        <v>3104.35</v>
       </c>
       <c r="AB2" t="n">
-        <v>2191.03</v>
+        <v>3268.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>2226.56</v>
+        <v>3306.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>2244.33</v>
+        <v>3353.13</v>
       </c>
       <c r="AE2" t="n">
-        <v>33.7</v>
+        <v>46.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.17</v>
+        <v>0.2</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>36.3</v>
+        <v>54</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.5</v>
+        <v>85.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>7</v>
+        <v>55.6</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>2270.21</v>
+        <v>3397.67</v>
       </c>
       <c r="AN2" t="n">
-        <v>2140.02</v>
+        <v>3137.08</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>HYUNDAI operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹179,474.08 Cr., a P/E ratio of 36.26, and YoY Revenue Growth of -0.5%, the company demonstrates strong institutional backing, solid operating profit margins (7.00%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.96, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.70 (Consolidation Zone), while MACD Line (3.60) trades below Signal (15.47) with an expanding histogram (-11.86). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.22% above the 200-day DMA (₹2052.76). Daily volatility envelope is bounded by ATR(14) of ₹57.35.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.45 (Consolidation Zone), while MACD Line (74.77) trades below Signal (102.69) with an expanding histogram (-27.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.40% above the 200-day DMA (₹2689.42). Daily volatility envelope is bounded by ATR(14) of ₹103.76.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HYUNDAI. Current Market Price (₹2,208.80) is positioned above the 30-day DMA (₹2,200.73), 50-day DMA (₹2,129.15), and 200-day DMA (₹2,052.76). The price distance from 200 DMA is +5.22%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,260.00) is positioned above the 30-day DMA (₹3,137.32), 50-day DMA (₹2,981.04), and 200-day DMA (₹2,689.42). The price distance from 200 DMA is +19.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[2208.8, 2215.43, 2222.05, 2228.68, 2235.31, 2241.93]</t>
+          <t>[3260.0, 3303.43, 3346.86, 3390.28, 3433.71, 3477.14]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[2208.8, 2238.37, 2254.49, 2268.41, 2281.19, 2293.23]</t>
+          <t>[3260.0, 3344.93, 3405.55, 3462.17, 3516.72, 3569.95]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[2208.8, 2198.22, 2197.72, 2198.88, 2200.9, 2203.46]</t>
+          <t>[3260.0, 3272.3, 3302.83, 3336.37, 3371.45, 3407.53]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2348.86</v>
+        <v>2542.65</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25000</v>
+        <v>300878.29</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3260</v>
+        <v>326.85</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹3239.25 - ₹3291.13</t>
+          <t>₹325.35 - ₹329.1</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3343.01</v>
+        <v>332.85</v>
       </c>
       <c r="I3" t="n">
-        <v>3137.32</v>
+        <v>322.09</v>
       </c>
       <c r="J3" t="n">
-        <v>2981.04</v>
+        <v>311.9</v>
       </c>
       <c r="K3" t="n">
-        <v>2689.42</v>
+        <v>274.44</v>
       </c>
       <c r="L3" t="n">
-        <v>19.4</v>
+        <v>17.46</v>
       </c>
       <c r="M3" t="n">
-        <v>74.77</v>
+        <v>1.94</v>
       </c>
       <c r="N3" t="n">
-        <v>102.69</v>
+        <v>3.71</v>
       </c>
       <c r="O3" t="n">
-        <v>-27.92</v>
+        <v>-1.77</v>
       </c>
       <c r="P3" t="n">
-        <v>103.76</v>
+        <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.39</v>
+        <v>12.29</v>
       </c>
       <c r="R3" t="n">
-        <v>48.4</v>
+        <v>47.1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.63</v>
+        <v>-1.32</v>
       </c>
       <c r="U3" t="n">
-        <v>53.3</v>
+        <v>54.1</v>
       </c>
       <c r="V3" t="n">
-        <v>3.39</v>
+        <v>2.51</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>3260</v>
+        <v>316.24</v>
       </c>
       <c r="Y3" t="n">
-        <v>4172</v>
+        <v>315.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>4172</v>
+        <v>305.81</v>
       </c>
       <c r="AA3" t="n">
-        <v>3104.35</v>
+        <v>315.61</v>
       </c>
       <c r="AB3" t="n">
-        <v>3268.33</v>
+        <v>327.43</v>
       </c>
       <c r="AC3" t="n">
-        <v>3306.56</v>
+        <v>329.16</v>
       </c>
       <c r="AD3" t="n">
-        <v>3353.13</v>
+        <v>331.48</v>
       </c>
       <c r="AE3" t="n">
-        <v>46.5</v>
+        <v>39.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>54</v>
+        <v>726.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85.3</v>
+        <v>182</v>
       </c>
       <c r="AK3" t="n">
-        <v>55.6</v>
+        <v>0.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>3393.55</v>
+        <v>338.27</v>
       </c>
       <c r="AN3" t="n">
-        <v>3137.57</v>
+        <v>316.46</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.96, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹300,878.29 Cr., a P/E ratio of 726.33, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.45 (Consolidation Zone), while MACD Line (74.77) trades below Signal (102.69) with an expanding histogram (-27.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.40% above the 200-day DMA (₹2689.42). Daily volatility envelope is bounded by ATR(14) of ₹103.76.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.71 (Consolidation Zone), while MACD Line (1.94) trades below Signal (3.71) with an expanding histogram (-1.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.46% above the 200-day DMA (₹274.44). Daily volatility envelope is bounded by ATR(14) of ₹7.50.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,260.00) is positioned above the 30-day DMA (₹3,137.32), 50-day DMA (₹2,981.04), and 200-day DMA (₹2,689.42). The price distance from 200 DMA is +19.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹326.85) is positioned above the 30-day DMA (₹322.09), 50-day DMA (₹311.90), and 200-day DMA (₹274.44). The price distance from 200 DMA is +17.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[3260.0, 3303.64, 3347.27, 3390.91, 3434.55, 3478.18]</t>
+          <t>[326.85, 327.83, 328.81, 329.79, 330.77, 331.75]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[3260.0, 3345.14, 3405.97, 3462.8, 3517.56, 3570.99]</t>
+          <t>[326.85, 330.83, 333.05, 334.99, 336.77, 338.46]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[3260.0, 3272.51, 3303.25, 3336.99, 3372.29, 3408.58]</t>
+          <t>[326.85, 325.58, 325.63, 325.9, 326.27, 326.72]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>4172</v>
+        <v>305.81</v>
       </c>
     </row>
     <row r="4">
@@ -995,16 +995,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>300878.29</v>
+        <v>63031.23</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,146 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>326.85</v>
+        <v>2270.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹325.35 - ₹329.1</t>
+          <t>₹2257.76 - ₹2288.6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>332.85</v>
+        <v>2319.44</v>
       </c>
       <c r="I4" t="n">
-        <v>322.09</v>
+        <v>2126.16</v>
       </c>
       <c r="J4" t="n">
-        <v>311.9</v>
+        <v>2009.95</v>
       </c>
       <c r="K4" t="n">
-        <v>274.44</v>
+        <v>1956.8</v>
       </c>
       <c r="L4" t="n">
-        <v>17.46</v>
+        <v>8.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1.94</v>
+        <v>33.95</v>
       </c>
       <c r="N4" t="n">
-        <v>3.71</v>
+        <v>54.05</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.77</v>
+        <v>-20.1</v>
       </c>
       <c r="P4" t="n">
-        <v>7.5</v>
+        <v>61.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.39</v>
+        <v>12.29</v>
       </c>
       <c r="R4" t="n">
-        <v>47.6</v>
+        <v>46.9</v>
       </c>
       <c r="S4" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.29</v>
+        <v>-1.21</v>
       </c>
       <c r="U4" t="n">
-        <v>54.1</v>
+        <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>2.51</v>
+        <v>3.12</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>323.67</v>
+        <v>2229.93</v>
       </c>
       <c r="Y4" t="n">
-        <v>347.28</v>
+        <v>2224.27</v>
       </c>
       <c r="Z4" t="n">
-        <v>347.28</v>
+        <v>2004.42</v>
       </c>
       <c r="AA4" t="n">
-        <v>315.61</v>
+        <v>2177.59</v>
       </c>
       <c r="AB4" t="n">
-        <v>327.43</v>
+        <v>2228.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>329.16</v>
+        <v>2311.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>331.48</v>
+        <v>2352.63</v>
       </c>
       <c r="AE4" t="n">
-        <v>39.7</v>
+        <v>43.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>726.3</v>
+        <v>51.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>182</v>
+        <v>8.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>338.61</v>
+        <v>2334.79</v>
       </c>
       <c r="AN4" t="n">
-        <v>315.76</v>
+        <v>2206.53</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹300,878.29 Cr., a P/E ratio of 726.33, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹63,031.23 Cr., a P/E ratio of 51.29, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.71 (Consolidation Zone), while MACD Line (1.94) trades below Signal (3.71) with an expanding histogram (-1.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.46% above the 200-day DMA (₹274.44). Daily volatility envelope is bounded by ATR(14) of ₹7.50.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.67 (Consolidation Zone), while MACD Line (33.95) trades below Signal (54.05) with an expanding histogram (-20.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.34% above the 200-day DMA (₹1956.80). Daily volatility envelope is bounded by ATR(14) of ₹61.68.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹326.85) is positioned above the 30-day DMA (₹322.09), 50-day DMA (₹311.90), and 200-day DMA (₹274.44). The price distance from 200 DMA is +17.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,270.10) is positioned above the 30-day DMA (₹2,126.16), 50-day DMA (₹2,009.95), and 200-day DMA (₹1,956.80). The price distance from 200 DMA is +8.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[326.85, 327.83, 328.81, 329.79, 330.77, 331.75]</t>
+          <t>[2270.1, 2307.8, 2345.49, 2383.19, 2420.88, 2458.58]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[326.85, 330.83, 333.05, 334.99, 336.77, 338.46]</t>
+          <t>[2270.1, 2332.47, 2380.38, 2425.92, 2470.22, 2513.74]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[326.85, 325.58, 325.63, 325.9, 326.27, 326.72]</t>
+          <t>[2270.1, 2289.29, 2319.32, 2351.14, 2383.88, 2417.2]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>347.28</v>
+        <v>2004.42</v>
       </c>
     </row>
     <row r="5">
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63031.23</v>
+        <v>30151.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,146 +1179,146 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2270.1</v>
+        <v>548.15</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹2257.76 - ₹2288.6</t>
+          <t>₹544.76 - ₹553.24</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2319.44</v>
+        <v>561.73</v>
       </c>
       <c r="I5" t="n">
-        <v>2126.16</v>
+        <v>522.25</v>
       </c>
       <c r="J5" t="n">
-        <v>2009.95</v>
+        <v>525.25</v>
       </c>
       <c r="K5" t="n">
-        <v>1956.8</v>
+        <v>523.6799999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>8.34</v>
+        <v>3.69</v>
       </c>
       <c r="M5" t="n">
-        <v>33.95</v>
+        <v>10.41</v>
       </c>
       <c r="N5" t="n">
-        <v>54.05</v>
+        <v>10.21</v>
       </c>
       <c r="O5" t="n">
-        <v>-20.1</v>
+        <v>0.2</v>
       </c>
       <c r="P5" t="n">
-        <v>61.68</v>
+        <v>16.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.39</v>
+        <v>12.29</v>
       </c>
       <c r="R5" t="n">
-        <v>46.9</v>
+        <v>46.1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.41</v>
+        <v>0.17</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.21</v>
+        <v>-1.97</v>
       </c>
       <c r="U5" t="n">
-        <v>53.3</v>
+        <v>46.7</v>
       </c>
       <c r="V5" t="n">
-        <v>3.12</v>
+        <v>4.8</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>2270.1</v>
+        <v>529.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>2440.89</v>
+        <v>528.05</v>
       </c>
       <c r="Z5" t="n">
-        <v>2440.89</v>
+        <v>520.29</v>
       </c>
       <c r="AA5" t="n">
-        <v>2177.59</v>
+        <v>522.6900000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>2228.83</v>
+        <v>547.92</v>
       </c>
       <c r="AC5" t="n">
-        <v>2311.36</v>
+        <v>552.24</v>
       </c>
       <c r="AD5" t="n">
-        <v>2352.63</v>
+        <v>556.3200000000001</v>
       </c>
       <c r="AE5" t="n">
-        <v>43.7</v>
+        <v>53.8</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.06</v>
+        <v>0.23</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>51.3</v>
+        <v>5.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>5.2</v>
+        <v>65.2</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>2333.88</v>
+        <v>561.97</v>
       </c>
       <c r="AN5" t="n">
-        <v>2205.6</v>
+        <v>533.88</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹63,031.23 Cr., a P/E ratio of 51.29, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,151.70 Cr., a P/E ratio of 5.25, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.67 (Consolidation Zone), while MACD Line (33.95) trades below Signal (54.05) with an expanding histogram (-20.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.34% above the 200-day DMA (₹1956.80). Daily volatility envelope is bounded by ATR(14) of ₹61.68.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.80 (Consolidation Zone), while MACD Line (10.41) trades above Signal (10.21) with an expanding histogram (+0.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.69% above the 200-day DMA (₹523.68). Daily volatility envelope is bounded by ATR(14) of ₹16.97.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,270.10) is positioned above the 30-day DMA (₹2,126.16), 50-day DMA (₹2,009.95), and 200-day DMA (₹1,956.80). The price distance from 200 DMA is +8.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹548.15) is positioned above the 30-day DMA (₹522.25), 50-day DMA (₹525.25), and 200-day DMA (₹523.68). The price distance from 200 DMA is +3.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[2270.1, 2307.8, 2345.49, 2383.19, 2420.88, 2458.58]</t>
+          <t>[548.15, 549.79, 551.44, 553.08, 554.73, 556.37]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[2270.1, 2332.47, 2380.38, 2425.92, 2470.22, 2513.74]</t>
+          <t>[548.15, 556.58, 561.04, 564.84, 568.3, 571.55]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[2270.1, 2289.29, 2319.32, 2351.14, 2383.88, 2417.2]</t>
+          <t>[548.15, 544.7, 544.24, 544.26, 544.54, 544.99]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>2440.89</v>
+        <v>520.29</v>
       </c>
     </row>
     <row r="6">
@@ -1381,7 +1381,7 @@
         <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.39</v>
+        <v>12.29</v>
       </c>
       <c r="R6" t="n">
         <v>46</v>
@@ -1402,13 +1402,13 @@
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>116.78</v>
+        <v>114.1</v>
       </c>
       <c r="Y6" t="n">
-        <v>125.05</v>
+        <v>113.84</v>
       </c>
       <c r="Z6" t="n">
-        <v>125.05</v>
+        <v>110.1</v>
       </c>
       <c r="AA6" t="n">
         <v>113.93</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
@@ -1449,10 +1449,10 @@
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>120.34</v>
+        <v>120.47</v>
       </c>
       <c r="AN6" t="n">
-        <v>114.12</v>
+        <v>114.25</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -1476,16 +1476,16 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[117.27, 118.98, 120.18, 121.29, 122.35, 123.38]</t>
+          <t>[117.27, 118.99, 120.18, 121.29, 122.35, 123.38]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[117.27, 117.43, 117.97, 118.58, 119.23, 119.9]</t>
+          <t>[117.27, 117.43, 117.97, 118.59, 119.23, 119.9]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>125.05</v>
+        <v>110.1</v>
       </c>
     </row>
     <row r="7">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30151.7</v>
+        <v>125561.34</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,146 +1513,146 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>548.15</v>
+        <v>11282</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹544.76 - ₹553.24</t>
+          <t>₹11240.61 - ₹11344.08</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>561.73</v>
+        <v>11447.54</v>
       </c>
       <c r="I7" t="n">
-        <v>522.25</v>
+        <v>11278.87</v>
       </c>
       <c r="J7" t="n">
-        <v>525.25</v>
+        <v>11082.86</v>
       </c>
       <c r="K7" t="n">
-        <v>523.6799999999999</v>
+        <v>10584.38</v>
       </c>
       <c r="L7" t="n">
-        <v>3.69</v>
+        <v>3.27</v>
       </c>
       <c r="M7" t="n">
-        <v>10.41</v>
+        <v>-41.34</v>
       </c>
       <c r="N7" t="n">
-        <v>10.21</v>
+        <v>-2.16</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2</v>
+        <v>-39.18</v>
       </c>
       <c r="P7" t="n">
-        <v>16.97</v>
+        <v>206.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.39</v>
+        <v>12.29</v>
       </c>
       <c r="R7" t="n">
-        <v>45.9</v>
+        <v>46</v>
       </c>
       <c r="S7" t="n">
-        <v>0.17</v>
+        <v>0.53</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.98</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="V7" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>541.51</v>
+        <v>11060.34</v>
       </c>
       <c r="Y7" t="n">
-        <v>576.66</v>
+        <v>10957.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>576.66</v>
+        <v>10360.47</v>
       </c>
       <c r="AA7" t="n">
-        <v>522.6900000000001</v>
+        <v>10971.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>547.92</v>
+        <v>11238.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>552.24</v>
+        <v>11406.66</v>
       </c>
       <c r="AD7" t="n">
-        <v>556.3200000000001</v>
+        <v>11531.33</v>
       </c>
       <c r="AE7" t="n">
-        <v>53.8</v>
+        <v>36.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.23</v>
+        <v>-0.02</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.3</v>
+        <v>14.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14.5</v>
+        <v>24.2</v>
       </c>
       <c r="AK7" t="n">
-        <v>65.2</v>
+        <v>734.6</v>
       </c>
       <c r="AL7" t="n">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="AM7" t="n">
-        <v>561.49</v>
+        <v>11614.58</v>
       </c>
       <c r="AN7" t="n">
-        <v>534.35</v>
+        <v>10967.84</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,151.70 Cr., a P/E ratio of 5.26, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹125,561.34 Cr., a P/E ratio of 14.17, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.80 (Consolidation Zone), while MACD Line (10.41) trades above Signal (10.21) with an expanding histogram (+0.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.69% above the 200-day DMA (₹523.68). Daily volatility envelope is bounded by ATR(14) of ₹16.97.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 36.48 (Consolidation Zone), while MACD Line (-41.34) trades below Signal (-2.16) with an expanding histogram (-39.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.27% above the 200-day DMA (₹10584.38). Daily volatility envelope is bounded by ATR(14) of ₹206.93.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹548.15) is positioned above the 30-day DMA (₹522.25), 50-day DMA (₹525.25), and 200-day DMA (₹523.68). The price distance from 200 DMA is +3.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,282.00) is positioned above the 30-day DMA (₹11,278.87), 50-day DMA (₹11,082.86), and 200-day DMA (₹10,584.38). The price distance from 200 DMA is +3.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[548.15, 549.79, 551.44, 553.08, 554.73, 556.37]</t>
+          <t>[11282.0, 11446.89, 11611.77, 11776.66, 11941.55, 12106.44]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[548.15, 556.58, 561.04, 564.84, 568.3, 571.55]</t>
+          <t>[11282.0, 11529.66, 11728.83, 11920.03, 12107.09, 12291.52]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[548.15, 544.7, 544.24, 544.26, 544.54, 544.99]</t>
+          <t>[11282.0, 11384.81, 11523.98, 11669.14, 11817.39, 11967.63]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>576.66</v>
+        <v>10360.47</v>
       </c>
     </row>
     <row r="8">
@@ -1663,831 +1663,163 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>125561.34</v>
+        <v>106000.03</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11282</v>
+        <v>732.75</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹11240.61 - ₹11344.08</t>
+          <t>₹729.55 - ₹737.55</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>11447.54</v>
+        <v>745.5599999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>11278.87</v>
+        <v>722.83</v>
       </c>
       <c r="J8" t="n">
-        <v>11082.86</v>
+        <v>728.36</v>
       </c>
       <c r="K8" t="n">
-        <v>10584.38</v>
+        <v>686</v>
       </c>
       <c r="L8" t="n">
-        <v>3.27</v>
+        <v>5.93</v>
       </c>
       <c r="M8" t="n">
-        <v>-41.34</v>
+        <v>-2.09</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.16</v>
+        <v>-2.08</v>
       </c>
       <c r="O8" t="n">
-        <v>-39.18</v>
+        <v>-0</v>
       </c>
       <c r="P8" t="n">
-        <v>206.93</v>
+        <v>16.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.39</v>
+        <v>12.29</v>
       </c>
       <c r="R8" t="n">
-        <v>45.6</v>
+        <v>40.9</v>
       </c>
       <c r="S8" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7</v>
+        <v>-1.49</v>
       </c>
       <c r="U8" t="n">
-        <v>50</v>
+        <v>44.3</v>
       </c>
       <c r="V8" t="n">
-        <v>3.95</v>
+        <v>11.45</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>11282</v>
+        <v>699.79</v>
       </c>
       <c r="Y8" t="n">
-        <v>12076.13</v>
+        <v>688.79</v>
       </c>
       <c r="Z8" t="n">
-        <v>12076.13</v>
+        <v>688.79</v>
       </c>
       <c r="AA8" t="n">
-        <v>10971.61</v>
+        <v>708.74</v>
       </c>
       <c r="AB8" t="n">
-        <v>11238.33</v>
+        <v>732.78</v>
       </c>
       <c r="AC8" t="n">
-        <v>11406.66</v>
+        <v>742.96</v>
       </c>
       <c r="AD8" t="n">
-        <v>11531.33</v>
+        <v>753.1799999999999</v>
       </c>
       <c r="AE8" t="n">
-        <v>36.5</v>
+        <v>58.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>14.2</v>
+        <v>48.7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24.2</v>
+        <v>15.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>734.6</v>
+        <v>20.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>11590.5</v>
+        <v>749.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>10960.91</v>
+        <v>712.89</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹125,561.34 Cr., a P/E ratio of 14.17, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,000.03 Cr., a P/E ratio of 48.72, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 36.48 (Consolidation Zone), while MACD Line (-41.34) trades below Signal (-2.16) with an expanding histogram (-39.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.27% above the 200-day DMA (₹10584.38). Daily volatility envelope is bounded by ATR(14) of ₹206.93.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.74 (Bullish Momentum Zone), while MACD Line (-2.09) trades below Signal (-2.08) with an expanding histogram (-0.00). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.93% above the 200-day DMA (₹686.00). Daily volatility envelope is bounded by ATR(14) of ₹16.01.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,282.00) is positioned above the 30-day DMA (₹11,278.87), 50-day DMA (₹11,082.86), and 200-day DMA (₹10,584.38). The price distance from 200 DMA is +3.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹732.75) is positioned above the 30-day DMA (₹722.83), 50-day DMA (₹728.36), and 200-day DMA (₹686.00). The price distance from 200 DMA is +5.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[11282.0, 11446.89, 11611.77, 11776.66, 11941.55, 12106.44]</t>
+          <t>[732.75, 734.95, 737.15, 739.34, 741.54, 743.74]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[11282.0, 11529.66, 11728.83, 11920.03, 12107.09, 12291.52]</t>
+          <t>[732.75, 741.35, 746.2, 750.43, 754.35, 758.06]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[11282.0, 11384.81, 11523.98, 11669.14, 11817.39, 11967.63]</t>
+          <t>[732.75, 730.15, 730.36, 731.03, 731.94, 733.0]</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>12076.13</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>43890</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>292.6</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>₹291.43 - ₹294.36</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>297.3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>287.18</v>
-      </c>
-      <c r="J9" t="n">
-        <v>283.36</v>
-      </c>
-      <c r="K9" t="n">
-        <v>278.69</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="R9" t="n">
-        <v>45</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="U9" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="V9" t="n">
-        <v>5</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X9" t="n">
-        <v>286.71</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>311.15</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>311.15</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>283.79</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>289.77</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>295.44</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>298.27</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>-53.2</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>301.19</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>284.12</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,890.00 Cr., a P/E ratio of 10.39, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.46 (Consolidation Zone), while MACD Line (-0.10) trades below Signal (1.17) with an expanding histogram (-1.27). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +1.71% above the 200-day DMA (₹278.69). Daily volatility envelope is bounded by ATR(14) of ₹5.88.</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹292.60) is positioned above the 30-day DMA (₹287.18), 50-day DMA (₹283.36), and 200-day DMA (₹278.69). The price distance from 200 DMA is +1.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>[292.6, 293.48, 294.36, 295.23, 296.11, 296.99]</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>[292.6, 295.83, 297.68, 299.3, 300.81, 302.24]</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>[292.6, 291.72, 291.86, 292.18, 292.59, 293.05]</t>
-        </is>
-      </c>
-      <c r="AU9" t="n">
-        <v>311.15</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>60900.7</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1010</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>₹1004.4 - ₹1018.4</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1032.39</v>
-      </c>
-      <c r="I10" t="n">
-        <v>980.86</v>
-      </c>
-      <c r="J10" t="n">
-        <v>955.17</v>
-      </c>
-      <c r="K10" t="n">
-        <v>850.98</v>
-      </c>
-      <c r="L10" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="M10" t="n">
-        <v>16.58</v>
-      </c>
-      <c r="N10" t="n">
-        <v>25.36</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-8.779999999999999</v>
-      </c>
-      <c r="P10" t="n">
-        <v>27.99</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="R10" t="n">
-        <v>44.6</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-1.57</v>
-      </c>
-      <c r="U10" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V10" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1010</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1105.23</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1105.23</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>968.01</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1002.9</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1017.1</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1024.2</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.39) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1047.16</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>969.87</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹60,900.70 Cr., a P/E ratio of 31.34, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.06 (Consolidation Zone), while MACD Line (16.58) trades below Signal (25.36) with an expanding histogram (-8.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.75% above the 200-day DMA (₹850.98). Daily volatility envelope is bounded by ATR(14) of ₹27.99.</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,010.00) is positioned above the 30-day DMA (₹980.86), 50-day DMA (₹955.17), and 200-day DMA (₹850.98). The price distance from 200 DMA is +14.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>[1010.0, 1022.84, 1035.67, 1048.51, 1061.34, 1074.18]</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>[1010.0, 1034.03, 1051.51, 1067.9, 1083.74, 1099.22]</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>[1010.0, 1014.44, 1023.79, 1033.96, 1044.55, 1055.4]</t>
-        </is>
-      </c>
-      <c r="AU10" t="n">
-        <v>1105.23</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>410340.82</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>412.5</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>₹411.26 - ₹414.36</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>417.47</v>
-      </c>
-      <c r="I11" t="n">
-        <v>408.48</v>
-      </c>
-      <c r="J11" t="n">
-        <v>399.68</v>
-      </c>
-      <c r="K11" t="n">
-        <v>399.79</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="P11" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="R11" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="U11" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X11" t="n">
-        <v>410.12</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>429.6</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>419.97</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>403.18</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>414.73</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>416.96</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>421.43</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>Low VIX (11.39) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>421.16</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>402.58</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹410,340.82 Cr., a P/E ratio of 20.21, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.58 (Consolidation Zone), while MACD Line (4.50) trades below Signal (6.01) with an expanding histogram (-1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹399.79). Daily volatility envelope is bounded by ATR(14) of ₹6.21.</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹412.50) is positioned above the 30-day DMA (₹408.48), 50-day DMA (₹399.68), and 200-day DMA (₹399.79). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>[412.5, 414.76, 417.03, 419.29, 421.56, 423.82]</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>[412.5, 417.25, 420.54, 423.6, 426.53, 429.38]</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>[412.5, 412.9, 414.39, 416.07, 417.83, 419.66]</t>
-        </is>
-      </c>
-      <c r="AU11" t="n">
-        <v>419.97</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>INDHOTEL</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>106000.03</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>732.75</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>₹729.55 - ₹737.55</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>745.5599999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>722.83</v>
-      </c>
-      <c r="J12" t="n">
-        <v>728.36</v>
-      </c>
-      <c r="K12" t="n">
-        <v>686</v>
-      </c>
-      <c r="L12" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>16.01</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="R12" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="U12" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X12" t="n">
-        <v>716.23</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>779.21</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>779.21</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>708.74</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>732.78</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>742.96</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>753.1799999999999</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>751.39</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>715.78</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,000.03 Cr., a P/E ratio of 48.72, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.74 (Bullish Momentum Zone), while MACD Line (-2.09) trades below Signal (-2.08) with an expanding histogram (-0.00). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.93% above the 200-day DMA (₹686.00). Daily volatility envelope is bounded by ATR(14) of ₹16.01.</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹732.75) is positioned above the 30-day DMA (₹722.83), 50-day DMA (₹728.36), and 200-day DMA (₹686.00). The price distance from 200 DMA is +5.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>[732.75, 734.95, 737.15, 739.34, 741.54, 743.74]</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>[732.75, 741.35, 746.2, 750.43, 754.35, 758.06]</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>[732.75, 730.15, 730.36, 731.03, 731.94, 733.0]</t>
-        </is>
-      </c>
-      <c r="AU12" t="n">
-        <v>779.21</v>
+        <v>688.79</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -713,10 +713,10 @@
         <v>103.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.29</v>
+        <v>11.39</v>
       </c>
       <c r="R2" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="S2" t="n">
         <v>0.28</v>
@@ -762,14 +762,14 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>54</v>
+        <v>54.1</v>
       </c>
       <c r="AJ2" t="n">
         <v>85.3</v>
@@ -781,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>3397.67</v>
+        <v>3390.34</v>
       </c>
       <c r="AN2" t="n">
-        <v>3137.08</v>
+        <v>3142.34</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.96, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -880,16 +880,16 @@
         <v>7.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.29</v>
+        <v>11.39</v>
       </c>
       <c r="R3" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="S3" t="n">
         <v>0.23</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.32</v>
+        <v>-1.3</v>
       </c>
       <c r="U3" t="n">
         <v>54.1</v>
@@ -929,14 +929,14 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>726.3</v>
+        <v>710.5</v>
       </c>
       <c r="AJ3" t="n">
         <v>182</v>
@@ -948,14 +948,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>338.27</v>
+        <v>337.95</v>
       </c>
       <c r="AN3" t="n">
-        <v>316.46</v>
+        <v>316.08</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹300,878.29 Cr., a P/E ratio of 726.33, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹300,878.29 Cr., a P/E ratio of 710.54, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1047,16 +1047,16 @@
         <v>61.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.29</v>
+        <v>11.39</v>
       </c>
       <c r="R4" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
       <c r="S4" t="n">
         <v>0.41</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.21</v>
+        <v>-1.22</v>
       </c>
       <c r="U4" t="n">
         <v>53.3</v>
@@ -1068,13 +1068,13 @@
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2229.93</v>
+        <v>2229.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>2224.27</v>
+        <v>2224.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>2004.42</v>
+        <v>2004.38</v>
       </c>
       <c r="AA4" t="n">
         <v>2177.59</v>
@@ -1096,14 +1096,14 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>51.3</v>
+        <v>48.5</v>
       </c>
       <c r="AJ4" t="n">
         <v>8.5</v>
@@ -1115,14 +1115,14 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>2334.79</v>
+        <v>2331.74</v>
       </c>
       <c r="AN4" t="n">
-        <v>2206.53</v>
+        <v>2209.55</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹63,031.23 Cr., a P/E ratio of 51.29, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹63,031.23 Cr., a P/E ratio of 48.55, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1137,21 +1137,21 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[2270.1, 2307.8, 2345.49, 2383.19, 2420.88, 2458.58]</t>
+          <t>[2270.1, 2307.76, 2345.42, 2383.08, 2420.74, 2458.4]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[2270.1, 2332.47, 2380.38, 2425.92, 2470.22, 2513.74]</t>
+          <t>[2270.1, 2332.43, 2380.31, 2425.81, 2470.08, 2513.56]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[2270.1, 2289.29, 2319.32, 2351.14, 2383.88, 2417.2]</t>
+          <t>[2270.1, 2289.26, 2319.25, 2351.03, 2383.73, 2417.02]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2004.42</v>
+        <v>2004.38</v>
       </c>
     </row>
     <row r="5">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30151.7</v>
+        <v>134777.73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,146 +1179,146 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>548.15</v>
+        <v>117.27</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹544.76 - ₹553.24</t>
+          <t>₹116.82 - ₹117.94</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>561.73</v>
+        <v>119.05</v>
       </c>
       <c r="I5" t="n">
-        <v>522.25</v>
+        <v>116.25</v>
       </c>
       <c r="J5" t="n">
-        <v>525.25</v>
+        <v>113.79</v>
       </c>
       <c r="K5" t="n">
-        <v>523.6799999999999</v>
+        <v>112.3</v>
       </c>
       <c r="L5" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="M5" t="n">
-        <v>10.41</v>
+        <v>0.59</v>
       </c>
       <c r="N5" t="n">
-        <v>10.21</v>
+        <v>0.78</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="P5" t="n">
-        <v>16.97</v>
+        <v>2.23</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.29</v>
+        <v>11.39</v>
       </c>
       <c r="R5" t="n">
-        <v>46.1</v>
+        <v>46.7</v>
       </c>
       <c r="S5" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.97</v>
+        <v>-1.04</v>
       </c>
       <c r="U5" t="n">
-        <v>46.7</v>
+        <v>50.8</v>
       </c>
       <c r="V5" t="n">
-        <v>4.8</v>
+        <v>2.38</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>529.08</v>
+        <v>114.1</v>
       </c>
       <c r="Y5" t="n">
-        <v>528.05</v>
+        <v>113.84</v>
       </c>
       <c r="Z5" t="n">
-        <v>520.29</v>
+        <v>110.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>522.6900000000001</v>
+        <v>113.93</v>
       </c>
       <c r="AB5" t="n">
-        <v>547.92</v>
+        <v>117.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>552.24</v>
+        <v>117.68</v>
       </c>
       <c r="AD5" t="n">
-        <v>556.3200000000001</v>
+        <v>118.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>53.8</v>
+        <v>54</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.23</v>
+        <v>-0.14</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>65.2</v>
+        <v>38.1</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>561.97</v>
+        <v>120.69</v>
       </c>
       <c r="AN5" t="n">
-        <v>533.88</v>
+        <v>113.94</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,151.70 Cr., a P/E ratio of 5.25, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,777.73 Cr., a P/E ratio of 6.10, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.80 (Consolidation Zone), while MACD Line (10.41) trades above Signal (10.21) with an expanding histogram (+0.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.69% above the 200-day DMA (₹523.68). Daily volatility envelope is bounded by ATR(14) of ₹16.97.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.02 (Consolidation Zone), while MACD Line (0.59) trades below Signal (0.78) with an expanding histogram (-0.19). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.71% above the 200-day DMA (₹112.30). Daily volatility envelope is bounded by ATR(14) of ₹2.23.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹548.15) is positioned above the 30-day DMA (₹522.25), 50-day DMA (₹525.25), and 200-day DMA (₹523.68). The price distance from 200 DMA is +3.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.27) is positioned above the 30-day DMA (₹116.25), 50-day DMA (₹113.79), and 200-day DMA (₹112.30). The price distance from 200 DMA is +3.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[548.15, 549.79, 551.44, 553.08, 554.73, 556.37]</t>
+          <t>[117.27, 118.09, 118.92, 119.74, 120.57, 121.39]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[548.15, 556.58, 561.04, 564.84, 568.3, 571.55]</t>
+          <t>[117.27, 118.99, 120.18, 121.29, 122.35, 123.38]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[548.15, 544.7, 544.24, 544.26, 544.54, 544.99]</t>
+          <t>[117.27, 117.43, 117.97, 118.59, 119.23, 119.9]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>520.29</v>
+        <v>110.1</v>
       </c>
     </row>
     <row r="6">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>134777.73</v>
+        <v>30151.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,146 +1346,146 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>117.27</v>
+        <v>548.15</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹116.82 - ₹117.94</t>
+          <t>₹544.76 - ₹553.24</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>119.05</v>
+        <v>561.73</v>
       </c>
       <c r="I6" t="n">
-        <v>116.25</v>
+        <v>522.25</v>
       </c>
       <c r="J6" t="n">
-        <v>113.79</v>
+        <v>525.25</v>
       </c>
       <c r="K6" t="n">
-        <v>112.3</v>
+        <v>523.6799999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="M6" t="n">
-        <v>0.59</v>
+        <v>10.41</v>
       </c>
       <c r="N6" t="n">
-        <v>0.78</v>
+        <v>10.21</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.19</v>
+        <v>0.2</v>
       </c>
       <c r="P6" t="n">
-        <v>2.23</v>
+        <v>16.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.29</v>
+        <v>11.39</v>
       </c>
       <c r="R6" t="n">
         <v>46</v>
       </c>
       <c r="S6" t="n">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.06</v>
+        <v>-1.98</v>
       </c>
       <c r="U6" t="n">
-        <v>50.8</v>
+        <v>46.7</v>
       </c>
       <c r="V6" t="n">
-        <v>2.38</v>
+        <v>4.8</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>114.1</v>
+        <v>529.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>113.84</v>
+        <v>528.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>110.1</v>
+        <v>520.29</v>
       </c>
       <c r="AA6" t="n">
-        <v>113.93</v>
+        <v>522.6900000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>117.09</v>
+        <v>547.92</v>
       </c>
       <c r="AC6" t="n">
-        <v>117.68</v>
+        <v>552.24</v>
       </c>
       <c r="AD6" t="n">
-        <v>118.09</v>
+        <v>556.3200000000001</v>
       </c>
       <c r="AE6" t="n">
-        <v>54</v>
+        <v>53.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.14</v>
+        <v>0.23</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>38.1</v>
+        <v>65.2</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>120.47</v>
+        <v>562.4299999999999</v>
       </c>
       <c r="AN6" t="n">
-        <v>114.25</v>
+        <v>533.6</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,777.73 Cr., a P/E ratio of 6.10, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,151.70 Cr., a P/E ratio of 5.23, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.02 (Consolidation Zone), while MACD Line (0.59) trades below Signal (0.78) with an expanding histogram (-0.19). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.71% above the 200-day DMA (₹112.30). Daily volatility envelope is bounded by ATR(14) of ₹2.23.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.80 (Consolidation Zone), while MACD Line (10.41) trades above Signal (10.21) with an expanding histogram (+0.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.69% above the 200-day DMA (₹523.68). Daily volatility envelope is bounded by ATR(14) of ₹16.97.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.27) is positioned above the 30-day DMA (₹116.25), 50-day DMA (₹113.79), and 200-day DMA (₹112.30). The price distance from 200 DMA is +3.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹548.15) is positioned above the 30-day DMA (₹522.25), 50-day DMA (₹525.25), and 200-day DMA (₹523.68). The price distance from 200 DMA is +3.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[117.27, 118.09, 118.92, 119.74, 120.57, 121.39]</t>
+          <t>[548.15, 549.79, 551.44, 553.08, 554.73, 556.37]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[117.27, 118.99, 120.18, 121.29, 122.35, 123.38]</t>
+          <t>[548.15, 556.58, 561.04, 564.84, 568.3, 571.55]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[117.27, 117.43, 117.97, 118.59, 119.23, 119.9]</t>
+          <t>[548.15, 544.7, 544.24, 544.26, 544.54, 544.99]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>110.1</v>
+        <v>520.29</v>
       </c>
     </row>
     <row r="7">
@@ -1548,10 +1548,10 @@
         <v>206.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>12.29</v>
+        <v>11.39</v>
       </c>
       <c r="R7" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
       <c r="S7" t="n">
         <v>0.53</v>
@@ -1569,13 +1569,13 @@
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>11060.34</v>
+        <v>11060.13</v>
       </c>
       <c r="Y7" t="n">
         <v>10957.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>10360.47</v>
+        <v>10360.28</v>
       </c>
       <c r="AA7" t="n">
         <v>10971.61</v>
@@ -1597,14 +1597,14 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="AJ7" t="n">
         <v>24.2</v>
@@ -1616,14 +1616,14 @@
         <v>11.6</v>
       </c>
       <c r="AM7" t="n">
-        <v>11614.58</v>
+        <v>11585.98</v>
       </c>
       <c r="AN7" t="n">
-        <v>10967.84</v>
+        <v>10945.86</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹125,561.34 Cr., a P/E ratio of 14.17, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
+          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹125,561.34 Cr., a P/E ratio of 13.83, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
@@ -1638,21 +1638,21 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[11282.0, 11446.89, 11611.77, 11776.66, 11941.55, 12106.44]</t>
+          <t>[11282.0, 11446.68, 11611.36, 11776.04, 11940.72, 12105.41]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[11282.0, 11529.66, 11728.83, 11920.03, 12107.09, 12291.52]</t>
+          <t>[11282.0, 11529.45, 11728.42, 11919.41, 12106.27, 12290.49]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[11282.0, 11384.81, 11523.98, 11669.14, 11817.39, 11967.63]</t>
+          <t>[11282.0, 11384.6, 11523.57, 11668.52, 11816.57, 11966.59]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>10360.47</v>
+        <v>10360.28</v>
       </c>
     </row>
     <row r="8">
@@ -1715,16 +1715,16 @@
         <v>16.01</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.29</v>
+        <v>11.39</v>
       </c>
       <c r="R8" t="n">
-        <v>40.9</v>
+        <v>40.7</v>
       </c>
       <c r="S8" t="n">
         <v>0.24</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.49</v>
+        <v>-1.5</v>
       </c>
       <c r="U8" t="n">
         <v>44.3</v>
@@ -1764,14 +1764,14 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.29) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>48.7</v>
+        <v>48.3</v>
       </c>
       <c r="AJ8" t="n">
         <v>15.1</v>
@@ -1783,14 +1783,14 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>749.62</v>
+        <v>751.11</v>
       </c>
       <c r="AN8" t="n">
-        <v>712.89</v>
+        <v>713.8</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,000.03 Cr., a P/E ratio of 48.72, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,000.03 Cr., a P/E ratio of 48.30, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU8"/>
+  <dimension ref="A1:AU12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25000</v>
+        <v>179474.08</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3260</v>
+        <v>2208.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹3239.25 - ₹3291.13</t>
+          <t>₹2197.33 - ₹2226.01</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3343.01</v>
+        <v>2254.68</v>
       </c>
       <c r="I2" t="n">
-        <v>3137.32</v>
+        <v>2200.73</v>
       </c>
       <c r="J2" t="n">
-        <v>2981.04</v>
+        <v>2129.15</v>
       </c>
       <c r="K2" t="n">
-        <v>2689.42</v>
+        <v>2052.76</v>
       </c>
       <c r="L2" t="n">
-        <v>19.4</v>
+        <v>5.22</v>
       </c>
       <c r="M2" t="n">
-        <v>74.77</v>
+        <v>3.6</v>
       </c>
       <c r="N2" t="n">
-        <v>102.69</v>
+        <v>15.47</v>
       </c>
       <c r="O2" t="n">
-        <v>-27.92</v>
+        <v>-11.86</v>
       </c>
       <c r="P2" t="n">
-        <v>103.76</v>
+        <v>57.35</v>
       </c>
       <c r="Q2" t="n">
         <v>11.39</v>
       </c>
       <c r="R2" t="n">
-        <v>48.2</v>
+        <v>49.4</v>
       </c>
       <c r="S2" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.65</v>
+        <v>-1.43</v>
       </c>
       <c r="U2" t="n">
-        <v>53.3</v>
+        <v>51.8</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>3191.82</v>
+        <v>2137.07</v>
       </c>
       <c r="Y2" t="n">
-        <v>3184.06</v>
+        <v>2132.74</v>
       </c>
       <c r="Z2" t="n">
-        <v>2542.65</v>
+        <v>2047.46</v>
       </c>
       <c r="AA2" t="n">
-        <v>3104.35</v>
+        <v>2122.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>3268.33</v>
+        <v>2191.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>3306.56</v>
+        <v>2226.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>3353.13</v>
+        <v>2244.33</v>
       </c>
       <c r="AE2" t="n">
-        <v>46.5</v>
+        <v>33.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>54.1</v>
+        <v>36.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>85.3</v>
+        <v>-0.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>55.6</v>
+        <v>7</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>3390.34</v>
+        <v>2277.69</v>
       </c>
       <c r="AN2" t="n">
-        <v>3142.34</v>
+        <v>2141.97</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>HYUNDAI operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹179,474.08 Cr., a P/E ratio of 36.23, and YoY Revenue Growth of -0.5%, the company demonstrates strong institutional backing, solid operating profit margins (7.00%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.45 (Consolidation Zone), while MACD Line (74.77) trades below Signal (102.69) with an expanding histogram (-27.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.40% above the 200-day DMA (₹2689.42). Daily volatility envelope is bounded by ATR(14) of ₹103.76.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.70 (Consolidation Zone), while MACD Line (3.60) trades below Signal (15.47) with an expanding histogram (-11.86). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.22% above the 200-day DMA (₹2052.76). Daily volatility envelope is bounded by ATR(14) of ₹57.35.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,260.00) is positioned above the 30-day DMA (₹3,137.32), 50-day DMA (₹2,981.04), and 200-day DMA (₹2,689.42). The price distance from 200 DMA is +19.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HYUNDAI. Current Market Price (₹2,208.80) is positioned above the 30-day DMA (₹2,200.73), 50-day DMA (₹2,129.15), and 200-day DMA (₹2,052.76). The price distance from 200 DMA is +5.22%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[3260.0, 3303.43, 3346.86, 3390.28, 3433.71, 3477.14]</t>
+          <t>[2208.8, 2215.43, 2222.05, 2228.68, 2235.31, 2241.93]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[3260.0, 3344.93, 3405.55, 3462.17, 3516.72, 3569.95]</t>
+          <t>[2208.8, 2238.37, 2254.49, 2268.41, 2281.19, 2293.23]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[3260.0, 3272.3, 3302.83, 3336.37, 3371.45, 3407.53]</t>
+          <t>[2208.8, 2198.22, 2197.72, 2198.88, 2200.9, 2203.46]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2542.65</v>
+        <v>2047.46</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>300878.29</v>
+        <v>25000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,87 +845,87 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>326.85</v>
+        <v>3260</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹325.35 - ₹329.1</t>
+          <t>₹3239.25 - ₹3291.13</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>332.85</v>
+        <v>3343.01</v>
       </c>
       <c r="I3" t="n">
-        <v>322.09</v>
+        <v>3137.32</v>
       </c>
       <c r="J3" t="n">
-        <v>311.9</v>
+        <v>2981.04</v>
       </c>
       <c r="K3" t="n">
-        <v>274.44</v>
+        <v>2689.42</v>
       </c>
       <c r="L3" t="n">
-        <v>17.46</v>
+        <v>19.4</v>
       </c>
       <c r="M3" t="n">
-        <v>1.94</v>
+        <v>74.77</v>
       </c>
       <c r="N3" t="n">
-        <v>3.71</v>
+        <v>102.69</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.77</v>
+        <v>-27.92</v>
       </c>
       <c r="P3" t="n">
-        <v>7.5</v>
+        <v>103.76</v>
       </c>
       <c r="Q3" t="n">
         <v>11.39</v>
       </c>
       <c r="R3" t="n">
-        <v>47.4</v>
+        <v>48.6</v>
       </c>
       <c r="S3" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3</v>
+        <v>-1.62</v>
       </c>
       <c r="U3" t="n">
-        <v>54.1</v>
+        <v>53.3</v>
       </c>
       <c r="V3" t="n">
-        <v>2.51</v>
+        <v>3.4</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>316.24</v>
+        <v>3191.99</v>
       </c>
       <c r="Y3" t="n">
-        <v>315.6</v>
+        <v>3184.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>305.81</v>
+        <v>2542.79</v>
       </c>
       <c r="AA3" t="n">
-        <v>315.61</v>
+        <v>3104.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>327.43</v>
+        <v>3268.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>329.16</v>
+        <v>3306.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>331.48</v>
+        <v>3353.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>39.7</v>
+        <v>46.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -936,55 +936,55 @@
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>710.5</v>
+        <v>54.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>182</v>
+        <v>85.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.6</v>
+        <v>55.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>337.95</v>
+        <v>3396.41</v>
       </c>
       <c r="AN3" t="n">
-        <v>316.08</v>
+        <v>3142.02</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹300,878.29 Cr., a P/E ratio of 710.54, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.71 (Consolidation Zone), while MACD Line (1.94) trades below Signal (3.71) with an expanding histogram (-1.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.46% above the 200-day DMA (₹274.44). Daily volatility envelope is bounded by ATR(14) of ₹7.50.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.45 (Consolidation Zone), while MACD Line (74.77) trades below Signal (102.69) with an expanding histogram (-27.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.40% above the 200-day DMA (₹2689.42). Daily volatility envelope is bounded by ATR(14) of ₹103.76.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹326.85) is positioned above the 30-day DMA (₹322.09), 50-day DMA (₹311.90), and 200-day DMA (₹274.44). The price distance from 200 DMA is +17.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,260.00) is positioned above the 30-day DMA (₹3,137.32), 50-day DMA (₹2,981.04), and 200-day DMA (₹2,689.42). The price distance from 200 DMA is +19.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[326.85, 327.83, 328.81, 329.79, 330.77, 331.75]</t>
+          <t>[3260.0, 3303.61, 3347.22, 3390.83, 3434.45, 3478.06]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[326.85, 330.83, 333.05, 334.99, 336.77, 338.46]</t>
+          <t>[3260.0, 3345.12, 3405.92, 3462.72, 3517.46, 3570.87]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[326.85, 325.58, 325.63, 325.9, 326.27, 326.72]</t>
+          <t>[3260.0, 3272.48, 3303.2, 3336.92, 3372.19, 3408.45]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>305.81</v>
+        <v>2542.79</v>
       </c>
     </row>
     <row r="4">
@@ -995,16 +995,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>63031.23</v>
+        <v>300878.29</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,146 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2270.1</v>
+        <v>326.85</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹2257.76 - ₹2288.6</t>
+          <t>₹325.35 - ₹329.1</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2319.44</v>
+        <v>332.85</v>
       </c>
       <c r="I4" t="n">
-        <v>2126.16</v>
+        <v>322.09</v>
       </c>
       <c r="J4" t="n">
-        <v>2009.95</v>
+        <v>311.9</v>
       </c>
       <c r="K4" t="n">
-        <v>1956.8</v>
+        <v>274.44</v>
       </c>
       <c r="L4" t="n">
-        <v>8.34</v>
+        <v>17.46</v>
       </c>
       <c r="M4" t="n">
-        <v>33.95</v>
+        <v>1.94</v>
       </c>
       <c r="N4" t="n">
-        <v>54.05</v>
+        <v>3.71</v>
       </c>
       <c r="O4" t="n">
-        <v>-20.1</v>
+        <v>-1.77</v>
       </c>
       <c r="P4" t="n">
-        <v>61.68</v>
+        <v>7.5</v>
       </c>
       <c r="Q4" t="n">
         <v>11.39</v>
       </c>
       <c r="R4" t="n">
-        <v>46.8</v>
+        <v>47.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0.41</v>
+        <v>0.23</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.22</v>
+        <v>-1.29</v>
       </c>
       <c r="U4" t="n">
-        <v>53.3</v>
+        <v>54.1</v>
       </c>
       <c r="V4" t="n">
-        <v>3.12</v>
+        <v>2.51</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2229.9</v>
+        <v>316.24</v>
       </c>
       <c r="Y4" t="n">
-        <v>2224.23</v>
+        <v>315.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>2004.38</v>
+        <v>305.81</v>
       </c>
       <c r="AA4" t="n">
-        <v>2177.59</v>
+        <v>315.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>2228.83</v>
+        <v>327.43</v>
       </c>
       <c r="AC4" t="n">
-        <v>2311.36</v>
+        <v>329.16</v>
       </c>
       <c r="AD4" t="n">
-        <v>2352.63</v>
+        <v>331.48</v>
       </c>
       <c r="AE4" t="n">
-        <v>43.7</v>
+        <v>39.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>48.5</v>
+        <v>710.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8.5</v>
+        <v>182</v>
       </c>
       <c r="AK4" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>2331.74</v>
+        <v>337.95</v>
       </c>
       <c r="AN4" t="n">
-        <v>2209.55</v>
+        <v>316.91</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹63,031.23 Cr., a P/E ratio of 48.55, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹300,878.29 Cr., a P/E ratio of 710.54, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.67 (Consolidation Zone), while MACD Line (33.95) trades below Signal (54.05) with an expanding histogram (-20.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.34% above the 200-day DMA (₹1956.80). Daily volatility envelope is bounded by ATR(14) of ₹61.68.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.71 (Consolidation Zone), while MACD Line (1.94) trades below Signal (3.71) with an expanding histogram (-1.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.46% above the 200-day DMA (₹274.44). Daily volatility envelope is bounded by ATR(14) of ₹7.50.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,270.10) is positioned above the 30-day DMA (₹2,126.16), 50-day DMA (₹2,009.95), and 200-day DMA (₹1,956.80). The price distance from 200 DMA is +8.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹326.85) is positioned above the 30-day DMA (₹322.09), 50-day DMA (₹311.90), and 200-day DMA (₹274.44). The price distance from 200 DMA is +17.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[2270.1, 2307.76, 2345.42, 2383.08, 2420.74, 2458.4]</t>
+          <t>[326.85, 327.83, 328.81, 329.79, 330.77, 331.75]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[2270.1, 2332.43, 2380.31, 2425.81, 2470.08, 2513.56]</t>
+          <t>[326.85, 330.83, 333.05, 334.99, 336.77, 338.46]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[2270.1, 2289.26, 2319.25, 2351.03, 2383.73, 2417.02]</t>
+          <t>[326.85, 325.58, 325.63, 325.9, 326.27, 326.72]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2004.38</v>
+        <v>305.81</v>
       </c>
     </row>
     <row r="5">
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>134777.73</v>
+        <v>63031.23</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,39 +1179,39 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>117.27</v>
+        <v>2270.1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹116.82 - ₹117.94</t>
+          <t>₹2257.76 - ₹2288.6</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>119.05</v>
+        <v>2319.44</v>
       </c>
       <c r="I5" t="n">
-        <v>116.25</v>
+        <v>2126.16</v>
       </c>
       <c r="J5" t="n">
-        <v>113.79</v>
+        <v>2009.95</v>
       </c>
       <c r="K5" t="n">
-        <v>112.3</v>
+        <v>1956.8</v>
       </c>
       <c r="L5" t="n">
-        <v>3.71</v>
+        <v>8.34</v>
       </c>
       <c r="M5" t="n">
-        <v>0.59</v>
+        <v>33.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0.78</v>
+        <v>54.05</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.19</v>
+        <v>-20.1</v>
       </c>
       <c r="P5" t="n">
-        <v>2.23</v>
+        <v>61.68</v>
       </c>
       <c r="Q5" t="n">
         <v>11.39</v>
@@ -1220,46 +1220,46 @@
         <v>46.7</v>
       </c>
       <c r="S5" t="n">
-        <v>0.28</v>
+        <v>0.41</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.04</v>
+        <v>-1.22</v>
       </c>
       <c r="U5" t="n">
-        <v>50.8</v>
+        <v>53.3</v>
       </c>
       <c r="V5" t="n">
-        <v>2.38</v>
+        <v>3.12</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>114.1</v>
+        <v>2229.93</v>
       </c>
       <c r="Y5" t="n">
-        <v>113.84</v>
+        <v>2224.27</v>
       </c>
       <c r="Z5" t="n">
-        <v>110.1</v>
+        <v>2004.42</v>
       </c>
       <c r="AA5" t="n">
-        <v>113.93</v>
+        <v>2177.59</v>
       </c>
       <c r="AB5" t="n">
-        <v>117.09</v>
+        <v>2228.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>117.68</v>
+        <v>2311.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>118.09</v>
+        <v>2352.63</v>
       </c>
       <c r="AE5" t="n">
-        <v>54</v>
+        <v>43.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1270,55 +1270,55 @@
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.1</v>
+        <v>51.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-6.4</v>
+        <v>8.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>38.1</v>
+        <v>5.2</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>120.69</v>
+        <v>2332.53</v>
       </c>
       <c r="AN5" t="n">
-        <v>113.94</v>
+        <v>2209.13</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,777.73 Cr., a P/E ratio of 6.10, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹63,031.23 Cr., a P/E ratio of 51.28, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.02 (Consolidation Zone), while MACD Line (0.59) trades below Signal (0.78) with an expanding histogram (-0.19). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.71% above the 200-day DMA (₹112.30). Daily volatility envelope is bounded by ATR(14) of ₹2.23.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.67 (Consolidation Zone), while MACD Line (33.95) trades below Signal (54.05) with an expanding histogram (-20.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.34% above the 200-day DMA (₹1956.80). Daily volatility envelope is bounded by ATR(14) of ₹61.68.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.27) is positioned above the 30-day DMA (₹116.25), 50-day DMA (₹113.79), and 200-day DMA (₹112.30). The price distance from 200 DMA is +3.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,270.10) is positioned above the 30-day DMA (₹2,126.16), 50-day DMA (₹2,009.95), and 200-day DMA (₹1,956.80). The price distance from 200 DMA is +8.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[117.27, 118.09, 118.92, 119.74, 120.57, 121.39]</t>
+          <t>[2270.1, 2307.8, 2345.49, 2383.19, 2420.88, 2458.58]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[117.27, 118.99, 120.18, 121.29, 122.35, 123.38]</t>
+          <t>[2270.1, 2332.47, 2380.38, 2425.92, 2470.22, 2513.74]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[117.27, 117.43, 117.97, 118.59, 119.23, 119.9]</t>
+          <t>[2270.1, 2289.29, 2319.32, 2351.14, 2383.88, 2417.2]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>110.1</v>
+        <v>2004.42</v>
       </c>
     </row>
     <row r="6">
@@ -1384,13 +1384,13 @@
         <v>11.39</v>
       </c>
       <c r="R6" t="n">
-        <v>46</v>
+        <v>46.6</v>
       </c>
       <c r="S6" t="n">
         <v>0.17</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.98</v>
+        <v>-1.94</v>
       </c>
       <c r="U6" t="n">
         <v>46.7</v>
@@ -1437,7 +1437,7 @@
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AJ6" t="n">
         <v>14.5</v>
@@ -1449,14 +1449,14 @@
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>562.4299999999999</v>
+        <v>561.6799999999999</v>
       </c>
       <c r="AN6" t="n">
-        <v>533.6</v>
+        <v>534.23</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,151.70 Cr., a P/E ratio of 5.23, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,151.70 Cr., a P/E ratio of 5.26, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>125561.34</v>
+        <v>134777.73</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,146 +1513,146 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>11282</v>
+        <v>117.27</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹11240.61 - ₹11344.08</t>
+          <t>₹116.82 - ₹117.94</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>11447.54</v>
+        <v>119.05</v>
       </c>
       <c r="I7" t="n">
-        <v>11278.87</v>
+        <v>116.25</v>
       </c>
       <c r="J7" t="n">
-        <v>11082.86</v>
+        <v>113.79</v>
       </c>
       <c r="K7" t="n">
-        <v>10584.38</v>
+        <v>112.3</v>
       </c>
       <c r="L7" t="n">
-        <v>3.27</v>
+        <v>3.71</v>
       </c>
       <c r="M7" t="n">
-        <v>-41.34</v>
+        <v>0.59</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.16</v>
+        <v>0.78</v>
       </c>
       <c r="O7" t="n">
-        <v>-39.18</v>
+        <v>-0.19</v>
       </c>
       <c r="P7" t="n">
-        <v>206.93</v>
+        <v>2.23</v>
       </c>
       <c r="Q7" t="n">
         <v>11.39</v>
       </c>
       <c r="R7" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.53</v>
+        <v>0.28</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.06</v>
       </c>
       <c r="U7" t="n">
-        <v>50</v>
+        <v>50.8</v>
       </c>
       <c r="V7" t="n">
-        <v>3.95</v>
+        <v>2.38</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>11060.13</v>
+        <v>114.1</v>
       </c>
       <c r="Y7" t="n">
-        <v>10957.24</v>
+        <v>113.84</v>
       </c>
       <c r="Z7" t="n">
-        <v>10360.28</v>
+        <v>110.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>10971.61</v>
+        <v>113.93</v>
       </c>
       <c r="AB7" t="n">
-        <v>11238.33</v>
+        <v>117.09</v>
       </c>
       <c r="AC7" t="n">
-        <v>11406.66</v>
+        <v>117.68</v>
       </c>
       <c r="AD7" t="n">
-        <v>11531.33</v>
+        <v>118.09</v>
       </c>
       <c r="AE7" t="n">
-        <v>36.5</v>
+        <v>54</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Low VIX (11.39) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>13.8</v>
+        <v>6.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24.2</v>
+        <v>-6.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>734.6</v>
+        <v>38.1</v>
       </c>
       <c r="AL7" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>11585.98</v>
+        <v>120.69</v>
       </c>
       <c r="AN7" t="n">
-        <v>10945.86</v>
+        <v>113.88</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹125,561.34 Cr., a P/E ratio of 13.83, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,777.73 Cr., a P/E ratio of 6.10, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 36.48 (Consolidation Zone), while MACD Line (-41.34) trades below Signal (-2.16) with an expanding histogram (-39.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.27% above the 200-day DMA (₹10584.38). Daily volatility envelope is bounded by ATR(14) of ₹206.93.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.02 (Consolidation Zone), while MACD Line (0.59) trades below Signal (0.78) with an expanding histogram (-0.19). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.71% above the 200-day DMA (₹112.30). Daily volatility envelope is bounded by ATR(14) of ₹2.23.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,282.00) is positioned above the 30-day DMA (₹11,278.87), 50-day DMA (₹11,082.86), and 200-day DMA (₹10,584.38). The price distance from 200 DMA is +3.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.27) is positioned above the 30-day DMA (₹116.25), 50-day DMA (₹113.79), and 200-day DMA (₹112.30). The price distance from 200 DMA is +3.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[11282.0, 11446.68, 11611.36, 11776.04, 11940.72, 12105.41]</t>
+          <t>[117.27, 118.09, 118.92, 119.74, 120.57, 121.39]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[11282.0, 11529.45, 11728.42, 11919.41, 12106.27, 12290.49]</t>
+          <t>[117.27, 118.98, 120.18, 121.29, 122.35, 123.38]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[11282.0, 11384.6, 11523.57, 11668.52, 11816.57, 11966.59]</t>
+          <t>[117.27, 117.43, 117.97, 118.58, 119.23, 119.9]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>10360.28</v>
+        <v>110.1</v>
       </c>
     </row>
     <row r="8">
@@ -1663,162 +1663,830 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>106000.03</v>
+        <v>125561.34</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>732.75</v>
+        <v>11282</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹729.55 - ₹737.55</t>
+          <t>₹11240.61 - ₹11344.08</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>745.5599999999999</v>
+        <v>11447.54</v>
       </c>
       <c r="I8" t="n">
-        <v>722.83</v>
+        <v>11278.87</v>
       </c>
       <c r="J8" t="n">
-        <v>728.36</v>
+        <v>11082.86</v>
       </c>
       <c r="K8" t="n">
-        <v>686</v>
+        <v>10584.38</v>
       </c>
       <c r="L8" t="n">
-        <v>5.93</v>
+        <v>3.27</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.09</v>
+        <v>-41.34</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.08</v>
+        <v>-2.16</v>
       </c>
       <c r="O8" t="n">
-        <v>-0</v>
+        <v>-39.18</v>
       </c>
       <c r="P8" t="n">
-        <v>16.01</v>
+        <v>206.93</v>
       </c>
       <c r="Q8" t="n">
         <v>11.39</v>
       </c>
       <c r="R8" t="n">
-        <v>40.7</v>
+        <v>46</v>
       </c>
       <c r="S8" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>44.3</v>
+        <v>50</v>
       </c>
       <c r="V8" t="n">
-        <v>11.45</v>
+        <v>3.95</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>699.79</v>
+        <v>11060.34</v>
       </c>
       <c r="Y8" t="n">
-        <v>688.79</v>
+        <v>10957.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>688.79</v>
+        <v>10360.47</v>
       </c>
       <c r="AA8" t="n">
-        <v>708.74</v>
+        <v>10971.61</v>
       </c>
       <c r="AB8" t="n">
-        <v>732.78</v>
+        <v>11238.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>742.96</v>
+        <v>11406.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>753.1799999999999</v>
+        <v>11531.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>58.7</v>
+        <v>36.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>48.3</v>
+        <v>14.2</v>
       </c>
       <c r="AJ8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>734.6</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>11571.98</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>10961.59</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹125,561.34 Cr., a P/E ratio of 14.18, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 36.48 (Consolidation Zone), while MACD Line (-41.34) trades below Signal (-2.16) with an expanding histogram (-39.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.27% above the 200-day DMA (₹10584.38). Daily volatility envelope is bounded by ATR(14) of ₹206.93.</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,282.00) is positioned above the 30-day DMA (₹11,278.87), 50-day DMA (₹11,082.86), and 200-day DMA (₹10,584.38). The price distance from 200 DMA is +3.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>[11282.0, 11446.89, 11611.77, 11776.66, 11941.55, 12106.44]</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>[11282.0, 11529.66, 11728.83, 11920.03, 12107.09, 12291.52]</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>[11282.0, 11384.81, 11523.98, 11669.14, 11817.39, 11967.63]</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>10360.47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>60900.7</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1010</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>₹1004.4 - ₹1018.4</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1032.39</v>
+      </c>
+      <c r="I9" t="n">
+        <v>980.86</v>
+      </c>
+      <c r="J9" t="n">
+        <v>955.17</v>
+      </c>
+      <c r="K9" t="n">
+        <v>850.98</v>
+      </c>
+      <c r="L9" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="N9" t="n">
+        <v>25.36</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="P9" t="n">
+        <v>27.99</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="R9" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="U9" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X9" t="n">
+        <v>988.27</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>985.89</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>903.71</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>968.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1002.9</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1017.1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1024.2</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Low VIX (11.39) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1051.33</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>971.39</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹60,900.70 Cr., a P/E ratio of 31.35, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.06 (Consolidation Zone), while MACD Line (16.58) trades below Signal (25.36) with an expanding histogram (-8.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.75% above the 200-day DMA (₹850.98). Daily volatility envelope is bounded by ATR(14) of ₹27.99.</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,010.00) is positioned above the 30-day DMA (₹980.86), 50-day DMA (₹955.17), and 200-day DMA (₹850.98). The price distance from 200 DMA is +14.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>[1010.0, 1022.84, 1035.67, 1048.51, 1061.34, 1074.18]</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>[1010.0, 1034.03, 1051.51, 1067.9, 1083.74, 1099.22]</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>[1010.0, 1014.44, 1023.79, 1033.96, 1044.55, 1055.4]</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>903.71</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>43890</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>292.6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>₹291.43 - ₹294.36</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>297.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>287.18</v>
+      </c>
+      <c r="J10" t="n">
+        <v>283.36</v>
+      </c>
+      <c r="K10" t="n">
+        <v>278.69</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="R10" t="n">
+        <v>45</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="U10" t="n">
+        <v>50.8</v>
+      </c>
+      <c r="V10" t="n">
+        <v>5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X10" t="n">
+        <v>280.13</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>279.66</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>268.68</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>283.79</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>289.77</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>295.44</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>298.27</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>-53.2</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>301.71</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>284.49</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,890.00 Cr., a P/E ratio of 10.43, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.46 (Consolidation Zone), while MACD Line (-0.10) trades below Signal (1.17) with an expanding histogram (-1.27). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +1.71% above the 200-day DMA (₹278.69). Daily volatility envelope is bounded by ATR(14) of ₹5.88.</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹292.60) is positioned above the 30-day DMA (₹287.18), 50-day DMA (₹283.36), and 200-day DMA (₹278.69). The price distance from 200 DMA is +1.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>[292.6, 293.48, 294.36, 295.23, 296.11, 296.99]</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>[292.6, 295.83, 297.68, 299.3, 300.81, 302.24]</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>[292.6, 291.72, 291.86, 292.18, 292.59, 293.05]</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>268.68</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>410340.82</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>₹411.26 - ₹414.36</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>417.47</v>
+      </c>
+      <c r="I11" t="n">
+        <v>408.48</v>
+      </c>
+      <c r="J11" t="n">
+        <v>399.68</v>
+      </c>
+      <c r="K11" t="n">
+        <v>399.79</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-1.51</v>
+      </c>
+      <c r="P11" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="R11" t="n">
+        <v>47</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="U11" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X11" t="n">
+        <v>400.72</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>412.37</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>412.37</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>403.18</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>414.73</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>416.96</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>421.43</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Low VIX (11.39) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>421</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>403.83</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹410,340.82 Cr., a P/E ratio of 20.20, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.58 (Consolidation Zone), while MACD Line (4.50) trades below Signal (6.01) with an expanding histogram (-1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹399.79). Daily volatility envelope is bounded by ATR(14) of ₹6.21.</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹412.50) is positioned above the 30-day DMA (₹408.48), 50-day DMA (₹399.68), and 200-day DMA (₹399.79). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>[412.5, 414.78, 417.05, 419.33, 421.6, 423.88]</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>[412.5, 417.26, 420.56, 423.63, 426.57, 429.43]</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>[412.5, 412.91, 414.42, 416.1, 417.88, 419.71]</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>412.37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>106000.03</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>732.75</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>₹729.55 - ₹737.55</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>745.5599999999999</v>
+      </c>
+      <c r="I12" t="n">
+        <v>722.83</v>
+      </c>
+      <c r="J12" t="n">
+        <v>728.36</v>
+      </c>
+      <c r="K12" t="n">
+        <v>686</v>
+      </c>
+      <c r="L12" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>16.01</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="R12" t="n">
+        <v>41</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="U12" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="V12" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X12" t="n">
+        <v>699.79</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>688.79</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>688.79</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>708.74</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>732.78</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>742.96</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>753.1799999999999</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>15.1</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AK12" t="n">
         <v>20.9</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AL12" t="n">
         <v>15</v>
       </c>
-      <c r="AM8" t="n">
-        <v>751.11</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>713.8</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,000.03 Cr., a P/E ratio of 48.30, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
+      <c r="AM12" t="n">
+        <v>750.46</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>714.77</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,000.03 Cr., a P/E ratio of 48.56, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.74 (Bullish Momentum Zone), while MACD Line (-2.09) trades below Signal (-2.08) with an expanding histogram (-0.00). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.93% above the 200-day DMA (₹686.00). Daily volatility envelope is bounded by ATR(14) of ₹16.01.</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹732.75) is positioned above the 30-day DMA (₹722.83), 50-day DMA (₹728.36), and 200-day DMA (₹686.00). The price distance from 200 DMA is +5.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>[732.75, 734.95, 737.15, 739.34, 741.54, 743.74]</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>[732.75, 741.35, 746.2, 750.43, 754.35, 758.06]</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AT12" t="inlineStr">
         <is>
           <t>[732.75, 730.15, 730.36, 731.03, 731.94, 733.0]</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AU12" t="n">
         <v>688.79</v>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU12"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,13 +716,13 @@
         <v>11.39</v>
       </c>
       <c r="R2" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="S2" t="n">
         <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.43</v>
+        <v>-1.45</v>
       </c>
       <c r="U2" t="n">
         <v>51.8</v>
@@ -734,13 +734,13 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2137.07</v>
+        <v>2208.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>2132.74</v>
+        <v>2401.92</v>
       </c>
       <c r="Z2" t="n">
-        <v>2047.46</v>
+        <v>2401.92</v>
       </c>
       <c r="AA2" t="n">
         <v>2122.78</v>
@@ -781,10 +781,10 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>2277.69</v>
+        <v>2274.45</v>
       </c>
       <c r="AN2" t="n">
-        <v>2141.97</v>
+        <v>2143.25</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2047.46</v>
+        <v>2401.92</v>
       </c>
     </row>
     <row r="3">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25000</v>
+        <v>82971.60000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         <v>11.39</v>
       </c>
       <c r="R3" t="n">
-        <v>48.6</v>
+        <v>48.2</v>
       </c>
       <c r="S3" t="n">
         <v>0.28</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.62</v>
+        <v>-1.65</v>
       </c>
       <c r="U3" t="n">
         <v>53.3</v>
@@ -901,13 +901,13 @@
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>3191.99</v>
+        <v>3260</v>
       </c>
       <c r="Y3" t="n">
-        <v>3184.23</v>
+        <v>4235.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>2542.79</v>
+        <v>4235.2</v>
       </c>
       <c r="AA3" t="n">
         <v>3104.35</v>
@@ -948,14 +948,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>3396.41</v>
+        <v>3393.68</v>
       </c>
       <c r="AN3" t="n">
-        <v>3142.02</v>
+        <v>3148.59</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹82,971.60 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -970,21 +970,21 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[3260.0, 3303.61, 3347.22, 3390.83, 3434.45, 3478.06]</t>
+          <t>[3260.0, 3303.43, 3346.86, 3390.28, 3433.71, 3477.14]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[3260.0, 3345.12, 3405.92, 3462.72, 3517.46, 3570.87]</t>
+          <t>[3260.0, 3344.93, 3405.55, 3462.17, 3516.72, 3569.95]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[3260.0, 3272.48, 3303.2, 3336.92, 3372.19, 3408.45]</t>
+          <t>[3260.0, 3272.3, 3302.83, 3336.37, 3371.45, 3407.53]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2542.79</v>
+        <v>4235.2</v>
       </c>
     </row>
     <row r="4">
@@ -995,16 +995,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>300878.29</v>
+        <v>63031.23</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,146 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>326.85</v>
+        <v>2270.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹325.35 - ₹329.1</t>
+          <t>₹2257.76 - ₹2288.6</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>332.85</v>
+        <v>2319.44</v>
       </c>
       <c r="I4" t="n">
-        <v>322.09</v>
+        <v>2126.16</v>
       </c>
       <c r="J4" t="n">
-        <v>311.9</v>
+        <v>2009.95</v>
       </c>
       <c r="K4" t="n">
-        <v>274.44</v>
+        <v>1956.8</v>
       </c>
       <c r="L4" t="n">
-        <v>17.46</v>
+        <v>8.34</v>
       </c>
       <c r="M4" t="n">
-        <v>1.94</v>
+        <v>33.95</v>
       </c>
       <c r="N4" t="n">
-        <v>3.71</v>
+        <v>54.05</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.77</v>
+        <v>-20.1</v>
       </c>
       <c r="P4" t="n">
-        <v>7.5</v>
+        <v>61.68</v>
       </c>
       <c r="Q4" t="n">
         <v>11.39</v>
       </c>
       <c r="R4" t="n">
-        <v>47.6</v>
+        <v>47.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.29</v>
+        <v>-1.18</v>
       </c>
       <c r="U4" t="n">
-        <v>54.1</v>
+        <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>2.51</v>
+        <v>3.12</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>316.24</v>
+        <v>2270.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>315.6</v>
+        <v>2613.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>305.81</v>
+        <v>2613.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>315.61</v>
+        <v>2177.59</v>
       </c>
       <c r="AB4" t="n">
-        <v>327.43</v>
+        <v>2228.83</v>
       </c>
       <c r="AC4" t="n">
-        <v>329.16</v>
+        <v>2311.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>331.48</v>
+        <v>2352.63</v>
       </c>
       <c r="AE4" t="n">
-        <v>39.7</v>
+        <v>43.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>710.5</v>
+        <v>51.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>182</v>
+        <v>8.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>337.95</v>
+        <v>2335.67</v>
       </c>
       <c r="AN4" t="n">
-        <v>316.91</v>
+        <v>2208.22</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹300,878.29 Cr., a P/E ratio of 710.54, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹63,031.23 Cr., a P/E ratio of 51.28, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.71 (Consolidation Zone), while MACD Line (1.94) trades below Signal (3.71) with an expanding histogram (-1.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.46% above the 200-day DMA (₹274.44). Daily volatility envelope is bounded by ATR(14) of ₹7.50.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.67 (Consolidation Zone), while MACD Line (33.95) trades below Signal (54.05) with an expanding histogram (-20.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.34% above the 200-day DMA (₹1956.80). Daily volatility envelope is bounded by ATR(14) of ₹61.68.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹326.85) is positioned above the 30-day DMA (₹322.09), 50-day DMA (₹311.90), and 200-day DMA (₹274.44). The price distance from 200 DMA is +17.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,270.10) is positioned above the 30-day DMA (₹2,126.16), 50-day DMA (₹2,009.95), and 200-day DMA (₹1,956.80). The price distance from 200 DMA is +8.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[326.85, 327.83, 328.81, 329.79, 330.77, 331.75]</t>
+          <t>[2270.1, 2307.8, 2345.49, 2383.19, 2420.88, 2458.58]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[326.85, 330.83, 333.05, 334.99, 336.77, 338.46]</t>
+          <t>[2270.1, 2332.47, 2380.38, 2425.92, 2470.22, 2513.74]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[326.85, 325.58, 325.63, 325.9, 326.27, 326.72]</t>
+          <t>[2270.1, 2289.29, 2319.32, 2351.14, 2383.88, 2417.2]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>305.81</v>
+        <v>2613.7</v>
       </c>
     </row>
     <row r="5">
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63031.23</v>
+        <v>300878.29</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,146 +1179,146 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2270.1</v>
+        <v>326.85</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹2257.76 - ₹2288.6</t>
+          <t>₹325.35 - ₹329.1</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2319.44</v>
+        <v>332.85</v>
       </c>
       <c r="I5" t="n">
-        <v>2126.16</v>
+        <v>322.09</v>
       </c>
       <c r="J5" t="n">
-        <v>2009.95</v>
+        <v>311.9</v>
       </c>
       <c r="K5" t="n">
-        <v>1956.8</v>
+        <v>274.44</v>
       </c>
       <c r="L5" t="n">
-        <v>8.34</v>
+        <v>17.46</v>
       </c>
       <c r="M5" t="n">
-        <v>33.95</v>
+        <v>1.94</v>
       </c>
       <c r="N5" t="n">
-        <v>54.05</v>
+        <v>3.71</v>
       </c>
       <c r="O5" t="n">
-        <v>-20.1</v>
+        <v>-1.77</v>
       </c>
       <c r="P5" t="n">
-        <v>61.68</v>
+        <v>7.5</v>
       </c>
       <c r="Q5" t="n">
         <v>11.39</v>
       </c>
       <c r="R5" t="n">
-        <v>46.7</v>
+        <v>47.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.41</v>
+        <v>0.23</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.22</v>
+        <v>-1.3</v>
       </c>
       <c r="U5" t="n">
-        <v>53.3</v>
+        <v>54.1</v>
       </c>
       <c r="V5" t="n">
-        <v>3.12</v>
+        <v>2.51</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>2229.93</v>
+        <v>326.85</v>
       </c>
       <c r="Y5" t="n">
-        <v>2224.27</v>
+        <v>352.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>2004.42</v>
+        <v>352.13</v>
       </c>
       <c r="AA5" t="n">
-        <v>2177.59</v>
+        <v>315.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>2228.83</v>
+        <v>327.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>2311.36</v>
+        <v>329.16</v>
       </c>
       <c r="AD5" t="n">
-        <v>2352.63</v>
+        <v>331.48</v>
       </c>
       <c r="AE5" t="n">
-        <v>43.7</v>
+        <v>39.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>51.3</v>
+        <v>710.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8.5</v>
+        <v>182</v>
       </c>
       <c r="AK5" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>2332.53</v>
+        <v>338.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>2209.13</v>
+        <v>315.84</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹63,031.23 Cr., a P/E ratio of 51.28, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹300,878.29 Cr., a P/E ratio of 710.54, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.67 (Consolidation Zone), while MACD Line (33.95) trades below Signal (54.05) with an expanding histogram (-20.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.34% above the 200-day DMA (₹1956.80). Daily volatility envelope is bounded by ATR(14) of ₹61.68.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.71 (Consolidation Zone), while MACD Line (1.94) trades below Signal (3.71) with an expanding histogram (-1.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.46% above the 200-day DMA (₹274.44). Daily volatility envelope is bounded by ATR(14) of ₹7.50.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,270.10) is positioned above the 30-day DMA (₹2,126.16), 50-day DMA (₹2,009.95), and 200-day DMA (₹1,956.80). The price distance from 200 DMA is +8.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹326.85) is positioned above the 30-day DMA (₹322.09), 50-day DMA (₹311.90), and 200-day DMA (₹274.44). The price distance from 200 DMA is +17.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[2270.1, 2307.8, 2345.49, 2383.19, 2420.88, 2458.58]</t>
+          <t>[326.85, 327.83, 328.81, 329.79, 330.77, 331.75]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[2270.1, 2332.47, 2380.38, 2425.92, 2470.22, 2513.74]</t>
+          <t>[326.85, 330.83, 333.05, 334.99, 336.77, 338.46]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[2270.1, 2289.29, 2319.32, 2351.14, 2383.88, 2417.2]</t>
+          <t>[326.85, 325.58, 325.63, 325.9, 326.27, 326.72]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>2004.42</v>
+        <v>352.13</v>
       </c>
     </row>
     <row r="6">
@@ -1402,13 +1402,13 @@
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>529.08</v>
+        <v>548.15</v>
       </c>
       <c r="Y6" t="n">
-        <v>528.05</v>
+        <v>582.13</v>
       </c>
       <c r="Z6" t="n">
-        <v>520.29</v>
+        <v>582.13</v>
       </c>
       <c r="AA6" t="n">
         <v>522.6900000000001</v>
@@ -1449,10 +1449,10 @@
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>561.6799999999999</v>
+        <v>561.86</v>
       </c>
       <c r="AN6" t="n">
-        <v>534.23</v>
+        <v>533.2</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>520.29</v>
+        <v>582.13</v>
       </c>
     </row>
     <row r="7">
@@ -1551,7 +1551,7 @@
         <v>11.39</v>
       </c>
       <c r="R7" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="S7" t="n">
         <v>0.28</v>
@@ -1569,13 +1569,13 @@
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>114.1</v>
+        <v>117.27</v>
       </c>
       <c r="Y7" t="n">
-        <v>113.84</v>
+        <v>125.91</v>
       </c>
       <c r="Z7" t="n">
-        <v>110.1</v>
+        <v>125.91</v>
       </c>
       <c r="AA7" t="n">
         <v>113.93</v>
@@ -1616,10 +1616,10 @@
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>120.69</v>
+        <v>120.57</v>
       </c>
       <c r="AN7" t="n">
-        <v>113.88</v>
+        <v>113.79</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -1643,16 +1643,16 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[117.27, 118.98, 120.18, 121.29, 122.35, 123.38]</t>
+          <t>[117.27, 118.99, 120.18, 121.29, 122.35, 123.38]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[117.27, 117.43, 117.97, 118.58, 119.23, 119.9]</t>
+          <t>[117.27, 117.43, 117.97, 118.59, 119.23, 119.9]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>110.1</v>
+        <v>125.91</v>
       </c>
     </row>
     <row r="8">
@@ -1680,45 +1680,45 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11282</v>
+        <v>11217</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹11240.61 - ₹11344.08</t>
+          <t>₹11175.85 - ₹11278.72</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>11447.54</v>
+        <v>11381.59</v>
       </c>
       <c r="I8" t="n">
-        <v>11278.87</v>
+        <v>11213.88</v>
       </c>
       <c r="J8" t="n">
-        <v>11082.86</v>
+        <v>11019.01</v>
       </c>
       <c r="K8" t="n">
-        <v>10584.38</v>
+        <v>10523.4</v>
       </c>
       <c r="L8" t="n">
         <v>3.27</v>
       </c>
       <c r="M8" t="n">
-        <v>-41.34</v>
+        <v>-41.1</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.16</v>
+        <v>-2.15</v>
       </c>
       <c r="O8" t="n">
-        <v>-39.18</v>
+        <v>-38.95</v>
       </c>
       <c r="P8" t="n">
-        <v>206.93</v>
+        <v>205.74</v>
       </c>
       <c r="Q8" t="n">
         <v>11.39</v>
       </c>
       <c r="R8" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
       <c r="S8" t="n">
         <v>0.53</v>
@@ -1736,25 +1736,25 @@
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>11060.34</v>
+        <v>11217</v>
       </c>
       <c r="Y8" t="n">
-        <v>10957.24</v>
+        <v>12393.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>10360.47</v>
+        <v>12393.57</v>
       </c>
       <c r="AA8" t="n">
-        <v>10971.61</v>
+        <v>10908.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>11238.33</v>
+        <v>11173.58</v>
       </c>
       <c r="AC8" t="n">
-        <v>11406.66</v>
+        <v>11340.94</v>
       </c>
       <c r="AD8" t="n">
-        <v>11531.33</v>
+        <v>11464.89</v>
       </c>
       <c r="AE8" t="n">
         <v>36.5</v>
@@ -1783,10 +1783,10 @@
         <v>11.6</v>
       </c>
       <c r="AM8" t="n">
-        <v>11571.98</v>
+        <v>11525.67</v>
       </c>
       <c r="AN8" t="n">
-        <v>10961.59</v>
+        <v>10871.47</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -1795,31 +1795,31 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 36.48 (Consolidation Zone), while MACD Line (-41.34) trades below Signal (-2.16) with an expanding histogram (-39.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.27% above the 200-day DMA (₹10584.38). Daily volatility envelope is bounded by ATR(14) of ₹206.93.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 36.48 (Consolidation Zone), while MACD Line (-41.10) trades below Signal (-2.15) with an expanding histogram (-38.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.27% above the 200-day DMA (₹10523.40). Daily volatility envelope is bounded by ATR(14) of ₹205.74.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,282.00) is positioned above the 30-day DMA (₹11,278.87), 50-day DMA (₹11,082.86), and 200-day DMA (₹10,584.38). The price distance from 200 DMA is +3.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,217.00) is positioned above the 30-day DMA (₹11,213.88), 50-day DMA (₹11,019.01), and 200-day DMA (₹10,523.40). The price distance from 200 DMA is +3.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[11282.0, 11446.89, 11611.77, 11776.66, 11941.55, 12106.44]</t>
+          <t>[11217.0, 11381.21, 11545.42, 11709.64, 11873.85, 12038.06]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[11282.0, 11529.66, 11728.83, 11920.03, 12107.09, 12291.52]</t>
+          <t>[11217.0, 11463.51, 11661.81, 11852.17, 12038.44, 12222.08]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[11282.0, 11384.81, 11523.98, 11669.14, 11817.39, 11967.63]</t>
+          <t>[11217.0, 11319.49, 11458.14, 11602.73, 11750.41, 11900.05]</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>10360.47</v>
+        <v>12393.57</v>
       </c>
     </row>
     <row r="9">
@@ -1830,664 +1830,163 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60900.7</v>
+        <v>106000.03</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1010</v>
+        <v>732.75</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹1004.4 - ₹1018.4</t>
+          <t>₹729.55 - ₹737.55</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1032.39</v>
+        <v>745.5599999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>980.86</v>
+        <v>722.83</v>
       </c>
       <c r="J9" t="n">
-        <v>955.17</v>
+        <v>728.36</v>
       </c>
       <c r="K9" t="n">
-        <v>850.98</v>
+        <v>686</v>
       </c>
       <c r="L9" t="n">
-        <v>14.75</v>
+        <v>5.93</v>
       </c>
       <c r="M9" t="n">
-        <v>16.58</v>
+        <v>-2.09</v>
       </c>
       <c r="N9" t="n">
-        <v>25.36</v>
+        <v>-2.08</v>
       </c>
       <c r="O9" t="n">
-        <v>-8.779999999999999</v>
+        <v>-0</v>
       </c>
       <c r="P9" t="n">
-        <v>27.99</v>
+        <v>16.01</v>
       </c>
       <c r="Q9" t="n">
         <v>11.39</v>
       </c>
       <c r="R9" t="n">
-        <v>45.4</v>
+        <v>41.1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.31</v>
+        <v>0.24</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.53</v>
+        <v>-1.48</v>
       </c>
       <c r="U9" t="n">
-        <v>51.7</v>
+        <v>44.3</v>
       </c>
       <c r="V9" t="n">
-        <v>3.81</v>
+        <v>11.45</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>988.27</v>
+        <v>726.3099999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>985.89</v>
+        <v>785.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>903.71</v>
+        <v>785.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>968.01</v>
+        <v>708.74</v>
       </c>
       <c r="AB9" t="n">
-        <v>1002.9</v>
+        <v>732.78</v>
       </c>
       <c r="AC9" t="n">
-        <v>1017.1</v>
+        <v>742.96</v>
       </c>
       <c r="AD9" t="n">
-        <v>1024.2</v>
+        <v>753.1799999999999</v>
       </c>
       <c r="AE9" t="n">
-        <v>33.1</v>
+        <v>58.7</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>31.3</v>
+        <v>48.6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23.9</v>
+        <v>15.1</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>20.9</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>1051.33</v>
+        <v>751.13</v>
       </c>
       <c r="AN9" t="n">
-        <v>971.39</v>
+        <v>715.58</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹60,900.70 Cr., a P/E ratio of 31.35, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,000.03 Cr., a P/E ratio of 48.56, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.06 (Consolidation Zone), while MACD Line (16.58) trades below Signal (25.36) with an expanding histogram (-8.78). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +14.75% above the 200-day DMA (₹850.98). Daily volatility envelope is bounded by ATR(14) of ₹27.99.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.74 (Bullish Momentum Zone), while MACD Line (-2.09) trades below Signal (-2.08) with an expanding histogram (-0.00). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.93% above the 200-day DMA (₹686.00). Daily volatility envelope is bounded by ATR(14) of ₹16.01.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,010.00) is positioned above the 30-day DMA (₹980.86), 50-day DMA (₹955.17), and 200-day DMA (₹850.98). The price distance from 200 DMA is +14.75%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹732.75) is positioned above the 30-day DMA (₹722.83), 50-day DMA (₹728.36), and 200-day DMA (₹686.00). The price distance from 200 DMA is +5.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[1010.0, 1022.84, 1035.67, 1048.51, 1061.34, 1074.18]</t>
+          <t>[732.75, 734.95, 737.15, 739.34, 741.54, 743.74]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[1010.0, 1034.03, 1051.51, 1067.9, 1083.74, 1099.22]</t>
+          <t>[732.75, 741.35, 746.2, 750.43, 754.35, 758.06]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[1010.0, 1014.44, 1023.79, 1033.96, 1044.55, 1055.4]</t>
+          <t>[732.75, 730.15, 730.36, 731.03, 731.94, 733.0]</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>903.71</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>43890</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>292.6</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>₹291.43 - ₹294.36</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>297.3</v>
-      </c>
-      <c r="I10" t="n">
-        <v>287.18</v>
-      </c>
-      <c r="J10" t="n">
-        <v>283.36</v>
-      </c>
-      <c r="K10" t="n">
-        <v>278.69</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-1.27</v>
-      </c>
-      <c r="P10" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="R10" t="n">
-        <v>45</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-1.18</v>
-      </c>
-      <c r="U10" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>5</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X10" t="n">
-        <v>280.13</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>279.66</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>268.68</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>283.79</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>289.77</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>295.44</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>298.27</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>-53.2</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>301.71</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>284.49</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,890.00 Cr., a P/E ratio of 10.43, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.46 (Consolidation Zone), while MACD Line (-0.10) trades below Signal (1.17) with an expanding histogram (-1.27). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +1.71% above the 200-day DMA (₹278.69). Daily volatility envelope is bounded by ATR(14) of ₹5.88.</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹292.60) is positioned above the 30-day DMA (₹287.18), 50-day DMA (₹283.36), and 200-day DMA (₹278.69). The price distance from 200 DMA is +1.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>[292.6, 293.48, 294.36, 295.23, 296.11, 296.99]</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>[292.6, 295.83, 297.68, 299.3, 300.81, 302.24]</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>[292.6, 291.72, 291.86, 292.18, 292.59, 293.05]</t>
-        </is>
-      </c>
-      <c r="AU10" t="n">
-        <v>268.68</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>410340.82</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>412.5</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>₹411.26 - ₹414.36</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>417.47</v>
-      </c>
-      <c r="I11" t="n">
-        <v>408.48</v>
-      </c>
-      <c r="J11" t="n">
-        <v>399.68</v>
-      </c>
-      <c r="K11" t="n">
-        <v>399.79</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>6.01</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="P11" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="R11" t="n">
-        <v>47</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="U11" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X11" t="n">
-        <v>400.72</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>412.37</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>412.37</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>403.18</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>414.73</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>416.96</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>421.43</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>Low VIX (11.39) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>421</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>403.83</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹410,340.82 Cr., a P/E ratio of 20.20, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.58 (Consolidation Zone), while MACD Line (4.50) trades below Signal (6.01) with an expanding histogram (-1.51). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹399.79). Daily volatility envelope is bounded by ATR(14) of ₹6.21.</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹412.50) is positioned above the 30-day DMA (₹408.48), 50-day DMA (₹399.68), and 200-day DMA (₹399.79). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>[412.5, 414.78, 417.05, 419.33, 421.6, 423.88]</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>[412.5, 417.26, 420.56, 423.63, 426.57, 429.43]</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>[412.5, 412.91, 414.42, 416.1, 417.88, 419.71]</t>
-        </is>
-      </c>
-      <c r="AU11" t="n">
-        <v>412.37</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>INDHOTEL</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>106000.03</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>732.75</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>₹729.55 - ₹737.55</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>745.5599999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>722.83</v>
-      </c>
-      <c r="J12" t="n">
-        <v>728.36</v>
-      </c>
-      <c r="K12" t="n">
-        <v>686</v>
-      </c>
-      <c r="L12" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>16.01</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="R12" t="n">
-        <v>41</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="U12" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="V12" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="W12" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X12" t="n">
-        <v>699.79</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>688.79</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>688.79</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>708.74</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>732.78</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>742.96</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>753.1799999999999</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>58.7</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>48.6</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>750.46</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>714.77</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,000.03 Cr., a P/E ratio of 48.56, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.74 (Bullish Momentum Zone), while MACD Line (-2.09) trades below Signal (-2.08) with an expanding histogram (-0.00). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.93% above the 200-day DMA (₹686.00). Daily volatility envelope is bounded by ATR(14) of ₹16.01.</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹732.75) is positioned above the 30-day DMA (₹722.83), 50-day DMA (₹728.36), and 200-day DMA (₹686.00). The price distance from 200 DMA is +5.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>[732.75, 734.95, 737.15, 739.34, 741.54, 743.74]</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>[732.75, 741.35, 746.2, 750.43, 754.35, 758.06]</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>[732.75, 730.15, 730.36, 731.03, 731.94, 733.0]</t>
-        </is>
-      </c>
-      <c r="AU12" t="n">
-        <v>688.79</v>
+        <v>785.75</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU9"/>
+  <dimension ref="A1:AU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,21 +656,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>179474.08</v>
+        <v>416060.72</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,166 +678,166 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2208.8</v>
+        <v>418.25</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹2197.33 - ₹2226.01</t>
+          <t>₹416.99 - ₹420.14</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2254.68</v>
+        <v>423.28</v>
       </c>
       <c r="I2" t="n">
-        <v>2200.73</v>
+        <v>409.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2129.15</v>
+        <v>400.39</v>
       </c>
       <c r="K2" t="n">
-        <v>2052.76</v>
+        <v>399.71</v>
       </c>
       <c r="L2" t="n">
-        <v>5.22</v>
+        <v>3.2</v>
       </c>
       <c r="M2" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="N2" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="R2" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="U2" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V2" t="n">
         <v>3.6</v>
-      </c>
-      <c r="N2" t="n">
-        <v>15.47</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-11.86</v>
-      </c>
-      <c r="P2" t="n">
-        <v>57.35</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>11.39</v>
-      </c>
-      <c r="R2" t="n">
-        <v>49</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="U2" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4.4</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2208.8</v>
+        <v>418.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>2401.92</v>
+        <v>443.54</v>
       </c>
       <c r="Z2" t="n">
-        <v>2401.92</v>
+        <v>421.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>2122.78</v>
+        <v>408.82</v>
       </c>
       <c r="AB2" t="n">
-        <v>2191.03</v>
+        <v>417.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>2226.56</v>
+        <v>420.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>2244.33</v>
+        <v>422.65</v>
       </c>
       <c r="AE2" t="n">
-        <v>33.7</v>
+        <v>42.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.17</v>
+        <v>-0.01</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Low VIX (11.45) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>36.2</v>
+        <v>20.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.5</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>7</v>
+        <v>28.5</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>2274.45</v>
+        <v>426.9</v>
       </c>
       <c r="AN2" t="n">
-        <v>2143.25</v>
+        <v>409.54</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>HYUNDAI operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹179,474.08 Cr., a P/E ratio of 36.23, and YoY Revenue Growth of -0.5%, the company demonstrates strong institutional backing, solid operating profit margins (7.00%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹416,060.72 Cr., a P/E ratio of 20.48, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 33.70 (Consolidation Zone), while MACD Line (3.60) trades below Signal (15.47) with an expanding histogram (-11.86). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.22% above the 200-day DMA (₹2052.76). Daily volatility envelope is bounded by ATR(14) of ₹57.35.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.84 (Consolidation Zone), while MACD Line (3.88) trades below Signal (5.59) with an expanding histogram (-1.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.20% above the 200-day DMA (₹399.71). Daily volatility envelope is bounded by ATR(14) of ₹6.29.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for HYUNDAI. Current Market Price (₹2,208.80) is positioned above the 30-day DMA (₹2,200.73), 50-day DMA (₹2,129.15), and 200-day DMA (₹2,052.76). The price distance from 200 DMA is +5.22%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹418.25) is positioned above the 30-day DMA (₹409.20), 50-day DMA (₹400.39), and 200-day DMA (₹399.71). The price distance from 200 DMA is +3.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[2208.8, 2215.43, 2222.05, 2228.68, 2235.31, 2241.93]</t>
+          <t>[418.25, 420.23, 422.21, 424.18, 426.16, 428.14]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[2208.8, 2238.37, 2254.49, 2268.41, 2281.19, 2293.23]</t>
+          <t>[418.25, 422.74, 425.76, 428.54, 431.19, 433.76]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[2208.8, 2198.22, 2197.72, 2198.88, 2200.9, 2203.46]</t>
+          <t>[418.25, 418.34, 419.54, 420.92, 422.39, 423.92]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2401.92</v>
+        <v>421.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>82971.60000000001</v>
+        <v>304192.24</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,166 +845,166 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3260</v>
+        <v>330.55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹3239.25 - ₹3291.13</t>
+          <t>₹329.19 - ₹332.59</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3343.01</v>
+        <v>335.99</v>
       </c>
       <c r="I3" t="n">
-        <v>3137.32</v>
+        <v>322.48</v>
       </c>
       <c r="J3" t="n">
-        <v>2981.04</v>
+        <v>312.65</v>
       </c>
       <c r="K3" t="n">
-        <v>2689.42</v>
+        <v>274.58</v>
       </c>
       <c r="L3" t="n">
-        <v>19.4</v>
+        <v>19.03</v>
       </c>
       <c r="M3" t="n">
-        <v>74.77</v>
+        <v>2.23</v>
       </c>
       <c r="N3" t="n">
-        <v>102.69</v>
+        <v>3.41</v>
       </c>
       <c r="O3" t="n">
-        <v>-27.92</v>
+        <v>-1.18</v>
       </c>
       <c r="P3" t="n">
-        <v>103.76</v>
+        <v>6.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.39</v>
+        <v>11.45</v>
       </c>
       <c r="R3" t="n">
-        <v>48.2</v>
+        <v>49.9</v>
       </c>
       <c r="S3" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.65</v>
+        <v>-1.03</v>
       </c>
       <c r="U3" t="n">
-        <v>53.3</v>
+        <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>3.4</v>
+        <v>2.52</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>3260</v>
+        <v>330.55</v>
       </c>
       <c r="Y3" t="n">
-        <v>4235.2</v>
+        <v>356.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>4235.2</v>
+        <v>356.11</v>
       </c>
       <c r="AA3" t="n">
-        <v>3104.35</v>
+        <v>320.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>3268.33</v>
+        <v>329.93</v>
       </c>
       <c r="AC3" t="n">
-        <v>3306.56</v>
+        <v>333.01</v>
       </c>
       <c r="AD3" t="n">
-        <v>3353.13</v>
+        <v>335.48</v>
       </c>
       <c r="AE3" t="n">
-        <v>46.5</v>
+        <v>48</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.45) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>54.1</v>
+        <v>718.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85.3</v>
+        <v>182</v>
       </c>
       <c r="AK3" t="n">
-        <v>55.6</v>
+        <v>0.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>3393.68</v>
+        <v>342.06</v>
       </c>
       <c r="AN3" t="n">
-        <v>3148.59</v>
+        <v>320.63</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹82,971.60 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹304,192.24 Cr., a P/E ratio of 718.37, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.45 (Consolidation Zone), while MACD Line (74.77) trades below Signal (102.69) with an expanding histogram (-27.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.40% above the 200-day DMA (₹2689.42). Daily volatility envelope is bounded by ATR(14) of ₹103.76.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.04 (Consolidation Zone), while MACD Line (2.23) trades below Signal (3.41) with an expanding histogram (-1.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.03% above the 200-day DMA (₹274.58). Daily volatility envelope is bounded by ATR(14) of ₹6.80.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,260.00) is positioned above the 30-day DMA (₹3,137.32), 50-day DMA (₹2,981.04), and 200-day DMA (₹2,689.42). The price distance from 200 DMA is +19.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹330.55) is positioned above the 30-day DMA (₹322.48), 50-day DMA (₹312.65), and 200-day DMA (₹274.58). The price distance from 200 DMA is +19.03%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[3260.0, 3303.43, 3346.86, 3390.28, 3433.71, 3477.14]</t>
+          <t>[330.55, 332.48, 334.41, 336.34, 338.27, 340.21]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[3260.0, 3344.93, 3405.55, 3462.17, 3516.72, 3569.95]</t>
+          <t>[330.55, 335.2, 338.26, 341.05, 343.71, 346.29]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[3260.0, 3272.3, 3302.83, 3336.37, 3371.45, 3407.53]</t>
+          <t>[330.55, 330.44, 331.53, 332.81, 334.19, 335.64]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>4235.2</v>
+        <v>356.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>63031.23</v>
+        <v>31240.83</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,166 +1012,166 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2270.1</v>
+        <v>567.95</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹2257.76 - ₹2288.6</t>
+          <t>₹564.59 - ₹572.99</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2319.44</v>
+        <v>581.4</v>
       </c>
       <c r="I4" t="n">
-        <v>2126.16</v>
+        <v>524.02</v>
       </c>
       <c r="J4" t="n">
-        <v>2009.95</v>
+        <v>525.63</v>
       </c>
       <c r="K4" t="n">
-        <v>1956.8</v>
+        <v>523.7</v>
       </c>
       <c r="L4" t="n">
-        <v>8.34</v>
+        <v>4.67</v>
       </c>
       <c r="M4" t="n">
-        <v>33.95</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>54.05</v>
+        <v>10.11</v>
       </c>
       <c r="O4" t="n">
-        <v>-20.1</v>
+        <v>-0.39</v>
       </c>
       <c r="P4" t="n">
-        <v>61.68</v>
+        <v>16.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.39</v>
+        <v>11.45</v>
       </c>
       <c r="R4" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0.41</v>
+        <v>0.18</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.18</v>
+        <v>-1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>53.3</v>
+        <v>48.3</v>
       </c>
       <c r="V4" t="n">
-        <v>3.12</v>
+        <v>4.93</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2270.1</v>
+        <v>567.95</v>
       </c>
       <c r="Y4" t="n">
-        <v>2613.7</v>
+        <v>603.15</v>
       </c>
       <c r="Z4" t="n">
-        <v>2613.7</v>
+        <v>603.15</v>
       </c>
       <c r="AA4" t="n">
-        <v>2177.59</v>
+        <v>542.73</v>
       </c>
       <c r="AB4" t="n">
-        <v>2228.83</v>
+        <v>560</v>
       </c>
       <c r="AC4" t="n">
-        <v>2311.36</v>
+        <v>576.35</v>
       </c>
       <c r="AD4" t="n">
-        <v>2352.63</v>
+        <v>584.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>43.7</v>
+        <v>56.4</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.06</v>
+        <v>0.22</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.45) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>51.3</v>
+        <v>5.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>5.2</v>
+        <v>65.2</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>2335.67</v>
+        <v>583.0599999999999</v>
       </c>
       <c r="AN4" t="n">
-        <v>2208.22</v>
+        <v>552.47</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹63,031.23 Cr., a P/E ratio of 51.28, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,240.83 Cr., a P/E ratio of 5.44, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.67 (Consolidation Zone), while MACD Line (33.95) trades below Signal (54.05) with an expanding histogram (-20.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.34% above the 200-day DMA (₹1956.80). Daily volatility envelope is bounded by ATR(14) of ₹61.68.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.36 (Bullish Momentum Zone), while MACD Line (9.72) trades below Signal (10.11) with an expanding histogram (-0.39). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.67% above the 200-day DMA (₹523.70). Daily volatility envelope is bounded by ATR(14) of ₹16.81.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,270.10) is positioned above the 30-day DMA (₹2,126.16), 50-day DMA (₹2,009.95), and 200-day DMA (₹1,956.80). The price distance from 200 DMA is +8.34%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹567.95) is positioned above the 30-day DMA (₹524.02), 50-day DMA (₹525.63), and 200-day DMA (₹523.70). The price distance from 200 DMA is +4.67%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[2270.1, 2307.8, 2345.49, 2383.19, 2420.88, 2458.58]</t>
+          <t>[567.95, 569.65, 571.36, 573.06, 574.77, 576.47]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[2270.1, 2332.47, 2380.38, 2425.92, 2470.22, 2513.74]</t>
+          <t>[567.95, 576.38, 580.87, 584.71, 588.21, 591.51]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[2270.1, 2289.29, 2319.32, 2351.14, 2383.88, 2417.2]</t>
+          <t>[567.95, 564.61, 564.23, 564.33, 564.68, 565.19]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2613.7</v>
+        <v>603.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>300878.29</v>
+        <v>134892.67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,157 +1179,157 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>326.85</v>
+        <v>117.37</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹325.35 - ₹329.1</t>
+          <t>₹116.94 - ₹118.01</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>332.85</v>
+        <v>119.08</v>
       </c>
       <c r="I5" t="n">
-        <v>322.09</v>
+        <v>116.33</v>
       </c>
       <c r="J5" t="n">
-        <v>311.9</v>
+        <v>114.03</v>
       </c>
       <c r="K5" t="n">
-        <v>274.44</v>
+        <v>112.31</v>
       </c>
       <c r="L5" t="n">
-        <v>17.46</v>
+        <v>4.42</v>
       </c>
       <c r="M5" t="n">
-        <v>1.94</v>
+        <v>0.64</v>
       </c>
       <c r="N5" t="n">
-        <v>3.71</v>
+        <v>0.75</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.77</v>
+        <v>-0.12</v>
       </c>
       <c r="P5" t="n">
-        <v>7.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.39</v>
+        <v>11.45</v>
       </c>
       <c r="R5" t="n">
-        <v>47.4</v>
+        <v>46.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.3</v>
+        <v>-0.99</v>
       </c>
       <c r="U5" t="n">
-        <v>54.1</v>
+        <v>53.3</v>
       </c>
       <c r="V5" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>326.85</v>
+        <v>117.37</v>
       </c>
       <c r="Y5" t="n">
-        <v>352.13</v>
+        <v>126.01</v>
       </c>
       <c r="Z5" t="n">
-        <v>352.13</v>
+        <v>126.01</v>
       </c>
       <c r="AA5" t="n">
-        <v>315.61</v>
+        <v>114.16</v>
       </c>
       <c r="AB5" t="n">
-        <v>327.43</v>
+        <v>117.27</v>
       </c>
       <c r="AC5" t="n">
-        <v>329.16</v>
+        <v>117.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>331.48</v>
+        <v>118.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>39.7</v>
+        <v>61.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.25</v>
+        <v>-0.11</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.45) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>710.5</v>
+        <v>6.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>182</v>
+        <v>-6.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.6</v>
+        <v>38.1</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>338.3</v>
+        <v>120.41</v>
       </c>
       <c r="AN5" t="n">
-        <v>315.84</v>
+        <v>114.14</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹300,878.29 Cr., a P/E ratio of 710.54, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,892.67 Cr., a P/E ratio of 6.11, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.71 (Consolidation Zone), while MACD Line (1.94) trades below Signal (3.71) with an expanding histogram (-1.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.46% above the 200-day DMA (₹274.44). Daily volatility envelope is bounded by ATR(14) of ₹7.50.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.75 (Bullish Momentum Zone), while MACD Line (0.64) trades below Signal (0.75) with an expanding histogram (-0.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.42% above the 200-day DMA (₹112.31). Daily volatility envelope is bounded by ATR(14) of ₹2.14.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹326.85) is positioned above the 30-day DMA (₹322.09), 50-day DMA (₹311.90), and 200-day DMA (₹274.44). The price distance from 200 DMA is +17.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.37) is positioned above the 30-day DMA (₹116.33), 50-day DMA (₹114.03), and 200-day DMA (₹112.31). The price distance from 200 DMA is +4.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[326.85, 327.83, 328.81, 329.79, 330.77, 331.75]</t>
+          <t>[117.37, 118.26, 119.15, 120.04, 120.93, 121.82]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[326.85, 330.83, 333.05, 334.99, 336.77, 338.46]</t>
+          <t>[117.37, 119.12, 120.36, 121.52, 122.64, 123.73]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[326.85, 325.58, 325.63, 325.9, 326.27, 326.72]</t>
+          <t>[117.37, 117.62, 118.24, 118.93, 119.64, 120.38]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>352.13</v>
+        <v>126.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30151.7</v>
+        <v>126874.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,157 +1346,157 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>548.15</v>
+        <v>11400</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹544.76 - ₹553.24</t>
+          <t>₹11355.25 - ₹11467.13</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>561.73</v>
+        <v>11579.02</v>
       </c>
       <c r="I6" t="n">
-        <v>522.25</v>
+        <v>11210.4</v>
       </c>
       <c r="J6" t="n">
-        <v>525.25</v>
+        <v>11032.95</v>
       </c>
       <c r="K6" t="n">
-        <v>523.6799999999999</v>
+        <v>10525.23</v>
       </c>
       <c r="L6" t="n">
-        <v>3.69</v>
+        <v>6.57</v>
       </c>
       <c r="M6" t="n">
-        <v>10.41</v>
+        <v>-24.46</v>
       </c>
       <c r="N6" t="n">
-        <v>10.21</v>
+        <v>-6.61</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2</v>
+        <v>-17.85</v>
       </c>
       <c r="P6" t="n">
-        <v>16.97</v>
+        <v>223.77</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.39</v>
+        <v>11.45</v>
       </c>
       <c r="R6" t="n">
-        <v>46.6</v>
+        <v>46.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.94</v>
+        <v>-1.09</v>
       </c>
       <c r="U6" t="n">
-        <v>46.7</v>
+        <v>51.7</v>
       </c>
       <c r="V6" t="n">
-        <v>4.8</v>
+        <v>3.88</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>548.15</v>
+        <v>11345.34</v>
       </c>
       <c r="Y6" t="n">
-        <v>582.13</v>
+        <v>12513.34</v>
       </c>
       <c r="Z6" t="n">
-        <v>582.13</v>
+        <v>12513.34</v>
       </c>
       <c r="AA6" t="n">
-        <v>522.6900000000001</v>
+        <v>11064.34</v>
       </c>
       <c r="AB6" t="n">
-        <v>547.92</v>
+        <v>11353.67</v>
       </c>
       <c r="AC6" t="n">
-        <v>552.24</v>
+        <v>11480.34</v>
       </c>
       <c r="AD6" t="n">
-        <v>556.3200000000001</v>
+        <v>11560.67</v>
       </c>
       <c r="AE6" t="n">
-        <v>53.8</v>
+        <v>48.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.23</v>
+        <v>0.01</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Low VIX (11.45) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.3</v>
+        <v>14.3</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14.5</v>
+        <v>24.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>65.2</v>
+        <v>734.6</v>
       </c>
       <c r="AL6" t="n">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="AM6" t="n">
-        <v>561.86</v>
+        <v>11712.13</v>
       </c>
       <c r="AN6" t="n">
-        <v>533.2</v>
+        <v>11079.54</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,151.70 Cr., a P/E ratio of 5.26, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹126,874.60 Cr., a P/E ratio of 14.33, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.80 (Consolidation Zone), while MACD Line (10.41) trades above Signal (10.21) with an expanding histogram (+0.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.69% above the 200-day DMA (₹523.68). Daily volatility envelope is bounded by ATR(14) of ₹16.97.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.57 (Consolidation Zone), while MACD Line (-24.46) trades below Signal (-6.61) with an expanding histogram (-17.85). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.57% above the 200-day DMA (₹10525.23). Daily volatility envelope is bounded by ATR(14) of ₹223.77.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹548.15) is positioned above the 30-day DMA (₹522.25), 50-day DMA (₹525.25), and 200-day DMA (₹523.68). The price distance from 200 DMA is +3.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,400.00) is positioned above the 30-day DMA (₹11,210.40), 50-day DMA (₹11,032.95), and 200-day DMA (₹10,525.23). The price distance from 200 DMA is +6.57%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[548.15, 549.79, 551.44, 553.08, 554.73, 556.37]</t>
+          <t>[11400.0, 11434.2, 11468.4, 11502.6, 11536.8, 11571.0]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[548.15, 556.58, 561.04, 564.84, 568.3, 571.55]</t>
+          <t>[11400.0, 11523.71, 11594.99, 11657.64, 11715.82, 11771.15]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[548.15, 544.7, 544.24, 544.26, 544.54, 544.99]</t>
+          <t>[11400.0, 11367.07, 11373.46, 11386.32, 11402.54, 11420.89]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>582.13</v>
+        <v>12513.34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1505,341 +1505,341 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>134777.73</v>
+        <v>25000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>117.27</v>
+        <v>3252</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹116.82 - ₹117.94</t>
+          <t>₹3231.11 - ₹3283.34</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>119.05</v>
+        <v>3335.57</v>
       </c>
       <c r="I7" t="n">
-        <v>116.25</v>
+        <v>3158.2</v>
       </c>
       <c r="J7" t="n">
-        <v>113.79</v>
+        <v>2990.66</v>
       </c>
       <c r="K7" t="n">
-        <v>112.3</v>
+        <v>2695.53</v>
       </c>
       <c r="L7" t="n">
-        <v>3.71</v>
+        <v>20.94</v>
       </c>
       <c r="M7" t="n">
-        <v>0.59</v>
+        <v>69.94</v>
       </c>
       <c r="N7" t="n">
-        <v>0.78</v>
+        <v>96.14</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.19</v>
+        <v>-26.2</v>
       </c>
       <c r="P7" t="n">
-        <v>2.23</v>
+        <v>104.46</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.39</v>
+        <v>11.45</v>
       </c>
       <c r="R7" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="S7" t="n">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.06</v>
+        <v>-2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>50.8</v>
+        <v>53.3</v>
       </c>
       <c r="V7" t="n">
-        <v>2.38</v>
+        <v>3.06</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>117.27</v>
+        <v>3252</v>
       </c>
       <c r="Y7" t="n">
-        <v>125.91</v>
+        <v>4207.71</v>
       </c>
       <c r="Z7" t="n">
-        <v>125.91</v>
+        <v>4207.71</v>
       </c>
       <c r="AA7" t="n">
-        <v>113.93</v>
+        <v>3095.31</v>
       </c>
       <c r="AB7" t="n">
-        <v>117.09</v>
+        <v>3245.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>117.68</v>
+        <v>3274.96</v>
       </c>
       <c r="AD7" t="n">
-        <v>118.09</v>
+        <v>3297.93</v>
       </c>
       <c r="AE7" t="n">
-        <v>54</v>
+        <v>45.1</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.14</v>
+        <v>0.11</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.45) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.1</v>
+        <v>53.9</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-6.4</v>
+        <v>85.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>38.1</v>
+        <v>55.6</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>120.57</v>
+        <v>3388.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>113.79</v>
+        <v>3136.5</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,777.73 Cr., a P/E ratio of 6.10, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.92, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.02 (Consolidation Zone), while MACD Line (0.59) trades below Signal (0.78) with an expanding histogram (-0.19). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.71% above the 200-day DMA (₹112.30). Daily volatility envelope is bounded by ATR(14) of ₹2.23.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 45.14 (Consolidation Zone), while MACD Line (69.94) trades below Signal (96.14) with an expanding histogram (-26.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.94% above the 200-day DMA (₹2695.53). Daily volatility envelope is bounded by ATR(14) of ₹104.46.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.27) is positioned above the 30-day DMA (₹116.25), 50-day DMA (₹113.79), and 200-day DMA (₹112.30). The price distance from 200 DMA is +3.71%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,252.00) is positioned above the 30-day DMA (₹3,158.20), 50-day DMA (₹2,990.66), and 200-day DMA (₹2,695.53). The price distance from 200 DMA is +20.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[117.27, 118.09, 118.92, 119.74, 120.57, 121.39]</t>
+          <t>[3252.0, 3281.99, 3311.97, 3341.96, 3371.95, 3401.93]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[117.27, 118.99, 120.18, 121.29, 122.35, 123.38]</t>
+          <t>[3252.0, 3323.77, 3371.06, 3414.33, 3455.51, 3495.36]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[117.27, 117.43, 117.97, 118.59, 119.23, 119.9]</t>
+          <t>[3252.0, 3250.65, 3267.66, 3287.68, 3309.27, 3331.86]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>125.91</v>
+        <v>4207.71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>125561.34</v>
+        <v>108046.98</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11217</v>
+        <v>746.9</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹11175.85 - ₹11278.72</t>
+          <t>₹743.93 - ₹751.36</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>11381.59</v>
+        <v>758.79</v>
       </c>
       <c r="I8" t="n">
-        <v>11213.88</v>
+        <v>722.89</v>
       </c>
       <c r="J8" t="n">
-        <v>11019.01</v>
+        <v>727.97</v>
       </c>
       <c r="K8" t="n">
-        <v>10523.4</v>
+        <v>686.01</v>
       </c>
       <c r="L8" t="n">
-        <v>3.27</v>
+        <v>6.81</v>
       </c>
       <c r="M8" t="n">
-        <v>-41.1</v>
+        <v>-0.93</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.15</v>
+        <v>-1.85</v>
       </c>
       <c r="O8" t="n">
-        <v>-38.95</v>
+        <v>0.93</v>
       </c>
       <c r="P8" t="n">
-        <v>205.74</v>
+        <v>14.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.39</v>
+        <v>11.45</v>
       </c>
       <c r="R8" t="n">
-        <v>45.8</v>
+        <v>42.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.28</v>
       </c>
       <c r="U8" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="V8" t="n">
-        <v>3.95</v>
+        <v>11.58</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>11217</v>
+        <v>742.1</v>
       </c>
       <c r="Y8" t="n">
-        <v>12393.57</v>
+        <v>800.9299999999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>12393.57</v>
+        <v>800.9299999999999</v>
       </c>
       <c r="AA8" t="n">
-        <v>10908.4</v>
+        <v>724.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>11173.58</v>
+        <v>747.63</v>
       </c>
       <c r="AC8" t="n">
-        <v>11340.94</v>
+        <v>754.26</v>
       </c>
       <c r="AD8" t="n">
-        <v>11464.89</v>
+        <v>761.63</v>
       </c>
       <c r="AE8" t="n">
-        <v>36.5</v>
+        <v>47.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.02</v>
+        <v>0.18</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Vol Spike 2.0x | Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.45) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>14.2</v>
+        <v>49.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24.2</v>
+        <v>15.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>734.6</v>
+        <v>20.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>11525.67</v>
+        <v>765.45</v>
       </c>
       <c r="AN8" t="n">
-        <v>10871.47</v>
+        <v>728.23</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹125,561.34 Cr., a P/E ratio of 14.18, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹108,046.98 Cr., a P/E ratio of 49.50, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 36.48 (Consolidation Zone), while MACD Line (-41.10) trades below Signal (-2.15) with an expanding histogram (-38.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.27% above the 200-day DMA (₹10523.40). Daily volatility envelope is bounded by ATR(14) of ₹205.74.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 47.15 (Consolidation Zone), while MACD Line (-0.93) trades above Signal (-1.85) with an expanding histogram (+0.93). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.81% above the 200-day DMA (₹686.01). Daily volatility envelope is bounded by ATR(14) of ₹14.87.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,217.00) is positioned above the 30-day DMA (₹11,213.88), 50-day DMA (₹11,019.01), and 200-day DMA (₹10,523.40). The price distance from 200 DMA is +3.27%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹746.90) is positioned above the 30-day DMA (₹722.89), 50-day DMA (₹727.97), and 200-day DMA (₹686.01). The price distance from 200 DMA is +6.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[11217.0, 11381.21, 11545.42, 11709.64, 11873.85, 12038.06]</t>
+          <t>[746.9, 749.14, 751.38, 753.62, 755.86, 758.1]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[11217.0, 11463.51, 11661.81, 11852.17, 12038.44, 12222.08]</t>
+          <t>[746.9, 755.09, 759.79, 763.92, 767.76, 771.4]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[11217.0, 11319.49, 11458.14, 11602.73, 11750.41, 11900.05]</t>
+          <t>[746.9, 744.68, 745.07, 745.9, 746.94, 748.13]</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>12393.57</v>
+        <v>800.9299999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>106000.03</v>
+        <v>60852.46</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1847,146 +1847,480 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>732.75</v>
+        <v>1009.2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹729.55 - ₹737.55</t>
+          <t>₹1003.49 - ₹1017.76</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>745.5599999999999</v>
+        <v>1032.03</v>
       </c>
       <c r="I9" t="n">
-        <v>722.83</v>
+        <v>985.39</v>
       </c>
       <c r="J9" t="n">
-        <v>728.36</v>
+        <v>956.52</v>
       </c>
       <c r="K9" t="n">
-        <v>686</v>
+        <v>851.29</v>
       </c>
       <c r="L9" t="n">
-        <v>5.93</v>
+        <v>18.64</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.09</v>
+        <v>15.27</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.08</v>
+        <v>23.34</v>
       </c>
       <c r="O9" t="n">
-        <v>-0</v>
+        <v>-8.07</v>
       </c>
       <c r="P9" t="n">
-        <v>16.01</v>
+        <v>28.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.39</v>
+        <v>11.45</v>
       </c>
       <c r="R9" t="n">
-        <v>41.1</v>
+        <v>41.9</v>
       </c>
       <c r="S9" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.48</v>
+        <v>-1.98</v>
       </c>
       <c r="U9" t="n">
-        <v>44.3</v>
+        <v>51.7</v>
       </c>
       <c r="V9" t="n">
-        <v>11.45</v>
+        <v>3.73</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>726.3099999999999</v>
+        <v>1009.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>785.75</v>
+        <v>1136.92</v>
       </c>
       <c r="Z9" t="n">
-        <v>785.75</v>
+        <v>1136.92</v>
       </c>
       <c r="AA9" t="n">
-        <v>708.74</v>
+        <v>966.39</v>
       </c>
       <c r="AB9" t="n">
-        <v>732.78</v>
+        <v>1004.07</v>
       </c>
       <c r="AC9" t="n">
-        <v>742.96</v>
+        <v>1014.94</v>
       </c>
       <c r="AD9" t="n">
-        <v>753.1799999999999</v>
+        <v>1020.67</v>
       </c>
       <c r="AE9" t="n">
-        <v>58.7</v>
+        <v>43.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.39) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.45) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>48.6</v>
+        <v>31.3</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15.1</v>
+        <v>23.9</v>
       </c>
       <c r="AK9" t="n">
-        <v>20.9</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>751.13</v>
+        <v>1051.14</v>
       </c>
       <c r="AN9" t="n">
-        <v>715.58</v>
+        <v>971.54</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,000.03 Cr., a P/E ratio of 48.56, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹60,852.46 Cr., a P/E ratio of 31.32, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.74 (Bullish Momentum Zone), while MACD Line (-2.09) trades below Signal (-2.08) with an expanding histogram (-0.00). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.93% above the 200-day DMA (₹686.00). Daily volatility envelope is bounded by ATR(14) of ₹16.01.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.42 (Consolidation Zone), while MACD Line (15.27) trades below Signal (23.34) with an expanding histogram (-8.07). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.64% above the 200-day DMA (₹851.29). Daily volatility envelope is bounded by ATR(14) of ₹28.54.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹732.75) is positioned above the 30-day DMA (₹722.83), 50-day DMA (₹728.36), and 200-day DMA (₹686.00). The price distance from 200 DMA is +5.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,009.20) is positioned above the 30-day DMA (₹985.39), 50-day DMA (₹956.52), and 200-day DMA (₹851.29). The price distance from 200 DMA is +18.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[732.75, 734.95, 737.15, 739.34, 741.54, 743.74]</t>
+          <t>[1009.2, 1012.23, 1015.26, 1018.28, 1021.31, 1024.34]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[732.75, 741.35, 746.2, 750.43, 754.35, 758.06]</t>
+          <t>[1009.2, 1023.64, 1031.4, 1038.06, 1044.14, 1049.86]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[732.75, 730.15, 730.36, 731.03, 731.94, 733.0]</t>
+          <t>[1009.2, 1003.67, 1003.15, 1003.45, 1004.19, 1005.19]</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>785.75</v>
+        <v>1136.92</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>60862.72</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2192</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>₹2178.89 - ₹2211.67</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>2244.46</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2137.24</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2019.77</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1959.51</v>
+      </c>
+      <c r="L10" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="M10" t="n">
+        <v>40.45</v>
+      </c>
+      <c r="N10" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-10.88</v>
+      </c>
+      <c r="P10" t="n">
+        <v>65.56999999999999</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="R10" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="U10" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2151.12</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2502.41</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2502.41</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2093.64</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2199.9</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2221.1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2250.2</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.45) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>2253.73</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2132.78</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,862.72 Cr., a P/E ratio of 49.51, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.21 (Consolidation Zone), while MACD Line (40.45) trades below Signal (51.33) with an expanding histogram (-10.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.85% above the 200-day DMA (₹1959.51). Daily volatility envelope is bounded by ATR(14) of ₹65.57.</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,192.00) is positioned above the 30-day DMA (₹2,137.24), 50-day DMA (₹2,019.77), and 200-day DMA (₹1,959.51). The price distance from 200 DMA is +15.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>[2192.0, 2198.58, 2205.15, 2211.73, 2218.3, 2224.88]</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>[2192.0, 2224.81, 2242.25, 2257.16, 2270.76, 2283.53]</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>[2192.0, 2178.9, 2177.33, 2177.65, 2178.96, 2180.89]</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>2502.41</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>43252.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>288.35</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>₹287.21 - ₹290.06</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>292.91</v>
+      </c>
+      <c r="I11" t="n">
+        <v>287.58</v>
+      </c>
+      <c r="J11" t="n">
+        <v>283.63</v>
+      </c>
+      <c r="K11" t="n">
+        <v>278.82</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>11.45</v>
+      </c>
+      <c r="R11" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="U11" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X11" t="n">
+        <v>286.55</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>316.54</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>316.54</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>279.8</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>288.33</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>289.66</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>290.98</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Vol Spike 2.1x | Low VIX (11.45) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>-53.2</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>297</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>280.24</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,252.50 Cr., a P/E ratio of 10.28, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 40.27 (Consolidation Zone), while MACD Line (0.41) trades below Signal (1.02) with an expanding histogram (-0.61). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.94% above the 200-day DMA (₹278.82). Daily volatility envelope is bounded by ATR(14) of ₹5.70.</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹288.35) is positioned above the 30-day DMA (₹287.58), 50-day DMA (₹283.63), and 200-day DMA (₹278.82). The price distance from 200 DMA is +4.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>[288.35, 289.22, 290.08, 290.95, 291.81, 292.68]</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>[288.35, 291.5, 293.3, 294.89, 296.37, 297.77]</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>[288.35, 287.51, 287.66, 287.98, 288.39, 288.85]</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>316.54</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU11"/>
+  <dimension ref="A1:AU10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>416060.72</v>
+        <v>412628.76</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,15 +678,15 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>418.25</v>
+        <v>414.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹416.99 - ₹420.14</t>
+          <t>₹413.54 - ₹416.69</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>423.28</v>
+        <v>419.83</v>
       </c>
       <c r="I2" t="n">
         <v>409.2</v>
@@ -713,10 +713,10 @@
         <v>6.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.45</v>
+        <v>11.25</v>
       </c>
       <c r="R2" t="n">
-        <v>52.5</v>
+        <v>52.7</v>
       </c>
       <c r="S2" t="n">
         <v>0.35</v>
@@ -734,25 +734,25 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
+        <v>414.8</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>439.96</v>
+      </c>
+      <c r="Z2" t="n">
         <v>418.25</v>
       </c>
-      <c r="Y2" t="n">
-        <v>443.54</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>421.73</v>
-      </c>
       <c r="AA2" t="n">
-        <v>408.82</v>
+        <v>405.37</v>
       </c>
       <c r="AB2" t="n">
-        <v>417.5</v>
+        <v>416.65</v>
       </c>
       <c r="AC2" t="n">
-        <v>420.45</v>
+        <v>418.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>422.65</v>
+        <v>422.7</v>
       </c>
       <c r="AE2" t="n">
         <v>42.8</v>
@@ -762,14 +762,14 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Low VIX (11.45) | LSTM Deep Net</t>
+          <t>Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AJ2" t="n">
         <v>21</v>
@@ -781,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>426.9</v>
+        <v>424.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>409.54</v>
+        <v>406.65</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹416,060.72 Cr., a P/E ratio of 20.48, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹412,628.76 Cr., a P/E ratio of 20.31, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -798,26 +798,26 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹418.25) is positioned above the 30-day DMA (₹409.20), 50-day DMA (₹400.39), and 200-day DMA (₹399.71). The price distance from 200 DMA is +3.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹414.80) is positioned above the 30-day DMA (₹409.20), 50-day DMA (₹400.39), and 200-day DMA (₹399.71). The price distance from 200 DMA is +3.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[418.25, 420.23, 422.21, 424.18, 426.16, 428.14]</t>
+          <t>[414.8, 416.15, 417.51, 418.86, 420.21, 421.57]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[418.25, 422.74, 425.76, 428.54, 431.19, 433.76]</t>
+          <t>[414.8, 418.67, 421.06, 423.22, 425.24, 427.19]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[418.25, 418.34, 419.54, 420.92, 422.39, 423.92]</t>
+          <t>[414.8, 414.27, 414.84, 415.59, 416.44, 417.35]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>421.73</v>
+        <v>418.25</v>
       </c>
     </row>
     <row r="3">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>304192.24</v>
+        <v>309209.15</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,15 +845,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>330.55</v>
+        <v>335.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹329.19 - ₹332.59</t>
+          <t>₹334.54 - ₹337.94</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>335.99</v>
+        <v>341.34</v>
       </c>
       <c r="I3" t="n">
         <v>322.48</v>
@@ -880,46 +880,46 @@
         <v>6.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.45</v>
+        <v>11.25</v>
       </c>
       <c r="R3" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.03</v>
+        <v>-0.98</v>
       </c>
       <c r="U3" t="n">
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>330.55</v>
+        <v>335.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>356.11</v>
+        <v>362.09</v>
       </c>
       <c r="Z3" t="n">
-        <v>356.11</v>
+        <v>362.09</v>
       </c>
       <c r="AA3" t="n">
-        <v>320.35</v>
+        <v>325.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>329.93</v>
+        <v>333.08</v>
       </c>
       <c r="AC3" t="n">
-        <v>333.01</v>
+        <v>339.31</v>
       </c>
       <c r="AD3" t="n">
-        <v>335.48</v>
+        <v>342.73</v>
       </c>
       <c r="AE3" t="n">
         <v>48</v>
@@ -929,14 +929,14 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.45) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>718.4</v>
+        <v>730.2</v>
       </c>
       <c r="AJ3" t="n">
         <v>182</v>
@@ -948,14 +948,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>342.06</v>
+        <v>348.58</v>
       </c>
       <c r="AN3" t="n">
-        <v>320.63</v>
+        <v>324.08</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹304,192.24 Cr., a P/E ratio of 718.37, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹309,209.15 Cr., a P/E ratio of 730.22, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -965,26 +965,26 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹330.55) is positioned above the 30-day DMA (₹322.48), 50-day DMA (₹312.65), and 200-day DMA (₹274.58). The price distance from 200 DMA is +19.03%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹335.90) is positioned above the 30-day DMA (₹322.48), 50-day DMA (₹312.65), and 200-day DMA (₹274.58). The price distance from 200 DMA is +19.03%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[330.55, 332.48, 334.41, 336.34, 338.27, 340.21]</t>
+          <t>[335.9, 338.78, 341.66, 344.53, 347.41, 350.29]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[330.55, 335.2, 338.26, 341.05, 343.71, 346.29]</t>
+          <t>[335.9, 341.5, 345.5, 349.24, 352.85, 356.37]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[330.55, 330.44, 331.53, 332.81, 334.19, 335.64]</t>
+          <t>[335.9, 336.74, 338.77, 341.0, 343.33, 345.73]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>356.11</v>
+        <v>362.09</v>
       </c>
     </row>
     <row r="4">
@@ -995,7 +995,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31240.83</v>
+        <v>126974.77</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,146 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>567.95</v>
+        <v>11409</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹564.59 - ₹572.99</t>
+          <t>₹11368.68 - ₹11469.49</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>581.4</v>
+        <v>11570.29</v>
       </c>
       <c r="I4" t="n">
-        <v>524.02</v>
+        <v>11202.02</v>
       </c>
       <c r="J4" t="n">
-        <v>525.63</v>
+        <v>11040.03</v>
       </c>
       <c r="K4" t="n">
-        <v>523.7</v>
+        <v>10524.86</v>
       </c>
       <c r="L4" t="n">
-        <v>4.67</v>
+        <v>6.58</v>
       </c>
       <c r="M4" t="n">
-        <v>9.720000000000001</v>
+        <v>-27.8</v>
       </c>
       <c r="N4" t="n">
-        <v>10.11</v>
+        <v>-14.3</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.39</v>
+        <v>-13.5</v>
       </c>
       <c r="P4" t="n">
-        <v>16.81</v>
+        <v>201.62</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.45</v>
+        <v>11.25</v>
       </c>
       <c r="R4" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="S4" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.76</v>
+        <v>-0.87</v>
       </c>
       <c r="U4" t="n">
-        <v>48.3</v>
+        <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>4.93</v>
+        <v>3.8</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>567.95</v>
+        <v>11366.84</v>
       </c>
       <c r="Y4" t="n">
-        <v>603.15</v>
+        <v>12523.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>603.15</v>
+        <v>12523.22</v>
       </c>
       <c r="AA4" t="n">
-        <v>542.73</v>
+        <v>11106.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>560</v>
+        <v>11356.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>576.35</v>
+        <v>11486.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>584.75</v>
+        <v>11563.67</v>
       </c>
       <c r="AE4" t="n">
-        <v>56.4</v>
+        <v>39.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.22</v>
+        <v>0.04</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.45) | LSTM Deep Net</t>
+          <t>Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>5.4</v>
+        <v>14.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>14.5</v>
+        <v>24.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>65.2</v>
+        <v>734.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="AM4" t="n">
-        <v>583.0599999999999</v>
+        <v>11740.37</v>
       </c>
       <c r="AN4" t="n">
-        <v>552.47</v>
+        <v>11069.05</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,240.83 Cr., a P/E ratio of 5.44, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹126,974.77 Cr., a P/E ratio of 14.34, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.36 (Bullish Momentum Zone), while MACD Line (9.72) trades below Signal (10.11) with an expanding histogram (-0.39). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.67% above the 200-day DMA (₹523.70). Daily volatility envelope is bounded by ATR(14) of ₹16.81.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.50 (Consolidation Zone), while MACD Line (-27.80) trades below Signal (-14.30) with an expanding histogram (-13.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.58% above the 200-day DMA (₹10524.86). Daily volatility envelope is bounded by ATR(14) of ₹201.62.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹567.95) is positioned above the 30-day DMA (₹524.02), 50-day DMA (₹525.63), and 200-day DMA (₹523.70). The price distance from 200 DMA is +4.67%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,409.00) is positioned above the 30-day DMA (₹11,202.02), 50-day DMA (₹11,040.03), and 200-day DMA (₹10,524.86). The price distance from 200 DMA is +6.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[567.95, 569.65, 571.36, 573.06, 574.77, 576.47]</t>
+          <t>[11409.0, 11443.23, 11477.45, 11511.68, 11545.91, 11580.13]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[567.95, 576.38, 580.87, 584.71, 588.21, 591.51]</t>
+          <t>[11409.0, 11523.87, 11591.51, 11651.37, 11707.2, 11760.47]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[567.95, 564.61, 564.23, 564.33, 564.68, 565.19]</t>
+          <t>[11409.0, 11382.74, 11391.92, 11406.92, 11424.94, 11444.89]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>603.15</v>
+        <v>12523.22</v>
       </c>
     </row>
     <row r="5">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>134892.67</v>
+        <v>31243.58</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,146 +1179,146 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>117.37</v>
+        <v>568</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹116.94 - ₹118.01</t>
+          <t>₹564.62 - ₹573.06</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>119.08</v>
+        <v>581.5</v>
       </c>
       <c r="I5" t="n">
-        <v>116.33</v>
+        <v>525.74</v>
       </c>
       <c r="J5" t="n">
-        <v>114.03</v>
+        <v>525.78</v>
       </c>
       <c r="K5" t="n">
-        <v>112.31</v>
+        <v>523.73</v>
       </c>
       <c r="L5" t="n">
-        <v>4.42</v>
+        <v>4.66</v>
       </c>
       <c r="M5" t="n">
-        <v>0.64</v>
+        <v>8.93</v>
       </c>
       <c r="N5" t="n">
-        <v>0.75</v>
+        <v>9.85</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.12</v>
+        <v>-0.92</v>
       </c>
       <c r="P5" t="n">
-        <v>2.14</v>
+        <v>16.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.45</v>
+        <v>11.25</v>
       </c>
       <c r="R5" t="n">
-        <v>46.4</v>
+        <v>47.8</v>
       </c>
       <c r="S5" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.99</v>
+        <v>-1.79</v>
       </c>
       <c r="U5" t="n">
-        <v>53.3</v>
+        <v>48.3</v>
       </c>
       <c r="V5" t="n">
-        <v>2.6</v>
+        <v>4.76</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>117.37</v>
+        <v>568</v>
       </c>
       <c r="Y5" t="n">
-        <v>126.01</v>
+        <v>603.71</v>
       </c>
       <c r="Z5" t="n">
-        <v>126.01</v>
+        <v>603.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>114.16</v>
+        <v>542.6900000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>117.27</v>
+        <v>561.9299999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>117.9</v>
+        <v>580.21</v>
       </c>
       <c r="AD5" t="n">
-        <v>118.43</v>
+        <v>592.4299999999999</v>
       </c>
       <c r="AE5" t="n">
-        <v>61.7</v>
+        <v>54.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.45) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>38.1</v>
+        <v>65.2</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>120.41</v>
+        <v>582.64</v>
       </c>
       <c r="AN5" t="n">
-        <v>114.14</v>
+        <v>552.88</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,892.67 Cr., a P/E ratio of 6.11, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,243.58 Cr., a P/E ratio of 5.45, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.75 (Bullish Momentum Zone), while MACD Line (0.64) trades below Signal (0.75) with an expanding histogram (-0.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.42% above the 200-day DMA (₹112.31). Daily volatility envelope is bounded by ATR(14) of ₹2.14.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.87 (Consolidation Zone), while MACD Line (8.93) trades below Signal (9.85) with an expanding histogram (-0.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.66% above the 200-day DMA (₹523.73). Daily volatility envelope is bounded by ATR(14) of ₹16.88.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.37) is positioned above the 30-day DMA (₹116.33), 50-day DMA (₹114.03), and 200-day DMA (₹112.31). The price distance from 200 DMA is +4.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹568.00) is positioned above the 30-day DMA (₹525.74), 50-day DMA (₹525.78), and 200-day DMA (₹523.73). The price distance from 200 DMA is +4.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[117.37, 118.26, 119.15, 120.04, 120.93, 121.82]</t>
+          <t>[568.0, 570.76, 573.52, 576.27, 579.03, 581.79]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[117.37, 119.12, 120.36, 121.52, 122.64, 123.73]</t>
+          <t>[568.0, 577.51, 583.06, 587.96, 592.53, 596.88]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[117.37, 117.62, 118.24, 118.93, 119.64, 120.38]</t>
+          <t>[568.0, 565.7, 566.36, 567.51, 568.91, 570.47]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>126.01</v>
+        <v>603.2</v>
       </c>
     </row>
     <row r="6">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>126874.6</v>
+        <v>135616.72</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,146 +1346,146 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>11400</v>
+        <v>118</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹11355.25 - ₹11467.13</t>
+          <t>₹117.57 - ₹118.64</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11579.02</v>
+        <v>119.71</v>
       </c>
       <c r="I6" t="n">
-        <v>11210.4</v>
+        <v>116.33</v>
       </c>
       <c r="J6" t="n">
-        <v>11032.95</v>
+        <v>114.03</v>
       </c>
       <c r="K6" t="n">
-        <v>10525.23</v>
+        <v>112.31</v>
       </c>
       <c r="L6" t="n">
-        <v>6.57</v>
+        <v>4.42</v>
       </c>
       <c r="M6" t="n">
-        <v>-24.46</v>
+        <v>0.64</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.61</v>
+        <v>0.75</v>
       </c>
       <c r="O6" t="n">
-        <v>-17.85</v>
+        <v>-0.12</v>
       </c>
       <c r="P6" t="n">
-        <v>223.77</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.45</v>
+        <v>11.25</v>
       </c>
       <c r="R6" t="n">
-        <v>46.4</v>
+        <v>45.8</v>
       </c>
       <c r="S6" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.09</v>
+        <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>51.7</v>
+        <v>53.3</v>
       </c>
       <c r="V6" t="n">
-        <v>3.88</v>
+        <v>2.6</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>11345.34</v>
+        <v>118</v>
       </c>
       <c r="Y6" t="n">
-        <v>12513.34</v>
+        <v>126.69</v>
       </c>
       <c r="Z6" t="n">
-        <v>12513.34</v>
+        <v>126.69</v>
       </c>
       <c r="AA6" t="n">
-        <v>11064.34</v>
+        <v>114.79</v>
       </c>
       <c r="AB6" t="n">
-        <v>11353.67</v>
+        <v>117.74</v>
       </c>
       <c r="AC6" t="n">
-        <v>11480.34</v>
+        <v>118.84</v>
       </c>
       <c r="AD6" t="n">
-        <v>11560.67</v>
+        <v>119.68</v>
       </c>
       <c r="AE6" t="n">
-        <v>48.6</v>
+        <v>61.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01</v>
+        <v>-0.11</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Low VIX (11.45) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>14.3</v>
+        <v>6.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24.2</v>
+        <v>-6.4</v>
       </c>
       <c r="AK6" t="n">
-        <v>734.6</v>
+        <v>38.1</v>
       </c>
       <c r="AL6" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>11712.13</v>
+        <v>121.04</v>
       </c>
       <c r="AN6" t="n">
-        <v>11079.54</v>
+        <v>114.72</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹126,874.60 Cr., a P/E ratio of 14.33, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹135,616.72 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.57 (Consolidation Zone), while MACD Line (-24.46) trades below Signal (-6.61) with an expanding histogram (-17.85). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.57% above the 200-day DMA (₹10525.23). Daily volatility envelope is bounded by ATR(14) of ₹223.77.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.75 (Bullish Momentum Zone), while MACD Line (0.64) trades below Signal (0.75) with an expanding histogram (-0.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.42% above the 200-day DMA (₹112.31). Daily volatility envelope is bounded by ATR(14) of ₹2.14.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,400.00) is positioned above the 30-day DMA (₹11,210.40), 50-day DMA (₹11,032.95), and 200-day DMA (₹10,525.23). The price distance from 200 DMA is +6.57%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹118.00) is positioned above the 30-day DMA (₹116.33), 50-day DMA (₹114.03), and 200-day DMA (₹112.31). The price distance from 200 DMA is +4.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[11400.0, 11434.2, 11468.4, 11502.6, 11536.8, 11571.0]</t>
+          <t>[118.0, 118.94, 119.89, 120.83, 121.78, 122.72]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[11400.0, 11523.71, 11594.99, 11657.64, 11715.82, 11771.15]</t>
+          <t>[118.0, 119.8, 121.1, 122.32, 123.49, 124.64]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[11400.0, 11367.07, 11373.46, 11386.32, 11402.54, 11420.89]</t>
+          <t>[118.0, 118.3, 118.98, 119.72, 120.49, 121.28]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>12513.34</v>
+        <v>126.69</v>
       </c>
     </row>
     <row r="7">
@@ -1496,16 +1496,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25000</v>
+        <v>60560.07</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,146 +1513,146 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3252</v>
+        <v>2181.1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹3231.11 - ₹3283.34</t>
+          <t>₹2168.34 - ₹2200.25</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3335.57</v>
+        <v>2232.16</v>
       </c>
       <c r="I7" t="n">
-        <v>3158.2</v>
+        <v>2143.45</v>
       </c>
       <c r="J7" t="n">
-        <v>2990.66</v>
+        <v>2026.16</v>
       </c>
       <c r="K7" t="n">
-        <v>2695.53</v>
+        <v>1961.52</v>
       </c>
       <c r="L7" t="n">
-        <v>20.94</v>
+        <v>15.73</v>
       </c>
       <c r="M7" t="n">
-        <v>69.94</v>
+        <v>37.59</v>
       </c>
       <c r="N7" t="n">
-        <v>96.14</v>
+        <v>47.03</v>
       </c>
       <c r="O7" t="n">
-        <v>-26.2</v>
+        <v>-9.44</v>
       </c>
       <c r="P7" t="n">
-        <v>104.46</v>
+        <v>63.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.45</v>
+        <v>11.25</v>
       </c>
       <c r="R7" t="n">
-        <v>43</v>
+        <v>43.7</v>
       </c>
       <c r="S7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.18</v>
+        <v>-1.97</v>
       </c>
       <c r="U7" t="n">
-        <v>53.3</v>
+        <v>55</v>
       </c>
       <c r="V7" t="n">
-        <v>3.06</v>
+        <v>3.19</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>3252</v>
+        <v>2142.17</v>
       </c>
       <c r="Y7" t="n">
-        <v>4207.71</v>
+        <v>2489.97</v>
       </c>
       <c r="Z7" t="n">
-        <v>4207.71</v>
+        <v>2489.97</v>
       </c>
       <c r="AA7" t="n">
-        <v>3095.31</v>
+        <v>2085.37</v>
       </c>
       <c r="AB7" t="n">
-        <v>3245.03</v>
+        <v>2196.27</v>
       </c>
       <c r="AC7" t="n">
-        <v>3274.96</v>
+        <v>2213.84</v>
       </c>
       <c r="AD7" t="n">
-        <v>3297.93</v>
+        <v>2246.57</v>
       </c>
       <c r="AE7" t="n">
-        <v>45.1</v>
+        <v>55.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.45) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>53.9</v>
+        <v>49.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>85.3</v>
+        <v>8.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>55.6</v>
+        <v>5.2</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>3388.26</v>
+        <v>2245.77</v>
       </c>
       <c r="AN7" t="n">
-        <v>3136.5</v>
+        <v>2123.48</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.92, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,560.07 Cr., a P/E ratio of 49.27, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 45.14 (Consolidation Zone), while MACD Line (69.94) trades below Signal (96.14) with an expanding histogram (-26.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.94% above the 200-day DMA (₹2695.53). Daily volatility envelope is bounded by ATR(14) of ₹104.46.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.51 (Bullish Momentum Zone), while MACD Line (37.59) trades below Signal (47.03) with an expanding histogram (-9.44). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.73% above the 200-day DMA (₹1961.52). Daily volatility envelope is bounded by ATR(14) of ₹63.82.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,252.00) is positioned above the 30-day DMA (₹3,158.20), 50-day DMA (₹2,990.66), and 200-day DMA (₹2,695.53). The price distance from 200 DMA is +20.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,181.10) is positioned above the 30-day DMA (₹2,143.45), 50-day DMA (₹2,026.16), and 200-day DMA (₹1,961.52). The price distance from 200 DMA is +15.73%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[3252.0, 3281.99, 3311.97, 3341.96, 3371.95, 3401.93]</t>
+          <t>[2181.1, 2187.64, 2194.19, 2200.73, 2207.27, 2213.82]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[3252.0, 3323.77, 3371.06, 3414.33, 3455.51, 3495.36]</t>
+          <t>[2181.1, 2213.17, 2230.29, 2244.94, 2258.33, 2270.9]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[3252.0, 3250.65, 3267.66, 3287.68, 3309.27, 3331.86]</t>
+          <t>[2181.1, 2168.5, 2167.11, 2167.57, 2168.98, 2171.01]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>4207.71</v>
+        <v>2489.97</v>
       </c>
     </row>
     <row r="8">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>108046.98</v>
+        <v>107772.12</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1680,15 +1680,15 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>746.9</v>
+        <v>745</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹743.93 - ₹751.36</t>
+          <t>₹742.03 - ₹749.46</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>758.79</v>
+        <v>756.89</v>
       </c>
       <c r="I8" t="n">
         <v>722.89</v>
@@ -1715,46 +1715,46 @@
         <v>14.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.45</v>
+        <v>11.25</v>
       </c>
       <c r="R8" t="n">
-        <v>42.1</v>
+        <v>42.7</v>
       </c>
       <c r="S8" t="n">
         <v>0.27</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.28</v>
+        <v>-1.26</v>
       </c>
       <c r="U8" t="n">
         <v>46.7</v>
       </c>
       <c r="V8" t="n">
-        <v>11.58</v>
+        <v>11.57</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>742.1</v>
+        <v>740.17</v>
       </c>
       <c r="Y8" t="n">
-        <v>800.9299999999999</v>
+        <v>798.89</v>
       </c>
       <c r="Z8" t="n">
-        <v>800.9299999999999</v>
+        <v>798.89</v>
       </c>
       <c r="AA8" t="n">
-        <v>724.6</v>
+        <v>722.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>747.63</v>
+        <v>747</v>
       </c>
       <c r="AC8" t="n">
-        <v>754.26</v>
+        <v>753</v>
       </c>
       <c r="AD8" t="n">
-        <v>761.63</v>
+        <v>761</v>
       </c>
       <c r="AE8" t="n">
         <v>47.2</v>
@@ -1764,14 +1764,14 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Vol Spike 2.0x | Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.45) | LSTM Deep Net</t>
+          <t>Vol Spike 2.0x | Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="AJ8" t="n">
         <v>15.1</v>
@@ -1783,14 +1783,14 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>765.45</v>
+        <v>762.49</v>
       </c>
       <c r="AN8" t="n">
-        <v>728.23</v>
+        <v>725.42</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹108,046.98 Cr., a P/E ratio of 49.50, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹107,772.12 Cr., a P/E ratio of 49.37, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -1800,26 +1800,26 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹746.90) is positioned above the 30-day DMA (₹722.89), 50-day DMA (₹727.97), and 200-day DMA (₹686.01). The price distance from 200 DMA is +6.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹745.00) is positioned above the 30-day DMA (₹722.89), 50-day DMA (₹727.97), and 200-day DMA (₹686.01). The price distance from 200 DMA is +6.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[746.9, 749.14, 751.38, 753.62, 755.86, 758.1]</t>
+          <t>[745.0, 747.23, 749.47, 751.7, 753.94, 756.17]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[746.9, 755.09, 759.79, 763.92, 767.76, 771.4]</t>
+          <t>[745.0, 753.18, 757.88, 762.01, 765.83, 769.47]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[746.9, 744.68, 745.07, 745.9, 746.94, 748.13]</t>
+          <t>[745.0, 742.77, 743.16, 743.98, 745.02, 746.2]</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>800.9299999999999</v>
+        <v>798.89</v>
       </c>
     </row>
     <row r="9">
@@ -1839,7 +1839,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60852.46</v>
+        <v>59996.24</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1847,98 +1847,98 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1009.2</v>
+        <v>995</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹1003.49 - ₹1017.76</t>
+          <t>₹989.4 - ₹1003.41</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1032.03</v>
+        <v>1017.42</v>
       </c>
       <c r="I9" t="n">
-        <v>985.39</v>
+        <v>989.35</v>
       </c>
       <c r="J9" t="n">
-        <v>956.52</v>
+        <v>956.71</v>
       </c>
       <c r="K9" t="n">
-        <v>851.29</v>
+        <v>851.66</v>
       </c>
       <c r="L9" t="n">
-        <v>18.64</v>
+        <v>18.59</v>
       </c>
       <c r="M9" t="n">
-        <v>15.27</v>
+        <v>12.75</v>
       </c>
       <c r="N9" t="n">
-        <v>23.34</v>
+        <v>20.95</v>
       </c>
       <c r="O9" t="n">
-        <v>-8.07</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>28.54</v>
+        <v>28.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.45</v>
+        <v>11.25</v>
       </c>
       <c r="R9" t="n">
-        <v>41.9</v>
+        <v>42.2</v>
       </c>
       <c r="S9" t="n">
         <v>0.19</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.98</v>
+        <v>-1.95</v>
       </c>
       <c r="U9" t="n">
         <v>51.7</v>
       </c>
       <c r="V9" t="n">
-        <v>3.73</v>
+        <v>3.54</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>1009.2</v>
+        <v>995</v>
       </c>
       <c r="Y9" t="n">
-        <v>1136.92</v>
+        <v>1120.93</v>
       </c>
       <c r="Z9" t="n">
-        <v>1136.92</v>
+        <v>1120.93</v>
       </c>
       <c r="AA9" t="n">
-        <v>966.39</v>
+        <v>952.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>1004.07</v>
+        <v>999.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>1014.94</v>
+        <v>1005.46</v>
       </c>
       <c r="AD9" t="n">
-        <v>1020.67</v>
+        <v>1015.93</v>
       </c>
       <c r="AE9" t="n">
-        <v>43.4</v>
+        <v>42.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.45) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>31.3</v>
+        <v>30.9</v>
       </c>
       <c r="AJ9" t="n">
         <v>23.9</v>
@@ -1950,43 +1950,43 @@
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>1051.14</v>
+        <v>1035.09</v>
       </c>
       <c r="AN9" t="n">
-        <v>971.54</v>
+        <v>957.11</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹60,852.46 Cr., a P/E ratio of 31.32, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹59,996.24 Cr., a P/E ratio of 30.88, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.42 (Consolidation Zone), while MACD Line (15.27) trades below Signal (23.34) with an expanding histogram (-8.07). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.64% above the 200-day DMA (₹851.29). Daily volatility envelope is bounded by ATR(14) of ₹28.54.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.19 (Consolidation Zone), while MACD Line (12.75) trades below Signal (20.95) with an expanding histogram (-8.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.59% above the 200-day DMA (₹851.66). Daily volatility envelope is bounded by ATR(14) of ₹28.02.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,009.20) is positioned above the 30-day DMA (₹985.39), 50-day DMA (₹956.52), and 200-day DMA (₹851.29). The price distance from 200 DMA is +18.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹995.00) is positioned above the 30-day DMA (₹989.35), 50-day DMA (₹956.71), and 200-day DMA (₹851.66). The price distance from 200 DMA is +18.59%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[1009.2, 1012.23, 1015.26, 1018.28, 1021.31, 1024.34]</t>
+          <t>[995.0, 997.98, 1000.97, 1003.95, 1006.94, 1009.92]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[1009.2, 1023.64, 1031.4, 1038.06, 1044.14, 1049.86]</t>
+          <t>[995.0, 1009.19, 1016.82, 1023.37, 1029.36, 1034.99]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[1009.2, 1003.67, 1003.15, 1003.45, 1004.19, 1005.19]</t>
+          <t>[995.0, 989.58, 989.08, 989.39, 990.13, 991.13]</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1136.92</v>
+        <v>1120.93</v>
       </c>
     </row>
     <row r="10">
@@ -1997,16 +1997,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>60862.72</v>
+        <v>25000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2014,313 +2014,146 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2192</v>
+        <v>3209</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹2178.89 - ₹2211.67</t>
+          <t>₹3188.04 - ₹3240.44</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2244.46</v>
+        <v>3292.85</v>
       </c>
       <c r="I10" t="n">
-        <v>2137.24</v>
+        <v>3179.33</v>
       </c>
       <c r="J10" t="n">
-        <v>2019.77</v>
+        <v>3000.69</v>
       </c>
       <c r="K10" t="n">
-        <v>1959.51</v>
+        <v>2701.74</v>
       </c>
       <c r="L10" t="n">
-        <v>15.85</v>
+        <v>20.66</v>
       </c>
       <c r="M10" t="n">
-        <v>40.45</v>
+        <v>65.67</v>
       </c>
       <c r="N10" t="n">
-        <v>51.33</v>
+        <v>90.11</v>
       </c>
       <c r="O10" t="n">
-        <v>-10.88</v>
+        <v>-24.44</v>
       </c>
       <c r="P10" t="n">
-        <v>65.56999999999999</v>
+        <v>104.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.45</v>
+        <v>11.25</v>
       </c>
       <c r="R10" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="S10" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.18</v>
+        <v>-2.4</v>
       </c>
       <c r="U10" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="V10" t="n">
-        <v>3.11</v>
+        <v>2.96</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>2151.12</v>
+        <v>3202.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>2502.41</v>
+        <v>4147.04</v>
       </c>
       <c r="Z10" t="n">
-        <v>2502.41</v>
+        <v>4147.04</v>
       </c>
       <c r="AA10" t="n">
-        <v>2093.64</v>
+        <v>3051.78</v>
       </c>
       <c r="AB10" t="n">
-        <v>2199.9</v>
+        <v>3210.83</v>
       </c>
       <c r="AC10" t="n">
-        <v>2221.1</v>
+        <v>3266.16</v>
       </c>
       <c r="AD10" t="n">
-        <v>2250.2</v>
+        <v>3323.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>51.2</v>
+        <v>39.8</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.45) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>49.5</v>
+        <v>53.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>8.5</v>
+        <v>85.3</v>
       </c>
       <c r="AK10" t="n">
-        <v>5.2</v>
+        <v>55.6</v>
       </c>
       <c r="AL10" t="n">
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>2253.73</v>
+        <v>3340.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>2132.78</v>
+        <v>3097.14</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,862.72 Cr., a P/E ratio of 49.51, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.21, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.21 (Consolidation Zone), while MACD Line (40.45) trades below Signal (51.33) with an expanding histogram (-10.88). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.85% above the 200-day DMA (₹1959.51). Daily volatility envelope is bounded by ATR(14) of ₹65.57.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.75 (Consolidation Zone), while MACD Line (65.67) trades below Signal (90.11) with an expanding histogram (-24.44). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.66% above the 200-day DMA (₹2701.74). Daily volatility envelope is bounded by ATR(14) of ₹104.81.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,192.00) is positioned above the 30-day DMA (₹2,137.24), 50-day DMA (₹2,019.77), and 200-day DMA (₹1,959.51). The price distance from 200 DMA is +15.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,209.00) is positioned above the 30-day DMA (₹3,179.33), 50-day DMA (₹3,000.69), and 200-day DMA (₹2,701.74). The price distance from 200 DMA is +20.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[2192.0, 2198.58, 2205.15, 2211.73, 2218.3, 2224.88]</t>
+          <t>[3209.0, 3218.63, 3228.25, 3237.88, 3247.51, 3257.13]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[2192.0, 2224.81, 2242.25, 2257.16, 2270.76, 2283.53]</t>
+          <t>[3209.0, 3260.55, 3287.55, 3310.5, 3331.36, 3350.88]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[2192.0, 2178.9, 2177.33, 2177.65, 2178.96, 2180.89]</t>
+          <t>[3209.0, 3187.18, 3183.79, 3183.42, 3184.62, 3186.82]</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>2502.41</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>43252.5</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>288.35</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>₹287.21 - ₹290.06</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>292.91</v>
-      </c>
-      <c r="I11" t="n">
-        <v>287.58</v>
-      </c>
-      <c r="J11" t="n">
-        <v>283.63</v>
-      </c>
-      <c r="K11" t="n">
-        <v>278.82</v>
-      </c>
-      <c r="L11" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-0.61</v>
-      </c>
-      <c r="P11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="R11" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="U11" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X11" t="n">
-        <v>286.55</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>316.54</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>316.54</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>279.8</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>288.33</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>289.66</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>290.98</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>Vol Spike 2.1x | Low VIX (11.45) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>-53.2</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>297</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>280.24</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,252.50 Cr., a P/E ratio of 10.28, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 40.27 (Consolidation Zone), while MACD Line (0.41) trades below Signal (1.02) with an expanding histogram (-0.61). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.94% above the 200-day DMA (₹278.82). Daily volatility envelope is bounded by ATR(14) of ₹5.70.</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹288.35) is positioned above the 30-day DMA (₹287.58), 50-day DMA (₹283.63), and 200-day DMA (₹278.82). The price distance from 200 DMA is +4.94%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>[288.35, 289.22, 290.08, 290.95, 291.81, 292.68]</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>[288.35, 291.5, 293.3, 294.89, 296.37, 297.77]</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>[288.35, 287.51, 287.66, 287.98, 288.39, 288.85]</t>
-        </is>
-      </c>
-      <c r="AU11" t="n">
-        <v>316.54</v>
+        <v>4147.04</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -656,188 +656,188 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>412628.76</v>
+        <v>310405.89</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🟢 HIGH CONVICTION BUY</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>414.8</v>
+        <v>337.2</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹413.54 - ₹416.69</t>
+          <t>₹335.84 - ₹339.24</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>419.83</v>
+        <v>342.64</v>
       </c>
       <c r="I2" t="n">
-        <v>409.2</v>
+        <v>322.48</v>
       </c>
       <c r="J2" t="n">
-        <v>400.39</v>
+        <v>312.65</v>
       </c>
       <c r="K2" t="n">
-        <v>399.71</v>
+        <v>274.58</v>
       </c>
       <c r="L2" t="n">
-        <v>3.2</v>
+        <v>19.03</v>
       </c>
       <c r="M2" t="n">
-        <v>3.88</v>
+        <v>2.23</v>
       </c>
       <c r="N2" t="n">
-        <v>5.59</v>
+        <v>3.41</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.7</v>
+        <v>-1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>6.29</v>
+        <v>6.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="R2" t="n">
-        <v>52.7</v>
+        <v>50</v>
       </c>
       <c r="S2" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.73</v>
+        <v>-0.93</v>
       </c>
       <c r="U2" t="n">
-        <v>51.7</v>
+        <v>55</v>
       </c>
       <c r="V2" t="n">
-        <v>3.6</v>
+        <v>2.57</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>414.8</v>
+        <v>331.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>439.96</v>
+        <v>324.03</v>
       </c>
       <c r="Z2" t="n">
-        <v>418.25</v>
+        <v>307.21</v>
       </c>
       <c r="AA2" t="n">
-        <v>405.37</v>
+        <v>327</v>
       </c>
       <c r="AB2" t="n">
-        <v>416.65</v>
+        <v>337.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>418.75</v>
+        <v>339.65</v>
       </c>
       <c r="AD2" t="n">
-        <v>422.7</v>
+        <v>342.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>42.8</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.01</v>
+        <v>0.25</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Low VIX (11.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>20.3</v>
+        <v>733</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="AK2" t="n">
-        <v>28.5</v>
+        <v>0.6</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>424.2</v>
+        <v>348.32</v>
       </c>
       <c r="AN2" t="n">
-        <v>406.65</v>
+        <v>326.28</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹412,628.76 Cr., a P/E ratio of 20.31, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹310,405.89 Cr., a P/E ratio of 733.04, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.84 (Consolidation Zone), while MACD Line (3.88) trades below Signal (5.59) with an expanding histogram (-1.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.20% above the 200-day DMA (₹399.71). Daily volatility envelope is bounded by ATR(14) of ₹6.29.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.04 (Consolidation Zone), while MACD Line (2.23) trades below Signal (3.41) with an expanding histogram (-1.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.03% above the 200-day DMA (₹274.58). Daily volatility envelope is bounded by ATR(14) of ₹6.80.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹414.80) is positioned above the 30-day DMA (₹409.20), 50-day DMA (₹400.39), and 200-day DMA (₹399.71). The price distance from 200 DMA is +3.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹337.20) is positioned above the 30-day DMA (₹322.48), 50-day DMA (₹312.65), and 200-day DMA (₹274.58). The price distance from 200 DMA is +19.03%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[414.8, 416.15, 417.51, 418.86, 420.21, 421.57]</t>
+          <t>[337.2, 340.33, 343.46, 346.59, 349.73, 352.86]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[414.8, 418.67, 421.06, 423.22, 425.24, 427.19]</t>
+          <t>[337.2, 343.05, 347.31, 351.31, 355.17, 358.94]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[414.8, 414.27, 414.84, 415.59, 416.44, 417.35]</t>
+          <t>[337.2, 338.29, 340.58, 343.06, 345.65, 348.3]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>418.25</v>
+        <v>307.21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>309209.15</v>
+        <v>411742.82</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,157 +845,157 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>335.9</v>
+        <v>413.9</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹334.54 - ₹337.94</t>
+          <t>₹412.64 - ₹415.79</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>341.34</v>
+        <v>418.93</v>
       </c>
       <c r="I3" t="n">
-        <v>322.48</v>
+        <v>409.2</v>
       </c>
       <c r="J3" t="n">
-        <v>312.65</v>
+        <v>400.39</v>
       </c>
       <c r="K3" t="n">
-        <v>274.58</v>
+        <v>399.71</v>
       </c>
       <c r="L3" t="n">
-        <v>19.03</v>
+        <v>3.2</v>
       </c>
       <c r="M3" t="n">
-        <v>2.23</v>
+        <v>3.88</v>
       </c>
       <c r="N3" t="n">
-        <v>3.41</v>
+        <v>5.59</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.18</v>
+        <v>-1.7</v>
       </c>
       <c r="P3" t="n">
-        <v>6.8</v>
+        <v>6.29</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="R3" t="n">
         <v>49.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.98</v>
+        <v>-0.75</v>
       </c>
       <c r="U3" t="n">
-        <v>55</v>
+        <v>51.7</v>
       </c>
       <c r="V3" t="n">
-        <v>2.56</v>
+        <v>3.6</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>335.9</v>
+        <v>403.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>362.09</v>
+        <v>411.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>362.09</v>
+        <v>411.47</v>
       </c>
       <c r="AA3" t="n">
-        <v>325.7</v>
+        <v>404.47</v>
       </c>
       <c r="AB3" t="n">
-        <v>333.08</v>
+        <v>415.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>339.31</v>
+        <v>416.54</v>
       </c>
       <c r="AD3" t="n">
-        <v>342.73</v>
+        <v>419.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>48</v>
+        <v>42.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.25</v>
+        <v>-0.01</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.25) | LSTM Deep Net</t>
+          <t>Low VIX (11.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>730.2</v>
+        <v>20.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.6</v>
+        <v>28.5</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>348.58</v>
+        <v>422.86</v>
       </c>
       <c r="AN3" t="n">
-        <v>324.08</v>
+        <v>405.02</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹309,209.15 Cr., a P/E ratio of 730.22, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹411,742.82 Cr., a P/E ratio of 20.27, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.04 (Consolidation Zone), while MACD Line (2.23) trades below Signal (3.41) with an expanding histogram (-1.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.03% above the 200-day DMA (₹274.58). Daily volatility envelope is bounded by ATR(14) of ₹6.80.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.84 (Consolidation Zone), while MACD Line (3.88) trades below Signal (5.59) with an expanding histogram (-1.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.20% above the 200-day DMA (₹399.71). Daily volatility envelope is bounded by ATR(14) of ₹6.29.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹335.90) is positioned above the 30-day DMA (₹322.48), 50-day DMA (₹312.65), and 200-day DMA (₹274.58). The price distance from 200 DMA is +19.03%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹413.90) is positioned above the 30-day DMA (₹409.20), 50-day DMA (₹400.39), and 200-day DMA (₹399.71). The price distance from 200 DMA is +3.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[335.9, 338.78, 341.66, 344.53, 347.41, 350.29]</t>
+          <t>[413.9, 415.14, 416.38, 417.63, 418.87, 420.11]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[335.9, 341.5, 345.5, 349.24, 352.85, 356.37]</t>
+          <t>[413.9, 417.66, 419.94, 421.98, 423.9, 425.73]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[335.9, 336.74, 338.77, 341.0, 343.33, 345.73]</t>
+          <t>[413.9, 413.26, 413.72, 414.36, 415.1, 415.89]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>362.09</v>
+        <v>411.47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>126974.77</v>
+        <v>83205.74000000001</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,157 +1012,157 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11409</v>
+        <v>3269.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹11368.68 - ₹11469.49</t>
+          <t>₹3248.24 - ₹3300.64</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11570.29</v>
+        <v>3353.05</v>
       </c>
       <c r="I4" t="n">
-        <v>11202.02</v>
+        <v>3179.33</v>
       </c>
       <c r="J4" t="n">
-        <v>11040.03</v>
+        <v>3000.69</v>
       </c>
       <c r="K4" t="n">
-        <v>10524.86</v>
+        <v>2701.74</v>
       </c>
       <c r="L4" t="n">
-        <v>6.58</v>
+        <v>20.66</v>
       </c>
       <c r="M4" t="n">
-        <v>-27.8</v>
+        <v>65.67</v>
       </c>
       <c r="N4" t="n">
-        <v>-14.3</v>
+        <v>90.11</v>
       </c>
       <c r="O4" t="n">
-        <v>-13.5</v>
+        <v>-24.44</v>
       </c>
       <c r="P4" t="n">
-        <v>201.62</v>
+        <v>104.81</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="R4" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.87</v>
+        <v>-1.91</v>
       </c>
       <c r="U4" t="n">
         <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>3.8</v>
+        <v>2.94</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>11366.84</v>
+        <v>3172.76</v>
       </c>
       <c r="Y4" t="n">
-        <v>12523.22</v>
+        <v>3106.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>12523.22</v>
+        <v>2590.47</v>
       </c>
       <c r="AA4" t="n">
-        <v>11106.57</v>
+        <v>3111.98</v>
       </c>
       <c r="AB4" t="n">
-        <v>11356.67</v>
+        <v>3252.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>11486.34</v>
+        <v>3291.86</v>
       </c>
       <c r="AD4" t="n">
-        <v>11563.67</v>
+        <v>3314.53</v>
       </c>
       <c r="AE4" t="n">
-        <v>39.5</v>
+        <v>39.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Low VIX (11.25) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>14.3</v>
+        <v>54.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24.2</v>
+        <v>85.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>734.6</v>
+        <v>55.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>11740.37</v>
+        <v>3399.23</v>
       </c>
       <c r="AN4" t="n">
-        <v>11069.05</v>
+        <v>3158.86</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹126,974.77 Cr., a P/E ratio of 14.34, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹83,205.74 Cr., a P/E ratio of 54.21, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.50 (Consolidation Zone), while MACD Line (-27.80) trades below Signal (-14.30) with an expanding histogram (-13.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.58% above the 200-day DMA (₹10524.86). Daily volatility envelope is bounded by ATR(14) of ₹201.62.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.75 (Consolidation Zone), while MACD Line (65.67) trades below Signal (90.11) with an expanding histogram (-24.44). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.66% above the 200-day DMA (₹2701.74). Daily volatility envelope is bounded by ATR(14) of ₹104.81.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,409.00) is positioned above the 30-day DMA (₹11,202.02), 50-day DMA (₹11,040.03), and 200-day DMA (₹10,524.86). The price distance from 200 DMA is +6.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,269.20) is positioned above the 30-day DMA (₹3,179.33), 50-day DMA (₹3,000.69), and 200-day DMA (₹2,701.74). The price distance from 200 DMA is +20.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[11409.0, 11443.23, 11477.45, 11511.68, 11545.91, 11580.13]</t>
+          <t>[3269.2, 3279.01, 3288.82, 3298.62, 3308.43, 3318.24]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[11409.0, 11523.87, 11591.51, 11651.37, 11707.2, 11760.47]</t>
+          <t>[3269.2, 3320.93, 3348.11, 3371.24, 3392.28, 3411.99]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[11409.0, 11382.74, 11391.92, 11406.92, 11424.94, 11444.89]</t>
+          <t>[3269.2, 3247.56, 3244.35, 3244.16, 3245.54, 3247.93]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>12523.22</v>
+        <v>2590.47</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31243.58</v>
+        <v>126017.64</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,157 +1179,157 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>568</v>
+        <v>11323</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹564.62 - ₹573.06</t>
+          <t>₹11282.68 - ₹11383.49</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>581.5</v>
+        <v>11484.29</v>
       </c>
       <c r="I5" t="n">
-        <v>525.74</v>
+        <v>11202.02</v>
       </c>
       <c r="J5" t="n">
-        <v>525.78</v>
+        <v>11040.03</v>
       </c>
       <c r="K5" t="n">
-        <v>523.73</v>
+        <v>10524.86</v>
       </c>
       <c r="L5" t="n">
-        <v>4.66</v>
+        <v>6.58</v>
       </c>
       <c r="M5" t="n">
-        <v>8.93</v>
+        <v>-27.8</v>
       </c>
       <c r="N5" t="n">
-        <v>9.85</v>
+        <v>-14.3</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.92</v>
+        <v>-13.5</v>
       </c>
       <c r="P5" t="n">
-        <v>16.88</v>
+        <v>201.62</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="R5" t="n">
-        <v>47.8</v>
+        <v>48.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.79</v>
+        <v>-0.89</v>
       </c>
       <c r="U5" t="n">
-        <v>48.3</v>
+        <v>53.3</v>
       </c>
       <c r="V5" t="n">
-        <v>4.76</v>
+        <v>3.78</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>568</v>
+        <v>10942.99</v>
       </c>
       <c r="Y5" t="n">
-        <v>603.71</v>
+        <v>10695.27</v>
       </c>
       <c r="Z5" t="n">
-        <v>603.2</v>
+        <v>10223.14</v>
       </c>
       <c r="AA5" t="n">
-        <v>542.6900000000001</v>
+        <v>11020.57</v>
       </c>
       <c r="AB5" t="n">
-        <v>561.9299999999999</v>
+        <v>11324</v>
       </c>
       <c r="AC5" t="n">
-        <v>580.21</v>
+        <v>11388</v>
       </c>
       <c r="AD5" t="n">
-        <v>592.4299999999999</v>
+        <v>11453</v>
       </c>
       <c r="AE5" t="n">
-        <v>54.9</v>
+        <v>39.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.25) | LSTM Deep Net</t>
+          <t>Low VIX (11.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.4</v>
+        <v>14.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14.5</v>
+        <v>24.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>65.2</v>
+        <v>734.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="AM5" t="n">
-        <v>582.64</v>
+        <v>11644.17</v>
       </c>
       <c r="AN5" t="n">
-        <v>552.88</v>
+        <v>10984.94</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,243.58 Cr., a P/E ratio of 5.45, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹126,017.64 Cr., a P/E ratio of 14.24, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.87 (Consolidation Zone), while MACD Line (8.93) trades below Signal (9.85) with an expanding histogram (-0.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.66% above the 200-day DMA (₹523.73). Daily volatility envelope is bounded by ATR(14) of ₹16.88.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.50 (Consolidation Zone), while MACD Line (-27.80) trades below Signal (-14.30) with an expanding histogram (-13.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.58% above the 200-day DMA (₹10524.86). Daily volatility envelope is bounded by ATR(14) of ₹201.62.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹568.00) is positioned above the 30-day DMA (₹525.74), 50-day DMA (₹525.78), and 200-day DMA (₹523.73). The price distance from 200 DMA is +4.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,323.00) is positioned above the 30-day DMA (₹11,202.02), 50-day DMA (₹11,040.03), and 200-day DMA (₹10,524.86). The price distance from 200 DMA is +6.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[568.0, 570.76, 573.52, 576.27, 579.03, 581.79]</t>
+          <t>[11323.0, 11356.97, 11390.94, 11424.91, 11458.88, 11492.84]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[568.0, 577.51, 583.06, 587.96, 592.53, 596.88]</t>
+          <t>[11323.0, 11437.62, 11504.99, 11564.59, 11620.17, 11673.18]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[568.0, 565.7, 566.36, 567.51, 568.91, 570.47]</t>
+          <t>[11323.0, 11296.48, 11305.4, 11320.14, 11337.91, 11357.6]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>603.2</v>
+        <v>10223.14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>135616.72</v>
+        <v>61563.97</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,500 +1346,500 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>118</v>
+        <v>1021</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹117.57 - ₹118.64</t>
+          <t>₹1015.4 - ₹1029.41</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>119.71</v>
+        <v>1043.42</v>
       </c>
       <c r="I6" t="n">
-        <v>116.33</v>
+        <v>989.35</v>
       </c>
       <c r="J6" t="n">
-        <v>114.03</v>
+        <v>956.71</v>
       </c>
       <c r="K6" t="n">
-        <v>112.31</v>
+        <v>851.66</v>
       </c>
       <c r="L6" t="n">
-        <v>4.42</v>
+        <v>18.59</v>
       </c>
       <c r="M6" t="n">
-        <v>0.64</v>
+        <v>12.75</v>
       </c>
       <c r="N6" t="n">
-        <v>0.75</v>
+        <v>20.95</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.12</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>28.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="R6" t="n">
-        <v>45.8</v>
+        <v>47.9</v>
       </c>
       <c r="S6" t="n">
-        <v>0.29</v>
+        <v>0.19</v>
       </c>
       <c r="T6" t="n">
-        <v>-1</v>
+        <v>-1.61</v>
       </c>
       <c r="U6" t="n">
         <v>53.3</v>
       </c>
       <c r="V6" t="n">
-        <v>2.6</v>
+        <v>3.54</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>118</v>
+        <v>993.87</v>
       </c>
       <c r="Y6" t="n">
-        <v>126.69</v>
+        <v>972.92</v>
       </c>
       <c r="Z6" t="n">
-        <v>126.69</v>
+        <v>927.3200000000001</v>
       </c>
       <c r="AA6" t="n">
-        <v>114.79</v>
+        <v>978.97</v>
       </c>
       <c r="AB6" t="n">
-        <v>117.74</v>
+        <v>1013.87</v>
       </c>
       <c r="AC6" t="n">
-        <v>118.84</v>
+        <v>1032.14</v>
       </c>
       <c r="AD6" t="n">
-        <v>119.68</v>
+        <v>1043.27</v>
       </c>
       <c r="AE6" t="n">
-        <v>61.7</v>
+        <v>42.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.11</v>
+        <v>0.23</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.1</v>
+        <v>31.7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-6.4</v>
+        <v>23.9</v>
       </c>
       <c r="AK6" t="n">
-        <v>38.1</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>121.04</v>
+        <v>1060.48</v>
       </c>
       <c r="AN6" t="n">
-        <v>114.72</v>
+        <v>982.33</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹135,616.72 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹61,563.97 Cr., a P/E ratio of 31.69, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.75 (Bullish Momentum Zone), while MACD Line (0.64) trades below Signal (0.75) with an expanding histogram (-0.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.42% above the 200-day DMA (₹112.31). Daily volatility envelope is bounded by ATR(14) of ₹2.14.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.19 (Consolidation Zone), while MACD Line (12.75) trades below Signal (20.95) with an expanding histogram (-8.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.59% above the 200-day DMA (₹851.66). Daily volatility envelope is bounded by ATR(14) of ₹28.02.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹118.00) is positioned above the 30-day DMA (₹116.33), 50-day DMA (₹114.03), and 200-day DMA (₹112.31). The price distance from 200 DMA is +4.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,021.00) is positioned above the 30-day DMA (₹989.35), 50-day DMA (₹956.71), and 200-day DMA (₹851.66). The price distance from 200 DMA is +18.59%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[118.0, 118.94, 119.89, 120.83, 121.78, 122.72]</t>
+          <t>[1021.0, 1024.06, 1027.13, 1030.19, 1033.25, 1036.31]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[118.0, 119.8, 121.1, 122.32, 123.49, 124.64]</t>
+          <t>[1021.0, 1035.27, 1042.98, 1049.6, 1055.67, 1061.38]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[118.0, 118.3, 118.98, 119.72, 120.49, 121.28]</t>
+          <t>[1021.0, 1015.66, 1015.24, 1015.63, 1016.44, 1017.52]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>126.69</v>
+        <v>927.3200000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>60560.07</v>
+        <v>31551.61</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2181.1</v>
+        <v>573.6</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹2168.34 - ₹2200.25</t>
+          <t>₹570.22 - ₹578.66</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2232.16</v>
+        <v>587.1</v>
       </c>
       <c r="I7" t="n">
-        <v>2143.45</v>
+        <v>525.74</v>
       </c>
       <c r="J7" t="n">
-        <v>2026.16</v>
+        <v>525.78</v>
       </c>
       <c r="K7" t="n">
-        <v>1961.52</v>
+        <v>523.73</v>
       </c>
       <c r="L7" t="n">
-        <v>15.73</v>
+        <v>4.66</v>
       </c>
       <c r="M7" t="n">
-        <v>37.59</v>
+        <v>8.93</v>
       </c>
       <c r="N7" t="n">
-        <v>47.03</v>
+        <v>9.85</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.44</v>
+        <v>-0.92</v>
       </c>
       <c r="P7" t="n">
-        <v>63.82</v>
+        <v>16.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="R7" t="n">
-        <v>43.7</v>
+        <v>47.5</v>
       </c>
       <c r="S7" t="n">
         <v>0.18</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.97</v>
+        <v>-1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>55</v>
+        <v>48.3</v>
       </c>
       <c r="V7" t="n">
-        <v>3.19</v>
+        <v>4.78</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>2142.17</v>
+        <v>562.52</v>
       </c>
       <c r="Y7" t="n">
-        <v>2489.97</v>
+        <v>550.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>2489.97</v>
+        <v>525.46</v>
       </c>
       <c r="AA7" t="n">
-        <v>2085.37</v>
+        <v>548.29</v>
       </c>
       <c r="AB7" t="n">
-        <v>2196.27</v>
+        <v>570.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>2213.84</v>
+        <v>577.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>2246.57</v>
+        <v>580.6</v>
       </c>
       <c r="AE7" t="n">
-        <v>55.5</v>
+        <v>54.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>49.3</v>
+        <v>5.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>8.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>5.2</v>
+        <v>65.2</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>2245.77</v>
+        <v>588.3200000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>2123.48</v>
+        <v>557.61</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,560.07 Cr., a P/E ratio of 49.27, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,551.61 Cr., a P/E ratio of 5.50, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.51 (Bullish Momentum Zone), while MACD Line (37.59) trades below Signal (47.03) with an expanding histogram (-9.44). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.73% above the 200-day DMA (₹1961.52). Daily volatility envelope is bounded by ATR(14) of ₹63.82.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.87 (Consolidation Zone), while MACD Line (8.93) trades below Signal (9.85) with an expanding histogram (-0.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.66% above the 200-day DMA (₹523.73). Daily volatility envelope is bounded by ATR(14) of ₹16.88.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,181.10) is positioned above the 30-day DMA (₹2,143.45), 50-day DMA (₹2,026.16), and 200-day DMA (₹1,961.52). The price distance from 200 DMA is +15.73%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹573.60) is positioned above the 30-day DMA (₹525.74), 50-day DMA (₹525.78), and 200-day DMA (₹523.73). The price distance from 200 DMA is +4.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[2181.1, 2187.64, 2194.19, 2200.73, 2207.27, 2213.82]</t>
+          <t>[573.6, 578.23, 582.86, 587.49, 592.11, 596.74]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[2181.1, 2213.17, 2230.29, 2244.94, 2258.33, 2270.9]</t>
+          <t>[573.6, 584.98, 592.4, 599.18, 605.61, 611.84]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[2181.1, 2168.5, 2167.11, 2167.57, 2168.98, 2171.01]</t>
+          <t>[573.6, 573.17, 575.7, 578.72, 581.99, 585.42]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>2489.97</v>
+        <v>525.46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>107772.12</v>
+        <v>135145.51</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>745</v>
+        <v>117.59</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹742.03 - ₹749.46</t>
+          <t>₹117.16 - ₹118.23</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>756.89</v>
+        <v>119.3</v>
       </c>
       <c r="I8" t="n">
-        <v>722.89</v>
+        <v>116.33</v>
       </c>
       <c r="J8" t="n">
-        <v>727.97</v>
+        <v>114.03</v>
       </c>
       <c r="K8" t="n">
-        <v>686.01</v>
+        <v>112.31</v>
       </c>
       <c r="L8" t="n">
-        <v>6.81</v>
+        <v>4.42</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.93</v>
+        <v>0.64</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.85</v>
+        <v>0.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0.93</v>
+        <v>-0.12</v>
       </c>
       <c r="P8" t="n">
-        <v>14.87</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="R8" t="n">
-        <v>42.7</v>
+        <v>46.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.26</v>
+        <v>-0.99</v>
       </c>
       <c r="U8" t="n">
-        <v>46.7</v>
+        <v>53.3</v>
       </c>
       <c r="V8" t="n">
-        <v>11.57</v>
+        <v>2.6</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>740.17</v>
+        <v>115.28</v>
       </c>
       <c r="Y8" t="n">
-        <v>798.89</v>
+        <v>112.78</v>
       </c>
       <c r="Z8" t="n">
-        <v>798.89</v>
+        <v>109.72</v>
       </c>
       <c r="AA8" t="n">
-        <v>722.7</v>
+        <v>114.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>747</v>
+        <v>117.86</v>
       </c>
       <c r="AC8" t="n">
-        <v>753</v>
+        <v>118.46</v>
       </c>
       <c r="AD8" t="n">
-        <v>761</v>
+        <v>119.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>47.2</v>
+        <v>61.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.18</v>
+        <v>-0.11</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Vol Spike 2.0x | Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.25) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>49.4</v>
+        <v>6.1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15.1</v>
+        <v>-6.4</v>
       </c>
       <c r="AK8" t="n">
-        <v>20.9</v>
+        <v>38.1</v>
       </c>
       <c r="AL8" t="n">
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>762.49</v>
+        <v>120.97</v>
       </c>
       <c r="AN8" t="n">
-        <v>725.42</v>
+        <v>114.6</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹107,772.12 Cr., a P/E ratio of 49.37, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹135,145.51 Cr., a P/E ratio of 6.12, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 47.15 (Consolidation Zone), while MACD Line (-0.93) trades above Signal (-1.85) with an expanding histogram (+0.93). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.81% above the 200-day DMA (₹686.01). Daily volatility envelope is bounded by ATR(14) of ₹14.87.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.75 (Bullish Momentum Zone), while MACD Line (0.64) trades below Signal (0.75) with an expanding histogram (-0.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.42% above the 200-day DMA (₹112.31). Daily volatility envelope is bounded by ATR(14) of ₹2.14.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹745.00) is positioned above the 30-day DMA (₹722.89), 50-day DMA (₹727.97), and 200-day DMA (₹686.01). The price distance from 200 DMA is +6.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.59) is positioned above the 30-day DMA (₹116.33), 50-day DMA (₹114.03), and 200-day DMA (₹112.31). The price distance from 200 DMA is +4.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[745.0, 747.23, 749.47, 751.7, 753.94, 756.17]</t>
+          <t>[117.59, 118.49, 119.4, 120.3, 121.2, 122.1]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[745.0, 753.18, 757.88, 762.01, 765.83, 769.47]</t>
+          <t>[117.59, 119.35, 120.61, 121.78, 122.91, 124.02]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[745.0, 742.77, 743.16, 743.98, 745.02, 746.2]</t>
+          <t>[117.59, 117.85, 118.49, 119.19, 119.92, 120.67]</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>798.89</v>
+        <v>109.72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>59996.24</v>
+        <v>60487.88</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1847,166 +1847,166 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>995</v>
+        <v>2178.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹989.4 - ₹1003.41</t>
+          <t>₹2165.74 - ₹2197.65</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1017.42</v>
+        <v>2229.56</v>
       </c>
       <c r="I9" t="n">
-        <v>989.35</v>
+        <v>2143.45</v>
       </c>
       <c r="J9" t="n">
-        <v>956.71</v>
+        <v>2026.16</v>
       </c>
       <c r="K9" t="n">
-        <v>851.66</v>
+        <v>1961.52</v>
       </c>
       <c r="L9" t="n">
-        <v>18.59</v>
+        <v>15.73</v>
       </c>
       <c r="M9" t="n">
-        <v>12.75</v>
+        <v>37.59</v>
       </c>
       <c r="N9" t="n">
-        <v>20.95</v>
+        <v>47.03</v>
       </c>
       <c r="O9" t="n">
-        <v>-8.199999999999999</v>
+        <v>-9.44</v>
       </c>
       <c r="P9" t="n">
-        <v>28.02</v>
+        <v>63.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="R9" t="n">
-        <v>42.2</v>
+        <v>43.7</v>
       </c>
       <c r="S9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.95</v>
+        <v>-1.97</v>
       </c>
       <c r="U9" t="n">
-        <v>51.7</v>
+        <v>55</v>
       </c>
       <c r="V9" t="n">
-        <v>3.54</v>
+        <v>3.19</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>995</v>
+        <v>2075.73</v>
       </c>
       <c r="Y9" t="n">
-        <v>1120.93</v>
+        <v>2002.03</v>
       </c>
       <c r="Z9" t="n">
-        <v>1120.93</v>
+        <v>2002.03</v>
       </c>
       <c r="AA9" t="n">
-        <v>952.97</v>
+        <v>2082.77</v>
       </c>
       <c r="AB9" t="n">
-        <v>999.33</v>
+        <v>2182.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>1005.46</v>
+        <v>2195.66</v>
       </c>
       <c r="AD9" t="n">
-        <v>1015.93</v>
+        <v>2212.83</v>
       </c>
       <c r="AE9" t="n">
-        <v>42.2</v>
+        <v>55.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>30.9</v>
+        <v>49.2</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23.9</v>
+        <v>8.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>5.2</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>1035.09</v>
+        <v>2244.52</v>
       </c>
       <c r="AN9" t="n">
-        <v>957.11</v>
+        <v>2119.97</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹59,996.24 Cr., a P/E ratio of 30.88, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,487.88 Cr., a P/E ratio of 49.21, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.19 (Consolidation Zone), while MACD Line (12.75) trades below Signal (20.95) with an expanding histogram (-8.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.59% above the 200-day DMA (₹851.66). Daily volatility envelope is bounded by ATR(14) of ₹28.02.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.51 (Bullish Momentum Zone), while MACD Line (37.59) trades below Signal (47.03) with an expanding histogram (-9.44). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.73% above the 200-day DMA (₹1961.52). Daily volatility envelope is bounded by ATR(14) of ₹63.82.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹995.00) is positioned above the 30-day DMA (₹989.35), 50-day DMA (₹956.71), and 200-day DMA (₹851.66). The price distance from 200 DMA is +18.59%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,178.50) is positioned above the 30-day DMA (₹2,143.45), 50-day DMA (₹2,026.16), and 200-day DMA (₹1,961.52). The price distance from 200 DMA is +15.73%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[995.0, 997.98, 1000.97, 1003.95, 1006.94, 1009.92]</t>
+          <t>[2178.5, 2185.04, 2191.57, 2198.11, 2204.64, 2211.18]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[995.0, 1009.19, 1016.82, 1023.37, 1029.36, 1034.99]</t>
+          <t>[2178.5, 2210.56, 2227.67, 2242.32, 2255.7, 2268.26]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[995.0, 989.58, 989.08, 989.39, 990.13, 991.13]</t>
+          <t>[2178.5, 2165.89, 2164.49, 2164.95, 2166.35, 2168.37]</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>1120.93</v>
+        <v>2002.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25000</v>
+        <v>107323.68</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2014,146 +2014,146 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3209</v>
+        <v>741.9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹3188.04 - ₹3240.44</t>
+          <t>₹738.93 - ₹746.36</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3292.85</v>
+        <v>753.79</v>
       </c>
       <c r="I10" t="n">
-        <v>3179.33</v>
+        <v>722.89</v>
       </c>
       <c r="J10" t="n">
-        <v>3000.69</v>
+        <v>727.97</v>
       </c>
       <c r="K10" t="n">
-        <v>2701.74</v>
+        <v>686.01</v>
       </c>
       <c r="L10" t="n">
-        <v>20.66</v>
+        <v>6.81</v>
       </c>
       <c r="M10" t="n">
-        <v>65.67</v>
+        <v>-0.93</v>
       </c>
       <c r="N10" t="n">
-        <v>90.11</v>
+        <v>-1.85</v>
       </c>
       <c r="O10" t="n">
-        <v>-24.44</v>
+        <v>0.93</v>
       </c>
       <c r="P10" t="n">
-        <v>104.81</v>
+        <v>14.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.25</v>
+        <v>11.19</v>
       </c>
       <c r="R10" t="n">
-        <v>40.8</v>
+        <v>42.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.4</v>
+        <v>-1.27</v>
       </c>
       <c r="U10" t="n">
-        <v>51.7</v>
+        <v>46.7</v>
       </c>
       <c r="V10" t="n">
-        <v>2.96</v>
+        <v>11.56</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>3202.25</v>
+        <v>715.04</v>
       </c>
       <c r="Y10" t="n">
-        <v>4147.04</v>
+        <v>687.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>4147.04</v>
+        <v>685.9299999999999</v>
       </c>
       <c r="AA10" t="n">
-        <v>3051.78</v>
+        <v>719.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>3210.83</v>
+        <v>743.85</v>
       </c>
       <c r="AC10" t="n">
-        <v>3266.16</v>
+        <v>747.45</v>
       </c>
       <c r="AD10" t="n">
-        <v>3323.33</v>
+        <v>753</v>
       </c>
       <c r="AE10" t="n">
-        <v>39.8</v>
+        <v>47.2</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.25) | LSTM Deep Net</t>
+          <t>Vol Spike 2.0x | Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.19) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>53.2</v>
+        <v>49.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>85.3</v>
+        <v>15.1</v>
       </c>
       <c r="AK10" t="n">
-        <v>55.6</v>
+        <v>20.9</v>
       </c>
       <c r="AL10" t="n">
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>3340.27</v>
+        <v>759.76</v>
       </c>
       <c r="AN10" t="n">
-        <v>3097.14</v>
+        <v>723.16</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.21, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹107,323.68 Cr., a P/E ratio of 49.17, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.75 (Consolidation Zone), while MACD Line (65.67) trades below Signal (90.11) with an expanding histogram (-24.44). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.66% above the 200-day DMA (₹2701.74). Daily volatility envelope is bounded by ATR(14) of ₹104.81.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 47.15 (Consolidation Zone), while MACD Line (-0.93) trades above Signal (-1.85) with an expanding histogram (+0.93). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.81% above the 200-day DMA (₹686.01). Daily volatility envelope is bounded by ATR(14) of ₹14.87.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,209.00) is positioned above the 30-day DMA (₹3,179.33), 50-day DMA (₹3,000.69), and 200-day DMA (₹2,701.74). The price distance from 200 DMA is +20.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹741.90) is positioned above the 30-day DMA (₹722.89), 50-day DMA (₹727.97), and 200-day DMA (₹686.01). The price distance from 200 DMA is +6.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[3209.0, 3218.63, 3228.25, 3237.88, 3247.51, 3257.13]</t>
+          <t>[741.9, 744.13, 746.35, 748.58, 750.8, 753.03]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[3209.0, 3260.55, 3287.55, 3310.5, 3331.36, 3350.88]</t>
+          <t>[741.9, 750.07, 754.76, 758.88, 762.7, 766.33]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[3209.0, 3187.18, 3183.79, 3183.42, 3184.62, 3186.82]</t>
+          <t>[741.9, 739.67, 740.04, 740.85, 741.88, 743.05]</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>4147.04</v>
+        <v>685.9299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>310405.89</v>
+        <v>314824.46</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,98 +678,98 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>337.2</v>
+        <v>342</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹335.84 - ₹339.24</t>
+          <t>₹340.59 - ₹344.11</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>342.64</v>
+        <v>347.63</v>
       </c>
       <c r="I2" t="n">
-        <v>322.48</v>
+        <v>323.34</v>
       </c>
       <c r="J2" t="n">
-        <v>312.65</v>
+        <v>313.66</v>
       </c>
       <c r="K2" t="n">
-        <v>274.58</v>
+        <v>274.78</v>
       </c>
       <c r="L2" t="n">
-        <v>19.03</v>
+        <v>22.24</v>
       </c>
       <c r="M2" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="N2" t="n">
-        <v>3.41</v>
+        <v>3.36</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.18</v>
+        <v>-0.21</v>
       </c>
       <c r="P2" t="n">
-        <v>6.8</v>
+        <v>7.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.19</v>
+        <v>11</v>
       </c>
       <c r="R2" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="S2" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.93</v>
+        <v>-0.99</v>
       </c>
       <c r="U2" t="n">
         <v>55</v>
       </c>
       <c r="V2" t="n">
-        <v>2.57</v>
+        <v>2.76</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>331.09</v>
+        <v>333.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>324.03</v>
+        <v>326.69</v>
       </c>
       <c r="Z2" t="n">
-        <v>307.21</v>
+        <v>311.19</v>
       </c>
       <c r="AA2" t="n">
-        <v>327</v>
+        <v>331.45</v>
       </c>
       <c r="AB2" t="n">
-        <v>337.15</v>
+        <v>339.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>339.65</v>
+        <v>344.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>342.1</v>
+        <v>346.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (11.0) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>733</v>
+        <v>727.7</v>
       </c>
       <c r="AJ2" t="n">
         <v>182</v>
@@ -781,43 +781,43 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>348.32</v>
+        <v>354.94</v>
       </c>
       <c r="AN2" t="n">
-        <v>326.28</v>
+        <v>330.98</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹310,405.89 Cr., a P/E ratio of 733.04, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹314,824.46 Cr., a P/E ratio of 727.66, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.04 (Consolidation Zone), while MACD Line (2.23) trades below Signal (3.41) with an expanding histogram (-1.18). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.03% above the 200-day DMA (₹274.58). Daily volatility envelope is bounded by ATR(14) of ₹6.80.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.05 (Bullish Momentum Zone), while MACD Line (3.15) trades below Signal (3.36) with an expanding histogram (-0.21). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +22.24% above the 200-day DMA (₹274.78). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹337.20) is positioned above the 30-day DMA (₹322.48), 50-day DMA (₹312.65), and 200-day DMA (₹274.58). The price distance from 200 DMA is +19.03%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹342.00) is positioned above the 30-day DMA (₹323.34), 50-day DMA (₹313.66), and 200-day DMA (₹274.78). The price distance from 200 DMA is +22.24%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[337.2, 340.33, 343.46, 346.59, 349.73, 352.86]</t>
+          <t>[342.0, 343.09, 344.18, 345.27, 346.35, 347.44]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[337.2, 343.05, 347.31, 351.31, 355.17, 358.94]</t>
+          <t>[342.0, 345.9, 348.16, 350.14, 351.98, 353.73]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[337.2, 338.29, 340.58, 343.06, 345.65, 348.3]</t>
+          <t>[342.0, 340.98, 341.19, 341.61, 342.14, 342.73]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>307.21</v>
+        <v>311.19</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>411742.82</v>
+        <v>60946.02</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>413.9</v>
+        <v>2195</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹412.64 - ₹415.79</t>
+          <t>₹2181.57 - ₹2215.15</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>418.93</v>
+        <v>2248.73</v>
       </c>
       <c r="I3" t="n">
-        <v>409.2</v>
+        <v>2149.07</v>
       </c>
       <c r="J3" t="n">
-        <v>400.39</v>
+        <v>2033.35</v>
       </c>
       <c r="K3" t="n">
-        <v>399.71</v>
+        <v>1963.6</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2</v>
+        <v>11.08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.88</v>
+        <v>35.41</v>
       </c>
       <c r="N3" t="n">
-        <v>5.59</v>
+        <v>44.71</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.7</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>6.29</v>
+        <v>67.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.19</v>
+        <v>11</v>
       </c>
       <c r="R3" t="n">
-        <v>49.8</v>
+        <v>50.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0.35</v>
+        <v>0.17</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.75</v>
+        <v>-1.72</v>
       </c>
       <c r="U3" t="n">
-        <v>51.7</v>
+        <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>3.6</v>
+        <v>3.09</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>403.8</v>
+        <v>2099.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>411.47</v>
+        <v>2056.08</v>
       </c>
       <c r="Z3" t="n">
-        <v>411.47</v>
+        <v>2017.19</v>
       </c>
       <c r="AA3" t="n">
-        <v>404.47</v>
+        <v>2094.26</v>
       </c>
       <c r="AB3" t="n">
-        <v>415.17</v>
+        <v>2184.73</v>
       </c>
       <c r="AC3" t="n">
-        <v>416.54</v>
+        <v>2209.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>419.17</v>
+        <v>2224.13</v>
       </c>
       <c r="AE3" t="n">
-        <v>42.8</v>
+        <v>46.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.01</v>
+        <v>0.11</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Low VIX (11.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.0) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>20.3</v>
+        <v>49.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>21</v>
+        <v>8.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>28.5</v>
+        <v>5.2</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>422.86</v>
+        <v>2258.42</v>
       </c>
       <c r="AN3" t="n">
-        <v>405.02</v>
+        <v>2133.44</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹411,742.82 Cr., a P/E ratio of 20.27, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,946.02 Cr., a P/E ratio of 49.58, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.84 (Consolidation Zone), while MACD Line (3.88) trades below Signal (5.59) with an expanding histogram (-1.70). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.20% above the 200-day DMA (₹399.71). Daily volatility envelope is bounded by ATR(14) of ₹6.29.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.18 (Consolidation Zone), while MACD Line (35.41) trades below Signal (44.71) with an expanding histogram (-9.29). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.08% above the 200-day DMA (₹1963.60). Daily volatility envelope is bounded by ATR(14) of ₹67.16.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹413.90) is positioned above the 30-day DMA (₹409.20), 50-day DMA (₹400.39), and 200-day DMA (₹399.71). The price distance from 200 DMA is +3.20%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,195.00) is positioned above the 30-day DMA (₹2,149.07), 50-day DMA (₹2,033.35), and 200-day DMA (₹1,963.60). The price distance from 200 DMA is +11.08%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[413.9, 415.14, 416.38, 417.63, 418.87, 420.11]</t>
+          <t>[2195.0, 2201.58, 2208.17, 2214.75, 2221.34, 2227.92]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[413.9, 417.66, 419.94, 421.98, 423.9, 425.73]</t>
+          <t>[2195.0, 2228.45, 2246.16, 2261.28, 2275.07, 2287.99]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[413.9, 413.26, 413.72, 414.36, 415.1, 415.89]</t>
+          <t>[2195.0, 2181.44, 2179.68, 2179.86, 2181.04, 2182.87]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>411.47</v>
+        <v>2017.19</v>
       </c>
     </row>
     <row r="4">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>83205.74000000001</v>
+        <v>83037.77</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,98 +1012,98 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3269.2</v>
+        <v>3262.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹3248.24 - ₹3300.64</t>
+          <t>₹3242.1 - ₹3293.35</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3353.05</v>
+        <v>3344.61</v>
       </c>
       <c r="I4" t="n">
-        <v>3179.33</v>
+        <v>3194.54</v>
       </c>
       <c r="J4" t="n">
-        <v>3000.69</v>
+        <v>3009.36</v>
       </c>
       <c r="K4" t="n">
-        <v>2701.74</v>
+        <v>2707.69</v>
       </c>
       <c r="L4" t="n">
-        <v>20.66</v>
+        <v>18.51</v>
       </c>
       <c r="M4" t="n">
-        <v>65.67</v>
+        <v>57.19</v>
       </c>
       <c r="N4" t="n">
-        <v>90.11</v>
+        <v>83.53</v>
       </c>
       <c r="O4" t="n">
-        <v>-24.44</v>
+        <v>-26.34</v>
       </c>
       <c r="P4" t="n">
-        <v>104.81</v>
+        <v>102.51</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.19</v>
+        <v>11</v>
       </c>
       <c r="R4" t="n">
-        <v>48.7</v>
+        <v>50.2</v>
       </c>
       <c r="S4" t="n">
         <v>0.17</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.91</v>
+        <v>-1.78</v>
       </c>
       <c r="U4" t="n">
         <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>3172.76</v>
+        <v>3194.38</v>
       </c>
       <c r="Y4" t="n">
-        <v>3106.22</v>
+        <v>3126.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>2590.47</v>
+        <v>2585.25</v>
       </c>
       <c r="AA4" t="n">
-        <v>3111.98</v>
+        <v>3108.84</v>
       </c>
       <c r="AB4" t="n">
-        <v>3252.33</v>
+        <v>3255.07</v>
       </c>
       <c r="AC4" t="n">
-        <v>3291.86</v>
+        <v>3297.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>3314.53</v>
+        <v>3332.07</v>
       </c>
       <c r="AE4" t="n">
-        <v>39.8</v>
+        <v>42.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.19) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.0) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
       <c r="AJ4" t="n">
         <v>85.3</v>
@@ -1115,43 +1115,43 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>3399.23</v>
+        <v>3398.94</v>
       </c>
       <c r="AN4" t="n">
-        <v>3158.86</v>
+        <v>3142.99</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹83,205.74 Cr., a P/E ratio of 54.21, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹83,037.77 Cr., a P/E ratio of 54.08, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.75 (Consolidation Zone), while MACD Line (65.67) trades below Signal (90.11) with an expanding histogram (-24.44). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.66% above the 200-day DMA (₹2701.74). Daily volatility envelope is bounded by ATR(14) of ₹104.81.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.62 (Consolidation Zone), while MACD Line (57.19) trades below Signal (83.53) with an expanding histogram (-26.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.51% above the 200-day DMA (₹2707.69). Daily volatility envelope is bounded by ATR(14) of ₹102.51.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,269.20) is positioned above the 30-day DMA (₹3,179.33), 50-day DMA (₹3,000.69), and 200-day DMA (₹2,701.74). The price distance from 200 DMA is +20.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,262.60) is positioned above the 30-day DMA (₹3,194.54), 50-day DMA (₹3,009.36), and 200-day DMA (₹2,707.69). The price distance from 200 DMA is +18.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[3269.2, 3279.01, 3288.82, 3298.62, 3308.43, 3318.24]</t>
+          <t>[3262.6, 3283.62, 3304.63, 3325.65, 3346.67, 3367.68]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[3269.2, 3320.93, 3348.11, 3371.24, 3392.28, 3411.99]</t>
+          <t>[3262.6, 3324.62, 3362.62, 3396.67, 3428.67, 3459.37]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[3269.2, 3247.56, 3244.35, 3244.16, 3245.54, 3247.93]</t>
+          <t>[3262.6, 3252.86, 3261.14, 3272.39, 3285.16, 3298.92]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2590.47</v>
+        <v>2585.25</v>
       </c>
     </row>
     <row r="5">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>126017.64</v>
+        <v>60719.81</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,146 +1179,146 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>11323</v>
+        <v>1007</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹11282.68 - ₹11383.49</t>
+          <t>₹1001.73 - ₹1014.91</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>11484.29</v>
+        <v>1028.1</v>
       </c>
       <c r="I5" t="n">
-        <v>11202.02</v>
+        <v>993.11</v>
       </c>
       <c r="J5" t="n">
-        <v>11040.03</v>
+        <v>956.95</v>
       </c>
       <c r="K5" t="n">
-        <v>10524.86</v>
+        <v>852.09</v>
       </c>
       <c r="L5" t="n">
-        <v>6.58</v>
+        <v>16.77</v>
       </c>
       <c r="M5" t="n">
-        <v>-27.8</v>
+        <v>10.77</v>
       </c>
       <c r="N5" t="n">
-        <v>-14.3</v>
+        <v>18.92</v>
       </c>
       <c r="O5" t="n">
-        <v>-13.5</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>201.62</v>
+        <v>26.37</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.19</v>
+        <v>11</v>
       </c>
       <c r="R5" t="n">
-        <v>48.2</v>
+        <v>46.8</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.89</v>
+        <v>-1.57</v>
       </c>
       <c r="U5" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="V5" t="n">
-        <v>3.78</v>
+        <v>3.59</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>10942.99</v>
+        <v>981.71</v>
       </c>
       <c r="Y5" t="n">
-        <v>10695.27</v>
+        <v>960.98</v>
       </c>
       <c r="Z5" t="n">
-        <v>10223.14</v>
+        <v>914.61</v>
       </c>
       <c r="AA5" t="n">
-        <v>11020.57</v>
+        <v>967.4400000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>11324</v>
+        <v>1009.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>11388</v>
+        <v>1022.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>11453</v>
+        <v>1038.6</v>
       </c>
       <c r="AE5" t="n">
-        <v>39.5</v>
+        <v>44.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.04</v>
+        <v>0.29</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Low VIX (11.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.0) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>14.2</v>
+        <v>31.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="AK5" t="n">
-        <v>734.6</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>11644.17</v>
+        <v>1048.78</v>
       </c>
       <c r="AN5" t="n">
-        <v>10984.94</v>
+        <v>968.3200000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹126,017.64 Cr., a P/E ratio of 14.24, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹60,719.81 Cr., a P/E ratio of 31.25, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 39.50 (Consolidation Zone), while MACD Line (-27.80) trades below Signal (-14.30) with an expanding histogram (-13.50). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.58% above the 200-day DMA (₹10524.86). Daily volatility envelope is bounded by ATR(14) of ₹201.62.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.71 (Consolidation Zone), while MACD Line (10.77) trades below Signal (18.92) with an expanding histogram (-8.14). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.77% above the 200-day DMA (₹852.09). Daily volatility envelope is bounded by ATR(14) of ₹26.37.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,323.00) is positioned above the 30-day DMA (₹11,202.02), 50-day DMA (₹11,040.03), and 200-day DMA (₹10,524.86). The price distance from 200 DMA is +6.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,007.00) is positioned above the 30-day DMA (₹993.11), 50-day DMA (₹956.95), and 200-day DMA (₹852.09). The price distance from 200 DMA is +16.77%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[11323.0, 11356.97, 11390.94, 11424.91, 11458.88, 11492.84]</t>
+          <t>[1007.0, 1010.02, 1013.04, 1016.06, 1019.08, 1022.1]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[11323.0, 11437.62, 11504.99, 11564.59, 11620.17, 11673.18]</t>
+          <t>[1007.0, 1020.57, 1027.96, 1034.33, 1040.18, 1045.69]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[11323.0, 11296.48, 11305.4, 11320.14, 11337.91, 11357.6]</t>
+          <t>[1007.0, 1002.11, 1001.85, 1002.36, 1003.26, 1004.41]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>10223.14</v>
+        <v>914.61</v>
       </c>
     </row>
     <row r="6">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>61563.97</v>
+        <v>83409.02</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,146 +1346,146 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1021</v>
+        <v>1805</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹1015.4 - ₹1029.41</t>
+          <t>₹1792.99 - ₹1823.01</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1043.42</v>
+        <v>1853.02</v>
       </c>
       <c r="I6" t="n">
-        <v>989.35</v>
+        <v>1793.35</v>
       </c>
       <c r="J6" t="n">
-        <v>956.71</v>
+        <v>1710.31</v>
       </c>
       <c r="K6" t="n">
-        <v>851.66</v>
+        <v>1650.46</v>
       </c>
       <c r="L6" t="n">
-        <v>18.59</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>12.75</v>
+        <v>12.32</v>
       </c>
       <c r="N6" t="n">
-        <v>20.95</v>
+        <v>24.85</v>
       </c>
       <c r="O6" t="n">
-        <v>-8.199999999999999</v>
+        <v>-12.53</v>
       </c>
       <c r="P6" t="n">
-        <v>28.02</v>
+        <v>60.03</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.19</v>
+        <v>11</v>
       </c>
       <c r="R6" t="n">
-        <v>47.9</v>
+        <v>46.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0.19</v>
+        <v>0.16</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.61</v>
+        <v>-2.13</v>
       </c>
       <c r="U6" t="n">
         <v>53.3</v>
       </c>
       <c r="V6" t="n">
-        <v>3.54</v>
+        <v>3.86</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>993.87</v>
+        <v>1711.38</v>
       </c>
       <c r="Y6" t="n">
-        <v>972.92</v>
+        <v>1646.63</v>
       </c>
       <c r="Z6" t="n">
-        <v>927.3200000000001</v>
+        <v>1646.63</v>
       </c>
       <c r="AA6" t="n">
-        <v>978.97</v>
+        <v>1714.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>1013.87</v>
+        <v>1795.03</v>
       </c>
       <c r="AC6" t="n">
-        <v>1032.14</v>
+        <v>1816.36</v>
       </c>
       <c r="AD6" t="n">
-        <v>1043.27</v>
+        <v>1827.73</v>
       </c>
       <c r="AE6" t="n">
-        <v>42.2</v>
+        <v>46.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.23</v>
+        <v>0.05</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.19) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.0) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>31.7</v>
+        <v>111.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23.9</v>
+        <v>40.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>10.2</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>1060.48</v>
+        <v>1863.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>982.33</v>
+        <v>1742.91</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹61,563.97 Cr., a P/E ratio of 31.69, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹83,409.02 Cr., a P/E ratio of 111.35, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.19 (Consolidation Zone), while MACD Line (12.75) trades below Signal (20.95) with an expanding histogram (-8.20). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.59% above the 200-day DMA (₹851.66). Daily volatility envelope is bounded by ATR(14) of ₹28.02.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (12.32) trades below Signal (24.85) with an expanding histogram (-12.53). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.64% above the 200-day DMA (₹1650.46). Daily volatility envelope is bounded by ATR(14) of ₹60.03.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,021.00) is positioned above the 30-day DMA (₹989.35), 50-day DMA (₹956.71), and 200-day DMA (₹851.66). The price distance from 200 DMA is +18.59%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,805.00) is positioned above the 30-day DMA (₹1,793.35), 50-day DMA (₹1,710.31), and 200-day DMA (₹1,650.46). The price distance from 200 DMA is +8.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[1021.0, 1024.06, 1027.13, 1030.19, 1033.25, 1036.31]</t>
+          <t>[1805.0, 1810.41, 1815.83, 1821.24, 1826.66, 1832.07]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[1021.0, 1035.27, 1042.98, 1049.6, 1055.67, 1061.38]</t>
+          <t>[1805.0, 1834.43, 1849.79, 1862.83, 1874.68, 1885.77]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[1021.0, 1015.66, 1015.24, 1015.63, 1016.44, 1017.52]</t>
+          <t>[1805.0, 1792.41, 1790.36, 1790.05, 1790.64, 1791.81]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>927.3200000000001</v>
+        <v>1646.63</v>
       </c>
     </row>
     <row r="7">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1505,154 +1505,154 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31551.61</v>
+        <v>410499.31</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>573.6</v>
+        <v>412.65</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹570.22 - ₹578.66</t>
+          <t>₹411.42 - ₹414.5</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>587.1</v>
+        <v>417.59</v>
       </c>
       <c r="I7" t="n">
-        <v>525.74</v>
+        <v>409.91</v>
       </c>
       <c r="J7" t="n">
-        <v>525.78</v>
+        <v>401.01</v>
       </c>
       <c r="K7" t="n">
-        <v>523.73</v>
+        <v>399.65</v>
       </c>
       <c r="L7" t="n">
-        <v>4.66</v>
+        <v>3.79</v>
       </c>
       <c r="M7" t="n">
-        <v>8.93</v>
+        <v>3.54</v>
       </c>
       <c r="N7" t="n">
-        <v>9.85</v>
+        <v>5.18</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.92</v>
+        <v>-1.64</v>
       </c>
       <c r="P7" t="n">
-        <v>16.88</v>
+        <v>6.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>11.19</v>
+        <v>11</v>
       </c>
       <c r="R7" t="n">
-        <v>47.5</v>
+        <v>45.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0.18</v>
+        <v>0.36</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.78</v>
+        <v>-0.86</v>
       </c>
       <c r="U7" t="n">
-        <v>48.3</v>
+        <v>51.7</v>
       </c>
       <c r="V7" t="n">
-        <v>4.78</v>
+        <v>3.58</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>562.52</v>
+        <v>400.19</v>
       </c>
       <c r="Y7" t="n">
-        <v>550.53</v>
+        <v>410.23</v>
       </c>
       <c r="Z7" t="n">
-        <v>525.46</v>
+        <v>410.23</v>
       </c>
       <c r="AA7" t="n">
-        <v>548.29</v>
+        <v>403.39</v>
       </c>
       <c r="AB7" t="n">
-        <v>570.15</v>
+        <v>414.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>577.1</v>
+        <v>416.11</v>
       </c>
       <c r="AD7" t="n">
-        <v>580.6</v>
+        <v>419.58</v>
       </c>
       <c r="AE7" t="n">
-        <v>54.9</v>
+        <v>38.6</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2</v>
+        <v>-0.03</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.19) | LSTM Deep Net</t>
+          <t>Low VIX (11.0) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.5</v>
+        <v>20.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AK7" t="n">
-        <v>65.2</v>
+        <v>28.5</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>588.3200000000001</v>
+        <v>421.31</v>
       </c>
       <c r="AN7" t="n">
-        <v>557.61</v>
+        <v>403.7</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,551.61 Cr., a P/E ratio of 5.50, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹410,499.31 Cr., a P/E ratio of 20.22, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.87 (Consolidation Zone), while MACD Line (8.93) trades below Signal (9.85) with an expanding histogram (-0.92). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.66% above the 200-day DMA (₹523.73). Daily volatility envelope is bounded by ATR(14) of ₹16.88.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 38.64 (Consolidation Zone), while MACD Line (3.54) trades below Signal (5.18) with an expanding histogram (-1.64). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.79% above the 200-day DMA (₹399.65). Daily volatility envelope is bounded by ATR(14) of ₹6.17.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹573.60) is positioned above the 30-day DMA (₹525.74), 50-day DMA (₹525.78), and 200-day DMA (₹523.73). The price distance from 200 DMA is +4.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹412.65) is positioned above the 30-day DMA (₹409.91), 50-day DMA (₹401.01), and 200-day DMA (₹399.65). The price distance from 200 DMA is +3.79%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[573.6, 578.23, 582.86, 587.49, 592.11, 596.74]</t>
+          <t>[412.65, 413.89, 415.13, 416.36, 417.6, 418.84]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[573.6, 584.98, 592.4, 599.18, 605.61, 611.84]</t>
+          <t>[412.65, 416.36, 418.62, 420.64, 422.54, 424.36]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[573.6, 573.17, 575.7, 578.72, 581.99, 585.42]</t>
+          <t>[412.65, 412.04, 412.51, 413.16, 413.9, 414.7]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>525.46</v>
+        <v>410.23</v>
       </c>
     </row>
     <row r="8">
@@ -1672,99 +1672,99 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>135145.51</v>
+        <v>134467.43</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>117.59</v>
+        <v>117</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹117.16 - ₹118.23</t>
+          <t>₹116.58 - ₹117.63</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>119.3</v>
+        <v>118.68</v>
       </c>
       <c r="I8" t="n">
-        <v>116.33</v>
+        <v>116.48</v>
       </c>
       <c r="J8" t="n">
-        <v>114.03</v>
+        <v>114.26</v>
       </c>
       <c r="K8" t="n">
-        <v>112.31</v>
+        <v>112.32</v>
       </c>
       <c r="L8" t="n">
-        <v>4.42</v>
+        <v>5.06</v>
       </c>
       <c r="M8" t="n">
-        <v>0.64</v>
+        <v>0.72</v>
       </c>
       <c r="N8" t="n">
         <v>0.75</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.19</v>
+        <v>11</v>
       </c>
       <c r="R8" t="n">
-        <v>46.4</v>
+        <v>44.1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.99</v>
+        <v>-1.05</v>
       </c>
       <c r="U8" t="n">
         <v>53.3</v>
       </c>
       <c r="V8" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>115.28</v>
+        <v>113.84</v>
       </c>
       <c r="Y8" t="n">
-        <v>112.78</v>
+        <v>111.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>109.72</v>
+        <v>109.17</v>
       </c>
       <c r="AA8" t="n">
-        <v>114.38</v>
+        <v>113.84</v>
       </c>
       <c r="AB8" t="n">
-        <v>117.86</v>
+        <v>117.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>118.46</v>
+        <v>118.26</v>
       </c>
       <c r="AD8" t="n">
-        <v>119.34</v>
+        <v>119.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>61.7</v>
+        <v>61</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.19) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.0) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
@@ -1783,43 +1783,43 @@
         <v>15</v>
       </c>
       <c r="AM8" t="n">
-        <v>120.97</v>
+        <v>120.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>114.6</v>
+        <v>113.74</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹135,145.51 Cr., a P/E ratio of 6.12, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,467.43 Cr., a P/E ratio of 6.09, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 61.75 (Bullish Momentum Zone), while MACD Line (0.64) trades below Signal (0.75) with an expanding histogram (-0.12). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.42% above the 200-day DMA (₹112.31). Daily volatility envelope is bounded by ATR(14) of ₹2.14.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.96 (Bullish Momentum Zone), while MACD Line (0.72) trades below Signal (0.75) with an expanding histogram (-0.03). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.06% above the 200-day DMA (₹112.32). Daily volatility envelope is bounded by ATR(14) of ₹2.11.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.59) is positioned above the 30-day DMA (₹116.33), 50-day DMA (₹114.03), and 200-day DMA (₹112.31). The price distance from 200 DMA is +4.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.00) is positioned above the 30-day DMA (₹116.48), 50-day DMA (₹114.26), and 200-day DMA (₹112.32). The price distance from 200 DMA is +5.06%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[117.59, 118.49, 119.4, 120.3, 121.2, 122.1]</t>
+          <t>[117.0, 117.35, 117.7, 118.05, 118.4, 118.75]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[117.59, 119.35, 120.61, 121.78, 122.91, 124.02]</t>
+          <t>[117.0, 118.19, 118.89, 119.51, 120.09, 120.64]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[117.59, 117.85, 118.49, 119.19, 119.92, 120.67]</t>
+          <t>[117.0, 116.72, 116.81, 116.96, 117.14, 117.34]</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>109.72</v>
+        <v>109.17</v>
       </c>
     </row>
     <row r="9">
@@ -1830,16 +1830,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60487.88</v>
+        <v>31078.56</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1847,146 +1847,146 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2178.5</v>
+        <v>565</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹2165.74 - ₹2197.65</t>
+          <t>₹561.36 - ₹570.46</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2229.56</v>
+        <v>579.55</v>
       </c>
       <c r="I9" t="n">
-        <v>2143.45</v>
+        <v>528.34</v>
       </c>
       <c r="J9" t="n">
-        <v>2026.16</v>
+        <v>526.3200000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>1961.52</v>
+        <v>523.89</v>
       </c>
       <c r="L9" t="n">
-        <v>15.73</v>
+        <v>8.42</v>
       </c>
       <c r="M9" t="n">
-        <v>37.59</v>
+        <v>9.93</v>
       </c>
       <c r="N9" t="n">
-        <v>47.03</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-9.44</v>
+        <v>0.06</v>
       </c>
       <c r="P9" t="n">
-        <v>63.82</v>
+        <v>18.19</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.19</v>
+        <v>11</v>
       </c>
       <c r="R9" t="n">
-        <v>43.7</v>
+        <v>37.9</v>
       </c>
       <c r="S9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.97</v>
+        <v>-2.53</v>
       </c>
       <c r="U9" t="n">
-        <v>55</v>
+        <v>46.7</v>
       </c>
       <c r="V9" t="n">
-        <v>3.19</v>
+        <v>4.29</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>2075.73</v>
+        <v>536.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>2002.03</v>
+        <v>518.02</v>
       </c>
       <c r="Z9" t="n">
-        <v>2002.03</v>
+        <v>517.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>2082.77</v>
+        <v>537.71</v>
       </c>
       <c r="AB9" t="n">
-        <v>2182.13</v>
+        <v>567.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>2195.66</v>
+        <v>571.5599999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>2212.83</v>
+        <v>578.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>55.5</v>
+        <v>64.2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.0) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>49.2</v>
+        <v>5.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>8.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>5.2</v>
+        <v>65.2</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>2244.52</v>
+        <v>579.42</v>
       </c>
       <c r="AN9" t="n">
-        <v>2119.97</v>
+        <v>550.59</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,487.88 Cr., a P/E ratio of 49.21, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,078.56 Cr., a P/E ratio of 5.41, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.51 (Bullish Momentum Zone), while MACD Line (37.59) trades below Signal (47.03) with an expanding histogram (-9.44). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.73% above the 200-day DMA (₹1961.52). Daily volatility envelope is bounded by ATR(14) of ₹63.82.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.22 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (9.86) with an expanding histogram (+0.06). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.42% above the 200-day DMA (₹523.89). Daily volatility envelope is bounded by ATR(14) of ₹18.19.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,178.50) is positioned above the 30-day DMA (₹2,143.45), 50-day DMA (₹2,026.16), and 200-day DMA (₹1,961.52). The price distance from 200 DMA is +15.73%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹565.00) is positioned above the 30-day DMA (₹528.34), 50-day DMA (₹526.32), and 200-day DMA (₹523.89). The price distance from 200 DMA is +8.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[2178.5, 2185.04, 2191.57, 2198.11, 2204.64, 2211.18]</t>
+          <t>[565.0, 566.69, 568.39, 570.08, 571.78, 573.47]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[2178.5, 2210.56, 2227.67, 2242.32, 2255.7, 2268.26]</t>
+          <t>[565.0, 573.97, 578.68, 582.69, 586.33, 589.75]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[2178.5, 2165.89, 2164.49, 2164.95, 2166.35, 2168.37]</t>
+          <t>[565.0, 561.24, 560.67, 560.63, 560.86, 561.27]</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>2002.03</v>
+        <v>517.55</v>
       </c>
     </row>
     <row r="10">
@@ -2006,7 +2006,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>107323.68</v>
+        <v>106506.34</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2014,98 +2014,98 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>741.9</v>
+        <v>736.25</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹738.93 - ₹746.36</t>
+          <t>₹733.34 - ₹740.61</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>753.79</v>
+        <v>747.87</v>
       </c>
       <c r="I10" t="n">
-        <v>722.89</v>
+        <v>723.4299999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>727.97</v>
+        <v>728.1</v>
       </c>
       <c r="K10" t="n">
-        <v>686.01</v>
+        <v>686.1</v>
       </c>
       <c r="L10" t="n">
-        <v>6.81</v>
+        <v>8.58</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.93</v>
+        <v>0.97</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.85</v>
+        <v>-1.29</v>
       </c>
       <c r="O10" t="n">
-        <v>0.93</v>
+        <v>2.26</v>
       </c>
       <c r="P10" t="n">
-        <v>14.87</v>
+        <v>14.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>11.19</v>
+        <v>11</v>
       </c>
       <c r="R10" t="n">
-        <v>42.5</v>
+        <v>37.1</v>
       </c>
       <c r="S10" t="n">
         <v>0.27</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.27</v>
+        <v>-1.45</v>
       </c>
       <c r="U10" t="n">
-        <v>46.7</v>
+        <v>45</v>
       </c>
       <c r="V10" t="n">
-        <v>11.56</v>
+        <v>11.59</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>715.04</v>
+        <v>709.86</v>
       </c>
       <c r="Y10" t="n">
-        <v>687.3</v>
+        <v>680.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>685.9299999999999</v>
+        <v>680.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>719.6</v>
+        <v>714.46</v>
       </c>
       <c r="AB10" t="n">
-        <v>743.85</v>
+        <v>740.47</v>
       </c>
       <c r="AC10" t="n">
-        <v>747.45</v>
+        <v>745.1900000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>753</v>
+        <v>754.12</v>
       </c>
       <c r="AE10" t="n">
-        <v>47.2</v>
+        <v>66.3</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Vol Spike 2.0x | Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.19) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (11.0) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
       <c r="AJ10" t="n">
         <v>15.1</v>
@@ -2117,43 +2117,43 @@
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>759.76</v>
+        <v>756.01</v>
       </c>
       <c r="AN10" t="n">
-        <v>723.16</v>
+        <v>717.72</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹107,323.68 Cr., a P/E ratio of 49.17, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,506.34 Cr., a P/E ratio of 48.92, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 47.15 (Consolidation Zone), while MACD Line (-0.93) trades above Signal (-1.85) with an expanding histogram (+0.93). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.81% above the 200-day DMA (₹686.01). Daily volatility envelope is bounded by ATR(14) of ₹14.87.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 66.30 (Bullish Momentum Zone), while MACD Line (0.97) trades above Signal (-1.29) with an expanding histogram (+2.26). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.58% above the 200-day DMA (₹686.10). Daily volatility envelope is bounded by ATR(14) of ₹14.53.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹741.90) is positioned above the 30-day DMA (₹722.89), 50-day DMA (₹727.97), and 200-day DMA (₹686.01). The price distance from 200 DMA is +6.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹736.25) is positioned above the 30-day DMA (₹723.43), 50-day DMA (₹728.10), and 200-day DMA (₹686.10). The price distance from 200 DMA is +8.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[741.9, 744.13, 746.35, 748.58, 750.8, 753.03]</t>
+          <t>[736.25, 738.46, 740.67, 742.88, 745.09, 747.29]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[741.9, 750.07, 754.76, 758.88, 762.7, 766.33]</t>
+          <t>[736.25, 744.27, 748.88, 752.94, 756.71, 760.29]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[741.9, 739.67, 740.04, 740.85, 741.88, 743.05]</t>
+          <t>[736.25, 734.1, 734.51, 735.33, 736.37, 737.55]</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>685.9299999999999</v>
+        <v>680.7</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU10"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,10 +713,10 @@
         <v>7.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="R2" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="S2" t="n">
         <v>0.26</v>
@@ -734,13 +734,13 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>333.75</v>
+        <v>342</v>
       </c>
       <c r="Y2" t="n">
-        <v>326.69</v>
+        <v>372.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>311.19</v>
+        <v>372.11</v>
       </c>
       <c r="AA2" t="n">
         <v>331.45</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (11.0) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
@@ -781,10 +781,10 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>354.94</v>
+        <v>353.76</v>
       </c>
       <c r="AN2" t="n">
-        <v>330.98</v>
+        <v>330.76</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>311.19</v>
+        <v>372.11</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60946.02</v>
+        <v>25000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2195</v>
+        <v>3262.6</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹2181.57 - ₹2215.15</t>
+          <t>₹3242.1 - ₹3293.35</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2248.73</v>
+        <v>3344.61</v>
       </c>
       <c r="I3" t="n">
-        <v>2149.07</v>
+        <v>3194.54</v>
       </c>
       <c r="J3" t="n">
-        <v>2033.35</v>
+        <v>3009.36</v>
       </c>
       <c r="K3" t="n">
-        <v>1963.6</v>
+        <v>2707.69</v>
       </c>
       <c r="L3" t="n">
-        <v>11.08</v>
+        <v>18.51</v>
       </c>
       <c r="M3" t="n">
-        <v>35.41</v>
+        <v>57.19</v>
       </c>
       <c r="N3" t="n">
-        <v>44.71</v>
+        <v>83.53</v>
       </c>
       <c r="O3" t="n">
-        <v>-9.289999999999999</v>
+        <v>-26.34</v>
       </c>
       <c r="P3" t="n">
-        <v>67.16</v>
+        <v>102.51</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="R3" t="n">
-        <v>50.2</v>
+        <v>49.9</v>
       </c>
       <c r="S3" t="n">
         <v>0.17</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.72</v>
+        <v>-1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>55</v>
+        <v>53.3</v>
       </c>
       <c r="V3" t="n">
-        <v>3.09</v>
+        <v>2.93</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>2099.05</v>
+        <v>3262.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>2056.08</v>
+        <v>4082.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>2017.19</v>
+        <v>4082.16</v>
       </c>
       <c r="AA3" t="n">
-        <v>2094.26</v>
+        <v>3108.84</v>
       </c>
       <c r="AB3" t="n">
-        <v>2184.73</v>
+        <v>3255.07</v>
       </c>
       <c r="AC3" t="n">
-        <v>2209.56</v>
+        <v>3297.34</v>
       </c>
       <c r="AD3" t="n">
-        <v>2224.13</v>
+        <v>3332.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>46.2</v>
+        <v>42.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.11</v>
+        <v>0.05</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.0) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>49.6</v>
+        <v>53.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8.5</v>
+        <v>85.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>5.2</v>
+        <v>55.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>2258.42</v>
+        <v>3394.85</v>
       </c>
       <c r="AN3" t="n">
-        <v>2133.44</v>
+        <v>3142.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,946.02 Cr., a P/E ratio of 49.58, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.19, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.18 (Consolidation Zone), while MACD Line (35.41) trades below Signal (44.71) with an expanding histogram (-9.29). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.08% above the 200-day DMA (₹1963.60). Daily volatility envelope is bounded by ATR(14) of ₹67.16.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.62 (Consolidation Zone), while MACD Line (57.19) trades below Signal (83.53) with an expanding histogram (-26.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.51% above the 200-day DMA (₹2707.69). Daily volatility envelope is bounded by ATR(14) of ₹102.51.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,195.00) is positioned above the 30-day DMA (₹2,149.07), 50-day DMA (₹2,033.35), and 200-day DMA (₹1,963.60). The price distance from 200 DMA is +11.08%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,262.60) is positioned above the 30-day DMA (₹3,194.54), 50-day DMA (₹3,009.36), and 200-day DMA (₹2,707.69). The price distance from 200 DMA is +18.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[2195.0, 2201.58, 2208.17, 2214.75, 2221.34, 2227.92]</t>
+          <t>[3262.6, 3283.62, 3304.63, 3325.65, 3346.67, 3367.68]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[2195.0, 2228.45, 2246.16, 2261.28, 2275.07, 2287.99]</t>
+          <t>[3262.6, 3324.62, 3362.62, 3396.67, 3428.67, 3459.37]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[2195.0, 2181.44, 2179.68, 2179.86, 2181.04, 2182.87]</t>
+          <t>[3262.6, 3252.86, 3261.14, 3272.39, 3285.16, 3298.92]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2017.19</v>
+        <v>4082.16</v>
       </c>
     </row>
     <row r="4">
@@ -995,7 +995,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1004,154 +1004,154 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>83037.77</v>
+        <v>410499.31</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3262.6</v>
+        <v>412.65</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹3242.1 - ₹3293.35</t>
+          <t>₹411.42 - ₹414.5</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3344.61</v>
+        <v>417.59</v>
       </c>
       <c r="I4" t="n">
-        <v>3194.54</v>
+        <v>409.91</v>
       </c>
       <c r="J4" t="n">
-        <v>3009.36</v>
+        <v>401.01</v>
       </c>
       <c r="K4" t="n">
-        <v>2707.69</v>
+        <v>399.65</v>
       </c>
       <c r="L4" t="n">
-        <v>18.51</v>
+        <v>3.79</v>
       </c>
       <c r="M4" t="n">
-        <v>57.19</v>
+        <v>3.54</v>
       </c>
       <c r="N4" t="n">
-        <v>83.53</v>
+        <v>5.18</v>
       </c>
       <c r="O4" t="n">
-        <v>-26.34</v>
+        <v>-1.64</v>
       </c>
       <c r="P4" t="n">
-        <v>102.51</v>
+        <v>6.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="R4" t="n">
-        <v>50.2</v>
+        <v>45.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.78</v>
+        <v>-0.87</v>
       </c>
       <c r="U4" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="V4" t="n">
-        <v>2.93</v>
+        <v>3.58</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>3194.38</v>
+        <v>412.65</v>
       </c>
       <c r="Y4" t="n">
-        <v>3126.44</v>
+        <v>438.88</v>
       </c>
       <c r="Z4" t="n">
-        <v>2585.25</v>
+        <v>420.58</v>
       </c>
       <c r="AA4" t="n">
-        <v>3108.84</v>
+        <v>403.39</v>
       </c>
       <c r="AB4" t="n">
-        <v>3255.07</v>
+        <v>414.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>3297.34</v>
+        <v>416.11</v>
       </c>
       <c r="AD4" t="n">
-        <v>3332.07</v>
+        <v>419.58</v>
       </c>
       <c r="AE4" t="n">
-        <v>42.6</v>
+        <v>38.6</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.0) | LSTM Deep Net</t>
+          <t>Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>54.1</v>
+        <v>20.2</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85.3</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
-        <v>55.6</v>
+        <v>28.5</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>3398.94</v>
+        <v>421.49</v>
       </c>
       <c r="AN4" t="n">
-        <v>3142.99</v>
+        <v>403.39</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹83,037.77 Cr., a P/E ratio of 54.08, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹410,499.31 Cr., a P/E ratio of 20.22, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.62 (Consolidation Zone), while MACD Line (57.19) trades below Signal (83.53) with an expanding histogram (-26.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.51% above the 200-day DMA (₹2707.69). Daily volatility envelope is bounded by ATR(14) of ₹102.51.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 38.64 (Consolidation Zone), while MACD Line (3.54) trades below Signal (5.18) with an expanding histogram (-1.64). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.79% above the 200-day DMA (₹399.65). Daily volatility envelope is bounded by ATR(14) of ₹6.17.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,262.60) is positioned above the 30-day DMA (₹3,194.54), 50-day DMA (₹3,009.36), and 200-day DMA (₹2,707.69). The price distance from 200 DMA is +18.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹412.65) is positioned above the 30-day DMA (₹409.91), 50-day DMA (₹401.01), and 200-day DMA (₹399.65). The price distance from 200 DMA is +3.79%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[3262.6, 3283.62, 3304.63, 3325.65, 3346.67, 3367.68]</t>
+          <t>[412.65, 413.89, 415.13, 416.36, 417.6, 418.84]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[3262.6, 3324.62, 3362.62, 3396.67, 3428.67, 3459.37]</t>
+          <t>[412.65, 416.36, 418.62, 420.64, 422.54, 424.36]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[3262.6, 3252.86, 3261.14, 3272.39, 3285.16, 3298.92]</t>
+          <t>[412.65, 412.04, 412.51, 413.16, 413.9, 414.7]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2585.25</v>
+        <v>420.58</v>
       </c>
     </row>
     <row r="5">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,154 +1171,154 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60719.81</v>
+        <v>134467.43</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1007</v>
+        <v>117</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹1001.73 - ₹1014.91</t>
+          <t>₹116.58 - ₹117.63</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1028.1</v>
+        <v>118.68</v>
       </c>
       <c r="I5" t="n">
-        <v>993.11</v>
+        <v>116.48</v>
       </c>
       <c r="J5" t="n">
-        <v>956.95</v>
+        <v>114.26</v>
       </c>
       <c r="K5" t="n">
-        <v>852.09</v>
+        <v>112.32</v>
       </c>
       <c r="L5" t="n">
-        <v>16.77</v>
+        <v>5.06</v>
       </c>
       <c r="M5" t="n">
-        <v>10.77</v>
+        <v>0.72</v>
       </c>
       <c r="N5" t="n">
-        <v>18.92</v>
+        <v>0.75</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.140000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="P5" t="n">
-        <v>26.37</v>
+        <v>2.11</v>
       </c>
       <c r="Q5" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="R5" t="n">
-        <v>46.8</v>
+        <v>44.1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.57</v>
+        <v>-1.05</v>
       </c>
       <c r="U5" t="n">
-        <v>51.7</v>
+        <v>53.3</v>
       </c>
       <c r="V5" t="n">
-        <v>3.59</v>
+        <v>2.44</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>981.71</v>
+        <v>117</v>
       </c>
       <c r="Y5" t="n">
-        <v>960.98</v>
+        <v>127.48</v>
       </c>
       <c r="Z5" t="n">
-        <v>914.61</v>
+        <v>127.48</v>
       </c>
       <c r="AA5" t="n">
-        <v>967.4400000000001</v>
+        <v>113.84</v>
       </c>
       <c r="AB5" t="n">
-        <v>1009.2</v>
+        <v>117.48</v>
       </c>
       <c r="AC5" t="n">
-        <v>1022.8</v>
+        <v>118.26</v>
       </c>
       <c r="AD5" t="n">
-        <v>1038.6</v>
+        <v>119.52</v>
       </c>
       <c r="AE5" t="n">
-        <v>44.7</v>
+        <v>61</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.29</v>
+        <v>-0.09</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.0) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>31.3</v>
+        <v>6.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23.9</v>
+        <v>-6.4</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>38.1</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1048.78</v>
+        <v>120.15</v>
       </c>
       <c r="AN5" t="n">
-        <v>968.3200000000001</v>
+        <v>113.67</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹60,719.81 Cr., a P/E ratio of 31.25, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,467.43 Cr., a P/E ratio of 6.09, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.71 (Consolidation Zone), while MACD Line (10.77) trades below Signal (18.92) with an expanding histogram (-8.14). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.77% above the 200-day DMA (₹852.09). Daily volatility envelope is bounded by ATR(14) of ₹26.37.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.96 (Bullish Momentum Zone), while MACD Line (0.72) trades below Signal (0.75) with an expanding histogram (-0.03). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.06% above the 200-day DMA (₹112.32). Daily volatility envelope is bounded by ATR(14) of ₹2.11.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,007.00) is positioned above the 30-day DMA (₹993.11), 50-day DMA (₹956.95), and 200-day DMA (₹852.09). The price distance from 200 DMA is +16.77%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.00) is positioned above the 30-day DMA (₹116.48), 50-day DMA (₹114.26), and 200-day DMA (₹112.32). The price distance from 200 DMA is +5.06%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[1007.0, 1010.02, 1013.04, 1016.06, 1019.08, 1022.1]</t>
+          <t>[117.0, 117.35, 117.7, 118.05, 118.4, 118.75]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[1007.0, 1020.57, 1027.96, 1034.33, 1040.18, 1045.69]</t>
+          <t>[117.0, 118.19, 118.89, 119.51, 120.09, 120.64]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[1007.0, 1002.11, 1001.85, 1002.36, 1003.26, 1004.41]</t>
+          <t>[117.0, 116.72, 116.81, 116.96, 117.14, 117.34]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>914.61</v>
+        <v>127.48</v>
       </c>
     </row>
     <row r="6">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,822 +1338,154 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>83409.02</v>
+        <v>31078.56</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1805</v>
+        <v>565</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹1792.99 - ₹1823.01</t>
+          <t>₹561.36 - ₹570.46</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1853.02</v>
+        <v>579.55</v>
       </c>
       <c r="I6" t="n">
-        <v>1793.35</v>
+        <v>528.34</v>
       </c>
       <c r="J6" t="n">
-        <v>1710.31</v>
+        <v>526.3200000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>1650.46</v>
+        <v>523.89</v>
       </c>
       <c r="L6" t="n">
-        <v>8.640000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="M6" t="n">
-        <v>12.32</v>
+        <v>9.93</v>
       </c>
       <c r="N6" t="n">
-        <v>24.85</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-12.53</v>
+        <v>0.06</v>
       </c>
       <c r="P6" t="n">
-        <v>60.03</v>
+        <v>18.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>11.25</v>
       </c>
       <c r="R6" t="n">
-        <v>46.4</v>
+        <v>38</v>
       </c>
       <c r="S6" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.13</v>
+        <v>-2.52</v>
       </c>
       <c r="U6" t="n">
-        <v>53.3</v>
+        <v>46.7</v>
       </c>
       <c r="V6" t="n">
-        <v>3.86</v>
+        <v>4.3</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>1711.38</v>
+        <v>555.35</v>
       </c>
       <c r="Y6" t="n">
-        <v>1646.63</v>
+        <v>625.04</v>
       </c>
       <c r="Z6" t="n">
-        <v>1646.63</v>
+        <v>625.04</v>
       </c>
       <c r="AA6" t="n">
-        <v>1714.96</v>
+        <v>537.71</v>
       </c>
       <c r="AB6" t="n">
-        <v>1795.03</v>
+        <v>567.38</v>
       </c>
       <c r="AC6" t="n">
-        <v>1816.36</v>
+        <v>571.5599999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>1827.73</v>
+        <v>578.13</v>
       </c>
       <c r="AE6" t="n">
-        <v>46.1</v>
+        <v>64.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.05</v>
+        <v>0.24</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.0) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.25) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>111.4</v>
+        <v>5.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>40.1</v>
+        <v>14.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>10.2</v>
+        <v>65.2</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>1863.5</v>
+        <v>579.36</v>
       </c>
       <c r="AN6" t="n">
-        <v>1742.91</v>
+        <v>549.89</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹83,409.02 Cr., a P/E ratio of 111.35, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,078.56 Cr., a P/E ratio of 5.41, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (12.32) trades below Signal (24.85) with an expanding histogram (-12.53). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.64% above the 200-day DMA (₹1650.46). Daily volatility envelope is bounded by ATR(14) of ₹60.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.22 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (9.86) with an expanding histogram (+0.06). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.42% above the 200-day DMA (₹523.89). Daily volatility envelope is bounded by ATR(14) of ₹18.19.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,805.00) is positioned above the 30-day DMA (₹1,793.35), 50-day DMA (₹1,710.31), and 200-day DMA (₹1,650.46). The price distance from 200 DMA is +8.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹565.00) is positioned above the 30-day DMA (₹528.34), 50-day DMA (₹526.32), and 200-day DMA (₹523.89). The price distance from 200 DMA is +8.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[1805.0, 1810.41, 1815.83, 1821.24, 1826.66, 1832.07]</t>
+          <t>[565.0, 566.69, 568.39, 570.08, 571.78, 573.47]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[1805.0, 1834.43, 1849.79, 1862.83, 1874.68, 1885.77]</t>
+          <t>[565.0, 573.97, 578.68, 582.69, 586.33, 589.75]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[1805.0, 1792.41, 1790.36, 1790.05, 1790.64, 1791.81]</t>
+          <t>[565.0, 561.24, 560.67, 560.63, 560.86, 561.27]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>1646.63</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>410499.31</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>412.65</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>₹411.42 - ₹414.5</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>417.59</v>
-      </c>
-      <c r="I7" t="n">
-        <v>409.91</v>
-      </c>
-      <c r="J7" t="n">
-        <v>401.01</v>
-      </c>
-      <c r="K7" t="n">
-        <v>399.65</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-1.64</v>
-      </c>
-      <c r="P7" t="n">
-        <v>6.17</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>11</v>
-      </c>
-      <c r="R7" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="U7" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X7" t="n">
-        <v>400.19</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>410.23</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>410.23</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>403.39</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>414.33</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>416.11</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>419.58</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>Low VIX (11.0) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>421.31</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>403.7</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹410,499.31 Cr., a P/E ratio of 20.22, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 38.64 (Consolidation Zone), while MACD Line (3.54) trades below Signal (5.18) with an expanding histogram (-1.64). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.79% above the 200-day DMA (₹399.65). Daily volatility envelope is bounded by ATR(14) of ₹6.17.</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹412.65) is positioned above the 30-day DMA (₹409.91), 50-day DMA (₹401.01), and 200-day DMA (₹399.65). The price distance from 200 DMA is +3.79%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>[412.65, 413.89, 415.13, 416.36, 417.6, 418.84]</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>[412.65, 416.36, 418.62, 420.64, 422.54, 424.36]</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>[412.65, 412.04, 412.51, 413.16, 413.9, 414.7]</t>
-        </is>
-      </c>
-      <c r="AU7" t="n">
-        <v>410.23</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>134467.43</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>117</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>₹116.58 - ₹117.63</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>118.68</v>
-      </c>
-      <c r="I8" t="n">
-        <v>116.48</v>
-      </c>
-      <c r="J8" t="n">
-        <v>114.26</v>
-      </c>
-      <c r="K8" t="n">
-        <v>112.32</v>
-      </c>
-      <c r="L8" t="n">
-        <v>5.06</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>11</v>
-      </c>
-      <c r="R8" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="U8" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X8" t="n">
-        <v>113.84</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>111.44</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>109.17</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>113.84</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>117.48</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>118.26</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>119.52</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>61</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.0) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>120.25</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>113.74</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,467.43 Cr., a P/E ratio of 6.09, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.96 (Bullish Momentum Zone), while MACD Line (0.72) trades below Signal (0.75) with an expanding histogram (-0.03). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.06% above the 200-day DMA (₹112.32). Daily volatility envelope is bounded by ATR(14) of ₹2.11.</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.00) is positioned above the 30-day DMA (₹116.48), 50-day DMA (₹114.26), and 200-day DMA (₹112.32). The price distance from 200 DMA is +5.06%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>[117.0, 117.35, 117.7, 118.05, 118.4, 118.75]</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>[117.0, 118.19, 118.89, 119.51, 120.09, 120.64]</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>[117.0, 116.72, 116.81, 116.96, 117.14, 117.34]</t>
-        </is>
-      </c>
-      <c r="AU8" t="n">
-        <v>109.17</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>31078.56</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>565</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>₹561.36 - ₹570.46</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>579.55</v>
-      </c>
-      <c r="I9" t="n">
-        <v>528.34</v>
-      </c>
-      <c r="J9" t="n">
-        <v>526.3200000000001</v>
-      </c>
-      <c r="K9" t="n">
-        <v>523.89</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="M9" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="N9" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="P9" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>11</v>
-      </c>
-      <c r="R9" t="n">
-        <v>37.9</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-2.53</v>
-      </c>
-      <c r="U9" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X9" t="n">
-        <v>536.4</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>518.02</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>517.55</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>537.71</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>567.38</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>571.5599999999999</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>578.13</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.0) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>579.42</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>550.59</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,078.56 Cr., a P/E ratio of 5.41, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.22 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (9.86) with an expanding histogram (+0.06). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.42% above the 200-day DMA (₹523.89). Daily volatility envelope is bounded by ATR(14) of ₹18.19.</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹565.00) is positioned above the 30-day DMA (₹528.34), 50-day DMA (₹526.32), and 200-day DMA (₹523.89). The price distance from 200 DMA is +8.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>[565.0, 566.69, 568.39, 570.08, 571.78, 573.47]</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>[565.0, 573.97, 578.68, 582.69, 586.33, 589.75]</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>[565.0, 561.24, 560.67, 560.63, 560.86, 561.27]</t>
-        </is>
-      </c>
-      <c r="AU9" t="n">
-        <v>517.55</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>INDHOTEL</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>106506.34</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>736.25</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>₹733.34 - ₹740.61</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>747.87</v>
-      </c>
-      <c r="I10" t="n">
-        <v>723.4299999999999</v>
-      </c>
-      <c r="J10" t="n">
-        <v>728.1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>686.1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="P10" t="n">
-        <v>14.53</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>11</v>
-      </c>
-      <c r="R10" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-1.45</v>
-      </c>
-      <c r="U10" t="n">
-        <v>45</v>
-      </c>
-      <c r="V10" t="n">
-        <v>11.59</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X10" t="n">
-        <v>709.86</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>680.7</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>680.7</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>714.46</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>740.47</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>745.1900000000001</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>754.12</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (11.0) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>756.01</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>717.72</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹106,506.34 Cr., a P/E ratio of 48.92, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 66.30 (Bullish Momentum Zone), while MACD Line (0.97) trades above Signal (-1.29) with an expanding histogram (+2.26). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.58% above the 200-day DMA (₹686.10). Daily volatility envelope is bounded by ATR(14) of ₹14.53.</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹736.25) is positioned above the 30-day DMA (₹723.43), 50-day DMA (₹728.10), and 200-day DMA (₹686.10). The price distance from 200 DMA is +8.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>[736.25, 738.46, 740.67, 742.88, 745.09, 747.29]</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>[736.25, 744.27, 748.88, 752.94, 756.71, 760.29]</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>[736.25, 734.1, 734.51, 735.33, 736.37, 737.55]</t>
-        </is>
-      </c>
-      <c r="AU10" t="n">
-        <v>680.7</v>
+        <v>625.04</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU6"/>
+  <dimension ref="A1:AU11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,188 +656,188 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>314824.46</v>
+        <v>135398.36</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🟢 HIGH CONVICTION BUY</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>342</v>
+        <v>117.81</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹340.59 - ₹344.11</t>
+          <t>₹117.41 - ₹118.41</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>347.63</v>
+        <v>119.42</v>
       </c>
       <c r="I2" t="n">
-        <v>323.34</v>
+        <v>116.58</v>
       </c>
       <c r="J2" t="n">
-        <v>313.66</v>
+        <v>114.5</v>
       </c>
       <c r="K2" t="n">
-        <v>274.78</v>
+        <v>112.31</v>
       </c>
       <c r="L2" t="n">
-        <v>22.24</v>
+        <v>4.18</v>
       </c>
       <c r="M2" t="n">
-        <v>3.15</v>
+        <v>0.7</v>
       </c>
       <c r="N2" t="n">
-        <v>3.36</v>
+        <v>0.74</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="P2" t="n">
-        <v>7.03</v>
+        <v>2.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.25</v>
+        <v>10.34</v>
       </c>
       <c r="R2" t="n">
-        <v>51</v>
+        <v>49.9</v>
       </c>
       <c r="S2" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.99</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>55</v>
+        <v>54.1</v>
       </c>
       <c r="V2" t="n">
-        <v>2.76</v>
+        <v>2.42</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>342</v>
+        <v>117.81</v>
       </c>
       <c r="Y2" t="n">
-        <v>372.11</v>
+        <v>128.57</v>
       </c>
       <c r="Z2" t="n">
-        <v>372.11</v>
+        <v>128.57</v>
       </c>
       <c r="AA2" t="n">
-        <v>331.45</v>
+        <v>114.79</v>
       </c>
       <c r="AB2" t="n">
-        <v>339.55</v>
+        <v>117.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>344.45</v>
+        <v>118.39</v>
       </c>
       <c r="AD2" t="n">
-        <v>346.9</v>
+        <v>118.97</v>
       </c>
       <c r="AE2" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.26</v>
+        <v>-0.12</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (11.25) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (10.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>727.7</v>
+        <v>6.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>182</v>
+        <v>-6.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.6</v>
+        <v>38.1</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>353.76</v>
+        <v>120.93</v>
       </c>
       <c r="AN2" t="n">
-        <v>330.76</v>
+        <v>114.73</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹314,824.46 Cr., a P/E ratio of 727.66, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹135,398.36 Cr., a P/E ratio of 6.18, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.05 (Bullish Momentum Zone), while MACD Line (3.15) trades below Signal (3.36) with an expanding histogram (-0.21). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +22.24% above the 200-day DMA (₹274.78). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.00 (Consolidation Zone), while MACD Line (0.70) trades below Signal (0.74) with an expanding histogram (-0.04). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹112.31). Daily volatility envelope is bounded by ATR(14) of ₹2.01.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹342.00) is positioned above the 30-day DMA (₹323.34), 50-day DMA (₹313.66), and 200-day DMA (₹274.78). The price distance from 200 DMA is +22.24%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.81) is positioned above the 30-day DMA (₹116.58), 50-day DMA (₹114.50), and 200-day DMA (₹112.31). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[342.0, 343.09, 344.18, 345.27, 346.35, 347.44]</t>
+          <t>[117.81, 118.95, 120.1, 121.24, 122.38, 123.53]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[342.0, 345.9, 348.16, 350.14, 351.98, 353.73]</t>
+          <t>[117.81, 119.76, 121.24, 122.64, 123.99, 125.33]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[342.0, 340.98, 341.19, 341.61, 342.14, 342.73]</t>
+          <t>[117.81, 118.35, 119.24, 120.19, 121.18, 122.18]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>372.11</v>
+        <v>128.57</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25000</v>
+        <v>60618.38</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,324 +845,324 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3262.6</v>
+        <v>2183.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹3242.1 - ₹3293.35</t>
+          <t>₹2169.77 - ₹2203.35</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3344.61</v>
+        <v>2236.93</v>
       </c>
       <c r="I3" t="n">
-        <v>3194.54</v>
+        <v>2149.07</v>
       </c>
       <c r="J3" t="n">
-        <v>3009.36</v>
+        <v>2033.35</v>
       </c>
       <c r="K3" t="n">
-        <v>2707.69</v>
+        <v>1963.6</v>
       </c>
       <c r="L3" t="n">
-        <v>18.51</v>
+        <v>11.08</v>
       </c>
       <c r="M3" t="n">
-        <v>57.19</v>
+        <v>35.41</v>
       </c>
       <c r="N3" t="n">
-        <v>83.53</v>
+        <v>44.71</v>
       </c>
       <c r="O3" t="n">
-        <v>-26.34</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>102.51</v>
+        <v>67.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.25</v>
+        <v>10.34</v>
       </c>
       <c r="R3" t="n">
-        <v>49.9</v>
+        <v>49.7</v>
       </c>
       <c r="S3" t="n">
         <v>0.17</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.8</v>
+        <v>-1.76</v>
       </c>
       <c r="U3" t="n">
-        <v>53.3</v>
+        <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>2.93</v>
+        <v>3.08</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>3262.6</v>
+        <v>2158.78</v>
       </c>
       <c r="Y3" t="n">
-        <v>4082.16</v>
+        <v>2379.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>4082.16</v>
+        <v>2379.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>3108.84</v>
+        <v>2082.46</v>
       </c>
       <c r="AB3" t="n">
-        <v>3255.07</v>
+        <v>2188.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>3297.34</v>
+        <v>2198.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>3332.07</v>
+        <v>2214.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>42.6</v>
+        <v>46.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (11.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (10.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>53.2</v>
+        <v>49.3</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85.3</v>
+        <v>8.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>55.6</v>
+        <v>5.2</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>3394.85</v>
+        <v>2248.85</v>
       </c>
       <c r="AN3" t="n">
-        <v>3142.54</v>
+        <v>2125.57</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.19, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,618.38 Cr., a P/E ratio of 49.30, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 42.62 (Consolidation Zone), while MACD Line (57.19) trades below Signal (83.53) with an expanding histogram (-26.34). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.51% above the 200-day DMA (₹2707.69). Daily volatility envelope is bounded by ATR(14) of ₹102.51.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.18 (Consolidation Zone), while MACD Line (35.41) trades below Signal (44.71) with an expanding histogram (-9.29). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.08% above the 200-day DMA (₹1963.60). Daily volatility envelope is bounded by ATR(14) of ₹67.16.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,262.60) is positioned above the 30-day DMA (₹3,194.54), 50-day DMA (₹3,009.36), and 200-day DMA (₹2,707.69). The price distance from 200 DMA is +18.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,183.20) is positioned above the 30-day DMA (₹2,149.07), 50-day DMA (₹2,033.35), and 200-day DMA (₹1,963.60). The price distance from 200 DMA is +11.08%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[3262.6, 3283.62, 3304.63, 3325.65, 3346.67, 3367.68]</t>
+          <t>[2183.2, 2189.75, 2196.3, 2202.85, 2209.4, 2215.95]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[3262.6, 3324.62, 3362.62, 3396.67, 3428.67, 3459.37]</t>
+          <t>[2183.2, 2216.61, 2234.29, 2249.38, 2263.13, 2276.02]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[3262.6, 3252.86, 3261.14, 3272.39, 3285.16, 3298.92]</t>
+          <t>[2183.2, 2169.6, 2167.81, 2167.95, 2169.1, 2170.9]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>4082.16</v>
+        <v>2379.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>410499.31</v>
+        <v>315883.07</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>412.65</v>
+        <v>343.15</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹411.42 - ₹414.5</t>
+          <t>₹341.74 - ₹345.26</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>417.59</v>
+        <v>348.77</v>
       </c>
       <c r="I4" t="n">
-        <v>409.91</v>
+        <v>324.14</v>
       </c>
       <c r="J4" t="n">
-        <v>401.01</v>
+        <v>314.78</v>
       </c>
       <c r="K4" t="n">
-        <v>399.65</v>
+        <v>275.03</v>
       </c>
       <c r="L4" t="n">
-        <v>3.79</v>
+        <v>24.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.54</v>
+        <v>4.33</v>
       </c>
       <c r="N4" t="n">
-        <v>5.18</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.64</v>
+        <v>0.77</v>
       </c>
       <c r="P4" t="n">
-        <v>6.17</v>
+        <v>7.03</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.25</v>
+        <v>10.34</v>
       </c>
       <c r="R4" t="n">
-        <v>45.2</v>
+        <v>49.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0.36</v>
+        <v>0.26</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.87</v>
+        <v>-1.05</v>
       </c>
       <c r="U4" t="n">
-        <v>51.7</v>
+        <v>55.7</v>
       </c>
       <c r="V4" t="n">
-        <v>3.58</v>
+        <v>2.73</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>412.65</v>
+        <v>343.15</v>
       </c>
       <c r="Y4" t="n">
-        <v>438.88</v>
+        <v>373.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>420.58</v>
+        <v>373.36</v>
       </c>
       <c r="AA4" t="n">
-        <v>403.39</v>
+        <v>332.61</v>
       </c>
       <c r="AB4" t="n">
-        <v>414.33</v>
+        <v>342.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>416.11</v>
+        <v>344.85</v>
       </c>
       <c r="AD4" t="n">
-        <v>419.58</v>
+        <v>346.55</v>
       </c>
       <c r="AE4" t="n">
-        <v>38.6</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.03</v>
+        <v>0.26</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Low VIX (11.25) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (10.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>20.2</v>
+        <v>714.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>182</v>
       </c>
       <c r="AK4" t="n">
-        <v>28.5</v>
+        <v>0.6</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>421.49</v>
+        <v>355.46</v>
       </c>
       <c r="AN4" t="n">
-        <v>403.39</v>
+        <v>332.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹410,499.31 Cr., a P/E ratio of 20.22, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹315,883.07 Cr., a P/E ratio of 714.90, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 38.64 (Consolidation Zone), while MACD Line (3.54) trades below Signal (5.18) with an expanding histogram (-1.64). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.79% above the 200-day DMA (₹399.65). Daily volatility envelope is bounded by ATR(14) of ₹6.17.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.91 (Bullish Momentum Zone), while MACD Line (4.33) trades above Signal (3.55) with an expanding histogram (+0.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +24.35% above the 200-day DMA (₹275.03). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹412.65) is positioned above the 30-day DMA (₹409.91), 50-day DMA (₹401.01), and 200-day DMA (₹399.65). The price distance from 200 DMA is +3.79%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹343.15) is positioned above the 30-day DMA (₹324.14), 50-day DMA (₹314.78), and 200-day DMA (₹275.03). The price distance from 200 DMA is +24.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[412.65, 413.89, 415.13, 416.36, 417.6, 418.84]</t>
+          <t>[343.15, 345.3, 347.45, 349.61, 351.76, 353.91]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[412.65, 416.36, 418.62, 420.64, 422.54, 424.36]</t>
+          <t>[343.15, 348.11, 351.43, 354.47, 357.38, 360.19]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[412.65, 412.04, 412.51, 413.16, 413.9, 414.7]</t>
+          <t>[343.15, 343.19, 344.47, 345.96, 347.54, 349.2]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>420.58</v>
+        <v>373.36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,165 +1171,165 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>134467.43</v>
+        <v>413533.44</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>117</v>
+        <v>415.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹116.58 - ₹117.63</t>
+          <t>₹414.49 - ₹417.52</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>118.68</v>
+        <v>420.55</v>
       </c>
       <c r="I5" t="n">
-        <v>116.48</v>
+        <v>410.57</v>
       </c>
       <c r="J5" t="n">
-        <v>114.26</v>
+        <v>401.7</v>
       </c>
       <c r="K5" t="n">
-        <v>112.32</v>
+        <v>399.56</v>
       </c>
       <c r="L5" t="n">
-        <v>5.06</v>
+        <v>3.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.72</v>
+        <v>3.06</v>
       </c>
       <c r="N5" t="n">
-        <v>0.75</v>
+        <v>4.76</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.03</v>
+        <v>-1.69</v>
       </c>
       <c r="P5" t="n">
-        <v>2.11</v>
+        <v>6.06</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.25</v>
+        <v>10.34</v>
       </c>
       <c r="R5" t="n">
-        <v>44.1</v>
+        <v>49</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.05</v>
+        <v>-0.72</v>
       </c>
       <c r="U5" t="n">
-        <v>53.3</v>
+        <v>52.5</v>
       </c>
       <c r="V5" t="n">
-        <v>2.44</v>
+        <v>3.59</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>117</v>
+        <v>415.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>127.48</v>
+        <v>439.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>127.48</v>
+        <v>423.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>113.84</v>
+        <v>406.61</v>
       </c>
       <c r="AB5" t="n">
-        <v>117.48</v>
+        <v>415.73</v>
       </c>
       <c r="AC5" t="n">
-        <v>118.26</v>
+        <v>417.21</v>
       </c>
       <c r="AD5" t="n">
-        <v>119.52</v>
+        <v>418.73</v>
       </c>
       <c r="AE5" t="n">
-        <v>61</v>
+        <v>38.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.25) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (10.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.1</v>
+        <v>20.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-6.4</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="n">
-        <v>38.1</v>
+        <v>28.5</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>120.15</v>
+        <v>424.62</v>
       </c>
       <c r="AN5" t="n">
-        <v>113.67</v>
+        <v>406.71</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,467.43 Cr., a P/E ratio of 6.09, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹413,533.44 Cr., a P/E ratio of 20.37, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.96 (Bullish Momentum Zone), while MACD Line (0.72) trades below Signal (0.75) with an expanding histogram (-0.03). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.06% above the 200-day DMA (₹112.32). Daily volatility envelope is bounded by ATR(14) of ₹2.11.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 38.09 (Consolidation Zone), while MACD Line (3.06) trades below Signal (4.76) with an expanding histogram (-1.69). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.28% above the 200-day DMA (₹399.56). Daily volatility envelope is bounded by ATR(14) of ₹6.06.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.00) is positioned above the 30-day DMA (₹116.48), 50-day DMA (₹114.26), and 200-day DMA (₹112.32). The price distance from 200 DMA is +5.06%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹415.70) is positioned above the 30-day DMA (₹410.57), 50-day DMA (₹401.70), and 200-day DMA (₹399.56). The price distance from 200 DMA is +3.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[117.0, 117.35, 117.7, 118.05, 118.4, 118.75]</t>
+          <t>[415.7, 416.95, 418.19, 419.44, 420.69, 421.94]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[117.0, 118.19, 118.89, 119.51, 120.09, 120.64]</t>
+          <t>[415.7, 419.37, 421.62, 423.64, 425.54, 427.36]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[117.0, 116.72, 116.81, 116.96, 117.14, 117.34]</t>
+          <t>[415.7, 415.13, 415.62, 416.29, 417.05, 417.87]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>127.48</v>
+        <v>423.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,154 +1338,989 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31078.56</v>
+        <v>25000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>565</v>
+        <v>3275.4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹561.36 - ₹570.46</t>
+          <t>₹3254.82 - ₹3306.28</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>579.55</v>
+        <v>3357.74</v>
       </c>
       <c r="I6" t="n">
-        <v>528.34</v>
+        <v>3207.03</v>
       </c>
       <c r="J6" t="n">
-        <v>526.3200000000001</v>
+        <v>3016.93</v>
       </c>
       <c r="K6" t="n">
-        <v>523.89</v>
+        <v>2713.68</v>
       </c>
       <c r="L6" t="n">
-        <v>8.42</v>
+        <v>20.23</v>
       </c>
       <c r="M6" t="n">
-        <v>9.93</v>
+        <v>54.17</v>
       </c>
       <c r="N6" t="n">
-        <v>9.859999999999999</v>
+        <v>77.66</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06</v>
+        <v>-23.49</v>
       </c>
       <c r="P6" t="n">
-        <v>18.19</v>
+        <v>102.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.25</v>
+        <v>10.34</v>
       </c>
       <c r="R6" t="n">
-        <v>38</v>
+        <v>48.6</v>
       </c>
       <c r="S6" t="n">
         <v>0.17</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.52</v>
+        <v>-1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>46.7</v>
+        <v>54.1</v>
       </c>
       <c r="V6" t="n">
-        <v>4.3</v>
+        <v>2.92</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>555.35</v>
+        <v>3275.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>625.04</v>
+        <v>4098.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>625.04</v>
+        <v>4098.18</v>
       </c>
       <c r="AA6" t="n">
-        <v>537.71</v>
+        <v>3121.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>567.38</v>
+        <v>3279.87</v>
       </c>
       <c r="AC6" t="n">
-        <v>571.5599999999999</v>
+        <v>3322.24</v>
       </c>
       <c r="AD6" t="n">
-        <v>578.13</v>
+        <v>3369.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>64.2</v>
+        <v>48.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.25) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (10.34) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.4</v>
+        <v>53.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14.5</v>
+        <v>85.3</v>
       </c>
       <c r="AK6" t="n">
-        <v>65.2</v>
+        <v>55.6</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>579.36</v>
+        <v>3416.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>549.89</v>
+        <v>3153.61</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,078.56 Cr., a P/E ratio of 5.41, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.40, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.22 (Bullish Momentum Zone), while MACD Line (9.93) trades above Signal (9.86) with an expanding histogram (+0.06). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.42% above the 200-day DMA (₹523.89). Daily volatility envelope is bounded by ATR(14) of ₹18.19.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.26 (Consolidation Zone), while MACD Line (54.17) trades below Signal (77.66) with an expanding histogram (-23.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.23% above the 200-day DMA (₹2713.68). Daily volatility envelope is bounded by ATR(14) of ₹102.92.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹565.00) is positioned above the 30-day DMA (₹528.34), 50-day DMA (₹526.32), and 200-day DMA (₹523.89). The price distance from 200 DMA is +8.42%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,275.40) is positioned above the 30-day DMA (₹3,207.03), 50-day DMA (₹3,016.93), and 200-day DMA (₹2,713.68). The price distance from 200 DMA is +20.23%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[565.0, 566.69, 568.39, 570.08, 571.78, 573.47]</t>
+          <t>[3275.4, 3296.51, 3317.62, 3338.73, 3359.83, 3380.94]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[565.0, 573.97, 578.68, 582.69, 586.33, 589.75]</t>
+          <t>[3275.4, 3337.68, 3375.84, 3410.03, 3442.17, 3473.0]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[565.0, 561.24, 560.67, 560.63, 560.86, 561.27]</t>
+          <t>[3275.4, 3265.63, 3273.95, 3285.25, 3298.08, 3311.9]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>625.04</v>
+        <v>4098.18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>84356.33</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1825.5</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>₹1813.49 - ₹1843.51</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1873.52</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1793.35</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1710.31</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1650.46</v>
+      </c>
+      <c r="L7" t="n">
+        <v>8.640000000000001</v>
+      </c>
+      <c r="M7" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="N7" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-12.53</v>
+      </c>
+      <c r="P7" t="n">
+        <v>60.03</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="R7" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="U7" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="V7" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1792.8</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2003.67</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2003.67</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1735.46</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1815.47</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1837.94</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1850.37</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>TTM Squeeze | Low VIX (10.34) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1888.84</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1764.66</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹84,356.33 Cr., a P/E ratio of 113.10, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (12.32) trades below Signal (24.85) with an expanding histogram (-12.53). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.64% above the 200-day DMA (₹1650.46). Daily volatility envelope is bounded by ATR(14) of ₹60.03.</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,825.50) is positioned above the 30-day DMA (₹1,793.35), 50-day DMA (₹1,710.31), and 200-day DMA (₹1,650.46). The price distance from 200 DMA is +8.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>[1825.5, 1830.98, 1836.45, 1841.93, 1847.41, 1852.88]</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>[1825.5, 1854.99, 1870.41, 1883.52, 1895.43, 1906.57]</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>[1825.5, 1812.97, 1810.99, 1810.74, 1811.39, 1812.61]</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>2003.67</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>63330.7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1050.3</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>₹1045.03 - ₹1058.21</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1071.4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>993.11</v>
+      </c>
+      <c r="J8" t="n">
+        <v>956.95</v>
+      </c>
+      <c r="K8" t="n">
+        <v>852.09</v>
+      </c>
+      <c r="L8" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="M8" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="N8" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="P8" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="R8" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="U8" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="V8" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1050.3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1158.23</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1158.23</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1010.74</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1039.17</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1069.14</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1087.97</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Low VIX (10.34) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1095.03</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1005.23</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹63,330.70 Cr., a P/E ratio of 32.58, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.71 (Consolidation Zone), while MACD Line (10.77) trades below Signal (18.92) with an expanding histogram (-8.14). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.77% above the 200-day DMA (₹852.09). Daily volatility envelope is bounded by ATR(14) of ₹26.37.</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,050.30) is positioned above the 30-day DMA (₹993.11), 50-day DMA (₹956.95), and 200-day DMA (₹852.09). The price distance from 200 DMA is +16.77%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>[1050.3, 1064.65, 1078.99, 1093.34, 1107.69, 1122.04]</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>[1050.3, 1075.2, 1093.91, 1111.61, 1128.79, 1145.62]</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>[1050.3, 1056.74, 1067.81, 1079.64, 1091.87, 1104.34]</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>1158.23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>126429.43</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>🟡 MODERATE BUY</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>11360</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>₹11320.91 - ₹11418.63</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>11516.35</v>
+      </c>
+      <c r="I9" t="n">
+        <v>11192.21</v>
+      </c>
+      <c r="J9" t="n">
+        <v>11069.59</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10528.34</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.24</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-7.28</v>
+      </c>
+      <c r="O9" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="P9" t="n">
+        <v>195.44</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="R9" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="U9" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X9" t="n">
+        <v>11360</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>12369.24</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>12369.24</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>11066.84</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>11310.33</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>11425.66</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>11491.33</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>Low VIX (10.34) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>734.6</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>11688.44</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>11037.16</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹126,429.43 Cr., a P/E ratio of 14.55, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.69 (Consolidation Zone), while MACD Line (7.66) trades above Signal (-7.28) with an expanding histogram (+14.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.24% above the 200-day DMA (₹10528.34). Daily volatility envelope is bounded by ATR(14) of ₹195.44.</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,360.00) is positioned above the 30-day DMA (₹11,192.21), 50-day DMA (₹11,069.59), and 200-day DMA (₹10,528.34). The price distance from 200 DMA is +6.24%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>[11360.0, 11394.08, 11428.16, 11462.24, 11496.32, 11530.4]</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>[11360.0, 11472.26, 11538.72, 11597.65, 11652.67, 11705.21]</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>[11360.0, 11335.45, 11345.24, 11360.69, 11379.06, 11399.29]</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>12369.24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>31491.11</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>572.5</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>₹568.95 - ₹577.83</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>586.7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>530.77</v>
+      </c>
+      <c r="J10" t="n">
+        <v>526.84</v>
+      </c>
+      <c r="K10" t="n">
+        <v>524.0599999999999</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="M10" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="R10" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="U10" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X10" t="n">
+        <v>563.5599999999999</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>633.33</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>633.33</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>545.87</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>570.85</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>577.65</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>582.8</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (10.34) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>588.28</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>555.96</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,491.11 Cr., a P/E ratio of 5.52, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.50 (Bullish Momentum Zone), while MACD Line (10.36) trades above Signal (9.96) with an expanding histogram (+0.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.81% above the 200-day DMA (₹524.06). Daily volatility envelope is bounded by ATR(14) of ₹17.75.</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹572.50) is positioned above the 30-day DMA (₹530.77), 50-day DMA (₹526.84), and 200-day DMA (₹524.06). The price distance from 200 DMA is +7.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>[572.5, 574.22, 575.94, 577.65, 579.37, 581.09]</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>[572.5, 581.32, 585.98, 589.95, 593.57, 596.97]</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>[572.5, 568.89, 568.4, 568.43, 568.72, 569.18]</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>633.33</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>107316.44</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>741.85</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>₹738.94 - ₹746.21</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>753.47</v>
+      </c>
+      <c r="I11" t="n">
+        <v>723.4299999999999</v>
+      </c>
+      <c r="J11" t="n">
+        <v>728.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>686.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P11" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="R11" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="U11" t="n">
+        <v>45</v>
+      </c>
+      <c r="V11" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X11" t="n">
+        <v>740.67</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>818.42</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>818.42</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>720.0599999999999</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>740.67</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>745.1900000000001</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>748.52</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (10.34) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>760.53</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>722.87</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹107,316.44 Cr., a P/E ratio of 49.29, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 66.30 (Bullish Momentum Zone), while MACD Line (0.97) trades above Signal (-1.29) with an expanding histogram (+2.26). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.58% above the 200-day DMA (₹686.10). Daily volatility envelope is bounded by ATR(14) of ₹14.53.</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹741.85) is positioned above the 30-day DMA (₹723.43), 50-day DMA (₹728.10), and 200-day DMA (₹686.10). The price distance from 200 DMA is +8.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>[741.85, 744.08, 746.3, 748.53, 750.75, 752.98]</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>[741.85, 749.89, 754.52, 758.59, 762.37, 765.97]</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>[741.85, 739.72, 740.14, 740.98, 742.04, 743.23]</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>818.42</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>135398.36</v>
+        <v>411096.21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>117.81</v>
+        <v>413.25</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹117.41 - ₹118.41</t>
+          <t>₹412.04 - ₹415.07</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>119.42</v>
+        <v>418.1</v>
       </c>
       <c r="I2" t="n">
-        <v>116.58</v>
+        <v>410.57</v>
       </c>
       <c r="J2" t="n">
-        <v>114.5</v>
+        <v>401.7</v>
       </c>
       <c r="K2" t="n">
-        <v>112.31</v>
+        <v>399.56</v>
       </c>
       <c r="L2" t="n">
-        <v>4.18</v>
+        <v>3.28</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7</v>
+        <v>3.06</v>
       </c>
       <c r="N2" t="n">
-        <v>0.74</v>
+        <v>4.76</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.04</v>
+        <v>-1.69</v>
       </c>
       <c r="P2" t="n">
-        <v>2.01</v>
+        <v>6.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="R2" t="n">
-        <v>49.9</v>
+        <v>49.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.71</v>
       </c>
       <c r="U2" t="n">
-        <v>54.1</v>
+        <v>52.5</v>
       </c>
       <c r="V2" t="n">
-        <v>2.42</v>
+        <v>3.58</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>117.81</v>
+        <v>413.25</v>
       </c>
       <c r="Y2" t="n">
-        <v>128.57</v>
+        <v>435.67</v>
       </c>
       <c r="Z2" t="n">
-        <v>128.57</v>
+        <v>421.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>114.79</v>
+        <v>404.16</v>
       </c>
       <c r="AB2" t="n">
-        <v>117.5</v>
+        <v>413.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>118.39</v>
+        <v>416.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>118.97</v>
+        <v>419.85</v>
       </c>
       <c r="AE2" t="n">
-        <v>50</v>
+        <v>38.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (10.34) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.2</v>
+        <v>20.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-6.4</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>38.1</v>
+        <v>28.5</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>120.93</v>
+        <v>422.45</v>
       </c>
       <c r="AN2" t="n">
-        <v>114.73</v>
+        <v>403.74</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹135,398.36 Cr., a P/E ratio of 6.18, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹411,096.21 Cr., a P/E ratio of 20.28, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.00 (Consolidation Zone), while MACD Line (0.70) trades below Signal (0.74) with an expanding histogram (-0.04). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹112.31). Daily volatility envelope is bounded by ATR(14) of ₹2.01.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 38.09 (Consolidation Zone), while MACD Line (3.06) trades below Signal (4.76) with an expanding histogram (-1.69). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.28% above the 200-day DMA (₹399.56). Daily volatility envelope is bounded by ATR(14) of ₹6.06.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.81) is positioned above the 30-day DMA (₹116.58), 50-day DMA (₹114.50), and 200-day DMA (₹112.31). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹413.25) is positioned above the 30-day DMA (₹410.57), 50-day DMA (₹401.70), and 200-day DMA (₹399.56). The price distance from 200 DMA is +3.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[117.81, 118.95, 120.1, 121.24, 122.38, 123.53]</t>
+          <t>[413.25, 414.49, 415.73, 416.97, 418.21, 419.45]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[117.81, 119.76, 121.24, 122.64, 123.99, 125.33]</t>
+          <t>[413.25, 416.91, 419.16, 421.17, 423.06, 424.87]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[117.81, 118.35, 119.24, 120.19, 121.18, 122.18]</t>
+          <t>[413.25, 412.67, 413.16, 413.82, 414.57, 415.38]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>128.57</v>
+        <v>421.2</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60618.38</v>
+        <v>135961.52</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2183.2</v>
+        <v>118.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹2169.77 - ₹2203.35</t>
+          <t>₹117.9 - ₹118.9</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2236.93</v>
+        <v>119.91</v>
       </c>
       <c r="I3" t="n">
-        <v>2149.07</v>
+        <v>116.58</v>
       </c>
       <c r="J3" t="n">
-        <v>2033.35</v>
+        <v>114.5</v>
       </c>
       <c r="K3" t="n">
-        <v>1963.6</v>
+        <v>112.31</v>
       </c>
       <c r="L3" t="n">
-        <v>11.08</v>
+        <v>4.18</v>
       </c>
       <c r="M3" t="n">
-        <v>35.41</v>
+        <v>0.7</v>
       </c>
       <c r="N3" t="n">
-        <v>44.71</v>
+        <v>0.74</v>
       </c>
       <c r="O3" t="n">
-        <v>-9.289999999999999</v>
+        <v>-0.04</v>
       </c>
       <c r="P3" t="n">
-        <v>67.16</v>
+        <v>2.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="R3" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.17</v>
+        <v>0.4</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.76</v>
+        <v>-0.67</v>
       </c>
       <c r="U3" t="n">
-        <v>55</v>
+        <v>54.1</v>
       </c>
       <c r="V3" t="n">
-        <v>3.08</v>
+        <v>2.42</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>2158.78</v>
+        <v>118.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>2379.5</v>
+        <v>129.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>2379.5</v>
+        <v>129.19</v>
       </c>
       <c r="AA3" t="n">
-        <v>2082.46</v>
+        <v>115.28</v>
       </c>
       <c r="AB3" t="n">
-        <v>2188.4</v>
+        <v>117.94</v>
       </c>
       <c r="AC3" t="n">
-        <v>2198.8</v>
+        <v>119.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>2214.4</v>
+        <v>120.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.11</v>
+        <v>-0.12</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (10.34) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>49.3</v>
+        <v>6.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8.5</v>
+        <v>-6.4</v>
       </c>
       <c r="AK3" t="n">
-        <v>5.2</v>
+        <v>38.1</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>2248.85</v>
+        <v>121.61</v>
       </c>
       <c r="AN3" t="n">
-        <v>2125.57</v>
+        <v>115.13</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,618.38 Cr., a P/E ratio of 49.30, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹135,961.52 Cr., a P/E ratio of 6.16, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.18 (Consolidation Zone), while MACD Line (35.41) trades below Signal (44.71) with an expanding histogram (-9.29). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.08% above the 200-day DMA (₹1963.60). Daily volatility envelope is bounded by ATR(14) of ₹67.16.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.00 (Consolidation Zone), while MACD Line (0.70) trades below Signal (0.74) with an expanding histogram (-0.04). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹112.31). Daily volatility envelope is bounded by ATR(14) of ₹2.01.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,183.20) is positioned above the 30-day DMA (₹2,149.07), 50-day DMA (₹2,033.35), and 200-day DMA (₹1,963.60). The price distance from 200 DMA is +11.08%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹118.30) is positioned above the 30-day DMA (₹116.58), 50-day DMA (₹114.50), and 200-day DMA (₹112.31). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[2183.2, 2189.75, 2196.3, 2202.85, 2209.4, 2215.95]</t>
+          <t>[118.3, 119.52, 120.73, 121.95, 123.16, 124.38]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[2183.2, 2216.61, 2234.29, 2249.38, 2263.13, 2276.02]</t>
+          <t>[118.3, 120.32, 121.87, 123.34, 124.77, 126.18]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[2183.2, 2169.6, 2167.81, 2167.95, 2169.1, 2170.9]</t>
+          <t>[118.3, 118.91, 119.88, 120.9, 121.95, 123.03]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2379.5</v>
+        <v>129.19</v>
       </c>
     </row>
     <row r="4">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>315883.07</v>
+        <v>315422.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,15 +1012,15 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>343.15</v>
+        <v>342.65</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹341.74 - ₹345.26</t>
+          <t>₹341.24 - ₹344.76</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>348.77</v>
+        <v>348.27</v>
       </c>
       <c r="I4" t="n">
         <v>324.14</v>
@@ -1047,16 +1047,16 @@
         <v>7.03</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="R4" t="n">
-        <v>49.3</v>
+        <v>48.8</v>
       </c>
       <c r="S4" t="n">
         <v>0.26</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.05</v>
+        <v>-1.07</v>
       </c>
       <c r="U4" t="n">
         <v>55.7</v>
@@ -1068,25 +1068,25 @@
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>343.15</v>
+        <v>342.65</v>
       </c>
       <c r="Y4" t="n">
-        <v>373.36</v>
+        <v>372.81</v>
       </c>
       <c r="Z4" t="n">
-        <v>373.36</v>
+        <v>372.81</v>
       </c>
       <c r="AA4" t="n">
-        <v>332.61</v>
+        <v>332.11</v>
       </c>
       <c r="AB4" t="n">
-        <v>342.7</v>
+        <v>342.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>344.85</v>
+        <v>344.51</v>
       </c>
       <c r="AD4" t="n">
-        <v>346.55</v>
+        <v>346.38</v>
       </c>
       <c r="AE4" t="n">
         <v>65.90000000000001</v>
@@ -1096,14 +1096,14 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (10.34) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>714.9</v>
+        <v>778.8</v>
       </c>
       <c r="AJ4" t="n">
         <v>182</v>
@@ -1115,14 +1115,14 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>355.46</v>
+        <v>354.71</v>
       </c>
       <c r="AN4" t="n">
-        <v>332.26</v>
+        <v>330.23</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹315,883.07 Cr., a P/E ratio of 714.90, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹315,422.80 Cr., a P/E ratio of 778.75, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1132,26 +1132,26 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹343.15) is positioned above the 30-day DMA (₹324.14), 50-day DMA (₹314.78), and 200-day DMA (₹275.03). The price distance from 200 DMA is +24.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹342.65) is positioned above the 30-day DMA (₹324.14), 50-day DMA (₹314.78), and 200-day DMA (₹275.03). The price distance from 200 DMA is +24.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[343.15, 345.3, 347.45, 349.61, 351.76, 353.91]</t>
+          <t>[342.65, 344.78, 346.91, 349.04, 351.16, 353.29]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[343.15, 348.11, 351.43, 354.47, 357.38, 360.19]</t>
+          <t>[342.65, 347.59, 350.88, 353.9, 356.78, 359.58]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[343.15, 343.19, 344.47, 345.96, 347.54, 349.2]</t>
+          <t>[342.65, 342.67, 343.93, 345.39, 346.95, 348.58]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>373.36</v>
+        <v>372.81</v>
       </c>
     </row>
     <row r="5">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>413533.44</v>
+        <v>25000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,146 +1179,146 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>415.7</v>
+        <v>3374</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹414.49 - ₹417.52</t>
+          <t>₹3353.42 - ₹3404.88</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>420.55</v>
+        <v>3456.34</v>
       </c>
       <c r="I5" t="n">
-        <v>410.57</v>
+        <v>3207.03</v>
       </c>
       <c r="J5" t="n">
-        <v>401.7</v>
+        <v>3016.93</v>
       </c>
       <c r="K5" t="n">
-        <v>399.56</v>
+        <v>2713.68</v>
       </c>
       <c r="L5" t="n">
-        <v>3.28</v>
+        <v>20.23</v>
       </c>
       <c r="M5" t="n">
-        <v>3.06</v>
+        <v>54.17</v>
       </c>
       <c r="N5" t="n">
-        <v>4.76</v>
+        <v>77.66</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.69</v>
+        <v>-23.49</v>
       </c>
       <c r="P5" t="n">
-        <v>6.06</v>
+        <v>102.92</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="R5" t="n">
-        <v>49</v>
+        <v>48.3</v>
       </c>
       <c r="S5" t="n">
-        <v>0.37</v>
+        <v>0.24</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.72</v>
+        <v>-1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>52.5</v>
+        <v>54.1</v>
       </c>
       <c r="V5" t="n">
-        <v>3.59</v>
+        <v>2.98</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>415.7</v>
+        <v>3374</v>
       </c>
       <c r="Y5" t="n">
-        <v>439.1</v>
+        <v>4234.94</v>
       </c>
       <c r="Z5" t="n">
-        <v>423.7</v>
+        <v>4234.94</v>
       </c>
       <c r="AA5" t="n">
-        <v>406.61</v>
+        <v>3219.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>415.73</v>
+        <v>3328.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>417.21</v>
+        <v>3419.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>418.73</v>
+        <v>3465</v>
       </c>
       <c r="AE5" t="n">
-        <v>38.1</v>
+        <v>48.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (10.34) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>20.4</v>
+        <v>55.9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21</v>
+        <v>85.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>28.5</v>
+        <v>55.6</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>424.62</v>
+        <v>3515.45</v>
       </c>
       <c r="AN5" t="n">
-        <v>406.71</v>
+        <v>3249.71</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹413,533.44 Cr., a P/E ratio of 20.37, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 55.90, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 38.09 (Consolidation Zone), while MACD Line (3.06) trades below Signal (4.76) with an expanding histogram (-1.69). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.28% above the 200-day DMA (₹399.56). Daily volatility envelope is bounded by ATR(14) of ₹6.06.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.26 (Consolidation Zone), while MACD Line (54.17) trades below Signal (77.66) with an expanding histogram (-23.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.23% above the 200-day DMA (₹2713.68). Daily volatility envelope is bounded by ATR(14) of ₹102.92.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹415.70) is positioned above the 30-day DMA (₹410.57), 50-day DMA (₹401.70), and 200-day DMA (₹399.56). The price distance from 200 DMA is +3.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,374.00) is positioned above the 30-day DMA (₹3,207.03), 50-day DMA (₹3,016.93), and 200-day DMA (₹2,713.68). The price distance from 200 DMA is +20.23%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[415.7, 416.95, 418.19, 419.44, 420.69, 421.94]</t>
+          <t>[3374.0, 3411.78, 3449.56, 3487.34, 3525.12, 3562.9]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[415.7, 419.37, 421.62, 423.64, 425.54, 427.36]</t>
+          <t>[3374.0, 3452.95, 3507.78, 3558.65, 3607.46, 3654.95]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[415.7, 415.13, 415.62, 416.29, 417.05, 417.87]</t>
+          <t>[3374.0, 3380.9, 3405.89, 3433.86, 3463.37, 3493.86]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>423.7</v>
+        <v>4234.94</v>
       </c>
     </row>
     <row r="6">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>25000</v>
+        <v>87165.89999999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,146 +1346,146 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3275.4</v>
+        <v>1886.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹3254.82 - ₹3306.28</t>
+          <t>₹1874.54 - ₹1903.94</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3357.74</v>
+        <v>1933.33</v>
       </c>
       <c r="I6" t="n">
-        <v>3207.03</v>
+        <v>1795.75</v>
       </c>
       <c r="J6" t="n">
-        <v>3016.93</v>
+        <v>1715.08</v>
       </c>
       <c r="K6" t="n">
-        <v>2713.68</v>
+        <v>1650.21</v>
       </c>
       <c r="L6" t="n">
-        <v>20.23</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>54.17</v>
+        <v>12.72</v>
       </c>
       <c r="N6" t="n">
-        <v>77.66</v>
+        <v>22.42</v>
       </c>
       <c r="O6" t="n">
-        <v>-23.49</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>102.92</v>
+        <v>58.79</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="R6" t="n">
-        <v>48.6</v>
+        <v>47.5</v>
       </c>
       <c r="S6" t="n">
         <v>0.17</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.87</v>
+        <v>-1.91</v>
       </c>
       <c r="U6" t="n">
-        <v>54.1</v>
+        <v>53.3</v>
       </c>
       <c r="V6" t="n">
-        <v>2.92</v>
+        <v>5.63</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>3275.4</v>
+        <v>1856.48</v>
       </c>
       <c r="Y6" t="n">
-        <v>4098.18</v>
+        <v>2070.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>4098.18</v>
+        <v>2070.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>3121.02</v>
+        <v>1798.11</v>
       </c>
       <c r="AB6" t="n">
-        <v>3279.87</v>
+        <v>1861.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>3322.24</v>
+        <v>1929.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>3369.07</v>
+        <v>1973.3</v>
       </c>
       <c r="AE6" t="n">
-        <v>48.3</v>
+        <v>44.9</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (10.34) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>53.4</v>
+        <v>116.9</v>
       </c>
       <c r="AJ6" t="n">
-        <v>85.3</v>
+        <v>40.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>55.6</v>
+        <v>10.2</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>3416.19</v>
+        <v>1947.52</v>
       </c>
       <c r="AN6" t="n">
-        <v>3153.61</v>
+        <v>1824.19</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 53.40, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹87,165.90 Cr., a P/E ratio of 116.87, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.26 (Consolidation Zone), while MACD Line (54.17) trades below Signal (77.66) with an expanding histogram (-23.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.23% above the 200-day DMA (₹2713.68). Daily volatility envelope is bounded by ATR(14) of ₹102.92.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.87 (Consolidation Zone), while MACD Line (12.72) trades below Signal (22.42) with an expanding histogram (-9.71). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.38% above the 200-day DMA (₹1650.21). Daily volatility envelope is bounded by ATR(14) of ₹58.79.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,275.40) is positioned above the 30-day DMA (₹3,207.03), 50-day DMA (₹3,016.93), and 200-day DMA (₹2,713.68). The price distance from 200 DMA is +20.23%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,886.30) is positioned above the 30-day DMA (₹1,795.75), 50-day DMA (₹1,715.08), and 200-day DMA (₹1,650.21). The price distance from 200 DMA is +9.38%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[3275.4, 3296.51, 3317.62, 3338.73, 3359.83, 3380.94]</t>
+          <t>[1886.3, 1891.96, 1897.62, 1903.28, 1908.94, 1914.59]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[3275.4, 3337.68, 3375.84, 3410.03, 3442.17, 3473.0]</t>
+          <t>[1886.3, 1915.48, 1930.88, 1944.01, 1955.97, 1967.18]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[3275.4, 3265.63, 3273.95, 3285.25, 3298.08, 3311.9]</t>
+          <t>[1886.3, 1874.32, 1872.67, 1872.73, 1873.66, 1875.16]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>4098.18</v>
+        <v>2070.4</v>
       </c>
     </row>
     <row r="7">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1505,7 +1505,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>84356.33</v>
+        <v>62860.37</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,146 +1513,146 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1825.5</v>
+        <v>1042.5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹1813.49 - ₹1843.51</t>
+          <t>₹1037.25 - ₹1050.37</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1873.52</v>
+        <v>1063.49</v>
       </c>
       <c r="I7" t="n">
-        <v>1793.35</v>
+        <v>997.08</v>
       </c>
       <c r="J7" t="n">
-        <v>1710.31</v>
+        <v>957.75</v>
       </c>
       <c r="K7" t="n">
-        <v>1650.46</v>
+        <v>852.74</v>
       </c>
       <c r="L7" t="n">
-        <v>8.640000000000001</v>
+        <v>18.09</v>
       </c>
       <c r="M7" t="n">
-        <v>12.32</v>
+        <v>10.06</v>
       </c>
       <c r="N7" t="n">
-        <v>24.85</v>
+        <v>17.14</v>
       </c>
       <c r="O7" t="n">
-        <v>-12.53</v>
+        <v>-7.09</v>
       </c>
       <c r="P7" t="n">
-        <v>60.03</v>
+        <v>26.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="R7" t="n">
-        <v>46.5</v>
+        <v>46.8</v>
       </c>
       <c r="S7" t="n">
-        <v>0.16</v>
+        <v>0.34</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.09</v>
+        <v>-1.26</v>
       </c>
       <c r="U7" t="n">
-        <v>53.3</v>
+        <v>52.5</v>
       </c>
       <c r="V7" t="n">
-        <v>3.93</v>
+        <v>3.58</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>1792.8</v>
+        <v>1042.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>2003.67</v>
+        <v>1148.51</v>
       </c>
       <c r="Z7" t="n">
-        <v>2003.67</v>
+        <v>1148.51</v>
       </c>
       <c r="AA7" t="n">
-        <v>1735.46</v>
+        <v>1003.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>1815.47</v>
+        <v>1036.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>1837.94</v>
+        <v>1063.94</v>
       </c>
       <c r="AD7" t="n">
-        <v>1850.37</v>
+        <v>1085.37</v>
       </c>
       <c r="AE7" t="n">
-        <v>46.1</v>
+        <v>47.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.05</v>
+        <v>0.25</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (10.34) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>113.1</v>
+        <v>32.3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>40.1</v>
+        <v>23.9</v>
       </c>
       <c r="AK7" t="n">
-        <v>10.2</v>
+        <v>23</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>1888.84</v>
+        <v>1086.54</v>
       </c>
       <c r="AN7" t="n">
-        <v>1764.66</v>
+        <v>1004.23</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹84,356.33 Cr., a P/E ratio of 113.10, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹62,860.37 Cr., a P/E ratio of 32.34, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.13 (Consolidation Zone), while MACD Line (12.32) trades below Signal (24.85) with an expanding histogram (-12.53). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.64% above the 200-day DMA (₹1650.46). Daily volatility envelope is bounded by ATR(14) of ₹60.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 47.46 (Consolidation Zone), while MACD Line (10.06) trades below Signal (17.14) with an expanding histogram (-7.09). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.09% above the 200-day DMA (₹852.74). Daily volatility envelope is bounded by ATR(14) of ₹26.24.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,825.50) is positioned above the 30-day DMA (₹1,793.35), 50-day DMA (₹1,710.31), and 200-day DMA (₹1,650.46). The price distance from 200 DMA is +8.64%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,042.50) is positioned above the 30-day DMA (₹997.08), 50-day DMA (₹957.75), and 200-day DMA (₹852.74). The price distance from 200 DMA is +18.09%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[1825.5, 1830.98, 1836.45, 1841.93, 1847.41, 1852.88]</t>
+          <t>[1042.5, 1055.71, 1068.92, 1082.12, 1095.33, 1108.54]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[1825.5, 1854.99, 1870.41, 1883.52, 1895.43, 1906.57]</t>
+          <t>[1042.5, 1066.21, 1083.76, 1100.31, 1116.33, 1132.01]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[1825.5, 1812.97, 1810.99, 1810.74, 1811.39, 1812.61]</t>
+          <t>[1042.5, 1047.84, 1057.78, 1068.49, 1079.59, 1090.94]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>2003.67</v>
+        <v>1148.51</v>
       </c>
     </row>
     <row r="8">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>63330.7</v>
+        <v>127419.94</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1680,146 +1680,146 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1050.3</v>
+        <v>11449</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>₹1045.03 - ₹1058.21</t>
+          <t>₹11409.91 - ₹11507.63</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1071.4</v>
+        <v>11605.35</v>
       </c>
       <c r="I8" t="n">
-        <v>993.11</v>
+        <v>11192.21</v>
       </c>
       <c r="J8" t="n">
-        <v>956.95</v>
+        <v>11069.59</v>
       </c>
       <c r="K8" t="n">
-        <v>852.09</v>
+        <v>10528.34</v>
       </c>
       <c r="L8" t="n">
-        <v>16.77</v>
+        <v>6.24</v>
       </c>
       <c r="M8" t="n">
-        <v>10.77</v>
+        <v>7.66</v>
       </c>
       <c r="N8" t="n">
-        <v>18.92</v>
+        <v>-7.28</v>
       </c>
       <c r="O8" t="n">
-        <v>-8.140000000000001</v>
+        <v>14.94</v>
       </c>
       <c r="P8" t="n">
-        <v>26.37</v>
+        <v>195.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="R8" t="n">
-        <v>46.4</v>
+        <v>45.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0.36</v>
+        <v>0.31</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.23</v>
+        <v>-0.93</v>
       </c>
       <c r="U8" t="n">
-        <v>51.7</v>
+        <v>52.5</v>
       </c>
       <c r="V8" t="n">
-        <v>3.66</v>
+        <v>3.97</v>
       </c>
       <c r="W8" t="n">
         <v>-0.77</v>
       </c>
       <c r="X8" t="n">
-        <v>1050.3</v>
+        <v>11449</v>
       </c>
       <c r="Y8" t="n">
-        <v>1158.23</v>
+        <v>12466.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>1158.23</v>
+        <v>12466.15</v>
       </c>
       <c r="AA8" t="n">
-        <v>1010.74</v>
+        <v>11155.84</v>
       </c>
       <c r="AB8" t="n">
-        <v>1039.17</v>
+        <v>11364.33</v>
       </c>
       <c r="AC8" t="n">
-        <v>1069.14</v>
+        <v>11533.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>1087.97</v>
+        <v>11618.33</v>
       </c>
       <c r="AE8" t="n">
-        <v>44.7</v>
+        <v>54.7</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.29</v>
+        <v>0.02</v>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (10.34) | LSTM Deep Net</t>
+          <t>Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH8" t="n">
         <v>0.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>32.6</v>
+        <v>14.7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="AK8" t="n">
-        <v>23</v>
+        <v>734.6</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="AM8" t="n">
-        <v>1095.03</v>
+        <v>11757.92</v>
       </c>
       <c r="AN8" t="n">
-        <v>1005.23</v>
+        <v>11097.04</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹63,330.70 Cr., a P/E ratio of 32.58, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹127,419.94 Cr., a P/E ratio of 14.66, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.71 (Consolidation Zone), while MACD Line (10.77) trades below Signal (18.92) with an expanding histogram (-8.14). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +16.77% above the 200-day DMA (₹852.09). Daily volatility envelope is bounded by ATR(14) of ₹26.37.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.69 (Consolidation Zone), while MACD Line (7.66) trades above Signal (-7.28) with an expanding histogram (+14.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.24% above the 200-day DMA (₹10528.34). Daily volatility envelope is bounded by ATR(14) of ₹195.44.</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,050.30) is positioned above the 30-day DMA (₹993.11), 50-day DMA (₹956.95), and 200-day DMA (₹852.09). The price distance from 200 DMA is +16.77%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,449.00) is positioned above the 30-day DMA (₹11,192.21), 50-day DMA (₹11,069.59), and 200-day DMA (₹10,528.34). The price distance from 200 DMA is +6.24%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>[1050.3, 1064.65, 1078.99, 1093.34, 1107.69, 1122.04]</t>
+          <t>[11449.0, 11483.35, 11517.69, 11552.04, 11586.39, 11620.73]</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>[1050.3, 1075.2, 1093.91, 1111.61, 1128.79, 1145.62]</t>
+          <t>[11449.0, 11561.52, 11628.25, 11687.45, 11742.74, 11795.54]</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>[1050.3, 1056.74, 1067.81, 1079.64, 1091.87, 1104.34]</t>
+          <t>[11449.0, 11424.71, 11434.78, 11450.49, 11469.12, 11489.63]</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>1158.23</v>
+        <v>12466.15</v>
       </c>
     </row>
     <row r="9">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1839,154 +1839,154 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>126429.43</v>
+        <v>31491.11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>11360</v>
+        <v>572.5</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>₹11320.91 - ₹11418.63</t>
+          <t>₹568.95 - ₹577.83</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>11516.35</v>
+        <v>586.7</v>
       </c>
       <c r="I9" t="n">
-        <v>11192.21</v>
+        <v>530.77</v>
       </c>
       <c r="J9" t="n">
-        <v>11069.59</v>
+        <v>526.84</v>
       </c>
       <c r="K9" t="n">
-        <v>10528.34</v>
+        <v>524.0599999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>6.24</v>
+        <v>7.81</v>
       </c>
       <c r="M9" t="n">
-        <v>7.66</v>
+        <v>10.36</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.28</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>14.94</v>
+        <v>0.4</v>
       </c>
       <c r="P9" t="n">
-        <v>195.44</v>
+        <v>17.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="R9" t="n">
-        <v>45.6</v>
+        <v>44</v>
       </c>
       <c r="S9" t="n">
-        <v>0.31</v>
+        <v>0.17</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-2.09</v>
       </c>
       <c r="U9" t="n">
-        <v>52.5</v>
+        <v>47.5</v>
       </c>
       <c r="V9" t="n">
-        <v>3.96</v>
+        <v>4.3</v>
       </c>
       <c r="W9" t="n">
         <v>-0.77</v>
       </c>
       <c r="X9" t="n">
-        <v>11360</v>
+        <v>563.5599999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>12369.24</v>
+        <v>633.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>12369.24</v>
+        <v>633.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>11066.84</v>
+        <v>545.87</v>
       </c>
       <c r="AB9" t="n">
-        <v>11310.33</v>
+        <v>571.08</v>
       </c>
       <c r="AC9" t="n">
-        <v>11425.66</v>
+        <v>578.11</v>
       </c>
       <c r="AD9" t="n">
-        <v>11491.33</v>
+        <v>583.73</v>
       </c>
       <c r="AE9" t="n">
-        <v>54.7</v>
+        <v>60.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Low VIX (10.34) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH9" t="n">
         <v>0.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>14.6</v>
+        <v>5.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>24.2</v>
+        <v>14.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>734.6</v>
+        <v>65.2</v>
       </c>
       <c r="AL9" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AM9" t="n">
-        <v>11688.44</v>
+        <v>586.71</v>
       </c>
       <c r="AN9" t="n">
-        <v>11037.16</v>
+        <v>558.38</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹126,429.43 Cr., a P/E ratio of 14.55, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,491.11 Cr., a P/E ratio of 5.49, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.69 (Consolidation Zone), while MACD Line (7.66) trades above Signal (-7.28) with an expanding histogram (+14.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.24% above the 200-day DMA (₹10528.34). Daily volatility envelope is bounded by ATR(14) of ₹195.44.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.50 (Bullish Momentum Zone), while MACD Line (10.36) trades above Signal (9.96) with an expanding histogram (+0.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.81% above the 200-day DMA (₹524.06). Daily volatility envelope is bounded by ATR(14) of ₹17.75.</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,360.00) is positioned above the 30-day DMA (₹11,192.21), 50-day DMA (₹11,069.59), and 200-day DMA (₹10,528.34). The price distance from 200 DMA is +6.24%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹572.50) is positioned above the 30-day DMA (₹530.77), 50-day DMA (₹526.84), and 200-day DMA (₹524.06). The price distance from 200 DMA is +7.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>[11360.0, 11394.08, 11428.16, 11462.24, 11496.32, 11530.4]</t>
+          <t>[572.5, 574.22, 575.94, 577.65, 579.37, 581.09]</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>[11360.0, 11472.26, 11538.72, 11597.65, 11652.67, 11705.21]</t>
+          <t>[572.5, 581.32, 585.98, 589.95, 593.57, 596.97]</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>[11360.0, 11335.45, 11345.24, 11360.69, 11379.06, 11399.29]</t>
+          <t>[572.5, 568.89, 568.4, 568.43, 568.72, 569.18]</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>12369.24</v>
+        <v>633.33</v>
       </c>
     </row>
     <row r="10">
@@ -1997,16 +1997,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31491.11</v>
+        <v>60946.02</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -2014,146 +2014,146 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>572.5</v>
+        <v>2195</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>₹568.95 - ₹577.83</t>
+          <t>₹2181.68 - ₹2214.98</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>586.7</v>
+        <v>2248.29</v>
       </c>
       <c r="I10" t="n">
-        <v>530.77</v>
+        <v>2155.41</v>
       </c>
       <c r="J10" t="n">
-        <v>526.84</v>
+        <v>2041.41</v>
       </c>
       <c r="K10" t="n">
-        <v>524.0599999999999</v>
+        <v>1965.75</v>
       </c>
       <c r="L10" t="n">
-        <v>7.81</v>
+        <v>11.66</v>
       </c>
       <c r="M10" t="n">
-        <v>10.36</v>
+        <v>34.42</v>
       </c>
       <c r="N10" t="n">
-        <v>9.960000000000001</v>
+        <v>42.65</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4</v>
+        <v>-8.23</v>
       </c>
       <c r="P10" t="n">
-        <v>17.75</v>
+        <v>66.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="R10" t="n">
-        <v>43.9</v>
+        <v>43.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.09</v>
+        <v>-2.06</v>
       </c>
       <c r="U10" t="n">
-        <v>47.5</v>
+        <v>54.1</v>
       </c>
       <c r="V10" t="n">
-        <v>4.3</v>
+        <v>3.23</v>
       </c>
       <c r="W10" t="n">
         <v>-0.77</v>
       </c>
       <c r="X10" t="n">
-        <v>563.5599999999999</v>
+        <v>2162.51</v>
       </c>
       <c r="Y10" t="n">
-        <v>633.33</v>
+        <v>2392.35</v>
       </c>
       <c r="Z10" t="n">
-        <v>633.33</v>
+        <v>2392.35</v>
       </c>
       <c r="AA10" t="n">
-        <v>545.87</v>
+        <v>2095.09</v>
       </c>
       <c r="AB10" t="n">
-        <v>570.85</v>
+        <v>2192.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>577.65</v>
+        <v>2206.66</v>
       </c>
       <c r="AD10" t="n">
-        <v>582.8</v>
+        <v>2218.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>60.5</v>
+        <v>49.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.18</v>
+        <v>0.14</v>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (10.34) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH10" t="n">
         <v>0.15</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.5</v>
+        <v>49.6</v>
       </c>
       <c r="AJ10" t="n">
-        <v>14.5</v>
+        <v>8.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>65.2</v>
+        <v>5.2</v>
       </c>
       <c r="AL10" t="n">
         <v>15</v>
       </c>
       <c r="AM10" t="n">
-        <v>588.28</v>
+        <v>2259.39</v>
       </c>
       <c r="AN10" t="n">
-        <v>555.96</v>
+        <v>2134.74</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,491.11 Cr., a P/E ratio of 5.52, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,946.02 Cr., a P/E ratio of 49.57, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.50 (Bullish Momentum Zone), while MACD Line (10.36) trades above Signal (9.96) with an expanding histogram (+0.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.81% above the 200-day DMA (₹524.06). Daily volatility envelope is bounded by ATR(14) of ₹17.75.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.43 (Consolidation Zone), while MACD Line (34.42) trades below Signal (42.65) with an expanding histogram (-8.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.66% above the 200-day DMA (₹1965.75). Daily volatility envelope is bounded by ATR(14) of ₹66.61.</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹572.50) is positioned above the 30-day DMA (₹530.77), 50-day DMA (₹526.84), and 200-day DMA (₹524.06). The price distance from 200 DMA is +7.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,195.00) is positioned above the 30-day DMA (₹2,155.41), 50-day DMA (₹2,041.41), and 200-day DMA (₹1,965.75). The price distance from 200 DMA is +11.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>[572.5, 574.22, 575.94, 577.65, 579.37, 581.09]</t>
+          <t>[2195.0, 2201.58, 2208.17, 2214.75, 2221.34, 2227.92]</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>[572.5, 581.32, 585.98, 589.95, 593.57, 596.97]</t>
+          <t>[2195.0, 2228.23, 2245.85, 2260.9, 2274.63, 2287.5]</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>[572.5, 568.89, 568.4, 568.43, 568.72, 569.18]</t>
+          <t>[2195.0, 2181.6, 2179.91, 2180.14, 2181.37, 2183.24]</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>633.33</v>
+        <v>2392.35</v>
       </c>
     </row>
     <row r="11">
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>107316.44</v>
+        <v>107584.07</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -2181,98 +2181,98 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>741.85</v>
+        <v>743.7</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>₹738.94 - ₹746.21</t>
+          <t>₹740.91 - ₹747.89</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>753.47</v>
+        <v>754.86</v>
       </c>
       <c r="I11" t="n">
-        <v>723.4299999999999</v>
+        <v>723.84</v>
       </c>
       <c r="J11" t="n">
-        <v>728.1</v>
+        <v>728.16</v>
       </c>
       <c r="K11" t="n">
-        <v>686.1</v>
+        <v>686.15</v>
       </c>
       <c r="L11" t="n">
-        <v>8.58</v>
+        <v>7.3</v>
       </c>
       <c r="M11" t="n">
-        <v>0.97</v>
+        <v>1.74</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.29</v>
+        <v>-0.68</v>
       </c>
       <c r="O11" t="n">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="P11" t="n">
-        <v>14.53</v>
+        <v>13.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.34</v>
+        <v>10.35</v>
       </c>
       <c r="R11" t="n">
-        <v>37.4</v>
+        <v>41.6</v>
       </c>
       <c r="S11" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.43</v>
+        <v>-1.2</v>
       </c>
       <c r="U11" t="n">
-        <v>45</v>
+        <v>45.9</v>
       </c>
       <c r="V11" t="n">
-        <v>11.6</v>
+        <v>11.66</v>
       </c>
       <c r="W11" t="n">
         <v>-0.77</v>
       </c>
       <c r="X11" t="n">
-        <v>740.67</v>
+        <v>743.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>818.42</v>
+        <v>820.46</v>
       </c>
       <c r="Z11" t="n">
-        <v>818.42</v>
+        <v>820.46</v>
       </c>
       <c r="AA11" t="n">
-        <v>720.0599999999999</v>
+        <v>722.77</v>
       </c>
       <c r="AB11" t="n">
-        <v>740.67</v>
+        <v>741.28</v>
       </c>
       <c r="AC11" t="n">
-        <v>745.1900000000001</v>
+        <v>746.41</v>
       </c>
       <c r="AD11" t="n">
-        <v>748.52</v>
+        <v>749.13</v>
       </c>
       <c r="AE11" t="n">
-        <v>66.3</v>
+        <v>55.2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (10.34) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH11" t="n">
         <v>0.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="AJ11" t="n">
         <v>15.1</v>
@@ -2284,43 +2284,43 @@
         <v>15</v>
       </c>
       <c r="AM11" t="n">
-        <v>760.53</v>
+        <v>761.4299999999999</v>
       </c>
       <c r="AN11" t="n">
-        <v>722.87</v>
+        <v>725.11</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹107,316.44 Cr., a P/E ratio of 49.29, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹107,584.07 Cr., a P/E ratio of 49.42, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 66.30 (Bullish Momentum Zone), while MACD Line (0.97) trades above Signal (-1.29) with an expanding histogram (+2.26). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.58% above the 200-day DMA (₹686.10). Daily volatility envelope is bounded by ATR(14) of ₹14.53.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.22 (Bullish Momentum Zone), while MACD Line (1.74) trades above Signal (-0.68) with an expanding histogram (+2.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.30% above the 200-day DMA (₹686.15). Daily volatility envelope is bounded by ATR(14) of ₹13.95.</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹741.85) is positioned above the 30-day DMA (₹723.43), 50-day DMA (₹728.10), and 200-day DMA (₹686.10). The price distance from 200 DMA is +8.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹743.70) is positioned above the 30-day DMA (₹723.84), 50-day DMA (₹728.16), and 200-day DMA (₹686.15). The price distance from 200 DMA is +7.30%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>[741.85, 744.08, 746.3, 748.53, 750.75, 752.98]</t>
+          <t>[743.7, 745.93, 748.16, 750.39, 752.62, 754.86]</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>[741.85, 749.89, 754.52, 758.59, 762.37, 765.97]</t>
+          <t>[743.7, 751.51, 756.06, 760.06, 763.79, 767.34]</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>[741.85, 739.72, 740.14, 740.98, 742.04, 743.23]</t>
+          <t>[743.7, 741.75, 742.24, 743.14, 744.25, 745.5]</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>818.42</v>
+        <v>820.46</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU11"/>
+  <dimension ref="A1:AU7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,7 +661,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>411096.21</v>
+        <v>135961.52</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,87 +678,87 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>413.25</v>
+        <v>118.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹412.04 - ₹415.07</t>
+          <t>₹117.9 - ₹118.9</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>418.1</v>
+        <v>119.91</v>
       </c>
       <c r="I2" t="n">
-        <v>410.57</v>
+        <v>116.58</v>
       </c>
       <c r="J2" t="n">
-        <v>401.7</v>
+        <v>114.5</v>
       </c>
       <c r="K2" t="n">
-        <v>399.56</v>
+        <v>112.31</v>
       </c>
       <c r="L2" t="n">
-        <v>3.28</v>
+        <v>4.18</v>
       </c>
       <c r="M2" t="n">
-        <v>3.06</v>
+        <v>0.7</v>
       </c>
       <c r="N2" t="n">
-        <v>4.76</v>
+        <v>0.74</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.69</v>
+        <v>-0.04</v>
       </c>
       <c r="P2" t="n">
-        <v>6.06</v>
+        <v>2.01</v>
       </c>
       <c r="Q2" t="n">
         <v>10.35</v>
       </c>
       <c r="R2" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="S2" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.71</v>
+        <v>-0.67</v>
       </c>
       <c r="U2" t="n">
-        <v>52.5</v>
+        <v>54.1</v>
       </c>
       <c r="V2" t="n">
-        <v>3.58</v>
+        <v>2.42</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>413.25</v>
+        <v>115.71</v>
       </c>
       <c r="Y2" t="n">
-        <v>435.67</v>
+        <v>111.63</v>
       </c>
       <c r="Z2" t="n">
-        <v>421.2</v>
+        <v>108.24</v>
       </c>
       <c r="AA2" t="n">
-        <v>404.16</v>
+        <v>115.28</v>
       </c>
       <c r="AB2" t="n">
-        <v>413.95</v>
+        <v>117.94</v>
       </c>
       <c r="AC2" t="n">
-        <v>416.55</v>
+        <v>119.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>419.85</v>
+        <v>120.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>38.1</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -769,55 +769,55 @@
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>20.3</v>
+        <v>6.1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>-6.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>28.5</v>
+        <v>38.1</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>422.45</v>
+        <v>121.42</v>
       </c>
       <c r="AN2" t="n">
-        <v>403.74</v>
+        <v>115.1</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹411,096.21 Cr., a P/E ratio of 20.28, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹135,961.52 Cr., a P/E ratio of 6.09, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 38.09 (Consolidation Zone), while MACD Line (3.06) trades below Signal (4.76) with an expanding histogram (-1.69). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.28% above the 200-day DMA (₹399.56). Daily volatility envelope is bounded by ATR(14) of ₹6.06.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.00 (Consolidation Zone), while MACD Line (0.70) trades below Signal (0.74) with an expanding histogram (-0.04). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹112.31). Daily volatility envelope is bounded by ATR(14) of ₹2.01.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹413.25) is positioned above the 30-day DMA (₹410.57), 50-day DMA (₹401.70), and 200-day DMA (₹399.56). The price distance from 200 DMA is +3.28%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹118.30) is positioned above the 30-day DMA (₹116.58), 50-day DMA (₹114.50), and 200-day DMA (₹112.31). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[413.25, 414.49, 415.73, 416.97, 418.21, 419.45]</t>
+          <t>[118.3, 119.52, 120.73, 121.95, 123.16, 124.38]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[413.25, 416.91, 419.16, 421.17, 423.06, 424.87]</t>
+          <t>[118.3, 120.32, 121.87, 123.34, 124.77, 126.18]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[413.25, 412.67, 413.16, 413.82, 414.57, 415.38]</t>
+          <t>[118.3, 118.91, 119.88, 120.9, 121.95, 123.03]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>421.2</v>
+        <v>108.24</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>135961.52</v>
+        <v>315422.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>118.3</v>
+        <v>342.65</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹117.9 - ₹118.9</t>
+          <t>₹341.24 - ₹344.76</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>119.91</v>
+        <v>348.27</v>
       </c>
       <c r="I3" t="n">
-        <v>116.58</v>
+        <v>324.14</v>
       </c>
       <c r="J3" t="n">
-        <v>114.5</v>
+        <v>314.78</v>
       </c>
       <c r="K3" t="n">
-        <v>112.31</v>
+        <v>275.03</v>
       </c>
       <c r="L3" t="n">
-        <v>4.18</v>
+        <v>24.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7</v>
+        <v>4.33</v>
       </c>
       <c r="N3" t="n">
-        <v>0.74</v>
+        <v>3.55</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.04</v>
+        <v>0.77</v>
       </c>
       <c r="P3" t="n">
-        <v>2.01</v>
+        <v>7.03</v>
       </c>
       <c r="Q3" t="n">
         <v>10.35</v>
       </c>
       <c r="R3" t="n">
-        <v>49.5</v>
+        <v>49.1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.67</v>
+        <v>-1.06</v>
       </c>
       <c r="U3" t="n">
-        <v>54.1</v>
+        <v>55.7</v>
       </c>
       <c r="V3" t="n">
-        <v>2.42</v>
+        <v>2.73</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>118.3</v>
+        <v>333.79</v>
       </c>
       <c r="Y3" t="n">
-        <v>129.19</v>
+        <v>323.56</v>
       </c>
       <c r="Z3" t="n">
-        <v>129.19</v>
+        <v>316.85</v>
       </c>
       <c r="AA3" t="n">
-        <v>115.28</v>
+        <v>332.11</v>
       </c>
       <c r="AB3" t="n">
-        <v>117.94</v>
+        <v>342.53</v>
       </c>
       <c r="AC3" t="n">
-        <v>119.27</v>
+        <v>344.51</v>
       </c>
       <c r="AD3" t="n">
-        <v>120.23</v>
+        <v>346.38</v>
       </c>
       <c r="AE3" t="n">
-        <v>50</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.12</v>
+        <v>0.26</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.2</v>
+        <v>761.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-6.4</v>
+        <v>182</v>
       </c>
       <c r="AK3" t="n">
-        <v>38.1</v>
+        <v>0.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>121.61</v>
+        <v>354.68</v>
       </c>
       <c r="AN3" t="n">
-        <v>115.13</v>
+        <v>330.84</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹135,961.52 Cr., a P/E ratio of 6.16, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹315,422.80 Cr., a P/E ratio of 761.44, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.00 (Consolidation Zone), while MACD Line (0.70) trades below Signal (0.74) with an expanding histogram (-0.04). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹112.31). Daily volatility envelope is bounded by ATR(14) of ₹2.01.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.91 (Bullish Momentum Zone), while MACD Line (4.33) trades above Signal (3.55) with an expanding histogram (+0.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +24.35% above the 200-day DMA (₹275.03). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹118.30) is positioned above the 30-day DMA (₹116.58), 50-day DMA (₹114.50), and 200-day DMA (₹112.31). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹342.65) is positioned above the 30-day DMA (₹324.14), 50-day DMA (₹314.78), and 200-day DMA (₹275.03). The price distance from 200 DMA is +24.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[118.3, 119.52, 120.73, 121.95, 123.16, 124.38]</t>
+          <t>[342.65, 344.78, 346.91, 349.04, 351.16, 353.29]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[118.3, 120.32, 121.87, 123.34, 124.77, 126.18]</t>
+          <t>[342.65, 347.59, 350.88, 353.9, 356.78, 359.58]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[118.3, 118.91, 119.88, 120.9, 121.95, 123.03]</t>
+          <t>[342.65, 342.67, 343.93, 345.39, 346.95, 348.58]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>129.19</v>
+        <v>316.85</v>
       </c>
     </row>
     <row r="4">
@@ -995,16 +995,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>315422.8</v>
+        <v>25000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,146 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>342.65</v>
+        <v>3374</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹341.24 - ₹344.76</t>
+          <t>₹3353.42 - ₹3404.88</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>348.27</v>
+        <v>3456.34</v>
       </c>
       <c r="I4" t="n">
-        <v>324.14</v>
+        <v>3207.03</v>
       </c>
       <c r="J4" t="n">
-        <v>314.78</v>
+        <v>3016.93</v>
       </c>
       <c r="K4" t="n">
-        <v>275.03</v>
+        <v>2713.68</v>
       </c>
       <c r="L4" t="n">
-        <v>24.35</v>
+        <v>20.23</v>
       </c>
       <c r="M4" t="n">
-        <v>4.33</v>
+        <v>54.17</v>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>77.66</v>
       </c>
       <c r="O4" t="n">
-        <v>0.77</v>
+        <v>-23.49</v>
       </c>
       <c r="P4" t="n">
-        <v>7.03</v>
+        <v>102.92</v>
       </c>
       <c r="Q4" t="n">
         <v>10.35</v>
       </c>
       <c r="R4" t="n">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.07</v>
+        <v>-1.65</v>
       </c>
       <c r="U4" t="n">
-        <v>55.7</v>
+        <v>54.1</v>
       </c>
       <c r="V4" t="n">
-        <v>2.73</v>
+        <v>2.98</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>342.65</v>
+        <v>3303.32</v>
       </c>
       <c r="Y4" t="n">
-        <v>372.81</v>
+        <v>3201.48</v>
       </c>
       <c r="Z4" t="n">
-        <v>372.81</v>
+        <v>2628.44</v>
       </c>
       <c r="AA4" t="n">
-        <v>332.11</v>
+        <v>3219.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>342.53</v>
+        <v>3328.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>344.51</v>
+        <v>3419.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>346.38</v>
+        <v>3465</v>
       </c>
       <c r="AE4" t="n">
-        <v>65.90000000000001</v>
+        <v>48.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (10.35) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>778.8</v>
+        <v>54.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>182</v>
+        <v>85.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6</v>
+        <v>55.6</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>354.71</v>
+        <v>3519.7</v>
       </c>
       <c r="AN4" t="n">
-        <v>330.23</v>
+        <v>3252.41</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹315,422.80 Cr., a P/E ratio of 778.75, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.91 (Bullish Momentum Zone), while MACD Line (4.33) trades above Signal (3.55) with an expanding histogram (+0.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +24.35% above the 200-day DMA (₹275.03). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.26 (Consolidation Zone), while MACD Line (54.17) trades below Signal (77.66) with an expanding histogram (-23.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.23% above the 200-day DMA (₹2713.68). Daily volatility envelope is bounded by ATR(14) of ₹102.92.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹342.65) is positioned above the 30-day DMA (₹324.14), 50-day DMA (₹314.78), and 200-day DMA (₹275.03). The price distance from 200 DMA is +24.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,374.00) is positioned above the 30-day DMA (₹3,207.03), 50-day DMA (₹3,016.93), and 200-day DMA (₹2,713.68). The price distance from 200 DMA is +20.23%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[342.65, 344.78, 346.91, 349.04, 351.16, 353.29]</t>
+          <t>[3374.0, 3411.78, 3449.56, 3487.34, 3525.12, 3562.9]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[342.65, 347.59, 350.88, 353.9, 356.78, 359.58]</t>
+          <t>[3374.0, 3452.95, 3507.78, 3558.65, 3607.46, 3654.95]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[342.65, 342.67, 343.93, 345.39, 346.95, 348.58]</t>
+          <t>[3374.0, 3380.9, 3405.89, 3433.86, 3463.37, 3493.86]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>372.81</v>
+        <v>2628.44</v>
       </c>
     </row>
     <row r="5">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25000</v>
+        <v>87165.89999999999</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,87 +1179,87 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3374</v>
+        <v>1886.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹3353.42 - ₹3404.88</t>
+          <t>₹1874.54 - ₹1903.94</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3456.34</v>
+        <v>1933.33</v>
       </c>
       <c r="I5" t="n">
-        <v>3207.03</v>
+        <v>1795.75</v>
       </c>
       <c r="J5" t="n">
-        <v>3016.93</v>
+        <v>1715.08</v>
       </c>
       <c r="K5" t="n">
-        <v>2713.68</v>
+        <v>1650.21</v>
       </c>
       <c r="L5" t="n">
-        <v>20.23</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>54.17</v>
+        <v>12.72</v>
       </c>
       <c r="N5" t="n">
-        <v>77.66</v>
+        <v>22.42</v>
       </c>
       <c r="O5" t="n">
-        <v>-23.49</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>102.92</v>
+        <v>58.79</v>
       </c>
       <c r="Q5" t="n">
         <v>10.35</v>
       </c>
       <c r="R5" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="S5" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.65</v>
+        <v>-1.9</v>
       </c>
       <c r="U5" t="n">
-        <v>54.1</v>
+        <v>53.3</v>
       </c>
       <c r="V5" t="n">
-        <v>2.98</v>
+        <v>5.63</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>3374</v>
+        <v>1784.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>4234.94</v>
+        <v>1657.65</v>
       </c>
       <c r="Z5" t="n">
-        <v>4234.94</v>
+        <v>1657.65</v>
       </c>
       <c r="AA5" t="n">
-        <v>3219.62</v>
+        <v>1798.11</v>
       </c>
       <c r="AB5" t="n">
-        <v>3328.5</v>
+        <v>1861.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>3419.5</v>
+        <v>1929.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>3465</v>
+        <v>1973.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>48.3</v>
+        <v>44.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
@@ -1270,55 +1270,55 @@
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>55.9</v>
+        <v>117.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>85.3</v>
+        <v>40.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>55.6</v>
+        <v>10.2</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>3515.45</v>
+        <v>1952.37</v>
       </c>
       <c r="AN5" t="n">
-        <v>3249.71</v>
+        <v>1822.75</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 55.90, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹87,165.90 Cr., a P/E ratio of 117.45, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.26 (Consolidation Zone), while MACD Line (54.17) trades below Signal (77.66) with an expanding histogram (-23.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.23% above the 200-day DMA (₹2713.68). Daily volatility envelope is bounded by ATR(14) of ₹102.92.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.87 (Consolidation Zone), while MACD Line (12.72) trades below Signal (22.42) with an expanding histogram (-9.71). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.38% above the 200-day DMA (₹1650.21). Daily volatility envelope is bounded by ATR(14) of ₹58.79.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,374.00) is positioned above the 30-day DMA (₹3,207.03), 50-day DMA (₹3,016.93), and 200-day DMA (₹2,713.68). The price distance from 200 DMA is +20.23%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,886.30) is positioned above the 30-day DMA (₹1,795.75), 50-day DMA (₹1,715.08), and 200-day DMA (₹1,650.21). The price distance from 200 DMA is +9.38%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[3374.0, 3411.78, 3449.56, 3487.34, 3525.12, 3562.9]</t>
+          <t>[1886.3, 1891.96, 1897.62, 1903.28, 1908.94, 1914.59]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[3374.0, 3452.95, 3507.78, 3558.65, 3607.46, 3654.95]</t>
+          <t>[1886.3, 1915.48, 1930.88, 1944.01, 1955.97, 1967.18]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[3374.0, 3380.9, 3405.89, 3433.86, 3463.37, 3493.86]</t>
+          <t>[1886.3, 1874.32, 1872.67, 1872.73, 1873.66, 1875.16]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>4234.94</v>
+        <v>1657.65</v>
       </c>
     </row>
     <row r="6">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1338,154 +1338,154 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>87165.89999999999</v>
+        <v>31491.11</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1886.3</v>
+        <v>572.5</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹1874.54 - ₹1903.94</t>
+          <t>₹568.95 - ₹577.83</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1933.33</v>
+        <v>586.7</v>
       </c>
       <c r="I6" t="n">
-        <v>1795.75</v>
+        <v>530.77</v>
       </c>
       <c r="J6" t="n">
-        <v>1715.08</v>
+        <v>526.84</v>
       </c>
       <c r="K6" t="n">
-        <v>1650.21</v>
+        <v>524.0599999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>9.380000000000001</v>
+        <v>7.81</v>
       </c>
       <c r="M6" t="n">
-        <v>12.72</v>
+        <v>10.36</v>
       </c>
       <c r="N6" t="n">
-        <v>22.42</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.710000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="P6" t="n">
-        <v>58.79</v>
+        <v>17.75</v>
       </c>
       <c r="Q6" t="n">
         <v>10.35</v>
       </c>
       <c r="R6" t="n">
-        <v>47.5</v>
+        <v>44.2</v>
       </c>
       <c r="S6" t="n">
         <v>0.17</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.91</v>
+        <v>-2.08</v>
       </c>
       <c r="U6" t="n">
-        <v>53.3</v>
+        <v>47.5</v>
       </c>
       <c r="V6" t="n">
-        <v>5.63</v>
+        <v>4.3</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>1856.48</v>
+        <v>541.71</v>
       </c>
       <c r="Y6" t="n">
-        <v>2070.4</v>
+        <v>518.01</v>
       </c>
       <c r="Z6" t="n">
-        <v>2070.4</v>
+        <v>514.8200000000001</v>
       </c>
       <c r="AA6" t="n">
-        <v>1798.11</v>
+        <v>545.87</v>
       </c>
       <c r="AB6" t="n">
-        <v>1861.4</v>
+        <v>571.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>1929.8</v>
+        <v>578.11</v>
       </c>
       <c r="AD6" t="n">
-        <v>1973.3</v>
+        <v>583.73</v>
       </c>
       <c r="AE6" t="n">
-        <v>44.9</v>
+        <v>60.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>116.9</v>
+        <v>5.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>40.1</v>
+        <v>14.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>10.2</v>
+        <v>65.2</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>1947.52</v>
+        <v>587.4400000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>1824.19</v>
+        <v>558.09</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹87,165.90 Cr., a P/E ratio of 116.87, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,491.11 Cr., a P/E ratio of 5.42, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.87 (Consolidation Zone), while MACD Line (12.72) trades below Signal (22.42) with an expanding histogram (-9.71). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.38% above the 200-day DMA (₹1650.21). Daily volatility envelope is bounded by ATR(14) of ₹58.79.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.50 (Bullish Momentum Zone), while MACD Line (10.36) trades above Signal (9.96) with an expanding histogram (+0.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.81% above the 200-day DMA (₹524.06). Daily volatility envelope is bounded by ATR(14) of ₹17.75.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,886.30) is positioned above the 30-day DMA (₹1,795.75), 50-day DMA (₹1,715.08), and 200-day DMA (₹1,650.21). The price distance from 200 DMA is +9.38%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹572.50) is positioned above the 30-day DMA (₹530.77), 50-day DMA (₹526.84), and 200-day DMA (₹524.06). The price distance from 200 DMA is +7.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[1886.3, 1891.96, 1897.62, 1903.28, 1908.94, 1914.59]</t>
+          <t>[572.5, 574.22, 575.94, 577.65, 579.37, 581.09]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[1886.3, 1915.48, 1930.88, 1944.01, 1955.97, 1967.18]</t>
+          <t>[572.5, 581.32, 585.98, 589.95, 593.57, 596.97]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[1886.3, 1874.32, 1872.67, 1872.73, 1873.66, 1875.16]</t>
+          <t>[572.5, 568.89, 568.4, 568.43, 568.72, 569.18]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>2070.4</v>
+        <v>514.8200000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1496,831 +1496,163 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>62860.37</v>
+        <v>107584.07</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1042.5</v>
+        <v>743.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹1037.25 - ₹1050.37</t>
+          <t>₹740.91 - ₹747.89</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1063.49</v>
+        <v>754.86</v>
       </c>
       <c r="I7" t="n">
-        <v>997.08</v>
+        <v>723.84</v>
       </c>
       <c r="J7" t="n">
-        <v>957.75</v>
+        <v>728.16</v>
       </c>
       <c r="K7" t="n">
-        <v>852.74</v>
+        <v>686.15</v>
       </c>
       <c r="L7" t="n">
-        <v>18.09</v>
+        <v>7.3</v>
       </c>
       <c r="M7" t="n">
-        <v>10.06</v>
+        <v>1.74</v>
       </c>
       <c r="N7" t="n">
-        <v>17.14</v>
+        <v>-0.68</v>
       </c>
       <c r="O7" t="n">
-        <v>-7.09</v>
+        <v>2.43</v>
       </c>
       <c r="P7" t="n">
-        <v>26.24</v>
+        <v>13.95</v>
       </c>
       <c r="Q7" t="n">
         <v>10.35</v>
       </c>
       <c r="R7" t="n">
-        <v>46.8</v>
+        <v>41.3</v>
       </c>
       <c r="S7" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.26</v>
+        <v>-1.21</v>
       </c>
       <c r="U7" t="n">
-        <v>52.5</v>
+        <v>45.9</v>
       </c>
       <c r="V7" t="n">
-        <v>3.58</v>
+        <v>11.66</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>1042.5</v>
+        <v>719.71</v>
       </c>
       <c r="Y7" t="n">
-        <v>1148.51</v>
+        <v>697.79</v>
       </c>
       <c r="Z7" t="n">
-        <v>1148.51</v>
+        <v>672.71</v>
       </c>
       <c r="AA7" t="n">
-        <v>1003.14</v>
+        <v>722.77</v>
       </c>
       <c r="AB7" t="n">
-        <v>1036.57</v>
+        <v>741.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>1063.94</v>
+        <v>746.41</v>
       </c>
       <c r="AD7" t="n">
-        <v>1085.37</v>
+        <v>749.13</v>
       </c>
       <c r="AE7" t="n">
-        <v>47.5</v>
+        <v>55.2</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (10.35) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>32.3</v>
+        <v>48.8</v>
       </c>
       <c r="AJ7" t="n">
-        <v>23.9</v>
+        <v>15.1</v>
       </c>
       <c r="AK7" t="n">
-        <v>23</v>
+        <v>20.9</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>1086.54</v>
+        <v>762.89</v>
       </c>
       <c r="AN7" t="n">
-        <v>1004.23</v>
+        <v>725.95</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹62,860.37 Cr., a P/E ratio of 32.34, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹107,584.07 Cr., a P/E ratio of 48.77, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 47.46 (Consolidation Zone), while MACD Line (10.06) trades below Signal (17.14) with an expanding histogram (-7.09). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.09% above the 200-day DMA (₹852.74). Daily volatility envelope is bounded by ATR(14) of ₹26.24.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.22 (Bullish Momentum Zone), while MACD Line (1.74) trades above Signal (-0.68) with an expanding histogram (+2.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.30% above the 200-day DMA (₹686.15). Daily volatility envelope is bounded by ATR(14) of ₹13.95.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,042.50) is positioned above the 30-day DMA (₹997.08), 50-day DMA (₹957.75), and 200-day DMA (₹852.74). The price distance from 200 DMA is +18.09%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹743.70) is positioned above the 30-day DMA (₹723.84), 50-day DMA (₹728.16), and 200-day DMA (₹686.15). The price distance from 200 DMA is +7.30%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[1042.5, 1055.71, 1068.92, 1082.12, 1095.33, 1108.54]</t>
+          <t>[743.7, 745.93, 748.16, 750.39, 752.62, 754.86]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[1042.5, 1066.21, 1083.76, 1100.31, 1116.33, 1132.01]</t>
+          <t>[743.7, 751.51, 756.06, 760.06, 763.79, 767.34]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[1042.5, 1047.84, 1057.78, 1068.49, 1079.59, 1090.94]</t>
+          <t>[743.7, 741.75, 742.24, 743.14, 744.25, 745.5]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1148.51</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>BAJAJHLDNG</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>127419.94</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>🟡 MODERATE BUY</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>11449</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>₹11409.91 - ₹11507.63</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>11605.35</v>
-      </c>
-      <c r="I8" t="n">
-        <v>11192.21</v>
-      </c>
-      <c r="J8" t="n">
-        <v>11069.59</v>
-      </c>
-      <c r="K8" t="n">
-        <v>10528.34</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7.66</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-7.28</v>
-      </c>
-      <c r="O8" t="n">
-        <v>14.94</v>
-      </c>
-      <c r="P8" t="n">
-        <v>195.44</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="R8" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="U8" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X8" t="n">
-        <v>11449</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>12466.15</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>12466.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>11155.84</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>11364.33</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>11533.66</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>11618.33</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>Low VIX (10.35) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>734.6</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>11757.92</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>11097.04</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹127,419.94 Cr., a P/E ratio of 14.66, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.69 (Consolidation Zone), while MACD Line (7.66) trades above Signal (-7.28) with an expanding histogram (+14.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.24% above the 200-day DMA (₹10528.34). Daily volatility envelope is bounded by ATR(14) of ₹195.44.</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,449.00) is positioned above the 30-day DMA (₹11,192.21), 50-day DMA (₹11,069.59), and 200-day DMA (₹10,528.34). The price distance from 200 DMA is +6.24%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>[11449.0, 11483.35, 11517.69, 11552.04, 11586.39, 11620.73]</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>[11449.0, 11561.52, 11628.25, 11687.45, 11742.74, 11795.54]</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>[11449.0, 11424.71, 11434.78, 11450.49, 11469.12, 11489.63]</t>
-        </is>
-      </c>
-      <c r="AU8" t="n">
-        <v>12466.15</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>31491.11</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>572.5</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>₹568.95 - ₹577.83</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>586.7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>530.77</v>
-      </c>
-      <c r="J9" t="n">
-        <v>526.84</v>
-      </c>
-      <c r="K9" t="n">
-        <v>524.0599999999999</v>
-      </c>
-      <c r="L9" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="M9" t="n">
-        <v>10.36</v>
-      </c>
-      <c r="N9" t="n">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P9" t="n">
-        <v>17.75</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="R9" t="n">
-        <v>44</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-2.09</v>
-      </c>
-      <c r="U9" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="V9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W9" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X9" t="n">
-        <v>563.5599999999999</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>633.33</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>633.33</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>545.87</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>571.08</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>578.11</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>583.73</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (10.35) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>586.71</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>558.38</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,491.11 Cr., a P/E ratio of 5.49, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.50 (Bullish Momentum Zone), while MACD Line (10.36) trades above Signal (9.96) with an expanding histogram (+0.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.81% above the 200-day DMA (₹524.06). Daily volatility envelope is bounded by ATR(14) of ₹17.75.</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹572.50) is positioned above the 30-day DMA (₹530.77), 50-day DMA (₹526.84), and 200-day DMA (₹524.06). The price distance from 200 DMA is +7.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>[572.5, 574.22, 575.94, 577.65, 579.37, 581.09]</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>[572.5, 581.32, 585.98, 589.95, 593.57, 596.97]</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>[572.5, 568.89, 568.4, 568.43, 568.72, 569.18]</t>
-        </is>
-      </c>
-      <c r="AU9" t="n">
-        <v>633.33</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>60946.02</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>2195</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>₹2181.68 - ₹2214.98</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>2248.29</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2155.41</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2041.41</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1965.75</v>
-      </c>
-      <c r="L10" t="n">
-        <v>11.66</v>
-      </c>
-      <c r="M10" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="N10" t="n">
-        <v>42.65</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-8.23</v>
-      </c>
-      <c r="P10" t="n">
-        <v>66.61</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="R10" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T10" t="n">
-        <v>-2.06</v>
-      </c>
-      <c r="U10" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="W10" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2162.51</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2392.35</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2392.35</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2095.09</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2192.33</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2206.66</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2218.33</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>2259.39</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2134.74</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,946.02 Cr., a P/E ratio of 49.57, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.43 (Consolidation Zone), while MACD Line (34.42) trades below Signal (42.65) with an expanding histogram (-8.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.66% above the 200-day DMA (₹1965.75). Daily volatility envelope is bounded by ATR(14) of ₹66.61.</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,195.00) is positioned above the 30-day DMA (₹2,155.41), 50-day DMA (₹2,041.41), and 200-day DMA (₹1,965.75). The price distance from 200 DMA is +11.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>[2195.0, 2201.58, 2208.17, 2214.75, 2221.34, 2227.92]</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>[2195.0, 2228.23, 2245.85, 2260.9, 2274.63, 2287.5]</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>[2195.0, 2181.6, 2179.91, 2180.14, 2181.37, 2183.24]</t>
-        </is>
-      </c>
-      <c r="AU10" t="n">
-        <v>2392.35</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>INDHOTEL</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>107584.07</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>743.7</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>₹740.91 - ₹747.89</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>754.86</v>
-      </c>
-      <c r="I11" t="n">
-        <v>723.84</v>
-      </c>
-      <c r="J11" t="n">
-        <v>728.16</v>
-      </c>
-      <c r="K11" t="n">
-        <v>686.15</v>
-      </c>
-      <c r="L11" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="P11" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="R11" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="V11" t="n">
-        <v>11.66</v>
-      </c>
-      <c r="W11" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X11" t="n">
-        <v>743.7</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>820.46</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>820.46</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>722.77</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>741.28</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>746.41</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>749.13</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>55.2</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH11" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>761.4299999999999</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>725.11</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹107,584.07 Cr., a P/E ratio of 49.42, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.22 (Bullish Momentum Zone), while MACD Line (1.74) trades above Signal (-0.68) with an expanding histogram (+2.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.30% above the 200-day DMA (₹686.15). Daily volatility envelope is bounded by ATR(14) of ₹13.95.</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹743.70) is positioned above the 30-day DMA (₹723.84), 50-day DMA (₹728.16), and 200-day DMA (₹686.15). The price distance from 200 DMA is +7.30%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>[743.7, 745.93, 748.16, 750.39, 752.62, 754.86]</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>[743.7, 751.51, 756.06, 760.06, 763.79, 767.34]</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>[743.7, 741.75, 742.24, 743.14, 744.25, 745.5]</t>
-        </is>
-      </c>
-      <c r="AU11" t="n">
-        <v>820.46</v>
+        <v>672.71</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU7"/>
+  <dimension ref="A1:AU8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,12 +656,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>135961.52</v>
+        <v>25000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,166 +678,166 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>118.3</v>
+        <v>3428.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹117.9 - ₹118.9</t>
+          <t>₹3408.29 - ₹3458.81</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>119.91</v>
+        <v>3509.33</v>
       </c>
       <c r="I2" t="n">
-        <v>116.58</v>
+        <v>3220.73</v>
       </c>
       <c r="J2" t="n">
-        <v>114.5</v>
+        <v>3026.7</v>
       </c>
       <c r="K2" t="n">
-        <v>112.31</v>
+        <v>2720.4</v>
       </c>
       <c r="L2" t="n">
-        <v>4.18</v>
+        <v>24.03</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7</v>
+        <v>60.07</v>
       </c>
       <c r="N2" t="n">
-        <v>0.74</v>
+        <v>74.14</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.04</v>
+        <v>-14.07</v>
       </c>
       <c r="P2" t="n">
-        <v>2.01</v>
+        <v>101.04</v>
       </c>
       <c r="Q2" t="n">
-        <v>10.35</v>
+        <v>11.4</v>
       </c>
       <c r="R2" t="n">
-        <v>49.6</v>
+        <v>48.8</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4</v>
+        <v>0.18</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.67</v>
+        <v>-1.72</v>
       </c>
       <c r="U2" t="n">
         <v>54.1</v>
       </c>
       <c r="V2" t="n">
-        <v>2.42</v>
+        <v>3.01</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>115.71</v>
+        <v>3309.59</v>
       </c>
       <c r="Y2" t="n">
-        <v>111.63</v>
+        <v>3209.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>108.24</v>
+        <v>2662.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>115.28</v>
+        <v>3276.94</v>
       </c>
       <c r="AB2" t="n">
-        <v>117.94</v>
+        <v>3413.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>119.27</v>
+        <v>3475.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>120.23</v>
+        <v>3522.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>50</v>
+        <v>65.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.12</v>
+        <v>0.06</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Strong RSI | Low VIX (11.4) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.1</v>
+        <v>54.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-6.4</v>
+        <v>85.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>38.1</v>
+        <v>55.6</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>121.42</v>
+        <v>3569.49</v>
       </c>
       <c r="AN2" t="n">
-        <v>115.1</v>
+        <v>3309.67</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹135,961.52 Cr., a P/E ratio of 6.09, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 54.93, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.00 (Consolidation Zone), while MACD Line (0.70) trades below Signal (0.74) with an expanding histogram (-0.04). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.18% above the 200-day DMA (₹112.31). Daily volatility envelope is bounded by ATR(14) of ₹2.01.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.23 (Bullish Momentum Zone), while MACD Line (60.07) trades below Signal (74.14) with an expanding histogram (-14.07). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +24.03% above the 200-day DMA (₹2720.40). Daily volatility envelope is bounded by ATR(14) of ₹101.04.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹118.30) is positioned above the 30-day DMA (₹116.58), 50-day DMA (₹114.50), and 200-day DMA (₹112.31). The price distance from 200 DMA is +4.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,428.50) is positioned above the 30-day DMA (₹3,220.73), 50-day DMA (₹3,026.70), and 200-day DMA (₹2,720.40). The price distance from 200 DMA is +24.03%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[118.3, 119.52, 120.73, 121.95, 123.16, 124.38]</t>
+          <t>[3428.5, 3438.79, 3449.07, 3459.36, 3469.64, 3479.93]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[118.3, 120.32, 121.87, 123.34, 124.77, 126.18]</t>
+          <t>[3428.5, 3479.2, 3506.23, 3529.36, 3550.48, 3570.3]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[118.3, 118.91, 119.88, 120.9, 121.95, 123.03]</t>
+          <t>[3428.5, 3408.47, 3406.2, 3406.85, 3409.02, 3412.15]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>108.24</v>
+        <v>2662.45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>315422.8</v>
+        <v>62637.28</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,157 +845,157 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>342.65</v>
+        <v>1038.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹341.24 - ₹344.76</t>
+          <t>₹1033.55 - ₹1046.67</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>348.27</v>
+        <v>1059.79</v>
       </c>
       <c r="I3" t="n">
-        <v>324.14</v>
+        <v>997.08</v>
       </c>
       <c r="J3" t="n">
-        <v>314.78</v>
+        <v>957.75</v>
       </c>
       <c r="K3" t="n">
-        <v>275.03</v>
+        <v>852.74</v>
       </c>
       <c r="L3" t="n">
-        <v>24.35</v>
+        <v>18.09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.33</v>
+        <v>10.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.55</v>
+        <v>17.14</v>
       </c>
       <c r="O3" t="n">
-        <v>0.77</v>
+        <v>-7.09</v>
       </c>
       <c r="P3" t="n">
-        <v>7.03</v>
+        <v>26.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.35</v>
+        <v>11.4</v>
       </c>
       <c r="R3" t="n">
-        <v>49.1</v>
+        <v>47</v>
       </c>
       <c r="S3" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.06</v>
+        <v>-1.3</v>
       </c>
       <c r="U3" t="n">
-        <v>55.7</v>
+        <v>51.7</v>
       </c>
       <c r="V3" t="n">
-        <v>2.73</v>
+        <v>3.63</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>333.79</v>
+        <v>1017.68</v>
       </c>
       <c r="Y3" t="n">
-        <v>323.56</v>
+        <v>986.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>316.85</v>
+        <v>921.59</v>
       </c>
       <c r="AA3" t="n">
-        <v>332.11</v>
+        <v>999.4400000000001</v>
       </c>
       <c r="AB3" t="n">
-        <v>342.53</v>
+        <v>1035.43</v>
       </c>
       <c r="AC3" t="n">
-        <v>344.51</v>
+        <v>1048.26</v>
       </c>
       <c r="AD3" t="n">
-        <v>346.38</v>
+        <v>1057.73</v>
       </c>
       <c r="AE3" t="n">
-        <v>65.90000000000001</v>
+        <v>47.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (10.35) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (11.4) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>761.4</v>
+        <v>32.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>182</v>
+        <v>23.9</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.6</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>354.68</v>
+        <v>1076.77</v>
       </c>
       <c r="AN3" t="n">
-        <v>330.84</v>
+        <v>999.2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹315,422.80 Cr., a P/E ratio of 761.44, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹62,637.28 Cr., a P/E ratio of 32.22, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.91 (Bullish Momentum Zone), while MACD Line (4.33) trades above Signal (3.55) with an expanding histogram (+0.77). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +24.35% above the 200-day DMA (₹275.03). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 47.46 (Consolidation Zone), while MACD Line (10.06) trades below Signal (17.14) with an expanding histogram (-7.09). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.09% above the 200-day DMA (₹852.74). Daily volatility envelope is bounded by ATR(14) of ₹26.24.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹342.65) is positioned above the 30-day DMA (₹324.14), 50-day DMA (₹314.78), and 200-day DMA (₹275.03). The price distance from 200 DMA is +24.35%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,038.80) is positioned above the 30-day DMA (₹997.08), 50-day DMA (₹957.75), and 200-day DMA (₹852.74). The price distance from 200 DMA is +18.09%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[342.65, 344.78, 346.91, 349.04, 351.16, 353.29]</t>
+          <t>[1038.8, 1051.09, 1063.37, 1075.66, 1087.94, 1100.23]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[342.65, 347.59, 350.88, 353.9, 356.78, 359.58]</t>
+          <t>[1038.8, 1061.58, 1078.22, 1093.84, 1108.94, 1123.7]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[342.65, 342.67, 343.93, 345.39, 346.95, 348.58]</t>
+          <t>[1038.8, 1043.21, 1052.24, 1062.02, 1072.2, 1082.62]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>316.85</v>
+        <v>921.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>25000</v>
+        <v>124492.92</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,333 +1012,333 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3374</v>
+        <v>11186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹3353.42 - ₹3404.88</t>
+          <t>₹11146.91 - ₹11244.63</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3456.34</v>
+        <v>11342.35</v>
       </c>
       <c r="I4" t="n">
-        <v>3207.03</v>
+        <v>11192.21</v>
       </c>
       <c r="J4" t="n">
-        <v>3016.93</v>
+        <v>11069.59</v>
       </c>
       <c r="K4" t="n">
-        <v>2713.68</v>
+        <v>10528.34</v>
       </c>
       <c r="L4" t="n">
-        <v>20.23</v>
+        <v>6.24</v>
       </c>
       <c r="M4" t="n">
-        <v>54.17</v>
+        <v>7.66</v>
       </c>
       <c r="N4" t="n">
-        <v>77.66</v>
+        <v>-7.28</v>
       </c>
       <c r="O4" t="n">
-        <v>-23.49</v>
+        <v>14.94</v>
       </c>
       <c r="P4" t="n">
-        <v>102.92</v>
+        <v>195.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.35</v>
+        <v>11.4</v>
       </c>
       <c r="R4" t="n">
-        <v>48.4</v>
+        <v>45.8</v>
       </c>
       <c r="S4" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.65</v>
+        <v>-0.95</v>
       </c>
       <c r="U4" t="n">
-        <v>54.1</v>
+        <v>51.7</v>
       </c>
       <c r="V4" t="n">
-        <v>2.98</v>
+        <v>4.18</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>3303.32</v>
+        <v>10828.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>3201.48</v>
+        <v>10498.97</v>
       </c>
       <c r="Z4" t="n">
-        <v>2628.44</v>
+        <v>10116.71</v>
       </c>
       <c r="AA4" t="n">
-        <v>3219.62</v>
+        <v>10892.84</v>
       </c>
       <c r="AB4" t="n">
-        <v>3328.5</v>
+        <v>11252.33</v>
       </c>
       <c r="AC4" t="n">
-        <v>3419.5</v>
+        <v>11323.66</v>
       </c>
       <c r="AD4" t="n">
-        <v>3465</v>
+        <v>11461.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>48.3</v>
+        <v>54.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
+          <t>Low VIX (11.4) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>54.1</v>
+        <v>14.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>85.3</v>
+        <v>24.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>55.6</v>
+        <v>734.6</v>
       </c>
       <c r="AL4" t="n">
-        <v>15</v>
+        <v>11.6</v>
       </c>
       <c r="AM4" t="n">
-        <v>3519.7</v>
+        <v>11500.65</v>
       </c>
       <c r="AN4" t="n">
-        <v>3252.41</v>
+        <v>10862.25</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 54.05, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹124,492.92 Cr., a P/E ratio of 14.07, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.26 (Consolidation Zone), while MACD Line (54.17) trades below Signal (77.66) with an expanding histogram (-23.49). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.23% above the 200-day DMA (₹2713.68). Daily volatility envelope is bounded by ATR(14) of ₹102.92.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.69 (Consolidation Zone), while MACD Line (7.66) trades above Signal (-7.28) with an expanding histogram (+14.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.24% above the 200-day DMA (₹10528.34). Daily volatility envelope is bounded by ATR(14) of ₹195.44.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,374.00) is positioned above the 30-day DMA (₹3,207.03), 50-day DMA (₹3,016.93), and 200-day DMA (₹2,713.68). The price distance from 200 DMA is +20.23%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,186.00) is positioned above the 30-day DMA (₹11,192.21), 50-day DMA (₹11,069.59), and 200-day DMA (₹10,528.34). The price distance from 200 DMA is +6.24%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[3374.0, 3411.78, 3449.56, 3487.34, 3525.12, 3562.9]</t>
+          <t>[11186.0, 11219.56, 11253.12, 11286.67, 11320.23, 11353.79]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[3374.0, 3452.95, 3507.78, 3558.65, 3607.46, 3654.95]</t>
+          <t>[11186.0, 11297.73, 11363.67, 11422.08, 11476.58, 11528.6]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[3374.0, 3380.9, 3405.89, 3433.86, 3463.37, 3493.86]</t>
+          <t>[11186.0, 11160.93, 11170.2, 11185.12, 11202.97, 11222.68]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2628.44</v>
+        <v>10116.71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>87165.89999999999</v>
+        <v>60784.97</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1886.3</v>
+        <v>2189.2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹1874.54 - ₹1903.94</t>
+          <t>₹2175.88 - ₹2209.18</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1933.33</v>
+        <v>2242.49</v>
       </c>
       <c r="I5" t="n">
-        <v>1795.75</v>
+        <v>2155.41</v>
       </c>
       <c r="J5" t="n">
-        <v>1715.08</v>
+        <v>2041.41</v>
       </c>
       <c r="K5" t="n">
-        <v>1650.21</v>
+        <v>1965.75</v>
       </c>
       <c r="L5" t="n">
-        <v>9.380000000000001</v>
+        <v>11.66</v>
       </c>
       <c r="M5" t="n">
-        <v>12.72</v>
+        <v>34.42</v>
       </c>
       <c r="N5" t="n">
-        <v>22.42</v>
+        <v>42.65</v>
       </c>
       <c r="O5" t="n">
-        <v>-9.710000000000001</v>
+        <v>-8.23</v>
       </c>
       <c r="P5" t="n">
-        <v>58.79</v>
+        <v>66.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>10.35</v>
+        <v>11.4</v>
       </c>
       <c r="R5" t="n">
-        <v>47.6</v>
+        <v>43.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.9</v>
+        <v>-2.07</v>
       </c>
       <c r="U5" t="n">
-        <v>53.3</v>
+        <v>55</v>
       </c>
       <c r="V5" t="n">
-        <v>5.63</v>
+        <v>3.37</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>1784.5</v>
+        <v>2072.97</v>
       </c>
       <c r="Y5" t="n">
-        <v>1657.65</v>
+        <v>2024.68</v>
       </c>
       <c r="Z5" t="n">
-        <v>1657.65</v>
+        <v>2024.68</v>
       </c>
       <c r="AA5" t="n">
-        <v>1798.11</v>
+        <v>2089.29</v>
       </c>
       <c r="AB5" t="n">
-        <v>1861.4</v>
+        <v>2179.13</v>
       </c>
       <c r="AC5" t="n">
-        <v>1929.8</v>
+        <v>2200.06</v>
       </c>
       <c r="AD5" t="n">
-        <v>1973.3</v>
+        <v>2210.93</v>
       </c>
       <c r="AE5" t="n">
-        <v>44.9</v>
+        <v>49.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.4) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>117.5</v>
+        <v>49.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>40.1</v>
+        <v>8.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>10.2</v>
+        <v>5.2</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1952.37</v>
+        <v>2254.15</v>
       </c>
       <c r="AN5" t="n">
-        <v>1822.75</v>
+        <v>2129.42</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>POLICYBZR operates in the Financial Services sector. With an estimated Market Cap of ₹87,165.90 Cr., a P/E ratio of 117.45, and YoY Revenue Growth of +40.1%, the company demonstrates strong institutional backing, solid operating profit margins (10.20%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,784.97 Cr., a P/E ratio of 49.44, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.87 (Consolidation Zone), while MACD Line (12.72) trades below Signal (22.42) with an expanding histogram (-9.71). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.38% above the 200-day DMA (₹1650.21). Daily volatility envelope is bounded by ATR(14) of ₹58.79.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.43 (Consolidation Zone), while MACD Line (34.42) trades below Signal (42.65) with an expanding histogram (-8.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.66% above the 200-day DMA (₹1965.75). Daily volatility envelope is bounded by ATR(14) of ₹66.61.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for POLICYBZR. Current Market Price (₹1,886.30) is positioned above the 30-day DMA (₹1,795.75), 50-day DMA (₹1,715.08), and 200-day DMA (₹1,650.21). The price distance from 200 DMA is +9.38%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,189.20) is positioned above the 30-day DMA (₹2,155.41), 50-day DMA (₹2,041.41), and 200-day DMA (₹1,965.75). The price distance from 200 DMA is +11.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[1886.3, 1891.96, 1897.62, 1903.28, 1908.94, 1914.59]</t>
+          <t>[2189.2, 2195.77, 2202.34, 2208.9, 2215.47, 2222.04]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[1886.3, 1915.48, 1930.88, 1944.01, 1955.97, 1967.18]</t>
+          <t>[2189.2, 2222.41, 2240.01, 2255.05, 2268.76, 2281.61]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[1886.3, 1874.32, 1872.67, 1872.73, 1873.66, 1875.16]</t>
+          <t>[2189.2, 2175.79, 2174.08, 2174.29, 2175.51, 2177.36]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1657.65</v>
+        <v>2024.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31491.11</v>
+        <v>313903.91</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,166 +1346,166 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>572.5</v>
+        <v>341</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹568.95 - ₹577.83</t>
+          <t>₹339.64 - ₹343.04</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>586.7</v>
+        <v>346.45</v>
       </c>
       <c r="I6" t="n">
-        <v>530.77</v>
+        <v>325.09</v>
       </c>
       <c r="J6" t="n">
-        <v>526.84</v>
+        <v>315.74</v>
       </c>
       <c r="K6" t="n">
-        <v>524.0599999999999</v>
+        <v>275.32</v>
       </c>
       <c r="L6" t="n">
-        <v>7.81</v>
+        <v>24.46</v>
       </c>
       <c r="M6" t="n">
-        <v>10.36</v>
+        <v>5.25</v>
       </c>
       <c r="N6" t="n">
-        <v>9.960000000000001</v>
+        <v>3.89</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
-        <v>17.75</v>
+        <v>6.81</v>
       </c>
       <c r="Q6" t="n">
-        <v>10.35</v>
+        <v>11.4</v>
       </c>
       <c r="R6" t="n">
-        <v>44.2</v>
+        <v>42.8</v>
       </c>
       <c r="S6" t="n">
-        <v>0.17</v>
+        <v>0.27</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.08</v>
+        <v>-1.26</v>
       </c>
       <c r="U6" t="n">
-        <v>47.5</v>
+        <v>54.1</v>
       </c>
       <c r="V6" t="n">
-        <v>4.3</v>
+        <v>2.42</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>541.71</v>
+        <v>331.93</v>
       </c>
       <c r="Y6" t="n">
-        <v>518.01</v>
+        <v>321.75</v>
       </c>
       <c r="Z6" t="n">
-        <v>514.8200000000001</v>
+        <v>315.32</v>
       </c>
       <c r="AA6" t="n">
-        <v>545.87</v>
+        <v>330.78</v>
       </c>
       <c r="AB6" t="n">
-        <v>571.08</v>
+        <v>340.93</v>
       </c>
       <c r="AC6" t="n">
-        <v>578.11</v>
+        <v>343.66</v>
       </c>
       <c r="AD6" t="n">
-        <v>583.73</v>
+        <v>346.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>60.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.18</v>
+        <v>0.29</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (10.35) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.4) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.4</v>
+        <v>757.8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14.5</v>
+        <v>182</v>
       </c>
       <c r="AK6" t="n">
-        <v>65.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>587.4400000000001</v>
+        <v>353.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>558.09</v>
+        <v>330.15</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,491.11 Cr., a P/E ratio of 5.42, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹313,903.91 Cr., a P/E ratio of 757.78, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 60.50 (Bullish Momentum Zone), while MACD Line (10.36) trades above Signal (9.96) with an expanding histogram (+0.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.81% above the 200-day DMA (₹524.06). Daily volatility envelope is bounded by ATR(14) of ₹17.75.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.12 (Bullish Momentum Zone), while MACD Line (5.25) trades above Signal (3.89) with an expanding histogram (+1.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +24.46% above the 200-day DMA (₹275.32). Daily volatility envelope is bounded by ATR(14) of ₹6.81.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹572.50) is positioned above the 30-day DMA (₹530.77), 50-day DMA (₹526.84), and 200-day DMA (₹524.06). The price distance from 200 DMA is +7.81%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹341.00) is positioned above the 30-day DMA (₹325.09), 50-day DMA (₹315.74), and 200-day DMA (₹275.32). The price distance from 200 DMA is +24.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[572.5, 574.22, 575.94, 577.65, 579.37, 581.09]</t>
+          <t>[341.0, 342.85, 344.7, 346.56, 348.41, 350.26]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[572.5, 581.32, 585.98, 589.95, 593.57, 596.97]</t>
+          <t>[341.0, 345.58, 348.56, 351.28, 353.86, 356.35]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[572.5, 568.89, 568.4, 568.43, 568.72, 569.18]</t>
+          <t>[341.0, 340.81, 341.81, 343.02, 344.32, 345.69]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>514.8200000000001</v>
+        <v>315.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>107584.07</v>
+        <v>135179.99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1513,146 +1513,313 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>743.7</v>
+        <v>117.62</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>₹740.91 - ₹747.89</t>
+          <t>₹117.21 - ₹118.23</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>754.86</v>
+        <v>119.25</v>
       </c>
       <c r="I7" t="n">
-        <v>723.84</v>
+        <v>116.55</v>
       </c>
       <c r="J7" t="n">
-        <v>728.16</v>
+        <v>114.75</v>
       </c>
       <c r="K7" t="n">
-        <v>686.15</v>
+        <v>112.34</v>
       </c>
       <c r="L7" t="n">
-        <v>7.3</v>
+        <v>5.31</v>
       </c>
       <c r="M7" t="n">
-        <v>1.74</v>
+        <v>0.77</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.68</v>
+        <v>0.74</v>
       </c>
       <c r="O7" t="n">
-        <v>2.43</v>
+        <v>0.03</v>
       </c>
       <c r="P7" t="n">
-        <v>13.95</v>
+        <v>2.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>10.35</v>
+        <v>11.4</v>
       </c>
       <c r="R7" t="n">
-        <v>41.3</v>
+        <v>42.6</v>
       </c>
       <c r="S7" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.21</v>
+        <v>-1.03</v>
       </c>
       <c r="U7" t="n">
-        <v>45.9</v>
+        <v>52.5</v>
       </c>
       <c r="V7" t="n">
-        <v>11.66</v>
+        <v>2.36</v>
       </c>
       <c r="W7" t="n">
         <v>-0.77</v>
       </c>
       <c r="X7" t="n">
-        <v>719.71</v>
+        <v>114.85</v>
       </c>
       <c r="Y7" t="n">
-        <v>697.79</v>
+        <v>111.04</v>
       </c>
       <c r="Z7" t="n">
-        <v>672.71</v>
+        <v>107.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>722.77</v>
+        <v>114.56</v>
       </c>
       <c r="AB7" t="n">
-        <v>741.28</v>
+        <v>117.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>746.41</v>
+        <v>118.45</v>
       </c>
       <c r="AD7" t="n">
-        <v>749.13</v>
+        <v>119.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>55.2</v>
+        <v>57.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (10.35) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (11.4) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH7" t="n">
         <v>0.15</v>
       </c>
       <c r="AI7" t="n">
-        <v>48.8</v>
+        <v>6.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>15.1</v>
+        <v>-6.4</v>
       </c>
       <c r="AK7" t="n">
-        <v>20.9</v>
+        <v>38.1</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>762.89</v>
+        <v>121.24</v>
       </c>
       <c r="AN7" t="n">
-        <v>725.95</v>
+        <v>114.61</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>INDHOTEL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹107,584.07 Cr., a P/E ratio of 48.77, and YoY Revenue Growth of +15.1%, the company demonstrates strong institutional backing, solid operating profit margins (20.87%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹135,179.99 Cr., a P/E ratio of 6.05, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.22 (Bullish Momentum Zone), while MACD Line (1.74) trades above Signal (-0.68) with an expanding histogram (+2.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.30% above the 200-day DMA (₹686.15). Daily volatility envelope is bounded by ATR(14) of ₹13.95.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.91 (Bullish Momentum Zone), while MACD Line (0.77) trades above Signal (0.74) with an expanding histogram (+0.03). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.31% above the 200-day DMA (₹112.34). Daily volatility envelope is bounded by ATR(14) of ₹2.04.</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for INDHOTEL. Current Market Price (₹743.70) is positioned above the 30-day DMA (₹723.84), 50-day DMA (₹728.16), and 200-day DMA (₹686.15). The price distance from 200 DMA is +7.30%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.62) is positioned above the 30-day DMA (₹116.55), 50-day DMA (₹114.75), and 200-day DMA (₹112.34). The price distance from 200 DMA is +5.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>[743.7, 745.93, 748.16, 750.39, 752.62, 754.86]</t>
+          <t>[117.62, 118.62, 119.62, 120.62, 121.62, 122.62]</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>[743.7, 751.51, 756.06, 760.06, 763.79, 767.34]</t>
+          <t>[117.62, 119.44, 120.77, 122.03, 123.25, 124.44]</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>[743.7, 741.75, 742.24, 743.14, 744.25, 745.5]</t>
+          <t>[117.62, 118.01, 118.75, 119.56, 120.39, 121.25]</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>672.71</v>
+        <v>107.43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>31367.34</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>570.25</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>₹566.79 - ₹575.43</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>584.0700000000001</v>
+      </c>
+      <c r="I8" t="n">
+        <v>533.25</v>
+      </c>
+      <c r="J8" t="n">
+        <v>527.51</v>
+      </c>
+      <c r="K8" t="n">
+        <v>524.36</v>
+      </c>
+      <c r="L8" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="M8" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="P8" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="U8" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X8" t="n">
+        <v>540.0599999999999</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>513.73</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>512.79</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>544.34</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>569.02</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>572.9400000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>575.62</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>58.6</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.4) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>585.5599999999999</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>555.1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,367.34 Cr., a P/E ratio of 5.40, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.58 (Bullish Momentum Zone), while MACD Line (11.18) trades above Signal (10.20) with an expanding histogram (+0.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.18% above the 200-day DMA (₹524.36). Daily volatility envelope is bounded by ATR(14) of ₹17.28.</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹570.25) is positioned above the 30-day DMA (₹533.25), 50-day DMA (₹527.51), and 200-day DMA (₹524.36). The price distance from 200 DMA is +9.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>[570.25, 571.96, 573.67, 575.38, 577.09, 578.8]</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>[570.25, 578.87, 583.44, 587.35, 590.91, 594.25]</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>[570.25, 566.78, 566.34, 566.41, 566.73, 567.22]</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>512.79</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU8"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,163 +661,163 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25000</v>
+        <v>308840.94</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3428.5</v>
+        <v>335.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹3408.29 - ₹3458.81</t>
+          <t>₹334.14 - ₹337.54</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3509.33</v>
+        <v>340.95</v>
       </c>
       <c r="I2" t="n">
-        <v>3220.73</v>
+        <v>325.09</v>
       </c>
       <c r="J2" t="n">
-        <v>3026.7</v>
+        <v>315.74</v>
       </c>
       <c r="K2" t="n">
-        <v>2720.4</v>
+        <v>275.32</v>
       </c>
       <c r="L2" t="n">
-        <v>24.03</v>
+        <v>24.46</v>
       </c>
       <c r="M2" t="n">
-        <v>60.07</v>
+        <v>5.25</v>
       </c>
       <c r="N2" t="n">
-        <v>74.14</v>
+        <v>3.89</v>
       </c>
       <c r="O2" t="n">
-        <v>-14.07</v>
+        <v>1.36</v>
       </c>
       <c r="P2" t="n">
-        <v>101.04</v>
+        <v>6.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>11.4</v>
+        <v>12.69</v>
       </c>
       <c r="R2" t="n">
-        <v>48.8</v>
+        <v>42.7</v>
       </c>
       <c r="S2" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.72</v>
+        <v>-1.29</v>
       </c>
       <c r="U2" t="n">
         <v>54.1</v>
       </c>
       <c r="V2" t="n">
-        <v>3.01</v>
+        <v>2.43</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>3309.59</v>
+        <v>326.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>3209.1</v>
+        <v>316.21</v>
       </c>
       <c r="Z2" t="n">
-        <v>2662.45</v>
+        <v>310.23</v>
       </c>
       <c r="AA2" t="n">
-        <v>3276.94</v>
+        <v>325.28</v>
       </c>
       <c r="AB2" t="n">
-        <v>3413.2</v>
+        <v>337.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>3475.3</v>
+        <v>341.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>3522.1</v>
+        <v>347.6</v>
       </c>
       <c r="AE2" t="n">
-        <v>65.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Strong RSI | Low VIX (11.4) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.69) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>54.9</v>
+        <v>745.6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>85.3</v>
+        <v>182</v>
       </c>
       <c r="AK2" t="n">
-        <v>55.6</v>
+        <v>0.6</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>3569.49</v>
+        <v>347.04</v>
       </c>
       <c r="AN2" t="n">
-        <v>3309.67</v>
+        <v>324.18</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>MCX operates in the Financial Services sector. With an estimated Market Cap of ₹25,000.00 Cr., a P/E ratio of 54.93, and YoY Revenue Growth of +85.3%, the company demonstrates strong institutional backing, solid operating profit margins (55.56%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹308,840.94 Cr., a P/E ratio of 745.56, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.23 (Bullish Momentum Zone), while MACD Line (60.07) trades below Signal (74.14) with an expanding histogram (-14.07). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +24.03% above the 200-day DMA (₹2720.40). Daily volatility envelope is bounded by ATR(14) of ₹101.04.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.12 (Bullish Momentum Zone), while MACD Line (5.25) trades above Signal (3.89) with an expanding histogram (+1.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +24.46% above the 200-day DMA (₹275.32). Daily volatility envelope is bounded by ATR(14) of ₹6.81.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MCX. Current Market Price (₹3,428.50) is positioned above the 30-day DMA (₹3,220.73), 50-day DMA (₹3,026.70), and 200-day DMA (₹2,720.40). The price distance from 200 DMA is +24.03%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹335.50) is positioned above the 30-day DMA (₹325.09), 50-day DMA (₹315.74), and 200-day DMA (₹275.32). The price distance from 200 DMA is +24.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[3428.5, 3438.79, 3449.07, 3459.36, 3469.64, 3479.93]</t>
+          <t>[335.5, 336.94, 338.38, 339.82, 341.26, 342.7]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[3428.5, 3479.2, 3506.23, 3529.36, 3550.48, 3570.3]</t>
+          <t>[335.5, 339.66, 342.23, 344.54, 346.71, 348.79]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[3428.5, 3408.47, 3406.2, 3406.85, 3409.02, 3412.15]</t>
+          <t>[335.5, 334.9, 335.49, 336.28, 337.17, 338.13]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2662.45</v>
+        <v>310.23</v>
       </c>
     </row>
     <row r="3">
@@ -828,7 +828,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -837,154 +837,154 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>62637.28</v>
+        <v>134605.35</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1038.8</v>
+        <v>117.12</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹1033.55 - ₹1046.67</t>
+          <t>₹116.71 - ₹117.73</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1059.79</v>
+        <v>118.75</v>
       </c>
       <c r="I3" t="n">
-        <v>997.08</v>
+        <v>116.55</v>
       </c>
       <c r="J3" t="n">
-        <v>957.75</v>
+        <v>114.75</v>
       </c>
       <c r="K3" t="n">
-        <v>852.74</v>
+        <v>112.34</v>
       </c>
       <c r="L3" t="n">
-        <v>18.09</v>
+        <v>5.31</v>
       </c>
       <c r="M3" t="n">
-        <v>10.06</v>
+        <v>0.77</v>
       </c>
       <c r="N3" t="n">
-        <v>17.14</v>
+        <v>0.74</v>
       </c>
       <c r="O3" t="n">
-        <v>-7.09</v>
+        <v>0.03</v>
       </c>
       <c r="P3" t="n">
-        <v>26.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.4</v>
+        <v>12.69</v>
       </c>
       <c r="R3" t="n">
-        <v>47</v>
+        <v>42.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3</v>
+        <v>-1.05</v>
       </c>
       <c r="U3" t="n">
-        <v>51.7</v>
+        <v>52.5</v>
       </c>
       <c r="V3" t="n">
-        <v>3.63</v>
+        <v>2.36</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>1017.68</v>
+        <v>114.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>986.28</v>
+        <v>110.58</v>
       </c>
       <c r="Z3" t="n">
-        <v>921.59</v>
+        <v>106.94</v>
       </c>
       <c r="AA3" t="n">
-        <v>999.4400000000001</v>
+        <v>114.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1035.43</v>
+        <v>117.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>1048.26</v>
+        <v>118.18</v>
       </c>
       <c r="AD3" t="n">
-        <v>1057.73</v>
+        <v>119.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>47.5</v>
+        <v>57.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.25</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (11.4) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.69) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>32.2</v>
+        <v>6.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>23.9</v>
+        <v>-6.4</v>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>38.1</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>1076.77</v>
+        <v>120.1</v>
       </c>
       <c r="AN3" t="n">
-        <v>999.2</v>
+        <v>113.92</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹62,637.28 Cr., a P/E ratio of 32.22, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,605.35 Cr., a P/E ratio of 6.09, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 47.46 (Consolidation Zone), while MACD Line (10.06) trades below Signal (17.14) with an expanding histogram (-7.09). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.09% above the 200-day DMA (₹852.74). Daily volatility envelope is bounded by ATR(14) of ₹26.24.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.91 (Bullish Momentum Zone), while MACD Line (0.77) trades above Signal (0.74) with an expanding histogram (+0.03). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.31% above the 200-day DMA (₹112.34). Daily volatility envelope is bounded by ATR(14) of ₹2.04.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,038.80) is positioned above the 30-day DMA (₹997.08), 50-day DMA (₹957.75), and 200-day DMA (₹852.74). The price distance from 200 DMA is +18.09%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.12) is positioned above the 30-day DMA (₹116.55), 50-day DMA (₹114.75), and 200-day DMA (₹112.34). The price distance from 200 DMA is +5.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[1038.8, 1051.09, 1063.37, 1075.66, 1087.94, 1100.23]</t>
+          <t>[117.12, 118.08, 119.05, 120.01, 120.98, 121.94]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[1038.8, 1061.58, 1078.22, 1093.84, 1108.94, 1123.7]</t>
+          <t>[117.12, 118.9, 120.2, 121.43, 122.61, 123.77]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[1038.8, 1043.21, 1052.24, 1062.02, 1072.2, 1082.62]</t>
+          <t>[117.12, 117.47, 118.18, 118.95, 119.76, 120.58]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>921.59</v>
+        <v>106.94</v>
       </c>
     </row>
     <row r="4">
@@ -995,163 +995,163 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>124492.92</v>
+        <v>60662.81</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>11186</v>
+        <v>2184.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹11146.91 - ₹11244.63</t>
+          <t>₹2172.47 - ₹2203.3</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11342.35</v>
+        <v>2234.14</v>
       </c>
       <c r="I4" t="n">
-        <v>11192.21</v>
+        <v>2162.26</v>
       </c>
       <c r="J4" t="n">
-        <v>11069.59</v>
+        <v>2049.1</v>
       </c>
       <c r="K4" t="n">
-        <v>10528.34</v>
+        <v>1968.08</v>
       </c>
       <c r="L4" t="n">
-        <v>6.24</v>
+        <v>11.53</v>
       </c>
       <c r="M4" t="n">
-        <v>7.66</v>
+        <v>33.25</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.28</v>
+        <v>40.77</v>
       </c>
       <c r="O4" t="n">
-        <v>14.94</v>
+        <v>-7.52</v>
       </c>
       <c r="P4" t="n">
-        <v>195.44</v>
+        <v>61.67</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.4</v>
+        <v>12.69</v>
       </c>
       <c r="R4" t="n">
-        <v>45.8</v>
+        <v>42</v>
       </c>
       <c r="S4" t="n">
-        <v>0.31</v>
+        <v>0.19</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.95</v>
+        <v>-1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>51.7</v>
+        <v>54.1</v>
       </c>
       <c r="V4" t="n">
-        <v>4.18</v>
+        <v>3.51</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>10828.8</v>
+        <v>2074.47</v>
       </c>
       <c r="Y4" t="n">
-        <v>10498.97</v>
+        <v>2020.61</v>
       </c>
       <c r="Z4" t="n">
-        <v>10116.71</v>
+        <v>2020.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>10892.84</v>
+        <v>2092.29</v>
       </c>
       <c r="AB4" t="n">
-        <v>11252.33</v>
+        <v>2182.63</v>
       </c>
       <c r="AC4" t="n">
-        <v>11323.66</v>
+        <v>2207.06</v>
       </c>
       <c r="AD4" t="n">
-        <v>11461.33</v>
+        <v>2229.33</v>
       </c>
       <c r="AE4" t="n">
-        <v>54.7</v>
+        <v>54.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Low VIX (11.4) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.69) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>14.1</v>
+        <v>49.3</v>
       </c>
       <c r="AJ4" t="n">
-        <v>24.2</v>
+        <v>8.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>734.6</v>
+        <v>5.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>11500.65</v>
+        <v>2252.13</v>
       </c>
       <c r="AN4" t="n">
-        <v>10862.25</v>
+        <v>2119.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG operates in the Financial Services sector. With an estimated Market Cap of ₹124,492.92 Cr., a P/E ratio of 14.07, and YoY Revenue Growth of +24.2%, the company demonstrates strong institutional backing, solid operating profit margins (734.64%), and healthy Return on Equity (11.60%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,662.81 Cr., a P/E ratio of 49.27, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.69 (Consolidation Zone), while MACD Line (7.66) trades above Signal (-7.28) with an expanding histogram (+14.94). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.24% above the 200-day DMA (₹10528.34). Daily volatility envelope is bounded by ATR(14) of ₹195.44.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.22 (Consolidation Zone), while MACD Line (33.25) trades below Signal (40.77) with an expanding histogram (-7.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.53% above the 200-day DMA (₹1968.08). Daily volatility envelope is bounded by ATR(14) of ₹61.67.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BAJAJHLDNG. Current Market Price (₹11,186.00) is positioned above the 30-day DMA (₹11,192.21), 50-day DMA (₹11,069.59), and 200-day DMA (₹10,528.34). The price distance from 200 DMA is +6.24%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,184.80) is positioned above the 30-day DMA (₹2,162.26), 50-day DMA (₹2,049.10), and 200-day DMA (₹1,968.08). The price distance from 200 DMA is +11.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[11186.0, 11219.56, 11253.12, 11286.67, 11320.23, 11353.79]</t>
+          <t>[2184.8, 2191.35, 2197.91, 2204.46, 2211.02, 2217.57]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[11186.0, 11297.73, 11363.67, 11422.08, 11476.58, 11528.6]</t>
+          <t>[2184.8, 2216.02, 2232.79, 2247.19, 2260.35, 2272.73]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[11186.0, 11160.93, 11170.2, 11185.12, 11202.97, 11222.68]</t>
+          <t>[2184.8, 2172.85, 2171.74, 2172.42, 2174.02, 2176.2]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>10116.71</v>
+        <v>2020.61</v>
       </c>
     </row>
     <row r="5">
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>60784.97</v>
+        <v>61624.27</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,146 +1179,146 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2189.2</v>
+        <v>1022</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹2175.88 - ₹2209.18</t>
+          <t>₹1016.4 - ₹1030.4</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2242.49</v>
+        <v>1044.4</v>
       </c>
       <c r="I5" t="n">
-        <v>2155.41</v>
+        <v>1001.8</v>
       </c>
       <c r="J5" t="n">
-        <v>2041.41</v>
+        <v>959.25</v>
       </c>
       <c r="K5" t="n">
-        <v>1965.75</v>
+        <v>853.76</v>
       </c>
       <c r="L5" t="n">
-        <v>11.66</v>
+        <v>22.11</v>
       </c>
       <c r="M5" t="n">
-        <v>34.42</v>
+        <v>12.21</v>
       </c>
       <c r="N5" t="n">
-        <v>42.65</v>
+        <v>16.16</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.23</v>
+        <v>-3.95</v>
       </c>
       <c r="P5" t="n">
-        <v>66.61</v>
+        <v>28</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.4</v>
+        <v>12.69</v>
       </c>
       <c r="R5" t="n">
-        <v>43.5</v>
+        <v>41</v>
       </c>
       <c r="S5" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.07</v>
+        <v>-1.95</v>
       </c>
       <c r="U5" t="n">
-        <v>55</v>
+        <v>50.8</v>
       </c>
       <c r="V5" t="n">
-        <v>3.37</v>
+        <v>3.62</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>2072.97</v>
+        <v>994.59</v>
       </c>
       <c r="Y5" t="n">
-        <v>2024.68</v>
+        <v>964.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>2024.68</v>
+        <v>903.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>2089.29</v>
+        <v>980</v>
       </c>
       <c r="AB5" t="n">
-        <v>2179.13</v>
+        <v>1026.97</v>
       </c>
       <c r="AC5" t="n">
-        <v>2200.06</v>
+        <v>1039.94</v>
       </c>
       <c r="AD5" t="n">
-        <v>2210.93</v>
+        <v>1057.87</v>
       </c>
       <c r="AE5" t="n">
-        <v>49.4</v>
+        <v>56.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.4) | LSTM Deep Net</t>
+          <t>Vol Spike 2.8x | Inst. Buying (CMF+) | Low VIX (12.69) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>49.4</v>
+        <v>31.7</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8.5</v>
+        <v>23.9</v>
       </c>
       <c r="AK5" t="n">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>2254.15</v>
+        <v>1060.75</v>
       </c>
       <c r="AN5" t="n">
-        <v>2129.42</v>
+        <v>979.61</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,784.97 Cr., a P/E ratio of 49.44, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹61,624.27 Cr., a P/E ratio of 31.70, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.43 (Consolidation Zone), while MACD Line (34.42) trades below Signal (42.65) with an expanding histogram (-8.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.66% above the 200-day DMA (₹1965.75). Daily volatility envelope is bounded by ATR(14) of ₹66.61.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.20 (Bullish Momentum Zone), while MACD Line (12.21) trades below Signal (16.16) with an expanding histogram (-3.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +22.11% above the 200-day DMA (₹853.76). Daily volatility envelope is bounded by ATR(14) of ₹28.00.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,189.20) is positioned above the 30-day DMA (₹2,155.41), 50-day DMA (₹2,041.41), and 200-day DMA (₹1,965.75). The price distance from 200 DMA is +11.66%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,022.00) is positioned above the 30-day DMA (₹1,001.80), 50-day DMA (₹959.25), and 200-day DMA (₹853.76). The price distance from 200 DMA is +22.11%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[2189.2, 2195.77, 2202.34, 2208.9, 2215.47, 2222.04]</t>
+          <t>[1022.0, 1027.34, 1032.67, 1038.01, 1043.35, 1048.69]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[2189.2, 2222.41, 2240.01, 2255.05, 2268.76, 2281.61]</t>
+          <t>[1022.0, 1038.54, 1048.51, 1057.41, 1065.75, 1073.73]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[2189.2, 2175.79, 2174.08, 2174.29, 2175.51, 2177.36]</t>
+          <t>[1022.0, 1018.94, 1020.8, 1023.46, 1026.55, 1029.9]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>2024.68</v>
+        <v>903.25</v>
       </c>
     </row>
     <row r="6">
@@ -1329,16 +1329,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>313903.91</v>
+        <v>31037.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,480 +1346,146 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>341</v>
+        <v>564.25</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹339.64 - ₹343.04</t>
+          <t>₹560.79 - ₹569.43</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>346.45</v>
+        <v>578.0700000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>325.09</v>
+        <v>533.25</v>
       </c>
       <c r="J6" t="n">
-        <v>315.74</v>
+        <v>527.51</v>
       </c>
       <c r="K6" t="n">
-        <v>275.32</v>
+        <v>524.36</v>
       </c>
       <c r="L6" t="n">
-        <v>24.46</v>
+        <v>9.18</v>
       </c>
       <c r="M6" t="n">
-        <v>5.25</v>
+        <v>11.18</v>
       </c>
       <c r="N6" t="n">
-        <v>3.89</v>
+        <v>10.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>0.97</v>
       </c>
       <c r="P6" t="n">
-        <v>6.81</v>
+        <v>17.28</v>
       </c>
       <c r="Q6" t="n">
-        <v>11.4</v>
+        <v>12.69</v>
       </c>
       <c r="R6" t="n">
-        <v>42.8</v>
+        <v>37.5</v>
       </c>
       <c r="S6" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.26</v>
+        <v>-2.41</v>
       </c>
       <c r="U6" t="n">
-        <v>54.1</v>
+        <v>47.5</v>
       </c>
       <c r="V6" t="n">
-        <v>2.42</v>
+        <v>4.47</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>331.93</v>
+        <v>534.17</v>
       </c>
       <c r="Y6" t="n">
-        <v>321.75</v>
+        <v>507.47</v>
       </c>
       <c r="Z6" t="n">
-        <v>315.32</v>
+        <v>507.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>330.78</v>
+        <v>538.34</v>
       </c>
       <c r="AB6" t="n">
-        <v>340.93</v>
+        <v>566.65</v>
       </c>
       <c r="AC6" t="n">
-        <v>343.66</v>
+        <v>569.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>346.33</v>
+        <v>574.75</v>
       </c>
       <c r="AE6" t="n">
-        <v>70.09999999999999</v>
+        <v>58.6</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.29</v>
+        <v>0.13</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (11.4) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.69) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>757.8</v>
+        <v>5.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>182</v>
+        <v>14.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.6</v>
+        <v>65.2</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>353.3</v>
+        <v>577.73</v>
       </c>
       <c r="AN6" t="n">
-        <v>330.15</v>
+        <v>550.29</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹313,903.91 Cr., a P/E ratio of 757.78, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,037.30 Cr., a P/E ratio of 5.41, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.12 (Bullish Momentum Zone), while MACD Line (5.25) trades above Signal (3.89) with an expanding histogram (+1.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +24.46% above the 200-day DMA (₹275.32). Daily volatility envelope is bounded by ATR(14) of ₹6.81.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.58 (Bullish Momentum Zone), while MACD Line (11.18) trades above Signal (10.20) with an expanding histogram (+0.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.18% above the 200-day DMA (₹524.36). Daily volatility envelope is bounded by ATR(14) of ₹17.28.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹341.00) is positioned above the 30-day DMA (₹325.09), 50-day DMA (₹315.74), and 200-day DMA (₹275.32). The price distance from 200 DMA is +24.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹564.25) is positioned above the 30-day DMA (₹533.25), 50-day DMA (₹527.51), and 200-day DMA (₹524.36). The price distance from 200 DMA is +9.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[341.0, 342.85, 344.7, 346.56, 348.41, 350.26]</t>
+          <t>[564.25, 565.94, 567.64, 569.33, 571.02, 572.71]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[341.0, 345.58, 348.56, 351.28, 353.86, 356.35]</t>
+          <t>[564.25, 572.85, 577.41, 581.3, 584.84, 588.16]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[341.0, 340.81, 341.81, 343.02, 344.32, 345.69]</t>
+          <t>[564.25, 560.76, 560.31, 560.35, 560.66, 561.13]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>315.32</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>135179.99</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>117.62</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>₹117.21 - ₹118.23</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>119.25</v>
-      </c>
-      <c r="I7" t="n">
-        <v>116.55</v>
-      </c>
-      <c r="J7" t="n">
-        <v>114.75</v>
-      </c>
-      <c r="K7" t="n">
-        <v>112.34</v>
-      </c>
-      <c r="L7" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="T7" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="U7" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="W7" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X7" t="n">
-        <v>114.85</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>111.04</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>107.43</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>114.56</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>117.85</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>118.45</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>119.27</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>57.9</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>TTM Squeeze | Low VIX (11.4) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>121.24</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>114.61</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹135,179.99 Cr., a P/E ratio of 6.05, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.91 (Bullish Momentum Zone), while MACD Line (0.77) trades above Signal (0.74) with an expanding histogram (+0.03). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.31% above the 200-day DMA (₹112.34). Daily volatility envelope is bounded by ATR(14) of ₹2.04.</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.62) is positioned above the 30-day DMA (₹116.55), 50-day DMA (₹114.75), and 200-day DMA (₹112.34). The price distance from 200 DMA is +5.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>[117.62, 118.62, 119.62, 120.62, 121.62, 122.62]</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>[117.62, 119.44, 120.77, 122.03, 123.25, 124.44]</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>[117.62, 118.01, 118.75, 119.56, 120.39, 121.25]</t>
-        </is>
-      </c>
-      <c r="AU7" t="n">
-        <v>107.43</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>31367.34</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>570.25</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>₹566.79 - ₹575.43</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>584.0700000000001</v>
-      </c>
-      <c r="I8" t="n">
-        <v>533.25</v>
-      </c>
-      <c r="J8" t="n">
-        <v>527.51</v>
-      </c>
-      <c r="K8" t="n">
-        <v>524.36</v>
-      </c>
-      <c r="L8" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="M8" t="n">
-        <v>11.18</v>
-      </c>
-      <c r="N8" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="P8" t="n">
-        <v>17.28</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-2.37</v>
-      </c>
-      <c r="U8" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="V8" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="W8" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X8" t="n">
-        <v>540.0599999999999</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>513.73</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>512.79</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>544.34</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>569.02</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>572.9400000000001</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>575.62</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (11.4) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>585.5599999999999</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>555.1</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,367.34 Cr., a P/E ratio of 5.40, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.58 (Bullish Momentum Zone), while MACD Line (11.18) trades above Signal (10.20) with an expanding histogram (+0.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.18% above the 200-day DMA (₹524.36). Daily volatility envelope is bounded by ATR(14) of ₹17.28.</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹570.25) is positioned above the 30-day DMA (₹533.25), 50-day DMA (₹527.51), and 200-day DMA (₹524.36). The price distance from 200 DMA is +9.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>[570.25, 571.96, 573.67, 575.38, 577.09, 578.8]</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>[570.25, 578.87, 583.44, 587.35, 590.91, 594.25]</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>[570.25, 566.78, 566.34, 566.41, 566.73, 567.22]</t>
-        </is>
-      </c>
-      <c r="AU8" t="n">
-        <v>512.79</v>
+        <v>507.4</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU6"/>
+  <dimension ref="A1:AU5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>308840.94</v>
+        <v>134605.35</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>335.5</v>
+        <v>117.12</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹334.14 - ₹337.54</t>
+          <t>₹116.71 - ₹117.73</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>340.95</v>
+        <v>118.75</v>
       </c>
       <c r="I2" t="n">
-        <v>325.09</v>
+        <v>116.55</v>
       </c>
       <c r="J2" t="n">
-        <v>315.74</v>
+        <v>114.75</v>
       </c>
       <c r="K2" t="n">
-        <v>275.32</v>
+        <v>112.34</v>
       </c>
       <c r="L2" t="n">
-        <v>24.46</v>
+        <v>5.31</v>
       </c>
       <c r="M2" t="n">
-        <v>5.25</v>
+        <v>0.77</v>
       </c>
       <c r="N2" t="n">
-        <v>3.89</v>
+        <v>0.74</v>
       </c>
       <c r="O2" t="n">
-        <v>1.36</v>
+        <v>0.03</v>
       </c>
       <c r="P2" t="n">
-        <v>6.81</v>
+        <v>2.04</v>
       </c>
       <c r="Q2" t="n">
         <v>12.69</v>
       </c>
       <c r="R2" t="n">
-        <v>42.7</v>
+        <v>43</v>
       </c>
       <c r="S2" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.29</v>
+        <v>-1.03</v>
       </c>
       <c r="U2" t="n">
-        <v>54.1</v>
+        <v>52.5</v>
       </c>
       <c r="V2" t="n">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>326.2</v>
+        <v>117.12</v>
       </c>
       <c r="Y2" t="n">
-        <v>316.21</v>
+        <v>130.62</v>
       </c>
       <c r="Z2" t="n">
-        <v>310.23</v>
+        <v>130.62</v>
       </c>
       <c r="AA2" t="n">
-        <v>325.28</v>
+        <v>114.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>337.55</v>
+        <v>117.62</v>
       </c>
       <c r="AC2" t="n">
-        <v>341.55</v>
+        <v>118.18</v>
       </c>
       <c r="AD2" t="n">
-        <v>347.6</v>
+        <v>119.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>70.09999999999999</v>
+        <v>57.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.29</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.69) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.69) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>745.6</v>
+        <v>6.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>182</v>
+        <v>-6.4</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.6</v>
+        <v>38.1</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>347.04</v>
+        <v>120.32</v>
       </c>
       <c r="AN2" t="n">
-        <v>324.18</v>
+        <v>114.24</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹308,840.94 Cr., a P/E ratio of 745.56, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,605.35 Cr., a P/E ratio of 6.15, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.12 (Bullish Momentum Zone), while MACD Line (5.25) trades above Signal (3.89) with an expanding histogram (+1.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +24.46% above the 200-day DMA (₹275.32). Daily volatility envelope is bounded by ATR(14) of ₹6.81.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.91 (Bullish Momentum Zone), while MACD Line (0.77) trades above Signal (0.74) with an expanding histogram (+0.03). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.31% above the 200-day DMA (₹112.34). Daily volatility envelope is bounded by ATR(14) of ₹2.04.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹335.50) is positioned above the 30-day DMA (₹325.09), 50-day DMA (₹315.74), and 200-day DMA (₹275.32). The price distance from 200 DMA is +24.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.12) is positioned above the 30-day DMA (₹116.55), 50-day DMA (₹114.75), and 200-day DMA (₹112.34). The price distance from 200 DMA is +5.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[335.5, 336.94, 338.38, 339.82, 341.26, 342.7]</t>
+          <t>[117.12, 118.08, 119.05, 120.01, 120.98, 121.94]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[335.5, 339.66, 342.23, 344.54, 346.71, 348.79]</t>
+          <t>[117.12, 118.9, 120.2, 121.43, 122.61, 123.77]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[335.5, 334.9, 335.49, 336.28, 337.17, 338.13]</t>
+          <t>[117.12, 117.47, 118.18, 118.95, 119.76, 120.58]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>310.23</v>
+        <v>130.62</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>134605.35</v>
+        <v>308840.94</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>117.12</v>
+        <v>335.5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹116.71 - ₹117.73</t>
+          <t>₹334.14 - ₹337.54</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>118.75</v>
+        <v>340.95</v>
       </c>
       <c r="I3" t="n">
-        <v>116.55</v>
+        <v>325.09</v>
       </c>
       <c r="J3" t="n">
-        <v>114.75</v>
+        <v>315.74</v>
       </c>
       <c r="K3" t="n">
-        <v>112.34</v>
+        <v>275.32</v>
       </c>
       <c r="L3" t="n">
-        <v>5.31</v>
+        <v>24.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0.77</v>
+        <v>5.25</v>
       </c>
       <c r="N3" t="n">
-        <v>0.74</v>
+        <v>3.89</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>2.04</v>
+        <v>6.81</v>
       </c>
       <c r="Q3" t="n">
         <v>12.69</v>
       </c>
       <c r="R3" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="S3" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.05</v>
+        <v>-1.29</v>
       </c>
       <c r="U3" t="n">
-        <v>52.5</v>
+        <v>54.1</v>
       </c>
       <c r="V3" t="n">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>114.33</v>
+        <v>335.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>110.58</v>
+        <v>373.52</v>
       </c>
       <c r="Z3" t="n">
-        <v>106.94</v>
+        <v>373.52</v>
       </c>
       <c r="AA3" t="n">
-        <v>114.06</v>
+        <v>325.28</v>
       </c>
       <c r="AB3" t="n">
-        <v>117.62</v>
+        <v>337.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>118.18</v>
+        <v>341.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>119.23</v>
+        <v>347.6</v>
       </c>
       <c r="AE3" t="n">
-        <v>57.9</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.29</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.69) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.69) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.1</v>
+        <v>762.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-6.4</v>
+        <v>182</v>
       </c>
       <c r="AK3" t="n">
-        <v>38.1</v>
+        <v>0.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>120.1</v>
+        <v>347.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>113.92</v>
+        <v>324.62</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,605.35 Cr., a P/E ratio of 6.09, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹308,840.94 Cr., a P/E ratio of 762.50, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.91 (Bullish Momentum Zone), while MACD Line (0.77) trades above Signal (0.74) with an expanding histogram (+0.03). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.31% above the 200-day DMA (₹112.34). Daily volatility envelope is bounded by ATR(14) of ₹2.04.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.12 (Bullish Momentum Zone), while MACD Line (5.25) trades above Signal (3.89) with an expanding histogram (+1.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +24.46% above the 200-day DMA (₹275.32). Daily volatility envelope is bounded by ATR(14) of ₹6.81.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.12) is positioned above the 30-day DMA (₹116.55), 50-day DMA (₹114.75), and 200-day DMA (₹112.34). The price distance from 200 DMA is +5.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹335.50) is positioned above the 30-day DMA (₹325.09), 50-day DMA (₹315.74), and 200-day DMA (₹275.32). The price distance from 200 DMA is +24.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[117.12, 118.08, 119.05, 120.01, 120.98, 121.94]</t>
+          <t>[335.5, 336.94, 338.38, 339.82, 341.26, 342.7]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[117.12, 118.9, 120.2, 121.43, 122.61, 123.77]</t>
+          <t>[335.5, 339.66, 342.23, 344.54, 346.71, 348.79]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[117.12, 117.47, 118.18, 118.95, 119.76, 120.58]</t>
+          <t>[335.5, 334.9, 335.49, 336.28, 337.17, 338.13]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>106.94</v>
+        <v>373.52</v>
       </c>
     </row>
     <row r="4">
@@ -1050,13 +1050,13 @@
         <v>12.69</v>
       </c>
       <c r="R4" t="n">
-        <v>42</v>
+        <v>42.6</v>
       </c>
       <c r="S4" t="n">
         <v>0.19</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.97</v>
+        <v>-1.94</v>
       </c>
       <c r="U4" t="n">
         <v>54.1</v>
@@ -1068,13 +1068,13 @@
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2074.47</v>
+        <v>2184.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>2020.61</v>
+        <v>2392.36</v>
       </c>
       <c r="Z4" t="n">
-        <v>2020.61</v>
+        <v>2392.36</v>
       </c>
       <c r="AA4" t="n">
         <v>2092.29</v>
@@ -1115,10 +1115,10 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>2252.13</v>
+        <v>2248.5</v>
       </c>
       <c r="AN4" t="n">
-        <v>2119.78</v>
+        <v>2120.89</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2020.61</v>
+        <v>2392.36</v>
       </c>
     </row>
     <row r="5">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61624.27</v>
+        <v>31037.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,313 +1179,146 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1022</v>
+        <v>564.25</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹1016.4 - ₹1030.4</t>
+          <t>₹560.79 - ₹569.43</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1044.4</v>
+        <v>578.0700000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>1001.8</v>
+        <v>533.25</v>
       </c>
       <c r="J5" t="n">
-        <v>959.25</v>
+        <v>527.51</v>
       </c>
       <c r="K5" t="n">
-        <v>853.76</v>
+        <v>524.36</v>
       </c>
       <c r="L5" t="n">
-        <v>22.11</v>
+        <v>9.18</v>
       </c>
       <c r="M5" t="n">
-        <v>12.21</v>
+        <v>11.18</v>
       </c>
       <c r="N5" t="n">
-        <v>16.16</v>
+        <v>10.2</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.95</v>
+        <v>0.97</v>
       </c>
       <c r="P5" t="n">
-        <v>28</v>
+        <v>17.28</v>
       </c>
       <c r="Q5" t="n">
         <v>12.69</v>
       </c>
       <c r="R5" t="n">
-        <v>41</v>
+        <v>37.9</v>
       </c>
       <c r="S5" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.95</v>
+        <v>-2.39</v>
       </c>
       <c r="U5" t="n">
-        <v>50.8</v>
+        <v>47.5</v>
       </c>
       <c r="V5" t="n">
-        <v>3.62</v>
+        <v>4.47</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>994.59</v>
+        <v>563.42</v>
       </c>
       <c r="Y5" t="n">
-        <v>964.13</v>
+        <v>641.73</v>
       </c>
       <c r="Z5" t="n">
-        <v>903.25</v>
+        <v>641.73</v>
       </c>
       <c r="AA5" t="n">
-        <v>980</v>
+        <v>538.34</v>
       </c>
       <c r="AB5" t="n">
-        <v>1026.97</v>
+        <v>566.65</v>
       </c>
       <c r="AC5" t="n">
-        <v>1039.94</v>
+        <v>569.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1057.87</v>
+        <v>574.75</v>
       </c>
       <c r="AE5" t="n">
-        <v>56.2</v>
+        <v>58.6</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Vol Spike 2.8x | Inst. Buying (CMF+) | Low VIX (12.69) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.69) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>31.7</v>
+        <v>5.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23.9</v>
+        <v>14.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>65.2</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1060.75</v>
+        <v>578.99</v>
       </c>
       <c r="AN5" t="n">
-        <v>979.61</v>
+        <v>549.34</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹61,624.27 Cr., a P/E ratio of 31.70, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,037.30 Cr., a P/E ratio of 5.49, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.20 (Bullish Momentum Zone), while MACD Line (12.21) trades below Signal (16.16) with an expanding histogram (-3.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +22.11% above the 200-day DMA (₹853.76). Daily volatility envelope is bounded by ATR(14) of ₹28.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.58 (Bullish Momentum Zone), while MACD Line (11.18) trades above Signal (10.20) with an expanding histogram (+0.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.18% above the 200-day DMA (₹524.36). Daily volatility envelope is bounded by ATR(14) of ₹17.28.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,022.00) is positioned above the 30-day DMA (₹1,001.80), 50-day DMA (₹959.25), and 200-day DMA (₹853.76). The price distance from 200 DMA is +22.11%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹564.25) is positioned above the 30-day DMA (₹533.25), 50-day DMA (₹527.51), and 200-day DMA (₹524.36). The price distance from 200 DMA is +9.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[1022.0, 1027.34, 1032.67, 1038.01, 1043.35, 1048.69]</t>
+          <t>[564.25, 565.94, 567.64, 569.33, 571.02, 572.71]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[1022.0, 1038.54, 1048.51, 1057.41, 1065.75, 1073.73]</t>
+          <t>[564.25, 572.85, 577.41, 581.3, 584.84, 588.16]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[1022.0, 1018.94, 1020.8, 1023.46, 1026.55, 1029.9]</t>
+          <t>[564.25, 560.76, 560.31, 560.35, 560.66, 561.13]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>903.25</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>31037.3</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>564.25</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>₹560.79 - ₹569.43</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>578.0700000000001</v>
-      </c>
-      <c r="I6" t="n">
-        <v>533.25</v>
-      </c>
-      <c r="J6" t="n">
-        <v>527.51</v>
-      </c>
-      <c r="K6" t="n">
-        <v>524.36</v>
-      </c>
-      <c r="L6" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="M6" t="n">
-        <v>11.18</v>
-      </c>
-      <c r="N6" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="P6" t="n">
-        <v>17.28</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="R6" t="n">
-        <v>37.5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-2.41</v>
-      </c>
-      <c r="U6" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X6" t="n">
-        <v>534.17</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>507.47</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>507.4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>538.34</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>566.65</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>569.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>574.75</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.69) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>577.73</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>550.29</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,037.30 Cr., a P/E ratio of 5.41, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.58 (Bullish Momentum Zone), while MACD Line (11.18) trades above Signal (10.20) with an expanding histogram (+0.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.18% above the 200-day DMA (₹524.36). Daily volatility envelope is bounded by ATR(14) of ₹17.28.</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹564.25) is positioned above the 30-day DMA (₹533.25), 50-day DMA (₹527.51), and 200-day DMA (₹524.36). The price distance from 200 DMA is +9.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>[564.25, 565.94, 567.64, 569.33, 571.02, 572.71]</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>[564.25, 572.85, 577.41, 581.3, 584.84, 588.16]</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>[564.25, 560.76, 560.31, 560.35, 560.66, 561.13]</t>
-        </is>
-      </c>
-      <c r="AU6" t="n">
-        <v>507.4</v>
+        <v>641.73</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,7 +656,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -670,106 +670,106 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>134605.35</v>
+        <v>134341.01</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>117.12</v>
+        <v>116.89</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹116.71 - ₹117.73</t>
+          <t>₹116.48 - ₹117.5</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>118.75</v>
+        <v>118.51</v>
       </c>
       <c r="I2" t="n">
-        <v>116.55</v>
+        <v>116.54</v>
       </c>
       <c r="J2" t="n">
-        <v>114.75</v>
+        <v>114.99</v>
       </c>
       <c r="K2" t="n">
-        <v>112.34</v>
+        <v>112.35</v>
       </c>
       <c r="L2" t="n">
-        <v>5.31</v>
+        <v>4.24</v>
       </c>
       <c r="M2" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="N2" t="n">
         <v>0.74</v>
       </c>
       <c r="O2" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.69</v>
+        <v>12.47</v>
       </c>
       <c r="R2" t="n">
-        <v>43</v>
+        <v>47.9</v>
       </c>
       <c r="S2" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.03</v>
+        <v>-0.75</v>
       </c>
       <c r="U2" t="n">
         <v>52.5</v>
       </c>
       <c r="V2" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>117.12</v>
+        <v>116.89</v>
       </c>
       <c r="Y2" t="n">
-        <v>130.62</v>
+        <v>130.65</v>
       </c>
       <c r="Z2" t="n">
-        <v>130.62</v>
+        <v>130.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>114.06</v>
+        <v>113.84</v>
       </c>
       <c r="AB2" t="n">
-        <v>117.62</v>
+        <v>117.07</v>
       </c>
       <c r="AC2" t="n">
-        <v>118.18</v>
+        <v>117.84</v>
       </c>
       <c r="AD2" t="n">
-        <v>119.23</v>
+        <v>118.78</v>
       </c>
       <c r="AE2" t="n">
-        <v>57.9</v>
+        <v>50.5</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.69) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.47) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AJ2" t="n">
         <v>-6.4</v>
@@ -781,230 +781,230 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>120.32</v>
+        <v>120.24</v>
       </c>
       <c r="AN2" t="n">
-        <v>114.24</v>
+        <v>113.78</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,605.35 Cr., a P/E ratio of 6.15, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,341.01 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.91 (Bullish Momentum Zone), while MACD Line (0.77) trades above Signal (0.74) with an expanding histogram (+0.03). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.31% above the 200-day DMA (₹112.34). Daily volatility envelope is bounded by ATR(14) of ₹2.04.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.46 (Consolidation Zone), while MACD Line (0.73) trades below Signal (0.74) with an expanding histogram (-0.01). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.24% above the 200-day DMA (₹112.35). Daily volatility envelope is bounded by ATR(14) of ₹2.03.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹117.12) is positioned above the 30-day DMA (₹116.55), 50-day DMA (₹114.75), and 200-day DMA (₹112.34). The price distance from 200 DMA is +5.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.89) is positioned above the 30-day DMA (₹116.54), 50-day DMA (₹114.99), and 200-day DMA (₹112.35). The price distance from 200 DMA is +4.24%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[117.12, 118.08, 119.05, 120.01, 120.98, 121.94]</t>
+          <t>[116.89, 118.1, 119.31, 120.51, 121.72, 122.93]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[117.12, 118.9, 120.2, 121.43, 122.61, 123.77]</t>
+          <t>[116.89, 118.91, 120.45, 121.92, 123.35, 124.75]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[117.12, 117.47, 118.18, 118.95, 119.76, 120.58]</t>
+          <t>[116.89, 117.49, 118.44, 119.46, 120.5, 121.57]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>130.62</v>
+        <v>130.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>308840.94</v>
+        <v>60996</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>335.5</v>
+        <v>2196.8</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹334.14 - ₹337.54</t>
+          <t>₹2185.66 - ₹2213.51</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>340.95</v>
+        <v>2241.37</v>
       </c>
       <c r="I3" t="n">
-        <v>325.09</v>
+        <v>2166.54</v>
       </c>
       <c r="J3" t="n">
-        <v>315.74</v>
+        <v>2057.09</v>
       </c>
       <c r="K3" t="n">
-        <v>275.32</v>
+        <v>1970.33</v>
       </c>
       <c r="L3" t="n">
-        <v>24.46</v>
+        <v>10.88</v>
       </c>
       <c r="M3" t="n">
-        <v>5.25</v>
+        <v>31.14</v>
       </c>
       <c r="N3" t="n">
-        <v>3.89</v>
+        <v>38.84</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>-7.71</v>
       </c>
       <c r="P3" t="n">
-        <v>6.81</v>
+        <v>55.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.69</v>
+        <v>12.47</v>
       </c>
       <c r="R3" t="n">
-        <v>42.7</v>
+        <v>47</v>
       </c>
       <c r="S3" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.29</v>
+        <v>-1.5</v>
       </c>
       <c r="U3" t="n">
         <v>54.1</v>
       </c>
       <c r="V3" t="n">
-        <v>2.43</v>
+        <v>4</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>335.5</v>
+        <v>2196.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>373.52</v>
+        <v>2405.49</v>
       </c>
       <c r="Z3" t="n">
-        <v>373.52</v>
+        <v>2405.49</v>
       </c>
       <c r="AA3" t="n">
-        <v>325.28</v>
+        <v>2113.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>337.55</v>
+        <v>2192.53</v>
       </c>
       <c r="AC3" t="n">
-        <v>341.55</v>
+        <v>2208.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>347.6</v>
+        <v>2220.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>70.09999999999999</v>
+        <v>43.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.29</v>
+        <v>0.13</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.69) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.47) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>762.5</v>
+        <v>49.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>182</v>
+        <v>8.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>347.08</v>
+        <v>2262.69</v>
       </c>
       <c r="AN3" t="n">
-        <v>324.62</v>
+        <v>2136.28</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹308,840.94 Cr., a P/E ratio of 762.50, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,996.00 Cr., a P/E ratio of 49.54, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.12 (Bullish Momentum Zone), while MACD Line (5.25) trades above Signal (3.89) with an expanding histogram (+1.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +24.46% above the 200-day DMA (₹275.32). Daily volatility envelope is bounded by ATR(14) of ₹6.81.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.57 (Consolidation Zone), while MACD Line (31.14) trades below Signal (38.84) with an expanding histogram (-7.71). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.88% above the 200-day DMA (₹1970.33). Daily volatility envelope is bounded by ATR(14) of ₹55.71.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹335.50) is positioned above the 30-day DMA (₹325.09), 50-day DMA (₹315.74), and 200-day DMA (₹275.32). The price distance from 200 DMA is +24.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,196.80) is positioned above the 30-day DMA (₹2,166.54), 50-day DMA (₹2,057.09), and 200-day DMA (₹1,970.33). The price distance from 200 DMA is +10.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[335.5, 336.94, 338.38, 339.82, 341.26, 342.7]</t>
+          <t>[2196.8, 2203.39, 2209.98, 2216.57, 2223.16, 2229.75]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[335.5, 339.66, 342.23, 344.54, 346.71, 348.79]</t>
+          <t>[2196.8, 2225.68, 2241.5, 2255.17, 2267.73, 2279.58]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[335.5, 334.9, 335.49, 336.28, 337.17, 338.13]</t>
+          <t>[2196.8, 2186.68, 2186.34, 2187.62, 2189.73, 2192.38]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>373.52</v>
+        <v>2405.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60662.81</v>
+        <v>306539.61</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,157 +1012,157 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2184.8</v>
+        <v>333</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹2172.47 - ₹2203.3</t>
+          <t>₹331.59 - ₹335.11</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2234.14</v>
+        <v>338.63</v>
       </c>
       <c r="I4" t="n">
-        <v>2162.26</v>
+        <v>325.68</v>
       </c>
       <c r="J4" t="n">
-        <v>2049.1</v>
+        <v>316.72</v>
       </c>
       <c r="K4" t="n">
-        <v>1968.08</v>
+        <v>275.54</v>
       </c>
       <c r="L4" t="n">
-        <v>11.53</v>
+        <v>21.76</v>
       </c>
       <c r="M4" t="n">
-        <v>33.25</v>
+        <v>5.34</v>
       </c>
       <c r="N4" t="n">
-        <v>40.77</v>
+        <v>4.18</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.52</v>
+        <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>61.67</v>
+        <v>7.03</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.69</v>
+        <v>12.47</v>
       </c>
       <c r="R4" t="n">
-        <v>42.6</v>
+        <v>43</v>
       </c>
       <c r="S4" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.94</v>
+        <v>-1.34</v>
       </c>
       <c r="U4" t="n">
         <v>54.1</v>
       </c>
       <c r="V4" t="n">
-        <v>3.51</v>
+        <v>2.48</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2184.8</v>
+        <v>333</v>
       </c>
       <c r="Y4" t="n">
-        <v>2392.36</v>
+        <v>370.74</v>
       </c>
       <c r="Z4" t="n">
-        <v>2392.36</v>
+        <v>370.74</v>
       </c>
       <c r="AA4" t="n">
-        <v>2092.29</v>
+        <v>322.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>2182.63</v>
+        <v>335.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>2207.06</v>
+        <v>337.89</v>
       </c>
       <c r="AD4" t="n">
-        <v>2229.33</v>
+        <v>342.77</v>
       </c>
       <c r="AE4" t="n">
-        <v>54.2</v>
+        <v>62.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.11</v>
+        <v>0.28</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.69) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.47) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>49.3</v>
+        <v>756.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8.5</v>
+        <v>182</v>
       </c>
       <c r="AK4" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>2248.5</v>
+        <v>344.32</v>
       </c>
       <c r="AN4" t="n">
-        <v>2120.89</v>
+        <v>322.09</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,662.81 Cr., a P/E ratio of 49.27, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹306,539.61 Cr., a P/E ratio of 756.82, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.22 (Consolidation Zone), while MACD Line (33.25) trades below Signal (40.77) with an expanding histogram (-7.52). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.53% above the 200-day DMA (₹1968.08). Daily volatility envelope is bounded by ATR(14) of ₹61.67.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.89 (Bullish Momentum Zone), while MACD Line (5.34) trades above Signal (4.18) with an expanding histogram (+1.16). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.76% above the 200-day DMA (₹275.54). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,184.80) is positioned above the 30-day DMA (₹2,162.26), 50-day DMA (₹2,049.10), and 200-day DMA (₹1,968.08). The price distance from 200 DMA is +11.53%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹333.00) is positioned above the 30-day DMA (₹325.68), 50-day DMA (₹316.72), and 200-day DMA (₹275.54). The price distance from 200 DMA is +21.76%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[2184.8, 2191.35, 2197.91, 2204.46, 2211.02, 2217.57]</t>
+          <t>[333.0, 334.0, 335.0, 336.0, 337.0, 337.99]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[2184.8, 2216.02, 2232.79, 2247.19, 2260.35, 2272.73]</t>
+          <t>[333.0, 336.81, 338.98, 340.87, 342.62, 344.28]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[2184.8, 2172.85, 2171.74, 2172.42, 2174.02, 2176.2]</t>
+          <t>[333.0, 331.89, 332.01, 332.34, 332.78, 333.28]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2392.36</v>
+        <v>370.74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31037.3</v>
+        <v>62365.94</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,146 +1179,313 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>564.25</v>
+        <v>1034.3</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹560.79 - ₹569.43</t>
+          <t>₹1028.7 - ₹1042.7</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>578.0700000000001</v>
+        <v>1056.7</v>
       </c>
       <c r="I5" t="n">
-        <v>533.25</v>
+        <v>1001.8</v>
       </c>
       <c r="J5" t="n">
-        <v>527.51</v>
+        <v>959.25</v>
       </c>
       <c r="K5" t="n">
-        <v>524.36</v>
+        <v>853.76</v>
       </c>
       <c r="L5" t="n">
-        <v>9.18</v>
+        <v>22.11</v>
       </c>
       <c r="M5" t="n">
-        <v>11.18</v>
+        <v>12.21</v>
       </c>
       <c r="N5" t="n">
-        <v>10.2</v>
+        <v>16.16</v>
       </c>
       <c r="O5" t="n">
-        <v>0.97</v>
+        <v>-3.95</v>
       </c>
       <c r="P5" t="n">
-        <v>17.28</v>
+        <v>28</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.69</v>
+        <v>12.47</v>
       </c>
       <c r="R5" t="n">
-        <v>37.9</v>
+        <v>40.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.39</v>
+        <v>-1.95</v>
       </c>
       <c r="U5" t="n">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="V5" t="n">
-        <v>4.47</v>
+        <v>3.48</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>563.42</v>
+        <v>1034.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>641.73</v>
+        <v>1203.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>641.73</v>
+        <v>1203.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>538.34</v>
+        <v>992.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>566.65</v>
+        <v>1033.57</v>
       </c>
       <c r="AC5" t="n">
-        <v>569.5</v>
+        <v>1047.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>574.75</v>
+        <v>1061.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>58.6</v>
+        <v>56.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.69) | LSTM Deep Net</t>
+          <t>Vol Spike 2.8x | Inst. Buying (CMF+) | Low VIX (12.47) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.5</v>
+        <v>32.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14.5</v>
+        <v>23.9</v>
       </c>
       <c r="AK5" t="n">
-        <v>65.2</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>578.99</v>
+        <v>1077.52</v>
       </c>
       <c r="AN5" t="n">
-        <v>549.34</v>
+        <v>992.78</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,037.30 Cr., a P/E ratio of 5.49, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹62,365.94 Cr., a P/E ratio of 32.11, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.58 (Bullish Momentum Zone), while MACD Line (11.18) trades above Signal (10.20) with an expanding histogram (+0.97). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.18% above the 200-day DMA (₹524.36). Daily volatility envelope is bounded by ATR(14) of ₹17.28.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.20 (Bullish Momentum Zone), while MACD Line (12.21) trades below Signal (16.16) with an expanding histogram (-3.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +22.11% above the 200-day DMA (₹853.76). Daily volatility envelope is bounded by ATR(14) of ₹28.00.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹564.25) is positioned above the 30-day DMA (₹533.25), 50-day DMA (₹527.51), and 200-day DMA (₹524.36). The price distance from 200 DMA is +9.18%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,034.30) is positioned above the 30-day DMA (₹1,001.80), 50-day DMA (₹959.25), and 200-day DMA (₹853.76). The price distance from 200 DMA is +22.11%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[564.25, 565.94, 567.64, 569.33, 571.02, 572.71]</t>
+          <t>[1034.3, 1042.0, 1049.69, 1057.39, 1065.09, 1072.79]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[564.25, 572.85, 577.41, 581.3, 584.84, 588.16]</t>
+          <t>[1034.3, 1053.2, 1065.53, 1076.79, 1087.49, 1097.83]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[564.25, 560.76, 560.31, 560.35, 560.66, 561.13]</t>
+          <t>[1034.3, 1033.6, 1037.82, 1042.84, 1048.29, 1054.0]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>641.73</v>
+        <v>1203.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>30905.29</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>561.85</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>₹558.63 - ₹566.67</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>574.72</v>
+      </c>
+      <c r="I6" t="n">
+        <v>535.66</v>
+      </c>
+      <c r="J6" t="n">
+        <v>528.0700000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>524.5700000000001</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P6" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>12.47</v>
+      </c>
+      <c r="R6" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X6" t="n">
+        <v>561.85</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>639</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>639</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>537.73</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>563.4299999999999</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>565.61</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>569.38</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>51</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.47) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>575.9299999999999</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>546.92</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,905.29 Cr., a P/E ratio of 5.46, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.02 (Consolidation Zone), while MACD Line (11.03) trades above Signal (10.37) with an expanding histogram (+0.66). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.56% above the 200-day DMA (₹524.57). Daily volatility envelope is bounded by ATR(14) of ₹16.08.</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹561.85) is positioned above the 30-day DMA (₹535.66), 50-day DMA (₹528.07), and 200-day DMA (₹524.57). The price distance from 200 DMA is +7.56%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>[561.85, 563.54, 565.22, 566.91, 568.59, 570.28]</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>[561.85, 569.97, 574.32, 578.05, 581.46, 584.66]</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>[561.85, 558.71, 558.4, 558.55, 558.94, 559.49]</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>639</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>134341.01</v>
+        <v>134007.71</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,15 +678,15 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>116.89</v>
+        <v>116.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹116.48 - ₹117.5</t>
+          <t>₹116.19 - ₹117.21</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>118.51</v>
+        <v>118.22</v>
       </c>
       <c r="I2" t="n">
         <v>116.54</v>
@@ -713,16 +713,16 @@
         <v>2.03</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.47</v>
+        <v>12.16</v>
       </c>
       <c r="R2" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.75</v>
+        <v>-0.76</v>
       </c>
       <c r="U2" t="n">
         <v>52.5</v>
@@ -734,25 +734,25 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>116.89</v>
+        <v>116.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>130.65</v>
+        <v>130.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>130.65</v>
+        <v>130.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>113.84</v>
+        <v>113.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>117.07</v>
+        <v>116.95</v>
       </c>
       <c r="AC2" t="n">
-        <v>117.84</v>
+        <v>117.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>118.78</v>
+        <v>118.73</v>
       </c>
       <c r="AE2" t="n">
         <v>50.5</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.47) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (12.16) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
@@ -781,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>120.24</v>
+        <v>119.9</v>
       </c>
       <c r="AN2" t="n">
-        <v>113.78</v>
+        <v>113.33</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,341.01 Cr., a P/E ratio of 6.14, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,007.71 Cr., a P/E ratio of 6.07, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -798,26 +798,26 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.89) is positioned above the 30-day DMA (₹116.54), 50-day DMA (₹114.99), and 200-day DMA (₹112.35). The price distance from 200 DMA is +4.24%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.60) is positioned above the 30-day DMA (₹116.54), 50-day DMA (₹114.99), and 200-day DMA (₹112.35). The price distance from 200 DMA is +4.24%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[116.89, 118.1, 119.31, 120.51, 121.72, 122.93]</t>
+          <t>[116.6, 117.79, 118.98, 120.17, 121.36, 122.54]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[116.89, 118.91, 120.45, 121.92, 123.35, 124.75]</t>
+          <t>[116.6, 118.6, 120.13, 121.57, 122.98, 124.36]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[116.89, 117.49, 118.44, 119.46, 120.5, 121.57]</t>
+          <t>[116.6, 117.18, 118.12, 119.11, 120.14, 121.18]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>130.65</v>
+        <v>130.3</v>
       </c>
     </row>
     <row r="3">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60996</v>
+        <v>61493.01</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,15 +845,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2196.8</v>
+        <v>2214.7</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹2185.66 - ₹2213.51</t>
+          <t>₹2203.56 - ₹2231.41</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2241.37</v>
+        <v>2259.27</v>
       </c>
       <c r="I3" t="n">
         <v>2166.54</v>
@@ -880,10 +880,10 @@
         <v>55.71</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.47</v>
+        <v>12.16</v>
       </c>
       <c r="R3" t="n">
-        <v>47</v>
+        <v>46.8</v>
       </c>
       <c r="S3" t="n">
         <v>0.21</v>
@@ -895,31 +895,31 @@
         <v>54.1</v>
       </c>
       <c r="V3" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>2196.8</v>
+        <v>2214.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>2405.49</v>
+        <v>2425.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>2405.49</v>
+        <v>2425.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2113.23</v>
+        <v>2131.13</v>
       </c>
       <c r="AB3" t="n">
-        <v>2192.53</v>
+        <v>2203.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>2208.56</v>
+        <v>2230.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>2220.33</v>
+        <v>2245.9</v>
       </c>
       <c r="AE3" t="n">
         <v>43.6</v>
@@ -929,14 +929,14 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.47) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.16) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>49.5</v>
+        <v>50.2</v>
       </c>
       <c r="AJ3" t="n">
         <v>8.5</v>
@@ -948,14 +948,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>2262.69</v>
+        <v>2283.19</v>
       </c>
       <c r="AN3" t="n">
-        <v>2136.28</v>
+        <v>2153.96</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,996.00 Cr., a P/E ratio of 49.54, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹61,493.01 Cr., a P/E ratio of 50.19, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -965,26 +965,26 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,196.80) is positioned above the 30-day DMA (₹2,166.54), 50-day DMA (₹2,057.09), and 200-day DMA (₹1,970.33). The price distance from 200 DMA is +10.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,214.70) is positioned above the 30-day DMA (₹2,166.54), 50-day DMA (₹2,057.09), and 200-day DMA (₹1,970.33). The price distance from 200 DMA is +10.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[2196.8, 2203.39, 2209.98, 2216.57, 2223.16, 2229.75]</t>
+          <t>[2214.7, 2221.34, 2227.99, 2234.63, 2241.28, 2247.92]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[2196.8, 2225.68, 2241.5, 2255.17, 2267.73, 2279.58]</t>
+          <t>[2214.7, 2243.63, 2259.5, 2273.23, 2285.85, 2297.75]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[2196.8, 2186.68, 2186.34, 2187.62, 2189.73, 2192.38]</t>
+          <t>[2214.7, 2204.63, 2204.35, 2205.68, 2207.85, 2210.55]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2405.49</v>
+        <v>2425.1</v>
       </c>
     </row>
     <row r="4">
@@ -995,163 +995,163 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>306539.61</v>
+        <v>62046.36</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>333</v>
+        <v>1029</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹331.59 - ₹335.11</t>
+          <t>₹1023.36 - ₹1037.46</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>338.63</v>
+        <v>1051.57</v>
       </c>
       <c r="I4" t="n">
-        <v>325.68</v>
+        <v>1005.95</v>
       </c>
       <c r="J4" t="n">
-        <v>316.72</v>
+        <v>960.59</v>
       </c>
       <c r="K4" t="n">
-        <v>275.54</v>
+        <v>854.66</v>
       </c>
       <c r="L4" t="n">
-        <v>21.76</v>
+        <v>19.58</v>
       </c>
       <c r="M4" t="n">
-        <v>5.34</v>
+        <v>12.13</v>
       </c>
       <c r="N4" t="n">
-        <v>4.18</v>
+        <v>15.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16</v>
+        <v>-3.23</v>
       </c>
       <c r="P4" t="n">
-        <v>7.03</v>
+        <v>28.21</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.47</v>
+        <v>12.16</v>
       </c>
       <c r="R4" t="n">
-        <v>43</v>
+        <v>45.4</v>
       </c>
       <c r="S4" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.34</v>
+        <v>-1.73</v>
       </c>
       <c r="U4" t="n">
-        <v>54.1</v>
+        <v>50.8</v>
       </c>
       <c r="V4" t="n">
-        <v>2.48</v>
+        <v>3.47</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>333</v>
+        <v>1029</v>
       </c>
       <c r="Y4" t="n">
-        <v>370.74</v>
+        <v>1197.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>370.74</v>
+        <v>1197.14</v>
       </c>
       <c r="AA4" t="n">
-        <v>322.45</v>
+        <v>986.6900000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>335.02</v>
+        <v>1031.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>337.89</v>
+        <v>1044.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>342.77</v>
+        <v>1059.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>62.9</v>
+        <v>46.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.47) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.16) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>756.8</v>
+        <v>31.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>182</v>
+        <v>23.9</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>344.32</v>
+        <v>1069.37</v>
       </c>
       <c r="AN4" t="n">
-        <v>322.09</v>
+        <v>991.8</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹306,539.61 Cr., a P/E ratio of 756.82, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹62,046.36 Cr., a P/E ratio of 31.95, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.89 (Bullish Momentum Zone), while MACD Line (5.34) trades above Signal (4.18) with an expanding histogram (+1.16). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.76% above the 200-day DMA (₹275.54). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.82 (Consolidation Zone), while MACD Line (12.13) trades below Signal (15.35) with an expanding histogram (-3.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.58% above the 200-day DMA (₹854.66). Daily volatility envelope is bounded by ATR(14) of ₹28.21.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹333.00) is positioned above the 30-day DMA (₹325.68), 50-day DMA (₹316.72), and 200-day DMA (₹275.54). The price distance from 200 DMA is +21.76%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,029.00) is positioned above the 30-day DMA (₹1,005.95), 50-day DMA (₹960.59), and 200-day DMA (₹854.66). The price distance from 200 DMA is +19.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[333.0, 334.0, 335.0, 336.0, 337.0, 337.99]</t>
+          <t>[1029.0, 1033.14, 1037.27, 1041.41, 1045.54, 1049.68]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[333.0, 336.81, 338.98, 340.87, 342.62, 344.28]</t>
+          <t>[1029.0, 1044.42, 1053.23, 1060.95, 1068.11, 1074.91]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[333.0, 331.89, 332.01, 332.34, 332.78, 333.28]</t>
+          <t>[1029.0, 1024.67, 1025.3, 1026.75, 1028.62, 1030.76]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>370.74</v>
+        <v>1197.14</v>
       </c>
     </row>
     <row r="5">
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62365.94</v>
+        <v>308380.67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,146 +1179,146 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1034.3</v>
+        <v>335</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹1028.7 - ₹1042.7</t>
+          <t>₹333.59 - ₹337.11</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1056.7</v>
+        <v>340.63</v>
       </c>
       <c r="I5" t="n">
-        <v>1001.8</v>
+        <v>325.68</v>
       </c>
       <c r="J5" t="n">
-        <v>959.25</v>
+        <v>316.72</v>
       </c>
       <c r="K5" t="n">
-        <v>853.76</v>
+        <v>275.54</v>
       </c>
       <c r="L5" t="n">
-        <v>22.11</v>
+        <v>21.76</v>
       </c>
       <c r="M5" t="n">
-        <v>12.21</v>
+        <v>5.34</v>
       </c>
       <c r="N5" t="n">
-        <v>16.16</v>
+        <v>4.18</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.95</v>
+        <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>28</v>
+        <v>7.03</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.47</v>
+        <v>12.16</v>
       </c>
       <c r="R5" t="n">
-        <v>40.4</v>
+        <v>42.8</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.95</v>
+        <v>-1.34</v>
       </c>
       <c r="U5" t="n">
-        <v>50</v>
+        <v>54.1</v>
       </c>
       <c r="V5" t="n">
-        <v>3.48</v>
+        <v>2.49</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>1034.3</v>
+        <v>335</v>
       </c>
       <c r="Y5" t="n">
-        <v>1203.3</v>
+        <v>372.97</v>
       </c>
       <c r="Z5" t="n">
-        <v>1203.3</v>
+        <v>372.97</v>
       </c>
       <c r="AA5" t="n">
-        <v>992.3</v>
+        <v>324.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>1033.57</v>
+        <v>335.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>1047.74</v>
+        <v>339.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>1061.17</v>
+        <v>343.73</v>
       </c>
       <c r="AE5" t="n">
-        <v>56.2</v>
+        <v>62.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Vol Spike 2.8x | Inst. Buying (CMF+) | Low VIX (12.47) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.16) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>32.1</v>
+        <v>712.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23.9</v>
+        <v>182</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>0.6</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1077.52</v>
+        <v>347.09</v>
       </c>
       <c r="AN5" t="n">
-        <v>992.78</v>
+        <v>323.48</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹62,365.94 Cr., a P/E ratio of 32.11, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹308,380.67 Cr., a P/E ratio of 712.77, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 56.20 (Bullish Momentum Zone), while MACD Line (12.21) trades below Signal (16.16) with an expanding histogram (-3.95). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +22.11% above the 200-day DMA (₹853.76). Daily volatility envelope is bounded by ATR(14) of ₹28.00.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.89 (Bullish Momentum Zone), while MACD Line (5.34) trades above Signal (4.18) with an expanding histogram (+1.16). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.76% above the 200-day DMA (₹275.54). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,034.30) is positioned above the 30-day DMA (₹1,001.80), 50-day DMA (₹959.25), and 200-day DMA (₹853.76). The price distance from 200 DMA is +22.11%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹335.00) is positioned above the 30-day DMA (₹325.68), 50-day DMA (₹316.72), and 200-day DMA (₹275.54). The price distance from 200 DMA is +21.76%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[1034.3, 1042.0, 1049.69, 1057.39, 1065.09, 1072.79]</t>
+          <t>[335.0, 336.0, 337.01, 338.01, 339.02, 340.02]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[1034.3, 1053.2, 1065.53, 1076.79, 1087.49, 1097.83]</t>
+          <t>[335.0, 338.82, 340.99, 342.89, 344.65, 346.31]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[1034.3, 1033.6, 1037.82, 1042.84, 1048.29, 1054.0]</t>
+          <t>[335.0, 333.9, 334.03, 334.36, 334.8, 335.31]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1203.3</v>
+        <v>372.97</v>
       </c>
     </row>
     <row r="6">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30905.29</v>
+        <v>31133.56</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,15 +1346,15 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>561.85</v>
+        <v>566</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹558.63 - ₹566.67</t>
+          <t>₹562.78 - ₹570.82</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>574.72</v>
+        <v>578.87</v>
       </c>
       <c r="I6" t="n">
         <v>535.66</v>
@@ -1381,46 +1381,46 @@
         <v>16.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.47</v>
+        <v>12.16</v>
       </c>
       <c r="R6" t="n">
-        <v>36.1</v>
+        <v>41.7</v>
       </c>
       <c r="S6" t="n">
         <v>0.19</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.3</v>
+        <v>-2</v>
       </c>
       <c r="U6" t="n">
-        <v>47.5</v>
+        <v>49.2</v>
       </c>
       <c r="V6" t="n">
-        <v>4.44</v>
+        <v>4.46</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>561.85</v>
+        <v>566</v>
       </c>
       <c r="Y6" t="n">
-        <v>639</v>
+        <v>643.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>639</v>
+        <v>643.73</v>
       </c>
       <c r="AA6" t="n">
-        <v>537.73</v>
+        <v>541.88</v>
       </c>
       <c r="AB6" t="n">
-        <v>563.4299999999999</v>
+        <v>564.72</v>
       </c>
       <c r="AC6" t="n">
-        <v>565.61</v>
+        <v>570.84</v>
       </c>
       <c r="AD6" t="n">
-        <v>569.38</v>
+        <v>575.67</v>
       </c>
       <c r="AE6" t="n">
         <v>51</v>
@@ -1430,14 +1430,14 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.47) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.16) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AJ6" t="n">
         <v>14.5</v>
@@ -1449,14 +1449,14 @@
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>575.9299999999999</v>
+        <v>580.3200000000001</v>
       </c>
       <c r="AN6" t="n">
-        <v>546.92</v>
+        <v>550.3099999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,905.29 Cr., a P/E ratio of 5.46, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,133.56 Cr., a P/E ratio of 5.43, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1466,26 +1466,26 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹561.85) is positioned above the 30-day DMA (₹535.66), 50-day DMA (₹528.07), and 200-day DMA (₹524.57). The price distance from 200 DMA is +7.56%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹566.00) is positioned above the 30-day DMA (₹535.66), 50-day DMA (₹528.07), and 200-day DMA (₹524.57). The price distance from 200 DMA is +7.56%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[561.85, 563.54, 565.22, 566.91, 568.59, 570.28]</t>
+          <t>[566.0, 567.7, 569.4, 571.09, 572.79, 574.49]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[561.85, 569.97, 574.32, 578.05, 581.46, 584.66]</t>
+          <t>[566.0, 574.13, 578.49, 582.24, 585.66, 588.87]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[561.85, 558.71, 558.4, 558.55, 558.94, 559.49]</t>
+          <t>[566.0, 562.87, 562.57, 562.74, 563.14, 563.7]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>639</v>
+        <v>643.73</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU6"/>
+  <dimension ref="A1:AU5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,7 +716,7 @@
         <v>12.16</v>
       </c>
       <c r="R2" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="S2" t="n">
         <v>0.39</v>
@@ -734,13 +734,13 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>116.6</v>
+        <v>113.51</v>
       </c>
       <c r="Y2" t="n">
-        <v>130.3</v>
+        <v>110.44</v>
       </c>
       <c r="Z2" t="n">
-        <v>130.3</v>
+        <v>105.88</v>
       </c>
       <c r="AA2" t="n">
         <v>113.55</v>
@@ -781,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>119.9</v>
+        <v>119.89</v>
       </c>
       <c r="AN2" t="n">
-        <v>113.33</v>
+        <v>113.63</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,007.71 Cr., a P/E ratio of 6.07, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,007.71 Cr., a P/E ratio of 6.10, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>130.3</v>
+        <v>105.88</v>
       </c>
     </row>
     <row r="3">
@@ -883,13 +883,13 @@
         <v>12.16</v>
       </c>
       <c r="R3" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
       <c r="S3" t="n">
         <v>0.21</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5</v>
+        <v>-1.49</v>
       </c>
       <c r="U3" t="n">
         <v>54.1</v>
@@ -901,13 +901,13 @@
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>2214.7</v>
+        <v>2109.91</v>
       </c>
       <c r="Y3" t="n">
-        <v>2425.1</v>
+        <v>2062.42</v>
       </c>
       <c r="Z3" t="n">
-        <v>2425.1</v>
+        <v>2011.21</v>
       </c>
       <c r="AA3" t="n">
         <v>2131.13</v>
@@ -936,7 +936,7 @@
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>50.2</v>
+        <v>49.9</v>
       </c>
       <c r="AJ3" t="n">
         <v>8.5</v>
@@ -948,14 +948,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>2283.19</v>
+        <v>2279.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>2153.96</v>
+        <v>2156.6</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹61,493.01 Cr., a P/E ratio of 50.19, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹61,493.01 Cr., a P/E ratio of 49.95, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2425.1</v>
+        <v>2011.21</v>
       </c>
     </row>
     <row r="4">
@@ -995,163 +995,163 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62046.36</v>
+        <v>308380.67</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1029</v>
+        <v>335</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹1023.36 - ₹1037.46</t>
+          <t>₹333.59 - ₹337.11</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1051.57</v>
+        <v>340.63</v>
       </c>
       <c r="I4" t="n">
-        <v>1005.95</v>
+        <v>325.68</v>
       </c>
       <c r="J4" t="n">
-        <v>960.59</v>
+        <v>316.72</v>
       </c>
       <c r="K4" t="n">
-        <v>854.66</v>
+        <v>275.54</v>
       </c>
       <c r="L4" t="n">
-        <v>19.58</v>
+        <v>21.76</v>
       </c>
       <c r="M4" t="n">
-        <v>12.13</v>
+        <v>5.34</v>
       </c>
       <c r="N4" t="n">
-        <v>15.35</v>
+        <v>4.18</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.23</v>
+        <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>28.21</v>
+        <v>7.03</v>
       </c>
       <c r="Q4" t="n">
         <v>12.16</v>
       </c>
       <c r="R4" t="n">
-        <v>45.4</v>
+        <v>43</v>
       </c>
       <c r="S4" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.73</v>
+        <v>-1.33</v>
       </c>
       <c r="U4" t="n">
-        <v>50.8</v>
+        <v>54.1</v>
       </c>
       <c r="V4" t="n">
-        <v>3.47</v>
+        <v>2.49</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>1029</v>
+        <v>320.72</v>
       </c>
       <c r="Y4" t="n">
-        <v>1197.14</v>
+        <v>313.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>1197.14</v>
+        <v>303.76</v>
       </c>
       <c r="AA4" t="n">
-        <v>986.6900000000001</v>
+        <v>324.45</v>
       </c>
       <c r="AB4" t="n">
-        <v>1031.8</v>
+        <v>335.53</v>
       </c>
       <c r="AC4" t="n">
-        <v>1044.2</v>
+        <v>339.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>1059.4</v>
+        <v>343.73</v>
       </c>
       <c r="AE4" t="n">
-        <v>46.8</v>
+        <v>62.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.16) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.16) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>31.9</v>
+        <v>712.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23.9</v>
+        <v>182</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>0.6</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>1069.37</v>
+        <v>346.75</v>
       </c>
       <c r="AN4" t="n">
-        <v>991.8</v>
+        <v>324.07</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹62,046.36 Cr., a P/E ratio of 31.95, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹308,380.67 Cr., a P/E ratio of 712.77, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.82 (Consolidation Zone), while MACD Line (12.13) trades below Signal (15.35) with an expanding histogram (-3.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.58% above the 200-day DMA (₹854.66). Daily volatility envelope is bounded by ATR(14) of ₹28.21.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.89 (Bullish Momentum Zone), while MACD Line (5.34) trades above Signal (4.18) with an expanding histogram (+1.16). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.76% above the 200-day DMA (₹275.54). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,029.00) is positioned above the 30-day DMA (₹1,005.95), 50-day DMA (₹960.59), and 200-day DMA (₹854.66). The price distance from 200 DMA is +19.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹335.00) is positioned above the 30-day DMA (₹325.68), 50-day DMA (₹316.72), and 200-day DMA (₹275.54). The price distance from 200 DMA is +21.76%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[1029.0, 1033.14, 1037.27, 1041.41, 1045.54, 1049.68]</t>
+          <t>[335.0, 336.0, 337.01, 338.01, 339.02, 340.02]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[1029.0, 1044.42, 1053.23, 1060.95, 1068.11, 1074.91]</t>
+          <t>[335.0, 338.82, 340.99, 342.89, 344.65, 346.31]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[1029.0, 1024.67, 1025.3, 1026.75, 1028.62, 1030.76]</t>
+          <t>[335.0, 333.9, 334.03, 334.36, 334.8, 335.31]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1197.14</v>
+        <v>303.76</v>
       </c>
     </row>
     <row r="5">
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>308380.67</v>
+        <v>31133.56</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,313 +1179,146 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>335</v>
+        <v>566</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹333.59 - ₹337.11</t>
+          <t>₹562.78 - ₹570.82</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>340.63</v>
+        <v>578.87</v>
       </c>
       <c r="I5" t="n">
-        <v>325.68</v>
+        <v>535.66</v>
       </c>
       <c r="J5" t="n">
-        <v>316.72</v>
+        <v>528.0700000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>275.54</v>
+        <v>524.5700000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>21.76</v>
+        <v>7.56</v>
       </c>
       <c r="M5" t="n">
-        <v>5.34</v>
+        <v>11.03</v>
       </c>
       <c r="N5" t="n">
-        <v>4.18</v>
+        <v>10.37</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>0.66</v>
       </c>
       <c r="P5" t="n">
-        <v>7.03</v>
+        <v>16.08</v>
       </c>
       <c r="Q5" t="n">
         <v>12.16</v>
       </c>
       <c r="R5" t="n">
-        <v>42.8</v>
+        <v>41.7</v>
       </c>
       <c r="S5" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.34</v>
+        <v>-2</v>
       </c>
       <c r="U5" t="n">
-        <v>54.1</v>
+        <v>49.2</v>
       </c>
       <c r="V5" t="n">
-        <v>2.49</v>
+        <v>4.46</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>335</v>
+        <v>534.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>372.97</v>
+        <v>513.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>372.97</v>
+        <v>500.09</v>
       </c>
       <c r="AA5" t="n">
-        <v>324.45</v>
+        <v>541.88</v>
       </c>
       <c r="AB5" t="n">
-        <v>335.53</v>
+        <v>564.72</v>
       </c>
       <c r="AC5" t="n">
-        <v>339.36</v>
+        <v>570.84</v>
       </c>
       <c r="AD5" t="n">
-        <v>343.73</v>
+        <v>575.67</v>
       </c>
       <c r="AE5" t="n">
-        <v>62.9</v>
+        <v>51</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.28</v>
+        <v>0.11</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.16) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.16) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>712.8</v>
+        <v>5.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>182</v>
+        <v>14.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.6</v>
+        <v>65.2</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>347.09</v>
+        <v>580.3200000000001</v>
       </c>
       <c r="AN5" t="n">
-        <v>323.48</v>
+        <v>551.12</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹308,380.67 Cr., a P/E ratio of 712.77, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,133.56 Cr., a P/E ratio of 5.41, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.89 (Bullish Momentum Zone), while MACD Line (5.34) trades above Signal (4.18) with an expanding histogram (+1.16). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.76% above the 200-day DMA (₹275.54). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.02 (Consolidation Zone), while MACD Line (11.03) trades above Signal (10.37) with an expanding histogram (+0.66). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.56% above the 200-day DMA (₹524.57). Daily volatility envelope is bounded by ATR(14) of ₹16.08.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹335.00) is positioned above the 30-day DMA (₹325.68), 50-day DMA (₹316.72), and 200-day DMA (₹275.54). The price distance from 200 DMA is +21.76%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹566.00) is positioned above the 30-day DMA (₹535.66), 50-day DMA (₹528.07), and 200-day DMA (₹524.57). The price distance from 200 DMA is +7.56%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[335.0, 336.0, 337.01, 338.01, 339.02, 340.02]</t>
+          <t>[566.0, 567.7, 569.4, 571.09, 572.79, 574.49]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[335.0, 338.82, 340.99, 342.89, 344.65, 346.31]</t>
+          <t>[566.0, 574.13, 578.49, 582.24, 585.66, 588.87]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[335.0, 333.9, 334.03, 334.36, 334.8, 335.31]</t>
+          <t>[566.0, 562.87, 562.57, 562.74, 563.14, 563.7]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>372.97</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>31133.56</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>566</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>₹562.78 - ₹570.82</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>578.87</v>
-      </c>
-      <c r="I6" t="n">
-        <v>535.66</v>
-      </c>
-      <c r="J6" t="n">
-        <v>528.0700000000001</v>
-      </c>
-      <c r="K6" t="n">
-        <v>524.5700000000001</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="M6" t="n">
-        <v>11.03</v>
-      </c>
-      <c r="N6" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="P6" t="n">
-        <v>16.08</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>12.16</v>
-      </c>
-      <c r="R6" t="n">
-        <v>41.7</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="U6" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="V6" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X6" t="n">
-        <v>566</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>643.73</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>643.73</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>541.88</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>564.72</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>570.84</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>575.67</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>51</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.16) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>580.3200000000001</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>550.3099999999999</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,133.56 Cr., a P/E ratio of 5.43, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.02 (Consolidation Zone), while MACD Line (11.03) trades above Signal (10.37) with an expanding histogram (+0.66). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.56% above the 200-day DMA (₹524.57). Daily volatility envelope is bounded by ATR(14) of ₹16.08.</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹566.00) is positioned above the 30-day DMA (₹535.66), 50-day DMA (₹528.07), and 200-day DMA (₹524.57). The price distance from 200 DMA is +7.56%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>[566.0, 567.7, 569.4, 571.09, 572.79, 574.49]</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>[566.0, 574.13, 578.49, 582.24, 585.66, 588.87]</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>[566.0, 562.87, 562.57, 562.74, 563.14, 563.7]</t>
-        </is>
-      </c>
-      <c r="AU6" t="n">
-        <v>643.73</v>
+        <v>500.09</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -716,7 +716,7 @@
         <v>12.16</v>
       </c>
       <c r="R2" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
       <c r="S2" t="n">
         <v>0.39</v>
@@ -781,10 +781,10 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>119.89</v>
+        <v>119.74</v>
       </c>
       <c r="AN2" t="n">
-        <v>113.63</v>
+        <v>113.44</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -883,13 +883,13 @@
         <v>12.16</v>
       </c>
       <c r="R3" t="n">
-        <v>46.9</v>
+        <v>46.4</v>
       </c>
       <c r="S3" t="n">
         <v>0.21</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.49</v>
+        <v>-1.51</v>
       </c>
       <c r="U3" t="n">
         <v>54.1</v>
@@ -901,10 +901,10 @@
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>2109.91</v>
+        <v>2109.93</v>
       </c>
       <c r="Y3" t="n">
-        <v>2062.42</v>
+        <v>2062.44</v>
       </c>
       <c r="Z3" t="n">
         <v>2011.21</v>
@@ -948,10 +948,10 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>2279.18</v>
+        <v>2274.49</v>
       </c>
       <c r="AN3" t="n">
-        <v>2156.6</v>
+        <v>2152.83</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>12.16</v>
       </c>
       <c r="R4" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="S4" t="n">
         <v>0.25</v>
@@ -1115,10 +1115,10 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>346.75</v>
+        <v>346.42</v>
       </c>
       <c r="AN4" t="n">
-        <v>324.07</v>
+        <v>323.75</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1217,13 +1217,13 @@
         <v>12.16</v>
       </c>
       <c r="R5" t="n">
-        <v>41.7</v>
+        <v>42.1</v>
       </c>
       <c r="S5" t="n">
         <v>0.19</v>
       </c>
       <c r="T5" t="n">
-        <v>-2</v>
+        <v>-1.98</v>
       </c>
       <c r="U5" t="n">
         <v>49.2</v>
@@ -1238,7 +1238,7 @@
         <v>534.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>513.4</v>
+        <v>513.41</v>
       </c>
       <c r="Z5" t="n">
         <v>500.09</v>
@@ -1282,10 +1282,10 @@
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>580.3200000000001</v>
+        <v>580.55</v>
       </c>
       <c r="AN5" t="n">
-        <v>551.12</v>
+        <v>551.02</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,19 +716,19 @@
         <v>12.16</v>
       </c>
       <c r="R2" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="S2" t="n">
         <v>0.39</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.76</v>
+        <v>-0.77</v>
       </c>
       <c r="U2" t="n">
         <v>52.5</v>
       </c>
       <c r="V2" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
@@ -781,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>119.74</v>
+        <v>119.9</v>
       </c>
       <c r="AN2" t="n">
-        <v>113.44</v>
+        <v>113.53</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,007.71 Cr., a P/E ratio of 6.10, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,007.71 Cr., a P/E ratio of 6.07, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -883,7 +883,7 @@
         <v>12.16</v>
       </c>
       <c r="R3" t="n">
-        <v>46.4</v>
+        <v>46.6</v>
       </c>
       <c r="S3" t="n">
         <v>0.21</v>
@@ -901,10 +901,10 @@
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>2109.93</v>
+        <v>2109.91</v>
       </c>
       <c r="Y3" t="n">
-        <v>2062.44</v>
+        <v>2062.42</v>
       </c>
       <c r="Z3" t="n">
         <v>2011.21</v>
@@ -948,10 +948,10 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>2274.49</v>
+        <v>2283.95</v>
       </c>
       <c r="AN3" t="n">
-        <v>2152.83</v>
+        <v>2155.81</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -995,163 +995,163 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>308380.67</v>
+        <v>62046.36</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>335</v>
+        <v>1029</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹333.59 - ₹337.11</t>
+          <t>₹1023.36 - ₹1037.46</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>340.63</v>
+        <v>1051.57</v>
       </c>
       <c r="I4" t="n">
-        <v>325.68</v>
+        <v>1005.95</v>
       </c>
       <c r="J4" t="n">
-        <v>316.72</v>
+        <v>960.59</v>
       </c>
       <c r="K4" t="n">
-        <v>275.54</v>
+        <v>854.66</v>
       </c>
       <c r="L4" t="n">
-        <v>21.76</v>
+        <v>19.58</v>
       </c>
       <c r="M4" t="n">
-        <v>5.34</v>
+        <v>12.13</v>
       </c>
       <c r="N4" t="n">
-        <v>4.18</v>
+        <v>15.35</v>
       </c>
       <c r="O4" t="n">
-        <v>1.16</v>
+        <v>-3.23</v>
       </c>
       <c r="P4" t="n">
-        <v>7.03</v>
+        <v>28.21</v>
       </c>
       <c r="Q4" t="n">
         <v>12.16</v>
       </c>
       <c r="R4" t="n">
-        <v>43.1</v>
+        <v>45.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.33</v>
+        <v>-1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>54.1</v>
+        <v>50.8</v>
       </c>
       <c r="V4" t="n">
-        <v>2.49</v>
+        <v>3.47</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>320.72</v>
+        <v>995.54</v>
       </c>
       <c r="Y4" t="n">
-        <v>313.46</v>
+        <v>972.63</v>
       </c>
       <c r="Z4" t="n">
-        <v>303.76</v>
+        <v>885.48</v>
       </c>
       <c r="AA4" t="n">
-        <v>324.45</v>
+        <v>986.6900000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>335.53</v>
+        <v>1031.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>339.36</v>
+        <v>1044.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>343.73</v>
+        <v>1059.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>62.9</v>
+        <v>46.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.16) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (12.16) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>712.8</v>
+        <v>31.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>182</v>
+        <v>23.9</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>346.42</v>
+        <v>1069.65</v>
       </c>
       <c r="AN4" t="n">
-        <v>323.75</v>
+        <v>991.11</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹308,380.67 Cr., a P/E ratio of 712.77, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹62,046.36 Cr., a P/E ratio of 31.95, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.89 (Bullish Momentum Zone), while MACD Line (5.34) trades above Signal (4.18) with an expanding histogram (+1.16). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.76% above the 200-day DMA (₹275.54). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.82 (Consolidation Zone), while MACD Line (12.13) trades below Signal (15.35) with an expanding histogram (-3.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.58% above the 200-day DMA (₹854.66). Daily volatility envelope is bounded by ATR(14) of ₹28.21.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹335.00) is positioned above the 30-day DMA (₹325.68), 50-day DMA (₹316.72), and 200-day DMA (₹275.54). The price distance from 200 DMA is +21.76%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,029.00) is positioned above the 30-day DMA (₹1,005.95), 50-day DMA (₹960.59), and 200-day DMA (₹854.66). The price distance from 200 DMA is +19.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[335.0, 336.0, 337.01, 338.01, 339.02, 340.02]</t>
+          <t>[1029.0, 1033.14, 1037.27, 1041.41, 1045.54, 1049.68]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[335.0, 338.82, 340.99, 342.89, 344.65, 346.31]</t>
+          <t>[1029.0, 1044.42, 1053.23, 1060.95, 1068.11, 1074.91]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[335.0, 333.9, 334.03, 334.36, 334.8, 335.31]</t>
+          <t>[1029.0, 1024.67, 1025.3, 1026.75, 1028.62, 1030.76]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>303.76</v>
+        <v>885.48</v>
       </c>
     </row>
     <row r="5">
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31133.56</v>
+        <v>308380.67</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,145 +1179,312 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>566</v>
+        <v>335</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹562.78 - ₹570.82</t>
+          <t>₹333.59 - ₹337.11</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>578.87</v>
+        <v>340.63</v>
       </c>
       <c r="I5" t="n">
-        <v>535.66</v>
+        <v>325.68</v>
       </c>
       <c r="J5" t="n">
-        <v>528.0700000000001</v>
+        <v>316.72</v>
       </c>
       <c r="K5" t="n">
-        <v>524.5700000000001</v>
+        <v>275.54</v>
       </c>
       <c r="L5" t="n">
-        <v>7.56</v>
+        <v>21.76</v>
       </c>
       <c r="M5" t="n">
-        <v>11.03</v>
+        <v>5.34</v>
       </c>
       <c r="N5" t="n">
-        <v>10.37</v>
+        <v>4.18</v>
       </c>
       <c r="O5" t="n">
-        <v>0.66</v>
+        <v>1.16</v>
       </c>
       <c r="P5" t="n">
-        <v>16.08</v>
+        <v>7.03</v>
       </c>
       <c r="Q5" t="n">
         <v>12.16</v>
       </c>
       <c r="R5" t="n">
-        <v>42.1</v>
+        <v>43.1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.98</v>
+        <v>-1.33</v>
       </c>
       <c r="U5" t="n">
-        <v>49.2</v>
+        <v>54.1</v>
       </c>
       <c r="V5" t="n">
-        <v>4.46</v>
+        <v>2.49</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>534.8</v>
+        <v>320.72</v>
       </c>
       <c r="Y5" t="n">
-        <v>513.41</v>
+        <v>313.46</v>
       </c>
       <c r="Z5" t="n">
-        <v>500.09</v>
+        <v>303.76</v>
       </c>
       <c r="AA5" t="n">
-        <v>541.88</v>
+        <v>324.45</v>
       </c>
       <c r="AB5" t="n">
-        <v>564.72</v>
+        <v>335.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>570.84</v>
+        <v>339.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>575.67</v>
+        <v>343.73</v>
       </c>
       <c r="AE5" t="n">
-        <v>51</v>
+        <v>62.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.11</v>
+        <v>0.28</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.16) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.16) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.4</v>
+        <v>712.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14.5</v>
+        <v>182</v>
       </c>
       <c r="AK5" t="n">
-        <v>65.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>580.55</v>
+        <v>346.78</v>
       </c>
       <c r="AN5" t="n">
-        <v>551.02</v>
+        <v>323.89</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,133.56 Cr., a P/E ratio of 5.41, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹308,380.67 Cr., a P/E ratio of 712.77, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.89 (Bullish Momentum Zone), while MACD Line (5.34) trades above Signal (4.18) with an expanding histogram (+1.16). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.76% above the 200-day DMA (₹275.54). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹335.00) is positioned above the 30-day DMA (₹325.68), 50-day DMA (₹316.72), and 200-day DMA (₹275.54). The price distance from 200 DMA is +21.76%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>[335.0, 336.0, 337.01, 338.01, 339.02, 340.02]</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>[335.0, 338.82, 340.99, 342.89, 344.65, 346.31]</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>[335.0, 333.9, 334.03, 334.36, 334.8, 335.31]</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>303.76</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>31133.56</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>566</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>₹562.78 - ₹570.82</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>578.87</v>
+      </c>
+      <c r="I6" t="n">
+        <v>535.66</v>
+      </c>
+      <c r="J6" t="n">
+        <v>528.0700000000001</v>
+      </c>
+      <c r="K6" t="n">
+        <v>524.5700000000001</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="M6" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="P6" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="R6" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="U6" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X6" t="n">
+        <v>534.8</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>513.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>500.09</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>541.88</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>564.72</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>570.84</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>575.67</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>51</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.16) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>581.58</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>551.1900000000001</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,133.56 Cr., a P/E ratio of 5.43, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
           <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.02 (Consolidation Zone), while MACD Line (11.03) trades above Signal (10.37) with an expanding histogram (+0.66). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.56% above the 200-day DMA (₹524.57). Daily volatility envelope is bounded by ATR(14) of ₹16.08.</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹566.00) is positioned above the 30-day DMA (₹535.66), 50-day DMA (₹528.07), and 200-day DMA (₹524.57). The price distance from 200 DMA is +7.56%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>[566.0, 567.7, 569.4, 571.09, 572.79, 574.49]</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>[566.0, 574.13, 578.49, 582.24, 585.66, 588.87]</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AT6" t="inlineStr">
         <is>
           <t>[566.0, 562.87, 562.57, 562.74, 563.14, 563.7]</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AU6" t="n">
         <v>500.09</v>
       </c>
     </row>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -716,31 +716,31 @@
         <v>12.16</v>
       </c>
       <c r="R2" t="n">
-        <v>47.7</v>
+        <v>48.2</v>
       </c>
       <c r="S2" t="n">
         <v>0.39</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.77</v>
+        <v>-0.75</v>
       </c>
       <c r="U2" t="n">
         <v>52.5</v>
       </c>
       <c r="V2" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>113.51</v>
+        <v>116.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>110.44</v>
+        <v>129.72</v>
       </c>
       <c r="Z2" t="n">
-        <v>105.88</v>
+        <v>129.72</v>
       </c>
       <c r="AA2" t="n">
         <v>113.55</v>
@@ -781,10 +781,10 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>119.9</v>
+        <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>113.53</v>
+        <v>113.33</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>105.88</v>
+        <v>129.72</v>
       </c>
     </row>
     <row r="3">
@@ -901,13 +901,13 @@
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>2109.91</v>
+        <v>2207.73</v>
       </c>
       <c r="Y3" t="n">
-        <v>2062.42</v>
+        <v>2458.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>2011.21</v>
+        <v>2458.3</v>
       </c>
       <c r="AA3" t="n">
         <v>2131.13</v>
@@ -936,7 +936,7 @@
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
       <c r="AJ3" t="n">
         <v>8.5</v>
@@ -948,14 +948,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>2283.95</v>
+        <v>2278.76</v>
       </c>
       <c r="AN3" t="n">
-        <v>2155.81</v>
+        <v>2152.14</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹61,493.01 Cr., a P/E ratio of 49.95, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹61,493.01 Cr., a P/E ratio of 50.19, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2011.21</v>
+        <v>2458.3</v>
       </c>
     </row>
     <row r="4">
@@ -1050,13 +1050,13 @@
         <v>12.16</v>
       </c>
       <c r="R4" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="S4" t="n">
         <v>0.19</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.74</v>
+        <v>-1.73</v>
       </c>
       <c r="U4" t="n">
         <v>50.8</v>
@@ -1068,13 +1068,13 @@
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>995.54</v>
+        <v>1029</v>
       </c>
       <c r="Y4" t="n">
-        <v>972.63</v>
+        <v>1205.34</v>
       </c>
       <c r="Z4" t="n">
-        <v>885.48</v>
+        <v>1205.34</v>
       </c>
       <c r="AA4" t="n">
         <v>986.6900000000001</v>
@@ -1115,10 +1115,10 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>1069.65</v>
+        <v>1070.79</v>
       </c>
       <c r="AN4" t="n">
-        <v>991.11</v>
+        <v>988.99</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>885.48</v>
+        <v>1205.34</v>
       </c>
     </row>
     <row r="5">
@@ -1217,13 +1217,13 @@
         <v>12.16</v>
       </c>
       <c r="R5" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="S5" t="n">
         <v>0.25</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.33</v>
+        <v>-1.32</v>
       </c>
       <c r="U5" t="n">
         <v>54.1</v>
@@ -1235,13 +1235,13 @@
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>320.72</v>
+        <v>335</v>
       </c>
       <c r="Y5" t="n">
-        <v>313.46</v>
+        <v>372.41</v>
       </c>
       <c r="Z5" t="n">
-        <v>303.76</v>
+        <v>372.41</v>
       </c>
       <c r="AA5" t="n">
         <v>324.45</v>
@@ -1282,10 +1282,10 @@
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>346.78</v>
+        <v>346.66</v>
       </c>
       <c r="AN5" t="n">
-        <v>323.89</v>
+        <v>324.4</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>303.76</v>
+        <v>372.41</v>
       </c>
     </row>
     <row r="6">
@@ -1384,13 +1384,13 @@
         <v>12.16</v>
       </c>
       <c r="R6" t="n">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="S6" t="n">
         <v>0.19</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.97</v>
+        <v>-2.01</v>
       </c>
       <c r="U6" t="n">
         <v>49.2</v>
@@ -1402,13 +1402,13 @@
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>534.8</v>
+        <v>559.59</v>
       </c>
       <c r="Y6" t="n">
-        <v>513.4</v>
+        <v>645.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>500.09</v>
+        <v>645.73</v>
       </c>
       <c r="AA6" t="n">
         <v>541.88</v>
@@ -1449,10 +1449,10 @@
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>581.58</v>
+        <v>579.84</v>
       </c>
       <c r="AN6" t="n">
-        <v>551.1900000000001</v>
+        <v>551.53</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>500.09</v>
+        <v>645.73</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -656,21 +656,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>134007.71</v>
+        <v>43627.51</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,500 +678,500 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>116.6</v>
+        <v>290.85</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹116.19 - ₹117.21</t>
+          <t>₹289.75 - ₹292.5</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>118.22</v>
+        <v>295.25</v>
       </c>
       <c r="I2" t="n">
-        <v>116.54</v>
+        <v>288.56</v>
       </c>
       <c r="J2" t="n">
-        <v>114.99</v>
+        <v>284.53</v>
       </c>
       <c r="K2" t="n">
-        <v>112.35</v>
+        <v>279.21</v>
       </c>
       <c r="L2" t="n">
-        <v>4.24</v>
+        <v>2.61</v>
       </c>
       <c r="M2" t="n">
-        <v>0.73</v>
+        <v>-0.09</v>
       </c>
       <c r="N2" t="n">
-        <v>0.74</v>
+        <v>0.31</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.01</v>
+        <v>-0.39</v>
       </c>
       <c r="P2" t="n">
-        <v>2.03</v>
+        <v>5.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>12.16</v>
+        <v>13.76</v>
       </c>
       <c r="R2" t="n">
-        <v>48.2</v>
+        <v>47.9</v>
       </c>
       <c r="S2" t="n">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.75</v>
+        <v>-0.99</v>
       </c>
       <c r="U2" t="n">
-        <v>52.5</v>
+        <v>55</v>
       </c>
       <c r="V2" t="n">
-        <v>2.32</v>
+        <v>5.28</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>116.6</v>
+        <v>290.85</v>
       </c>
       <c r="Y2" t="n">
-        <v>129.72</v>
+        <v>318.95</v>
       </c>
       <c r="Z2" t="n">
-        <v>129.72</v>
+        <v>318.95</v>
       </c>
       <c r="AA2" t="n">
-        <v>113.55</v>
+        <v>282.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>116.95</v>
+        <v>289.88</v>
       </c>
       <c r="AC2" t="n">
-        <v>117.67</v>
+        <v>294.01</v>
       </c>
       <c r="AD2" t="n">
-        <v>118.73</v>
+        <v>297.18</v>
       </c>
       <c r="AE2" t="n">
-        <v>50.5</v>
+        <v>44.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.08</v>
+        <v>0.1</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (12.16) | LSTM Deep Net</t>
+          <t>Low VIX (13.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.1</v>
+        <v>10.4</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-6.4</v>
+        <v>-53.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>38.1</v>
+        <v>11.3</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>120</v>
+        <v>299.94</v>
       </c>
       <c r="AN2" t="n">
-        <v>113.33</v>
+        <v>282.59</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PNB operates in the Financial Services sector. With an estimated Market Cap of ₹134,007.71 Cr., a P/E ratio of 6.07, and YoY Revenue Growth of -6.4%, the company demonstrates strong institutional backing, solid operating profit margins (38.15%), and healthy Return on Equity (14.97%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,627.51 Cr., a P/E ratio of 10.37, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.46 (Consolidation Zone), while MACD Line (0.73) trades below Signal (0.74) with an expanding histogram (-0.01). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.24% above the 200-day DMA (₹112.35). Daily volatility envelope is bounded by ATR(14) of ₹2.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.57 (Consolidation Zone), while MACD Line (-0.09) trades below Signal (0.31) with an expanding histogram (-0.39). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.61% above the 200-day DMA (₹279.21). Daily volatility envelope is bounded by ATR(14) of ₹5.50.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PNB. Current Market Price (₹116.60) is positioned above the 30-day DMA (₹116.54), 50-day DMA (₹114.99), and 200-day DMA (₹112.35). The price distance from 200 DMA is +4.24%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹290.85) is positioned above the 30-day DMA (₹288.56), 50-day DMA (₹284.53), and 200-day DMA (₹279.21). The price distance from 200 DMA is +2.61%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[116.6, 117.79, 118.98, 120.17, 121.36, 122.54]</t>
+          <t>[290.85, 291.72, 292.6, 293.47, 294.34, 295.21]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[116.6, 118.6, 120.13, 121.57, 122.98, 124.36]</t>
+          <t>[290.85, 293.92, 295.71, 297.28, 298.74, 300.13]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[116.6, 117.18, 118.12, 119.11, 120.14, 121.18]</t>
+          <t>[290.85, 290.07, 290.26, 290.61, 291.04, 291.52]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>129.72</v>
+        <v>318.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>61493.01</v>
+        <v>31499.36</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2214.7</v>
+        <v>572.65</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹2203.56 - ₹2231.41</t>
+          <t>₹569.56 - ₹577.29</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2259.27</v>
+        <v>585.02</v>
       </c>
       <c r="I3" t="n">
-        <v>2166.54</v>
+        <v>538.1799999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>2057.09</v>
+        <v>528.61</v>
       </c>
       <c r="K3" t="n">
-        <v>1970.33</v>
+        <v>524.8</v>
       </c>
       <c r="L3" t="n">
-        <v>10.88</v>
+        <v>7.85</v>
       </c>
       <c r="M3" t="n">
-        <v>31.14</v>
+        <v>10.93</v>
       </c>
       <c r="N3" t="n">
-        <v>38.84</v>
+        <v>10.48</v>
       </c>
       <c r="O3" t="n">
-        <v>-7.71</v>
+        <v>0.45</v>
       </c>
       <c r="P3" t="n">
-        <v>55.71</v>
+        <v>15.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.16</v>
+        <v>13.76</v>
       </c>
       <c r="R3" t="n">
-        <v>46.6</v>
+        <v>44.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.51</v>
+        <v>-1.75</v>
       </c>
       <c r="U3" t="n">
-        <v>54.1</v>
+        <v>50</v>
       </c>
       <c r="V3" t="n">
-        <v>4.03</v>
+        <v>4.49</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>2207.73</v>
+        <v>567.15</v>
       </c>
       <c r="Y3" t="n">
-        <v>2458.3</v>
+        <v>653.3099999999999</v>
       </c>
       <c r="Z3" t="n">
-        <v>2458.3</v>
+        <v>653.3099999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>2131.13</v>
+        <v>549.45</v>
       </c>
       <c r="AB3" t="n">
-        <v>2203.4</v>
+        <v>569.42</v>
       </c>
       <c r="AC3" t="n">
-        <v>2230.3</v>
+        <v>576.34</v>
       </c>
       <c r="AD3" t="n">
-        <v>2245.9</v>
+        <v>580.02</v>
       </c>
       <c r="AE3" t="n">
-        <v>43.6</v>
+        <v>57</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.16) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>50.2</v>
+        <v>5.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>5.2</v>
+        <v>65.2</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>2278.76</v>
+        <v>587.8</v>
       </c>
       <c r="AN3" t="n">
-        <v>2152.14</v>
+        <v>558.2</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹61,493.01 Cr., a P/E ratio of 50.19, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,499.36 Cr., a P/E ratio of 5.49, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 43.57 (Consolidation Zone), while MACD Line (31.14) trades below Signal (38.84) with an expanding histogram (-7.71). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.88% above the 200-day DMA (₹1970.33). Daily volatility envelope is bounded by ATR(14) of ₹55.71.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.02 (Bullish Momentum Zone), while MACD Line (10.93) trades above Signal (10.48) with an expanding histogram (+0.45). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.85% above the 200-day DMA (₹524.80). Daily volatility envelope is bounded by ATR(14) of ₹15.46.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,214.70) is positioned above the 30-day DMA (₹2,166.54), 50-day DMA (₹2,057.09), and 200-day DMA (₹1,970.33). The price distance from 200 DMA is +10.88%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹572.65) is positioned above the 30-day DMA (₹538.18), 50-day DMA (₹528.61), and 200-day DMA (₹524.80). The price distance from 200 DMA is +7.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[2214.7, 2221.34, 2227.99, 2234.63, 2241.28, 2247.92]</t>
+          <t>[572.65, 574.37, 576.09, 577.8, 579.52, 581.24]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[2214.7, 2243.63, 2259.5, 2273.23, 2285.85, 2297.75]</t>
+          <t>[572.65, 580.55, 584.83, 588.52, 591.89, 595.07]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[2214.7, 2204.63, 2204.35, 2205.68, 2207.85, 2210.55]</t>
+          <t>[572.65, 569.73, 569.52, 569.77, 570.24, 570.87]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2458.3</v>
+        <v>653.3099999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62046.36</v>
+        <v>60596.17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1029</v>
+        <v>2182.4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹1023.36 - ₹1037.46</t>
+          <t>₹2171.45 - ₹2198.82</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1051.57</v>
+        <v>2226.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1005.95</v>
+        <v>2171.19</v>
       </c>
       <c r="J4" t="n">
-        <v>960.59</v>
+        <v>2065.61</v>
       </c>
       <c r="K4" t="n">
-        <v>854.66</v>
+        <v>1972.76</v>
       </c>
       <c r="L4" t="n">
-        <v>19.58</v>
+        <v>12.26</v>
       </c>
       <c r="M4" t="n">
-        <v>12.13</v>
+        <v>31.51</v>
       </c>
       <c r="N4" t="n">
-        <v>15.35</v>
+        <v>37.38</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.23</v>
+        <v>-5.86</v>
       </c>
       <c r="P4" t="n">
-        <v>28.21</v>
+        <v>54.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.16</v>
+        <v>13.76</v>
       </c>
       <c r="R4" t="n">
-        <v>45.5</v>
+        <v>42.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.73</v>
+        <v>-1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>50.8</v>
+        <v>53.3</v>
       </c>
       <c r="V4" t="n">
-        <v>3.47</v>
+        <v>3.61</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>1029</v>
+        <v>2182.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1205.34</v>
+        <v>2422.44</v>
       </c>
       <c r="Z4" t="n">
-        <v>1205.34</v>
+        <v>2422.44</v>
       </c>
       <c r="AA4" t="n">
-        <v>986.6900000000001</v>
+        <v>2100.27</v>
       </c>
       <c r="AB4" t="n">
-        <v>1031.8</v>
+        <v>2190.07</v>
       </c>
       <c r="AC4" t="n">
-        <v>1044.2</v>
+        <v>2202.54</v>
       </c>
       <c r="AD4" t="n">
-        <v>1059.4</v>
+        <v>2222.67</v>
       </c>
       <c r="AE4" t="n">
-        <v>46.8</v>
+        <v>50.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.17</v>
+        <v>0.1</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (12.16) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>31.9</v>
+        <v>49.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23.9</v>
+        <v>8.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>5.2</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>1070.79</v>
+        <v>2247.49</v>
       </c>
       <c r="AN4" t="n">
-        <v>988.99</v>
+        <v>2119.76</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹62,046.36 Cr., a P/E ratio of 31.95, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,596.17 Cr., a P/E ratio of 49.45, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 46.82 (Consolidation Zone), while MACD Line (12.13) trades below Signal (15.35) with an expanding histogram (-3.23). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.58% above the 200-day DMA (₹854.66). Daily volatility envelope is bounded by ATR(14) of ₹28.21.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.94 (Consolidation Zone), while MACD Line (31.51) trades below Signal (37.38) with an expanding histogram (-5.86). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1972.76). Daily volatility envelope is bounded by ATR(14) of ₹54.75.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,029.00) is positioned above the 30-day DMA (₹1,005.95), 50-day DMA (₹960.59), and 200-day DMA (₹854.66). The price distance from 200 DMA is +19.58%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,182.40) is positioned above the 30-day DMA (₹2,171.19), 50-day DMA (₹2,065.61), and 200-day DMA (₹1,972.76). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[1029.0, 1033.14, 1037.27, 1041.41, 1045.54, 1049.68]</t>
+          <t>[2182.4, 2192.92, 2203.45, 2213.97, 2224.5, 2235.02]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[1029.0, 1044.42, 1053.23, 1060.95, 1068.11, 1074.91]</t>
+          <t>[2182.4, 2214.82, 2234.42, 2251.9, 2268.3, 2283.99]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[1029.0, 1024.67, 1025.3, 1026.75, 1028.62, 1030.76]</t>
+          <t>[2182.4, 2176.5, 2180.22, 2185.52, 2191.65, 2198.29]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1205.34</v>
+        <v>2422.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>308380.67</v>
+        <v>61292.64</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,166 +1179,166 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>335</v>
+        <v>1016.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹333.59 - ₹337.11</t>
+          <t>₹1010.86 - ₹1024.96</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>340.63</v>
+        <v>1039.07</v>
       </c>
       <c r="I5" t="n">
-        <v>325.68</v>
+        <v>1010.12</v>
       </c>
       <c r="J5" t="n">
-        <v>316.72</v>
+        <v>961.83</v>
       </c>
       <c r="K5" t="n">
-        <v>275.54</v>
+        <v>855.67</v>
       </c>
       <c r="L5" t="n">
-        <v>21.76</v>
+        <v>20.26</v>
       </c>
       <c r="M5" t="n">
-        <v>5.34</v>
+        <v>12.48</v>
       </c>
       <c r="N5" t="n">
-        <v>4.18</v>
+        <v>14.78</v>
       </c>
       <c r="O5" t="n">
-        <v>1.16</v>
+        <v>-2.3</v>
       </c>
       <c r="P5" t="n">
-        <v>7.03</v>
+        <v>28.21</v>
       </c>
       <c r="Q5" t="n">
-        <v>12.16</v>
+        <v>13.76</v>
       </c>
       <c r="R5" t="n">
-        <v>43.2</v>
+        <v>41.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.32</v>
+        <v>-1.97</v>
       </c>
       <c r="U5" t="n">
-        <v>54.1</v>
+        <v>50</v>
       </c>
       <c r="V5" t="n">
-        <v>2.49</v>
+        <v>3.74</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>335</v>
+        <v>1005.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>372.41</v>
+        <v>1190.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>372.41</v>
+        <v>1190.7</v>
       </c>
       <c r="AA5" t="n">
-        <v>324.45</v>
+        <v>974.1799999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>335.53</v>
+        <v>1016.47</v>
       </c>
       <c r="AC5" t="n">
-        <v>339.36</v>
+        <v>1033.44</v>
       </c>
       <c r="AD5" t="n">
-        <v>343.73</v>
+        <v>1050.37</v>
       </c>
       <c r="AE5" t="n">
-        <v>62.9</v>
+        <v>44.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (12.16) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>712.8</v>
+        <v>31.6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>182</v>
+        <v>23.9</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.6</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>346.66</v>
+        <v>1058.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>324.4</v>
+        <v>977.7</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹308,380.67 Cr., a P/E ratio of 712.77, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹61,292.64 Cr., a P/E ratio of 31.56, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.89 (Bullish Momentum Zone), while MACD Line (5.34) trades above Signal (4.18) with an expanding histogram (+1.16). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.76% above the 200-day DMA (₹275.54). Daily volatility envelope is bounded by ATR(14) of ₹7.03.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.22 (Consolidation Zone), while MACD Line (12.48) trades below Signal (14.78) with an expanding histogram (-2.30). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.26% above the 200-day DMA (₹855.67). Daily volatility envelope is bounded by ATR(14) of ₹28.21.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹335.00) is positioned above the 30-day DMA (₹325.68), 50-day DMA (₹316.72), and 200-day DMA (₹275.54). The price distance from 200 DMA is +21.76%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,016.50) is positioned above the 30-day DMA (₹1,010.12), 50-day DMA (₹961.83), and 200-day DMA (₹855.67). The price distance from 200 DMA is +20.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[335.0, 336.0, 337.01, 338.01, 339.02, 340.02]</t>
+          <t>[1016.5, 1019.55, 1022.6, 1025.65, 1028.7, 1031.75]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[335.0, 338.82, 340.99, 342.89, 344.65, 346.31]</t>
+          <t>[1016.5, 1030.84, 1038.56, 1045.2, 1051.27, 1056.98]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[335.0, 333.9, 334.03, 334.36, 334.8, 335.31]</t>
+          <t>[1016.5, 1011.09, 1010.63, 1010.99, 1011.77, 1012.82]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>372.41</v>
+        <v>1190.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31133.56</v>
+        <v>302811.42</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,146 +1346,146 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>566</v>
+        <v>328.95</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹562.78 - ₹570.82</t>
+          <t>₹327.51 - ₹331.11</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>578.87</v>
+        <v>334.7</v>
       </c>
       <c r="I6" t="n">
-        <v>535.66</v>
+        <v>326.23</v>
       </c>
       <c r="J6" t="n">
-        <v>528.0700000000001</v>
+        <v>317.69</v>
       </c>
       <c r="K6" t="n">
-        <v>524.5700000000001</v>
+        <v>275.8</v>
       </c>
       <c r="L6" t="n">
-        <v>7.56</v>
+        <v>21.47</v>
       </c>
       <c r="M6" t="n">
-        <v>11.03</v>
+        <v>5.31</v>
       </c>
       <c r="N6" t="n">
-        <v>10.37</v>
+        <v>4.41</v>
       </c>
       <c r="O6" t="n">
-        <v>0.66</v>
+        <v>0.9</v>
       </c>
       <c r="P6" t="n">
-        <v>16.08</v>
+        <v>7.19</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.16</v>
+        <v>13.76</v>
       </c>
       <c r="R6" t="n">
-        <v>41.4</v>
+        <v>40.3</v>
       </c>
       <c r="S6" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.01</v>
+        <v>-1.51</v>
       </c>
       <c r="U6" t="n">
-        <v>49.2</v>
+        <v>51.7</v>
       </c>
       <c r="V6" t="n">
-        <v>4.46</v>
+        <v>2.47</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>559.59</v>
+        <v>328.95</v>
       </c>
       <c r="Y6" t="n">
-        <v>645.73</v>
+        <v>365.68</v>
       </c>
       <c r="Z6" t="n">
-        <v>645.73</v>
+        <v>365.68</v>
       </c>
       <c r="AA6" t="n">
-        <v>541.88</v>
+        <v>318.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>564.72</v>
+        <v>330.93</v>
       </c>
       <c r="AC6" t="n">
-        <v>570.84</v>
+        <v>333.11</v>
       </c>
       <c r="AD6" t="n">
-        <v>575.67</v>
+        <v>337.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>51</v>
+        <v>64.8</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (12.16) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.76) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.4</v>
+        <v>699.9</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14.5</v>
+        <v>182</v>
       </c>
       <c r="AK6" t="n">
-        <v>65.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL6" t="n">
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>579.84</v>
+        <v>340.42</v>
       </c>
       <c r="AN6" t="n">
-        <v>551.53</v>
+        <v>318.12</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,133.56 Cr., a P/E ratio of 5.43, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹302,811.42 Cr., a P/E ratio of 699.89, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.02 (Consolidation Zone), while MACD Line (11.03) trades above Signal (10.37) with an expanding histogram (+0.66). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.56% above the 200-day DMA (₹524.57). Daily volatility envelope is bounded by ATR(14) of ₹16.08.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.79 (Bullish Momentum Zone), while MACD Line (5.31) trades above Signal (4.41) with an expanding histogram (+0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.47% above the 200-day DMA (₹275.80). Daily volatility envelope is bounded by ATR(14) of ₹7.19.</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹566.00) is positioned above the 30-day DMA (₹535.66), 50-day DMA (₹528.07), and 200-day DMA (₹524.57). The price distance from 200 DMA is +7.56%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹328.95) is positioned above the 30-day DMA (₹326.23), 50-day DMA (₹317.69), and 200-day DMA (₹275.80). The price distance from 200 DMA is +21.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[566.0, 567.7, 569.4, 571.09, 572.79, 574.49]</t>
+          <t>[328.95, 329.97, 330.99, 332.01, 333.03, 334.04]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[566.0, 574.13, 578.49, 582.24, 585.66, 588.87]</t>
+          <t>[328.95, 332.84, 335.05, 336.99, 338.77, 340.47]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[566.0, 562.87, 562.57, 562.74, 563.14, 563.7]</t>
+          <t>[328.95, 327.81, 327.94, 328.27, 328.71, 329.22]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>645.73</v>
+        <v>365.68</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU6"/>
+  <dimension ref="A1:AU5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43627.51</v>
+        <v>43477.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,15 +678,15 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>290.85</v>
+        <v>289.85</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹289.75 - ₹292.5</t>
+          <t>₹288.75 - ₹291.5</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>295.25</v>
+        <v>294.25</v>
       </c>
       <c r="I2" t="n">
         <v>288.56</v>
@@ -713,46 +713,46 @@
         <v>5.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.76</v>
+        <v>13.64</v>
       </c>
       <c r="R2" t="n">
-        <v>47.9</v>
+        <v>47.6</v>
       </c>
       <c r="S2" t="n">
         <v>0.28</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.99</v>
+        <v>-1</v>
       </c>
       <c r="U2" t="n">
         <v>55</v>
       </c>
       <c r="V2" t="n">
-        <v>5.28</v>
+        <v>5.27</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>290.85</v>
+        <v>289.85</v>
       </c>
       <c r="Y2" t="n">
-        <v>318.95</v>
+        <v>317.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>318.95</v>
+        <v>317.85</v>
       </c>
       <c r="AA2" t="n">
-        <v>282.6</v>
+        <v>281.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>289.88</v>
+        <v>289.55</v>
       </c>
       <c r="AC2" t="n">
-        <v>294.01</v>
+        <v>293.35</v>
       </c>
       <c r="AD2" t="n">
-        <v>297.18</v>
+        <v>296.85</v>
       </c>
       <c r="AE2" t="n">
         <v>44.6</v>
@@ -762,14 +762,14 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Low VIX (13.76) | LSTM Deep Net</t>
+          <t>Low VIX (13.64) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="AJ2" t="n">
         <v>-53.2</v>
@@ -781,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>299.94</v>
+        <v>298.59</v>
       </c>
       <c r="AN2" t="n">
-        <v>282.59</v>
+        <v>281.32</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,627.51 Cr., a P/E ratio of 10.37, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,477.50 Cr., a P/E ratio of 10.33, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -798,26 +798,26 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹290.85) is positioned above the 30-day DMA (₹288.56), 50-day DMA (₹284.53), and 200-day DMA (₹279.21). The price distance from 200 DMA is +2.61%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹289.85) is positioned above the 30-day DMA (₹288.56), 50-day DMA (₹284.53), and 200-day DMA (₹279.21). The price distance from 200 DMA is +2.61%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[290.85, 291.72, 292.6, 293.47, 294.34, 295.21]</t>
+          <t>[289.85, 290.72, 291.59, 292.46, 293.33, 294.2]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[290.85, 293.92, 295.71, 297.28, 298.74, 300.13]</t>
+          <t>[289.85, 292.92, 294.7, 296.27, 297.73, 299.12]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[290.85, 290.07, 290.26, 290.61, 291.04, 291.52]</t>
+          <t>[289.85, 289.07, 289.26, 289.6, 290.03, 290.51]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>318.95</v>
+        <v>317.85</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31499.36</v>
+        <v>61001.55</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>572.65</v>
+        <v>2197</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹569.56 - ₹577.29</t>
+          <t>₹2186.05 - ₹2213.43</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>585.02</v>
+        <v>2240.8</v>
       </c>
       <c r="I3" t="n">
-        <v>538.1799999999999</v>
+        <v>2171.19</v>
       </c>
       <c r="J3" t="n">
-        <v>528.61</v>
+        <v>2065.61</v>
       </c>
       <c r="K3" t="n">
-        <v>524.8</v>
+        <v>1972.76</v>
       </c>
       <c r="L3" t="n">
-        <v>7.85</v>
+        <v>12.26</v>
       </c>
       <c r="M3" t="n">
-        <v>10.93</v>
+        <v>31.51</v>
       </c>
       <c r="N3" t="n">
-        <v>10.48</v>
+        <v>37.38</v>
       </c>
       <c r="O3" t="n">
-        <v>0.45</v>
+        <v>-5.86</v>
       </c>
       <c r="P3" t="n">
-        <v>15.46</v>
+        <v>54.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.76</v>
+        <v>13.64</v>
       </c>
       <c r="R3" t="n">
-        <v>44.5</v>
+        <v>42</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.75</v>
+        <v>-1.7</v>
       </c>
       <c r="U3" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="V3" t="n">
-        <v>4.49</v>
+        <v>3.61</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>567.15</v>
+        <v>2197</v>
       </c>
       <c r="Y3" t="n">
-        <v>653.3099999999999</v>
+        <v>2438.65</v>
       </c>
       <c r="Z3" t="n">
-        <v>653.3099999999999</v>
+        <v>2438.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>549.45</v>
+        <v>2114.87</v>
       </c>
       <c r="AB3" t="n">
-        <v>569.42</v>
+        <v>2194.03</v>
       </c>
       <c r="AC3" t="n">
-        <v>576.34</v>
+        <v>2213.16</v>
       </c>
       <c r="AD3" t="n">
-        <v>580.02</v>
+        <v>2229.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>57</v>
+        <v>50.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.64) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.5</v>
+        <v>49.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14.5</v>
+        <v>8.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>65.2</v>
+        <v>5.2</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>587.8</v>
+        <v>2262.8</v>
       </c>
       <c r="AN3" t="n">
-        <v>558.2</v>
+        <v>2137.47</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,499.36 Cr., a P/E ratio of 5.49, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹61,001.55 Cr., a P/E ratio of 49.60, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.02 (Bullish Momentum Zone), while MACD Line (10.93) trades above Signal (10.48) with an expanding histogram (+0.45). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.85% above the 200-day DMA (₹524.80). Daily volatility envelope is bounded by ATR(14) of ₹15.46.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.94 (Consolidation Zone), while MACD Line (31.51) trades below Signal (37.38) with an expanding histogram (-5.86). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1972.76). Daily volatility envelope is bounded by ATR(14) of ₹54.75.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹572.65) is positioned above the 30-day DMA (₹538.18), 50-day DMA (₹528.61), and 200-day DMA (₹524.80). The price distance from 200 DMA is +7.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,197.00) is positioned above the 30-day DMA (₹2,171.19), 50-day DMA (₹2,065.61), and 200-day DMA (₹1,972.76). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[572.65, 574.37, 576.09, 577.8, 579.52, 581.24]</t>
+          <t>[2197.0, 2211.85, 2226.69, 2241.54, 2256.38, 2271.23]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[572.65, 580.55, 584.83, 588.52, 591.89, 595.07]</t>
+          <t>[2197.0, 2233.75, 2257.66, 2279.47, 2300.18, 2320.2]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[572.65, 569.73, 569.52, 569.77, 570.24, 570.87]</t>
+          <t>[2197.0, 2195.42, 2203.46, 2213.09, 2223.53, 2234.5]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>653.3099999999999</v>
+        <v>2438.65</v>
       </c>
     </row>
     <row r="4">
@@ -995,16 +995,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60596.17</v>
+        <v>304652.51</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,146 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2182.4</v>
+        <v>330.95</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹2171.45 - ₹2198.82</t>
+          <t>₹329.51 - ₹333.11</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2226.2</v>
+        <v>336.7</v>
       </c>
       <c r="I4" t="n">
-        <v>2171.19</v>
+        <v>326.23</v>
       </c>
       <c r="J4" t="n">
-        <v>2065.61</v>
+        <v>317.69</v>
       </c>
       <c r="K4" t="n">
-        <v>1972.76</v>
+        <v>275.8</v>
       </c>
       <c r="L4" t="n">
-        <v>12.26</v>
+        <v>21.47</v>
       </c>
       <c r="M4" t="n">
-        <v>31.51</v>
+        <v>5.31</v>
       </c>
       <c r="N4" t="n">
-        <v>37.38</v>
+        <v>4.41</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.86</v>
+        <v>0.9</v>
       </c>
       <c r="P4" t="n">
-        <v>54.75</v>
+        <v>7.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.76</v>
+        <v>13.64</v>
       </c>
       <c r="R4" t="n">
-        <v>42.6</v>
+        <v>40</v>
       </c>
       <c r="S4" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.68</v>
+        <v>-1.51</v>
       </c>
       <c r="U4" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="V4" t="n">
-        <v>3.61</v>
+        <v>2.46</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2182.4</v>
+        <v>330.95</v>
       </c>
       <c r="Y4" t="n">
-        <v>2422.44</v>
+        <v>367.91</v>
       </c>
       <c r="Z4" t="n">
-        <v>2422.44</v>
+        <v>367.91</v>
       </c>
       <c r="AA4" t="n">
-        <v>2100.27</v>
+        <v>320.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>2190.07</v>
+        <v>331.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>2202.54</v>
+        <v>334.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>2222.67</v>
+        <v>338.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>50.9</v>
+        <v>64.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.64) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>49.5</v>
+        <v>704.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>8.5</v>
+        <v>182</v>
       </c>
       <c r="AK4" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>2247.49</v>
+        <v>343.1</v>
       </c>
       <c r="AN4" t="n">
-        <v>2119.76</v>
+        <v>319.32</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,596.17 Cr., a P/E ratio of 49.45, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹304,652.51 Cr., a P/E ratio of 704.15, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.94 (Consolidation Zone), while MACD Line (31.51) trades below Signal (37.38) with an expanding histogram (-5.86). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1972.76). Daily volatility envelope is bounded by ATR(14) of ₹54.75.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.79 (Bullish Momentum Zone), while MACD Line (5.31) trades above Signal (4.41) with an expanding histogram (+0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.47% above the 200-day DMA (₹275.80). Daily volatility envelope is bounded by ATR(14) of ₹7.19.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,182.40) is positioned above the 30-day DMA (₹2,171.19), 50-day DMA (₹2,065.61), and 200-day DMA (₹1,972.76). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹330.95) is positioned above the 30-day DMA (₹326.23), 50-day DMA (₹317.69), and 200-day DMA (₹275.80). The price distance from 200 DMA is +21.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[2182.4, 2192.92, 2203.45, 2213.97, 2224.5, 2235.02]</t>
+          <t>[330.95, 332.09, 333.23, 334.38, 335.52, 336.66]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[2182.4, 2214.82, 2234.42, 2251.9, 2268.3, 2283.99]</t>
+          <t>[330.95, 334.97, 337.3, 339.35, 341.27, 343.09]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[2182.4, 2176.5, 2180.22, 2185.52, 2191.65, 2198.29]</t>
+          <t>[330.95, 329.94, 330.19, 330.64, 331.21, 331.84]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2422.44</v>
+        <v>367.91</v>
       </c>
     </row>
     <row r="5">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61292.64</v>
+        <v>31031.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,313 +1179,146 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1016.5</v>
+        <v>564.15</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹1010.86 - ₹1024.96</t>
+          <t>₹561.06 - ₹568.79</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1039.07</v>
+        <v>576.52</v>
       </c>
       <c r="I5" t="n">
-        <v>1010.12</v>
+        <v>538.1799999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>961.83</v>
+        <v>528.61</v>
       </c>
       <c r="K5" t="n">
-        <v>855.67</v>
+        <v>524.8</v>
       </c>
       <c r="L5" t="n">
-        <v>20.26</v>
+        <v>7.85</v>
       </c>
       <c r="M5" t="n">
-        <v>12.48</v>
+        <v>10.93</v>
       </c>
       <c r="N5" t="n">
-        <v>14.78</v>
+        <v>10.48</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.3</v>
+        <v>0.45</v>
       </c>
       <c r="P5" t="n">
-        <v>28.21</v>
+        <v>15.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.76</v>
+        <v>13.64</v>
       </c>
       <c r="R5" t="n">
-        <v>41.2</v>
+        <v>38.9</v>
       </c>
       <c r="S5" t="n">
         <v>0.19</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.97</v>
+        <v>-2.05</v>
       </c>
       <c r="U5" t="n">
-        <v>50</v>
+        <v>48.3</v>
       </c>
       <c r="V5" t="n">
-        <v>3.74</v>
+        <v>4.47</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>1005.8</v>
+        <v>558.45</v>
       </c>
       <c r="Y5" t="n">
-        <v>1190.7</v>
+        <v>643.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>1190.7</v>
+        <v>643.61</v>
       </c>
       <c r="AA5" t="n">
-        <v>974.1799999999999</v>
+        <v>540.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1016.47</v>
+        <v>567.12</v>
       </c>
       <c r="AC5" t="n">
-        <v>1033.44</v>
+        <v>571.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>1050.37</v>
+        <v>579.3200000000001</v>
       </c>
       <c r="AE5" t="n">
-        <v>44.2</v>
+        <v>57</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.76) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.64) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>31.6</v>
+        <v>5.4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>23.9</v>
+        <v>14.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>65.2</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1058.36</v>
+        <v>579.21</v>
       </c>
       <c r="AN5" t="n">
-        <v>977.7</v>
+        <v>547.73</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹61,292.64 Cr., a P/E ratio of 31.56, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,031.80 Cr., a P/E ratio of 5.41, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.22 (Consolidation Zone), while MACD Line (12.48) trades below Signal (14.78) with an expanding histogram (-2.30). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +20.26% above the 200-day DMA (₹855.67). Daily volatility envelope is bounded by ATR(14) of ₹28.21.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.02 (Bullish Momentum Zone), while MACD Line (10.93) trades above Signal (10.48) with an expanding histogram (+0.45). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.85% above the 200-day DMA (₹524.80). Daily volatility envelope is bounded by ATR(14) of ₹15.46.</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,016.50) is positioned above the 30-day DMA (₹1,010.12), 50-day DMA (₹961.83), and 200-day DMA (₹855.67). The price distance from 200 DMA is +20.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹564.15) is positioned above the 30-day DMA (₹538.18), 50-day DMA (₹528.61), and 200-day DMA (₹524.80). The price distance from 200 DMA is +7.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[1016.5, 1019.55, 1022.6, 1025.65, 1028.7, 1031.75]</t>
+          <t>[564.15, 565.84, 567.53, 569.23, 570.92, 572.61]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[1016.5, 1030.84, 1038.56, 1045.2, 1051.27, 1056.98]</t>
+          <t>[564.15, 572.03, 576.28, 579.94, 583.29, 586.44]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[1016.5, 1011.09, 1010.63, 1010.99, 1011.77, 1012.82]</t>
+          <t>[564.15, 561.2, 560.97, 561.19, 561.64, 562.24]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1190.7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>302811.42</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>328.95</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>₹327.51 - ₹331.11</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>334.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>326.23</v>
-      </c>
-      <c r="J6" t="n">
-        <v>317.69</v>
-      </c>
-      <c r="K6" t="n">
-        <v>275.8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>21.47</v>
-      </c>
-      <c r="M6" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="N6" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="P6" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>13.76</v>
-      </c>
-      <c r="R6" t="n">
-        <v>40.3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-1.51</v>
-      </c>
-      <c r="U6" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X6" t="n">
-        <v>328.95</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>365.68</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>365.68</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>318.17</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>330.93</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>333.11</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>337.28</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.76) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>699.9</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>182</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>340.42</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>318.12</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹302,811.42 Cr., a P/E ratio of 699.89, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.79 (Bullish Momentum Zone), while MACD Line (5.31) trades above Signal (4.41) with an expanding histogram (+0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.47% above the 200-day DMA (₹275.80). Daily volatility envelope is bounded by ATR(14) of ₹7.19.</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹328.95) is positioned above the 30-day DMA (₹326.23), 50-day DMA (₹317.69), and 200-day DMA (₹275.80). The price distance from 200 DMA is +21.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>[328.95, 329.97, 330.99, 332.01, 333.03, 334.04]</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>[328.95, 332.84, 335.05, 336.99, 338.77, 340.47]</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>[328.95, 327.81, 327.94, 328.27, 328.71, 329.22]</t>
-        </is>
-      </c>
-      <c r="AU6" t="n">
-        <v>365.68</v>
+        <v>643.61</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AU4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,7 +716,7 @@
         <v>13.64</v>
       </c>
       <c r="R2" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="S2" t="n">
         <v>0.28</v>
@@ -734,13 +734,13 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>289.85</v>
+        <v>281.16</v>
       </c>
       <c r="Y2" t="n">
-        <v>317.85</v>
+        <v>270.06</v>
       </c>
       <c r="Z2" t="n">
-        <v>317.85</v>
+        <v>263.35</v>
       </c>
       <c r="AA2" t="n">
         <v>281.6</v>
@@ -769,7 +769,7 @@
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="AJ2" t="n">
         <v>-53.2</v>
@@ -781,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>298.59</v>
+        <v>298.52</v>
       </c>
       <c r="AN2" t="n">
-        <v>281.32</v>
+        <v>281.81</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,477.50 Cr., a P/E ratio of 10.33, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,477.50 Cr., a P/E ratio of 10.21, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>317.85</v>
+        <v>263.35</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>61001.55</v>
+        <v>304652.51</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2197</v>
+        <v>330.95</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹2186.05 - ₹2213.43</t>
+          <t>₹329.51 - ₹333.11</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2240.8</v>
+        <v>336.7</v>
       </c>
       <c r="I3" t="n">
-        <v>2171.19</v>
+        <v>326.23</v>
       </c>
       <c r="J3" t="n">
-        <v>2065.61</v>
+        <v>317.69</v>
       </c>
       <c r="K3" t="n">
-        <v>1972.76</v>
+        <v>275.8</v>
       </c>
       <c r="L3" t="n">
-        <v>12.26</v>
+        <v>21.47</v>
       </c>
       <c r="M3" t="n">
-        <v>31.51</v>
+        <v>5.31</v>
       </c>
       <c r="N3" t="n">
-        <v>37.38</v>
+        <v>4.41</v>
       </c>
       <c r="O3" t="n">
-        <v>-5.86</v>
+        <v>0.9</v>
       </c>
       <c r="P3" t="n">
-        <v>54.75</v>
+        <v>7.19</v>
       </c>
       <c r="Q3" t="n">
         <v>13.64</v>
       </c>
       <c r="R3" t="n">
-        <v>42</v>
+        <v>40.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.7</v>
+        <v>-1.49</v>
       </c>
       <c r="U3" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="V3" t="n">
-        <v>3.61</v>
+        <v>2.46</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>2197</v>
+        <v>324.72</v>
       </c>
       <c r="Y3" t="n">
-        <v>2438.65</v>
+        <v>314.03</v>
       </c>
       <c r="Z3" t="n">
-        <v>2438.65</v>
+        <v>303.76</v>
       </c>
       <c r="AA3" t="n">
-        <v>2114.87</v>
+        <v>320.17</v>
       </c>
       <c r="AB3" t="n">
-        <v>2194.03</v>
+        <v>331.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>2213.16</v>
+        <v>334.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>2229.33</v>
+        <v>338.15</v>
       </c>
       <c r="AE3" t="n">
-        <v>50.9</v>
+        <v>64.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.64) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.64) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>49.6</v>
+        <v>719.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8.5</v>
+        <v>182</v>
       </c>
       <c r="AK3" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>2262.8</v>
+        <v>342.66</v>
       </c>
       <c r="AN3" t="n">
-        <v>2137.47</v>
+        <v>320.09</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹61,001.55 Cr., a P/E ratio of 49.60, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹304,652.51 Cr., a P/E ratio of 719.46, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.94 (Consolidation Zone), while MACD Line (31.51) trades below Signal (37.38) with an expanding histogram (-5.86). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1972.76). Daily volatility envelope is bounded by ATR(14) of ₹54.75.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.79 (Bullish Momentum Zone), while MACD Line (5.31) trades above Signal (4.41) with an expanding histogram (+0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.47% above the 200-day DMA (₹275.80). Daily volatility envelope is bounded by ATR(14) of ₹7.19.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,197.00) is positioned above the 30-day DMA (₹2,171.19), 50-day DMA (₹2,065.61), and 200-day DMA (₹1,972.76). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹330.95) is positioned above the 30-day DMA (₹326.23), 50-day DMA (₹317.69), and 200-day DMA (₹275.80). The price distance from 200 DMA is +21.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[2197.0, 2211.85, 2226.69, 2241.54, 2256.38, 2271.23]</t>
+          <t>[330.95, 332.09, 333.23, 334.38, 335.52, 336.66]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[2197.0, 2233.75, 2257.66, 2279.47, 2300.18, 2320.2]</t>
+          <t>[330.95, 334.97, 337.3, 339.35, 341.27, 343.09]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[2197.0, 2195.42, 2203.46, 2213.09, 2223.53, 2234.5]</t>
+          <t>[330.95, 329.94, 330.19, 330.64, 331.21, 331.84]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2438.65</v>
+        <v>303.76</v>
       </c>
     </row>
     <row r="4">
@@ -995,16 +995,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>304652.51</v>
+        <v>31031.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,313 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>330.95</v>
+        <v>564.15</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹329.51 - ₹333.11</t>
+          <t>₹561.06 - ₹568.79</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>336.7</v>
+        <v>576.52</v>
       </c>
       <c r="I4" t="n">
-        <v>326.23</v>
+        <v>538.1799999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>317.69</v>
+        <v>528.61</v>
       </c>
       <c r="K4" t="n">
-        <v>275.8</v>
+        <v>524.8</v>
       </c>
       <c r="L4" t="n">
-        <v>21.47</v>
+        <v>7.85</v>
       </c>
       <c r="M4" t="n">
-        <v>5.31</v>
+        <v>10.93</v>
       </c>
       <c r="N4" t="n">
-        <v>4.41</v>
+        <v>10.48</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9</v>
+        <v>0.45</v>
       </c>
       <c r="P4" t="n">
-        <v>7.19</v>
+        <v>15.46</v>
       </c>
       <c r="Q4" t="n">
         <v>13.64</v>
       </c>
       <c r="R4" t="n">
-        <v>40</v>
+        <v>38.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.51</v>
+        <v>-2.07</v>
       </c>
       <c r="U4" t="n">
-        <v>51.7</v>
+        <v>48.3</v>
       </c>
       <c r="V4" t="n">
-        <v>2.46</v>
+        <v>4.47</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>330.95</v>
+        <v>541.5599999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>367.91</v>
+        <v>515.3099999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>367.91</v>
+        <v>500.09</v>
       </c>
       <c r="AA4" t="n">
-        <v>320.17</v>
+        <v>540.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>331.5</v>
+        <v>567.12</v>
       </c>
       <c r="AC4" t="n">
-        <v>334.55</v>
+        <v>571.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>338.15</v>
+        <v>579.3200000000001</v>
       </c>
       <c r="AE4" t="n">
-        <v>64.8</v>
+        <v>57</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.64) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.64) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>704.1</v>
+        <v>5.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>182</v>
+        <v>14.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.6</v>
+        <v>65.2</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>343.1</v>
+        <v>578.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>319.32</v>
+        <v>550.16</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹304,652.51 Cr., a P/E ratio of 704.15, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,031.80 Cr., a P/E ratio of 5.43, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.79 (Bullish Momentum Zone), while MACD Line (5.31) trades above Signal (4.41) with an expanding histogram (+0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.47% above the 200-day DMA (₹275.80). Daily volatility envelope is bounded by ATR(14) of ₹7.19.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.02 (Bullish Momentum Zone), while MACD Line (10.93) trades above Signal (10.48) with an expanding histogram (+0.45). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.85% above the 200-day DMA (₹524.80). Daily volatility envelope is bounded by ATR(14) of ₹15.46.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹330.95) is positioned above the 30-day DMA (₹326.23), 50-day DMA (₹317.69), and 200-day DMA (₹275.80). The price distance from 200 DMA is +21.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹564.15) is positioned above the 30-day DMA (₹538.18), 50-day DMA (₹528.61), and 200-day DMA (₹524.80). The price distance from 200 DMA is +7.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[330.95, 332.09, 333.23, 334.38, 335.52, 336.66]</t>
+          <t>[564.15, 565.84, 567.53, 569.23, 570.92, 572.61]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[330.95, 334.97, 337.3, 339.35, 341.27, 343.09]</t>
+          <t>[564.15, 572.03, 576.28, 579.94, 583.29, 586.44]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[330.95, 329.94, 330.19, 330.64, 331.21, 331.84]</t>
+          <t>[564.15, 561.2, 560.97, 561.19, 561.64, 562.24]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>367.91</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>31031.8</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>564.15</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>₹561.06 - ₹568.79</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>576.52</v>
-      </c>
-      <c r="I5" t="n">
-        <v>538.1799999999999</v>
-      </c>
-      <c r="J5" t="n">
-        <v>528.61</v>
-      </c>
-      <c r="K5" t="n">
-        <v>524.8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="M5" t="n">
-        <v>10.93</v>
-      </c>
-      <c r="N5" t="n">
-        <v>10.48</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P5" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="R5" t="n">
-        <v>38.9</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="U5" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X5" t="n">
-        <v>558.45</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>643.61</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>643.61</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>540.95</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>567.12</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>571.74</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>579.3200000000001</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>57</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.64) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>579.21</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>547.73</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,031.80 Cr., a P/E ratio of 5.41, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.02 (Bullish Momentum Zone), while MACD Line (10.93) trades above Signal (10.48) with an expanding histogram (+0.45). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.85% above the 200-day DMA (₹524.80). Daily volatility envelope is bounded by ATR(14) of ₹15.46.</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹564.15) is positioned above the 30-day DMA (₹538.18), 50-day DMA (₹528.61), and 200-day DMA (₹524.80). The price distance from 200 DMA is +7.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>[564.15, 565.84, 567.53, 569.23, 570.92, 572.61]</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>[564.15, 572.03, 576.28, 579.94, 583.29, 586.44]</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>[564.15, 561.2, 560.97, 561.19, 561.64, 562.24]</t>
-        </is>
-      </c>
-      <c r="AU5" t="n">
-        <v>643.61</v>
+        <v>500.09</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU4"/>
+  <dimension ref="A1:AU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,188 +656,188 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43477.5</v>
+        <v>61359.72</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>289.85</v>
+        <v>2209.9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹288.75 - ₹291.5</t>
+          <t>₹2198.95 - ₹2226.32</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>294.25</v>
+        <v>2253.7</v>
       </c>
       <c r="I2" t="n">
-        <v>288.56</v>
+        <v>2171.19</v>
       </c>
       <c r="J2" t="n">
-        <v>284.53</v>
+        <v>2065.61</v>
       </c>
       <c r="K2" t="n">
-        <v>279.21</v>
+        <v>1972.76</v>
       </c>
       <c r="L2" t="n">
-        <v>2.61</v>
+        <v>12.26</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.09</v>
+        <v>31.51</v>
       </c>
       <c r="N2" t="n">
-        <v>0.31</v>
+        <v>37.38</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.39</v>
+        <v>-5.86</v>
       </c>
       <c r="P2" t="n">
-        <v>5.5</v>
+        <v>54.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.64</v>
+        <v>13.89</v>
       </c>
       <c r="R2" t="n">
-        <v>47.5</v>
+        <v>42.3</v>
       </c>
       <c r="S2" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="T2" t="n">
-        <v>-1</v>
+        <v>-1.67</v>
       </c>
       <c r="U2" t="n">
-        <v>55</v>
+        <v>53.3</v>
       </c>
       <c r="V2" t="n">
-        <v>5.27</v>
+        <v>3.62</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>281.16</v>
+        <v>2178.14</v>
       </c>
       <c r="Y2" t="n">
-        <v>270.06</v>
+        <v>2106.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>263.35</v>
+        <v>2023.02</v>
       </c>
       <c r="AA2" t="n">
-        <v>281.6</v>
+        <v>2127.77</v>
       </c>
       <c r="AB2" t="n">
-        <v>289.55</v>
+        <v>2199.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>293.35</v>
+        <v>2226.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>296.85</v>
+        <v>2243.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>44.6</v>
+        <v>50.9</v>
       </c>
       <c r="AF2" t="n">
         <v>0.1</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Low VIX (13.64) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.2</v>
+        <v>49.9</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-53.2</v>
+        <v>8.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>11.3</v>
+        <v>5.2</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>298.52</v>
+        <v>2275.18</v>
       </c>
       <c r="AN2" t="n">
-        <v>281.81</v>
+        <v>2150.44</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,477.50 Cr., a P/E ratio of 10.21, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹61,359.72 Cr., a P/E ratio of 49.90, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 44.57 (Consolidation Zone), while MACD Line (-0.09) trades below Signal (0.31) with an expanding histogram (-0.39). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.61% above the 200-day DMA (₹279.21). Daily volatility envelope is bounded by ATR(14) of ₹5.50.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.94 (Consolidation Zone), while MACD Line (31.51) trades below Signal (37.38) with an expanding histogram (-5.86). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1972.76). Daily volatility envelope is bounded by ATR(14) of ₹54.75.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹289.85) is positioned above the 30-day DMA (₹288.56), 50-day DMA (₹284.53), and 200-day DMA (₹279.21). The price distance from 200 DMA is +2.61%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,209.90) is positioned above the 30-day DMA (₹2,171.19), 50-day DMA (₹2,065.61), and 200-day DMA (₹1,972.76). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[289.85, 290.72, 291.59, 292.46, 293.33, 294.2]</t>
+          <t>[2209.9, 2227.47, 2245.05, 2262.62, 2280.2, 2297.77]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[289.85, 292.92, 294.7, 296.27, 297.73, 299.12]</t>
+          <t>[2209.9, 2249.37, 2276.02, 2300.55, 2324.0, 2346.74]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[289.85, 289.07, 289.26, 289.6, 290.03, 290.51]</t>
+          <t>[2209.9, 2211.05, 2221.82, 2234.17, 2247.35, 2261.04]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>263.35</v>
+        <v>2023.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>304652.51</v>
+        <v>30765.02</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,313 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>330.95</v>
+        <v>559.3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹329.51 - ₹333.11</t>
+          <t>₹556.28 - ₹563.82</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>336.7</v>
+        <v>571.36</v>
       </c>
       <c r="I3" t="n">
-        <v>326.23</v>
+        <v>540.71</v>
       </c>
       <c r="J3" t="n">
-        <v>317.69</v>
+        <v>529.0599999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>275.8</v>
+        <v>525</v>
       </c>
       <c r="L3" t="n">
-        <v>21.47</v>
+        <v>7.46</v>
       </c>
       <c r="M3" t="n">
-        <v>5.31</v>
+        <v>10.59</v>
       </c>
       <c r="N3" t="n">
-        <v>4.41</v>
+        <v>10.5</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9</v>
+        <v>0.08</v>
       </c>
       <c r="P3" t="n">
-        <v>7.19</v>
+        <v>15.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.64</v>
+        <v>13.89</v>
       </c>
       <c r="R3" t="n">
-        <v>40.5</v>
+        <v>38.1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.49</v>
+        <v>-2.05</v>
       </c>
       <c r="U3" t="n">
-        <v>51.7</v>
+        <v>48.3</v>
       </c>
       <c r="V3" t="n">
-        <v>2.46</v>
+        <v>4.42</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>324.72</v>
+        <v>537.22</v>
       </c>
       <c r="Y3" t="n">
-        <v>314.03</v>
+        <v>505.88</v>
       </c>
       <c r="Z3" t="n">
-        <v>303.76</v>
+        <v>495.78</v>
       </c>
       <c r="AA3" t="n">
-        <v>320.17</v>
+        <v>536.6799999999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>331.5</v>
+        <v>561.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>334.55</v>
+        <v>564.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>338.15</v>
+        <v>570.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>64.8</v>
+        <v>50.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.64) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (13.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>719.5</v>
+        <v>5.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>182</v>
+        <v>14.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.6</v>
+        <v>65.2</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>342.66</v>
+        <v>573.17</v>
       </c>
       <c r="AN3" t="n">
-        <v>320.09</v>
+        <v>545.5599999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹304,652.51 Cr., a P/E ratio of 719.46, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,765.02 Cr., a P/E ratio of 5.38, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.79 (Bullish Momentum Zone), while MACD Line (5.31) trades above Signal (4.41) with an expanding histogram (+0.90). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +21.47% above the 200-day DMA (₹275.80). Daily volatility envelope is bounded by ATR(14) of ₹7.19.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.64 (Consolidation Zone), while MACD Line (10.59) trades above Signal (10.50) with an expanding histogram (+0.08). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.46% above the 200-day DMA (₹525.00). Daily volatility envelope is bounded by ATR(14) of ₹15.08.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹330.95) is positioned above the 30-day DMA (₹326.23), 50-day DMA (₹317.69), and 200-day DMA (₹275.80). The price distance from 200 DMA is +21.47%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹559.30) is positioned above the 30-day DMA (₹540.71), 50-day DMA (₹529.06), and 200-day DMA (₹525.00). The price distance from 200 DMA is +7.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[330.95, 332.09, 333.23, 334.38, 335.52, 336.66]</t>
+          <t>[559.3, 560.98, 562.66, 564.33, 566.01, 567.69]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[330.95, 334.97, 337.3, 339.35, 341.27, 343.09]</t>
+          <t>[559.3, 567.01, 571.19, 574.78, 578.07, 581.18]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[330.95, 329.94, 330.19, 330.64, 331.21, 331.84]</t>
+          <t>[559.3, 556.45, 556.26, 556.5, 556.96, 557.57]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>303.76</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>31031.8</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>564.15</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>₹561.06 - ₹568.79</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>576.52</v>
-      </c>
-      <c r="I4" t="n">
-        <v>538.1799999999999</v>
-      </c>
-      <c r="J4" t="n">
-        <v>528.61</v>
-      </c>
-      <c r="K4" t="n">
-        <v>524.8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="M4" t="n">
-        <v>10.93</v>
-      </c>
-      <c r="N4" t="n">
-        <v>10.48</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="P4" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>13.64</v>
-      </c>
-      <c r="R4" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-2.07</v>
-      </c>
-      <c r="U4" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X4" t="n">
-        <v>541.5599999999999</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>515.3099999999999</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>500.09</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>540.95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>567.12</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>571.74</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>579.3200000000001</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>57</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.64) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>578.28</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>550.16</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹31,031.80 Cr., a P/E ratio of 5.43, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 57.02 (Bullish Momentum Zone), while MACD Line (10.93) trades above Signal (10.48) with an expanding histogram (+0.45). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.85% above the 200-day DMA (₹524.80). Daily volatility envelope is bounded by ATR(14) of ₹15.46.</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹564.15) is positioned above the 30-day DMA (₹538.18), 50-day DMA (₹528.61), and 200-day DMA (₹524.80). The price distance from 200 DMA is +7.85%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>[564.15, 565.84, 567.53, 569.23, 570.92, 572.61]</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>[564.15, 572.03, 576.28, 579.94, 583.29, 586.44]</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>[564.15, 561.2, 560.97, 561.19, 561.64, 562.24]</t>
-        </is>
-      </c>
-      <c r="AU4" t="n">
-        <v>500.09</v>
+        <v>495.78</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU3"/>
+  <dimension ref="A1:AU4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>61359.72</v>
+        <v>60768.32</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,98 +678,98 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2209.9</v>
+        <v>2188.6</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹2198.95 - ₹2226.32</t>
+          <t>₹2177.67 - ₹2204.99</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2253.7</v>
+        <v>2232.3</v>
       </c>
       <c r="I2" t="n">
-        <v>2171.19</v>
+        <v>2175.31</v>
       </c>
       <c r="J2" t="n">
-        <v>2065.61</v>
+        <v>2073.4</v>
       </c>
       <c r="K2" t="n">
-        <v>1972.76</v>
+        <v>1975.16</v>
       </c>
       <c r="L2" t="n">
-        <v>12.26</v>
+        <v>11.23</v>
       </c>
       <c r="M2" t="n">
-        <v>31.51</v>
+        <v>30.04</v>
       </c>
       <c r="N2" t="n">
-        <v>37.38</v>
+        <v>35.91</v>
       </c>
       <c r="O2" t="n">
-        <v>-5.86</v>
+        <v>-5.87</v>
       </c>
       <c r="P2" t="n">
-        <v>54.75</v>
+        <v>54.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.89</v>
+        <v>13.41</v>
       </c>
       <c r="R2" t="n">
-        <v>42.3</v>
+        <v>39.9</v>
       </c>
       <c r="S2" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.67</v>
+        <v>-1.79</v>
       </c>
       <c r="U2" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="V2" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2178.14</v>
+        <v>2120.68</v>
       </c>
       <c r="Y2" t="n">
-        <v>2106.18</v>
+        <v>2051.83</v>
       </c>
       <c r="Z2" t="n">
-        <v>2023.02</v>
+        <v>2003.52</v>
       </c>
       <c r="AA2" t="n">
-        <v>2127.77</v>
+        <v>2106.66</v>
       </c>
       <c r="AB2" t="n">
-        <v>2199.4</v>
+        <v>2192.83</v>
       </c>
       <c r="AC2" t="n">
-        <v>2226.7</v>
+        <v>2213.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>2243.5</v>
+        <v>2238.53</v>
       </c>
       <c r="AE2" t="n">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.89) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.41) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
       <c r="AJ2" t="n">
         <v>8.5</v>
@@ -781,43 +781,43 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>2275.18</v>
+        <v>2252.43</v>
       </c>
       <c r="AN2" t="n">
-        <v>2150.44</v>
+        <v>2129.77</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹61,359.72 Cr., a P/E ratio of 49.90, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,768.32 Cr., a P/E ratio of 49.42, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.94 (Consolidation Zone), while MACD Line (31.51) trades below Signal (37.38) with an expanding histogram (-5.86). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +12.26% above the 200-day DMA (₹1972.76). Daily volatility envelope is bounded by ATR(14) of ₹54.75.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.39 (Consolidation Zone), while MACD Line (30.04) trades below Signal (35.91) with an expanding histogram (-5.87). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.23% above the 200-day DMA (₹1975.16). Daily volatility envelope is bounded by ATR(14) of ₹54.63.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,209.90) is positioned above the 30-day DMA (₹2,171.19), 50-day DMA (₹2,065.61), and 200-day DMA (₹1,972.76). The price distance from 200 DMA is +12.26%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,188.60) is positioned above the 30-day DMA (₹2,175.31), 50-day DMA (₹2,073.40), and 200-day DMA (₹1,975.16). The price distance from 200 DMA is +11.23%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[2209.9, 2227.47, 2245.05, 2262.62, 2280.2, 2297.77]</t>
+          <t>[2188.6, 2195.17, 2201.73, 2208.3, 2214.86, 2221.43]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[2209.9, 2249.37, 2276.02, 2300.55, 2324.0, 2346.74]</t>
+          <t>[2188.6, 2217.02, 2232.63, 2246.15, 2258.57, 2270.29]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[2209.9, 2211.05, 2221.82, 2234.17, 2247.35, 2261.04]</t>
+          <t>[2188.6, 2178.78, 2178.55, 2179.91, 2182.09, 2184.78]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2023.02</v>
+        <v>2003.52</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30765.02</v>
+        <v>301798.84</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,313 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>559.3</v>
+        <v>327.85</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹556.28 - ₹563.82</t>
+          <t>₹326.37 - ₹330.07</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>571.36</v>
+        <v>333.76</v>
       </c>
       <c r="I3" t="n">
-        <v>540.71</v>
+        <v>326.66</v>
       </c>
       <c r="J3" t="n">
-        <v>529.0599999999999</v>
+        <v>318.56</v>
       </c>
       <c r="K3" t="n">
-        <v>525</v>
+        <v>276</v>
       </c>
       <c r="L3" t="n">
-        <v>7.46</v>
+        <v>19.91</v>
       </c>
       <c r="M3" t="n">
-        <v>10.59</v>
+        <v>4.91</v>
       </c>
       <c r="N3" t="n">
-        <v>10.5</v>
+        <v>4.51</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="P3" t="n">
-        <v>15.08</v>
+        <v>7.39</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.89</v>
+        <v>13.41</v>
       </c>
       <c r="R3" t="n">
-        <v>38.1</v>
+        <v>39.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.05</v>
+        <v>-1.59</v>
       </c>
       <c r="U3" t="n">
-        <v>48.3</v>
+        <v>50</v>
       </c>
       <c r="V3" t="n">
-        <v>4.42</v>
+        <v>2.54</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>537.22</v>
+        <v>321.78</v>
       </c>
       <c r="Y3" t="n">
-        <v>505.88</v>
+        <v>311.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>495.78</v>
+        <v>300.91</v>
       </c>
       <c r="AA3" t="n">
-        <v>536.6799999999999</v>
+        <v>316.77</v>
       </c>
       <c r="AB3" t="n">
-        <v>561.15</v>
+        <v>328.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>564.9</v>
+        <v>332.69</v>
       </c>
       <c r="AD3" t="n">
-        <v>570.5</v>
+        <v>337.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>50.6</v>
+        <v>59.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (13.89) | LSTM Deep Net</t>
+          <t>Low VIX (13.41) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.4</v>
+        <v>712.7</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14.5</v>
+        <v>182</v>
       </c>
       <c r="AK3" t="n">
-        <v>65.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>573.17</v>
+        <v>339.57</v>
       </c>
       <c r="AN3" t="n">
-        <v>545.5599999999999</v>
+        <v>317.55</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,765.02 Cr., a P/E ratio of 5.38, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹301,798.84 Cr., a P/E ratio of 712.72, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.12 (Bullish Momentum Zone), while MACD Line (4.91) trades above Signal (4.51) with an expanding histogram (+0.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.91% above the 200-day DMA (₹276.00). Daily volatility envelope is bounded by ATR(14) of ₹7.39.</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹327.85) is positioned above the 30-day DMA (₹326.66), 50-day DMA (₹318.56), and 200-day DMA (₹276.00). The price distance from 200 DMA is +19.91%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>[327.85, 329.09, 330.33, 331.56, 332.8, 334.04]</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>[327.85, 332.04, 334.51, 336.68, 338.71, 340.65]</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>[327.85, 326.87, 327.19, 327.72, 328.37, 329.08]</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>300.91</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>30170.96</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>548.5</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>₹545.48 - ₹553.02</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>560.5599999999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>540.71</v>
+      </c>
+      <c r="J4" t="n">
+        <v>529.0599999999999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>525</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="N4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="P4" t="n">
+        <v>15.08</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="R4" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="U4" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X4" t="n">
+        <v>526.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>493.58</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>486.22</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>525.88</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>554.58</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>560.66</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>572.83</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>TTM Squeeze | Low VIX (13.41) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>563.0700000000001</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>534.21</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,170.96 Cr., a P/E ratio of 5.26, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
           <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.64 (Consolidation Zone), while MACD Line (10.59) trades above Signal (10.50) with an expanding histogram (+0.08). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.46% above the 200-day DMA (₹525.00). Daily volatility envelope is bounded by ATR(14) of ₹15.08.</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹559.30) is positioned above the 30-day DMA (₹540.71), 50-day DMA (₹529.06), and 200-day DMA (₹525.00). The price distance from 200 DMA is +7.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>[559.3, 560.98, 562.66, 564.33, 566.01, 567.69]</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>[559.3, 567.01, 571.19, 574.78, 578.07, 581.18]</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>[559.3, 556.45, 556.26, 556.5, 556.96, 557.57]</t>
-        </is>
-      </c>
-      <c r="AU3" t="n">
-        <v>495.78</v>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹548.50) is positioned above the 30-day DMA (₹540.71), 50-day DMA (₹529.06), and 200-day DMA (₹525.00). The price distance from 200 DMA is +7.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>[548.5, 550.15, 551.79, 553.44, 555.08, 556.73]</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>[548.5, 556.18, 560.32, 563.88, 567.14, 570.21]</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>[548.5, 545.62, 545.39, 545.6, 546.03, 546.61]</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>486.22</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU4"/>
+  <dimension ref="A1:AU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>60768.32</v>
+        <v>301798.84</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,480 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2188.6</v>
+        <v>327.85</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹2177.67 - ₹2204.99</t>
+          <t>₹326.37 - ₹330.07</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2232.3</v>
+        <v>333.76</v>
       </c>
       <c r="I2" t="n">
-        <v>2175.31</v>
+        <v>326.66</v>
       </c>
       <c r="J2" t="n">
-        <v>2073.4</v>
+        <v>318.56</v>
       </c>
       <c r="K2" t="n">
-        <v>1975.16</v>
+        <v>276</v>
       </c>
       <c r="L2" t="n">
-        <v>11.23</v>
+        <v>19.91</v>
       </c>
       <c r="M2" t="n">
-        <v>30.04</v>
+        <v>4.91</v>
       </c>
       <c r="N2" t="n">
-        <v>35.91</v>
+        <v>4.51</v>
       </c>
       <c r="O2" t="n">
-        <v>-5.87</v>
+        <v>0.4</v>
       </c>
       <c r="P2" t="n">
-        <v>54.63</v>
+        <v>7.39</v>
       </c>
       <c r="Q2" t="n">
         <v>13.41</v>
       </c>
       <c r="R2" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="S2" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.79</v>
+        <v>-1.58</v>
       </c>
       <c r="U2" t="n">
-        <v>51.7</v>
+        <v>50</v>
       </c>
       <c r="V2" t="n">
-        <v>3.68</v>
+        <v>2.54</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2120.68</v>
+        <v>327.85</v>
       </c>
       <c r="Y2" t="n">
-        <v>2051.83</v>
+        <v>363.46</v>
       </c>
       <c r="Z2" t="n">
-        <v>2003.52</v>
+        <v>363.46</v>
       </c>
       <c r="AA2" t="n">
-        <v>2106.66</v>
+        <v>316.77</v>
       </c>
       <c r="AB2" t="n">
-        <v>2192.83</v>
+        <v>328.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>2213.56</v>
+        <v>332.69</v>
       </c>
       <c r="AD2" t="n">
-        <v>2238.53</v>
+        <v>337.52</v>
       </c>
       <c r="AE2" t="n">
-        <v>51.4</v>
+        <v>59.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.41) | LSTM Deep Net</t>
+          <t>Low VIX (13.41) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>49.4</v>
+        <v>712.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>8.5</v>
+        <v>182</v>
       </c>
       <c r="AK2" t="n">
-        <v>5.2</v>
+        <v>0.6</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>2252.43</v>
+        <v>339.61</v>
       </c>
       <c r="AN2" t="n">
-        <v>2129.77</v>
+        <v>317.24</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,768.32 Cr., a P/E ratio of 49.42, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹301,798.84 Cr., a P/E ratio of 712.72, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.39 (Consolidation Zone), while MACD Line (30.04) trades below Signal (35.91) with an expanding histogram (-5.87). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.23% above the 200-day DMA (₹1975.16). Daily volatility envelope is bounded by ATR(14) of ₹54.63.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.12 (Bullish Momentum Zone), while MACD Line (4.91) trades above Signal (4.51) with an expanding histogram (+0.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.91% above the 200-day DMA (₹276.00). Daily volatility envelope is bounded by ATR(14) of ₹7.39.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,188.60) is positioned above the 30-day DMA (₹2,175.31), 50-day DMA (₹2,073.40), and 200-day DMA (₹1,975.16). The price distance from 200 DMA is +11.23%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹327.85) is positioned above the 30-day DMA (₹326.66), 50-day DMA (₹318.56), and 200-day DMA (₹276.00). The price distance from 200 DMA is +19.91%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[2188.6, 2195.17, 2201.73, 2208.3, 2214.86, 2221.43]</t>
+          <t>[327.85, 329.09, 330.33, 331.56, 332.8, 334.04]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[2188.6, 2217.02, 2232.63, 2246.15, 2258.57, 2270.29]</t>
+          <t>[327.85, 332.04, 334.51, 336.68, 338.71, 340.65]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[2188.6, 2178.78, 2178.55, 2179.91, 2182.09, 2184.78]</t>
+          <t>[327.85, 326.87, 327.19, 327.72, 328.37, 329.08]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2003.52</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>301798.84</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>327.85</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>₹326.37 - ₹330.07</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>333.76</v>
-      </c>
-      <c r="I3" t="n">
-        <v>326.66</v>
-      </c>
-      <c r="J3" t="n">
-        <v>318.56</v>
-      </c>
-      <c r="K3" t="n">
-        <v>276</v>
-      </c>
-      <c r="L3" t="n">
-        <v>19.91</v>
-      </c>
-      <c r="M3" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="R3" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-1.59</v>
-      </c>
-      <c r="U3" t="n">
-        <v>50</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X3" t="n">
-        <v>321.78</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>311.19</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>300.91</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>316.77</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>328.17</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>332.69</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>337.52</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Low VIX (13.41) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>712.7</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>182</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>339.57</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>317.55</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹301,798.84 Cr., a P/E ratio of 712.72, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.12 (Bullish Momentum Zone), while MACD Line (4.91) trades above Signal (4.51) with an expanding histogram (+0.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.91% above the 200-day DMA (₹276.00). Daily volatility envelope is bounded by ATR(14) of ₹7.39.</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹327.85) is positioned above the 30-day DMA (₹326.66), 50-day DMA (₹318.56), and 200-day DMA (₹276.00). The price distance from 200 DMA is +19.91%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>[327.85, 329.09, 330.33, 331.56, 332.8, 334.04]</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>[327.85, 332.04, 334.51, 336.68, 338.71, 340.65]</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>[327.85, 326.87, 327.19, 327.72, 328.37, 329.08]</t>
-        </is>
-      </c>
-      <c r="AU3" t="n">
-        <v>300.91</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>30170.96</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>548.5</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>₹545.48 - ₹553.02</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>560.5599999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>540.71</v>
-      </c>
-      <c r="J4" t="n">
-        <v>529.0599999999999</v>
-      </c>
-      <c r="K4" t="n">
-        <v>525</v>
-      </c>
-      <c r="L4" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="M4" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="N4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="P4" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>13.41</v>
-      </c>
-      <c r="R4" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-2.14</v>
-      </c>
-      <c r="U4" t="n">
-        <v>48.3</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X4" t="n">
-        <v>526.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>493.58</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>486.22</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>525.88</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>554.58</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>560.66</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>572.83</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>TTM Squeeze | Low VIX (13.41) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>563.0700000000001</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>534.21</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>LICHSGFIN operates in the Financial Services sector. With an estimated Market Cap of ₹30,170.96 Cr., a P/E ratio of 5.26, and YoY Revenue Growth of +14.5%, the company demonstrates strong institutional backing, solid operating profit margins (65.18%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 50.64 (Consolidation Zone), while MACD Line (10.59) trades above Signal (10.50) with an expanding histogram (+0.08). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.46% above the 200-day DMA (₹525.00). Daily volatility envelope is bounded by ATR(14) of ₹15.08.</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for LICHSGFIN. Current Market Price (₹548.50) is positioned above the 30-day DMA (₹540.71), 50-day DMA (₹529.06), and 200-day DMA (₹525.00). The price distance from 200 DMA is +7.46%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>[548.5, 550.15, 551.79, 553.44, 555.08, 556.73]</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>[548.5, 556.18, 560.32, 563.88, 567.14, 570.21]</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>[548.5, 545.62, 545.39, 545.6, 546.03, 546.61]</t>
-        </is>
-      </c>
-      <c r="AU4" t="n">
-        <v>486.22</v>
+        <v>363.46</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,168 +656,335 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>301798.84</v>
+        <v>61054.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>327.85</v>
+        <v>2198.9</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹326.37 - ₹330.07</t>
+          <t>₹2187.97 - ₹2215.29</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>333.76</v>
+        <v>2242.6</v>
       </c>
       <c r="I2" t="n">
-        <v>326.66</v>
+        <v>2175.31</v>
       </c>
       <c r="J2" t="n">
-        <v>318.56</v>
+        <v>2073.4</v>
       </c>
       <c r="K2" t="n">
-        <v>276</v>
+        <v>1975.16</v>
       </c>
       <c r="L2" t="n">
-        <v>19.91</v>
+        <v>11.23</v>
       </c>
       <c r="M2" t="n">
-        <v>4.91</v>
+        <v>30.04</v>
       </c>
       <c r="N2" t="n">
-        <v>4.51</v>
+        <v>35.91</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4</v>
+        <v>-5.87</v>
       </c>
       <c r="P2" t="n">
-        <v>7.39</v>
+        <v>54.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.41</v>
+        <v>13.22</v>
       </c>
       <c r="R2" t="n">
-        <v>40</v>
+        <v>45.3</v>
       </c>
       <c r="S2" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.58</v>
+        <v>-1.54</v>
       </c>
       <c r="U2" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="V2" t="n">
-        <v>2.54</v>
+        <v>3.7</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>327.85</v>
+        <v>2198.05</v>
       </c>
       <c r="Y2" t="n">
-        <v>363.46</v>
+        <v>2430.54</v>
       </c>
       <c r="Z2" t="n">
-        <v>363.46</v>
+        <v>2430.54</v>
       </c>
       <c r="AA2" t="n">
-        <v>316.77</v>
+        <v>2116.96</v>
       </c>
       <c r="AB2" t="n">
-        <v>328.17</v>
+        <v>2203.73</v>
       </c>
       <c r="AC2" t="n">
-        <v>332.69</v>
+        <v>2219.66</v>
       </c>
       <c r="AD2" t="n">
-        <v>337.52</v>
+        <v>2240.43</v>
       </c>
       <c r="AE2" t="n">
-        <v>59.1</v>
+        <v>51.4</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Low VIX (13.41) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.22) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>712.7</v>
+        <v>49.6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>182</v>
+        <v>8.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.6</v>
+        <v>5.2</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>339.61</v>
+        <v>2256.71</v>
       </c>
       <c r="AN2" t="n">
-        <v>317.24</v>
+        <v>2134.41</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹301,798.84 Cr., a P/E ratio of 712.72, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹61,054.30 Cr., a P/E ratio of 49.65, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 59.12 (Bullish Momentum Zone), while MACD Line (4.91) trades above Signal (4.51) with an expanding histogram (+0.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +19.91% above the 200-day DMA (₹276.00). Daily volatility envelope is bounded by ATR(14) of ₹7.39.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.39 (Consolidation Zone), while MACD Line (30.04) trades below Signal (35.91) with an expanding histogram (-5.87). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.23% above the 200-day DMA (₹1975.16). Daily volatility envelope is bounded by ATR(14) of ₹54.63.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹327.85) is positioned above the 30-day DMA (₹326.66), 50-day DMA (₹318.56), and 200-day DMA (₹276.00). The price distance from 200 DMA is +19.91%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,198.90) is positioned above the 30-day DMA (₹2,175.31), 50-day DMA (₹2,073.40), and 200-day DMA (₹1,975.16). The price distance from 200 DMA is +11.23%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[327.85, 329.09, 330.33, 331.56, 332.8, 334.04]</t>
+          <t>[2198.9, 2205.5, 2212.09, 2218.69, 2225.29, 2231.88]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[327.85, 332.04, 334.51, 336.68, 338.71, 340.65]</t>
+          <t>[2198.9, 2227.35, 2243.0, 2256.54, 2268.99, 2280.74]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[327.85, 326.87, 327.19, 327.72, 328.37, 329.08]</t>
+          <t>[2198.9, 2189.11, 2188.92, 2190.3, 2192.51, 2195.24]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>363.46</v>
+        <v>2430.54</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>29173.05</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>181.07</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>₹179.9 - ₹182.83</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>185.76</v>
+      </c>
+      <c r="I3" t="n">
+        <v>173.76</v>
+      </c>
+      <c r="J3" t="n">
+        <v>172.71</v>
+      </c>
+      <c r="K3" t="n">
+        <v>175.19</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="R3" t="n">
+        <v>41</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="U3" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X3" t="n">
+        <v>180.64</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>196.46</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>196.46</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>172.27</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>181.53</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>183.91</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>186.75</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.22) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>188.62</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>173.64</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>BANDHANBNK operates in the Financial Services sector. With an estimated Market Cap of ₹29,173.05 Cr., a P/E ratio of 21.05, and YoY Revenue Growth of +21.6%, the company demonstrates strong institutional backing, solid operating profit margins (13.62%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.58 (Bullish Momentum Zone), while MACD Line (3.24) trades above Signal (1.76) with an expanding histogram (+1.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.78% above the 200-day DMA (₹175.19). Daily volatility envelope is bounded by ATR(14) of ₹5.87.</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BANDHANBNK. Current Market Price (₹181.07) is positioned above the 30-day DMA (₹173.76), 50-day DMA (₹172.71), and 200-day DMA (₹175.19). The price distance from 200 DMA is +5.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>[181.07, 181.61, 182.16, 182.7, 183.24, 183.79]</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>[181.07, 183.96, 185.48, 186.76, 187.94, 189.03]</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>[181.07, 179.85, 179.67, 179.65, 179.72, 179.85]</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>196.46</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU3"/>
+  <dimension ref="A1:AU4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>61054.3</v>
+        <v>166836</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2198.9</v>
+        <v>674</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹2187.97 - ₹2215.29</t>
+          <t>₹670.75 - ₹678.88</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2242.6</v>
+        <v>687.01</v>
       </c>
       <c r="I2" t="n">
-        <v>2175.31</v>
+        <v>665.9400000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>2073.4</v>
+        <v>661.48</v>
       </c>
       <c r="K2" t="n">
-        <v>1975.16</v>
+        <v>621.33</v>
       </c>
       <c r="L2" t="n">
-        <v>11.23</v>
+        <v>5.1</v>
       </c>
       <c r="M2" t="n">
-        <v>30.04</v>
+        <v>0.27</v>
       </c>
       <c r="N2" t="n">
-        <v>35.91</v>
+        <v>-1.05</v>
       </c>
       <c r="O2" t="n">
-        <v>-5.87</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>54.63</v>
+        <v>16.26</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.22</v>
+        <v>13.49</v>
       </c>
       <c r="R2" t="n">
-        <v>45.3</v>
+        <v>50.1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.54</v>
+        <v>-1.27</v>
       </c>
       <c r="U2" t="n">
-        <v>53.3</v>
+        <v>59</v>
       </c>
       <c r="V2" t="n">
-        <v>3.7</v>
+        <v>7.92</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2198.05</v>
+        <v>669.98</v>
       </c>
       <c r="Y2" t="n">
-        <v>2430.54</v>
+        <v>731.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>2430.54</v>
+        <v>731.29</v>
       </c>
       <c r="AA2" t="n">
-        <v>2116.96</v>
+        <v>649.61</v>
       </c>
       <c r="AB2" t="n">
-        <v>2203.73</v>
+        <v>667</v>
       </c>
       <c r="AC2" t="n">
-        <v>2219.66</v>
+        <v>681</v>
       </c>
       <c r="AD2" t="n">
-        <v>2240.43</v>
+        <v>688</v>
       </c>
       <c r="AE2" t="n">
-        <v>51.4</v>
+        <v>49.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.15</v>
+        <v>-0.2</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.22) | LSTM Deep Net</t>
+          <t>Low VIX (13.49) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>49.6</v>
+        <v>37.5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>8.5</v>
+        <v>-52.9</v>
       </c>
       <c r="AK2" t="n">
-        <v>5.2</v>
+        <v>65.8</v>
       </c>
       <c r="AL2" t="n">
-        <v>15</v>
+        <v>10.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>2256.71</v>
+        <v>694.02</v>
       </c>
       <c r="AN2" t="n">
-        <v>2134.41</v>
+        <v>652.92</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹61,054.30 Cr., a P/E ratio of 49.65, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹166,836.00 Cr., a P/E ratio of 37.53, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 51.39 (Consolidation Zone), while MACD Line (30.04) trades below Signal (35.91) with an expanding histogram (-5.87). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +11.23% above the 200-day DMA (₹1975.16). Daily volatility envelope is bounded by ATR(14) of ₹54.63.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.23 (Consolidation Zone), while MACD Line (0.27) trades above Signal (-1.05) with an expanding histogram (+1.31). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.10% above the 200-day DMA (₹621.33). Daily volatility envelope is bounded by ATR(14) of ₹16.26.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,198.90) is positioned above the 30-day DMA (₹2,175.31), 50-day DMA (₹2,073.40), and 200-day DMA (₹1,975.16). The price distance from 200 DMA is +11.23%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DLF. Current Market Price (₹674.00) is positioned above the 30-day DMA (₹665.94), 50-day DMA (₹661.48), and 200-day DMA (₹621.33). The price distance from 200 DMA is +5.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[2198.9, 2205.5, 2212.09, 2218.69, 2225.29, 2231.88]</t>
+          <t>[674.0, 676.02, 678.04, 680.07, 682.09, 684.11]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[2198.9, 2227.35, 2243.0, 2256.54, 2268.99, 2280.74]</t>
+          <t>[674.0, 682.52, 687.24, 691.33, 695.09, 698.65]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[2198.9, 2189.11, 2188.92, 2190.3, 2192.51, 2195.24]</t>
+          <t>[674.0, 671.14, 671.15, 671.62, 672.33, 673.2]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2430.54</v>
+        <v>731.29</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29173.05</v>
+        <v>60809.97</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,313 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>181.07</v>
+        <v>2190.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹179.9 - ₹182.83</t>
+          <t>₹2178.95 - ₹2206.83</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>185.76</v>
+        <v>2234.71</v>
       </c>
       <c r="I3" t="n">
-        <v>173.76</v>
+        <v>2178.03</v>
       </c>
       <c r="J3" t="n">
-        <v>172.71</v>
+        <v>2080.92</v>
       </c>
       <c r="K3" t="n">
-        <v>175.19</v>
+        <v>1977.45</v>
       </c>
       <c r="L3" t="n">
-        <v>5.78</v>
+        <v>10.68</v>
       </c>
       <c r="M3" t="n">
-        <v>3.24</v>
+        <v>27.87</v>
       </c>
       <c r="N3" t="n">
-        <v>1.76</v>
+        <v>34.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.48</v>
+        <v>-6.43</v>
       </c>
       <c r="P3" t="n">
-        <v>5.87</v>
+        <v>55.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.22</v>
+        <v>13.49</v>
       </c>
       <c r="R3" t="n">
-        <v>41</v>
+        <v>44.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="T3" t="n">
-        <v>-2.37</v>
+        <v>-1.63</v>
       </c>
       <c r="U3" t="n">
-        <v>45.9</v>
+        <v>52.5</v>
       </c>
       <c r="V3" t="n">
-        <v>6.74</v>
+        <v>3.78</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>180.64</v>
+        <v>2190.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>196.46</v>
+        <v>2420.81</v>
       </c>
       <c r="Z3" t="n">
-        <v>196.46</v>
+        <v>2420.81</v>
       </c>
       <c r="AA3" t="n">
-        <v>172.27</v>
+        <v>2106.46</v>
       </c>
       <c r="AB3" t="n">
-        <v>181.53</v>
+        <v>2198.73</v>
       </c>
       <c r="AC3" t="n">
-        <v>183.91</v>
+        <v>2215.86</v>
       </c>
       <c r="AD3" t="n">
-        <v>186.75</v>
+        <v>2241.63</v>
       </c>
       <c r="AE3" t="n">
-        <v>62.6</v>
+        <v>52.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.22) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.49) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>21.1</v>
+        <v>49.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>21.6</v>
+        <v>8.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>13.6</v>
+        <v>5.2</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>188.62</v>
+        <v>2254.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>173.64</v>
+        <v>2128.74</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>BANDHANBNK operates in the Financial Services sector. With an estimated Market Cap of ₹29,173.05 Cr., a P/E ratio of 21.05, and YoY Revenue Growth of +21.6%, the company demonstrates strong institutional backing, solid operating profit margins (13.62%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,809.97 Cr., a P/E ratio of 49.45, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.44 (Consolidation Zone), while MACD Line (27.87) trades below Signal (34.30) with an expanding histogram (-6.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.68% above the 200-day DMA (₹1977.45). Daily volatility envelope is bounded by ATR(14) of ₹55.76.</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,190.10) is positioned above the 30-day DMA (₹2,178.03), 50-day DMA (₹2,080.92), and 200-day DMA (₹1,977.45). The price distance from 200 DMA is +10.68%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>[2190.1, 2196.67, 2203.24, 2209.81, 2216.38, 2222.95]</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>[2190.1, 2218.97, 2234.78, 2248.44, 2260.99, 2272.82]</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>[2190.1, 2179.94, 2179.58, 2180.84, 2182.93, 2185.55]</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>2420.81</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>28715.48</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>178.23</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>₹177.06 - ₹179.99</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>182.92</v>
+      </c>
+      <c r="I4" t="n">
+        <v>173.76</v>
+      </c>
+      <c r="J4" t="n">
+        <v>172.71</v>
+      </c>
+      <c r="K4" t="n">
+        <v>175.19</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="R4" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="U4" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="V4" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X4" t="n">
+        <v>177.37</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>193.38</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>193.38</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>169.43</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>179.95</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>182.64</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>187.06</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.49) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>185.98</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>171.14</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>BANDHANBNK operates in the Financial Services sector. With an estimated Market Cap of ₹28,715.48 Cr., a P/E ratio of 21.24, and YoY Revenue Growth of +21.6%, the company demonstrates strong institutional backing, solid operating profit margins (13.62%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
           <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.58 (Bullish Momentum Zone), while MACD Line (3.24) trades above Signal (1.76) with an expanding histogram (+1.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.78% above the 200-day DMA (₹175.19). Daily volatility envelope is bounded by ATR(14) of ₹5.87.</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BANDHANBNK. Current Market Price (₹181.07) is positioned above the 30-day DMA (₹173.76), 50-day DMA (₹172.71), and 200-day DMA (₹175.19). The price distance from 200 DMA is +5.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>[181.07, 181.61, 182.16, 182.7, 183.24, 183.79]</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>[181.07, 183.96, 185.48, 186.76, 187.94, 189.03]</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>[181.07, 179.85, 179.67, 179.65, 179.72, 179.85]</t>
-        </is>
-      </c>
-      <c r="AU3" t="n">
-        <v>196.46</v>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BANDHANBNK. Current Market Price (₹178.23) is positioned above the 30-day DMA (₹173.76), 50-day DMA (₹172.71), and 200-day DMA (₹175.19). The price distance from 200 DMA is +5.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>[178.23, 178.76, 179.3, 179.83, 180.37, 180.9]</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>[178.23, 181.11, 182.62, 183.9, 185.06, 186.15]</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>[178.23, 177.0, 176.81, 176.79, 176.85, 176.97]</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>193.38</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU4"/>
+  <dimension ref="A1:AU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,31 +716,31 @@
         <v>13.49</v>
       </c>
       <c r="R2" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="S2" t="n">
         <v>0.22</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.27</v>
+        <v>-1.26</v>
       </c>
       <c r="U2" t="n">
         <v>59</v>
       </c>
       <c r="V2" t="n">
-        <v>7.92</v>
+        <v>7.91</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>669.98</v>
+        <v>647.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>731.29</v>
+        <v>606.84</v>
       </c>
       <c r="Z2" t="n">
-        <v>731.29</v>
+        <v>606.65</v>
       </c>
       <c r="AA2" t="n">
         <v>649.61</v>
@@ -769,7 +769,7 @@
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="AJ2" t="n">
         <v>-52.9</v>
@@ -781,14 +781,14 @@
         <v>10.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>694.02</v>
+        <v>693.11</v>
       </c>
       <c r="AN2" t="n">
-        <v>652.92</v>
+        <v>653.42</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹166,836.00 Cr., a P/E ratio of 37.53, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
+          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹166,836.00 Cr., a P/E ratio of 37.59, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>731.29</v>
+        <v>606.65</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60809.97</v>
+        <v>28715.48</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,313 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2190.1</v>
+        <v>178.23</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹2178.95 - ₹2206.83</t>
+          <t>₹177.06 - ₹179.99</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2234.71</v>
+        <v>182.92</v>
       </c>
       <c r="I3" t="n">
-        <v>2178.03</v>
+        <v>173.76</v>
       </c>
       <c r="J3" t="n">
-        <v>2080.92</v>
+        <v>172.71</v>
       </c>
       <c r="K3" t="n">
-        <v>1977.45</v>
+        <v>175.19</v>
       </c>
       <c r="L3" t="n">
-        <v>10.68</v>
+        <v>5.78</v>
       </c>
       <c r="M3" t="n">
-        <v>27.87</v>
+        <v>3.24</v>
       </c>
       <c r="N3" t="n">
-        <v>34.3</v>
+        <v>1.76</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.43</v>
+        <v>1.48</v>
       </c>
       <c r="P3" t="n">
-        <v>55.76</v>
+        <v>5.87</v>
       </c>
       <c r="Q3" t="n">
         <v>13.49</v>
       </c>
       <c r="R3" t="n">
-        <v>44.3</v>
+        <v>40.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.63</v>
+        <v>-2.42</v>
       </c>
       <c r="U3" t="n">
-        <v>52.5</v>
+        <v>45.9</v>
       </c>
       <c r="V3" t="n">
-        <v>3.78</v>
+        <v>6.73</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>2190.1</v>
+        <v>171.31</v>
       </c>
       <c r="Y3" t="n">
-        <v>2420.81</v>
+        <v>172.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>2420.81</v>
+        <v>172.16</v>
       </c>
       <c r="AA3" t="n">
-        <v>2106.46</v>
+        <v>169.43</v>
       </c>
       <c r="AB3" t="n">
-        <v>2198.73</v>
+        <v>179.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>2215.86</v>
+        <v>182.64</v>
       </c>
       <c r="AD3" t="n">
-        <v>2241.63</v>
+        <v>187.06</v>
       </c>
       <c r="AE3" t="n">
-        <v>52.4</v>
+        <v>62.6</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Low VIX (13.49) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.49) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>49.4</v>
+        <v>21.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>8.5</v>
+        <v>21.6</v>
       </c>
       <c r="AK3" t="n">
-        <v>5.2</v>
+        <v>13.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>2254.33</v>
+        <v>185.85</v>
       </c>
       <c r="AN3" t="n">
-        <v>2128.74</v>
+        <v>170.71</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹60,809.97 Cr., a P/E ratio of 49.45, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>BANDHANBNK operates in the Financial Services sector. With an estimated Market Cap of ₹28,715.48 Cr., a P/E ratio of 21.24, and YoY Revenue Growth of +21.6%, the company demonstrates strong institutional backing, solid operating profit margins (13.62%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.44 (Consolidation Zone), while MACD Line (27.87) trades below Signal (34.30) with an expanding histogram (-6.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.68% above the 200-day DMA (₹1977.45). Daily volatility envelope is bounded by ATR(14) of ₹55.76.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.58 (Bullish Momentum Zone), while MACD Line (3.24) trades above Signal (1.76) with an expanding histogram (+1.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.78% above the 200-day DMA (₹175.19). Daily volatility envelope is bounded by ATR(14) of ₹5.87.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,190.10) is positioned above the 30-day DMA (₹2,178.03), 50-day DMA (₹2,080.92), and 200-day DMA (₹1,977.45). The price distance from 200 DMA is +10.68%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BANDHANBNK. Current Market Price (₹178.23) is positioned above the 30-day DMA (₹173.76), 50-day DMA (₹172.71), and 200-day DMA (₹175.19). The price distance from 200 DMA is +5.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[2190.1, 2196.67, 2203.24, 2209.81, 2216.38, 2222.95]</t>
+          <t>[178.23, 178.76, 179.3, 179.83, 180.37, 180.9]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[2190.1, 2218.97, 2234.78, 2248.44, 2260.99, 2272.82]</t>
+          <t>[178.23, 181.11, 182.62, 183.9, 185.06, 186.15]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[2190.1, 2179.94, 2179.58, 2180.84, 2182.93, 2185.55]</t>
+          <t>[178.23, 177.0, 176.81, 176.79, 176.85, 176.97]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>2420.81</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>BANDHANBNK</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>28715.48</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>178.23</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>₹177.06 - ₹179.99</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>182.92</v>
-      </c>
-      <c r="I4" t="n">
-        <v>173.76</v>
-      </c>
-      <c r="J4" t="n">
-        <v>172.71</v>
-      </c>
-      <c r="K4" t="n">
-        <v>175.19</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P4" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="R4" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-2.42</v>
-      </c>
-      <c r="U4" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="V4" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X4" t="n">
-        <v>177.37</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>193.38</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>193.38</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>169.43</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>179.95</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>182.64</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>187.06</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.49) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>185.98</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>171.14</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>BANDHANBNK operates in the Financial Services sector. With an estimated Market Cap of ₹28,715.48 Cr., a P/E ratio of 21.24, and YoY Revenue Growth of +21.6%, the company demonstrates strong institutional backing, solid operating profit margins (13.62%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.58 (Bullish Momentum Zone), while MACD Line (3.24) trades above Signal (1.76) with an expanding histogram (+1.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.78% above the 200-day DMA (₹175.19). Daily volatility envelope is bounded by ATR(14) of ₹5.87.</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BANDHANBNK. Current Market Price (₹178.23) is positioned above the 30-day DMA (₹173.76), 50-day DMA (₹172.71), and 200-day DMA (₹175.19). The price distance from 200 DMA is +5.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>[178.23, 178.76, 179.3, 179.83, 180.37, 180.9]</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>[178.23, 181.11, 182.62, 183.9, 185.06, 186.15]</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>[178.23, 177.0, 176.81, 176.79, 176.85, 176.97]</t>
-        </is>
-      </c>
-      <c r="AU4" t="n">
-        <v>193.38</v>
+        <v>172.16</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU3"/>
+  <dimension ref="A1:AU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,335 +656,168 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>166836</v>
+        <v>28628.48</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>674</v>
+        <v>177.69</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹670.75 - ₹678.88</t>
+          <t>₹176.47 - ₹179.52</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>687.01</v>
+        <v>182.58</v>
       </c>
       <c r="I2" t="n">
-        <v>665.9400000000001</v>
+        <v>174.06</v>
       </c>
       <c r="J2" t="n">
-        <v>661.48</v>
+        <v>172.83</v>
       </c>
       <c r="K2" t="n">
-        <v>621.33</v>
+        <v>175.33</v>
       </c>
       <c r="L2" t="n">
-        <v>5.1</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>0.27</v>
+        <v>2.8</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.05</v>
+        <v>1.97</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>0.83</v>
       </c>
       <c r="P2" t="n">
-        <v>16.26</v>
+        <v>6.11</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.49</v>
+        <v>14.05</v>
       </c>
       <c r="R2" t="n">
-        <v>50.3</v>
+        <v>39.1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.26</v>
+        <v>-2.65</v>
       </c>
       <c r="U2" t="n">
-        <v>59</v>
+        <v>45.9</v>
       </c>
       <c r="V2" t="n">
-        <v>7.91</v>
+        <v>6.76</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>647.09</v>
+        <v>171.44</v>
       </c>
       <c r="Y2" t="n">
-        <v>606.84</v>
+        <v>171.64</v>
       </c>
       <c r="Z2" t="n">
-        <v>606.65</v>
+        <v>171.64</v>
       </c>
       <c r="AA2" t="n">
-        <v>649.61</v>
+        <v>168.52</v>
       </c>
       <c r="AB2" t="n">
-        <v>667</v>
+        <v>178.58</v>
       </c>
       <c r="AC2" t="n">
-        <v>681</v>
+        <v>180.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>688</v>
+        <v>182.39</v>
       </c>
       <c r="AE2" t="n">
-        <v>49.2</v>
+        <v>53.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Low VIX (13.49) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>37.6</v>
+        <v>21.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-52.9</v>
+        <v>21.6</v>
       </c>
       <c r="AK2" t="n">
-        <v>65.8</v>
+        <v>13.6</v>
       </c>
       <c r="AL2" t="n">
-        <v>10.1</v>
+        <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>693.11</v>
+        <v>185.04</v>
       </c>
       <c r="AN2" t="n">
-        <v>653.42</v>
+        <v>169.94</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹166,836.00 Cr., a P/E ratio of 37.59, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
+          <t>BANDHANBNK operates in the Financial Services sector. With an estimated Market Cap of ₹28,628.48 Cr., a P/E ratio of 21.18, and YoY Revenue Growth of +21.6%, the company demonstrates strong institutional backing, solid operating profit margins (13.62%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 49.23 (Consolidation Zone), while MACD Line (0.27) trades above Signal (-1.05) with an expanding histogram (+1.31). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.10% above the 200-day DMA (₹621.33). Daily volatility envelope is bounded by ATR(14) of ₹16.26.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.59 (Consolidation Zone), while MACD Line (2.80) trades above Signal (1.97) with an expanding histogram (+0.83). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +1.65% above the 200-day DMA (₹175.33). Daily volatility envelope is bounded by ATR(14) of ₹6.11.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DLF. Current Market Price (₹674.00) is positioned above the 30-day DMA (₹665.94), 50-day DMA (₹661.48), and 200-day DMA (₹621.33). The price distance from 200 DMA is +5.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BANDHANBNK. Current Market Price (₹177.69) is positioned above the 30-day DMA (₹174.06), 50-day DMA (₹172.83), and 200-day DMA (₹175.33). The price distance from 200 DMA is +1.65%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[674.0, 676.02, 678.04, 680.07, 682.09, 684.11]</t>
+          <t>[177.69, 178.22, 178.76, 179.29, 179.82, 180.36]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[674.0, 682.52, 687.24, 691.33, 695.09, 698.65]</t>
+          <t>[177.69, 180.67, 182.21, 183.52, 184.71, 185.82]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[674.0, 671.14, 671.15, 671.62, 672.33, 673.2]</t>
+          <t>[177.69, 176.39, 176.16, 176.11, 176.15, 176.25]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>606.65</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BANDHANBNK</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>28715.48</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>178.23</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>₹177.06 - ₹179.99</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>182.92</v>
-      </c>
-      <c r="I3" t="n">
-        <v>173.76</v>
-      </c>
-      <c r="J3" t="n">
-        <v>172.71</v>
-      </c>
-      <c r="K3" t="n">
-        <v>175.19</v>
-      </c>
-      <c r="L3" t="n">
-        <v>5.78</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>13.49</v>
-      </c>
-      <c r="R3" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-2.42</v>
-      </c>
-      <c r="U3" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X3" t="n">
-        <v>171.31</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>172.16</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>172.16</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>169.43</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>179.95</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>182.64</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>187.06</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.49) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>185.85</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>170.71</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>BANDHANBNK operates in the Financial Services sector. With an estimated Market Cap of ₹28,715.48 Cr., a P/E ratio of 21.24, and YoY Revenue Growth of +21.6%, the company demonstrates strong institutional backing, solid operating profit margins (13.62%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.58 (Bullish Momentum Zone), while MACD Line (3.24) trades above Signal (1.76) with an expanding histogram (+1.48). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +5.78% above the 200-day DMA (₹175.19). Daily volatility envelope is bounded by ATR(14) of ₹5.87.</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BANDHANBNK. Current Market Price (₹178.23) is positioned above the 30-day DMA (₹173.76), 50-day DMA (₹172.71), and 200-day DMA (₹175.19). The price distance from 200 DMA is +5.78%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>[178.23, 178.76, 179.3, 179.83, 180.37, 180.9]</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>[178.23, 181.11, 182.62, 183.9, 185.06, 186.15]</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>[178.23, 177.0, 176.81, 176.79, 176.85, 176.97]</t>
-        </is>
-      </c>
-      <c r="AU3" t="n">
-        <v>172.16</v>
+        <v>171.64</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28628.48</v>
+        <v>104694.48</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>177.69</v>
+        <v>2535</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹176.47 - ₹179.52</t>
+          <t>₹2522.16 - ₹2554.26</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>182.58</v>
+        <v>2586.37</v>
       </c>
       <c r="I2" t="n">
-        <v>174.06</v>
+        <v>2374.21</v>
       </c>
       <c r="J2" t="n">
-        <v>172.83</v>
+        <v>2412.24</v>
       </c>
       <c r="K2" t="n">
-        <v>175.33</v>
+        <v>2296.09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>2.8</v>
+        <v>31.9</v>
       </c>
       <c r="N2" t="n">
-        <v>1.97</v>
+        <v>6.94</v>
       </c>
       <c r="O2" t="n">
-        <v>0.83</v>
+        <v>24.96</v>
       </c>
       <c r="P2" t="n">
-        <v>6.11</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.05</v>
+        <v>14.45</v>
       </c>
       <c r="R2" t="n">
-        <v>39.1</v>
+        <v>36.8</v>
       </c>
       <c r="S2" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.65</v>
+        <v>-1.97</v>
       </c>
       <c r="U2" t="n">
-        <v>45.9</v>
+        <v>43.3</v>
       </c>
       <c r="V2" t="n">
-        <v>6.76</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>171.44</v>
+        <v>2466.59</v>
       </c>
       <c r="Y2" t="n">
-        <v>171.64</v>
+        <v>2406.77</v>
       </c>
       <c r="Z2" t="n">
-        <v>171.64</v>
+        <v>2338.52</v>
       </c>
       <c r="AA2" t="n">
-        <v>168.52</v>
+        <v>2438.68</v>
       </c>
       <c r="AB2" t="n">
-        <v>178.58</v>
+        <v>2515.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>180.04</v>
+        <v>2554.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>182.39</v>
+        <v>2574.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>53.6</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | LSTM Deep Net</t>
+          <t>Vol Spike 2.5x | Inst. Buying (CMF+) | Strong RSI | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>21.2</v>
+        <v>51.2</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21.6</v>
+        <v>12.9</v>
       </c>
       <c r="AK2" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>185.04</v>
+        <v>2603.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>169.94</v>
+        <v>2469.44</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>BANDHANBNK operates in the Financial Services sector. With an estimated Market Cap of ₹28,628.48 Cr., a P/E ratio of 21.18, and YoY Revenue Growth of +21.6%, the company demonstrates strong institutional backing, solid operating profit margins (13.62%), and healthy Return on Equity (15.00%).</t>
+          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹104,694.48 Cr., a P/E ratio of 51.21, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 53.59 (Consolidation Zone), while MACD Line (2.80) trades above Signal (1.97) with an expanding histogram (+0.83). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +1.65% above the 200-day DMA (₹175.33). Daily volatility envelope is bounded by ATR(14) of ₹6.11.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 73.05 (Bullish Momentum Zone), while MACD Line (31.90) trades above Signal (6.94) with an expanding histogram (+24.96). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.05% above the 200-day DMA (₹2296.09). Daily volatility envelope is bounded by ATR(14) of ₹64.21.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for BANDHANBNK. Current Market Price (₹177.69) is positioned above the 30-day DMA (₹174.06), 50-day DMA (₹172.83), and 200-day DMA (₹175.33). The price distance from 200 DMA is +1.65%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,535.00) is positioned above the 30-day DMA (₹2,374.21), 50-day DMA (₹2,412.24), and 200-day DMA (₹2,296.09). The price distance from 200 DMA is +9.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[177.69, 178.22, 178.76, 179.29, 179.82, 180.36]</t>
+          <t>[2535.0, 2542.6, 2550.21, 2557.81, 2565.42, 2573.02]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[177.69, 180.67, 182.21, 183.52, 184.71, 185.82]</t>
+          <t>[2535.0, 2568.29, 2586.54, 2602.3, 2616.79, 2630.46]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[177.69, 176.39, 176.16, 176.11, 176.15, 176.25]</t>
+          <t>[2535.0, 2523.34, 2522.97, 2524.45, 2526.89, 2529.95]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>171.64</v>
+        <v>2338.52</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -656,21 +656,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Basic Materials</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>104694.48</v>
+        <v>58744.18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2535</v>
+        <v>2190.1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹2522.16 - ₹2554.26</t>
+          <t>₹2178.95 - ₹2206.83</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2586.37</v>
+        <v>2234.71</v>
       </c>
       <c r="I2" t="n">
-        <v>2374.21</v>
+        <v>2178.03</v>
       </c>
       <c r="J2" t="n">
-        <v>2412.24</v>
+        <v>2080.92</v>
       </c>
       <c r="K2" t="n">
-        <v>2296.09</v>
+        <v>1977.45</v>
       </c>
       <c r="L2" t="n">
-        <v>9.050000000000001</v>
+        <v>10.68</v>
       </c>
       <c r="M2" t="n">
-        <v>31.9</v>
+        <v>27.87</v>
       </c>
       <c r="N2" t="n">
-        <v>6.94</v>
+        <v>34.3</v>
       </c>
       <c r="O2" t="n">
-        <v>24.96</v>
+        <v>-6.43</v>
       </c>
       <c r="P2" t="n">
-        <v>64.20999999999999</v>
+        <v>55.76</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.45</v>
+        <v>14.46</v>
       </c>
       <c r="R2" t="n">
-        <v>36.8</v>
+        <v>42.5</v>
       </c>
       <c r="S2" t="n">
         <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.97</v>
+        <v>-1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>43.3</v>
+        <v>53.3</v>
       </c>
       <c r="V2" t="n">
-        <v>8.390000000000001</v>
+        <v>4.04</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2466.59</v>
+        <v>2190.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>2406.77</v>
+        <v>2334.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>2338.52</v>
+        <v>2334.12</v>
       </c>
       <c r="AA2" t="n">
-        <v>2438.68</v>
+        <v>2106.46</v>
       </c>
       <c r="AB2" t="n">
-        <v>2515.37</v>
+        <v>2198.73</v>
       </c>
       <c r="AC2" t="n">
-        <v>2554.64</v>
+        <v>2215.86</v>
       </c>
       <c r="AD2" t="n">
-        <v>2574.27</v>
+        <v>2241.63</v>
       </c>
       <c r="AE2" t="n">
-        <v>73.09999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Vol Spike 2.5x | Inst. Buying (CMF+) | Strong RSI | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>51.2</v>
+        <v>47.8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12.9</v>
+        <v>8.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>13.9</v>
+        <v>5.2</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>2603.4</v>
+        <v>2255.39</v>
       </c>
       <c r="AN2" t="n">
-        <v>2469.44</v>
+        <v>2133.44</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹104,694.48 Cr., a P/E ratio of 51.21, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
+          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹58,744.18 Cr., a P/E ratio of 47.77, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 73.05 (Bullish Momentum Zone), while MACD Line (31.90) trades above Signal (6.94) with an expanding histogram (+24.96). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.05% above the 200-day DMA (₹2296.09). Daily volatility envelope is bounded by ATR(14) of ₹64.21.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.44 (Consolidation Zone), while MACD Line (27.87) trades below Signal (34.30) with an expanding histogram (-6.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.68% above the 200-day DMA (₹1977.45). Daily volatility envelope is bounded by ATR(14) of ₹55.76.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,535.00) is positioned above the 30-day DMA (₹2,374.21), 50-day DMA (₹2,412.24), and 200-day DMA (₹2,296.09). The price distance from 200 DMA is +9.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,190.10) is positioned above the 30-day DMA (₹2,178.03), 50-day DMA (₹2,080.92), and 200-day DMA (₹1,977.45). The price distance from 200 DMA is +10.68%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[2535.0, 2542.6, 2550.21, 2557.81, 2565.42, 2573.02]</t>
+          <t>[2190.1, 2196.67, 2203.24, 2209.81, 2216.38, 2222.95]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[2535.0, 2568.29, 2586.54, 2602.3, 2616.79, 2630.46]</t>
+          <t>[2190.1, 2218.97, 2234.78, 2248.44, 2260.99, 2272.82]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[2535.0, 2523.34, 2522.97, 2524.45, 2526.89, 2529.95]</t>
+          <t>[2190.1, 2179.94, 2179.58, 2180.84, 2182.93, 2185.55]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2338.52</v>
+        <v>2334.12</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -656,21 +656,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>58744.18</v>
+        <v>104706.93</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2190.1</v>
+        <v>2535</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹2178.95 - ₹2206.83</t>
+          <t>₹2522.16 - ₹2554.26</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2234.71</v>
+        <v>2586.37</v>
       </c>
       <c r="I2" t="n">
-        <v>2178.03</v>
+        <v>2374.21</v>
       </c>
       <c r="J2" t="n">
-        <v>2080.92</v>
+        <v>2412.24</v>
       </c>
       <c r="K2" t="n">
-        <v>1977.45</v>
+        <v>2296.09</v>
       </c>
       <c r="L2" t="n">
-        <v>10.68</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>27.87</v>
+        <v>31.9</v>
       </c>
       <c r="N2" t="n">
-        <v>34.3</v>
+        <v>6.94</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.43</v>
+        <v>24.96</v>
       </c>
       <c r="P2" t="n">
-        <v>55.76</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="Q2" t="n">
         <v>14.46</v>
       </c>
       <c r="R2" t="n">
-        <v>42.5</v>
+        <v>36.8</v>
       </c>
       <c r="S2" t="n">
         <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.72</v>
+        <v>-1.97</v>
       </c>
       <c r="U2" t="n">
-        <v>53.3</v>
+        <v>43.3</v>
       </c>
       <c r="V2" t="n">
-        <v>4.04</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2190.1</v>
+        <v>2535</v>
       </c>
       <c r="Y2" t="n">
-        <v>2334.12</v>
+        <v>2735.89</v>
       </c>
       <c r="Z2" t="n">
-        <v>2334.12</v>
+        <v>2735.89</v>
       </c>
       <c r="AA2" t="n">
-        <v>2106.46</v>
+        <v>2438.68</v>
       </c>
       <c r="AB2" t="n">
-        <v>2198.73</v>
+        <v>2515.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>2215.86</v>
+        <v>2554.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>2241.63</v>
+        <v>2574.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>52.4</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | LSTM Deep Net</t>
+          <t>Vol Spike 2.5x | Inst. Buying (CMF+) | Strong RSI | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>47.8</v>
+        <v>50.6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>8.5</v>
+        <v>12.9</v>
       </c>
       <c r="AK2" t="n">
-        <v>5.2</v>
+        <v>13.9</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>2255.39</v>
+        <v>2600.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>2133.44</v>
+        <v>2467.34</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>APLAPOLLO operates in the Basic Materials sector. With an estimated Market Cap of ₹58,744.18 Cr., a P/E ratio of 47.77, and YoY Revenue Growth of +8.5%, the company demonstrates strong institutional backing, solid operating profit margins (5.23%), and healthy Return on Equity (15.00%).</t>
+          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹104,706.93 Cr., a P/E ratio of 50.56, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.44 (Consolidation Zone), while MACD Line (27.87) trades below Signal (34.30) with an expanding histogram (-6.43). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.68% above the 200-day DMA (₹1977.45). Daily volatility envelope is bounded by ATR(14) of ₹55.76.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 73.05 (Bullish Momentum Zone), while MACD Line (31.90) trades above Signal (6.94) with an expanding histogram (+24.96). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.05% above the 200-day DMA (₹2296.09). Daily volatility envelope is bounded by ATR(14) of ₹64.21.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for APLAPOLLO. Current Market Price (₹2,190.10) is positioned above the 30-day DMA (₹2,178.03), 50-day DMA (₹2,080.92), and 200-day DMA (₹1,977.45). The price distance from 200 DMA is +10.68%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,535.00) is positioned above the 30-day DMA (₹2,374.21), 50-day DMA (₹2,412.24), and 200-day DMA (₹2,296.09). The price distance from 200 DMA is +9.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[2190.1, 2196.67, 2203.24, 2209.81, 2216.38, 2222.95]</t>
+          <t>[2535.0, 2545.95, 2556.89, 2567.84, 2578.78, 2589.73]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[2190.1, 2218.97, 2234.78, 2248.44, 2260.99, 2272.82]</t>
+          <t>[2535.0, 2571.63, 2593.22, 2612.32, 2630.15, 2647.16]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[2190.1, 2179.94, 2179.58, 2180.84, 2182.93, 2185.55]</t>
+          <t>[2535.0, 2526.68, 2529.65, 2534.47, 2540.25, 2546.65]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2334.12</v>
+        <v>2735.89</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -716,13 +716,13 @@
         <v>14.46</v>
       </c>
       <c r="R2" t="n">
-        <v>36.8</v>
+        <v>37.3</v>
       </c>
       <c r="S2" t="n">
         <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.97</v>
+        <v>-1.95</v>
       </c>
       <c r="U2" t="n">
         <v>43.3</v>
@@ -734,13 +734,13 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2535</v>
+        <v>2463</v>
       </c>
       <c r="Y2" t="n">
-        <v>2735.89</v>
+        <v>2494.26</v>
       </c>
       <c r="Z2" t="n">
-        <v>2735.89</v>
+        <v>2367.65</v>
       </c>
       <c r="AA2" t="n">
         <v>2438.68</v>
@@ -781,10 +781,10 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>2600.2</v>
+        <v>2597.13</v>
       </c>
       <c r="AN2" t="n">
-        <v>2467.34</v>
+        <v>2467.02</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2735.89</v>
+        <v>2367.65</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -716,13 +716,13 @@
         <v>14.46</v>
       </c>
       <c r="R2" t="n">
-        <v>37.3</v>
+        <v>36.7</v>
       </c>
       <c r="S2" t="n">
         <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.95</v>
+        <v>-1.97</v>
       </c>
       <c r="U2" t="n">
         <v>43.3</v>
@@ -769,7 +769,7 @@
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>50.6</v>
+        <v>51.3</v>
       </c>
       <c r="AJ2" t="n">
         <v>12.9</v>
@@ -781,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>2597.13</v>
+        <v>2598.59</v>
       </c>
       <c r="AN2" t="n">
-        <v>2467.02</v>
+        <v>2467.93</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹104,706.93 Cr., a P/E ratio of 50.56, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
+          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹104,706.93 Cr., a P/E ratio of 51.28, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -716,7 +716,7 @@
         <v>14.46</v>
       </c>
       <c r="R2" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="S2" t="n">
         <v>0.21</v>
@@ -781,10 +781,10 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>2598.59</v>
+        <v>2599.71</v>
       </c>
       <c r="AN2" t="n">
-        <v>2467.93</v>
+        <v>2466.61</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>104706.93</v>
+        <v>104694.48</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -716,13 +716,13 @@
         <v>14.46</v>
       </c>
       <c r="R2" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="S2" t="n">
         <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.97</v>
+        <v>-1.98</v>
       </c>
       <c r="U2" t="n">
         <v>43.3</v>
@@ -734,13 +734,13 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2463</v>
+        <v>2535</v>
       </c>
       <c r="Y2" t="n">
-        <v>2494.26</v>
+        <v>2735.89</v>
       </c>
       <c r="Z2" t="n">
-        <v>2367.65</v>
+        <v>2735.89</v>
       </c>
       <c r="AA2" t="n">
         <v>2438.68</v>
@@ -781,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>2599.71</v>
+        <v>2601.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>2466.61</v>
+        <v>2467.58</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹104,706.93 Cr., a P/E ratio of 51.28, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
+          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹104,694.48 Cr., a P/E ratio of 51.30, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2367.65</v>
+        <v>2735.89</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AU4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,168 +656,502 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>104694.48</v>
+        <v>166291.43</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2535</v>
+        <v>671.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹2522.16 - ₹2554.26</t>
+          <t>₹668.43 - ₹676.85</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2586.37</v>
+        <v>685.27</v>
       </c>
       <c r="I2" t="n">
-        <v>2374.21</v>
+        <v>665.49</v>
       </c>
       <c r="J2" t="n">
-        <v>2412.24</v>
+        <v>662.58</v>
       </c>
       <c r="K2" t="n">
-        <v>2296.09</v>
+        <v>621.13</v>
       </c>
       <c r="L2" t="n">
-        <v>9.050000000000001</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
-        <v>31.9</v>
+        <v>0.79</v>
       </c>
       <c r="N2" t="n">
-        <v>6.94</v>
+        <v>-0.31</v>
       </c>
       <c r="O2" t="n">
-        <v>24.96</v>
+        <v>1.1</v>
       </c>
       <c r="P2" t="n">
-        <v>64.20999999999999</v>
+        <v>16.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.46</v>
+        <v>15.12</v>
       </c>
       <c r="R2" t="n">
-        <v>36.6</v>
+        <v>47.2</v>
       </c>
       <c r="S2" t="n">
         <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.98</v>
+        <v>-1.47</v>
       </c>
       <c r="U2" t="n">
-        <v>43.3</v>
+        <v>58.3</v>
       </c>
       <c r="V2" t="n">
-        <v>9.449999999999999</v>
+        <v>9.02</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2535</v>
+        <v>658.6799999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>2735.89</v>
+        <v>701.3200000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>2735.89</v>
+        <v>701.3200000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>2438.68</v>
+        <v>646.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>2515.37</v>
+        <v>670.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>2554.64</v>
+        <v>677</v>
       </c>
       <c r="AD2" t="n">
-        <v>2574.27</v>
+        <v>682.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>73.09999999999999</v>
+        <v>54.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.24</v>
+        <v>-0.18</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Vol Spike 2.5x | Inst. Buying (CMF+) | Strong RSI | LSTM Deep Net</t>
+          <t>LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>51.3</v>
+        <v>37.4</v>
       </c>
       <c r="AJ2" t="n">
+        <v>-52.9</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>692.52</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>651.97</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹166,291.43 Cr., a P/E ratio of 37.41, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.30 (Consolidation Zone), while MACD Line (0.79) trades above Signal (-0.31) with an expanding histogram (+1.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.00% above the 200-day DMA (₹621.13). Daily volatility envelope is bounded by ATR(14) of ₹16.84.</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DLF. Current Market Price (₹671.80) is positioned above the 30-day DMA (₹665.49), 50-day DMA (₹662.58), and 200-day DMA (₹621.13). The price distance from 200 DMA is +6.00%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>[671.8, 673.82, 675.83, 677.85, 679.86, 681.88]</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>[671.8, 680.55, 685.35, 689.51, 693.33, 696.94]</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>[671.8, 668.76, 668.69, 669.1, 669.76, 670.58]</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>701.3200000000001</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>43387.5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>289.25</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>₹288.11 - ₹290.95</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>293.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>288.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>285.37</v>
+      </c>
+      <c r="K3" t="n">
+        <v>279.62</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="R3" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>55</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X3" t="n">
+        <v>285.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>301.96</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>301.96</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>280.73</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>289.92</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>293.34</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>297.42</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>TTM Squeeze | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-53.2</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>297.31</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>280.99</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,387.50 Cr., a P/E ratio of 10.31, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.08 (Consolidation Zone), while MACD Line (-0.30) trades below Signal (0.02) with an expanding histogram (-0.32). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.10% above the 200-day DMA (₹279.62). Daily volatility envelope is bounded by ATR(14) of ₹5.68.</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹289.25) is positioned above the 30-day DMA (₹288.40), 50-day DMA (₹285.37), and 200-day DMA (₹279.62). The price distance from 200 DMA is +2.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>[289.25, 290.12, 290.99, 291.85, 292.72, 293.59]</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>[289.25, 292.39, 294.2, 295.79, 297.27, 298.67]</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>[289.25, 288.41, 288.57, 288.9, 289.31, 289.78]</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>301.96</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>103864.35</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2514.9</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>₹2502.04 - ₹2534.18</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>2566.32</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2379.21</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2411.79</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2298.06</v>
+      </c>
+      <c r="L4" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="M4" t="n">
+        <v>37.27</v>
+      </c>
+      <c r="N4" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="O4" t="n">
+        <v>24.26</v>
+      </c>
+      <c r="P4" t="n">
+        <v>64.28</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="R4" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-2.11</v>
+      </c>
+      <c r="U4" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2479.87</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2714.2</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2714.2</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2418.48</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2516.73</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2537.46</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2560.03</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Strong RSI | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>12.9</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AK4" t="n">
         <v>13.9</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AL4" t="n">
         <v>15</v>
       </c>
-      <c r="AM2" t="n">
-        <v>2601.55</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2467.58</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹104,694.48 Cr., a P/E ratio of 51.30, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 73.05 (Bullish Momentum Zone), while MACD Line (31.90) trades above Signal (6.94) with an expanding histogram (+24.96). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +9.05% above the 200-day DMA (₹2296.09). Daily volatility envelope is bounded by ATR(14) of ₹64.21.</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,535.00) is positioned above the 30-day DMA (₹2,374.21), 50-day DMA (₹2,412.24), and 200-day DMA (₹2,296.09). The price distance from 200 DMA is +9.05%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>[2535.0, 2545.95, 2556.89, 2567.84, 2578.78, 2589.73]</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>[2535.0, 2571.63, 2593.22, 2612.32, 2630.15, 2647.16]</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>[2535.0, 2526.68, 2529.65, 2534.47, 2540.25, 2546.65]</t>
-        </is>
-      </c>
-      <c r="AU2" t="n">
-        <v>2735.89</v>
+      <c r="AM4" t="n">
+        <v>2580.3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2448.52</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹103,864.35 Cr., a P/E ratio of 50.89, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 72.56 (Bullish Momentum Zone), while MACD Line (37.27) trades above Signal (13.01) with an expanding histogram (+24.26). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.31% above the 200-day DMA (₹2298.06). Daily volatility envelope is bounded by ATR(14) of ₹64.28.</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,514.90) is positioned above the 30-day DMA (₹2,379.21), 50-day DMA (₹2,411.79), and 200-day DMA (₹2,298.06). The price distance from 200 DMA is +10.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>[2514.9, 2522.44, 2529.99, 2537.53, 2545.08, 2552.62]</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>[2514.9, 2548.16, 2566.35, 2582.07, 2596.5, 2610.12]</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>[2514.9, 2503.16, 2502.72, 2504.13, 2506.51, 2509.5]</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>2714.2</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU4"/>
+  <dimension ref="A1:AU5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,7 +656,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>166291.43</v>
+        <v>167009.28</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,98 +678,98 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>671.8</v>
+        <v>674.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹668.43 - ₹676.85</t>
+          <t>₹671.45 - ₹679.58</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>685.27</v>
+        <v>687.7</v>
       </c>
       <c r="I2" t="n">
-        <v>665.49</v>
+        <v>664.3</v>
       </c>
       <c r="J2" t="n">
-        <v>662.58</v>
+        <v>663.4400000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>621.13</v>
+        <v>621.0599999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>0.79</v>
+        <v>1.26</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.31</v>
+        <v>0.12</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="P2" t="n">
-        <v>16.84</v>
+        <v>16.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>15.12</v>
+        <v>14.45</v>
       </c>
       <c r="R2" t="n">
-        <v>47.2</v>
+        <v>45</v>
       </c>
       <c r="S2" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.47</v>
+        <v>-1.49</v>
       </c>
       <c r="U2" t="n">
-        <v>58.3</v>
+        <v>59</v>
       </c>
       <c r="V2" t="n">
-        <v>9.02</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>658.6799999999999</v>
+        <v>654.0599999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>701.3200000000001</v>
+        <v>652.64</v>
       </c>
       <c r="Z2" t="n">
-        <v>701.3200000000001</v>
+        <v>652.64</v>
       </c>
       <c r="AA2" t="n">
-        <v>646.55</v>
+        <v>650.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>670.5</v>
+        <v>673.53</v>
       </c>
       <c r="AC2" t="n">
-        <v>677</v>
+        <v>676.21</v>
       </c>
       <c r="AD2" t="n">
-        <v>682.2</v>
+        <v>677.73</v>
       </c>
       <c r="AE2" t="n">
-        <v>54.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.18</v>
+        <v>-0.13</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>LSTM Deep Net</t>
+          <t>Strong RSI | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="AJ2" t="n">
         <v>-52.9</v>
@@ -781,49 +781,49 @@
         <v>10.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>692.52</v>
+        <v>692.51</v>
       </c>
       <c r="AN2" t="n">
-        <v>651.97</v>
+        <v>653.55</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹166,291.43 Cr., a P/E ratio of 37.41, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
+          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹167,009.28 Cr., a P/E ratio of 37.57, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.30 (Consolidation Zone), while MACD Line (0.79) trades above Signal (-0.31) with an expanding histogram (+1.10). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.00% above the 200-day DMA (₹621.13). Daily volatility envelope is bounded by ATR(14) of ₹16.84.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 67.09 (Bullish Momentum Zone), while MACD Line (1.26) trades above Signal (0.12) with an expanding histogram (+1.14). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.36% above the 200-day DMA (₹621.06). Daily volatility envelope is bounded by ATR(14) of ₹16.25.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DLF. Current Market Price (₹671.80) is positioned above the 30-day DMA (₹665.49), 50-day DMA (₹662.58), and 200-day DMA (₹621.13). The price distance from 200 DMA is +6.00%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DLF. Current Market Price (₹674.70) is positioned above the 30-day DMA (₹664.30), 50-day DMA (₹663.44), and 200-day DMA (₹621.06). The price distance from 200 DMA is +8.36%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[671.8, 673.82, 675.83, 677.85, 679.86, 681.88]</t>
+          <t>[674.7, 676.72, 678.75, 680.77, 682.8, 684.82]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[671.8, 680.55, 685.35, 689.51, 693.33, 696.94]</t>
+          <t>[674.7, 683.22, 687.94, 692.03, 695.8, 699.35]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[671.8, 668.76, 668.69, 669.1, 669.76, 670.58]</t>
+          <t>[674.7, 671.85, 671.85, 672.33, 673.05, 673.92]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>701.3200000000001</v>
+        <v>652.64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>43387.5</v>
+        <v>43912.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,15 +845,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>289.25</v>
+        <v>292.75</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹288.11 - ₹290.95</t>
+          <t>₹291.61 - ₹294.45</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>293.8</v>
+        <v>297.3</v>
       </c>
       <c r="I3" t="n">
         <v>288.4</v>
@@ -880,46 +880,46 @@
         <v>5.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>15.12</v>
+        <v>14.45</v>
       </c>
       <c r="R3" t="n">
-        <v>43.7</v>
+        <v>44</v>
       </c>
       <c r="S3" t="n">
         <v>0.27</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2</v>
+        <v>-1.17</v>
       </c>
       <c r="U3" t="n">
         <v>55</v>
       </c>
       <c r="V3" t="n">
-        <v>6.21</v>
+        <v>6.25</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>285.5</v>
+        <v>285.43</v>
       </c>
       <c r="Y3" t="n">
-        <v>301.96</v>
+        <v>279</v>
       </c>
       <c r="Z3" t="n">
-        <v>301.96</v>
+        <v>279</v>
       </c>
       <c r="AA3" t="n">
-        <v>280.73</v>
+        <v>284.23</v>
       </c>
       <c r="AB3" t="n">
-        <v>289.92</v>
+        <v>292.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>293.34</v>
+        <v>293.66</v>
       </c>
       <c r="AD3" t="n">
-        <v>297.42</v>
+        <v>294.58</v>
       </c>
       <c r="AE3" t="n">
         <v>48.1</v>
@@ -936,7 +936,7 @@
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="AJ3" t="n">
         <v>-53.2</v>
@@ -948,14 +948,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>297.31</v>
+        <v>301.37</v>
       </c>
       <c r="AN3" t="n">
-        <v>280.99</v>
+        <v>284.35</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,387.50 Cr., a P/E ratio of 10.31, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,912.50 Cr., a P/E ratio of 10.43, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -965,46 +965,46 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹289.25) is positioned above the 30-day DMA (₹288.40), 50-day DMA (₹285.37), and 200-day DMA (₹279.62). The price distance from 200 DMA is +2.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹292.75) is positioned above the 30-day DMA (₹288.40), 50-day DMA (₹285.37), and 200-day DMA (₹279.62). The price distance from 200 DMA is +2.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[289.25, 290.12, 290.99, 291.85, 292.72, 293.59]</t>
+          <t>[292.75, 293.63, 294.51, 295.38, 296.26, 297.14]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[289.25, 292.39, 294.2, 295.79, 297.27, 298.67]</t>
+          <t>[292.75, 295.9, 297.72, 299.32, 300.81, 302.22]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[289.25, 288.41, 288.57, 288.9, 289.31, 289.78]</t>
+          <t>[292.75, 291.92, 292.1, 292.43, 292.85, 293.33]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>301.96</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>103864.35</v>
+        <v>62471.46</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,146 +1012,313 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2514.9</v>
+        <v>1036.05</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹2502.04 - ₹2534.18</t>
+          <t>₹1030.76 - ₹1043.98</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2566.32</v>
+        <v>1057.21</v>
       </c>
       <c r="I4" t="n">
-        <v>2379.21</v>
+        <v>1016.93</v>
       </c>
       <c r="J4" t="n">
-        <v>2411.79</v>
+        <v>970.4400000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>2298.06</v>
+        <v>860.46</v>
       </c>
       <c r="L4" t="n">
-        <v>10.31</v>
+        <v>17.51</v>
       </c>
       <c r="M4" t="n">
-        <v>37.27</v>
+        <v>3.41</v>
       </c>
       <c r="N4" t="n">
-        <v>13.01</v>
+        <v>7.81</v>
       </c>
       <c r="O4" t="n">
-        <v>24.26</v>
+        <v>-4.4</v>
       </c>
       <c r="P4" t="n">
-        <v>64.28</v>
+        <v>26.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.12</v>
+        <v>14.45</v>
       </c>
       <c r="R4" t="n">
-        <v>34.1</v>
+        <v>39.1</v>
       </c>
       <c r="S4" t="n">
         <v>0.21</v>
       </c>
       <c r="T4" t="n">
-        <v>-2.11</v>
+        <v>-1.88</v>
       </c>
       <c r="U4" t="n">
-        <v>43.3</v>
+        <v>47.5</v>
       </c>
       <c r="V4" t="n">
-        <v>9.34</v>
+        <v>3.67</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2479.87</v>
+        <v>1010.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>2714.2</v>
+        <v>1004.39</v>
       </c>
       <c r="Z4" t="n">
-        <v>2714.2</v>
+        <v>986.22</v>
       </c>
       <c r="AA4" t="n">
-        <v>2418.48</v>
+        <v>996.38</v>
       </c>
       <c r="AB4" t="n">
-        <v>2516.73</v>
+        <v>1030.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>2537.46</v>
+        <v>1043.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>2560.03</v>
+        <v>1051.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>72.59999999999999</v>
+        <v>55.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.27</v>
+        <v>-0.02</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | LSTM Deep Net</t>
+          <t>LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>50.9</v>
+        <v>32.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12.9</v>
+        <v>23.9</v>
       </c>
       <c r="AK4" t="n">
-        <v>13.9</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>2580.3</v>
+        <v>1074.59</v>
       </c>
       <c r="AN4" t="n">
-        <v>2448.52</v>
+        <v>997.1900000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹103,864.35 Cr., a P/E ratio of 50.89, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹62,471.46 Cr., a P/E ratio of 32.12, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 72.56 (Bullish Momentum Zone), while MACD Line (37.27) trades above Signal (13.01) with an expanding histogram (+24.26). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.31% above the 200-day DMA (₹2298.06). Daily volatility envelope is bounded by ATR(14) of ₹64.28.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.12 (Bullish Momentum Zone), while MACD Line (3.41) trades below Signal (7.81) with an expanding histogram (-4.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.51% above the 200-day DMA (₹860.46). Daily volatility envelope is bounded by ATR(14) of ₹26.45.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,514.90) is positioned above the 30-day DMA (₹2,379.21), 50-day DMA (₹2,411.79), and 200-day DMA (₹2,298.06). The price distance from 200 DMA is +10.31%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,036.05) is positioned above the 30-day DMA (₹1,016.93), 50-day DMA (₹970.44), and 200-day DMA (₹860.46). The price distance from 200 DMA is +17.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[2514.9, 2522.44, 2529.99, 2537.53, 2545.08, 2552.62]</t>
+          <t>[1036.05, 1039.16, 1042.27, 1045.37, 1048.48, 1051.59]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[2514.9, 2548.16, 2566.35, 2582.07, 2596.5, 2610.12]</t>
+          <t>[1036.05, 1049.74, 1057.23, 1063.7, 1069.64, 1075.25]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[2514.9, 2503.16, 2502.72, 2504.13, 2506.51, 2509.5]</t>
+          <t>[1036.05, 1031.22, 1031.05, 1031.63, 1032.61, 1033.85]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2714.2</v>
+        <v>986.22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>102456.04</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2480.8</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>₹2467.58 - ₹2500.63</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>2533.68</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2387.72</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2410.9</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2302.04</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="M5" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="N5" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="P5" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="R5" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="U5" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="V5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2397.3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2367.6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2283.94</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2381.65</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>2479.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2484.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2488.2</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>66</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Strong RSI | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2546.65</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>2419.88</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹102,456.04 Cr., a P/E ratio of 50.20, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.99 (Bullish Momentum Zone), while MACD Line (39.07) trades above Signal (22.70) with an expanding histogram (+16.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.69% above the 200-day DMA (₹2302.04). Daily volatility envelope is bounded by ATR(14) of ₹66.10.</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,480.80) is positioned above the 30-day DMA (₹2,387.72), 50-day DMA (₹2,410.90), and 200-day DMA (₹2,302.04). The price distance from 200 DMA is +7.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>[2480.8, 2488.24, 2495.68, 2503.13, 2510.57, 2518.01]</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>[2480.8, 2514.68, 2533.08, 2548.92, 2563.45, 2577.13]</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>[2480.8, 2468.41, 2467.64, 2468.78, 2470.91, 2473.67]</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>2283.94</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU5"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>167009.28</v>
+        <v>44475</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>674.7</v>
+        <v>296.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹671.45 - ₹679.58</t>
+          <t>₹295.36 - ₹298.2</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>687.7</v>
+        <v>301.05</v>
       </c>
       <c r="I2" t="n">
-        <v>664.3</v>
+        <v>288.4</v>
       </c>
       <c r="J2" t="n">
-        <v>663.4400000000001</v>
+        <v>285.37</v>
       </c>
       <c r="K2" t="n">
-        <v>621.0599999999999</v>
+        <v>279.62</v>
       </c>
       <c r="L2" t="n">
-        <v>8.359999999999999</v>
+        <v>2.1</v>
       </c>
       <c r="M2" t="n">
-        <v>1.26</v>
+        <v>-0.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="O2" t="n">
-        <v>1.14</v>
+        <v>-0.32</v>
       </c>
       <c r="P2" t="n">
-        <v>16.25</v>
+        <v>5.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.45</v>
+        <v>13.91</v>
       </c>
       <c r="R2" t="n">
-        <v>45</v>
+        <v>47.8</v>
       </c>
       <c r="S2" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.49</v>
+        <v>-1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="V2" t="n">
-        <v>8.789999999999999</v>
+        <v>6.3</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>654.0599999999999</v>
+        <v>289.18</v>
       </c>
       <c r="Y2" t="n">
-        <v>652.64</v>
+        <v>282.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>652.64</v>
+        <v>282.58</v>
       </c>
       <c r="AA2" t="n">
-        <v>650.33</v>
+        <v>287.98</v>
       </c>
       <c r="AB2" t="n">
-        <v>673.53</v>
+        <v>295.12</v>
       </c>
       <c r="AC2" t="n">
-        <v>676.21</v>
+        <v>299.24</v>
       </c>
       <c r="AD2" t="n">
-        <v>677.73</v>
+        <v>301.97</v>
       </c>
       <c r="AE2" t="n">
-        <v>67.09999999999999</v>
+        <v>48.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.13</v>
+        <v>-0.01</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Strong RSI | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (13.91) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>37.6</v>
+        <v>10.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-52.9</v>
+        <v>-53.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>65.8</v>
+        <v>11.3</v>
       </c>
       <c r="AL2" t="n">
-        <v>10.1</v>
+        <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>692.51</v>
+        <v>305.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>653.55</v>
+        <v>287.7</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹167,009.28 Cr., a P/E ratio of 37.57, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹44,475.00 Cr., a P/E ratio of 10.73, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 67.09 (Bullish Momentum Zone), while MACD Line (1.26) trades above Signal (0.12) with an expanding histogram (+1.14). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.36% above the 200-day DMA (₹621.06). Daily volatility envelope is bounded by ATR(14) of ₹16.25.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.08 (Consolidation Zone), while MACD Line (-0.30) trades below Signal (0.02) with an expanding histogram (-0.32). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.10% above the 200-day DMA (₹279.62). Daily volatility envelope is bounded by ATR(14) of ₹5.68.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DLF. Current Market Price (₹674.70) is positioned above the 30-day DMA (₹664.30), 50-day DMA (₹663.44), and 200-day DMA (₹621.06). The price distance from 200 DMA is +8.36%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹296.50) is positioned above the 30-day DMA (₹288.40), 50-day DMA (₹285.37), and 200-day DMA (₹279.62). The price distance from 200 DMA is +2.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[674.7, 676.72, 678.75, 680.77, 682.8, 684.82]</t>
+          <t>[296.5, 297.39, 298.28, 299.17, 300.06, 300.95]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[674.7, 683.22, 687.94, 692.03, 695.8, 699.35]</t>
+          <t>[296.5, 299.66, 301.49, 303.11, 304.6, 306.03]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[674.7, 671.85, 671.85, 672.33, 673.05, 673.92]</t>
+          <t>[296.5, 295.68, 295.87, 296.22, 296.65, 297.14]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>652.64</v>
+        <v>282.58</v>
       </c>
     </row>
     <row r="3">
@@ -828,163 +828,163 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>43912.5</v>
+        <v>301798.84</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>292.75</v>
+        <v>327.85</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹291.61 - ₹294.45</t>
+          <t>₹326.16 - ₹330.38</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>297.3</v>
+        <v>334.6</v>
       </c>
       <c r="I3" t="n">
-        <v>288.4</v>
+        <v>325.91</v>
       </c>
       <c r="J3" t="n">
-        <v>285.37</v>
+        <v>321.81</v>
       </c>
       <c r="K3" t="n">
-        <v>279.62</v>
+        <v>276.73</v>
       </c>
       <c r="L3" t="n">
-        <v>2.1</v>
+        <v>15.93</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02</v>
+        <v>2.49</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.32</v>
+        <v>-2.29</v>
       </c>
       <c r="P3" t="n">
-        <v>5.68</v>
+        <v>8.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>14.45</v>
+        <v>13.91</v>
       </c>
       <c r="R3" t="n">
-        <v>44</v>
+        <v>46.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0.27</v>
+        <v>0.21</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.17</v>
+        <v>-1.56</v>
       </c>
       <c r="U3" t="n">
-        <v>55</v>
+        <v>50.8</v>
       </c>
       <c r="V3" t="n">
-        <v>6.25</v>
+        <v>2.48</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>285.43</v>
+        <v>321.92</v>
       </c>
       <c r="Y3" t="n">
-        <v>279</v>
+        <v>319.78</v>
       </c>
       <c r="Z3" t="n">
-        <v>279</v>
+        <v>312.08</v>
       </c>
       <c r="AA3" t="n">
-        <v>284.23</v>
+        <v>315.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>292.33</v>
+        <v>325.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>293.66</v>
+        <v>330.94</v>
       </c>
       <c r="AD3" t="n">
-        <v>294.58</v>
+        <v>334.02</v>
       </c>
       <c r="AE3" t="n">
-        <v>48.1</v>
+        <v>54.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.01</v>
+        <v>0.08</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>TTM Squeeze | LSTM Deep Net</t>
+          <t>Low VIX (13.91) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>10.4</v>
+        <v>697.6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-53.2</v>
+        <v>182</v>
       </c>
       <c r="AK3" t="n">
-        <v>11.3</v>
+        <v>0.6</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>301.37</v>
+        <v>338.59</v>
       </c>
       <c r="AN3" t="n">
-        <v>284.35</v>
+        <v>316.51</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,912.50 Cr., a P/E ratio of 10.43, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹301,798.84 Cr., a P/E ratio of 697.55, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.08 (Consolidation Zone), while MACD Line (-0.30) trades below Signal (0.02) with an expanding histogram (-0.32). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.10% above the 200-day DMA (₹279.62). Daily volatility envelope is bounded by ATR(14) of ₹5.68.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.40 (Consolidation Zone), while MACD Line (0.20) trades below Signal (2.49) with an expanding histogram (-2.29). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.93% above the 200-day DMA (₹276.73). Daily volatility envelope is bounded by ATR(14) of ₹8.44.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹292.75) is positioned above the 30-day DMA (₹288.40), 50-day DMA (₹285.37), and 200-day DMA (₹279.62). The price distance from 200 DMA is +2.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹327.85) is positioned above the 30-day DMA (₹325.91), 50-day DMA (₹321.81), and 200-day DMA (₹276.73). The price distance from 200 DMA is +15.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[292.75, 293.63, 294.51, 295.38, 296.26, 297.14]</t>
+          <t>[327.85, 328.83, 329.82, 330.8, 331.78, 332.77]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[292.75, 295.9, 297.72, 299.32, 300.81, 302.22]</t>
+          <t>[327.85, 332.21, 334.59, 336.65, 338.53, 340.31]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[292.75, 291.92, 292.1, 292.43, 292.85, 293.33]</t>
+          <t>[327.85, 326.3, 326.24, 326.42, 326.72, 327.11]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>279</v>
+        <v>312.08</v>
       </c>
     </row>
     <row r="4">
@@ -995,16 +995,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>62471.46</v>
+        <v>165425.07</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,146 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1036.05</v>
+        <v>668.3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹1030.76 - ₹1043.98</t>
+          <t>₹665.05 - ₹673.17</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1057.21</v>
+        <v>681.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1016.93</v>
+        <v>664.3</v>
       </c>
       <c r="J4" t="n">
-        <v>970.4400000000001</v>
+        <v>663.4400000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>860.46</v>
+        <v>621.0599999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>17.51</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>3.41</v>
+        <v>1.26</v>
       </c>
       <c r="N4" t="n">
-        <v>7.81</v>
+        <v>0.12</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.4</v>
+        <v>1.14</v>
       </c>
       <c r="P4" t="n">
-        <v>26.45</v>
+        <v>16.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>14.45</v>
+        <v>13.91</v>
       </c>
       <c r="R4" t="n">
-        <v>39.1</v>
+        <v>44.8</v>
       </c>
       <c r="S4" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.88</v>
+        <v>-1.52</v>
       </c>
       <c r="U4" t="n">
-        <v>47.5</v>
+        <v>57.4</v>
       </c>
       <c r="V4" t="n">
-        <v>3.67</v>
+        <v>8.76</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>1010.88</v>
+        <v>647.67</v>
       </c>
       <c r="Y4" t="n">
-        <v>1004.39</v>
+        <v>646.45</v>
       </c>
       <c r="Z4" t="n">
-        <v>986.22</v>
+        <v>646.45</v>
       </c>
       <c r="AA4" t="n">
-        <v>996.38</v>
+        <v>643.92</v>
       </c>
       <c r="AB4" t="n">
-        <v>1030.5</v>
+        <v>669.58</v>
       </c>
       <c r="AC4" t="n">
-        <v>1043.9</v>
+        <v>674.21</v>
       </c>
       <c r="AD4" t="n">
-        <v>1051.75</v>
+        <v>680.13</v>
       </c>
       <c r="AE4" t="n">
-        <v>55.1</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.02</v>
+        <v>-0.13</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (13.91) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>32.1</v>
+        <v>36.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23.9</v>
+        <v>-52.9</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>65.8</v>
       </c>
       <c r="AL4" t="n">
-        <v>15</v>
+        <v>10.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>1074.59</v>
+        <v>687.42</v>
       </c>
       <c r="AN4" t="n">
-        <v>997.1900000000001</v>
+        <v>648.4400000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹62,471.46 Cr., a P/E ratio of 32.12, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹165,425.07 Cr., a P/E ratio of 36.40, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.12 (Bullish Momentum Zone), while MACD Line (3.41) trades below Signal (7.81) with an expanding histogram (-4.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.51% above the 200-day DMA (₹860.46). Daily volatility envelope is bounded by ATR(14) of ₹26.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 67.09 (Bullish Momentum Zone), while MACD Line (1.26) trades above Signal (0.12) with an expanding histogram (+1.14). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.36% above the 200-day DMA (₹621.06). Daily volatility envelope is bounded by ATR(14) of ₹16.25.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,036.05) is positioned above the 30-day DMA (₹1,016.93), 50-day DMA (₹970.44), and 200-day DMA (₹860.46). The price distance from 200 DMA is +17.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DLF. Current Market Price (₹668.30) is positioned above the 30-day DMA (₹664.30), 50-day DMA (₹663.44), and 200-day DMA (₹621.06). The price distance from 200 DMA is +8.36%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[1036.05, 1039.16, 1042.27, 1045.37, 1048.48, 1051.59]</t>
+          <t>[668.3, 670.3, 672.31, 674.31, 676.32, 678.32]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[1036.05, 1049.74, 1057.23, 1063.7, 1069.64, 1075.25]</t>
+          <t>[668.3, 676.8, 681.5, 685.57, 689.32, 692.86]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[1036.05, 1031.22, 1031.05, 1031.63, 1032.61, 1033.85]</t>
+          <t>[668.3, 665.43, 665.42, 665.87, 666.57, 667.42]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>986.22</v>
+        <v>646.45</v>
       </c>
     </row>
     <row r="5">
@@ -1162,16 +1162,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>102456.04</v>
+        <v>63885.44</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,146 +1179,313 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2480.8</v>
+        <v>1059.5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹2467.58 - ₹2500.63</t>
+          <t>₹1054.21 - ₹1067.43</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2533.68</v>
+        <v>1080.66</v>
       </c>
       <c r="I5" t="n">
-        <v>2387.72</v>
+        <v>1016.93</v>
       </c>
       <c r="J5" t="n">
-        <v>2410.9</v>
+        <v>970.4400000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>2302.04</v>
+        <v>860.46</v>
       </c>
       <c r="L5" t="n">
-        <v>7.69</v>
+        <v>17.51</v>
       </c>
       <c r="M5" t="n">
-        <v>39.07</v>
+        <v>3.41</v>
       </c>
       <c r="N5" t="n">
-        <v>22.7</v>
+        <v>7.81</v>
       </c>
       <c r="O5" t="n">
-        <v>16.36</v>
+        <v>-4.4</v>
       </c>
       <c r="P5" t="n">
-        <v>66.09999999999999</v>
+        <v>26.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.45</v>
+        <v>13.91</v>
       </c>
       <c r="R5" t="n">
-        <v>35.9</v>
+        <v>42.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="T5" t="n">
-        <v>-2.13</v>
+        <v>-1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>43.3</v>
+        <v>47.5</v>
       </c>
       <c r="V5" t="n">
-        <v>7.6</v>
+        <v>3.73</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>2397.3</v>
+        <v>1042.11</v>
       </c>
       <c r="Y5" t="n">
-        <v>2367.6</v>
+        <v>1035.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>2283.94</v>
+        <v>1008.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>2381.65</v>
+        <v>1019.83</v>
       </c>
       <c r="AB5" t="n">
-        <v>2479.1</v>
+        <v>1046.18</v>
       </c>
       <c r="AC5" t="n">
-        <v>2484.5</v>
+        <v>1075.26</v>
       </c>
       <c r="AD5" t="n">
-        <v>2488.2</v>
+        <v>1091.03</v>
       </c>
       <c r="AE5" t="n">
-        <v>66</v>
+        <v>55.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.24</v>
+        <v>-0.02</v>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | LSTM Deep Net</t>
+          <t>Low VIX (13.91) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>50.2</v>
+        <v>32.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>12.9</v>
+        <v>23.9</v>
       </c>
       <c r="AK5" t="n">
-        <v>13.9</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>2546.65</v>
+        <v>1099.63</v>
       </c>
       <c r="AN5" t="n">
-        <v>2419.88</v>
+        <v>1018.9</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹102,456.04 Cr., a P/E ratio of 50.20, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹63,885.44 Cr., a P/E ratio of 32.15, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.12 (Bullish Momentum Zone), while MACD Line (3.41) trades below Signal (7.81) with an expanding histogram (-4.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.51% above the 200-day DMA (₹860.46). Daily volatility envelope is bounded by ATR(14) of ₹26.45.</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,059.50) is positioned above the 30-day DMA (₹1,016.93), 50-day DMA (₹970.44), and 200-day DMA (₹860.46). The price distance from 200 DMA is +17.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>[1059.5, 1062.68, 1065.86, 1069.04, 1072.21, 1075.39]</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>[1059.5, 1073.26, 1080.82, 1087.36, 1093.37, 1099.05]</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>[1059.5, 1054.74, 1054.64, 1055.29, 1056.35, 1057.65]</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>1008.55</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MANKIND</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>103393.45</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2503.2</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>₹2489.98 - ₹2523.03</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>2556.08</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2387.72</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2410.9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2302.04</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="M6" t="n">
+        <v>39.07</v>
+      </c>
+      <c r="N6" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="P6" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="R6" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="U6" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2419.66</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2392.11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2304.57</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2404.05</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>2492.2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2519.9</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2536.6</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>66</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.91) | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2565.53</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>2440.44</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹103,393.45 Cr., a P/E ratio of 51.79, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
           <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.99 (Bullish Momentum Zone), while MACD Line (39.07) trades above Signal (22.70) with an expanding histogram (+16.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.69% above the 200-day DMA (₹2302.04). Daily volatility envelope is bounded by ATR(14) of ₹66.10.</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,480.80) is positioned above the 30-day DMA (₹2,387.72), 50-day DMA (₹2,410.90), and 200-day DMA (₹2,302.04). The price distance from 200 DMA is +7.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>[2480.8, 2488.24, 2495.68, 2503.13, 2510.57, 2518.01]</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>[2480.8, 2514.68, 2533.08, 2548.92, 2563.45, 2577.13]</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>[2480.8, 2468.41, 2467.64, 2468.78, 2470.91, 2473.67]</t>
-        </is>
-      </c>
-      <c r="AU5" t="n">
-        <v>2283.94</v>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,503.20) is positioned above the 30-day DMA (₹2,387.72), 50-day DMA (₹2,410.90), and 200-day DMA (₹2,302.04). The price distance from 200 DMA is +7.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>[2503.2, 2510.71, 2518.22, 2525.73, 2533.24, 2540.75]</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>[2503.2, 2537.15, 2555.61, 2571.52, 2586.12, 2599.87]</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>[2503.2, 2490.88, 2490.18, 2491.38, 2493.58, 2496.41]</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>2304.57</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>44475</v>
+        <v>44625</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,98 +678,98 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>296.5</v>
+        <v>297.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹295.36 - ₹298.2</t>
+          <t>₹296.24 - ₹299.39</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>301.05</v>
+        <v>302.53</v>
       </c>
       <c r="I2" t="n">
-        <v>288.4</v>
+        <v>288.3</v>
       </c>
       <c r="J2" t="n">
-        <v>285.37</v>
+        <v>285.68</v>
       </c>
       <c r="K2" t="n">
-        <v>279.62</v>
+        <v>279.74</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1</v>
+        <v>3.67</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.3</v>
+        <v>0.04</v>
       </c>
       <c r="N2" t="n">
         <v>0.02</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.32</v>
+        <v>0.02</v>
       </c>
       <c r="P2" t="n">
-        <v>5.68</v>
+        <v>6.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.91</v>
+        <v>13.61</v>
       </c>
       <c r="R2" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.01</v>
+        <v>-1.15</v>
       </c>
       <c r="U2" t="n">
-        <v>55</v>
+        <v>56.7</v>
       </c>
       <c r="V2" t="n">
-        <v>6.3</v>
+        <v>6.66</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>289.18</v>
+        <v>289.45</v>
       </c>
       <c r="Y2" t="n">
-        <v>282.8</v>
+        <v>286.43</v>
       </c>
       <c r="Z2" t="n">
-        <v>282.58</v>
+        <v>283.53</v>
       </c>
       <c r="AA2" t="n">
-        <v>287.98</v>
+        <v>288.07</v>
       </c>
       <c r="AB2" t="n">
-        <v>295.12</v>
+        <v>295.45</v>
       </c>
       <c r="AC2" t="n">
-        <v>299.24</v>
+        <v>299.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>301.97</v>
+        <v>302.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>48.1</v>
+        <v>52.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (13.91) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (13.61) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="AJ2" t="n">
         <v>-53.2</v>
@@ -781,43 +781,43 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>305.4</v>
+        <v>305.75</v>
       </c>
       <c r="AN2" t="n">
-        <v>287.7</v>
+        <v>289.22</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹44,475.00 Cr., a P/E ratio of 10.73, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹44,625.00 Cr., a P/E ratio of 10.60, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.08 (Consolidation Zone), while MACD Line (-0.30) trades below Signal (0.02) with an expanding histogram (-0.32). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +2.10% above the 200-day DMA (₹279.62). Daily volatility envelope is bounded by ATR(14) of ₹5.68.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.87 (Consolidation Zone), while MACD Line (0.04) trades above Signal (0.02) with an expanding histogram (+0.02). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.67% above the 200-day DMA (₹279.74). Daily volatility envelope is bounded by ATR(14) of ₹6.29.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹296.50) is positioned above the 30-day DMA (₹288.40), 50-day DMA (₹285.37), and 200-day DMA (₹279.62). The price distance from 200 DMA is +2.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹297.50) is positioned above the 30-day DMA (₹288.30), 50-day DMA (₹285.68), and 200-day DMA (₹279.74). The price distance from 200 DMA is +3.67%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[296.5, 297.39, 298.28, 299.17, 300.06, 300.95]</t>
+          <t>[297.5, 298.39, 299.29, 300.18, 301.07, 301.96]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[296.5, 299.66, 301.49, 303.11, 304.6, 306.03]</t>
+          <t>[297.5, 300.91, 302.84, 304.53, 306.1, 307.59]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[296.5, 295.68, 295.87, 296.22, 296.65, 297.14]</t>
+          <t>[297.5, 296.51, 296.62, 296.91, 297.3, 297.74]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>282.58</v>
+        <v>283.53</v>
       </c>
     </row>
     <row r="3">
@@ -837,7 +837,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>301798.84</v>
+        <v>302857.45</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,15 +845,15 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>327.85</v>
+        <v>329</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹326.16 - ₹330.38</t>
+          <t>₹327.31 - ₹331.53</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>334.6</v>
+        <v>335.75</v>
       </c>
       <c r="I3" t="n">
         <v>325.91</v>
@@ -880,10 +880,10 @@
         <v>8.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.91</v>
+        <v>13.61</v>
       </c>
       <c r="R3" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="S3" t="n">
         <v>0.21</v>
@@ -895,31 +895,31 @@
         <v>50.8</v>
       </c>
       <c r="V3" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>321.92</v>
+        <v>323.31</v>
       </c>
       <c r="Y3" t="n">
-        <v>319.78</v>
+        <v>321.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>312.08</v>
+        <v>313.17</v>
       </c>
       <c r="AA3" t="n">
-        <v>315.2</v>
+        <v>316.35</v>
       </c>
       <c r="AB3" t="n">
-        <v>325.02</v>
+        <v>326.1</v>
       </c>
       <c r="AC3" t="n">
-        <v>330.94</v>
+        <v>333.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>334.02</v>
+        <v>337.2</v>
       </c>
       <c r="AE3" t="n">
         <v>54.4</v>
@@ -929,14 +929,14 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Low VIX (13.91) | LSTM Deep Net</t>
+          <t>Low VIX (13.61) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>697.6</v>
+        <v>700</v>
       </c>
       <c r="AJ3" t="n">
         <v>182</v>
@@ -948,14 +948,14 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>338.59</v>
+        <v>340.29</v>
       </c>
       <c r="AN3" t="n">
-        <v>316.51</v>
+        <v>318.42</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹301,798.84 Cr., a P/E ratio of 697.55, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹302,857.45 Cr., a P/E ratio of 700.00, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -965,26 +965,26 @@
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹327.85) is positioned above the 30-day DMA (₹325.91), 50-day DMA (₹321.81), and 200-day DMA (₹276.73). The price distance from 200 DMA is +15.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹329.00) is positioned above the 30-day DMA (₹325.91), 50-day DMA (₹321.81), and 200-day DMA (₹276.73). The price distance from 200 DMA is +15.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[327.85, 328.83, 329.82, 330.8, 331.78, 332.77]</t>
+          <t>[329.0, 329.99, 330.97, 331.96, 332.95, 333.93]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[327.85, 332.21, 334.59, 336.65, 338.53, 340.31]</t>
+          <t>[329.0, 333.36, 335.75, 337.81, 339.7, 341.48]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[327.85, 326.3, 326.24, 326.42, 326.72, 327.11]</t>
+          <t>[329.0, 327.46, 327.4, 327.58, 327.89, 328.28]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>312.08</v>
+        <v>313.17</v>
       </c>
     </row>
     <row r="4">
@@ -1004,23 +1004,23 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>165425.07</v>
+        <v>164880.5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>668.3</v>
+        <v>666.1</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹665.05 - ₹673.17</t>
+          <t>₹662.85 - ₹670.97</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>681.3</v>
+        <v>679.1</v>
       </c>
       <c r="I4" t="n">
         <v>664.3</v>
@@ -1047,46 +1047,46 @@
         <v>16.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.91</v>
+        <v>13.61</v>
       </c>
       <c r="R4" t="n">
-        <v>44.8</v>
+        <v>45.3</v>
       </c>
       <c r="S4" t="n">
         <v>0.22</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.52</v>
+        <v>-1.51</v>
       </c>
       <c r="U4" t="n">
         <v>57.4</v>
       </c>
       <c r="V4" t="n">
-        <v>8.76</v>
+        <v>8.75</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>647.67</v>
+        <v>645.47</v>
       </c>
       <c r="Y4" t="n">
-        <v>646.45</v>
+        <v>644.3200000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>646.45</v>
+        <v>644.3200000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>643.92</v>
+        <v>641.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>669.58</v>
+        <v>668.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>674.21</v>
+        <v>672.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>680.13</v>
+        <v>679.4</v>
       </c>
       <c r="AE4" t="n">
         <v>67.09999999999999</v>
@@ -1096,14 +1096,14 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (13.91) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (13.61) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>36.4</v>
+        <v>37.1</v>
       </c>
       <c r="AJ4" t="n">
         <v>-52.9</v>
@@ -1115,14 +1115,14 @@
         <v>10.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>687.42</v>
+        <v>687.03</v>
       </c>
       <c r="AN4" t="n">
-        <v>648.4400000000001</v>
+        <v>646.3</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹165,425.07 Cr., a P/E ratio of 36.40, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
+          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹164,880.50 Cr., a P/E ratio of 37.09, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1132,26 +1132,26 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DLF. Current Market Price (₹668.30) is positioned above the 30-day DMA (₹664.30), 50-day DMA (₹663.44), and 200-day DMA (₹621.06). The price distance from 200 DMA is +8.36%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DLF. Current Market Price (₹666.10) is positioned above the 30-day DMA (₹664.30), 50-day DMA (₹663.44), and 200-day DMA (₹621.06). The price distance from 200 DMA is +8.36%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[668.3, 670.3, 672.31, 674.31, 676.32, 678.32]</t>
+          <t>[666.1, 668.1, 670.1, 672.09, 674.09, 676.09]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[668.3, 676.8, 681.5, 685.57, 689.32, 692.86]</t>
+          <t>[666.1, 674.6, 679.29, 683.35, 687.09, 690.63]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[668.3, 665.43, 665.42, 665.87, 666.57, 667.42]</t>
+          <t>[666.1, 663.22, 663.2, 663.65, 664.34, 665.19]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>646.45</v>
+        <v>644.3200000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>63885.44</v>
+        <v>65190.88</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1179,15 +1179,15 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1059.5</v>
+        <v>1081.15</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>₹1054.21 - ₹1067.43</t>
+          <t>₹1075.86 - ₹1089.08</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1080.66</v>
+        <v>1102.31</v>
       </c>
       <c r="I5" t="n">
         <v>1016.93</v>
@@ -1214,46 +1214,46 @@
         <v>26.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.91</v>
+        <v>13.61</v>
       </c>
       <c r="R5" t="n">
         <v>42.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.69</v>
+        <v>-1.62</v>
       </c>
       <c r="U5" t="n">
         <v>47.5</v>
       </c>
       <c r="V5" t="n">
-        <v>3.73</v>
+        <v>3.81</v>
       </c>
       <c r="W5" t="n">
         <v>-0.77</v>
       </c>
       <c r="X5" t="n">
-        <v>1042.11</v>
+        <v>1072.47</v>
       </c>
       <c r="Y5" t="n">
-        <v>1035.13</v>
+        <v>1064.98</v>
       </c>
       <c r="Z5" t="n">
-        <v>1008.55</v>
+        <v>1029.87</v>
       </c>
       <c r="AA5" t="n">
-        <v>1019.83</v>
+        <v>1041.48</v>
       </c>
       <c r="AB5" t="n">
-        <v>1046.18</v>
+        <v>1061.42</v>
       </c>
       <c r="AC5" t="n">
-        <v>1075.26</v>
+        <v>1105.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>1091.03</v>
+        <v>1130.32</v>
       </c>
       <c r="AE5" t="n">
         <v>55.1</v>
@@ -1263,14 +1263,14 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Low VIX (13.91) | LSTM Deep Net</t>
+          <t>Low VIX (13.61) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH5" t="n">
         <v>0.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>32.2</v>
+        <v>32.8</v>
       </c>
       <c r="AJ5" t="n">
         <v>23.9</v>
@@ -1282,14 +1282,14 @@
         <v>15</v>
       </c>
       <c r="AM5" t="n">
-        <v>1099.63</v>
+        <v>1125.67</v>
       </c>
       <c r="AN5" t="n">
-        <v>1018.9</v>
+        <v>1041.45</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹63,885.44 Cr., a P/E ratio of 32.15, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹65,190.88 Cr., a P/E ratio of 32.81, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
@@ -1299,26 +1299,26 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,059.50) is positioned above the 30-day DMA (₹1,016.93), 50-day DMA (₹970.44), and 200-day DMA (₹860.46). The price distance from 200 DMA is +17.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,081.15) is positioned above the 30-day DMA (₹1,016.93), 50-day DMA (₹970.44), and 200-day DMA (₹860.46). The price distance from 200 DMA is +17.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>[1059.5, 1062.68, 1065.86, 1069.04, 1072.21, 1075.39]</t>
+          <t>[1081.15, 1090.56, 1099.97, 1109.39, 1118.8, 1128.21]</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>[1059.5, 1073.26, 1080.82, 1087.36, 1093.37, 1099.05]</t>
+          <t>[1081.15, 1101.14, 1114.93, 1127.71, 1139.95, 1151.86]</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>[1059.5, 1054.74, 1054.64, 1055.29, 1056.35, 1057.65]</t>
+          <t>[1081.15, 1082.63, 1088.75, 1095.64, 1102.93, 1110.47]</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1008.55</v>
+        <v>1029.87</v>
       </c>
     </row>
     <row r="6">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>103393.45</v>
+        <v>103261.27</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1346,15 +1346,15 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2503.2</v>
+        <v>2500</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>₹2489.98 - ₹2523.03</t>
+          <t>₹2486.78 - ₹2519.83</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2556.08</v>
+        <v>2552.88</v>
       </c>
       <c r="I6" t="n">
         <v>2387.72</v>
@@ -1381,46 +1381,46 @@
         <v>66.09999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.91</v>
+        <v>13.61</v>
       </c>
       <c r="R6" t="n">
-        <v>39.2</v>
+        <v>38.6</v>
       </c>
       <c r="S6" t="n">
         <v>0.2</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.95</v>
+        <v>-1.98</v>
       </c>
       <c r="U6" t="n">
         <v>43.3</v>
       </c>
       <c r="V6" t="n">
-        <v>7.61</v>
+        <v>7.6</v>
       </c>
       <c r="W6" t="n">
         <v>-0.77</v>
       </c>
       <c r="X6" t="n">
-        <v>2419.66</v>
+        <v>2416.47</v>
       </c>
       <c r="Y6" t="n">
-        <v>2392.11</v>
+        <v>2388.74</v>
       </c>
       <c r="Z6" t="n">
-        <v>2304.57</v>
+        <v>2301.62</v>
       </c>
       <c r="AA6" t="n">
-        <v>2404.05</v>
+        <v>2400.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>2492.2</v>
+        <v>2491.13</v>
       </c>
       <c r="AC6" t="n">
-        <v>2519.9</v>
+        <v>2517.76</v>
       </c>
       <c r="AD6" t="n">
-        <v>2536.6</v>
+        <v>2535.53</v>
       </c>
       <c r="AE6" t="n">
         <v>66</v>
@@ -1430,14 +1430,14 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.91) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.61) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH6" t="n">
         <v>0.15</v>
       </c>
       <c r="AI6" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="AJ6" t="n">
         <v>12.9</v>
@@ -1449,14 +1449,14 @@
         <v>15</v>
       </c>
       <c r="AM6" t="n">
-        <v>2565.53</v>
+        <v>2563.87</v>
       </c>
       <c r="AN6" t="n">
-        <v>2440.44</v>
+        <v>2429.25</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹103,393.45 Cr., a P/E ratio of 51.79, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
+          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹103,261.27 Cr., a P/E ratio of 51.73, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
@@ -1466,26 +1466,26 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,503.20) is positioned above the 30-day DMA (₹2,387.72), 50-day DMA (₹2,410.90), and 200-day DMA (₹2,302.04). The price distance from 200 DMA is +7.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,500.00) is positioned above the 30-day DMA (₹2,387.72), 50-day DMA (₹2,410.90), and 200-day DMA (₹2,302.04). The price distance from 200 DMA is +7.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>[2503.2, 2510.71, 2518.22, 2525.73, 2533.24, 2540.75]</t>
+          <t>[2500.0, 2507.5, 2515.0, 2522.5, 2530.0, 2537.5]</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>[2503.2, 2537.15, 2555.61, 2571.52, 2586.12, 2599.87]</t>
+          <t>[2500.0, 2533.94, 2552.39, 2568.3, 2582.88, 2596.62]</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>[2503.2, 2490.88, 2490.18, 2491.38, 2493.58, 2496.41]</t>
+          <t>[2500.0, 2487.67, 2486.96, 2488.15, 2490.34, 2493.16]</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>2304.57</v>
+        <v>2301.62</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU6"/>
+  <dimension ref="A1:AU4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>44625</v>
+        <v>302857.45</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>297.5</v>
+        <v>329</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹296.24 - ₹299.39</t>
+          <t>₹327.31 - ₹331.53</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>302.53</v>
+        <v>335.75</v>
       </c>
       <c r="I2" t="n">
-        <v>288.3</v>
+        <v>325.91</v>
       </c>
       <c r="J2" t="n">
-        <v>285.68</v>
+        <v>321.81</v>
       </c>
       <c r="K2" t="n">
-        <v>279.74</v>
+        <v>276.73</v>
       </c>
       <c r="L2" t="n">
-        <v>3.67</v>
+        <v>15.93</v>
       </c>
       <c r="M2" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.02</v>
+        <v>2.49</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02</v>
+        <v>-2.29</v>
       </c>
       <c r="P2" t="n">
-        <v>6.29</v>
+        <v>8.44</v>
       </c>
       <c r="Q2" t="n">
         <v>13.61</v>
       </c>
       <c r="R2" t="n">
-        <v>48</v>
+        <v>48.9</v>
       </c>
       <c r="S2" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.15</v>
+        <v>-1.57</v>
       </c>
       <c r="U2" t="n">
-        <v>56.7</v>
+        <v>50.8</v>
       </c>
       <c r="V2" t="n">
-        <v>6.66</v>
+        <v>2.49</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>289.45</v>
+        <v>322.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>286.43</v>
+        <v>339.83</v>
       </c>
       <c r="Z2" t="n">
-        <v>283.53</v>
+        <v>339.71</v>
       </c>
       <c r="AA2" t="n">
-        <v>288.07</v>
+        <v>316.35</v>
       </c>
       <c r="AB2" t="n">
-        <v>295.45</v>
+        <v>326.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>299.9</v>
+        <v>333.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>302.3</v>
+        <v>337.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>52.9</v>
+        <v>54.4</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (13.61) | LSTM Deep Net</t>
+          <t>Low VIX (13.61) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.6</v>
+        <v>685.4</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-53.2</v>
+        <v>182</v>
       </c>
       <c r="AK2" t="n">
-        <v>11.3</v>
+        <v>0.6</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>305.75</v>
+        <v>339.81</v>
       </c>
       <c r="AN2" t="n">
-        <v>289.22</v>
+        <v>318</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹44,625.00 Cr., a P/E ratio of 10.60, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹302,857.45 Cr., a P/E ratio of 685.42, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.87 (Consolidation Zone), while MACD Line (0.04) trades above Signal (0.02) with an expanding histogram (+0.02). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.67% above the 200-day DMA (₹279.74). Daily volatility envelope is bounded by ATR(14) of ₹6.29.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.40 (Consolidation Zone), while MACD Line (0.20) trades below Signal (2.49) with an expanding histogram (-2.29). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.93% above the 200-day DMA (₹276.73). Daily volatility envelope is bounded by ATR(14) of ₹8.44.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹297.50) is positioned above the 30-day DMA (₹288.30), 50-day DMA (₹285.68), and 200-day DMA (₹279.74). The price distance from 200 DMA is +3.67%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹329.00) is positioned above the 30-day DMA (₹325.91), 50-day DMA (₹321.81), and 200-day DMA (₹276.73). The price distance from 200 DMA is +15.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[297.5, 298.39, 299.29, 300.18, 301.07, 301.96]</t>
+          <t>[329.0, 329.99, 330.97, 331.96, 332.95, 333.93]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[297.5, 300.91, 302.84, 304.53, 306.1, 307.59]</t>
+          <t>[329.0, 333.36, 335.75, 337.81, 339.7, 341.48]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[297.5, 296.51, 296.62, 296.91, 297.3, 297.74]</t>
+          <t>[329.0, 327.46, 327.4, 327.58, 327.89, 328.28]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>283.53</v>
+        <v>339.71</v>
       </c>
     </row>
     <row r="3">
@@ -828,16 +828,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>302857.45</v>
+        <v>164880.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,146 +845,146 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>329</v>
+        <v>666.1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹327.31 - ₹331.53</t>
+          <t>₹662.85 - ₹670.97</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>335.75</v>
+        <v>679.1</v>
       </c>
       <c r="I3" t="n">
-        <v>325.91</v>
+        <v>664.3</v>
       </c>
       <c r="J3" t="n">
-        <v>321.81</v>
+        <v>663.4400000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>276.73</v>
+        <v>621.0599999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>15.93</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2</v>
+        <v>1.26</v>
       </c>
       <c r="N3" t="n">
-        <v>2.49</v>
+        <v>0.12</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.29</v>
+        <v>1.14</v>
       </c>
       <c r="P3" t="n">
-        <v>8.44</v>
+        <v>16.25</v>
       </c>
       <c r="Q3" t="n">
         <v>13.61</v>
       </c>
       <c r="R3" t="n">
-        <v>46.2</v>
+        <v>45</v>
       </c>
       <c r="S3" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.56</v>
+        <v>-1.52</v>
       </c>
       <c r="U3" t="n">
-        <v>50.8</v>
+        <v>57.4</v>
       </c>
       <c r="V3" t="n">
-        <v>2.49</v>
+        <v>8.75</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>323.31</v>
+        <v>643.52</v>
       </c>
       <c r="Y3" t="n">
-        <v>321.15</v>
+        <v>701.3200000000001</v>
       </c>
       <c r="Z3" t="n">
-        <v>313.17</v>
+        <v>701.3200000000001</v>
       </c>
       <c r="AA3" t="n">
-        <v>316.35</v>
+        <v>641.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>326.1</v>
+        <v>668.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>333.1</v>
+        <v>672.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>337.2</v>
+        <v>679.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>54.4</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.08</v>
+        <v>-0.13</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Low VIX (13.61) | LSTM Deep Net</t>
+          <t>Strong RSI | Low VIX (13.61) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>700</v>
+        <v>37.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>182</v>
+        <v>-52.9</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.6</v>
+        <v>65.8</v>
       </c>
       <c r="AL3" t="n">
-        <v>15</v>
+        <v>10.1</v>
       </c>
       <c r="AM3" t="n">
-        <v>340.29</v>
+        <v>687.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>318.42</v>
+        <v>645.85</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹302,857.45 Cr., a P/E ratio of 700.00, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹164,880.50 Cr., a P/E ratio of 37.09, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.40 (Consolidation Zone), while MACD Line (0.20) trades below Signal (2.49) with an expanding histogram (-2.29). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.93% above the 200-day DMA (₹276.73). Daily volatility envelope is bounded by ATR(14) of ₹8.44.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 67.09 (Bullish Momentum Zone), while MACD Line (1.26) trades above Signal (0.12) with an expanding histogram (+1.14). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.36% above the 200-day DMA (₹621.06). Daily volatility envelope is bounded by ATR(14) of ₹16.25.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹329.00) is positioned above the 30-day DMA (₹325.91), 50-day DMA (₹321.81), and 200-day DMA (₹276.73). The price distance from 200 DMA is +15.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DLF. Current Market Price (₹666.10) is positioned above the 30-day DMA (₹664.30), 50-day DMA (₹663.44), and 200-day DMA (₹621.06). The price distance from 200 DMA is +8.36%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[329.0, 329.99, 330.97, 331.96, 332.95, 333.93]</t>
+          <t>[666.1, 668.1, 670.1, 672.09, 674.09, 676.09]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[329.0, 333.36, 335.75, 337.81, 339.7, 341.48]</t>
+          <t>[666.1, 674.6, 679.29, 683.35, 687.09, 690.63]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[329.0, 327.46, 327.4, 327.58, 327.89, 328.28]</t>
+          <t>[666.1, 663.22, 663.2, 663.65, 664.34, 665.19]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>313.17</v>
+        <v>701.3200000000001</v>
       </c>
     </row>
     <row r="4">
@@ -995,497 +995,163 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>164880.5</v>
+        <v>65190.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>666.1</v>
+        <v>1081.15</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹662.85 - ₹670.97</t>
+          <t>₹1075.86 - ₹1089.08</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>679.1</v>
+        <v>1102.31</v>
       </c>
       <c r="I4" t="n">
-        <v>664.3</v>
+        <v>1016.93</v>
       </c>
       <c r="J4" t="n">
-        <v>663.4400000000001</v>
+        <v>970.4400000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>621.0599999999999</v>
+        <v>860.46</v>
       </c>
       <c r="L4" t="n">
-        <v>8.359999999999999</v>
+        <v>17.51</v>
       </c>
       <c r="M4" t="n">
-        <v>1.26</v>
+        <v>3.41</v>
       </c>
       <c r="N4" t="n">
-        <v>0.12</v>
+        <v>7.81</v>
       </c>
       <c r="O4" t="n">
-        <v>1.14</v>
+        <v>-4.4</v>
       </c>
       <c r="P4" t="n">
-        <v>16.25</v>
+        <v>26.45</v>
       </c>
       <c r="Q4" t="n">
         <v>13.61</v>
       </c>
       <c r="R4" t="n">
-        <v>45.3</v>
+        <v>45</v>
       </c>
       <c r="S4" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.51</v>
+        <v>-1.63</v>
       </c>
       <c r="U4" t="n">
-        <v>57.4</v>
+        <v>47.5</v>
       </c>
       <c r="V4" t="n">
-        <v>8.75</v>
+        <v>3.81</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>645.47</v>
+        <v>1069.26</v>
       </c>
       <c r="Y4" t="n">
-        <v>644.3200000000001</v>
+        <v>1126.96</v>
       </c>
       <c r="Z4" t="n">
-        <v>644.3200000000001</v>
+        <v>1070.71</v>
       </c>
       <c r="AA4" t="n">
-        <v>641.72</v>
+        <v>1041.48</v>
       </c>
       <c r="AB4" t="n">
-        <v>668.85</v>
+        <v>1061.42</v>
       </c>
       <c r="AC4" t="n">
-        <v>672.75</v>
+        <v>1105.74</v>
       </c>
       <c r="AD4" t="n">
-        <v>679.4</v>
+        <v>1130.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>67.09999999999999</v>
+        <v>55.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (13.61) | LSTM Deep Net</t>
+          <t>Low VIX (13.61) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>37.1</v>
+        <v>33.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-52.9</v>
+        <v>23.9</v>
       </c>
       <c r="AK4" t="n">
-        <v>65.8</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
-        <v>10.1</v>
+        <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>687.03</v>
+        <v>1123.17</v>
       </c>
       <c r="AN4" t="n">
-        <v>646.3</v>
+        <v>1040.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹164,880.50 Cr., a P/E ratio of 37.09, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
+          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹65,190.88 Cr., a P/E ratio of 33.51, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 67.09 (Bullish Momentum Zone), while MACD Line (1.26) trades above Signal (0.12) with an expanding histogram (+1.14). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.36% above the 200-day DMA (₹621.06). Daily volatility envelope is bounded by ATR(14) of ₹16.25.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.12 (Bullish Momentum Zone), while MACD Line (3.41) trades below Signal (7.81) with an expanding histogram (-4.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.51% above the 200-day DMA (₹860.46). Daily volatility envelope is bounded by ATR(14) of ₹26.45.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DLF. Current Market Price (₹666.10) is positioned above the 30-day DMA (₹664.30), 50-day DMA (₹663.44), and 200-day DMA (₹621.06). The price distance from 200 DMA is +8.36%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,081.15) is positioned above the 30-day DMA (₹1,016.93), 50-day DMA (₹970.44), and 200-day DMA (₹860.46). The price distance from 200 DMA is +17.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[666.1, 668.1, 670.1, 672.09, 674.09, 676.09]</t>
+          <t>[1081.15, 1090.59, 1100.03, 1109.47, 1118.92, 1128.36]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[666.1, 674.6, 679.29, 683.35, 687.09, 690.63]</t>
+          <t>[1081.15, 1101.17, 1114.99, 1127.8, 1140.07, 1152.01]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[666.1, 663.22, 663.2, 663.65, 664.34, 665.19]</t>
+          <t>[1081.15, 1082.66, 1088.81, 1095.73, 1103.05, 1110.62]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>644.3200000000001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>65190.88</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1081.15</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>₹1075.86 - ₹1089.08</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1102.31</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1016.93</v>
-      </c>
-      <c r="J5" t="n">
-        <v>970.4400000000001</v>
-      </c>
-      <c r="K5" t="n">
-        <v>860.46</v>
-      </c>
-      <c r="L5" t="n">
-        <v>17.51</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="N5" t="n">
-        <v>7.81</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>26.45</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="R5" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-1.62</v>
-      </c>
-      <c r="U5" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="V5" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1072.47</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1064.98</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1029.87</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1041.48</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1061.42</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1105.74</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1130.32</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Low VIX (13.61) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1125.67</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1041.45</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹65,190.88 Cr., a P/E ratio of 32.81, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.12 (Bullish Momentum Zone), while MACD Line (3.41) trades below Signal (7.81) with an expanding histogram (-4.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.51% above the 200-day DMA (₹860.46). Daily volatility envelope is bounded by ATR(14) of ₹26.45.</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,081.15) is positioned above the 30-day DMA (₹1,016.93), 50-day DMA (₹970.44), and 200-day DMA (₹860.46). The price distance from 200 DMA is +17.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>[1081.15, 1090.56, 1099.97, 1109.39, 1118.8, 1128.21]</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>[1081.15, 1101.14, 1114.93, 1127.71, 1139.95, 1151.86]</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>[1081.15, 1082.63, 1088.75, 1095.64, 1102.93, 1110.47]</t>
-        </is>
-      </c>
-      <c r="AU5" t="n">
-        <v>1029.87</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>MANKIND</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>103261.27</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>₹2486.78 - ₹2519.83</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>2552.88</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2387.72</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2410.9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2302.04</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7.69</v>
-      </c>
-      <c r="M6" t="n">
-        <v>39.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="O6" t="n">
-        <v>16.36</v>
-      </c>
-      <c r="P6" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="R6" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-1.98</v>
-      </c>
-      <c r="U6" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="V6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2416.47</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>2388.74</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2301.62</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2400.85</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2491.13</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2517.76</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2535.53</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>66</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.61) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>2563.87</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>2429.25</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹103,261.27 Cr., a P/E ratio of 51.73, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.99 (Bullish Momentum Zone), while MACD Line (39.07) trades above Signal (22.70) with an expanding histogram (+16.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.69% above the 200-day DMA (₹2302.04). Daily volatility envelope is bounded by ATR(14) of ₹66.10.</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,500.00) is positioned above the 30-day DMA (₹2,387.72), 50-day DMA (₹2,410.90), and 200-day DMA (₹2,302.04). The price distance from 200 DMA is +7.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>[2500.0, 2507.5, 2515.0, 2522.5, 2530.0, 2537.5]</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>[2500.0, 2533.94, 2552.39, 2568.3, 2582.88, 2596.62]</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>[2500.0, 2487.67, 2486.96, 2488.15, 2490.34, 2493.16]</t>
-        </is>
-      </c>
-      <c r="AU6" t="n">
-        <v>2301.62</v>
+        <v>1070.71</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -656,7 +656,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>302857.45</v>
+        <v>305296.86</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,98 +678,98 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>329</v>
+        <v>331.65</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹327.31 - ₹331.53</t>
+          <t>₹329.91 - ₹334.26</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>335.75</v>
+        <v>338.6</v>
       </c>
       <c r="I2" t="n">
-        <v>325.91</v>
+        <v>325.84</v>
       </c>
       <c r="J2" t="n">
-        <v>321.81</v>
+        <v>322.23</v>
       </c>
       <c r="K2" t="n">
-        <v>276.73</v>
+        <v>276.94</v>
       </c>
       <c r="L2" t="n">
-        <v>15.93</v>
+        <v>18.8</v>
       </c>
       <c r="M2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="R2" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="S2" t="n">
         <v>0.2</v>
       </c>
-      <c r="N2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-2.29</v>
-      </c>
-      <c r="P2" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>13.61</v>
-      </c>
-      <c r="R2" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.21</v>
-      </c>
       <c r="T2" t="n">
-        <v>-1.57</v>
+        <v>-1.48</v>
       </c>
       <c r="U2" t="n">
         <v>50.8</v>
       </c>
       <c r="V2" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>322.33</v>
+        <v>324.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>339.83</v>
+        <v>342.44</v>
       </c>
       <c r="Z2" t="n">
-        <v>339.71</v>
+        <v>342.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>316.35</v>
+        <v>318.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>326.1</v>
+        <v>329.65</v>
       </c>
       <c r="AC2" t="n">
-        <v>333.1</v>
+        <v>334.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>337.2</v>
+        <v>337.75</v>
       </c>
       <c r="AE2" t="n">
-        <v>54.4</v>
+        <v>58.6</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Low VIX (13.61) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (13.78) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>685.4</v>
+        <v>705.6</v>
       </c>
       <c r="AJ2" t="n">
         <v>182</v>
@@ -781,63 +781,63 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>339.81</v>
+        <v>343.33</v>
       </c>
       <c r="AN2" t="n">
-        <v>318</v>
+        <v>320.94</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹302,857.45 Cr., a P/E ratio of 685.42, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹305,296.86 Cr., a P/E ratio of 705.64, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.40 (Consolidation Zone), while MACD Line (0.20) trades below Signal (2.49) with an expanding histogram (-2.29). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +15.93% above the 200-day DMA (₹276.73). Daily volatility envelope is bounded by ATR(14) of ₹8.44.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.63 (Bullish Momentum Zone), while MACD Line (0.58) trades below Signal (2.11) with an expanding histogram (-1.53). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.80% above the 200-day DMA (₹276.94). Daily volatility envelope is bounded by ATR(14) of ₹8.69.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹329.00) is positioned above the 30-day DMA (₹325.91), 50-day DMA (₹321.81), and 200-day DMA (₹276.73). The price distance from 200 DMA is +15.93%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹331.65) is positioned above the 30-day DMA (₹325.84), 50-day DMA (₹322.23), and 200-day DMA (₹276.94). The price distance from 200 DMA is +18.80%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[329.0, 329.99, 330.97, 331.96, 332.95, 333.93]</t>
+          <t>[331.65, 332.64, 333.64, 334.63, 335.63, 336.62]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[329.0, 333.36, 335.75, 337.81, 339.7, 341.48]</t>
+          <t>[331.65, 336.12, 338.56, 340.65, 342.58, 344.4]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[329.0, 327.46, 327.4, 327.58, 327.89, 328.28]</t>
+          <t>[331.65, 330.04, 329.95, 330.12, 330.42, 330.8]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>339.71</v>
+        <v>342.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>164880.5</v>
+        <v>44392.51</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -845,166 +845,166 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>666.1</v>
+        <v>295.95</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹662.85 - ₹670.97</t>
+          <t>₹294.69 - ₹297.84</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>679.1</v>
+        <v>300.98</v>
       </c>
       <c r="I3" t="n">
-        <v>664.3</v>
+        <v>288.3</v>
       </c>
       <c r="J3" t="n">
-        <v>663.4400000000001</v>
+        <v>285.68</v>
       </c>
       <c r="K3" t="n">
-        <v>621.0599999999999</v>
+        <v>279.74</v>
       </c>
       <c r="L3" t="n">
-        <v>8.359999999999999</v>
+        <v>3.67</v>
       </c>
       <c r="M3" t="n">
-        <v>1.26</v>
+        <v>0.04</v>
       </c>
       <c r="N3" t="n">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="O3" t="n">
-        <v>1.14</v>
+        <v>0.02</v>
       </c>
       <c r="P3" t="n">
-        <v>16.25</v>
+        <v>6.29</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.61</v>
+        <v>13.78</v>
       </c>
       <c r="R3" t="n">
-        <v>45</v>
+        <v>50.9</v>
       </c>
       <c r="S3" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.52</v>
+        <v>-1.16</v>
       </c>
       <c r="U3" t="n">
-        <v>57.4</v>
+        <v>56.7</v>
       </c>
       <c r="V3" t="n">
-        <v>8.75</v>
+        <v>6.64</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>643.52</v>
+        <v>287.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>701.3200000000001</v>
+        <v>305.13</v>
       </c>
       <c r="Z3" t="n">
-        <v>701.3200000000001</v>
+        <v>305.13</v>
       </c>
       <c r="AA3" t="n">
-        <v>641.72</v>
+        <v>286.52</v>
       </c>
       <c r="AB3" t="n">
-        <v>668.85</v>
+        <v>296.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>672.75</v>
+        <v>298.95</v>
       </c>
       <c r="AD3" t="n">
-        <v>679.4</v>
+        <v>301.95</v>
       </c>
       <c r="AE3" t="n">
-        <v>67.09999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.13</v>
+        <v>0.02</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>Strong RSI | Low VIX (13.61) | LSTM Deep Net</t>
+          <t>TTM Squeeze | Low VIX (13.78) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>37.1</v>
+        <v>10.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-52.9</v>
+        <v>-53.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>65.8</v>
+        <v>11.3</v>
       </c>
       <c r="AL3" t="n">
-        <v>10.1</v>
+        <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>687.08</v>
+        <v>304.87</v>
       </c>
       <c r="AN3" t="n">
-        <v>645.85</v>
+        <v>287.11</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>DLF operates in the Real Estate sector. With an estimated Market Cap of ₹164,880.50 Cr., a P/E ratio of 37.09, and YoY Revenue Growth of -52.9%, the company demonstrates strong institutional backing, solid operating profit margins (65.79%), and healthy Return on Equity (10.10%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹44,392.51 Cr., a P/E ratio of 10.82, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 67.09 (Bullish Momentum Zone), while MACD Line (1.26) trades above Signal (0.12) with an expanding histogram (+1.14). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.36% above the 200-day DMA (₹621.06). Daily volatility envelope is bounded by ATR(14) of ₹16.25.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.87 (Consolidation Zone), while MACD Line (0.04) trades above Signal (0.02) with an expanding histogram (+0.02). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.67% above the 200-day DMA (₹279.74). Daily volatility envelope is bounded by ATR(14) of ₹6.29.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for DLF. Current Market Price (₹666.10) is positioned above the 30-day DMA (₹664.30), 50-day DMA (₹663.44), and 200-day DMA (₹621.06). The price distance from 200 DMA is +8.36%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹295.95) is positioned above the 30-day DMA (₹288.30), 50-day DMA (₹285.68), and 200-day DMA (₹279.74). The price distance from 200 DMA is +3.67%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[666.1, 668.1, 670.1, 672.09, 674.09, 676.09]</t>
+          <t>[295.95, 296.84, 297.73, 298.61, 299.5, 300.39]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[666.1, 674.6, 679.29, 683.35, 687.09, 690.63]</t>
+          <t>[295.95, 299.35, 301.28, 302.97, 304.53, 306.01]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[666.1, 663.22, 663.2, 663.65, 664.34, 665.19]</t>
+          <t>[295.95, 294.95, 295.06, 295.35, 295.73, 296.17]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>701.3200000000001</v>
+        <v>305.13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>65190.88</v>
+        <v>103628.94</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,146 +1012,146 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1081.15</v>
+        <v>2509.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹1075.86 - ₹1089.08</t>
+          <t>₹2495.98 - ₹2529.03</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1102.31</v>
+        <v>2562.08</v>
       </c>
       <c r="I4" t="n">
-        <v>1016.93</v>
+        <v>2387.72</v>
       </c>
       <c r="J4" t="n">
-        <v>970.4400000000001</v>
+        <v>2410.9</v>
       </c>
       <c r="K4" t="n">
-        <v>860.46</v>
+        <v>2302.04</v>
       </c>
       <c r="L4" t="n">
-        <v>17.51</v>
+        <v>7.69</v>
       </c>
       <c r="M4" t="n">
-        <v>3.41</v>
+        <v>39.07</v>
       </c>
       <c r="N4" t="n">
-        <v>7.81</v>
+        <v>22.7</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.4</v>
+        <v>16.36</v>
       </c>
       <c r="P4" t="n">
-        <v>26.45</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.61</v>
+        <v>13.78</v>
       </c>
       <c r="R4" t="n">
-        <v>45</v>
+        <v>38.6</v>
       </c>
       <c r="S4" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.63</v>
+        <v>-1.97</v>
       </c>
       <c r="U4" t="n">
-        <v>47.5</v>
+        <v>43.3</v>
       </c>
       <c r="V4" t="n">
-        <v>3.81</v>
+        <v>7.61</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>1069.26</v>
+        <v>2418.31</v>
       </c>
       <c r="Y4" t="n">
-        <v>1126.96</v>
+        <v>2724.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>1070.71</v>
+        <v>2724.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>1041.48</v>
+        <v>2410.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1061.42</v>
+        <v>2513.37</v>
       </c>
       <c r="AC4" t="n">
-        <v>1105.74</v>
+        <v>2525.84</v>
       </c>
       <c r="AD4" t="n">
-        <v>1130.32</v>
+        <v>2542.47</v>
       </c>
       <c r="AE4" t="n">
-        <v>55.1</v>
+        <v>66</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.02</v>
+        <v>0.24</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Low VIX (13.61) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.78) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>33.5</v>
+        <v>50.8</v>
       </c>
       <c r="AJ4" t="n">
-        <v>23.9</v>
+        <v>12.9</v>
       </c>
       <c r="AK4" t="n">
-        <v>23</v>
+        <v>13.9</v>
       </c>
       <c r="AL4" t="n">
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>1123.17</v>
+        <v>2575.09</v>
       </c>
       <c r="AN4" t="n">
-        <v>1040.78</v>
+        <v>2438.42</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MOTILALOFS operates in the Financial Services sector. With an estimated Market Cap of ₹65,190.88 Cr., a P/E ratio of 33.51, and YoY Revenue Growth of +23.9%, the company demonstrates strong institutional backing, solid operating profit margins (22.96%), and healthy Return on Equity (15.00%).</t>
+          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹103,628.94 Cr., a P/E ratio of 50.77, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 55.12 (Bullish Momentum Zone), while MACD Line (3.41) trades below Signal (7.81) with an expanding histogram (-4.40). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +17.51% above the 200-day DMA (₹860.46). Daily volatility envelope is bounded by ATR(14) of ₹26.45.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.99 (Bullish Momentum Zone), while MACD Line (39.07) trades above Signal (22.70) with an expanding histogram (+16.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.69% above the 200-day DMA (₹2302.04). Daily volatility envelope is bounded by ATR(14) of ₹66.10.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MOTILALOFS. Current Market Price (₹1,081.15) is positioned above the 30-day DMA (₹1,016.93), 50-day DMA (₹970.44), and 200-day DMA (₹860.46). The price distance from 200 DMA is +17.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,509.20) is positioned above the 30-day DMA (₹2,387.72), 50-day DMA (₹2,410.90), and 200-day DMA (₹2,302.04). The price distance from 200 DMA is +7.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[1081.15, 1090.59, 1100.03, 1109.47, 1118.92, 1128.36]</t>
+          <t>[2509.2, 2516.73, 2524.26, 2531.78, 2539.31, 2546.84]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[1081.15, 1101.17, 1114.99, 1127.8, 1140.07, 1152.01]</t>
+          <t>[2509.2, 2543.17, 2561.65, 2577.58, 2592.19, 2605.96]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[1081.15, 1082.66, 1088.81, 1095.73, 1103.05, 1110.62]</t>
+          <t>[2509.2, 2496.9, 2496.21, 2497.44, 2499.65, 2502.5]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1070.71</v>
+        <v>2724.2</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -670,23 +670,23 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>305296.86</v>
+        <v>301936.91</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>331.65</v>
+        <v>328</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹329.91 - ₹334.26</t>
+          <t>₹326.26 - ₹330.61</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>338.6</v>
+        <v>334.95</v>
       </c>
       <c r="I2" t="n">
         <v>325.84</v>
@@ -713,19 +713,19 @@
         <v>8.69</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.78</v>
+        <v>13.89</v>
       </c>
       <c r="R2" t="n">
-        <v>51.8</v>
+        <v>47.8</v>
       </c>
       <c r="S2" t="n">
         <v>0.2</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.48</v>
+        <v>-1.69</v>
       </c>
       <c r="U2" t="n">
-        <v>50.8</v>
+        <v>49.2</v>
       </c>
       <c r="V2" t="n">
         <v>2.47</v>
@@ -734,25 +734,25 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>324.52</v>
+        <v>320.57</v>
       </c>
       <c r="Y2" t="n">
-        <v>342.44</v>
+        <v>338.67</v>
       </c>
       <c r="Z2" t="n">
-        <v>342.44</v>
+        <v>338.67</v>
       </c>
       <c r="AA2" t="n">
-        <v>318.62</v>
+        <v>314.97</v>
       </c>
       <c r="AB2" t="n">
-        <v>329.65</v>
+        <v>328.43</v>
       </c>
       <c r="AC2" t="n">
-        <v>334.7</v>
+        <v>332.26</v>
       </c>
       <c r="AD2" t="n">
-        <v>337.75</v>
+        <v>336.53</v>
       </c>
       <c r="AE2" t="n">
         <v>58.6</v>
@@ -762,14 +762,14 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (13.78) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Low VIX (13.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>705.6</v>
+        <v>697.9</v>
       </c>
       <c r="AJ2" t="n">
         <v>182</v>
@@ -781,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>343.33</v>
+        <v>339.38</v>
       </c>
       <c r="AN2" t="n">
-        <v>320.94</v>
+        <v>317.69</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹305,296.86 Cr., a P/E ratio of 705.64, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹301,936.91 Cr., a P/E ratio of 697.87, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -798,26 +798,26 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹331.65) is positioned above the 30-day DMA (₹325.84), 50-day DMA (₹322.23), and 200-day DMA (₹276.94). The price distance from 200 DMA is +18.80%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹328.00) is positioned above the 30-day DMA (₹325.84), 50-day DMA (₹322.23), and 200-day DMA (₹276.94). The price distance from 200 DMA is +18.80%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[331.65, 332.64, 333.64, 334.63, 335.63, 336.62]</t>
+          <t>[328.0, 328.98, 329.97, 330.95, 331.94, 332.92]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[331.65, 336.12, 338.56, 340.65, 342.58, 344.4]</t>
+          <t>[328.0, 332.46, 334.88, 336.97, 338.89, 340.69]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[331.65, 330.04, 329.95, 330.12, 330.42, 330.8]</t>
+          <t>[328.0, 326.38, 326.28, 326.44, 326.72, 327.09]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>342.44</v>
+        <v>338.67</v>
       </c>
     </row>
     <row r="3">
@@ -837,106 +837,106 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44392.51</v>
+        <v>44550</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>🟡 MODERATE BUY</t>
+          <t>🔴 AVOID / HOLD</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>295.95</v>
+        <v>297</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>₹294.69 - ₹297.84</t>
+          <t>₹295.74 - ₹298.89</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>300.98</v>
+        <v>302.03</v>
       </c>
       <c r="I3" t="n">
-        <v>288.3</v>
+        <v>288.35</v>
       </c>
       <c r="J3" t="n">
-        <v>285.68</v>
+        <v>286.17</v>
       </c>
       <c r="K3" t="n">
-        <v>279.74</v>
+        <v>279.9</v>
       </c>
       <c r="L3" t="n">
-        <v>3.67</v>
+        <v>6.29</v>
       </c>
       <c r="M3" t="n">
-        <v>0.04</v>
+        <v>0.91</v>
       </c>
       <c r="N3" t="n">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02</v>
+        <v>0.71</v>
       </c>
       <c r="P3" t="n">
         <v>6.29</v>
       </c>
       <c r="Q3" t="n">
-        <v>13.78</v>
+        <v>13.89</v>
       </c>
       <c r="R3" t="n">
-        <v>50.9</v>
+        <v>47.4</v>
       </c>
       <c r="S3" t="n">
         <v>0.25</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.16</v>
+        <v>-1.29</v>
       </c>
       <c r="U3" t="n">
-        <v>56.7</v>
+        <v>55.7</v>
       </c>
       <c r="V3" t="n">
-        <v>6.64</v>
+        <v>6.74</v>
       </c>
       <c r="W3" t="n">
         <v>-0.77</v>
       </c>
       <c r="X3" t="n">
-        <v>287.03</v>
+        <v>289.16</v>
       </c>
       <c r="Y3" t="n">
-        <v>305.13</v>
+        <v>306.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>305.13</v>
+        <v>306.21</v>
       </c>
       <c r="AA3" t="n">
-        <v>286.52</v>
+        <v>287.57</v>
       </c>
       <c r="AB3" t="n">
-        <v>296.6</v>
+        <v>296.95</v>
       </c>
       <c r="AC3" t="n">
-        <v>298.95</v>
+        <v>299.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>301.95</v>
+        <v>302.3</v>
       </c>
       <c r="AE3" t="n">
-        <v>52.9</v>
+        <v>62.8</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.02</v>
+        <v>0.14</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>TTM Squeeze | Low VIX (13.78) | LSTM Deep Net</t>
+          <t>Vol Spike 2.8x | Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (13.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH3" t="n">
         <v>0.15</v>
       </c>
       <c r="AI3" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="AJ3" t="n">
         <v>-53.2</v>
@@ -948,43 +948,43 @@
         <v>15</v>
       </c>
       <c r="AM3" t="n">
-        <v>304.87</v>
+        <v>305.83</v>
       </c>
       <c r="AN3" t="n">
-        <v>287.11</v>
+        <v>288.16</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹44,392.51 Cr., a P/E ratio of 10.82, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹44,550.00 Cr., a P/E ratio of 10.58, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 52.87 (Consolidation Zone), while MACD Line (0.04) trades above Signal (0.02) with an expanding histogram (+0.02). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.67% above the 200-day DMA (₹279.74). Daily volatility envelope is bounded by ATR(14) of ₹6.29.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.80 (Bullish Momentum Zone), while MACD Line (0.91) trades above Signal (0.20) with an expanding histogram (+0.71). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.29% above the 200-day DMA (₹279.90). Daily volatility envelope is bounded by ATR(14) of ₹6.29.</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹295.95) is positioned above the 30-day DMA (₹288.30), 50-day DMA (₹285.68), and 200-day DMA (₹279.74). The price distance from 200 DMA is +3.67%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹297.00) is positioned above the 30-day DMA (₹288.35), 50-day DMA (₹286.17), and 200-day DMA (₹279.90). The price distance from 200 DMA is +6.29%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>[295.95, 296.84, 297.73, 298.61, 299.5, 300.39]</t>
+          <t>[297.0, 297.89, 298.78, 299.67, 300.56, 301.45]</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>[295.95, 299.35, 301.28, 302.97, 304.53, 306.01]</t>
+          <t>[297.0, 300.41, 302.34, 304.03, 305.59, 307.08]</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>[295.95, 294.95, 295.06, 295.35, 295.73, 296.17]</t>
+          <t>[297.0, 296.01, 296.12, 296.41, 296.79, 297.24]</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>305.13</v>
+        <v>306.21</v>
       </c>
     </row>
     <row r="4">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>103628.94</v>
+        <v>103261.27</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1012,98 +1012,98 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2509.2</v>
+        <v>2500</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>₹2495.98 - ₹2529.03</t>
+          <t>₹2486.93 - ₹2519.61</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2562.08</v>
+        <v>2552.29</v>
       </c>
       <c r="I4" t="n">
-        <v>2387.72</v>
+        <v>2392.22</v>
       </c>
       <c r="J4" t="n">
-        <v>2410.9</v>
+        <v>2408.54</v>
       </c>
       <c r="K4" t="n">
-        <v>2302.04</v>
+        <v>2303.83</v>
       </c>
       <c r="L4" t="n">
-        <v>7.69</v>
+        <v>8.51</v>
       </c>
       <c r="M4" t="n">
-        <v>39.07</v>
+        <v>38.75</v>
       </c>
       <c r="N4" t="n">
-        <v>22.7</v>
+        <v>25.91</v>
       </c>
       <c r="O4" t="n">
-        <v>16.36</v>
+        <v>12.84</v>
       </c>
       <c r="P4" t="n">
-        <v>66.09999999999999</v>
+        <v>65.36</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.78</v>
+        <v>13.89</v>
       </c>
       <c r="R4" t="n">
-        <v>38.6</v>
+        <v>36</v>
       </c>
       <c r="S4" t="n">
         <v>0.2</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.97</v>
+        <v>-2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>43.3</v>
+        <v>42.6</v>
       </c>
       <c r="V4" t="n">
-        <v>7.61</v>
+        <v>7.56</v>
       </c>
       <c r="W4" t="n">
         <v>-0.77</v>
       </c>
       <c r="X4" t="n">
-        <v>2418.31</v>
+        <v>2413.41</v>
       </c>
       <c r="Y4" t="n">
-        <v>2724.2</v>
+        <v>2714.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>2724.2</v>
+        <v>2714.22</v>
       </c>
       <c r="AA4" t="n">
-        <v>2410.05</v>
+        <v>2401.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>2513.37</v>
+        <v>2503.37</v>
       </c>
       <c r="AC4" t="n">
-        <v>2525.84</v>
+        <v>2526.64</v>
       </c>
       <c r="AD4" t="n">
-        <v>2542.47</v>
+        <v>2553.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>66</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.78) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH4" t="n">
         <v>0.15</v>
       </c>
       <c r="AI4" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="AJ4" t="n">
         <v>12.9</v>
@@ -1115,43 +1115,43 @@
         <v>15</v>
       </c>
       <c r="AM4" t="n">
-        <v>2575.09</v>
+        <v>2560.85</v>
       </c>
       <c r="AN4" t="n">
-        <v>2438.42</v>
+        <v>2431.89</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹103,628.94 Cr., a P/E ratio of 50.77, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
+          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹103,261.27 Cr., a P/E ratio of 50.59, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 65.99 (Bullish Momentum Zone), while MACD Line (39.07) trades above Signal (22.70) with an expanding histogram (+16.36). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +7.69% above the 200-day DMA (₹2302.04). Daily volatility envelope is bounded by ATR(14) of ₹66.10.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.92 (Bullish Momentum Zone), while MACD Line (38.75) trades above Signal (25.91) with an expanding histogram (+12.84). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.51% above the 200-day DMA (₹2303.83). Daily volatility envelope is bounded by ATR(14) of ₹65.36.</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,509.20) is positioned above the 30-day DMA (₹2,387.72), 50-day DMA (₹2,410.90), and 200-day DMA (₹2,302.04). The price distance from 200 DMA is +7.69%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,500.00) is positioned above the 30-day DMA (₹2,392.22), 50-day DMA (₹2,408.54), and 200-day DMA (₹2,303.83). The price distance from 200 DMA is +8.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>[2509.2, 2516.73, 2524.26, 2531.78, 2539.31, 2546.84]</t>
+          <t>[2500.0, 2507.5, 2515.0, 2522.5, 2530.0, 2537.5]</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>[2509.2, 2543.17, 2561.65, 2577.58, 2592.19, 2605.96]</t>
+          <t>[2500.0, 2533.65, 2551.98, 2567.79, 2582.29, 2595.96]</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>[2509.2, 2496.9, 2496.21, 2497.44, 2499.65, 2502.5]</t>
+          <t>[2500.0, 2487.89, 2487.27, 2488.54, 2490.78, 2493.65]</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>2724.2</v>
+        <v>2714.22</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU4"/>
+  <dimension ref="A1:AU2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,16 +661,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>301936.91</v>
+        <v>103261.27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,480 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>328</v>
+        <v>2500</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹326.26 - ₹330.61</t>
+          <t>₹2486.93 - ₹2519.61</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>334.95</v>
+        <v>2552.29</v>
       </c>
       <c r="I2" t="n">
-        <v>325.84</v>
+        <v>2392.22</v>
       </c>
       <c r="J2" t="n">
-        <v>322.23</v>
+        <v>2408.54</v>
       </c>
       <c r="K2" t="n">
-        <v>276.94</v>
+        <v>2303.83</v>
       </c>
       <c r="L2" t="n">
-        <v>18.8</v>
+        <v>8.51</v>
       </c>
       <c r="M2" t="n">
-        <v>0.58</v>
+        <v>38.75</v>
       </c>
       <c r="N2" t="n">
-        <v>2.11</v>
+        <v>25.91</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.53</v>
+        <v>12.84</v>
       </c>
       <c r="P2" t="n">
-        <v>8.69</v>
+        <v>65.36</v>
       </c>
       <c r="Q2" t="n">
         <v>13.89</v>
       </c>
       <c r="R2" t="n">
-        <v>47.8</v>
+        <v>36</v>
       </c>
       <c r="S2" t="n">
         <v>0.2</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.69</v>
+        <v>-2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>49.2</v>
+        <v>42.6</v>
       </c>
       <c r="V2" t="n">
-        <v>2.47</v>
+        <v>7.56</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>320.57</v>
+        <v>2454.78</v>
       </c>
       <c r="Y2" t="n">
-        <v>338.67</v>
+        <v>2437.91</v>
       </c>
       <c r="Z2" t="n">
-        <v>338.67</v>
+        <v>2321.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>314.97</v>
+        <v>2401.95</v>
       </c>
       <c r="AB2" t="n">
-        <v>328.43</v>
+        <v>2503.37</v>
       </c>
       <c r="AC2" t="n">
-        <v>332.26</v>
+        <v>2526.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>336.53</v>
+        <v>2553.27</v>
       </c>
       <c r="AE2" t="n">
-        <v>58.6</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Low VIX (13.89) | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.89) | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>697.9</v>
+        <v>50.6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>182</v>
+        <v>12.9</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.6</v>
+        <v>13.9</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>339.38</v>
+        <v>2567.11</v>
       </c>
       <c r="AN2" t="n">
-        <v>317.69</v>
+        <v>2437.4</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>ETERNAL operates in the Consumer Cyclical sector. With an estimated Market Cap of ₹301,936.91 Cr., a P/E ratio of 697.87, and YoY Revenue Growth of +182.0%, the company demonstrates strong institutional backing, solid operating profit margins (0.64%), and healthy Return on Equity (15.00%).</t>
+          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹103,261.27 Cr., a P/E ratio of 50.59, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 58.63 (Bullish Momentum Zone), while MACD Line (0.58) trades below Signal (2.11) with an expanding histogram (-1.53). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +18.80% above the 200-day DMA (₹276.94). Daily volatility envelope is bounded by ATR(14) of ₹8.69.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.92 (Bullish Momentum Zone), while MACD Line (38.75) trades above Signal (25.91) with an expanding histogram (+12.84). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.51% above the 200-day DMA (₹2303.83). Daily volatility envelope is bounded by ATR(14) of ₹65.36.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for ETERNAL. Current Market Price (₹328.00) is positioned above the 30-day DMA (₹325.84), 50-day DMA (₹322.23), and 200-day DMA (₹276.94). The price distance from 200 DMA is +18.80%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,500.00) is positioned above the 30-day DMA (₹2,392.22), 50-day DMA (₹2,408.54), and 200-day DMA (₹2,303.83). The price distance from 200 DMA is +8.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[328.0, 328.98, 329.97, 330.95, 331.94, 332.92]</t>
+          <t>[2500.0, 2507.5, 2515.0, 2522.5, 2530.0, 2537.5]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[328.0, 332.46, 334.88, 336.97, 338.89, 340.69]</t>
+          <t>[2500.0, 2533.65, 2551.98, 2567.79, 2582.29, 2595.96]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[328.0, 326.38, 326.28, 326.44, 326.72, 327.09]</t>
+          <t>[2500.0, 2487.89, 2487.27, 2488.54, 2490.78, 2493.65]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>338.67</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>44550</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>297</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>₹295.74 - ₹298.89</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>302.03</v>
-      </c>
-      <c r="I3" t="n">
-        <v>288.35</v>
-      </c>
-      <c r="J3" t="n">
-        <v>286.17</v>
-      </c>
-      <c r="K3" t="n">
-        <v>279.9</v>
-      </c>
-      <c r="L3" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="P3" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="R3" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T3" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="U3" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="V3" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="W3" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X3" t="n">
-        <v>289.16</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>306.21</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>306.21</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>287.57</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>296.95</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>299.65</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>302.3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>Vol Spike 2.8x | Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | Low VIX (13.89) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>-53.2</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>305.83</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>288.16</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹44,550.00 Cr., a P/E ratio of 10.58, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.80 (Bullish Momentum Zone), while MACD Line (0.91) trades above Signal (0.20) with an expanding histogram (+0.71). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.29% above the 200-day DMA (₹279.90). Daily volatility envelope is bounded by ATR(14) of ₹6.29.</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹297.00) is positioned above the 30-day DMA (₹288.35), 50-day DMA (₹286.17), and 200-day DMA (₹279.90). The price distance from 200 DMA is +6.29%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>[297.0, 297.89, 298.78, 299.67, 300.56, 301.45]</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>[297.0, 300.41, 302.34, 304.03, 305.59, 307.08]</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>[297.0, 296.01, 296.12, 296.41, 296.79, 297.24]</t>
-        </is>
-      </c>
-      <c r="AU3" t="n">
-        <v>306.21</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>MANKIND</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>103261.27</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>🔴 AVOID / HOLD</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>₹2486.93 - ₹2519.61</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>2552.29</v>
-      </c>
-      <c r="I4" t="n">
-        <v>2392.22</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2408.54</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2303.83</v>
-      </c>
-      <c r="L4" t="n">
-        <v>8.51</v>
-      </c>
-      <c r="M4" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="N4" t="n">
-        <v>25.91</v>
-      </c>
-      <c r="O4" t="n">
-        <v>12.84</v>
-      </c>
-      <c r="P4" t="n">
-        <v>65.36</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="R4" t="n">
-        <v>36</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-2.08</v>
-      </c>
-      <c r="U4" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="V4" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2413.41</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2714.22</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2714.22</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2401.95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>2503.37</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2526.64</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2553.27</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>70.90000000000001</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.89) | LSTM Deep Net</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>2560.85</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2431.89</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹103,261.27 Cr., a P/E ratio of 50.59, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.92 (Bullish Momentum Zone), while MACD Line (38.75) trades above Signal (25.91) with an expanding histogram (+12.84). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.51% above the 200-day DMA (₹2303.83). Daily volatility envelope is bounded by ATR(14) of ₹65.36.</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,500.00) is positioned above the 30-day DMA (₹2,392.22), 50-day DMA (₹2,408.54), and 200-day DMA (₹2,303.83). The price distance from 200 DMA is +8.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>[2500.0, 2507.5, 2515.0, 2522.5, 2530.0, 2537.5]</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>[2500.0, 2533.65, 2551.98, 2567.79, 2582.29, 2595.96]</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>[2500.0, 2487.89, 2487.27, 2488.54, 2490.78, 2493.65]</t>
-        </is>
-      </c>
-      <c r="AU4" t="n">
-        <v>2714.22</v>
+        <v>2321.1</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -656,21 +656,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>103261.27</v>
+        <v>43545</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,146 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2500</v>
+        <v>290.3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹2486.93 - ₹2519.61</t>
+          <t>₹289.04 - ₹292.19</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2552.29</v>
+        <v>295.33</v>
       </c>
       <c r="I2" t="n">
-        <v>2392.22</v>
+        <v>288.35</v>
       </c>
       <c r="J2" t="n">
-        <v>2408.54</v>
+        <v>286.17</v>
       </c>
       <c r="K2" t="n">
-        <v>2303.83</v>
+        <v>279.9</v>
       </c>
       <c r="L2" t="n">
-        <v>8.51</v>
+        <v>6.29</v>
       </c>
       <c r="M2" t="n">
-        <v>38.75</v>
+        <v>0.91</v>
       </c>
       <c r="N2" t="n">
-        <v>25.91</v>
+        <v>0.2</v>
       </c>
       <c r="O2" t="n">
-        <v>12.84</v>
+        <v>0.71</v>
       </c>
       <c r="P2" t="n">
-        <v>65.36</v>
+        <v>6.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.89</v>
+        <v>14.99</v>
       </c>
       <c r="R2" t="n">
-        <v>36</v>
+        <v>43.5</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="T2" t="n">
-        <v>-2.08</v>
+        <v>-1.49</v>
       </c>
       <c r="U2" t="n">
-        <v>42.6</v>
+        <v>56.7</v>
       </c>
       <c r="V2" t="n">
-        <v>7.56</v>
+        <v>6.61</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>2454.78</v>
+        <v>286.24</v>
       </c>
       <c r="Y2" t="n">
-        <v>2437.91</v>
+        <v>284.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>2321.1</v>
+        <v>284.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>2401.95</v>
+        <v>280.87</v>
       </c>
       <c r="AB2" t="n">
-        <v>2503.37</v>
+        <v>292.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>2526.64</v>
+        <v>295.01</v>
       </c>
       <c r="AD2" t="n">
-        <v>2553.27</v>
+        <v>299.73</v>
       </c>
       <c r="AE2" t="n">
-        <v>70.90000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | Strong RSI | Low VIX (13.89) | LSTM Deep Net</t>
+          <t>Vol Spike 2.8x | Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>50.6</v>
+        <v>10.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12.9</v>
+        <v>-53.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>13.9</v>
+        <v>11.3</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>2567.11</v>
+        <v>298.95</v>
       </c>
       <c r="AN2" t="n">
-        <v>2437.4</v>
+        <v>281.84</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>MANKIND operates in the Healthcare sector. With an estimated Market Cap of ₹103,261.27 Cr., a P/E ratio of 50.59, and YoY Revenue Growth of +12.9%, the company demonstrates strong institutional backing, solid operating profit margins (13.86%), and healthy Return on Equity (15.00%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,545.00 Cr., a P/E ratio of 10.35, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.92 (Bullish Momentum Zone), while MACD Line (38.75) trades above Signal (25.91) with an expanding histogram (+12.84). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +8.51% above the 200-day DMA (₹2303.83). Daily volatility envelope is bounded by ATR(14) of ₹65.36.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.80 (Bullish Momentum Zone), while MACD Line (0.91) trades above Signal (0.20) with an expanding histogram (+0.71). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.29% above the 200-day DMA (₹279.90). Daily volatility envelope is bounded by ATR(14) of ₹6.29.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for MANKIND. Current Market Price (₹2,500.00) is positioned above the 30-day DMA (₹2,392.22), 50-day DMA (₹2,408.54), and 200-day DMA (₹2,303.83). The price distance from 200 DMA is +8.51%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹290.30) is positioned above the 30-day DMA (₹288.35), 50-day DMA (₹286.17), and 200-day DMA (₹279.90). The price distance from 200 DMA is +6.29%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[2500.0, 2507.5, 2515.0, 2522.5, 2530.0, 2537.5]</t>
+          <t>[290.3, 291.17, 292.04, 292.91, 293.78, 294.65]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[2500.0, 2533.65, 2551.98, 2567.79, 2582.29, 2595.96]</t>
+          <t>[290.3, 293.69, 295.6, 297.27, 298.81, 300.28]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[2500.0, 2487.89, 2487.27, 2488.54, 2490.78, 2493.65]</t>
+          <t>[290.3, 289.29, 289.37, 289.65, 290.01, 290.44]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2321.1</v>
+        <v>284.3</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43545</v>
+        <v>43275</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,54 +678,54 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>290.3</v>
+        <v>288.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹289.04 - ₹292.19</t>
+          <t>₹287.26 - ₹290.36</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>295.33</v>
+        <v>293.45</v>
       </c>
       <c r="I2" t="n">
-        <v>288.35</v>
+        <v>288.5</v>
       </c>
       <c r="J2" t="n">
-        <v>286.17</v>
+        <v>286.56</v>
       </c>
       <c r="K2" t="n">
-        <v>279.9</v>
+        <v>280.03</v>
       </c>
       <c r="L2" t="n">
-        <v>6.29</v>
+        <v>6.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.91</v>
+        <v>1.54</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="O2" t="n">
-        <v>0.71</v>
+        <v>1.07</v>
       </c>
       <c r="P2" t="n">
-        <v>6.29</v>
+        <v>6.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.99</v>
+        <v>15.27</v>
       </c>
       <c r="R2" t="n">
-        <v>43.5</v>
+        <v>45.4</v>
       </c>
       <c r="S2" t="n">
         <v>0.25</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.49</v>
+        <v>-1.39</v>
       </c>
       <c r="U2" t="n">
-        <v>56.7</v>
+        <v>55.7</v>
       </c>
       <c r="V2" t="n">
         <v>6.61</v>
@@ -734,35 +734,35 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>286.24</v>
+        <v>288.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>284.3</v>
+        <v>286.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>284.3</v>
+        <v>282.54</v>
       </c>
       <c r="AA2" t="n">
-        <v>280.87</v>
+        <v>279.22</v>
       </c>
       <c r="AB2" t="n">
-        <v>292.23</v>
+        <v>291.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>295.01</v>
+        <v>294.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>299.73</v>
+        <v>300.1</v>
       </c>
       <c r="AE2" t="n">
-        <v>62.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Vol Spike 2.8x | Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | LSTM Deep Net</t>
+          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
@@ -781,43 +781,43 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>298.95</v>
+        <v>296.72</v>
       </c>
       <c r="AN2" t="n">
-        <v>281.84</v>
+        <v>280.32</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,545.00 Cr., a P/E ratio of 10.35, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,275.00 Cr., a P/E ratio of 10.28, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 62.80 (Bullish Momentum Zone), while MACD Line (0.91) trades above Signal (0.20) with an expanding histogram (+0.71). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.29% above the 200-day DMA (₹279.90). Daily volatility envelope is bounded by ATR(14) of ₹6.29.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.44 (Bullish Momentum Zone), while MACD Line (1.54) trades above Signal (0.47) with an expanding histogram (+1.07). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.06% above the 200-day DMA (₹280.03). Daily volatility envelope is bounded by ATR(14) of ₹6.19.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹290.30) is positioned above the 30-day DMA (₹288.35), 50-day DMA (₹286.17), and 200-day DMA (₹279.90). The price distance from 200 DMA is +6.29%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹288.50) is positioned above the 30-day DMA (₹288.50), 50-day DMA (₹286.56), and 200-day DMA (₹280.03). The price distance from 200 DMA is +6.06%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[290.3, 291.17, 292.04, 292.91, 293.78, 294.65]</t>
+          <t>[288.5, 289.37, 290.23, 291.1, 291.96, 292.83]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[290.3, 293.69, 295.6, 297.27, 298.81, 300.28]</t>
+          <t>[288.5, 291.84, 293.73, 295.38, 296.91, 298.36]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[290.3, 289.29, 289.37, 289.65, 290.01, 290.44]</t>
+          <t>[288.5, 287.51, 287.61, 287.88, 288.25, 288.68]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>284.3</v>
+        <v>282.54</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -689,58 +689,58 @@
         <v>293.45</v>
       </c>
       <c r="I2" t="n">
-        <v>288.5</v>
+        <v>288.68</v>
       </c>
       <c r="J2" t="n">
-        <v>286.56</v>
+        <v>286.37</v>
       </c>
       <c r="K2" t="n">
-        <v>280.03</v>
+        <v>279.76</v>
       </c>
       <c r="L2" t="n">
-        <v>6.06</v>
+        <v>6.16</v>
       </c>
       <c r="M2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="N2" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="O2" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="P2" t="n">
         <v>6.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>15.27</v>
+        <v>15.28</v>
       </c>
       <c r="R2" t="n">
-        <v>45.4</v>
+        <v>44.1</v>
       </c>
       <c r="S2" t="n">
         <v>0.25</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.39</v>
+        <v>-1.45</v>
       </c>
       <c r="U2" t="n">
-        <v>55.7</v>
+        <v>56.7</v>
       </c>
       <c r="V2" t="n">
-        <v>6.61</v>
+        <v>6.98</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>288.4</v>
+        <v>284.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>286.25</v>
+        <v>297.03</v>
       </c>
       <c r="Z2" t="n">
-        <v>282.54</v>
+        <v>296.94</v>
       </c>
       <c r="AA2" t="n">
         <v>279.22</v>
@@ -758,7 +758,7 @@
         <v>64.40000000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="AJ2" t="n">
         <v>-53.2</v>
@@ -781,24 +781,24 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>296.72</v>
+        <v>297.47</v>
       </c>
       <c r="AN2" t="n">
-        <v>280.32</v>
+        <v>280.16</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,275.00 Cr., a P/E ratio of 10.28, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,275.00 Cr., a P/E ratio of 10.58, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.44 (Bullish Momentum Zone), while MACD Line (1.54) trades above Signal (0.47) with an expanding histogram (+1.07). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.06% above the 200-day DMA (₹280.03). Daily volatility envelope is bounded by ATR(14) of ₹6.19.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.44 (Bullish Momentum Zone), while MACD Line (1.55) trades above Signal (0.51) with an expanding histogram (+1.04). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.16% above the 200-day DMA (₹279.76). Daily volatility envelope is bounded by ATR(14) of ₹6.19.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹288.50) is positioned above the 30-day DMA (₹288.50), 50-day DMA (₹286.56), and 200-day DMA (₹280.03). The price distance from 200 DMA is +6.06%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹288.50) is positioned above the 30-day DMA (₹288.68), 50-day DMA (₹286.37), and 200-day DMA (₹279.76). The price distance from 200 DMA is +6.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>282.54</v>
+        <v>296.94</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -656,7 +656,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -670,106 +670,106 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43275</v>
+        <v>43770</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>🔴 AVOID / HOLD</t>
+          <t>🟡 MODERATE BUY</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>288.5</v>
+        <v>291.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹287.26 - ₹290.36</t>
+          <t>₹290.48 - ₹293.78</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>293.45</v>
+        <v>297.08</v>
       </c>
       <c r="I2" t="n">
-        <v>288.68</v>
+        <v>288.54</v>
       </c>
       <c r="J2" t="n">
-        <v>286.37</v>
+        <v>286.58</v>
       </c>
       <c r="K2" t="n">
-        <v>279.76</v>
+        <v>279.89</v>
       </c>
       <c r="L2" t="n">
-        <v>6.16</v>
+        <v>3.08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="N2" t="n">
-        <v>0.51</v>
+        <v>0.68</v>
       </c>
       <c r="O2" t="n">
-        <v>1.04</v>
+        <v>0.67</v>
       </c>
       <c r="P2" t="n">
-        <v>6.19</v>
+        <v>6.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>15.28</v>
+        <v>14.63</v>
       </c>
       <c r="R2" t="n">
-        <v>44.1</v>
+        <v>48.7</v>
       </c>
       <c r="S2" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.45</v>
+        <v>-1.35</v>
       </c>
       <c r="U2" t="n">
         <v>56.7</v>
       </c>
       <c r="V2" t="n">
-        <v>6.98</v>
+        <v>6.9</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>284.03</v>
+        <v>285.14</v>
       </c>
       <c r="Y2" t="n">
-        <v>297.03</v>
+        <v>300.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>296.94</v>
+        <v>300.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>279.22</v>
+        <v>281.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>291.15</v>
+        <v>292.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>294.3</v>
+        <v>295.11</v>
       </c>
       <c r="AD2" t="n">
-        <v>300.1</v>
+        <v>298.43</v>
       </c>
       <c r="AE2" t="n">
-        <v>64.40000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Inst. Buying (CMF+) | TTM Squeeze | Strong RSI | LSTM Deep Net</t>
+          <t>TTM Squeeze | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="AJ2" t="n">
         <v>-53.2</v>
@@ -781,43 +781,43 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>297.47</v>
+        <v>300.93</v>
       </c>
       <c r="AN2" t="n">
-        <v>280.16</v>
+        <v>283.45</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,275.00 Cr., a P/E ratio of 10.58, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,770.00 Cr., a P/E ratio of 10.40, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 64.44 (Bullish Momentum Zone), while MACD Line (1.55) trades above Signal (0.51) with an expanding histogram (+1.04). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +6.16% above the 200-day DMA (₹279.76). Daily volatility envelope is bounded by ATR(14) of ₹6.19.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.30 (Consolidation Zone), while MACD Line (1.35) trades above Signal (0.68) with an expanding histogram (+0.67). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.08% above the 200-day DMA (₹279.89). Daily volatility envelope is bounded by ATR(14) of ₹6.60.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹288.50) is positioned above the 30-day DMA (₹288.68), 50-day DMA (₹286.37), and 200-day DMA (₹279.76). The price distance from 200 DMA is +6.16%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹291.80) is positioned above the 30-day DMA (₹288.54), 50-day DMA (₹286.58), and 200-day DMA (₹279.89). The price distance from 200 DMA is +3.08%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[288.5, 289.37, 290.23, 291.1, 291.96, 292.83]</t>
+          <t>[291.8, 292.68, 293.55, 294.43, 295.3, 296.18]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[288.5, 291.84, 293.73, 295.38, 296.91, 298.36]</t>
+          <t>[291.8, 295.31, 297.28, 299.0, 300.58, 302.08]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[288.5, 287.51, 287.61, 287.88, 288.25, 288.68]</t>
+          <t>[291.8, 290.7, 290.75, 291.0, 291.34, 291.75]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>296.94</v>
+        <v>300.33</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43770</v>
+        <v>43725</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,15 +678,15 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>291.8</v>
+        <v>291.5</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹290.48 - ₹293.78</t>
+          <t>₹290.18 - ₹293.48</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>297.08</v>
+        <v>296.78</v>
       </c>
       <c r="I2" t="n">
         <v>288.54</v>
@@ -713,16 +713,16 @@
         <v>6.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.63</v>
+        <v>14.38</v>
       </c>
       <c r="R2" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
       <c r="S2" t="n">
         <v>0.24</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.35</v>
+        <v>-1.36</v>
       </c>
       <c r="U2" t="n">
         <v>56.7</v>
@@ -734,25 +734,25 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>285.14</v>
+        <v>284.73</v>
       </c>
       <c r="Y2" t="n">
-        <v>300.33</v>
+        <v>300.03</v>
       </c>
       <c r="Z2" t="n">
-        <v>300.33</v>
+        <v>300.03</v>
       </c>
       <c r="AA2" t="n">
-        <v>281.91</v>
+        <v>281.61</v>
       </c>
       <c r="AB2" t="n">
-        <v>292.13</v>
+        <v>292.03</v>
       </c>
       <c r="AC2" t="n">
-        <v>295.11</v>
+        <v>294.91</v>
       </c>
       <c r="AD2" t="n">
-        <v>298.43</v>
+        <v>298.33</v>
       </c>
       <c r="AE2" t="n">
         <v>54.3</v>
@@ -781,14 +781,14 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>300.93</v>
+        <v>300.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>283.45</v>
+        <v>282.73</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,770.00 Cr., a P/E ratio of 10.40, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,725.00 Cr., a P/E ratio of 10.39, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -798,26 +798,26 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹291.80) is positioned above the 30-day DMA (₹288.54), 50-day DMA (₹286.58), and 200-day DMA (₹279.89). The price distance from 200 DMA is +3.08%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹291.50) is positioned above the 30-day DMA (₹288.54), 50-day DMA (₹286.58), and 200-day DMA (₹279.89). The price distance from 200 DMA is +3.08%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[291.8, 292.68, 293.55, 294.43, 295.3, 296.18]</t>
+          <t>[291.5, 292.37, 293.25, 294.12, 295.0, 295.87]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[291.8, 295.31, 297.28, 299.0, 300.58, 302.08]</t>
+          <t>[291.5, 295.01, 296.98, 298.69, 300.28, 301.77]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[291.8, 290.7, 290.75, 291.0, 291.34, 291.75]</t>
+          <t>[291.5, 290.4, 290.45, 290.7, 291.04, 291.45]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>300.33</v>
+        <v>300.03</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -716,7 +716,7 @@
         <v>14.38</v>
       </c>
       <c r="R2" t="n">
-        <v>48.4</v>
+        <v>45.6</v>
       </c>
       <c r="S2" t="n">
         <v>0.24</v>
@@ -734,13 +734,13 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>284.73</v>
+        <v>281.63</v>
       </c>
       <c r="Y2" t="n">
-        <v>300.03</v>
+        <v>287.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>300.03</v>
+        <v>282.54</v>
       </c>
       <c r="AA2" t="n">
         <v>281.61</v>
@@ -781,10 +781,10 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>300.1</v>
+        <v>299.68</v>
       </c>
       <c r="AN2" t="n">
-        <v>282.73</v>
+        <v>283.06</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>300.03</v>
+        <v>282.54</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -716,7 +716,7 @@
         <v>14.38</v>
       </c>
       <c r="R2" t="n">
-        <v>45.6</v>
+        <v>48.5</v>
       </c>
       <c r="S2" t="n">
         <v>0.24</v>
@@ -734,13 +734,13 @@
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>281.63</v>
+        <v>285.65</v>
       </c>
       <c r="Y2" t="n">
-        <v>287.22</v>
+        <v>303.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>282.54</v>
+        <v>303.15</v>
       </c>
       <c r="AA2" t="n">
         <v>281.61</v>
@@ -781,10 +781,10 @@
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>299.68</v>
+        <v>300.59</v>
       </c>
       <c r="AN2" t="n">
-        <v>283.06</v>
+        <v>282.38</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>282.54</v>
+        <v>303.15</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU2"/>
+  <dimension ref="A1:AU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,21 +656,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43725</v>
+        <v>438950.27</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -678,146 +678,313 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>291.5</v>
+        <v>441.25</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>₹290.18 - ₹293.48</t>
+          <t>₹439.08 - ₹444.51</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>296.78</v>
+        <v>449.95</v>
       </c>
       <c r="I2" t="n">
-        <v>288.54</v>
+        <v>418.75</v>
       </c>
       <c r="J2" t="n">
-        <v>286.58</v>
+        <v>409.47</v>
       </c>
       <c r="K2" t="n">
-        <v>279.89</v>
+        <v>399.46</v>
       </c>
       <c r="L2" t="n">
-        <v>3.08</v>
+        <v>10.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.35</v>
+        <v>6.58</v>
       </c>
       <c r="N2" t="n">
-        <v>0.68</v>
+        <v>3.73</v>
       </c>
       <c r="O2" t="n">
-        <v>0.67</v>
+        <v>2.85</v>
       </c>
       <c r="P2" t="n">
-        <v>6.6</v>
+        <v>10.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.38</v>
+        <v>15.35</v>
       </c>
       <c r="R2" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.36</v>
+        <v>-1.54</v>
       </c>
       <c r="U2" t="n">
-        <v>56.7</v>
+        <v>55.9</v>
       </c>
       <c r="V2" t="n">
-        <v>6.9</v>
+        <v>5.43</v>
       </c>
       <c r="W2" t="n">
         <v>-0.77</v>
       </c>
       <c r="X2" t="n">
-        <v>285.65</v>
+        <v>430.76</v>
       </c>
       <c r="Y2" t="n">
-        <v>303.15</v>
+        <v>450.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>303.15</v>
+        <v>450.22</v>
       </c>
       <c r="AA2" t="n">
-        <v>281.61</v>
+        <v>424.94</v>
       </c>
       <c r="AB2" t="n">
-        <v>292.03</v>
+        <v>441.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>294.91</v>
+        <v>443.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>298.33</v>
+        <v>446.02</v>
       </c>
       <c r="AE2" t="n">
-        <v>54.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>TTM Squeeze | LSTM Deep Net</t>
+          <t>Strong RSI | LSTM Deep Net</t>
         </is>
       </c>
       <c r="AH2" t="n">
         <v>0.15</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.4</v>
+        <v>21.6</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-53.2</v>
+        <v>21</v>
       </c>
       <c r="AK2" t="n">
-        <v>11.3</v>
+        <v>28.5</v>
       </c>
       <c r="AL2" t="n">
         <v>15</v>
       </c>
       <c r="AM2" t="n">
-        <v>300.59</v>
+        <v>450.71</v>
       </c>
       <c r="AN2" t="n">
-        <v>282.38</v>
+        <v>432.4</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,725.00 Cr., a P/E ratio of 10.39, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+          <t>KOTAKBANK operates in the Financial Services sector. With an estimated Market Cap of ₹438,950.27 Cr., a P/E ratio of 21.63, and YoY Revenue Growth of +21.0%, the company demonstrates strong institutional backing, solid operating profit margins (28.47%), and healthy Return on Equity (15.00%).</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 54.30 (Consolidation Zone), while MACD Line (1.35) trades above Signal (0.68) with an expanding histogram (+0.67). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +3.08% above the 200-day DMA (₹279.89). Daily volatility envelope is bounded by ATR(14) of ₹6.60.</t>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 70.10 (Bullish Momentum Zone), while MACD Line (6.58) trades above Signal (3.73) with an expanding histogram (+2.85). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +10.40% above the 200-day DMA (₹399.46). Daily volatility envelope is bounded by ATR(14) of ₹10.87.</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹291.50) is positioned above the 30-day DMA (₹288.54), 50-day DMA (₹286.58), and 200-day DMA (₹279.89). The price distance from 200 DMA is +3.08%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for KOTAKBANK. Current Market Price (₹441.25) is positioned above the 30-day DMA (₹418.75), 50-day DMA (₹409.47), and 200-day DMA (₹399.46). The price distance from 200 DMA is +10.40%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>[291.5, 292.37, 293.25, 294.12, 295.0, 295.87]</t>
+          <t>[441.25, 442.57, 443.9, 445.22, 446.55, 447.87]</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>[291.5, 295.01, 296.98, 298.69, 300.28, 301.77]</t>
+          <t>[441.25, 446.92, 450.05, 452.75, 455.24, 457.59]</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>[291.5, 290.4, 290.45, 290.7, 291.04, 291.45]</t>
+          <t>[441.25, 439.31, 439.29, 439.57, 440.02, 440.58]</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>303.15</v>
+        <v>450.22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PETRONET</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>43380.01</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>🔴 AVOID / HOLD</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>289.2</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>₹287.91 - ₹291.13</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>294.35</v>
+      </c>
+      <c r="I3" t="n">
+        <v>288.63</v>
+      </c>
+      <c r="J3" t="n">
+        <v>286.87</v>
+      </c>
+      <c r="K3" t="n">
+        <v>280.02</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="R3" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-1.48</v>
+      </c>
+      <c r="U3" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="V3" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="W3" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="X3" t="n">
+        <v>283.47</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>300.75</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>300.75</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>279.54</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>290.58</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>292.66</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>296.13</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>49</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>TTM Squeeze | LSTM Deep Net</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>-53.2</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>297.73</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>280.23</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>PETRONET operates in the Energy sector. With an estimated Market Cap of ₹43,380.01 Cr., a P/E ratio of 10.31, and YoY Revenue Growth of -53.2%, the company demonstrates strong institutional backing, solid operating profit margins (11.32%), and healthy Return on Equity (15.00%).</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>Technical indicators confirm a Positive CAR Super Breakout. RSI(14) is currently at 48.95 (Consolidation Zone), while MACD Line (1.41) trades above Signal (0.82) with an expanding histogram (+0.59). Moving Averages are aligned in perfect Golden Stack (CMP &gt; 30 DMA &gt; 50 DMA &gt; 200 DMA) with price trading +4.10% above the 200-day DMA (₹280.02). Daily volatility envelope is bounded by ATR(14) of ₹6.44.</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Initialization.py scanner logic confirms a CAR (Cumulative Average Return) Super Breakout for PETRONET. Current Market Price (₹289.20) is positioned above the 30-day DMA (₹288.63), 50-day DMA (₹286.87), and 200-day DMA (₹280.02). The price distance from 200 DMA is +4.10%, indicating a high-conviction institutional momentum stack across short, medium, and long-term trend horizons.</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>[289.2, 290.07, 290.94, 291.8, 292.67, 293.54]</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>[289.2, 292.64, 294.58, 296.26, 297.82, 299.3]</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>[289.2, 288.14, 288.2, 288.46, 288.81, 289.22]</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>300.75</v>
       </c>
     </row>
   </sheetData>

--- a/Breakout_ML_Quant_Predictions.xlsx
+++ b/Breakout_ML_Quant_Predictions.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU3"/>
+  <dimension ref="A1:AU4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,7 +656,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>438950.27</v>
+        <v>439696.36</v>
       </c>
     